--- a/results_test.xlsx
+++ b/results_test.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="160">
   <si>
     <t>seed</t>
   </si>
@@ -22,6 +22,9 @@
     <t>branching_strategy</t>
   </si>
   <si>
+    <t>search_strategy</t>
+  </si>
+  <si>
     <t>learn_type</t>
   </si>
   <si>
@@ -256,6 +259,18 @@
     <t>focus_avg_gap_days_per_patient</t>
   </si>
   <si>
+    <t>focus_DRG_E65A_count</t>
+  </si>
+  <si>
+    <t>focus_DRG_E65A_avg_los</t>
+  </si>
+  <si>
+    <t>focus_DRG_E65A_avg_req</t>
+  </si>
+  <si>
+    <t>focus_DRG_E65A_ai_share_pct</t>
+  </si>
+  <si>
     <t>focus_DRG_E65B_count</t>
   </si>
   <si>
@@ -388,97 +403,97 @@
     <t>post_continuity_violations_count</t>
   </si>
   <si>
-    <t>sp</t>
+    <t>mp</t>
+  </si>
+  <si>
+    <t>bfs</t>
   </si>
   <si>
     <t>sigmoid</t>
   </si>
   <si>
-    <t>[3, 1, 1]</t>
-  </si>
-  <si>
-    <t>{1: 1}</t>
-  </si>
-  <si>
-    <t>[1, 5, 6, 7, 8, 10, 12, 13, 14, 17, 18, 19, 27, 32, 33, 34, 35, 42, 44, 45, 46, 48, 49, 51, 52, 54, 55, 56, 57, 58, 61, 64, 68, 69, 72, 74, 76, 80]</t>
-  </si>
-  <si>
-    <t>[11, 29, 47, 53]</t>
-  </si>
-  <si>
-    <t>[2, 3, 4, 9, 15, 16, 20, 21, 22, 23, 24, 25, 26, 28, 30, 31, 36, 37, 38, 39, 40, 41, 43, 50, 59, 60, 62, 63, 65, 66, 67, 70, 71, 73, 75, 77, 78, 79, 81, 82]</t>
-  </si>
-  <si>
-    <t>[2, 3, 4, 9, 11, 15, 16, 20, 21, 22, 23, 24, 25, 26, 28, 29, 30, 31, 36, 37, 38, 39, 40, 41, 43, 47, 50, 53, 59, 60, 62, 63, 65, 66, 67, 70, 71, 73, 75, 77, 78, 79, 81, 82]</t>
-  </si>
-  <si>
-    <t>{1: 1, 2: 1, 3: 1, 4: 1, 5: 1, 6: 1, 7: 1, 8: 1, 9: 1, 10: 1, 11: 1, 12: 1, 13: 1, 14: 2, 15: 1, 16: 1, 17: 1, 18: 1, 19: 1, 20: 1, 21: 1, 22: 1, 23: 1, 24: 1, 25: 1, 26: 1, 27: 1, 28: 1, 29: 1, 30: 1, 31: 1, 32: 1, 33: 1, 34: 1, 35: 1, 36: 1, 37: 2, 38: 1, 39: 1, 40: 1, 41: 1, 42: 2, 43: 1, 44: 1, 45: 1, 46: 1, 47: 1, 48: 1, 49: 1, 50: 1, 51: 1, 52: 1, 53: 1, 54: 1, 55: 1, 56: 1, 57: 1, 58: 1, 59: 1, 60: 1, 61: 1, 62: 1, 63: 1, 64: 1, 65: 1, 66: 1, 67: 1, 68: 1, 69: 1, 70: 1, 71: 1, 72: 1, 73: 1, 74: 1, 75: 1, 76: 1, 77: 1, 78: 1, 79: 1, 80: 1, 81: 1, 82: 1}</t>
-  </si>
-  <si>
-    <t>{2: 0, 3: 0, 4: 0, 9: 0, 11: 1, 15: 0, 16: 0, 20: 0, 21: 0, 22: 0, 23: 0, 24: 0, 25: 0, 26: 0, 28: 0, 29: 1, 30: 0, 31: 0, 36: 0, 37: 0, 38: 0, 39: 0, 40: 0, 41: 0, 43: 0, 47: 1, 50: 0, 53: 1, 59: 0, 60: 0, 62: 0, 63: 0, 65: 0, 66: 0, 67: 0, 70: 0, 71: 0, 73: 0, 75: 0, 77: 0, 78: 0, 79: 0, 81: 0, 82: 0}</t>
-  </si>
-  <si>
-    <t>{(1, -36): 4, (1, -35): 0, (1, -34): 4, (1, -33): 4, (1, -32): 4, (1, -31): 4, (1, -30): 4, (1, -29): 4, (1, -28): 0, (1, -27): 4, (1, -26): 4, (1, -25): 4, (1, -24): 4, (1, -23): 4, (1, -22): 4, (1, -21): 0, (1, -20): 4, (1, -19): 4, (1, -18): 4, (1, -17): 4, (1, -16): 4, (1, -15): 4, (1, -14): 0, (1, -13): 4, (1, -12): 4, (1, -11): 4, (1, -10): 4, (1, -9): 4, (1, -8): 4, (1, -7): 0, (1, -6): 4, (1, -5): 4, (1, -4): 4, (1, -3): 4, (1, -2): 4, (1, -1): 4, (1, 0): 0, (1, 1): 4, (1, 2): 4, (1, 3): 4, (1, 4): 4, (1, 5): 4, (1, 6): 4, (1, 7): 0, (1, 8): 4, (1, 9): 4, (1, 10): 4, (1, 11): 4, (1, 12): 4, (1, 13): 4, (1, 14): 0, (1, 15): 4, (1, 16): 4, (1, 17): 4, (1, 18): 4, (1, 19): 4, (1, 20): 4, (1, 21): 0, (1, 22): 4, (1, 23): 4, (1, 24): 4, (1, 25): 4, (1, 26): 4, (1, 27): 4, (1, 28): 0, (1, 29): 4, (1, 30): 4, (1, 31): 4, (1, 32): 4, (1, 33): 4, (1, 34): 4, (1, 35): 0, (1, 36): 4, (1, 37): 4, (1, 38): 4, (1, 39): 4, (1, 40): 4, (1, 41): 4, (1, 42): 0, (2, -36): 4, (2, -35): 4, (2, -34): 0, (2, -33): 4, (2, -32): 4, (2, -31): 4, (2, -30): 4, (2, -29): 4, (2, -28): 4, (2, -27): 0, (2, -26): 4, (2, -25): 4, (2, -24): 4, (2, -23): 4, (2, -22): 4, (2, -21): 4, (2, -20): 0, (2, -19): 4, (2, -18): 4, (2, -17): 4, (2, -16): 4, (2, -15): 4, (2, -14): 4, (2, -13): 0, (2, -12): 4, (2, -11): 4, (2, -10): 4, (2, -9): 4, (2, -8): 4, (2, -7): 4, (2, -6): 0, (2, -5): 4, (2, -4): 4, (2, -3): 4, (2, -2): 4, (2, -1): 4, (2, 0): 4, (2, 1): 0, (2, 2): 4, (2, 3): 4, (2, 4): 4, (2, 5): 4, (2, 6): 4, (2, 7): 4, (2, 8): 0, (2, 9): 4, (2, 10): 4, (2, 11): 4, (2, 12): 4, (2, 13): 4, (2, 14): 4, (2, 15): 0, (2, 16): 4, (2, 17): 4, (2, 18): 4, (2, 19): 4, (2, 20): 4, (2, 21): 4, (2, 22): 0, (2, 23): 4, (2, 24): 4, (2, 25): 4, (2, 26): 4, (2, 27): 4, (2, 28): 4, (2, 29): 0, (2, 30): 4, (2, 31): 4, (2, 32): 4, (2, 33): 4, (2, 34): 4, (2, 35): 4, (2, 36): 0, (2, 37): 4, (2, 38): 4, (2, 39): 4, (2, 40): 4, (2, 41): 4, (2, 42): 4, (3, -36): 4, (3, -35): 4, (3, -34): 4, (3, -33): 0, (3, -32): 4, (3, -31): 4, (3, -30): 4, (3, -29): 4, (3, -28): 4, (3, -27): 4, (3, -26): 0, (3, -25): 4, (3, -24): 4, (3, -23): 4, (3, -22): 4, (3, -21): 4, (3, -20): 4, (3, -19): 0, (3, -18): 4, (3, -17): 4, (3, -16): 4, (3, -15): 4, (3, -14): 4, (3, -13): 4, (3, -12): 0, (3, -11): 4, (3, -10): 4, (3, -9): 4, (3, -8): 4, (3, -7): 4, (3, -6): 4, (3, -5): 0, (3, -4): 4, (3, -3): 4, (3, -2): 4, (3, -1): 4, (3, 0): 4, (3, 1): 4, (3, 2): 0, (3, 3): 4, (3, 4): 4, (3, 5): 4, (3, 6): 4, (3, 7): 4, (3, 8): 4, (3, 9): 0, (3, 10): 4, (3, 11): 4, (3, 12): 4, (3, 13): 4, (3, 14): 4, (3, 15): 4, (3, 16): 0, (3, 17): 4, (3, 18): 4, (3, 19): 4, (3, 20): 4, (3, 21): 4, (3, 22): 4, (3, 23): 0, (3, 24): 4, (3, 25): 4, (3, 26): 4, (3, 27): 4, (3, 28): 4, (3, 29): 4, (3, 30): 0, (3, 31): 4, (3, 32): 4, (3, 33): 4, (3, 34): 4, (3, 35): 4, (3, 36): 4, (3, 37): 0, (3, 38): 4, (3, 39): 4, (3, 40): 4, (3, 41): 4, (3, 42): 4}</t>
-  </si>
-  <si>
-    <t>{1: 12, 2: 22, 3: 16, 4: 20, 5: 13, 6: 9, 7: 13, 8: 11, 9: 14, 10: 5, 11: 5, 12: 4, 13: 9, 14: 7, 15: 11, 16: 8, 17: 8, 18: 9, 19: 7, 20: 5, 21: 12, 22: 11, 23: 5, 24: 7, 25: 8, 26: 4, 27: 7, 28: 10, 29: 3, 30: 7, 31: 12, 32: 4, 33: 5, 34: 3, 35: 5, 36: 9, 37: 6, 38: 4, 39: 6, 40: 7, 41: 5, 42: 10, 43: 7, 44: 5, 45: 2, 46: 4, 47: 7, 48: 8, 49: 5, 50: 5, 51: 4, 52: 4, 53: 4, 54: 7, 55: 4, 56: 7, 57: 8, 58: 3, 59: 8, 60: 6, 61: 7, 62: 5, 63: 11, 64: 7, 65: 4, 66: 3, 67: 5, 68: 4, 69: 5, 70: 3, 71: 7, 72: 5, 73: 9, 74: 5, 75: 6, 76: 6, 77: 8, 78: 7, 79: 4, 80: 7, 81: 4, 82: 5}</t>
-  </si>
-  <si>
-    <t>{1: -16, 2: 17, 3: 17, 4: 30, 5: -22, 6: -18, 7: -25, 8: -18, 9: 22, 10: -26, 11: 5, 12: -19, 13: -13, 14: -3, 15: 30, 16: 11, 17: -35, 18: -15, 19: -25, 20: 32, 21: 27, 22: 27, 23: 29, 24: 22, 25: 38, 26: 26, 27: -16, 28: 30, 29: 2, 30: 23, 31: 8, 32: -3, 33: -8, 34: -11, 35: -27, 36: 28, 37: 26, 38: 41, 39: 18, 40: 8, 41: 23, 42: -25, 43: 17, 44: -2, 45: -23, 46: -20, 47: 5, 48: -17, 49: 0, 50: 11, 51: -5, 52: -26, 53: 2, 54: -18, 55: -18, 56: -20, 57: -7, 58: -31, 59: 15, 60: 38, 61: -5, 62: 20, 63: 37, 64: -33, 65: 27, 66: 30, 67: 14, 68: -24, 69: -4, 70: 32, 71: 33, 72: -20, 73: 31, 74: -6, 75: 20, 76: -25, 77: 40, 78: 11, 79: 20, 80: -19, 81: 12, 82: 9}</t>
-  </si>
-  <si>
-    <t>{(1, 1, -16): 1, (1, 1, -15): 1, (1, 1, -13): 1, (1, 1, -10): 1, (1, 1, -8): 1, (1, 1, -5): 1, (1, 1, -3): 1, (1, 1, 1): 1, (5, 2, -22): 1, (5, 2, -21): 1, (5, 2, -19): 1, (5, 2, -16): 1, (5, 2, -14): 1, (5, 2, -11): 1, (5, 2, -9): 1, (5, 2, -5): 1, (6, 3, -18): 1, (6, 3, -17): 1, (6, 3, -16): 1, (6, 3, -15): 1, (6, 3, -11): 1, (6, 3, -10): 1, (6, 3, -7): 1, (7, 3, -25): 1, (7, 3, -24): 1, (7, 3, -23): 1, (7, 3, -22): 1, (7, 3, -18): 1, (7, 3, -17): 1, (7, 3, -13): 1, (7, 3, -11): 1, (7, 3, -8): 1, (8, 1, -18): 1, (8, 1, -17): 1, (8, 1, -16): 1, (8, 1, -15): 1, (8, 1, -11): 1, (8, 1, -10): 1, (8, 1, -6): 1, (8, 1, -5): 1, (10, 2, -26): 1, (10, 2, -25): 1, (10, 2, -24): 1, (10, 2, -23): 1, (10, 2, -21): 1, (12, 2, -19): 1, (12, 2, -18): 1, (12, 2, -17): 1, (12, 2, -16): 1, (13, 1, -13): 1, (13, 1, -12): 1, (13, 1, -11): 1, (13, 1, -10): 1, (13, 1, -6): 1, (13, 1, -5): 1, (13, 1, -2): 1, (14, 3, -3): 2, (14, 3, -2): 2, (14, 3, -1): 2, (14, 3, 0): 2, (14, 3, 4): 2, (14, 3, 5): 2, (17, 2, -35): 1, (17, 2, -33): 1, (17, 2, -32): 1, (17, 2, -28): 1, (17, 2, -26): 1, (17, 2, -25): 1, (18, 1, -15): 1, (18, 1, -13): 1, (18, 1, -12): 1, (18, 1, -8): 1, (18, 1, -6): 1, (18, 1, -3): 1, (19, 2, -25): 1, (19, 2, -24): 1, (19, 2, -23): 1, (19, 2, -22): 1, (19, 2, -18): 1, (19, 2, -17): 1, (27, 3, -16): 1, (27, 3, -15): 1, (27, 3, -14): 1, (27, 3, -13): 1, (27, 3, -9): 1, (27, 3, -8): 1, (32, 1, -3): 1, (32, 1, -2): 1, (32, 1, -1): 1, (32, 1, 1): 1, (33, 2, -8): 1, (33, 2, -7): 1, (33, 2, -5): 1, (33, 2, -2): 1, (34, 1, -11): 1, (34, 1, -10): 1, (34, 1, -9): 1, (35, 3, -27): 1, (35, 3, -25): 1, (35, 3, -24): 1, (35, 3, -21): 1, (42, 1, -25): 2, (42, 1, -24): 2, (42, 1, -23): 2, (42, 1, -22): 2, (42, 1, -18): 2, (42, 1, -17): 2, (42, 1, -12): 2, (44, 2, -2): 1, (44, 2, -1): 1, (44, 2, 0): 1, (44, 2, 4): 1, (45, 2, -23): 1, (45, 2, -22): 1, (46, 3, -20): 1, (46, 3, -18): 1, (46, 3, -17): 1, (46, 3, -16): 1, (48, 2, -17): 1, (48, 2, -16): 1, (48, 2, -15): 1, (48, 2, -14): 1, (48, 2, -10): 1, (48, 2, -9): 1, (48, 2, -8): 1, (49, 3, 0): 1, (49, 3, 1): 1, (49, 3, 3): 1, (49, 3, 6): 1, (51, 2, -5): 1, (51, 2, -4): 1, (51, 2, -3): 1, (51, 2, -2): 1, (52, 1, -26): 1, (52, 1, -25): 1, (52, 1, -24): 1, (52, 1, -23): 1, (54, 3, -18): 1, (54, 3, -17): 1, (54, 3, -16): 1, (54, 3, -15): 1, (54, 3, -11): 1, (54, 3, -10): 1, (55, 2, -18): 1, (55, 2, -17): 1, (55, 2, -16): 1, (55, 2, -15): 1, (56, 3, -20): 1, (56, 3, -15): 1, (56, 3, -14): 1, (56, 3, -10): 1, (57, 2, -7): 1, (57, 2, -5): 1, (57, 2, -4): 1, (57, 2, 0): 1, (57, 2, 2): 1, (57, 2, 3): 1, (58, 1, -31): 1, (58, 1, -30): 1, (58, 1, -29): 1, (61, 1, -5): 1, (61, 1, -4): 1, (61, 1, -3): 1, (61, 1, -2): 1, (61, 1, 2): 1, (61, 1, 3): 1, (64, 2, -33): 1, (64, 2, -32): 1, (64, 2, -31): 1, (64, 2, -30): 1, (64, 2, -26): 1, (64, 2, -25): 1, (68, 3, -24): 1, (68, 3, -23): 1, (68, 3, -22): 1, (68, 3, -21): 1, (69, 3, -4): 1, (69, 3, -3): 1, (69, 3, -2): 1, (69, 3, -1): 1, (69, 3, 1): 1, (72, 1, -20): 1, (72, 1, -19): 1, (72, 1, -18): 1, (72, 1, -17): 1, (72, 1, -15): 1, (74, 3, -6): 1, (74, 3, -4): 1, (74, 3, -3): 1, (74, 3, 0): 1, (76, 1, -25): 1, (76, 1, -24): 1, (76, 1, -23): 1, (76, 1, -22): 1, (76, 1, -16): 1, (80, 2, -19): 1, (80, 2, -18): 1, (80, 2, -14): 1, (80, 2, -12): 1, (80, 2, -10): 1}</t>
-  </si>
-  <si>
-    <t>{1: 18, 5: 18, 6: 12, 7: 18, 8: 14, 10: 6, 12: 4, 13: 12, 14: 9, 17: 11, 18: 13, 19: 9, 27: 9, 32: 5, 33: 7, 34: 3, 35: 7, 42: 14, 44: 7, 45: 2, 46: 5, 48: 10, 49: 7, 51: 4, 52: 4, 54: 9, 55: 4, 56: 11, 57: 11, 58: 3, 61: 9, 64: 9, 68: 4, 69: 6, 72: 6, 74: 7, 76: 10, 80: 10}</t>
-  </si>
-  <si>
-    <t>{(11, 1, 1): 0, (11, 1, 2): 0, (11, 1, 3): 0, (11, 1, 4): 0, (11, 1, 5): 0, (11, 1, 6): 0, (11, 1, 7): 0, (11, 1, 8): 0, (11, 1, 9): 0, (11, 1, 10): 0, (11, 1, 11): 0, (11, 1, 12): 0, (11, 1, 13): 0, (11, 1, 14): 0, (11, 1, 15): 0, (11, 1, 16): 0, (11, 1, 17): 0, (11, 1, 18): 0, (11, 1, 19): 0, (11, 1, 20): 0, (11, 1, 21): 0, (11, 1, 22): 0, (11, 1, 23): 0, (11, 1, 24): 0, (11, 1, 25): 0, (11, 1, 26): 0, (11, 1, 27): 0, (11, 1, 28): 0, (11, 1, 29): 0, (11, 1, 30): 0, (11, 1, 31): 0, (11, 1, 32): 0, (11, 1, 33): 0, (11, 1, 34): 0, (11, 1, 35): 0, (11, 1, 36): 0, (11, 1, 37): 0, (11, 1, 38): 0, (11, 1, 39): 0, (11, 1, 40): 0, (11, 1, 41): 0, (11, 1, 42): 0, (11, 2, 1): 0, (11, 2, 2): 0, (11, 2, 3): 0, (11, 2, 4): 0, (11, 2, 5): 1, (11, 2, 6): 1, (11, 2, 7): 1, (11, 2, 8): 0, (11, 2, 9): 1, (11, 2, 10): 1, (11, 2, 11): 0, (11, 2, 12): 0, (11, 2, 13): 0, (11, 2, 14): 0, (11, 2, 15): 0, (11, 2, 16): 0, (11, 2, 17): 0, (11, 2, 18): 0, (11, 2, 19): 0, (11, 2, 20): 0, (11, 2, 21): 0, (11, 2, 22): 0, (11, 2, 23): 0, (11, 2, 24): 0, (11, 2, 25): 0, (11, 2, 26): 0, (11, 2, 27): 0, (11, 2, 28): 0, (11, 2, 29): 0, (11, 2, 30): 0, (11, 2, 31): 0, (11, 2, 32): 0, (11, 2, 33): 0, (11, 2, 34): 0, (11, 2, 35): 0, (11, 2, 36): 0, (11, 2, 37): 0, (11, 2, 38): 0, (11, 2, 39): 0, (11, 2, 40): 0, (11, 2, 41): 0, (11, 2, 42): 0, (11, 3, 1): 0, (11, 3, 2): 0, (11, 3, 3): 0, (11, 3, 4): 0, (11, 3, 5): 0, (11, 3, 6): 0, (11, 3, 7): 0, (11, 3, 8): 0, (11, 3, 9): 0, (11, 3, 10): 0, (11, 3, 11): 0, (11, 3, 12): 0, (11, 3, 13): 0, (11, 3, 14): 0, (11, 3, 15): 0, (11, 3, 16): 0, (11, 3, 17): 0, (11, 3, 18): 0, (11, 3, 19): 0, (11, 3, 20): 0, (11, 3, 21): 0, (11, 3, 22): 0, (11, 3, 23): 0, (11, 3, 24): 0, (11, 3, 25): 0, (11, 3, 26): 0, (11, 3, 27): 0, (11, 3, 28): 0, (11, 3, 29): 0, (11, 3, 30): 0, (11, 3, 31): 0, (11, 3, 32): 0, (11, 3, 33): 0, (11, 3, 34): 0, (11, 3, 35): 0, (11, 3, 36): 0, (11, 3, 37): 0, (11, 3, 38): 0, (11, 3, 39): 0, (11, 3, 40): 0, (11, 3, 41): 0, (11, 3, 42): 0, (29, 1, 1): 0, (29, 1, 2): 0, (29, 1, 3): 0, (29, 1, 4): 0, (29, 1, 5): 0, (29, 1, 6): 0, (29, 1, 7): 0, (29, 1, 8): 0, (29, 1, 9): 0, (29, 1, 10): 0, (29, 1, 11): 0, (29, 1, 12): 0, (29, 1, 13): 0, (29, 1, 14): 0, (29, 1, 15): 0, (29, 1, 16): 0, (29, 1, 17): 0, (29, 1, 18): 0, (29, 1, 19): 0, (29, 1, 20): 0, (29, 1, 21): 0, (29, 1, 22): 0, (29, 1, 23): 0, (29, 1, 24): 0, (29, 1, 25): 0, (29, 1, 26): 0, (29, 1, 27): 0, (29, 1, 28): 0, (29, 1, 29): 0, (29, 1, 30): 0, (29, 1, 31): 0, (29, 1, 32): 0, (29, 1, 33): 0, (29, 1, 34): 0, (29, 1, 35): 0, (29, 1, 36): 0, (29, 1, 37): 0, (29, 1, 38): 0, (29, 1, 39): 0, (29, 1, 40): 0, (29, 1, 41): 0, (29, 1, 42): 0, (29, 2, 1): 0, (29, 2, 2): 1, (29, 2, 3): 1, (29, 2, 4): 1, (29, 2, 5): 0, (29, 2, 6): 0, (29, 2, 7): 0, (29, 2, 8): 0, (29, 2, 9): 0, (29, 2, 10): 0, (29, 2, 11): 0, (29, 2, 12): 0, (29, 2, 13): 0, (29, 2, 14): 0, (29, 2, 15): 0, (29, 2, 16): 0, (29, 2, 17): 0, (29, 2, 18): 0, (29, 2, 19): 0, (29, 2, 20): 0, (29, 2, 21): 0, (29, 2, 22): 0, (29, 2, 23): 0, (29, 2, 24): 0, (29, 2, 25): 0, (29, 2, 26): 0, (29, 2, 27): 0, (29, 2, 28): 0, (29, 2, 29): 0, (29, 2, 30): 0, (29, 2, 31): 0, (29, 2, 32): 0, (29, 2, 33): 0, (29, 2, 34): 0, (29, 2, 35): 0, (29, 2, 36): 0, (29, 2, 37): 0, (29, 2, 38): 0, (29, 2, 39): 0, (29, 2, 40): 0, (29, 2, 41): 0, (29, 2, 42): 0, (29, 3, 1): 0, (29, 3, 2): 0, (29, 3, 3): 0, (29, 3, 4): 0, (29, 3, 5): 0, (29, 3, 6): 0, (29, 3, 7): 0, (29, 3, 8): 0, (29, 3, 9): 0, (29, 3, 10): 0, (29, 3, 11): 0, (29, 3, 12): 0, (29, 3, 13): 0, (29, 3, 14): 0, (29, 3, 15): 0, (29, 3, 16): 0, (29, 3, 17): 0, (29, 3, 18): 0, (29, 3, 19): 0, (29, 3, 20): 0, (29, 3, 21): 0, (29, 3, 22): 0, (29, 3, 23): 0, (29, 3, 24): 0, (29, 3, 25): 0, (29, 3, 26): 0, (29, 3, 27): 0, (29, 3, 28): 0, (29, 3, 29): 0, (29, 3, 30): 0, (29, 3, 31): 0, (29, 3, 32): 0, (29, 3, 33): 0, (29, 3, 34): 0, (29, 3, 35): 0, (29, 3, 36): 0, (29, 3, 37): 0, (29, 3, 38): 0, (29, 3, 39): 0, (29, 3, 40): 0, (29, 3, 41): 0, (29, 3, 42): 0, (47, 1, 1): 0, (47, 1, 2): 0, (47, 1, 3): 0, (47, 1, 4): 0, (47, 1, 5): 1, (47, 1, 6): 1, (47, 1, 7): 0, (47, 1, 8): 1, (47, 1, 9): 1, (47, 1, 10): 1, (47, 1, 11): 1, (47, 1, 12): 1, (47, 1, 13): 0, (47, 1, 14): 0, (47, 1, 15): 0, (47, 1, 16): 0, (47, 1, 17): 0, (47, 1, 18): 0, (47, 1, 19): 0, (47, 1, 20): 0, (47, 1, 21): 0, (47, 1, 22): 0, (47, 1, 23): 0, (47, 1, 24): 0, (47, 1, 25): 0, (47, 1, 26): 0, (47, 1, 27): 0, (47, 1, 28): 0, (47, 1, 29): 0, (47, 1, 30): 0, (47, 1, 31): 0, (47, 1, 32): 0, (47, 1, 33): 0, (47, 1, 34): 0, (47, 1, 35): 0, (47, 1, 36): 0, (47, 1, 37): 0, (47, 1, 38): 0, (47, 1, 39): 0, (47, 1, 40): 0, (47, 1, 41): 0, (47, 1, 42): 0, (47, 2, 1): 0, (47, 2, 2): 0, (47, 2, 3): 0, (47, 2, 4): 0, (47, 2, 5): 0, (47, 2, 6): 0, (47, 2, 7): 0, (47, 2, 8): 0, (47, 2, 9): 0, (47, 2, 10): 0, (47, 2, 11): 0, (47, 2, 12): 0, (47, 2, 13): 0, (47, 2, 14): 0, (47, 2, 15): 0, (47, 2, 16): 0, (47, 2, 17): 0, (47, 2, 18): 0, (47, 2, 19): 0, (47, 2, 20): 0, (47, 2, 21): 0, (47, 2, 22): 0, (47, 2, 23): 0, (47, 2, 24): 0, (47, 2, 25): 0, (47, 2, 26): 0, (47, 2, 27): 0, (47, 2, 28): 0, (47, 2, 29): 0, (47, 2, 30): 0, (47, 2, 31): 0, (47, 2, 32): 0, (47, 2, 33): 0, (47, 2, 34): 0, (47, 2, 35): 0, (47, 2, 36): 0, (47, 2, 37): 0, (47, 2, 38): 0, (47, 2, 39): 0, (47, 2, 40): 0, (47, 2, 41): 0, (47, 2, 42): 0, (47, 3, 1): 0, (47, 3, 2): 0, (47, 3, 3): 0, (47, 3, 4): 0, (47, 3, 5): 0, (47, 3, 6): 0, (47, 3, 7): 0, (47, 3, 8): 0, (47, 3, 9): 0, (47, 3, 10): 0, (47, 3, 11): 0, (47, 3, 12): 0, (47, 3, 13): 0, (47, 3, 14): 0, (47, 3, 15): 0, (47, 3, 16): 0, (47, 3, 17): 0, (47, 3, 18): 0, (47, 3, 19): 0, (47, 3, 20): 0, (47, 3, 21): 0, (47, 3, 22): 0, (47, 3, 23): 0, (47, 3, 24): 0, (47, 3, 25): 0, (47, 3, 26): 0, (47, 3, 27): 0, (47, 3, 28): 0, (47, 3, 29): 0, (47, 3, 30): 0, (47, 3, 31): 0, (47, 3, 32): 0, (47, 3, 33): 0, (47, 3, 34): 0, (47, 3, 35): 0, (47, 3, 36): 0, (47, 3, 37): 0, (47, 3, 38): 0, (47, 3, 39): 0, (47, 3, 40): 0, (47, 3, 41): 0, (47, 3, 42): 0, (53, 1, 1): 0, (53, 1, 2): 1, (53, 1, 3): 1, (53, 1, 4): 1, (53, 1, 5): 1, (53, 1, 6): 0, (53, 1, 7): 0, (53, 1, 8): 0, (53, 1, 9): 0, (53, 1, 10): 0, (53, 1, 11): 0, (53, 1, 12): 0, (53, 1, 13): 0, (53, 1, 14): 0, (53, 1, 15): 0, (53, 1, 16): 0, (53, 1, 17): 0, (53, 1, 18): 0, (53, 1, 19): 0, (53, 1, 20): 0, (53, 1, 21): 0, (53, 1, 22): 0, (53, 1, 23): 0, (53, 1, 24): 0, (53, 1, 25): 0, (53, 1, 26): 0, (53, 1, 27): 0, (53, 1, 28): 0, (53, 1, 29): 0, (53, 1, 30): 0, (53, 1, 31): 0, (53, 1, 32): 0, (53, 1, 33): 0, (53, 1, 34): 0, (53, 1, 35): 0, (53, 1, 36): 0, (53, 1, 37): 0, (53, 1, 38): 0, (53, 1, 39): 0, (53, 1, 40): 0, (53, 1, 41): 0, (53, 1, 42): 0, (53, 2, 1): 0, (53, 2, 2): 0, (53, 2, 3): 0, (53, 2, 4): 0, (53, 2, 5): 0, (53, 2, 6): 0, (53, 2, 7): 0, (53, 2, 8): 0, (53, 2, 9): 0, (53, 2, 10): 0, (53, 2, 11): 0, (53, 2, 12): 0, (53, 2, 13): 0, (53, 2, 14): 0, (53, 2, 15): 0, (53, 2, 16): 0, (53, 2, 17): 0, (53, 2, 18): 0, (53, 2, 19): 0, (53, 2, 20): 0, (53, 2, 21): 0, (53, 2, 22): 0, (53, 2, 23): 0, (53, 2, 24): 0, (53, 2, 25): 0, (53, 2, 26): 0, (53, 2, 27): 0, (53, 2, 28): 0, (53, 2, 29): 0, (53, 2, 30): 0, (53, 2, 31): 0, (53, 2, 32): 0, (53, 2, 33): 0, (53, 2, 34): 0, (53, 2, 35): 0, (53, 2, 36): 0, (53, 2, 37): 0, (53, 2, 38): 0, (53, 2, 39): 0, (53, 2, 40): 0, (53, 2, 41): 0, (53, 2, 42): 0, (53, 3, 1): 0, (53, 3, 2): 0, (53, 3, 3): 0, (53, 3, 4): 0, (53, 3, 5): 0, (53, 3, 6): 0, (53, 3, 7): 0, (53, 3, 8): 0, (53, 3, 9): 0, (53, 3, 10): 0, (53, 3, 11): 0, (53, 3, 12): 0, (53, 3, 13): 0, (53, 3, 14): 0, (53, 3, 15): 0, (53, 3, 16): 0, (53, 3, 17): 0, (53, 3, 18): 0, (53, 3, 19): 0, (53, 3, 20): 0, (53, 3, 21): 0, (53, 3, 22): 0, (53, 3, 23): 0, (53, 3, 24): 0, (53, 3, 25): 0, (53, 3, 26): 0, (53, 3, 27): 0, (53, 3, 28): 0, (53, 3, 29): 0, (53, 3, 30): 0, (53, 3, 31): 0, (53, 3, 32): 0, (53, 3, 33): 0, (53, 3, 34): 0, (53, 3, 35): 0, (53, 3, 36): 0, (53, 3, 37): 0, (53, 3, 38): 0, (53, 3, 39): 0, (53, 3, 40): 0, (53, 3, 41): 0, (53, 3, 42): 0}</t>
-  </si>
-  <si>
-    <t>{11: 6, 29: 3, 47: 8, 53: 4}</t>
+    <t>[6]</t>
+  </si>
+  <si>
+    <t>[5, 13, 14, 15, 17, 18, 19, 20, 22, 25, 27, 28, 30, 32, 34, 36, 37, 40, 44, 47, 59, 60, 63, 65, 67, 68, 72, 74, 79, 88, 94, 95, 97, 99, 101, 102, 104, 106, 111, 113, 115, 116, 118, 122, 124, 129, 130]</t>
+  </si>
+  <si>
+    <t>[1, 2, 6, 7, 16, 26, 35, 38, 39, 41, 42, 43, 46, 48, 49, 51, 52, 57, 70, 73, 75, 82, 84, 86, 87, 89, 92, 96, 98, 100, 107, 108, 109, 110, 112, 117, 120, 121, 123, 125, 131, 133, 134, 135]</t>
+  </si>
+  <si>
+    <t>[3, 4, 8, 9, 10, 11, 12, 21, 23, 24, 29, 31, 33, 45, 50, 53, 54, 55, 56, 58, 61, 62, 64, 66, 69, 71, 76, 77, 78, 80, 81, 83, 85, 90, 91, 93, 103, 105, 114, 119, 126, 127, 128, 132]</t>
+  </si>
+  <si>
+    <t>[1, 2, 3, 4, 6, 7, 8, 9, 10, 11, 12, 16, 21, 23, 24, 26, 29, 31, 33, 35, 38, 39, 41, 42, 43, 45, 46, 48, 49, 50, 51, 52, 53, 54, 55, 56, 57, 58, 61, 62, 64, 66, 69, 70, 71, 73, 75, 76, 77, 78, 80, 81, 82, 83, 84, 85, 86, 87, 89, 90, 91, 92, 93, 96, 98, 100, 103, 105, 107, 108, 109, 110, 112, 114, 117, 119, 120, 121, 123, 125, 126, 127, 128, 131, 132, 133, 134, 135]</t>
+  </si>
+  <si>
+    <t>{1: 2, 2: 1, 3: 1, 4: 1, 5: 1, 6: 1, 7: 1, 8: 1, 9: 1, 10: 1, 11: 2, 12: 1, 13: 1, 14: 1, 15: 1, 16: 1, 17: 2, 18: 2, 19: 2, 20: 1, 21: 1, 22: 1, 23: 2, 24: 1, 25: 1, 26: 1, 27: 2, 28: 1, 29: 1, 30: 1, 31: 1, 32: 1, 33: 1, 34: 2, 35: 2, 36: 2, 37: 1, 38: 1, 39: 1, 40: 1, 41: 1, 42: 1, 43: 1, 44: 1, 45: 1, 46: 1, 47: 1, 48: 1, 49: 1, 50: 1, 51: 3, 52: 1, 53: 1, 54: 1, 55: 1, 56: 1, 57: 1, 58: 1, 59: 1, 60: 1, 61: 1, 62: 1, 63: 1, 64: 1, 65: 1, 66: 1, 67: 1, 68: 1, 69: 2, 70: 1, 71: 1, 72: 1, 73: 1, 74: 1, 75: 1, 76: 1, 77: 1, 78: 1, 79: 1, 80: 2, 81: 1, 82: 2, 83: 1, 84: 2, 85: 1, 86: 1, 87: 1, 88: 1, 89: 1, 90: 1, 91: 1, 92: 1, 93: 1, 94: 1, 95: 1, 96: 1, 97: 1, 98: 1, 99: 2, 100: 1, 101: 1, 102: 1, 103: 1, 104: 1, 105: 1, 106: 1, 107: 1, 108: 1, 109: 1, 110: 1, 111: 1, 112: 1, 113: 1, 114: 1, 115: 1, 116: 1, 117: 1, 118: 1, 119: 1, 120: 1, 121: 1, 122: 1, 123: 1, 124: 1, 125: 1, 126: 1, 127: 1, 128: 1, 129: 1, 130: 1, 131: 1, 132: 1, 133: 1, 134: 1, 135: 1}</t>
+  </si>
+  <si>
+    <t>{1: 1, 2: 1, 3: 0, 4: 0, 6: 1, 7: 1, 8: 0, 9: 0, 10: 0, 11: 0, 12: 0, 16: 1, 21: 0, 23: 0, 24: 0, 26: 1, 29: 0, 31: 0, 33: 0, 35: 1, 38: 1, 39: 1, 41: 1, 42: 1, 43: 1, 45: 0, 46: 1, 48: 1, 49: 1, 50: 0, 51: 1, 52: 1, 53: 0, 54: 0, 55: 0, 56: 0, 57: 1, 58: 0, 61: 0, 62: 0, 64: 0, 66: 0, 69: 0, 70: 1, 71: 0, 73: 1, 75: 1, 76: 0, 77: 0, 78: 0, 80: 0, 81: 0, 82: 1, 83: 0, 84: 1, 85: 0, 86: 1, 87: 1, 89: 1, 90: 0, 91: 0, 92: 1, 93: 0, 96: 1, 98: 1, 100: 1, 103: 0, 105: 0, 107: 1, 108: 1, 109: 1, 110: 1, 112: 1, 114: 0, 117: 1, 119: 0, 120: 1, 121: 1, 123: 1, 125: 1, 126: 0, 127: 0, 128: 0, 131: 1, 132: 0, 133: 1, 134: 1, 135: 1}</t>
+  </si>
+  <si>
+    <t>{(1, -36): 4, (1, -35): 0, (1, -34): 4, (1, -33): 4, (1, -32): 4, (1, -31): 4, (1, -30): 4, (1, -29): 4, (1, -28): 0, (1, -27): 4, (1, -26): 4, (1, -25): 4, (1, -24): 4, (1, -23): 4, (1, -22): 4, (1, -21): 0, (1, -20): 4, (1, -19): 4, (1, -18): 4, (1, -17): 4, (1, -16): 4, (1, -15): 4, (1, -14): 0, (1, -13): 4, (1, -12): 4, (1, -11): 4, (1, -10): 4, (1, -9): 4, (1, -8): 4, (1, -7): 0, (1, -6): 4, (1, -5): 4, (1, -4): 4, (1, -3): 4, (1, -2): 4, (1, -1): 4, (1, 0): 0, (1, 1): 4, (1, 2): 4, (1, 3): 4, (1, 4): 4, (1, 5): 4, (1, 6): 4, (1, 7): 0, (1, 8): 4, (1, 9): 4, (1, 10): 4, (1, 11): 4, (1, 12): 4, (1, 13): 4, (1, 14): 0, (1, 15): 4, (1, 16): 4, (1, 17): 4, (1, 18): 4, (1, 19): 4, (1, 20): 4, (1, 21): 0, (1, 22): 4, (1, 23): 4, (1, 24): 4, (1, 25): 4, (1, 26): 4, (1, 27): 4, (1, 28): 0, (1, 29): 4, (1, 30): 4, (1, 31): 4, (1, 32): 4, (1, 33): 4, (1, 34): 4, (1, 35): 0, (1, 36): 4, (1, 37): 4, (1, 38): 4, (1, 39): 4, (1, 40): 4, (1, 41): 4, (1, 42): 0, (1, 43): 4, (1, 44): 4, (1, 45): 4, (1, 46): 4, (1, 47): 4, (1, 48): 4, (1, 49): 0, (1, 50): 4, (1, 51): 4, (1, 52): 4, (1, 53): 4, (1, 54): 4, (1, 55): 4, (1, 56): 0, (1, 57): 4, (1, 58): 4, (1, 59): 4, (1, 60): 4, (1, 61): 4, (1, 62): 4, (1, 63): 0, (1, 64): 4, (1, 65): 4, (1, 66): 4, (1, 67): 4, (1, 68): 4, (1, 69): 4, (2, -36): 4, (2, -35): 4, (2, -34): 0, (2, -33): 4, (2, -32): 4, (2, -31): 4, (2, -30): 4, (2, -29): 4, (2, -28): 4, (2, -27): 0, (2, -26): 4, (2, -25): 4, (2, -24): 4, (2, -23): 4, (2, -22): 4, (2, -21): 4, (2, -20): 0, (2, -19): 4, (2, -18): 4, (2, -17): 4, (2, -16): 4, (2, -15): 4, (2, -14): 4, (2, -13): 0, (2, -12): 4, (2, -11): 4, (2, -10): 4, (2, -9): 4, (2, -8): 4, (2, -7): 4, (2, -6): 0, (2, -5): 4, (2, -4): 4, (2, -3): 4, (2, -2): 4, (2, -1): 4, (2, 0): 4, (2, 1): 0, (2, 2): 4, (2, 3): 4, (2, 4): 4, (2, 5): 4, (2, 6): 4, (2, 7): 4, (2, 8): 0, (2, 9): 4, (2, 10): 4, (2, 11): 4, (2, 12): 4, (2, 13): 4, (2, 14): 4, (2, 15): 0, (2, 16): 4, (2, 17): 4, (2, 18): 4, (2, 19): 4, (2, 20): 4, (2, 21): 4, (2, 22): 0, (2, 23): 4, (2, 24): 4, (2, 25): 4, (2, 26): 4, (2, 27): 4, (2, 28): 4, (2, 29): 0, (2, 30): 4, (2, 31): 4, (2, 32): 4, (2, 33): 4, (2, 34): 4, (2, 35): 4, (2, 36): 0, (2, 37): 4, (2, 38): 4, (2, 39): 4, (2, 40): 4, (2, 41): 4, (2, 42): 4, (2, 43): 0, (2, 44): 4, (2, 45): 4, (2, 46): 4, (2, 47): 4, (2, 48): 4, (2, 49): 4, (2, 50): 0, (2, 51): 4, (2, 52): 4, (2, 53): 4, (2, 54): 4, (2, 55): 4, (2, 56): 4, (2, 57): 0, (2, 58): 4, (2, 59): 4, (2, 60): 4, (2, 61): 4, (2, 62): 4, (2, 63): 4, (2, 64): 0, (2, 65): 4, (2, 66): 4, (2, 67): 4, (2, 68): 4, (2, 69): 4, (3, -36): 4, (3, -35): 4, (3, -34): 4, (3, -33): 0, (3, -32): 4, (3, -31): 4, (3, -30): 4, (3, -29): 4, (3, -28): 4, (3, -27): 4, (3, -26): 0, (3, -25): 4, (3, -24): 4, (3, -23): 4, (3, -22): 4, (3, -21): 4, (3, -20): 4, (3, -19): 0, (3, -18): 4, (3, -17): 4, (3, -16): 4, (3, -15): 4, (3, -14): 4, (3, -13): 4, (3, -12): 0, (3, -11): 4, (3, -10): 4, (3, -9): 4, (3, -8): 4, (3, -7): 4, (3, -6): 4, (3, -5): 0, (3, -4): 4, (3, -3): 4, (3, -2): 4, (3, -1): 4, (3, 0): 4, (3, 1): 4, (3, 2): 0, (3, 3): 4, (3, 4): 4, (3, 5): 4, (3, 6): 4, (3, 7): 4, (3, 8): 4, (3, 9): 0, (3, 10): 4, (3, 11): 4, (3, 12): 4, (3, 13): 4, (3, 14): 4, (3, 15): 4, (3, 16): 0, (3, 17): 4, (3, 18): 4, (3, 19): 4, (3, 20): 4, (3, 21): 4, (3, 22): 4, (3, 23): 0, (3, 24): 4, (3, 25): 4, (3, 26): 4, (3, 27): 4, (3, 28): 4, (3, 29): 4, (3, 30): 0, (3, 31): 4, (3, 32): 4, (3, 33): 4, (3, 34): 4, (3, 35): 4, (3, 36): 4, (3, 37): 0, (3, 38): 4, (3, 39): 4, (3, 40): 4, (3, 41): 4, (3, 42): 4, (3, 43): 4, (3, 44): 0, (3, 45): 4, (3, 46): 4, (3, 47): 4, (3, 48): 4, (3, 49): 4, (3, 50): 4, (3, 51): 0, (3, 52): 4, (3, 53): 4, (3, 54): 4, (3, 55): 4, (3, 56): 4, (3, 57): 4, (3, 58): 0, (3, 59): 4, (3, 60): 4, (3, 61): 4, (3, 62): 4, (3, 63): 4, (3, 64): 4, (3, 65): 0, (3, 66): 4, (3, 67): 4, (3, 68): 4, (3, 69): 4, (4, -36): 4, (4, -35): 4, (4, -34): 4, (4, -33): 4, (4, -32): 0, (4, -31): 4, (4, -30): 4, (4, -29): 4, (4, -28): 4, (4, -27): 4, (4, -26): 4, (4, -25): 0, (4, -24): 4, (4, -23): 4, (4, -22): 4, (4, -21): 4, (4, -20): 4, (4, -19): 4, (4, -18): 0, (4, -17): 4, (4, -16): 4, (4, -15): 4, (4, -14): 4, (4, -13): 4, (4, -12): 4, (4, -11): 0, (4, -10): 4, (4, -9): 4, (4, -8): 4, (4, -7): 4, (4, -6): 4, (4, -5): 4, (4, -4): 0, (4, -3): 4, (4, -2): 4, (4, -1): 4, (4, 0): 4, (4, 1): 4, (4, 2): 4, (4, 3): 0, (4, 4): 4, (4, 5): 4, (4, 6): 4, (4, 7): 4, (4, 8): 4, (4, 9): 4, (4, 10): 0, (4, 11): 4, (4, 12): 4, (4, 13): 4, (4, 14): 4, (4, 15): 4, (4, 16): 4, (4, 17): 0, (4, 18): 4, (4, 19): 4, (4, 20): 4, (4, 21): 4, (4, 22): 4, (4, 23): 4, (4, 24): 0, (4, 25): 4, (4, 26): 4, (4, 27): 4, (4, 28): 4, (4, 29): 4, (4, 30): 4, (4, 31): 0, (4, 32): 4, (4, 33): 4, (4, 34): 4, (4, 35): 4, (4, 36): 4, (4, 37): 4, (4, 38): 0, (4, 39): 4, (4, 40): 4, (4, 41): 4, (4, 42): 4, (4, 43): 4, (4, 44): 4, (4, 45): 0, (4, 46): 4, (4, 47): 4, (4, 48): 4, (4, 49): 4, (4, 50): 4, (4, 51): 4, (4, 52): 0, (4, 53): 4, (4, 54): 4, (4, 55): 4, (4, 56): 4, (4, 57): 4, (4, 58): 4, (4, 59): 0, (4, 60): 4, (4, 61): 4, (4, 62): 4, (4, 63): 4, (4, 64): 4, (4, 65): 4, (4, 66): 0, (4, 67): 4, (4, 68): 4, (4, 69): 4}</t>
+  </si>
+  <si>
+    <t>{1: 11, 2: 15, 3: 14, 4: 13, 5: 11, 6: 24, 7: 17, 8: 9, 9: 7, 10: 11, 11: 5, 12: 9, 13: 8, 14: 7, 15: 5, 16: 3, 17: 6, 18: 5, 19: 6, 20: 8, 21: 7, 22: 10, 23: 9, 24: 9, 25: 5, 26: 13, 27: 5, 28: 8, 29: 12, 30: 4, 31: 8, 32: 13, 33: 4, 34: 5, 35: 9, 36: 8, 37: 3, 38: 6, 39: 8, 40: 5, 41: 8, 42: 8, 43: 5, 44: 6, 45: 4, 46: 10, 47: 9, 48: 4, 49: 8, 50: 6, 51: 7, 52: 9, 53: 6, 54: 4, 55: 9, 56: 8, 57: 10, 58: 10, 59: 9, 60: 9, 61: 8, 62: 7, 63: 9, 64: 6, 65: 10, 66: 7, 67: 3, 68: 11, 69: 6, 70: 9, 71: 8, 72: 6, 73: 4, 74: 9, 75: 7, 76: 4, 77: 8, 78: 4, 79: 3, 80: 4, 81: 6, 82: 9, 83: 7, 84: 6, 85: 10, 86: 5, 87: 4, 88: 7, 89: 5, 90: 6, 91: 5, 92: 5, 93: 8, 94: 7, 95: 5, 96: 3, 97: 10, 98: 6, 99: 5, 100: 2, 101: 4, 102: 3, 103: 4, 104: 5, 105: 3, 106: 4, 107: 2, 108: 10, 109: 5, 110: 8, 111: 7, 112: 5, 113: 3, 114: 9, 115: 9, 116: 3, 117: 7, 118: 9, 119: 8, 120: 5, 121: 6, 122: 6, 123: 5, 124: 8, 125: 2, 126: 5, 127: 8, 128: 5, 129: 10, 130: 8, 131: 7, 132: 10, 133: 7, 134: 5, 135: 6}</t>
+  </si>
+  <si>
+    <t>{1: 16, 2: 15, 3: 45, 4: 50, 5: 0, 6: 22, 7: 30, 8: 39, 9: 64, 10: 43, 11: 57, 12: 34, 13: -9, 14: -6, 15: -35, 16: 17, 17: -19, 18: -6, 19: -20, 20: -35, 21: 45, 22: -2, 23: 33, 24: 59, 25: -5, 26: 25, 27: -23, 28: -24, 29: 38, 30: -27, 31: 68, 32: -10, 33: 66, 34: -29, 35: 6, 36: -12, 37: -10, 38: 5, 39: 14, 40: -8, 41: 28, 42: 22, 43: 22, 44: -32, 45: 60, 46: 5, 47: -17, 48: 26, 49: 9, 50: 61, 51: 13, 52: 3, 53: 52, 54: 50, 55: 66, 56: 54, 57: 24, 58: 52, 59: -25, 60: -35, 61: 34, 62: 47, 63: -15, 64: 44, 65: -10, 66: 53, 67: -6, 68: -4, 69: 46, 70: 17, 71: 51, 72: -29, 73: 32, 74: -27, 75: 8, 76: 56, 77: 36, 78: 39, 79: -17, 80: 63, 81: 59, 82: 24, 83: 50, 84: 19, 85: 51, 86: 7, 87: 25, 88: -9, 89: 21, 90: 65, 91: 58, 92: 32, 93: 38, 94: -34, 95: -18, 96: 24, 97: 0, 98: 1, 99: -10, 100: 29, 101: -6, 102: -36, 103: 57, 104: -4, 105: 44, 106: -12, 107: 31, 108: 1, 109: 25, 110: 25, 111: -10, 112: 14, 113: -22, 114: 62, 115: -23, 116: -32, 117: 26, 118: -18, 119: 52, 120: 17, 121: 9, 122: -26, 123: 1, 124: -1, 125: 2, 126: 39, 127: 57, 128: 36, 129: -14, 130: -19, 131: 21, 132: 35, 133: 23, 134: 9, 135: 32}</t>
+  </si>
+  <si>
+    <t>{(5, 2, 0): 1, (5, 2, 2): 1, (5, 2, 3): 1, (5, 2, 7): 1, (5, 2, 9): 1, (5, 2, 12): 1, (5, 2, 14): 1, (13, 1, -9): 1, (13, 1, -8): 1, (13, 1, -6): 1, (13, 1, -3): 1, (13, 1, -1): 1, (13, 1, 1): 1, (14, 3, -6): 1, (14, 3, -4): 1, (14, 3, -3): 1, (14, 3, 1): 1, (14, 3, 3): 1, (15, 4, -35): 1, (15, 4, -34): 1, (15, 4, -33): 1, (15, 4, -29): 1, (17, 4, -19): 2, (17, 4, -17): 2, (17, 4, -16): 2, (17, 4, -12): 2, (18, 3, -6): 2, (18, 3, -4): 2, (18, 3, -3): 2, (18, 3, 0): 2, (19, 1, -20): 2, (19, 1, -19): 2, (19, 1, -18): 2, (19, 1, -17): 2, (19, 1, -13): 2, (20, 2, -35): 1, (20, 2, -33): 1, (20, 2, -32): 1, (20, 2, -28): 1, (20, 2, -26): 1, (20, 2, -25): 1, (22, 4, -2): 1, (22, 4, -1): 1, (22, 4, 0): 1, (22, 4, 1): 1, (22, 4, 5): 1, (22, 4, 6): 1, (22, 4, 11): 1, (25, 2, -5): 1, (25, 2, -4): 1, (25, 2, -3): 1, (25, 2, -2): 1, (25, 2, 0): 1, (27, 3, -23): 2, (27, 3, -22): 2, (27, 3, -21): 2, (27, 3, -20): 2, (27, 3, -18): 2, (28, 1, -24): 1, (28, 1, -23): 1, (28, 1, -22): 1, (28, 1, -18): 1, (28, 1, -17): 1, (28, 1, -13): 1, (30, 4, -27): 1, (30, 4, -26): 1, (30, 4, -24): 1, (30, 4, -23): 1, (32, 2, -10): 1, (32, 2, -9): 1, (32, 2, -8): 1, (32, 2, -7): 1, (32, 2, -3): 1, (32, 2, -2): 1, (32, 2, 2): 1, (32, 2, 3): 1, (32, 2, 7): 1, (34, 1, -29): 2, (34, 1, -27): 2, (34, 1, -26): 2, (34, 1, -23): 2, (36, 4, -12): 2, (36, 4, -10): 2, (36, 4, -9): 2, (36, 4, -5): 2, (36, 4, -3): 2, (36, 4, -2): 2, (37, 3, -10): 1, (37, 3, -9): 1, (37, 3, -8): 1, (40, 3, -8): 1, (40, 3, -7): 1, (40, 3, -6): 1, (40, 3, -2): 1, (44, 2, -32): 1, (44, 2, -31): 1, (44, 2, -30): 1, (44, 2, -29): 1, (44, 2, -25): 1, (47, 1, -17): 1, (47, 1, -16): 1, (47, 1, -15): 1, (47, 1, -11): 1, (47, 1, -10): 1, (47, 1, -6): 1, (59, 3, -25): 1, (59, 3, -24): 1, (59, 3, -23): 1, (59, 3, -22): 1, (59, 3, -18): 1, (59, 3, -17): 1, (59, 3, -14): 1, (60, 2, -35): 1, (60, 2, -33): 1, (60, 2, -32): 1, (60, 2, -28): 1, (60, 2, -26): 1, (60, 2, -23): 1, (63, 4, -15): 1, (63, 4, -14): 1, (63, 4, -13): 1, (63, 4, -9): 1, (63, 4, -8): 1, (63, 4, -3): 1, (65, 1, -10): 1, (65, 1, -9): 1, (65, 1, -8): 1, (65, 1, -4): 1, (65, 1, -3): 1, (65, 1, 2): 1, (65, 1, 3): 1, (67, 4, -6): 1, (67, 4, -5): 1, (67, 4, -3): 1, (68, 3, -4): 1, (68, 3, -3): 1, (68, 3, -2): 1, (68, 3, -1): 1, (68, 3, 3): 1, (68, 3, 4): 1, (68, 3, 8): 1, (68, 3, 10): 1, (72, 2, -29): 1, (72, 2, -28): 1, (72, 2, -26): 1, (72, 2, -23): 1, (72, 2, -22): 1, (74, 1, -27): 1, (74, 1, -26): 1, (74, 1, -25): 1, (74, 1, -24): 1, (74, 1, -20): 1, (74, 1, -19): 1, (74, 1, -16): 1, (79, 2, -17): 1, (79, 2, -16): 1, (79, 2, -15): 1, (88, 4, -9): 1, (88, 4, -8): 1, (88, 4, -7): 1, (88, 4, -6): 1, (88, 4, -2): 1, (88, 4, -1): 1, (94, 3, -34): 1, (94, 3, -32): 1, (94, 3, -31): 1, (94, 3, -27): 1, (94, 3, -25): 1, (95, 2, -18): 1, (95, 2, -17): 1, (95, 2, -16): 1, (95, 2, -15): 1, (95, 2, -12): 1, (97, 3, 0): 1, (97, 3, 1): 1, (97, 3, 3): 1, (97, 3, 6): 1, (97, 3, 8): 1, (97, 3, 11): 1, (97, 3, 13): 1, (99, 1, -10): 2, (99, 1, -9): 2, (99, 1, -8): 2, (99, 1, -4): 2, (101, 4, -6): 1, (101, 4, -5): 1, (101, 4, -1): 1, (102, 2, -36): 1, (102, 2, -35): 1, (102, 2, -33): 1, (104, 2, -4): 1, (104, 2, -3): 1, (104, 2, -2): 1, (104, 2, -1): 1, (104, 2, 2): 1, (106, 1, -12): 1, (106, 1, -11): 1, (106, 1, -6): 1, (111, 4, -10): 1, (111, 4, -8): 1, (111, 4, -7): 1, (111, 4, -1): 1, (113, 3, -22): 1, (113, 3, -21): 1, (113, 3, -20): 1, (115, 4, -23): 1, (115, 4, -22): 1, (115, 4, -21): 1, (115, 4, -20): 1, (115, 4, -16): 1, (115, 4, -15): 1, (115, 4, -10): 1, (116, 2, -32): 1, (116, 2, -31): 1, (116, 2, -30): 1, (118, 3, -18): 1, (118, 3, -17): 1, (118, 3, -16): 1, (118, 3, -15): 1, (118, 3, -11): 1, (118, 3, -10): 1, (118, 3, -7): 1, (122, 1, -26): 1, (122, 1, -25): 1, (122, 1, -24): 1, (122, 1, -23): 1, (122, 1, -19): 1, (124, 2, -1): 1, (124, 2, 0): 1, (124, 2, 2): 1, (124, 2, 5): 1, (124, 2, 7): 1, (124, 2, 9): 1, (129, 4, -14): 1, (129, 4, -13): 1, (129, 4, -8): 1, (129, 4, -7): 1, (129, 4, 0): 1, (130, 2, -19): 1, (130, 2, -18): 1, (130, 2, -17): 1, (130, 2, -16): 1, (130, 2, -12): 1, (130, 2, -11): 1, (130, 2, -10): 1}</t>
+  </si>
+  <si>
+    <t>{5: 15, 13: 11, 14: 10, 15: 7, 17: 8, 18: 7, 19: 8, 20: 11, 22: 14, 25: 6, 27: 6, 28: 12, 30: 5, 32: 18, 34: 7, 36: 11, 37: 3, 40: 7, 44: 8, 47: 12, 59: 12, 60: 13, 63: 13, 65: 14, 67: 4, 68: 15, 72: 8, 74: 12, 79: 3, 88: 9, 94: 10, 95: 7, 97: 14, 99: 7, 101: 6, 102: 4, 104: 7, 106: 7, 111: 10, 113: 3, 115: 14, 116: 3, 118: 12, 122: 8, 124: 11, 129: 15, 130: 10}</t>
+  </si>
+  <si>
+    <t>{(43, 1, 1): 0, (43, 1, 2): 0, (43, 1, 3): 0, (43, 1, 4): 0, (43, 1, 5): 0, (43, 1, 6): 0, (43, 1, 7): 0, (43, 1, 8): 0, (43, 1, 9): 0, (43, 1, 10): 0, (43, 1, 11): 0, (43, 1, 12): 0, (43, 1, 13): 0, (43, 1, 14): 0, (43, 1, 15): 0, (43, 1, 16): 0, (43, 1, 17): 0, (43, 1, 18): 0, (43, 1, 19): 0, (43, 1, 20): 0, (43, 1, 21): 0, (43, 1, 22): 1, (43, 1, 23): 1, (43, 1, 24): 1, (43, 1, 25): 1, (43, 1, 26): 1, (43, 1, 27): 0, (43, 1, 28): 0, (43, 1, 29): 0, (43, 1, 30): 0, (43, 1, 31): 0, (43, 1, 32): 0, (43, 1, 33): 0, (43, 1, 34): 0, (43, 1, 35): 0, (43, 1, 36): 0, (43, 1, 37): 0, (43, 1, 38): 0, (43, 1, 39): 0, (43, 1, 40): 0, (43, 1, 41): 0, (43, 1, 42): 0, (43, 1, 43): 0, (43, 1, 44): 0, (43, 1, 45): 0, (43, 1, 46): 0, (43, 1, 47): 0, (43, 1, 48): 0, (43, 1, 49): 0, (43, 1, 50): 0, (43, 1, 51): 0, (43, 1, 52): 0, (43, 1, 53): 0, (43, 1, 54): 0, (43, 1, 55): 0, (43, 1, 56): 0, (43, 1, 57): 0, (43, 1, 58): 0, (43, 1, 59): 0, (43, 1, 60): 0, (43, 1, 61): 0, (43, 1, 62): 0, (43, 1, 63): 0, (43, 1, 64): 0, (43, 1, 65): 0, (43, 1, 66): 0, (43, 1, 67): 0, (43, 1, 68): 0, (43, 1, 69): 0, (43, 2, 1): 0, (43, 2, 2): 0, (43, 2, 3): 0, (43, 2, 4): 0, (43, 2, 5): 0, (43, 2, 6): 0, (43, 2, 7): 0, (43, 2, 8): 0, (43, 2, 9): 0, (43, 2, 10): 0, (43, 2, 11): 0, (43, 2, 12): 0, (43, 2, 13): 0, (43, 2, 14): 0, (43, 2, 15): 0, (43, 2, 16): 0, (43, 2, 17): 0, (43, 2, 18): 0, (43, 2, 19): 0, (43, 2, 20): 0, (43, 2, 21): 0, (43, 2, 22): 0, (43, 2, 23): 0, (43, 2, 24): 0, (43, 2, 25): 0, (43, 2, 26): 0, (43, 2, 27): 0, (43, 2, 28): 0, (43, 2, 29): 0, (43, 2, 30): 0, (43, 2, 31): 0, (43, 2, 32): 0, (43, 2, 33): 0, (43, 2, 34): 0, (43, 2, 35): 0, (43, 2, 36): 0, (43, 2, 37): 0, (43, 2, 38): 0, (43, 2, 39): 0, (43, 2, 40): 0, (43, 2, 41): 0, (43, 2, 42): 0, (43, 2, 43): 0, (43, 2, 44): 0, (43, 2, 45): 0, (43, 2, 46): 0, (43, 2, 47): 0, (43, 2, 48): 0, (43, 2, 49): 0, (43, 2, 50): 0, (43, 2, 51): 0, (43, 2, 52): 0, (43, 2, 53): 0, (43, 2, 54): 0, (43, 2, 55): 0, (43, 2, 56): 0, (43, 2, 57): 0, (43, 2, 58): 0, (43, 2, 59): 0, (43, 2, 60): 0, (43, 2, 61): 0, (43, 2, 62): 0, (43, 2, 63): 0, (43, 2, 64): 0, (43, 2, 65): 0, (43, 2, 66): 0, (43, 2, 67): 0, (43, 2, 68): 0, (43, 2, 69): 0, (43, 3, 1): 0, (43, 3, 2): 0, (43, 3, 3): 0, (43, 3, 4): 0, (43, 3, 5): 0, (43, 3, 6): 0, (43, 3, 7): 0, (43, 3, 8): 0, (43, 3, 9): 0, (43, 3, 10): 0, (43, 3, 11): 0, (43, 3, 12): 0, (43, 3, 13): 0, (43, 3, 14): 0, (43, 3, 15): 0, (43, 3, 16): 0, (43, 3, 17): 0, (43, 3, 18): 0, (43, 3, 19): 0, (43, 3, 20): 0, (43, 3, 21): 0, (43, 3, 22): 0, (43, 3, 23): 0, (43, 3, 24): 0, (43, 3, 25): 0, (43, 3, 26): 0, (43, 3, 27): 0, (43, 3, 28): 0, (43, 3, 29): 0, (43, 3, 30): 0, (43, 3, 31): 0, (43, 3, 32): 0, (43, 3, 33): 0, (43, 3, 34): 0, (43, 3, 35): 0, (43, 3, 36): 0, (43, 3, 37): 0, (43, 3, 38): 0, (43, 3, 39): 0, (43, 3, 40): 0, (43, 3, 41): 0, (43, 3, 42): 0, (43, 3, 43): 0, (43, 3, 44): 0, (43, 3, 45): 0, (43, 3, 46): 0, (43, 3, 47): 0, (43, 3, 48): 0, (43, 3, 49): 0, (43, 3, 50): 0, (43, 3, 51): 0, (43, 3, 52): 0, (43, 3, 53): 0, (43, 3, 54): 0, (43, 3, 55): 0, (43, 3, 56): 0, (43, 3, 57): 0, (43, 3, 58): 0, (43, 3, 59): 0, (43, 3, 60): 0, (43, 3, 61): 0, (43, 3, 62): 0, (43, 3, 63): 0, (43, 3, 64): 0, (43, 3, 65): 0, (43, 3, 66): 0, (43, 3, 67): 0, (43, 3, 68): 0, (43, 3, 69): 0, (43, 4, 1): 0, (43, 4, 2): 0, (43, 4, 3): 0, (43, 4, 4): 0, (43, 4, 5): 0, (43, 4, 6): 0, (43, 4, 7): 0, (43, 4, 8): 0, (43, 4, 9): 0, (43, 4, 10): 0, (43, 4, 11): 0, (43, 4, 12): 0, (43, 4, 13): 0, (43, 4, 14): 0, (43, 4, 15): 0, (43, 4, 16): 0, (43, 4, 17): 0, (43, 4, 18): 0, (43, 4, 19): 0, (43, 4, 20): 0, (43, 4, 21): 0, (43, 4, 22): 0, (43, 4, 23): 0, (43, 4, 24): 0, (43, 4, 25): 0, (43, 4, 26): 0, (43, 4, 27): 0, (43, 4, 28): 0, (43, 4, 29): 0, (43, 4, 30): 0, (43, 4, 31): 0, (43, 4, 32): 0, (43, 4, 33): 0, (43, 4, 34): 0, (43, 4, 35): 0, (43, 4, 36): 0, (43, 4, 37): 0, (43, 4, 38): 0, (43, 4, 39): 0, (43, 4, 40): 0, (43, 4, 41): 0, (43, 4, 42): 0, (43, 4, 43): 0, (43, 4, 44): 0, (43, 4, 45): 0, (43, 4, 46): 0, (43, 4, 47): 0, (43, 4, 48): 0, (43, 4, 49): 0, (43, 4, 50): 0, (43, 4, 51): 0, (43, 4, 52): 0, (43, 4, 53): 0, (43, 4, 54): 0, (43, 4, 55): 0, (43, 4, 56): 0, (43, 4, 57): 0, (43, 4, 58): 0, (43, 4, 59): 0, (43, 4, 60): 0, (43, 4, 61): 0, (43, 4, 62): 0, (43, 4, 63): 0, (43, 4, 64): 0, (43, 4, 65): 0, (43, 4, 66): 0, (43, 4, 67): 0, (43, 4, 68): 0, (43, 4, 69): 0, (48, 1, 1): 0, (48, 1, 2): 0, (48, 1, 3): 0, (48, 1, 4): 0, (48, 1, 5): 0, (48, 1, 6): 0, (48, 1, 7): 0, (48, 1, 8): 0, (48, 1, 9): 0, (48, 1, 10): 0, (48, 1, 11): 0, (48, 1, 12): 0, (48, 1, 13): 0, (48, 1, 14): 0, (48, 1, 15): 0, (48, 1, 16): 0, (48, 1, 17): 0, (48, 1, 18): 0, (48, 1, 19): 0, (48, 1, 20): 0, (48, 1, 21): 0, (48, 1, 22): 0, (48, 1, 23): 0, (48, 1, 24): 0, (48, 1, 25): 0, (48, 1, 26): 0, (48, 1, 27): 0, (48, 1, 28): 0, (48, 1, 29): 0, (48, 1, 30): 0, (48, 1, 31): 0, (48, 1, 32): 0, (48, 1, 33): 0, (48, 1, 34): 0, (48, 1, 35): 0, (48, 1, 36): 0, (48, 1, 37): 0, (48, 1, 38): 0, (48, 1, 39): 0, (48, 1, 40): 0, (48, 1, 41): 0, (48, 1, 42): 0, (48, 1, 43): 0, (48, 1, 44): 0, (48, 1, 45): 0, (48, 1, 46): 0, (48, 1, 47): 0, (48, 1, 48): 0, (48, 1, 49): 0, (48, 1, 50): 0, (48, 1, 51): 0, (48, 1, 52): 0, (48, 1, 53): 0, (48, 1, 54): 0, (48, 1, 55): 0, (48, 1, 56): 0, (48, 1, 57): 0, (48, 1, 58): 0, (48, 1, 59): 0, (48, 1, 60): 0, (48, 1, 61): 0, (48, 1, 62): 0, (48, 1, 63): 0, (48, 1, 64): 0, (48, 1, 65): 0, (48, 1, 66): 0, (48, 1, 67): 0, (48, 1, 68): 0, (48, 1, 69): 0, (48, 2, 1): 0, (48, 2, 2): 0, (48, 2, 3): 0, (48, 2, 4): 0, (48, 2, 5): 0, (48, 2, 6): 0, (48, 2, 7): 0, (48, 2, 8): 0, (48, 2, 9): 0, (48, 2, 10): 0, (48, 2, 11): 0, (48, 2, 12): 0, (48, 2, 13): 0, (48, 2, 14): 0, (48, 2, 15): 0, (48, 2, 16): 0, (48, 2, 17): 0, (48, 2, 18): 0, (48, 2, 19): 0, (48, 2, 20): 0, (48, 2, 21): 0, (48, 2, 22): 0, (48, 2, 23): 0, (48, 2, 24): 0, (48, 2, 25): 0, (48, 2, 26): 0, (48, 2, 27): 0, (48, 2, 28): 0, (48, 2, 29): 0, (48, 2, 30): 0, (48, 2, 31): 0, (48, 2, 32): 0, (48, 2, 33): 0, (48, 2, 34): 0, (48, 2, 35): 0, (48, 2, 36): 0, (48, 2, 37): 0, (48, 2, 38): 0, (48, 2, 39): 0, (48, 2, 40): 0, (48, 2, 41): 0, (48, 2, 42): 0, (48, 2, 43): 0, (48, 2, 44): 0, (48, 2, 45): 0, (48, 2, 46): 0, (48, 2, 47): 0, (48, 2, 48): 0, (48, 2, 49): 0, (48, 2, 50): 0, (48, 2, 51): 0, (48, 2, 52): 0, (48, 2, 53): 0, (48, 2, 54): 0, (48, 2, 55): 0, (48, 2, 56): 0, (48, 2, 57): 0, (48, 2, 58): 0, (48, 2, 59): 0, (48, 2, 60): 0, (48, 2, 61): 0, (48, 2, 62): 0, (48, 2, 63): 0, (48, 2, 64): 0, (48, 2, 65): 0, (48, 2, 66): 0, (48, 2, 67): 0, (48, 2, 68): 0, (48, 2, 69): 0, (48, 3, 1): 0, (48, 3, 2): 0, (48, 3, 3): 0, (48, 3, 4): 0, (48, 3, 5): 0, (48, 3, 6): 0, (48, 3, 7): 0, (48, 3, 8): 0, (48, 3, 9): 0, (48, 3, 10): 0, (48, 3, 11): 0, (48, 3, 12): 0, (48, 3, 13): 0, (48, 3, 14): 0, (48, 3, 15): 0, (48, 3, 16): 0, (48, 3, 17): 0, (48, 3, 18): 0, (48, 3, 19): 0, (48, 3, 20): 0, (48, 3, 21): 0, (48, 3, 22): 0, (48, 3, 23): 0, (48, 3, 24): 0, (48, 3, 25): 0, (48, 3, 26): 1, (48, 3, 27): 1, (48, 3, 28): 1, (48, 3, 29): 1, (48, 3, 30): 0, (48, 3, 31): 0, (48, 3, 32): 0, (48, 3, 33): 0, (48, 3, 34): 0, (48, 3, 35): 0, (48, 3, 36): 0, (48, 3, 37): 0, (48, 3, 38): 0, (48, 3, 39): 0, (48, 3, 40): 0, (48, 3, 41): 0, (48, 3, 42): 0, (48, 3, 43): 0, (48, 3, 44): 0, (48, 3, 45): 0, (48, 3, 46): 0, (48, 3, 47): 0, (48, 3, 48): 0, (48, 3, 49): 0, (48, 3, 50): 0, (48, 3, 51): 0, (48, 3, 52): 0, (48, 3, 53): 0, (48, 3, 54): 0, (48, 3, 55): 0, (48, 3, 56): 0, (48, 3, 57): 0, (48, 3, 58): 0, (48, 3, 59): 0, (48, 3, 60): 0, (48, 3, 61): 0, (48, 3, 62): 0, (48, 3, 63): 0, (48, 3, 64): 0, (48, 3, 65): 0, (48, 3, 66): 0, (48, 3, 67): 0, (48, 3, 68): 0, (48, 3, 69): 0, (48, 4, 1): 0, (48, 4, 2): 0, (48, 4, 3): 0, (48, 4, 4): 0, (48, 4, 5): 0, (48, 4, 6): 0, (48, 4, 7): 0, (48, 4, 8): 0, (48, 4, 9): 0, (48, 4, 10): 0, (48, 4, 11): 0, (48, 4, 12): 0, (48, 4, 13): 0, (48, 4, 14): 0, (48, 4, 15): 0, (48, 4, 16): 0, (48, 4, 17): 0, (48, 4, 18): 0, (48, 4, 19): 0, (48, 4, 20): 0, (48, 4, 21): 0, (48, 4, 22): 0, (48, 4, 23): 0, (48, 4, 24): 0, (48, 4, 25): 0, (48, 4, 26): 0, (48, 4, 27): 0, (48, 4, 28): 0, (48, 4, 29): 0, (48, 4, 30): 0, (48, 4, 31): 0, (48, 4, 32): 0, (48, 4, 33): 0, (48, 4, 34): 0, (48, 4, 35): 0, (48, 4, 36): 0, (48, 4, 37): 0, (48, 4, 38): 0, (48, 4, 39): 0, (48, 4, 40): 0, (48, 4, 41): 0, (48, 4, 42): 0, (48, 4, 43): 0, (48, 4, 44): 0, (48, 4, 45): 0, (48, 4, 46): 0, (48, 4, 47): 0, (48, 4, 48): 0, (48, 4, 49): 0, (48, 4, 50): 0, (48, 4, 51): 0, (48, 4, 52): 0, (48, 4, 53): 0, (48, 4, 54): 0, (48, 4, 55): 0, (48, 4, 56): 0, (48, 4, 57): 0, (48, 4, 58): 0, (48, 4, 59): 0, (48, 4, 60): 0, (48, 4, 61): 0, (48, 4, 62): 0, (48, 4, 63): 0, (48, 4, 64): 0, (48, 4, 65): 0, (48, 4, 66): 0, (48, 4, 67): 0, (48, 4, 68): 0, (48, 4, 69): 0, (49, 1, 1): 0, (49, 1, 2): 0, (49, 1, 3): 0, (49, 1, 4): 0, (49, 1, 5): 0, (49, 1, 6): 0, (49, 1, 7): 0, (49, 1, 8): 0, (49, 1, 9): 1, (49, 1, 10): 1, (49, 1, 11): 1, (49, 1, 12): 1, (49, 1, 13): 1, (49, 1, 14): 0, (49, 1, 15): 1, (49, 1, 16): 1, (49, 1, 17): 1, (49, 1, 18): 0, (49, 1, 19): 0, (49, 1, 20): 0, (49, 1, 21): 0, (49, 1, 22): 0, (49, 1, 23): 0, (49, 1, 24): 0, (49, 1, 25): 0, (49, 1, 26): 0, (49, 1, 27): 0, (49, 1, 28): 0, (49, 1, 29): 0, (49, 1, 30): 0, (49, 1, 31): 0, (49, 1, 32): 0, (49, 1, 33): 0, (49, 1, 34): 0, (49, 1, 35): 0, (49, 1, 36): 0, (49, 1, 37): 0, (49, 1, 38): 0, (49, 1, 39): 0, (49, 1, 40): 0, (49, 1, 41): 0, (49, 1, 42): 0, (49, 1, 43): 0, (49, 1, 44): 0, (49, 1, 45): 0, (49, 1, 46): 0, (49, 1, 47): 0, (49, 1, 48): 0, (49, 1, 49): 0, (49, 1, 50): 0, (49, 1, 51): 0, (49, 1, 52): 0, (49, 1, 53): 0, (49, 1, 54): 0, (49, 1, 55): 0, (49, 1, 56): 0, (49, 1, 57): 0, (49, 1, 58): 0, (49, 1, 59): 0, (49, 1, 60): 0, (49, 1, 61): 0, (49, 1, 62): 0, (49, 1, 63): 0, (49, 1, 64): 0, (49, 1, 65): 0, (49, 1, 66): 0, (49, 1, 67): 0, (49, 1, 68): 0, (49, 1, 69): 0, (49, 2, 1): 0, (49, 2, 2): 0, (49, 2, 3): 0, (49, 2, 4): 0, (49, 2, 5): 0, (49, 2, 6): 0, (49, 2, 7): 0, (49, 2, 8): 0, (49, 2, 9): 0, (49, 2, 10): 0, (49, 2, 11): 0, (49, 2, 12): 0, (49, 2, 13): 0, (49, 2, 14): 0, (49, 2, 15): 0, (49, 2, 16): 0, (49, 2, 17): 0, (49, 2, 18): 0, (49, 2, 19): 0, (49, 2, 20): 0, (49, 2, 21): 0, (49, 2, 22): 0, (49, 2, 23): 0, (49, 2, 24): 0, (49, 2, 25): 0, (49, 2, 26): 0, (49, 2, 27): 0, (49, 2, 28): 0, (49, 2, 29): 0, (49, 2, 30): 0, (49, 2, 31): 0, (49, 2, 32): 0, (49, 2, 33): 0, (49, 2, 34): 0, (49, 2, 35): 0, (49, 2, 36): 0, (49, 2, 37): 0, (49, 2, 38): 0, (49, 2, 39): 0, (49, 2, 40): 0, (49, 2, 41): 0, (49, 2, 42): 0, (49, 2, 43): 0, (49, 2, 44): 0, (49, 2, 45): 0, (49, 2, 46): 0, (49, 2, 47): 0, (49, 2, 48): 0, (49, 2, 49): 0, (49, 2, 50): 0, (49, 2, 51): 0, (49, 2, 52): 0, (49, 2, 53): 0, (49, 2, 54): 0, (49, 2, 55): 0, (49, 2, 56): 0, (49, 2, 57): 0, (49, 2, 58): 0, (49, 2, 59): 0, (49, 2, 60): 0, (49, 2, 61): 0, (49, 2, 62): 0, (49, 2, 63): 0, (49, 2, 64): 0, (49, 2, 65): 0, (49, 2, 66): 0, (49, 2, 67): 0, (49, 2, 68): 0, (49, 2, 69): 0, (49, 3, 1): 0, (49, 3, 2): 0, (49, 3, 3): 0, (49, 3, 4): 0, (49, 3, 5): 0, (49, 3, 6): 0, (49, 3, 7): 0, (49, 3, 8): 0, (49, 3, 9): 0, (49, 3, 10): 0, (49, 3, 11): 0, (49, 3, 12): 0, (49, 3, 13): 0, (49, 3, 14): 0, (49, 3, 15): 0, (49, 3, 16): 0, (49, 3, 17): 0, (49, 3, 18): 0, (49, 3, 19): 0, (49, 3, 20): 0, (49, 3, 21): 0, (49, 3, 22): 0, (49, 3, 23): 0, (49, 3, 24): 0, (49, 3, 25): 0, (49, 3, 26): 0, (49, 3, 27): 0, (49, 3, 28): 0, (49, 3, 29): 0, (49, 3, 30): 0, (49, 3, 31): 0, (49, 3, 32): 0, (49, 3, 33): 0, (49, 3, 34): 0, (49, 3, 35): 0, (49, 3, 36): 0, (49, 3, 37): 0, (49, 3, 38): 0, (49, 3, 39): 0, (49, 3, 40): 0, (49, 3, 41): 0, (49, 3, 42): 0, (49, 3, 43): 0, (49, 3, 44): 0, (49, 3, 45): 0, (49, 3, 46): 0, (49, 3, 47): 0, (49, 3, 48): 0, (49, 3, 49): 0, (49, 3, 50): 0, (49, 3, 51): 0, (49, 3, 52): 0, (49, 3, 53): 0, (49, 3, 54): 0, (49, 3, 55): 0, (49, 3, 56): 0, (49, 3, 57): 0, (49, 3, 58): 0, (49, 3, 59): 0, (49, 3, 60): 0, (49, 3, 61): 0, (49, 3, 62): 0, (49, 3, 63): 0, (49, 3, 64): 0, (49, 3, 65): 0, (49, 3, 66): 0, (49, 3, 67): 0, (49, 3, 68): 0, (49, 3, 69): 0, (49, 4, 1): 0, (49, 4, 2): 0, (49, 4, 3): 0, (49, 4, 4): 0, (49, 4, 5): 0, (49, 4, 6): 0, (49, 4, 7): 0, (49, 4, 8): 0, (49, 4, 9): 0, (49, 4, 10): 0, (49, 4, 11): 0, (49, 4, 12): 0, (49, 4, 13): 0, (49, 4, 14): 0, (49, 4, 15): 0, (49, 4, 16): 0, (49, 4, 17): 0, (49, 4, 18): 0, (49, 4, 19): 0, (49, 4, 20): 0, (49, 4, 21): 0, (49, 4, 22): 0, (49, 4, 23): 0, (49, 4, 24): 0, (49, 4, 25): 0, (49, 4, 26): 0, (49, 4, 27): 0, (49, 4, 28): 0, (49, 4, 29): 0, (49, 4, 30): 0, (49, 4, 31): 0, (49, 4, 32): 0, (49, 4, 33): 0, (49, 4, 34): 0, (49, 4, 35): 0, (49, 4, 36): 0, (49, 4, 37): 0, (49, 4, 38): 0, (49, 4, 39): 0, (49, 4, 40): 0, (49, 4, 41): 0, (49, 4, 42): 0, (49, 4, 43): 0, (49, 4, 44): 0, (49, 4, 45): 0, (49, 4, 46): 0, (49, 4, 47): 0, (49, 4, 48): 0, (49, 4, 49): 0, (49, 4, 50): 0, (49, 4, 51): 0, (49, 4, 52): 0, (49, 4, 53): 0, (49, 4, 54): 0, (49, 4, 55): 0, (49, 4, 56): 0, (49, 4, 57): 0, (49, 4, 58): 0, (49, 4, 59): 0, (49, 4, 60): 0, (49, 4, 61): 0, (49, 4, 62): 0, (49, 4, 63): 0, (49, 4, 64): 0, (49, 4, 65): 0, (49, 4, 66): 0, (49, 4, 67): 0, (49, 4, 68): 0, (49, 4, 69): 0, (51, 1, 1): 0, (51, 1, 2): 0, (51, 1, 3): 0, (51, 1, 4): 0, (51, 1, 5): 0, (51, 1, 6): 0, (51, 1, 7): 0, (51, 1, 8): 0, (51, 1, 9): 0, (51, 1, 10): 0, (51, 1, 11): 0, (51, 1, 12): 0, (51, 1, 13): 0, (51, 1, 14): 0, (51, 1, 15): 0, (51, 1, 16): 0, (51, 1, 17): 0, (51, 1, 18): 0, (51, 1, 19): 0, (51, 1, 20): 0, (51, 1, 21): 0, (51, 1, 22): 0, (51, 1, 23): 0, (51, 1, 24): 0, (51, 1, 25): 0, (51, 1, 26): 0, (51, 1, 27): 0, (51, 1, 28): 0, (51, 1, 29): 0, (51, 1, 30): 0, (51, 1, 31): 0, (51, 1, 32): 0, (51, 1, 33): 0, (51, 1, 34): 0, (51, 1, 35): 0, (51, 1, 36): 0, (51, 1, 37): 0, (51, 1, 38): 0, (51, 1, 39): 0, (51, 1, 40): 0, (51, 1, 41): 0, (51, 1, 42): 0, (51, 1, 43): 0, (51, 1, 44): 0, (51, 1, 45): 0, (51, 1, 46): 0, (51, 1, 47): 0, (51, 1, 48): 0, (51, 1, 49): 0, (51, 1, 50): 0, (51, 1, 51): 0, (51, 1, 52): 0, (51, 1, 53): 0, (51, 1, 54): 0, (51, 1, 55): 0, (51, 1, 56): 0, (51, 1, 57): 0, (51, 1, 58): 0, (51, 1, 59): 0, (51, 1, 60): 0, (51, 1, 61): 0, (51, 1, 62): 0, (51, 1, 63): 0, (51, 1, 64): 0, (51, 1, 65): 0, (51, 1, 66): 0, (51, 1, 67): 0, (51, 1, 68): 0, (51, 1, 69): 0, (51, 2, 1): 0, (51, 2, 2): 0, (51, 2, 3): 0, (51, 2, 4): 0, (51, 2, 5): 0, (51, 2, 6): 0, (51, 2, 7): 0, (51, 2, 8): 0, (51, 2, 9): 0, (51, 2, 10): 0, (51, 2, 11): 0, (51, 2, 12): 0, (51, 2, 13): 0, (51, 2, 14): 0, (51, 2, 15): 0, (51, 2, 16): 0, (51, 2, 17): 0, (51, 2, 18): 0, (51, 2, 19): 0, (51, 2, 20): 0, (51, 2, 21): 0, (51, 2, 22): 0, (51, 2, 23): 0, (51, 2, 24): 0, (51, 2, 25): 0, (51, 2, 26): 0, (51, 2, 27): 0, (51, 2, 28): 0, (51, 2, 29): 0, (51, 2, 30): 0, (51, 2, 31): 0, (51, 2, 32): 0, (51, 2, 33): 0, (51, 2, 34): 0, (51, 2, 35): 0, (51, 2, 36): 0, (51, 2, 37): 0, (51, 2, 38): 0, (51, 2, 39): 0, (51, 2, 40): 0, (51, 2, 41): 0, (51, 2, 42): 0, (51, 2, 43): 0, (51, 2, 44): 0, (51, 2, 45): 0, (51, 2, 46): 0, (51, 2, 47): 0, (51, 2, 48): 0, (51, 2, 49): 0, (51, 2, 50): 0, (51, 2, 51): 0, (51, 2, 52): 0, (51, 2, 53): 0, (51, 2, 54): 0, (51, 2, 55): 0, (51, 2, 56): 0, (51, 2, 57): 0, (51, 2, 58): 0, (51, 2, 59): 0, (51, 2, 60): 0, (51, 2, 61): 0, (51, 2, 62): 0, (51, 2, 63): 0, (51, 2, 64): 0, (51, 2, 65): 0, (51, 2, 66): 0, (51, 2, 67): 0, (51, 2, 68): 0, (51, 2, 69): 0, (51, 3, 1): 0, (51, 3, 2): 0, (51, 3, 3): 0, (51, 3, 4): 0, (51, 3, 5): 0, (51, 3, 6): 0, (51, 3, 7): 0, (51, 3, 8): 0, (51, 3, 9): 0, (51, 3, 10): 0, (51, 3, 11): 0, (51, 3, 12): 0, (51, 3, 13): 0, (51, 3, 14): 0, (51, 3, 15): 0, (51, 3, 16): 0, (51, 3, 17): 0, (51, 3, 18): 0, (51, 3, 19): 0, (51, 3, 20): 0, (51, 3, 21): 0, (51, 3, 22): 0, (51, 3, 23): 0, (51, 3, 24): 0, (51, 3, 25): 0, (51, 3, 26): 0, (51, 3, 27): 0, (51, 3, 28): 0, (51, 3, 29): 0, (51, 3, 30): 0, (51, 3, 31): 0, (51, 3, 32): 0, (51, 3, 33): 0, (51, 3, 34): 0, (51, 3, 35): 0, (51, 3, 36): 0, (51, 3, 37): 0, (51, 3, 38): 0, (51, 3, 39): 0, (51, 3, 40): 0, (51, 3, 41): 0, (51, 3, 42): 0, (51, 3, 43): 0, (51, 3, 44): 0, (51, 3, 45): 0, (51, 3, 46): 0, (51, 3, 47): 0, (51, 3, 48): 0, (51, 3, 49): 0, (51, 3, 50): 0, (51, 3, 51): 0, (51, 3, 52): 0, (51, 3, 53): 0, (51, 3, 54): 0, (51, 3, 55): 0, (51, 3, 56): 0, (51, 3, 57): 0, (51, 3, 58): 0, (51, 3, 59): 0, (51, 3, 60): 0, (51, 3, 61): 0, (51, 3, 62): 0, (51, 3, 63): 0, (51, 3, 64): 0, (51, 3, 65): 0, (51, 3, 66): 0, (51, 3, 67): 0, (51, 3, 68): 0, (51, 3, 69): 0, (51, 4, 1): 0, (51, 4, 2): 0, (51, 4, 3): 0, (51, 4, 4): 0, (51, 4, 5): 0, (51, 4, 6): 0, (51, 4, 7): 0, (51, 4, 8): 0, (51, 4, 9): 0, (51, 4, 10): 0, (51, 4, 11): 0, (51, 4, 12): 0, (51, 4, 13): 1, (51, 4, 14): 1, (51, 4, 15): 1, (51, 4, 16): 1, (51, 4, 17): 0, (51, 4, 18): 1, (51, 4, 19): 1, (51, 4, 20): 1, (51, 4, 21): 0, (51, 4, 22): 0, (51, 4, 23): 0, (51, 4, 24): 0, (51, 4, 25): 0, (51, 4, 26): 0, (51, 4, 27): 0, (51, 4, 28): 0, (51, 4, 29): 0, (51, 4, 30): 0, (51, 4, 31): 0, (51, 4, 32): 0, (51, 4, 33): 0, (51, 4, 34): 0, (51, 4, 35): 0, (51, 4, 36): 0, (51, 4, 37): 0, (51, 4, 38): 0, (51, 4, 39): 0, (51, 4, 40): 0, (51, 4, 41): 0, (51, 4, 42): 0, (51, 4, 43): 0, (51, 4, 44): 0, (51, 4, 45): 0, (51, 4, 46): 0, (51, 4, 47): 0, (51, 4, 48): 0, (51, 4, 49): 0, (51, 4, 50): 0, (51, 4, 51): 0, (51, 4, 52): 0, (51, 4, 53): 0, (51, 4, 54): 0, (51, 4, 55): 0, (51, 4, 56): 0, (51, 4, 57): 0, (51, 4, 58): 0, (51, 4, 59): 0, (51, 4, 60): 0, (51, 4, 61): 0, (51, 4, 62): 0, (51, 4, 63): 0, (51, 4, 64): 0, (51, 4, 65): 0, (51, 4, 66): 0, (51, 4, 67): 0, (51, 4, 68): 0, (51, 4, 69): 0, (75, 1, 1): 0, (75, 1, 2): 0, (75, 1, 3): 0, (75, 1, 4): 0, (75, 1, 5): 0, (75, 1, 6): 0, (75, 1, 7): 0, (75, 1, 8): 1, (75, 1, 9): 1, (75, 1, 10): 1, (75, 1, 11): 1, (75, 1, 12): 1, (75, 1, 13): 1, (75, 1, 14): 0, (75, 1, 15): 1, (75, 1, 16): 0, (75, 1, 17): 0, (75, 1, 18): 0, (75, 1, 19): 0, (75, 1, 20): 0, (75, 1, 21): 0, (75, 1, 22): 0, (75, 1, 23): 0, (75, 1, 24): 0, (75, 1, 25): 0, (75, 1, 26): 0, (75, 1, 27): 0, (75, 1, 28): 0, (75, 1, 29): 0, (75, 1, 30): 0, (75, 1, 31): 0, (75, 1, 32): 0, (75, 1, 33): 0, (75, 1, 34): 0, (75, 1, 35): 0, (75, 1, 36): 0, (75, 1, 37): 0, (75, 1, 38): 0, (75, 1, 39): 0, (75, 1, 40): 0, (75, 1, 41): 0, (75, 1, 42): 0, (75, 1, 43): 0, (75, 1, 44): 0, (75, 1, 45): 0, (75, 1, 46): 0, (75, 1, 47): 0, (75, 1, 48): 0, (75, 1, 49): 0, (75, 1, 50): 0, (75, 1, 51): 0, (75, 1, 52): 0, (75, 1, 53): 0, (75, 1, 54): 0, (75, 1, 55): 0, (75, 1, 56): 0, (75, 1, 57): 0, (75, 1, 58): 0, (75, 1, 59): 0, (75, 1, 60): 0, (75, 1, 61): 0, (75, 1, 62): 0, (75, 1, 63): 0, (75, 1, 64): 0, (75, 1, 65): 0, (75, 1, 66): 0, (75, 1, 67): 0, (75, 1, 68): 0, (75, 1, 69): 0, (75, 2, 1): 0, (75, 2, 2): 0, (75, 2, 3): 0, (75, 2, 4): 0, (75, 2, 5): 0, (75, 2, 6): 0, (75, 2, 7): 0, (75, 2, 8): 0, (75, 2, 9): 0, (75, 2, 10): 0, (75, 2, 11): 0, (75, 2, 12): 0, (75, 2, 13): 0, (75, 2, 14): 0, (75, 2, 15): 0, (75, 2, 16): 0, (75, 2, 17): 0, (75, 2, 18): 0, (75, 2, 19): 0, (75, 2, 20): 0, (75, 2, 21): 0, (75, 2, 22): 0, (75, 2, 23): 0, (75, 2, 24): 0, (75, 2, 25): 0, (75, 2, 26): 0, (75, 2, 27): 0, (75, 2, 28): 0, (75, 2, 29): 0, (75, 2, 30): 0, (75, 2, 31): 0, (75, 2, 32): 0, (75, 2, 33): 0, (75, 2, 34): 0, (75, 2, 35): 0, (75, 2, 36): 0, (75, 2, 37): 0, (75, 2, 38): 0, (75, 2, 39): 0, (75, 2, 40): 0, (75, 2, 41): 0, (75, 2, 42): 0, (75, 2, 43): 0, (75, 2, 44): 0, (75, 2, 45): 0, (75, 2, 46): 0, (75, 2, 47): 0, (75, 2, 48): 0, (75, 2, 49): 0, (75, 2, 50): 0, (75, 2, 51): 0, (75, 2, 52): 0, (75, 2, 53): 0, (75, 2, 54): 0, (75, 2, 55): 0, (75, 2, 56): 0, (75, 2, 57): 0, (75, 2, 58): 0, (75, 2, 59): 0, (75, 2, 60): 0, (75, 2, 61): 0, (75, 2, 62): 0, (75, 2, 63): 0, (75, 2, 64): 0, (75, 2, 65): 0, (75, 2, 66): 0, (75, 2, 67): 0, (75, 2, 68): 0, (75, 2, 69): 0, (75, 3, 1): 0, (75, 3, 2): 0, (75, 3, 3): 0, (75, 3, 4): 0, (75, 3, 5): 0, (75, 3, 6): 0, (75, 3, 7): 0, (75, 3, 8): 0, (75, 3, 9): 0, (75, 3, 10): 0, (75, 3, 11): 0, (75, 3, 12): 0, (75, 3, 13): 0, (75, 3, 14): 0, (75, 3, 15): 0, (75, 3, 16): 0, (75, 3, 17): 0, (75, 3, 18): 0, (75, 3, 19): 0, (75, 3, 20): 0, (75, 3, 21): 0, (75, 3, 22): 0, (75, 3, 23): 0, (75, 3, 24): 0, (75, 3, 25): 0, (75, 3, 26): 0, (75, 3, 27): 0, (75, 3, 28): 0, (75, 3, 29): 0, (75, 3, 30): 0, (75, 3, 31): 0, (75, 3, 32): 0, (75, 3, 33): 0, (75, 3, 34): 0, (75, 3, 35): 0, (75, 3, 36): 0, (75, 3, 37): 0, (75, 3, 38): 0, (75, 3, 39): 0, (75, 3, 40): 0, (75, 3, 41): 0, (75, 3, 42): 0, (75, 3, 43): 0, (75, 3, 44): 0, (75, 3, 45): 0, (75, 3, 46): 0, (75, 3, 47): 0, (75, 3, 48): 0, (75, 3, 49): 0, (75, 3, 50): 0, (75, 3, 51): 0, (75, 3, 52): 0, (75, 3, 53): 0, (75, 3, 54): 0, (75, 3, 55): 0, (75, 3, 56): 0, (75, 3, 57): 0, (75, 3, 58): 0, (75, 3, 59): 0, (75, 3, 60): 0, (75, 3, 61): 0, (75, 3, 62): 0, (75, 3, 63): 0, (75, 3, 64): 0, (75, 3, 65): 0, (75, 3, 66): 0, (75, 3, 67): 0, (75, 3, 68): 0, (75, 3, 69): 0, (75, 4, 1): 0, (75, 4, 2): 0, (75, 4, 3): 0, (75, 4, 4): 0, (75, 4, 5): 0, (75, 4, 6): 0, (75, 4, 7): 0, (75, 4, 8): 0, (75, 4, 9): 0, (75, 4, 10): 0, (75, 4, 11): 0, (75, 4, 12): 0, (75, 4, 13): 0, (75, 4, 14): 0, (75, 4, 15): 0, (75, 4, 16): 0, (75, 4, 17): 0, (75, 4, 18): 0, (75, 4, 19): 0, (75, 4, 20): 0, (75, 4, 21): 0, (75, 4, 22): 0, (75, 4, 23): 0, (75, 4, 24): 0, (75, 4, 25): 0, (75, 4, 26): 0, (75, 4, 27): 0, (75, 4, 28): 0, (75, 4, 29): 0, (75, 4, 30): 0, (75, 4, 31): 0, (75, 4, 32): 0, (75, 4, 33): 0, (75, 4, 34): 0, (75, 4, 35): 0, (75, 4, 36): 0, (75, 4, 37): 0, (75, 4, 38): 0, (75, 4, 39): 0, (75, 4, 40): 0, (75, 4, 41): 0, (75, 4, 42): 0, (75, 4, 43): 0, (75, 4, 44): 0, (75, 4, 45): 0, (75, 4, 46): 0, (75, 4, 47): 0, (75, 4, 48): 0, (75, 4, 49): 0, (75, 4, 50): 0, (75, 4, 51): 0, (75, 4, 52): 0, (75, 4, 53): 0, (75, 4, 54): 0, (75, 4, 55): 0, (75, 4, 56): 0, (75, 4, 57): 0, (75, 4, 58): 0, (75, 4, 59): 0, (75, 4, 60): 0, (75, 4, 61): 0, (75, 4, 62): 0, (75, 4, 63): 0, (75, 4, 64): 0, (75, 4, 65): 0, (75, 4, 66): 0, (75, 4, 67): 0, (75, 4, 68): 0, (75, 4, 69): 0, (86, 1, 1): 0, (86, 1, 2): 0, (86, 1, 3): 0, (86, 1, 4): 0, (86, 1, 5): 0, (86, 1, 6): 0, (86, 1, 7): 0, (86, 1, 8): 0, (86, 1, 9): 0, (86, 1, 10): 0, (86, 1, 11): 0, (86, 1, 12): 0, (86, 1, 13): 0, (86, 1, 14): 0, (86, 1, 15): 0, (86, 1, 16): 0, (86, 1, 17): 0, (86, 1, 18): 0, (86, 1, 19): 0, (86, 1, 20): 0, (86, 1, 21): 0, (86, 1, 22): 0, (86, 1, 23): 0, (86, 1, 24): 0, (86, 1, 25): 0, (86, 1, 26): 0, (86, 1, 27): 0, (86, 1, 28): 0, (86, 1, 29): 0, (86, 1, 30): 0, (86, 1, 31): 0, (86, 1, 32): 0, (86, 1, 33): 0, (86, 1, 34): 0, (86, 1, 35): 0, (86, 1, 36): 0, (86, 1, 37): 0, (86, 1, 38): 0, (86, 1, 39): 0, (86, 1, 40): 0, (86, 1, 41): 0, (86, 1, 42): 0, (86, 1, 43): 0, (86, 1, 44): 0, (86, 1, 45): 0, (86, 1, 46): 0, (86, 1, 47): 0, (86, 1, 48): 0, (86, 1, 49): 0, (86, 1, 50): 0, (86, 1, 51): 0, (86, 1, 52): 0, (86, 1, 53): 0, (86, 1, 54): 0, (86, 1, 55): 0, (86, 1, 56): 0, (86, 1, 57): 0, (86, 1, 58): 0, (86, 1, 59): 0, (86, 1, 60): 0, (86, 1, 61): 0, (86, 1, 62): 0, (86, 1, 63): 0, (86, 1, 64): 0, (86, 1, 65): 0, (86, 1, 66): 0, (86, 1, 67): 0, (86, 1, 68): 0, (86, 1, 69): 0, (86, 2, 1): 0, (86, 2, 2): 0, (86, 2, 3): 0, (86, 2, 4): 0, (86, 2, 5): 0, (86, 2, 6): 0, (86, 2, 7): 0, (86, 2, 8): 0, (86, 2, 9): 0, (86, 2, 10): 0, (86, 2, 11): 0, (86, 2, 12): 0, (86, 2, 13): 0, (86, 2, 14): 0, (86, 2, 15): 0, (86, 2, 16): 0, (86, 2, 17): 0, (86, 2, 18): 0, (86, 2, 19): 0, (86, 2, 20): 0, (86, 2, 21): 0, (86, 2, 22): 0, (86, 2, 23): 0, (86, 2, 24): 0, (86, 2, 25): 0, (86, 2, 26): 0, (86, 2, 27): 0, (86, 2, 28): 0, (86, 2, 29): 0, (86, 2, 30): 0, (86, 2, 31): 0, (86, 2, 32): 0, (86, 2, 33): 0, (86, 2, 34): 0, (86, 2, 35): 0, (86, 2, 36): 0, (86, 2, 37): 0, (86, 2, 38): 0, (86, 2, 39): 0, (86, 2, 40): 0, (86, 2, 41): 0, (86, 2, 42): 0, (86, 2, 43): 0, (86, 2, 44): 0, (86, 2, 45): 0, (86, 2, 46): 0, (86, 2, 47): 0, (86, 2, 48): 0, (86, 2, 49): 0, (86, 2, 50): 0, (86, 2, 51): 0, (86, 2, 52): 0, (86, 2, 53): 0, (86, 2, 54): 0, (86, 2, 55): 0, (86, 2, 56): 0, (86, 2, 57): 0, (86, 2, 58): 0, (86, 2, 59): 0, (86, 2, 60): 0, (86, 2, 61): 0, (86, 2, 62): 0, (86, 2, 63): 0, (86, 2, 64): 0, (86, 2, 65): 0, (86, 2, 66): 0, (86, 2, 67): 0, (86, 2, 68): 0, (86, 2, 69): 0, (86, 3, 1): 0, (86, 3, 2): 0, (86, 3, 3): 0, (86, 3, 4): 0, (86, 3, 5): 0, (86, 3, 6): 0, (86, 3, 7): 0, (86, 3, 8): 0, (86, 3, 9): 0, (86, 3, 10): 0, (86, 3, 11): 0, (86, 3, 12): 0, (86, 3, 13): 0, (86, 3, 14): 0, (86, 3, 15): 0, (86, 3, 16): 0, (86, 3, 17): 0, (86, 3, 18): 0, (86, 3, 19): 0, (86, 3, 20): 0, (86, 3, 21): 0, (86, 3, 22): 0, (86, 3, 23): 0, (86, 3, 24): 0, (86, 3, 25): 0, (86, 3, 26): 0, (86, 3, 27): 0, (86, 3, 28): 0, (86, 3, 29): 0, (86, 3, 30): 0, (86, 3, 31): 0, (86, 3, 32): 0, (86, 3, 33): 0, (86, 3, 34): 0, (86, 3, 35): 0, (86, 3, 36): 0, (86, 3, 37): 0, (86, 3, 38): 0, (86, 3, 39): 0, (86, 3, 40): 0, (86, 3, 41): 0, (86, 3, 42): 0, (86, 3, 43): 0, (86, 3, 44): 0, (86, 3, 45): 0, (86, 3, 46): 0, (86, 3, 47): 0, (86, 3, 48): 0, (86, 3, 49): 0, (86, 3, 50): 0, (86, 3, 51): 0, (86, 3, 52): 0, (86, 3, 53): 0, (86, 3, 54): 0, (86, 3, 55): 0, (86, 3, 56): 0, (86, 3, 57): 0, (86, 3, 58): 0, (86, 3, 59): 0, (86, 3, 60): 0, (86, 3, 61): 0, (86, 3, 62): 0, (86, 3, 63): 0, (86, 3, 64): 0, (86, 3, 65): 0, (86, 3, 66): 0, (86, 3, 67): 0, (86, 3, 68): 0, (86, 3, 69): 0, (86, 4, 1): 0, (86, 4, 2): 0, (86, 4, 3): 0, (86, 4, 4): 0, (86, 4, 5): 0, (86, 4, 6): 0, (86, 4, 7): 1, (86, 4, 8): 1, (86, 4, 9): 1, (86, 4, 10): 0, (86, 4, 11): 1, (86, 4, 12): 1, (86, 4, 13): 0, (86, 4, 14): 0, (86, 4, 15): 0, (86, 4, 16): 0, (86, 4, 17): 0, (86, 4, 18): 0, (86, 4, 19): 0, (86, 4, 20): 0, (86, 4, 21): 0, (86, 4, 22): 0, (86, 4, 23): 0, (86, 4, 24): 0, (86, 4, 25): 0, (86, 4, 26): 0, (86, 4, 27): 0, (86, 4, 28): 0, (86, 4, 29): 0, (86, 4, 30): 0, (86, 4, 31): 0, (86, 4, 32): 0, (86, 4, 33): 0, (86, 4, 34): 0, (86, 4, 35): 0, (86, 4, 36): 0, (86, 4, 37): 0, (86, 4, 38): 0, (86, 4, 39): 0, (86, 4, 40): 0, (86, 4, 41): 0, (86, 4, 42): 0, (86, 4, 43): 0, (86, 4, 44): 0, (86, 4, 45): 0, (86, 4, 46): 0, (86, 4, 47): 0, (86, 4, 48): 0, (86, 4, 49): 0, (86, 4, 50): 0, (86, 4, 51): 0, (86, 4, 52): 0, (86, 4, 53): 0, (86, 4, 54): 0, (86, 4, 55): 0, (86, 4, 56): 0, (86, 4, 57): 0, (86, 4, 58): 0, (86, 4, 59): 0, (86, 4, 60): 0, (86, 4, 61): 0, (86, 4, 62): 0, (86, 4, 63): 0, (86, 4, 64): 0, (86, 4, 65): 0, (86, 4, 66): 0, (86, 4, 67): 0, (86, 4, 68): 0, (86, 4, 69): 0, (96, 1, 1): 0, (96, 1, 2): 0, (96, 1, 3): 0, (96, 1, 4): 0, (96, 1, 5): 0, (96, 1, 6): 0, (96, 1, 7): 0, (96, 1, 8): 0, (96, 1, 9): 0, (96, 1, 10): 0, (96, 1, 11): 0, (96, 1, 12): 0, (96, 1, 13): 0, (96, 1, 14): 0, (96, 1, 15): 0, (96, 1, 16): 0, (96, 1, 17): 0, (96, 1, 18): 0, (96, 1, 19): 0, (96, 1, 20): 0, (96, 1, 21): 0, (96, 1, 22): 0, (96, 1, 23): 0, (96, 1, 24): 0, (96, 1, 25): 0, (96, 1, 26): 0, (96, 1, 27): 0, (96, 1, 28): 0, (96, 1, 29): 0, (96, 1, 30): 0, (96, 1, 31): 0, (96, 1, 32): 0, (96, 1, 33): 0, (96, 1, 34): 0, (96, 1, 35): 0, (96, 1, 36): 0, (96, 1, 37): 0, (96, 1, 38): 0, (96, 1, 39): 0, (96, 1, 40): 0, (96, 1, 41): 0, (96, 1, 42): 0, (96, 1, 43): 0, (96, 1, 44): 0, (96, 1, 45): 0, (96, 1, 46): 0, (96, 1, 47): 0, (96, 1, 48): 0, (96, 1, 49): 0, (96, 1, 50): 0, (96, 1, 51): 0, (96, 1, 52): 0, (96, 1, 53): 0, (96, 1, 54): 0, (96, 1, 55): 0, (96, 1, 56): 0, (96, 1, 57): 0, (96, 1, 58): 0, (96, 1, 59): 0, (96, 1, 60): 0, (96, 1, 61): 0, (96, 1, 62): 0, (96, 1, 63): 0, (96, 1, 64): 0, (96, 1, 65): 0, (96, 1, 66): 0, (96, 1, 67): 0, (96, 1, 68): 0, (96, 1, 69): 0, (96, 2, 1): 0, (96, 2, 2): 0, (96, 2, 3): 0, (96, 2, 4): 0, (96, 2, 5): 0, (96, 2, 6): 0, (96, 2, 7): 0, (96, 2, 8): 0, (96, 2, 9): 0, (96, 2, 10): 0, (96, 2, 11): 0, (96, 2, 12): 0, (96, 2, 13): 0, (96, 2, 14): 0, (96, 2, 15): 0, (96, 2, 16): 0, (96, 2, 17): 0, (96, 2, 18): 0, (96, 2, 19): 0, (96, 2, 20): 0, (96, 2, 21): 0, (96, 2, 22): 0, (96, 2, 23): 0, (96, 2, 24): 0, (96, 2, 25): 0, (96, 2, 26): 0, (96, 2, 27): 0, (96, 2, 28): 0, (96, 2, 29): 0, (96, 2, 30): 0, (96, 2, 31): 0, (96, 2, 32): 0, (96, 2, 33): 0, (96, 2, 34): 0, (96, 2, 35): 0, (96, 2, 36): 0, (96, 2, 37): 0, (96, 2, 38): 0, (96, 2, 39): 0, (96, 2, 40): 0, (96, 2, 41): 0, (96, 2, 42): 0, (96, 2, 43): 0, (96, 2, 44): 0, (96, 2, 45): 0, (96, 2, 46): 0, (96, 2, 47): 0, (96, 2, 48): 0, (96, 2, 49): 0, (96, 2, 50): 0, (96, 2, 51): 0, (96, 2, 52): 0, (96, 2, 53): 0, (96, 2, 54): 0, (96, 2, 55): 0, (96, 2, 56): 0, (96, 2, 57): 0, (96, 2, 58): 0, (96, 2, 59): 0, (96, 2, 60): 0, (96, 2, 61): 0, (96, 2, 62): 0, (96, 2, 63): 0, (96, 2, 64): 0, (96, 2, 65): 0, (96, 2, 66): 0, (96, 2, 67): 0, (96, 2, 68): 0, (96, 2, 69): 0, (96, 3, 1): 0, (96, 3, 2): 0, (96, 3, 3): 0, (96, 3, 4): 0, (96, 3, 5): 0, (96, 3, 6): 0, (96, 3, 7): 0, (96, 3, 8): 0, (96, 3, 9): 0, (96, 3, 10): 0, (96, 3, 11): 0, (96, 3, 12): 0, (96, 3, 13): 0, (96, 3, 14): 0, (96, 3, 15): 0, (96, 3, 16): 0, (96, 3, 17): 0, (96, 3, 18): 0, (96, 3, 19): 0, (96, 3, 20): 0, (96, 3, 21): 0, (96, 3, 22): 0, (96, 3, 23): 0, (96, 3, 24): 1, (96, 3, 25): 1, (96, 3, 26): 1, (96, 3, 27): 0, (96, 3, 28): 0, (96, 3, 29): 0, (96, 3, 30): 0, (96, 3, 31): 0, (96, 3, 32): 0, (96, 3, 33): 0, (96, 3, 34): 0, (96, 3, 35): 0, (96, 3, 36): 0, (96, 3, 37): 0, (96, 3, 38): 0, (96, 3, 39): 0, (96, 3, 40): 0, (96, 3, 41): 0, (96, 3, 42): 0, (96, 3, 43): 0, (96, 3, 44): 0, (96, 3, 45): 0, (96, 3, 46): 0, (96, 3, 47): 0, (96, 3, 48): 0, (96, 3, 49): 0, (96, 3, 50): 0, (96, 3, 51): 0, (96, 3, 52): 0, (96, 3, 53): 0, (96, 3, 54): 0, (96, 3, 55): 0, (96, 3, 56): 0, (96, 3, 57): 0, (96, 3, 58): 0, (96, 3, 59): 0, (96, 3, 60): 0, (96, 3, 61): 0, (96, 3, 62): 0, (96, 3, 63): 0, (96, 3, 64): 0, (96, 3, 65): 0, (96, 3, 66): 0, (96, 3, 67): 0, (96, 3, 68): 0, (96, 3, 69): 0, (96, 4, 1): 0, (96, 4, 2): 0, (96, 4, 3): 0, (96, 4, 4): 0, (96, 4, 5): 0, (96, 4, 6): 0, (96, 4, 7): 0, (96, 4, 8): 0, (96, 4, 9): 0, (96, 4, 10): 0, (96, 4, 11): 0, (96, 4, 12): 0, (96, 4, 13): 0, (96, 4, 14): 0, (96, 4, 15): 0, (96, 4, 16): 0, (96, 4, 17): 0, (96, 4, 18): 0, (96, 4, 19): 0, (96, 4, 20): 0, (96, 4, 21): 0, (96, 4, 22): 0, (96, 4, 23): 0, (96, 4, 24): 0, (96, 4, 25): 0, (96, 4, 26): 0, (96, 4, 27): 0, (96, 4, 28): 0, (96, 4, 29): 0, (96, 4, 30): 0, (96, 4, 31): 0, (96, 4, 32): 0, (96, 4, 33): 0, (96, 4, 34): 0, (96, 4, 35): 0, (96, 4, 36): 0, (96, 4, 37): 0, (96, 4, 38): 0, (96, 4, 39): 0, (96, 4, 40): 0, (96, 4, 41): 0, (96, 4, 42): 0, (96, 4, 43): 0, (96, 4, 44): 0, (96, 4, 45): 0, (96, 4, 46): 0, (96, 4, 47): 0, (96, 4, 48): 0, (96, 4, 49): 0, (96, 4, 50): 0, (96, 4, 51): 0, (96, 4, 52): 0, (96, 4, 53): 0, (96, 4, 54): 0, (96, 4, 55): 0, (96, 4, 56): 0, (96, 4, 57): 0, (96, 4, 58): 0, (96, 4, 59): 0, (96, 4, 60): 0, (96, 4, 61): 0, (96, 4, 62): 0, (96, 4, 63): 0, (96, 4, 64): 0, (96, 4, 65): 0, (96, 4, 66): 0, (96, 4, 67): 0, (96, 4, 68): 0, (96, 4, 69): 0, (98, 1, 1): 1, (98, 1, 2): 1, (98, 1, 3): 1, (98, 1, 4): 1, (98, 1, 5): 1, (98, 1, 6): 1, (98, 1, 7): 0, (98, 1, 8): 0, (98, 1, 9): 0, (98, 1, 10): 0, (98, 1, 11): 0, (98, 1, 12): 0, (98, 1, 13): 0, (98, 1, 14): 0, (98, 1, 15): 0, (98, 1, 16): 0, (98, 1, 17): 0, (98, 1, 18): 0, (98, 1, 19): 0, (98, 1, 20): 0, (98, 1, 21): 0, (98, 1, 22): 0, (98, 1, 23): 0, (98, 1, 24): 0, (98, 1, 25): 0, (98, 1, 26): 0, (98, 1, 27): 0, (98, 1, 28): 0, (98, 1, 29): 0, (98, 1, 30): 0, (98, 1, 31): 0, (98, 1, 32): 0, (98, 1, 33): 0, (98, 1, 34): 0, (98, 1, 35): 0, (98, 1, 36): 0, (98, 1, 37): 0, (98, 1, 38): 0, (98, 1, 39): 0, (98, 1, 40): 0, (98, 1, 41): 0, (98, 1, 42): 0, (98, 1, 43): 0, (98, 1, 44): 0, (98, 1, 45): 0, (98, 1, 46): 0, (98, 1, 47): 0, (98, 1, 48): 0, (98, 1, 49): 0, (98, 1, 50): 0, (98, 1, 51): 0, (98, 1, 52): 0, (98, 1, 53): 0, (98, 1, 54): 0, (98, 1, 55): 0, (98, 1, 56): 0, (98, 1, 57): 0, (98, 1, 58): 0, (98, 1, 59): 0, (98, 1, 60): 0, (98, 1, 61): 0, (98, 1, 62): 0, (98, 1, 63): 0, (98, 1, 64): 0, (98, 1, 65): 0, (98, 1, 66): 0, (98, 1, 67): 0, (98, 1, 68): 0, (98, 1, 69): 0, (98, 2, 1): 0, (98, 2, 2): 0, (98, 2, 3): 0, (98, 2, 4): 0, (98, 2, 5): 0, (98, 2, 6): 0, (98, 2, 7): 0, (98, 2, 8): 0, (98, 2, 9): 0, (98, 2, 10): 0, (98, 2, 11): 0, (98, 2, 12): 0, (98, 2, 13): 0, (98, 2, 14): 0, (98, 2, 15): 0, (98, 2, 16): 0, (98, 2, 17): 0, (98, 2, 18): 0, (98, 2, 19): 0, (98, 2, 20): 0, (98, 2, 21): 0, (98, 2, 22): 0, (98, 2, 23): 0, (98, 2, 24): 0, (98, 2, 25): 0, (98, 2, 26): 0, (98, 2, 27): 0, (98, 2, 28): 0, (98, 2, 29): 0, (98, 2, 30): 0, (98, 2, 31): 0, (98, 2, 32): 0, (98, 2, 33): 0, (98, 2, 34): 0, (98, 2, 35): 0, (98, 2, 36): 0, (98, 2, 37): 0, (98, 2, 38): 0, (98, 2, 39): 0, (98, 2, 40): 0, (98, 2, 41): 0, (98, 2, 42): 0, (98, 2, 43): 0, (98, 2, 44): 0, (98, 2, 45): 0, (98, 2, 46): 0, (98, 2, 47): 0, (98, 2, 48): 0, (98, 2, 49): 0, (98, 2, 50): 0, (98, 2, 51): 0, (98, 2, 52): 0, (98, 2, 53): 0, (98, 2, 54): 0, (98, 2, 55): 0, (98, 2, 56): 0, (98, 2, 57): 0, (98, 2, 58): 0, (98, 2, 59): 0, (98, 2, 60): 0, (98, 2, 61): 0, (98, 2, 62): 0, (98, 2, 63): 0, (98, 2, 64):</t>
+  </si>
+  <si>
+    <t>{43: 5, 48: 4, 49: 9, 51: 8, 75: 8, 86: 6, 96: 3, 98: 6, 100: 2, 107: 2, 123: 5, 134: 5, 38: 7, 52: 10, 73: 4, 87: 4, 109: 5, 120: 5, 121: 6, 125: 2, 133: 8, 135: 6, 7: 18, 16: 3, 35: 10, 39: 9, 41: 9, 46: 11, 70: 10, 82: 10, 89: 6, 108: 11, 112: 6, 1: 12, 2: 16, 26: 14, 42: 9, 57: 11, 84: 7, 92: 5, 110: 9, 117: 8, 131: 8, 6: 26}</t>
   </si>
   <si>
     <t>{}</t>
   </si>
   <si>
-    <t>{15: 12, 16: 9, 20: 6, 23: 6, 24: 8, 25: 5, 26: 6, 30: 8, 31: 13, 38: 2, 39: 7, 40: 8, 41: 6, 43: 8, 50: 7, 59: 9, 60: 5, 62: 6, 63: 6, 65: 6, 66: 5, 67: 6, 70: 5, 71: 8, 75: 7, 77: 3, 78: 8, 79: 6, 81: 6, 82: 7, 2: 25, 3: 19, 4: 13, 9: 17, 21: 15, 22: 13, 28: 12, 36: 11, 37: 8, 73: 11}</t>
-  </si>
-  <si>
-    <t>{(11, 1): 0, (11, 2): 0, (11, 3): 0, (11, 4): 0, (11, 5): 1, (11, 6): 1, (11, 7): 1, (11, 8): 1, (11, 9): 1, (11, 10): 1, (11, 11): 0, (11, 12): 0, (11, 13): 0, (11, 14): 0, (11, 15): 0, (11, 16): 0, (11, 17): 0, (11, 18): 0, (11, 19): 0, (11, 20): 0, (11, 21): 0, (11, 22): 0, (11, 23): 0, (11, 24): 0, (11, 25): 0, (11, 26): 0, (11, 27): 0, (11, 28): 0, (11, 29): 0, (11, 30): 0, (11, 31): 0, (11, 32): 0, (11, 33): 0, (11, 34): 0, (11, 35): 0, (11, 36): 0, (11, 37): 0, (11, 38): 0, (11, 39): 0, (11, 40): 0, (11, 41): 0, (11, 42): 0, (29, 1): 0, (29, 2): 1, (29, 3): 1, (29, 4): 1, (29, 5): 0, (29, 6): 0, (29, 7): 0, (29, 8): 0, (29, 9): 0, (29, 10): 0, (29, 11): 0, (29, 12): 0, (29, 13): 0, (29, 14): 0, (29, 15): 0, (29, 16): 0, (29, 17): 0, (29, 18): 0, (29, 19): 0, (29, 20): 0, (29, 21): 0, (29, 22): 0, (29, 23): 0, (29, 24): 0, (29, 25): 0, (29, 26): 0, (29, 27): 0, (29, 28): 0, (29, 29): 0, (29, 30): 0, (29, 31): 0, (29, 32): 0, (29, 33): 0, (29, 34): 0, (29, 35): 0, (29, 36): 0, (29, 37): 0, (29, 38): 0, (29, 39): 0, (29, 40): 0, (29, 41): 0, (29, 42): 0, (47, 1): 0, (47, 2): 0, (47, 3): 0, (47, 4): 0, (47, 5): 1, (47, 6): 1, (47, 7): 1, (47, 8): 1, (47, 9): 1, (47, 10): 1, (47, 11): 1, (47, 12): 1, (47, 13): 0, (47, 14): 0, (47, 15): 0, (47, 16): 0, (47, 17): 0, (47, 18): 0, (47, 19): 0, (47, 20): 0, (47, 21): 0, (47, 22): 0, (47, 23): 0, (47, 24): 0, (47, 25): 0, (47, 26): 0, (47, 27): 0, (47, 28): 0, (47, 29): 0, (47, 30): 0, (47, 31): 0, (47, 32): 0, (47, 33): 0, (47, 34): 0, (47, 35): 0, (47, 36): 0, (47, 37): 0, (47, 38): 0, (47, 39): 0, (47, 40): 0, (47, 41): 0, (47, 42): 0, (53, 1): 0, (53, 2): 1, (53, 3): 1, (53, 4): 1, (53, 5): 1, (53, 6): 0, (53, 7): 0, (53, 8): 0, (53, 9): 0, (53, 10): 0, (53, 11): 0, (53, 12): 0, (53, 13): 0, (53, 14): 0, (53, 15): 0, (53, 16): 0, (53, 17): 0, (53, 18): 0, (53, 19): 0, (53, 20): 0, (53, 21): 0, (53, 22): 0, (53, 23): 0, (53, 24): 0, (53, 25): 0, (53, 26): 0, (53, 27): 0, (53, 28): 0, (53, 29): 0, (53, 30): 0, (53, 31): 0, (53, 32): 0, (53, 33): 0, (53, 34): 0, (53, 35): 0, (53, 36): 0, (53, 37): 0, (53, 38): 0, (53, 39): 0, (53, 40): 0, (53, 41): 0, (53, 42): 0}</t>
-  </si>
-  <si>
-    <t>{(11, 1): 0, (11, 2): 0, (11, 3): 0, (11, 4): 0, (11, 5): 0, (11, 6): 0, (11, 7): 0, (11, 8): 1, (11, 9): 1, (11, 10): 1, (11, 11): 1, (11, 12): 1, (11, 13): 1, (11, 14): 1, (11, 15): 1, (11, 16): 1, (11, 17): 1, (11, 18): 1, (11, 19): 1, (11, 20): 1, (11, 21): 1, (11, 22): 1, (11, 23): 1, (11, 24): 1, (11, 25): 1, (11, 26): 1, (11, 27): 1, (11, 28): 1, (11, 29): 1, (11, 30): 1, (11, 31): 1, (11, 32): 1, (11, 33): 1, (11, 34): 1, (11, 35): 1, (11, 36): 1, (11, 37): 1, (11, 38): 1, (11, 39): 1, (11, 40): 1, (11, 41): 1, (11, 42): 1, (29, 1): 0, (29, 2): 0, (29, 3): 0, (29, 4): 0, (29, 5): 0, (29, 6): 0, (29, 7): 0, (29, 8): 0, (29, 9): 0, (29, 10): 0, (29, 11): 0, (29, 12): 0, (29, 13): 0, (29, 14): 0, (29, 15): 0, (29, 16): 0, (29, 17): 0, (29, 18): 0, (29, 19): 0, (29, 20): 0, (29, 21): 0, (29, 22): 0, (29, 23): 0, (29, 24): 0, (29, 25): 0, (29, 26): 0, (29, 27): 0, (29, 28): 0, (29, 29): 0, (29, 30): 0, (29, 31): 0, (29, 32): 0, (29, 33): 0, (29, 34): 0, (29, 35): 0, (29, 36): 0, (29, 37): 0, (29, 38): 0, (29, 39): 0, (29, 40): 0, (29, 41): 0, (29, 42): 0, (47, 1): 0, (47, 2): 0, (47, 3): 0, (47, 4): 0, (47, 5): 0, (47, 6): 0, (47, 7): 1, (47, 8): 1, (47, 9): 1, (47, 10): 1, (47, 11): 1, (47, 12): 1, (47, 13): 1, (47, 14): 1, (47, 15): 1, (47, 16): 1, (47, 17): 1, (47, 18): 1, (47, 19): 1, (47, 20): 1, (47, 21): 1, (47, 22): 1, (47, 23): 1, (47, 24): 1, (47, 25): 1, (47, 26): 1, (47, 27): 1, (47, 28): 1, (47, 29): 1, (47, 30): 1, (47, 31): 1, (47, 32): 1, (47, 33): 1, (47, 34): 1, (47, 35): 1, (47, 36): 1, (47, 37): 1, (47, 38): 1, (47, 39): 1, (47, 40): 1, (47, 41): 1, (47, 42): 1, (53, 1): 0, (53, 2): 0, (53, 3): 0, (53, 4): 0, (53, 5): 0, (53, 6): 0, (53, 7): 0, (53, 8): 0, (53, 9): 0, (53, 10): 0, (53, 11): 0, (53, 12): 0, (53, 13): 0, (53, 14): 0, (53, 15): 0, (53, 16): 0, (53, 17): 0, (53, 18): 0, (53, 19): 0, (53, 20): 0, (53, 21): 0, (53, 22): 0, (53, 23): 0, (53, 24): 0, (53, 25): 0, (53, 26): 0, (53, 27): 0, (53, 28): 0, (53, 29): 0, (53, 30): 0, (53, 31): 0, (53, 32): 0, (53, 33): 0, (53, 34): 0, (53, 35): 0, (53, 36): 0, (53, 37): 0, (53, 38): 0, (53, 39): 0, (53, 40): 0, (53, 41): 0, (53, 42): 0}</t>
-  </si>
-  <si>
-    <t>{(11, 1): 0.0, (11, 2): 0.0, (11, 3): 0.0, (11, 4): 0.0, (11, 5): 0.5051001633268003, (11, 6): 0.5051001633268003, (11, 7): 0.5051001633268003, (11, 8): 0.5075500204164625, (11, 9): 0.5075500204164625, (11, 10): 0.5075500204164625, (11, 11): 0.0, (11, 12): 0.0, (11, 13): 0.0, (11, 14): 0.0, (11, 15): 0.0, (11, 16): 0.0, (11, 17): 0.0, (11, 18): 0.0, (11, 19): 0.0, (11, 20): 0.0, (11, 21): 0.0, (11, 22): 0.0, (11, 23): 0.0, (11, 24): 0.0, (11, 25): 0.0, (11, 26): 0.0, (11, 27): 0.0, (11, 28): 0.0, (11, 29): 0.0, (11, 30): 0.0, (11, 31): 0.0, (11, 32): 0.0, (11, 33): 0.0, (11, 34): 0.0, (11, 35): 0.0, (11, 36): 0.0, (11, 37): 0.0, (11, 38): 0.0, (11, 39): 0.0, (11, 40): 0.0, (11, 41): 0.0, (11, 42): 0.0, (29, 1): 0.0, (29, 2): 0.5051001633268003, (29, 3): 0.5051001633268003, (29, 4): 0.5051001633268003, (29, 5): 0.0, (29, 6): 0.0, (29, 7): 0.0, (29, 8): 0.0, (29, 9): 0.0, (29, 10): 0.0, (29, 11): 0.0, (29, 12): 0.0, (29, 13): 0.0, (29, 14): 0.0, (29, 15): 0.0, (29, 16): 0.0, (29, 17): 0.0, (29, 18): 0.0, (29, 19): 0.0, (29, 20): 0.0, (29, 21): 0.0, (29, 22): 0.0, (29, 23): 0.0, (29, 24): 0.0, (29, 25): 0.0, (29, 26): 0.0, (29, 27): 0.0, (29, 28): 0.0, (29, 29): 0.0, (29, 30): 0.0, (29, 31): 0.0, (29, 32): 0.0, (29, 33): 0.0, (29, 34): 0.0, (29, 35): 0.0, (29, 36): 0.0, (29, 37): 0.0, (29, 38): 0.0, (29, 39): 0.0, (29, 40): 0.0, (29, 41): 0.0, (29, 42): 0.0, (47, 1): 0.0, (47, 2): 0.0, (47, 3): 0.0, (47, 4): 0.0, (47, 5): 0.5051001633268003, (47, 6): 0.5051001633268003, (47, 7): 0.5075500204164625, (47, 8): 0.5075500204164625, (47, 9): 0.5075500204164625, (47, 10): 0.5075500204164625, (47, 11): 0.5075500204164625, (47, 12): 0.5075500204164625, (47, 13): 0.0, (47, 14): 0.0, (47, 15): 0.0, (47, 16): 0.0, (47, 17): 0.0, (47, 18): 0.0, (47, 19): 0.0, (47, 20): 0.0, (47, 21): 0.0, (47, 22): 0.0, (47, 23): 0.0, (47, 24): 0.0, (47, 25): 0.0, (47, 26): 0.0, (47, 27): 0.0, (47, 28): 0.0, (47, 29): 0.0, (47, 30): 0.0, (47, 31): 0.0, (47, 32): 0.0, (47, 33): 0.0, (47, 34): 0.0, (47, 35): 0.0, (47, 36): 0.0, (47, 37): 0.0, (47, 38): 0.0, (47, 39): 0.0, (47, 40): 0.0, (47, 41): 0.0, (47, 42): 0.0, (53, 1): 0.0, (53, 2): 0.5051001633268003, (53, 3): 0.5051001633268003, (53, 4): 0.5051001633268003, (53, 5): 0.5051001633268003, (53, 6): 0.0, (53, 7): 0.0, (53, 8): 0.0, (53, 9): 0.0, (53, 10): 0.0, (53, 11): 0.0, (53, 12): 0.0, (53, 13): 0.0, (53, 14): 0.0, (53, 15): 0.0, (53, 16): 0.0, (53, 17): 0.0, (53, 18): 0.0, (53, 19): 0.0, (53, 20): 0.0, (53, 21): 0.0, (53, 22): 0.0, (53, 23): 0.0, (53, 24): 0.0, (53, 25): 0.0, (53, 26): 0.0, (53, 27): 0.0, (53, 28): 0.0, (53, 29): 0.0, (53, 30): 0.0, (53, 31): 0.0, (53, 32): 0.0, (53, 33): 0.0, (53, 34): 0.0, (53, 35): 0.0, (53, 36): 0.0, (53, 37): 0.0, (53, 38): 0.0, (53, 39): 0.0, (53, 40): 0.0, (53, 41): 0.0, (53, 42): 0.0}</t>
-  </si>
-  <si>
-    <t>{(11, 1): 0.0, (11, 2): 0.0, (11, 3): 0.0, (11, 4): 0.0, (11, 5): 1.0, (11, 6): 2.0, (11, 7): 3.0, (11, 8): 3.5075500204164625, (11, 9): 4.5075500204164625, (11, 10): 5.5075500204164625, (11, 11): 5.5075500204164625, (11, 12): 5.5075500204164625, (11, 13): 5.5075500204164625, (11, 14): 5.5075500204164625, (11, 15): 5.5075500204164625, (11, 16): 5.5075500204164625, (11, 17): 5.5075500204164625, (11, 18): 5.5075500204164625, (11, 19): 5.5075500204164625, (11, 20): 5.5075500204164625, (11, 21): 5.5075500204164625, (11, 22): 5.5075500204164625, (11, 23): 5.5075500204164625, (11, 24): 5.5075500204164625, (11, 25): 5.5075500204164625, (11, 26): 5.5075500204164625, (11, 27): 5.5075500204164625, (11, 28): 5.5075500204164625, (11, 29): 5.5075500204164625, (11, 30): 5.5075500204164625, (11, 31): 5.5075500204164625, (11, 32): 5.5075500204164625, (11, 33): 5.5075500204164625, (11, 34): 5.5075500204164625, (11, 35): 5.5075500204164625, (11, 36): 5.5075500204164625, (11, 37): 5.5075500204164625, (11, 38): 5.5075500204164625, (11, 39): 5.5075500204164625, (11, 40): 5.5075500204164625, (11, 41): 5.5075500204164625, (11, 42): 5.5075500204164625, (29, 1): 0.0, (29, 2): 1.0, (29, 3): 2.0, (29, 4): 3.0, (29, 5): 3.0, (29, 6): 3.0, (29, 7): 3.0, (29, 8): 3.0, (29, 9): 3.0, (29, 10): 3.0, (29, 11): 3.0, (29, 12): 3.0, (29, 13): 3.0, (29, 14): 3.0, (29, 15): 3.0, (29, 16): 3.0, (29, 17): 3.0, (29, 18): 3.0, (29, 19): 3.0, (29, 20): 3.0, (29, 21): 3.0, (29, 22): 3.0, (29, 23): 3.0, (29, 24): 3.0, (29, 25): 3.0, (29, 26): 3.0, (29, 27): 3.0, (29, 28): 3.0, (29, 29): 3.0, (29, 30): 3.0, (29, 31): 3.0, (29, 32): 3.0, (29, 33): 3.0, (29, 34): 3.0, (29, 35): 3.0, (29, 36): 3.0, (29, 37): 3.0, (29, 38): 3.0, (29, 39): 3.0, (29, 40): 3.0, (29, 41): 3.0, (29, 42): 3.0, (47, 1): 0.0, (47, 2): 0.0, (47, 3): 0.0, (47, 4): 0.0, (47, 5): 1.0, (47, 6): 2.0, (47, 7): 2.5075500204164625, (47, 8): 3.5075500204164625, (47, 9): 4.5075500204164625, (47, 10): 5.5075500204164625, (47, 11): 6.5075500204164625, (47, 12): 7.5075500204164625, (47, 13): 7.5075500204164625, (47, 14): 7.5075500204164625, (47, 15): 7.5075500204164625, (47, 16): 7.5075500204164625, (47, 17): 7.5075500204164625, (47, 18): 7.5075500204164625, (47, 19): 7.5075500204164625, (47, 20): 7.5075500204164625, (47, 21): 7.5075500204164625, (47, 22): 7.5075500204164625, (47, 23): 7.5075500204164625, (47, 24): 7.5075500204164625, (47, 25): 7.5075500204164625, (47, 26): 7.5075500204164625, (47, 27): 7.5075500204164625, (47, 28): 7.5075500204164625, (47, 29): 7.5075500204164625, (47, 30): 7.5075500204164625, (47, 31): 7.5075500204164625, (47, 32): 7.5075500204164625, (47, 33): 7.5075500204164625, (47, 34): 7.5075500204164625, (47, 35): 7.5075500204164625, (47, 36): 7.5075500204164625, (47, 37): 7.5075500204164625, (47, 38): 7.5075500204164625, (47, 39): 7.5075500204164625, (47, 40): 7.5075500204164625, (47, 41): 7.5075500204164625, (47, 42): 7.5075500204164625, (53, 1): 0.0, (53, 2): 1.0, (53, 3): 2.0, (53, 4): 3.0, (53, 5): 4.0, (53, 6): 4.0, (53, 7): 4.0, (53, 8): 4.0, (53, 9): 4.0, (53, 10): 4.0, (53, 11): 4.0, (53, 12): 4.0, (53, 13): 4.0, (53, 14): 4.0, (53, 15): 4.0, (53, 16): 4.0, (53, 17): 4.0, (53, 18): 4.0, (53, 19): 4.0, (53, 20): 4.0, (53, 21): 4.0, (53, 22): 4.0, (53, 23): 4.0, (53, 24): 4.0, (53, 25): 4.0, (53, 26): 4.0, (53, 27): 4.0, (53, 28): 4.0, (53, 29): 4.0, (53, 30): 4.0, (53, 31): 4.0, (53, 32): 4.0, (53, 33): 4.0, (53, 34): 4.0, (53, 35): 4.0, (53, 36): 4.0, (53, 37): 4.0, (53, 38): 4.0, (53, 39): 4.0, (53, 40): 4.0, (53, 41): 4.0, (53, 42): 4.0}</t>
-  </si>
-  <si>
-    <t>{(11, 1): 0, (11, 2): 0, (11, 3): 0, (11, 4): 0, (11, 5): 0, (11, 6): 0, (11, 7): 0, (11, 8): 0, (11, 9): 0, (11, 10): 1, (11, 11): 0, (11, 12): 0, (11, 13): 0, (11, 14): 0, (11, 15): 0, (11, 16): 0, (11, 17): 0, (11, 18): 0, (11, 19): 0, (11, 20): 0, (11, 21): 0, (11, 22): 0, (11, 23): 0, (11, 24): 0, (11, 25): 0, (11, 26): 0, (11, 27): 0, (11, 28): 0, (11, 29): 0, (11, 30): 0, (11, 31): 0, (11, 32): 0, (11, 33): 0, (11, 34): 0, (11, 35): 0, (11, 36): 0, (11, 37): 0, (11, 38): 0, (11, 39): 0, (11, 40): 0, (11, 41): 0, (11, 42): 0, (29, 1): 0, (29, 2): 0, (29, 3): 0, (29, 4): 1, (29, 5): 0, (29, 6): 0, (29, 7): 0, (29, 8): 0, (29, 9): 0, (29, 10): 0, (29, 11): 0, (29, 12): 0, (29, 13): 0, (29, 14): 0, (29, 15): 0, (29, 16): 0, (29, 17): 0, (29, 18): 0, (29, 19): 0, (29, 20): 0, (29, 21): 0, (29, 22): 0, (29, 23): 0, (29, 24): 0, (29, 25): 0, (29, 26): 0, (29, 27): 0, (29, 28): 0, (29, 29): 0, (29, 30): 0, (29, 31): 0, (29, 32): 0, (29, 33): 0, (29, 34): 0, (29, 35): 0, (29, 36): 0, (29, 37): 0, (29, 38): 0, (29, 39): 0, (29, 40): 0, (29, 41): 0, (29, 42): 0, (47, 1): 0, (47, 2): 0, (47, 3): 0, (47, 4): 0, (47, 5): 0, (47, 6): 0, (47, 7): 0, (47, 8): 0, (47, 9): 0, (47, 10): 0, (47, 11): 0, (47, 12): 1, (47, 13): 0, (47, 14): 0, (47, 15): 0, (47, 16): 0, (47, 17): 0, (47, 18): 0, (47, 19): 0, (47, 20): 0, (47, 21): 0, (47, 22): 0, (47, 23): 0, (47, 24): 0, (47, 25): 0, (47, 26): 0, (47, 27): 0, (47, 28): 0, (47, 29): 0, (47, 30): 0, (47, 31): 0, (47, 32): 0, (47, 33): 0, (47, 34): 0, (47, 35): 0, (47, 36): 0, (47, 37): 0, (47, 38): 0, (47, 39): 0, (47, 40): 0, (47, 41): 0, (47, 42): 0, (53, 1): 0, (53, 2): 0, (53, 3): 0, (53, 4): 0, (53, 5): 1, (53, 6): 0, (53, 7): 0, (53, 8): 0, (53, 9): 0, (53, 10): 0, (53, 11): 0, (53, 12): 0, (53, 13): 0, (53, 14): 0, (53, 15): 0, (53, 16): 0, (53, 17): 0, (53, 18): 0, (53, 19): 0, (53, 20): 0, (53, 21): 0, (53, 22): 0, (53, 23): 0, (53, 24): 0, (53, 25): 0, (53, 26): 0, (53, 27): 0, (53, 28): 0, (53, 29): 0, (53, 30): 0, (53, 31): 0, (53, 32): 0, (53, 33): 0, (53, 34): 0, (53, 35): 0, (53, 36): 0, (53, 37): 0, (53, 38): 0, (53, 39): 0, (53, 40): 0, (53, 41): 0, (53, 42): 0}</t>
-  </si>
-  <si>
-    <t>{(11, 1): 0, (11, 2): 1, (11, 3): 0, (29, 1): 0, (29, 2): 1, (29, 3): 0, (47, 1): 1, (47, 2): 0, (47, 3): 0, (53, 1): 1, (53, 2): 0, (53, 3): 0}</t>
-  </si>
-  <si>
-    <t>{(2, 1): 0, (2, 2): 0, (2, 3): 0, (2, 4): 0, (2, 5): 0, (2, 6): 0, (2, 7): 0, (2, 8): 0, (2, 9): 0, (2, 10): 0, (2, 11): 0, (2, 12): 0, (2, 13): 0, (2, 14): 0, (2, 15): 0, (2, 16): 0, (2, 17): 1, (2, 18): 1, (2, 19): 1, (2, 20): 1, (2, 21): 1, (2, 22): 1, (2, 23): 1, (2, 24): 1, (2, 25): 1, (2, 26): 1, (2, 27): 1, (2, 28): 1, (2, 29): 1, (2, 30): 1, (2, 31): 1, (2, 32): 1, (2, 33): 1, (2, 34): 1, (2, 35): 1, (2, 36): 1, (2, 37): 1, (2, 38): 1, (2, 39): 1, (2, 40): 1, (2, 41): 1, (2, 42): 0, (3, 1): 0, (3, 2): 0, (3, 3): 0, (3, 4): 0, (3, 5): 0, (3, 6): 0, (3, 7): 0, (3, 8): 0, (3, 9): 0, (3, 10): 0, (3, 11): 0, (3, 12): 0, (3, 13): 0, (3, 14): 0, (3, 15): 0, (3, 16): 0, (3, 17): 1, (3, 18): 1, (3, 19): 1, (3, 20): 1, (3, 21): 1, (3, 22): 1, (3, 23): 1, (3, 24): 1, (3, 25): 1, (3, 26): 1, (3, 27): 1, (3, 28): 1, (3, 29): 1, (3, 30): 1, (3, 31): 1, (3, 32): 1, (3, 33): 1, (3, 34): 1, (3, 35): 1, (3, 36): 0, (3, 37): 0, (3, 38): 0, (3, 39): 0, (3, 40): 0, (3, 41): 0, (3, 42): 0, (4, 1): 0, (4, 2): 0, (4, 3): 0, (4, 4): 0, (4, 5): 0, (4, 6): 0, (4, 7): 0, (4, 8): 0, (4, 9): 0, (4, 10): 0, (4, 11): 0, (4, 12): 0, (4, 13): 0, (4, 14): 0, (4, 15): 0, (4, 16): 0, (4, 17): 0, (4, 18): 0, (4, 19): 0, (4, 20): 0, (4, 21): 0, (4, 22): 0, (4, 23): 0, (4, 24): 0, (4, 25): 0, (4, 26): 0, (4, 27): 0, (4, 28): 0, (4, 29): 0, (4, 30): 1, (4, 31): 1, (4, 32): 1, (4, 33): 1, (4, 34): 1, (4, 35): 1, (4, 36): 1, (4, 37): 1, (4, 38): 1, (4, 39): 1, (4, 40): 1, (4, 41): 1, (4, 42): 1, (9, 1): 0, (9, 2): 0, (9, 3): 0, (9, 4): 0, (9, 5): 0, (9, 6): 0, (9, 7): 0, (9, 8): 0, (9, 9): 0, (9, 10): 0, (9, 11): 0, (9, 12): 0, (9, 13): 0, (9, 14): 0, (9, 15): 0, (9, 16): 0, (9, 17): 0, (9, 18): 0, (9, 19): 0, (9, 20): 0, (9, 21): 0, (9, 22): 1, (9, 23): 1, (9, 24): 1, (9, 25): 1, (9, 26): 1, (9, 27): 1, (9, 28): 1, (9, 29): 1, (9, 30): 1, (9, 31): 1, (9, 32): 1, (9, 33): 1, (9, 34): 1, (9, 35): 1, (9, 36): 1, (9, 37): 1, (9, 38): 1, (9, 39): 0, (9, 40): 0, (9, 41): 0, (9, 42): 0, (15, 1): 0, (15, 2): 0, (15, 3): 0, (15, 4): 0, (15, 5): 0, (15, 6): 0, (15, 7): 0, (15, 8): 0, (15, 9): 0, (15, 10): 0, (15, 11): 0, (15, 12): 0, (15, 13): 0, (15, 14): 0, (15, 15): 0, (15, 16): 0, (15, 17): 0, (15, 18): 0, (15, 19): 0, (15, 20): 0, (15, 21): 0, (15, 22): 0, (15, 23): 0, (15, 24): 0, (15, 25): 0, (15, 26): 0, (15, 27): 0, (15, 28): 0, (15, 29): 0, (15, 30): 1, (15, 31): 1, (15, 32): 1, (15, 33): 1, (15, 34): 1, (15, 35): 1, (15, 36): 1, (15, 37): 1, (15, 38): 1, (15, 39): 1, (15, 40): 1, (15, 41): 1, (15, 42): 0, (16, 1): 0, (16, 2): 0, (16, 3): 0, (16, 4): 0, (16, 5): 0, (16, 6): 0, (16, 7): 0, (16, 8): 0, (16, 9): 0, (16, 10): 0, (16, 11): 1, (16, 12): 1, (16, 13): 1, (16, 14): 1, (16, 15): 1, (16, 16): 1, (16, 17): 1, (16, 18): 1, (16, 19): 1, (16, 20): 0, (16, 21): 0, (16, 22): 0, (16, 23): 0, (16, 24): 0, (16, 25): 0, (16, 26): 0, (16, 27): 0, (16, 28): 0, (16, 29): 0, (16, 30): 0, (16, 31): 0, (16, 32): 0, (16, 33): 0, (16, 34): 0, (16, 35): 0, (16, 36): 0, (16, 37): 0, (16, 38): 0, (16, 39): 0, (16, 40): 0, (16, 41): 0, (16, 42): 0, (20, 1): 0, (20, 2): 0, (20, 3): 0, (20, 4): 0, (20, 5): 0, (20, 6): 0, (20, 7): 0, (20, 8): 0, (20, 9): 0, (20, 10): 0, (20, 11): 0, (20, 12): 0, (20, 13): 0, (20, 14): 0, (20, 15): 0, (20, 16): 0, (20, 17): 0, (20, 18): 0, (20, 19): 0, (20, 20): 0, (20, 21): 0, (20, 22): 0, (20, 23): 0, (20, 24): 0, (20, 25): 0, (20, 26): 0, (20, 27): 0, (20, 28): 0, (20, 29): 0, (20, 30): 0, (20, 31): 0, (20, 32): 1, (20, 33): 1, (20, 34): 1, (20, 35): 1, (20, 36): 1, (20, 37): 1, (20, 38): 0, (20, 39): 0, (20, 40): 0, (20, 41): 0, (20, 42): 0, (21, 1): 0, (21, 2): 0, (21, 3): 0, (21, 4): 0, (21, 5): 0, (21, 6): 0, (21, 7): 0, (21, 8): 0, (21, 9): 0, (21, 10): 0, (21, 11): 0, (21, 12): 0, (21, 13): 0, (21, 14): 0, (21, 15): 0, (21, 16): 0, (21, 17): 0, (21, 18): 0, (21, 19): 0, (21, 20): 0, (21, 21): 0, (21, 22): 0, (21, 23): 0, (21, 24): 0, (21, 25): 0, (21, 26): 0, (21, 27): 1, (21, 28): 1, (21, 29): 1, (21, 30): 1, (21, 31): 1, (21, 32): 1, (21, 33): 1, (21, 34): 1, (21, 35): 1, (21, 36): 1, (21, 37): 1, (21, 38): 1, (21, 39): 1, (21, 40): 1, (21, 41): 1, (21, 42): 0, (22, 1): 0, (22, 2): 0, (22, 3): 0, (22, 4): 0, (22, 5): 0, (22, 6): 0, (22, 7): 0, (22, 8): 0, (22, 9): 0, (22, 10): 0, (22, 11): 0, (22, 12): 0, (22, 13): 0, (22, 14): 0, (22, 15): 0, (22, 16): 0, (22, 17): 0, (22, 18): 0, (22, 19): 0, (22, 20): 0, (22, 21): 0, (22, 22): 0, (22, 23): 0, (22, 24): 0, (22, 25): 0, (22, 26): 0, (22, 27): 1, (22, 28): 1, (22, 29): 1, (22, 30): 1, (22, 31): 1, (22, 32): 1, (22, 33): 1, (22, 34): 1, (22, 35): 1, (22, 36): 1, (22, 37): 1, (22, 38): 1, (22, 39): 1, (22, 40): 0, (22, 41): 0, (22, 42): 0, (23, 1): 0, (23, 2): 0, (23, 3): 0, (23, 4): 0, (23, 5): 0, (23, 6): 0, (23, 7): 0, (23, 8): 0, (23, 9): 0, (23, 10): 0, (23, 11): 0, (23, 12): 0, (23, 13): 0, (23, 14): 0, (23, 15): 0, (23, 16): 0, (23, 17): 0, (23, 18): 0, (23, 19): 0, (23, 20): 0, (23, 21): 0, (23, 22): 0, (23, 23): 0, (23, 24): 0, (23, 25): 0, (23, 26): 0, (23, 27): 0, (23, 28): 0, (23, 29): 1, (23, 30): 1, (23, 31): 1, (23, 32): 1, (23, 33): 1, (23, 34): 1, (23, 35): 0, (23, 36): 0, (23, 37): 0, (23, 38): 0, (23, 39): 0, (23, 40): 0, (23, 41): 0, (23, 42): 0, (24, 1): 0, (24, 2): 0, (24, 3): 0, (24, 4): 0, (24, 5): 0, (24, 6): 0, (24, 7): 0, (24, 8): 0, (24, 9): 0, (24, 10): 0, (24, 11): 0, (24, 12): 0, (24, 13): 0, (24, 14): 0, (24, 15): 0, (24, 16): 0, (24, 17): 0, (24, 18): 0, (24, 19): 0, (24, 20): 0, (24, 21): 0, (24, 22): 1, (24, 23): 1, (24, 24): 1, (24, 25): 1, (24, 26): 1, (24, 27): 1, (24, 28): 1, (24, 29): 1, (24, 30): 0, (24, 31): 0, (24, 32): 0, (24, 33): 0, (24, 34): 0, (24, 35): 0, (24, 36): 0, (24, 37): 0, (24, 38): 0, (24, 39): 0, (24, 40): 0, (24, 41): 0, (24, 42): 0, (25, 1): 0, (25, 2): 0, (25, 3): 0, (25, 4): 0, (25, 5): 0, (25, 6): 0, (25, 7): 0, (25, 8): 0, (25, 9): 0, (25, 10): 0, (25, 11): 0, (25, 12): 0, (25, 13): 0, (25, 14): 0, (25, 15): 0, (25, 16): 0, (25, 17): 0, (25, 18): 0, (25, 19): 0, (25, 20): 0, (25, 21): 0, (25, 22): 0, (25, 23): 0, (25, 24): 0, (25, 25): 0, (25, 26): 0, (25, 27): 0, (25, 28): 0, (25, 29): 0, (25, 30): 0, (25, 31): 0, (25, 32): 0, (25, 33): 0, (25, 34): 0, (25, 35): 0, (25, 36): 0, (25, 37): 0, (25, 38): 1, (25, 39): 1, (25, 40): 1, (25, 41): 1, (25, 42): 1, (26, 1): 0, (26, 2): 0, (26, 3): 0, (26, 4): 0, (26, 5): 0, (26, 6): 0, (26, 7): 0, (26, 8): 0, (26, 9): 0, (26, 10): 0, (26, 11): 0, (26, 12): 0, (26, 13): 0, (26, 14): 0, (26, 15): 0, (26, 16): 0, (26, 17): 0, (26, 18): 0, (26, 19): 0, (26, 20): 0, (26, 21): 0, (26, 22): 0, (26, 23): 0, (26, 24): 0, (26, 25): 0, (26, 26): 1, (26, 27): 1, (26, 28): 1, (26, 29): 1, (26, 30): 1, (26, 31): 1, (26, 32): 0, (26, 33): 0, (26, 34): 0, (26, 35): 0, (26, 36): 0, (26, 37): 0, (26, 38): 0, (26, 39): 0, (26, 40): 0, (26, 41): 0, (26, 42): 0, (28, 1): 0, (28, 2): 0, (28, 3): 0, (28, 4): 0, (28, 5): 0, (28, 6): 0, (28, 7): 0, (28, 8): 0, (28, 9): 0, (28, 10): 0, (28, 11): 0, (28, 12): 0, (28, 13): 0, (28, 14): 0, (28, 15): 0, (28, 16): 0, (28, 17): 0, (28, 18): 0, (28, 19): 0, (28, 20): 0, (28, 21): 0, (28, 22): 0, (28, 23): 0, (28, 24): 0, (28, 25): 0, (28, 26): 0, (28, 27): 0, (28, 28): 0, (28, 29): 0, (28, 30): 1, (28, 31): 1, (28, 32): 1, (28, 33): 1, (28, 34): 1, (28, 35): 1, (28, 36): 1, (28, 37): 1, (28, 38): 1, (28, 39): 1, (28, 40): 1, (28, 41): 1, (28, 42): 0, (30, 1): 0, (30, 2): 0, (30, 3): 0, (30, 4): 0, (30, 5): 0, (30, 6): 0, (30, 7): 0, (30, 8): 0, (30, 9): 0, (30, 10): 0, (30, 11): 0, (30, 12): 0, (30, 13): 0, (30, 14): 0, (30, 15): 0, (30, 16): 0, (30, 17): 0, (30, 18): 0, (30, 19): 0, (30, 20): 0, (30, 21): 0, (30, 22): 0, (30, 23): 1, (30, 24): 1, (30, 25): 1, (30, 26): 1, (30, 27): 1, (30, 28): 1, (30, 29): 1, (30, 30): 1, (30, 31): 0, (30, 32): 0, (30, 33): 0, (30, 34): 0, (30, 35): 0, (30, 36): 0, (30, 37): 0, (30, 38): 0, (30, 39): 0, (30, 40): 0, (30, 41): 0, (30, 42): 0, (31, 1): 0, (31, 2): 0, (31, 3): 0, (31, 4): 0, (31, 5): 0, (31, 6): 0, (31, 7): 0, (31, 8): 1, (31, 9): 1, (31, 10): 1, (31, 11): 1, (31, 12): 1, (31, 13): 1, (31, 14): 1, (31, 15): 1, (31, 16): 1, (31, 17): 1, (31, 18): 1, (31, 19): 1, (31, 20): 1, (31, 21): 0, (31, 22): 0, (31, 23): 0, (31, 24): 0, (31, 25): 0, (31, 26): 0, (31, 27): 0, (31, 28): 0, (31, 29): 0, (31, 30): 0, (31, 31): 0, (31, 32): 0, (31, 33): 0, (31, 34): 0, (31, 35): 0, (31, 36): 0, (31, 37): 0, (31, 38): 0, (31, 39): 0, (31, 40): 0, (31, 41): 0, (31, 42): 0, (36, 1): 0, (36, 2): 0, (36, 3): 0, (36, 4): 0, (36, 5): 0, (36, 6): 0, (36, 7): 0, (36, 8): 0, (36, 9): 0, (36, 10): 0, (36, 11): 0, (36, 12): 0, (36, 13): 0, (36, 14): 0, (36, 15): 0, (36, 16): 0, (36, 17): 0, (36, 18): 0, (36, 19): 0, (36, 20): 0, (36, 21): 0, (36, 22): 0, (36, 23): 0, (36, 24): 0, (36, 25): 0, (36, 26): 0, (36, 27): 0, (36, 28): 1, (36, 29): 1, (36, 30): 1, (36, 31): 1, (36, 32): 1, (36, 33): 1, (36, 34): 1, (36, 35): 1, (36, 36): 1, (36, 37): 1, (36, 38): 1, (36, 39): 0, (36, 40): 0, (36, 41): 0, (36, 42): 0, (37, 1): 0, (37, 2): 0, (37, 3): 0, (37, 4): 0, (37, 5): 0, (37, 6): 0, (37, 7): 0, (37, 8): 0, (37, 9): 0, (37, 10): 0, (37, 11): 0, (37, 12): 0, (37, 13): 0, (37, 14): 0, (37, 15): 0, (37, 16): 0, (37, 17): 0, (37, 18): 0, (37, 19): 0, (37, 20): 0, (37, 21): 0, (37, 22): 0, (37, 23): 0, (37, 24): 0, (37, 25): 0, (37, 26): 1, (37, 27): 1, (37, 28): 1, (37, 29): 1, (37, 30): 1, (37, 31): 1, (37, 32): 1, (37, 33): 1, (37, 34): 0, (37, 35): 0, (37, 36): 0, (37, 37): 0, (37, 38): 0, (37, 39): 0, (37, 40): 0, (37, 41): 0, (37, 42): 0, (38, 1): 0, (38, 2): 0, (38, 3): 0, (38, 4): 0, (38, 5): 0, (38, 6): 0, (38, 7): 0, (38, 8): 0, (38, 9): 0, (38, 10): 0, (38, 11): 0, (38, 12): 0, (38, 13): 0, (38, 14): 0, (38, 15): 0, (38, 16): 0, (38, 17): 0, (38, 18): 0, (38, 19): 0, (38, 20): 0, (38, 21): 0, (38, 22): 0, (38, 23): 0, (38, 24): 0, (38, 25): 0, (38, 26): 0, (38, 27): 0, (38, 28): 0, (38, 29): 0, (38, 30): 0, (38, 31): 0, (38, 32): 0, (38, 33): 0, (38, 34): 0, (38, 35): 0, (38, 36): 0, (38, 37): 0, (38, 38): 0, (38, 39): 0, (38, 40): 0, (38, 41): 1, (38, 42): 1, (39, 1): 0, (39, 2): 0, (39, 3): 0, (39, 4): 0, (39, 5): 0, (39, 6): 0, (39, 7): 0, (39, 8): 0, (39, 9): 0, (39, 10): 0, (39, 11): 0, (39, 12): 0, (39, 13): 0, (39, 14): 0, (39, 15): 0, (39, 16): 0, (39, 17): 0, (39, 18): 1, (39, 19): 1, (39, 20): 1, (39, 21): 1, (39, 22): 1, (39, 23): 1, (39, 24): 1, (39, 25): 0, (39, 26): 0, (39, 27): 0, (39, 28): 0, (39, 29): 0, (39, 30): 0, (39, 31): 0, (39, 32): 0, (39, 33): 0, (39, 34): 0, (39, 35): 0, (39, 36): 0, (39, 37): 0, (39, 38): 0, (39, 39): 0, (39, 40): 0, (39, 41): 0, (39, 42): 0, (40, 1): 0, (40, 2): 0, (40, 3): 0, (40, 4): 0, (40, 5): 0, (40, 6): 0, (40, 7): 0, (40, 8): 1, (40, 9): 1, (40, 10): 1, (40, 11): 1, (40, 12): 1, (40, 13): 1, (40, 14): 1, (40, 15): 1, (40, 16): 0, (40, 17): 0, (40, 18): 0, (40, 19): 0, (40, 20): 0, (40, 21): 0, (40, 22): 0, (40, 23): 0, (40, 24): 0, (40, 25): 0, (40, 26): 0, (40, 27): 0, (40, 28): 0, (40, 29): 0, (40, 30): 0, (40, 31): 0, (40, 32): 0, (40, 33): 0, (40, 34): 0, (40, 35): 0, (40, 36): 0, (40, 37): 0, (40, 38): 0, (40, 39): 0, (40, 40): 0, (40, 41): 0, (40, 42): 0, (41, 1): 0, (41, 2): 0, (41, 3): 0, (41, 4): 0, (41, 5): 0, (41, 6): 0, (41, 7): 0, (41, 8): 0, (41, 9): 0, (41, 10): 0, (41, 11): 0, (41, 12): 0, (41, 13): 0, (41, 14): 0, (41, 15): 0, (41, 16): 0, (41, 17): 0, (41, 18): 0, (41, 19): 0, (41, 20): 0, (41, 21): 0, (41, 22): 0, (41, 23): 1, (41, 24): 1, (41, 25): 1, (41, 26): 1, (41, 27): 1, (41, 28): 1, (41, 29): 0, (41, 30): 0, (41, 31): 0, (41, 32): 0, (41, 33): 0, (41, 34): 0, (41, 35): 0, (41, 36): 0, (41, 37): 0, (41, 38): 0, (41, 39): 0, (41, 40): 0, (41, 41): 0, (41, 42): 0, (43, 1): 0, (43, 2): 0, (43, 3): 0, (43, 4): 0, (43, 5): 0, (43, 6): 0, (43, 7): 0, (43, 8): 0, (43, 9): 0, (43, 10): 0, (43, 11): 0, (43, 12): 0, (43, 13): 0, (43, 14): 0, (43, 15): 0, (43, 16): 0, (43, 17): 1, (43, 18): 1, (43, 19): 1, (43, 20): 1, (43, 21): 1, (43, 22): 1, (43, 23): 1, (43, 24): 1, (43, 25): 0, (43, 26): 0, (43, 27): 0, (43, 28): 0, (43, 29): 0, (43, 30): 0, (43, 31): 0, (43, 32): 0, (43, 33): 0, (43, 34): 0, (43, 35): 0, (43, 36): 0, (43, 37): 0, (43, 38): 0, (43, 39): 0, (43, 40): 0, (43, 41): 0, (43, 42): 0, (50, 1): 0, (50, 2): 0, (50, 3): 0, (50, 4): 0, (50, 5): 0, (50, 6): 0, (50, 7): 0, (50, 8): 0, (50, 9): 0, (50, 10): 0, (50, 11): 1, (50, 12): 1, (50, 13): 1, (50, 14): 1, (50, 15): 1, (50, 16): 1, (50, 17): 1, (50, 18): 0, (50, 19): 0, (50, 20): 0, (50, 21): 0, (50, 22): 0, (50, 23): 0, (50, 24): 0, (50, 25): 0, (50, 26): 0, (50, 27): 0, (50, 28): 0, (50, 29): 0, (50, 30): 0, (50, 31): 0, (50, 32): 0, (50, 33): 0, (50, 34): 0, (50, 35): 0, (50, 36): 0, (50, 37): 0, (50, 38): 0, (50, 39): 0, (50, 40): 0, (50, 41): 0, (50, 42): 0, (59, 1): 0, (59, 2): 0, (59, 3): 0, (59, 4): 0, (59, 5): 0, (59, 6): 0, (59, 7): 0, (59, 8): 0, (59, 9): 0, (59, 10): 0, (59, 11): 0, (59, 12): 0, (59, 13): 0, (59, 14): 0, (59, 15): 1, (59, 16): 1, (59, 17): 1, (59, 18): 1, (59, 19): 1, (59, 20): 1, (59, 21): 1, (59, 22): 1, (59, 23): 1, (59, 24): 0, (59, 25): 0, (59, 26): 0, (59, 27): 0, (59, 28): 0, (59, 29): 0, (59, 30): 0, (59, 31): 0, (59, 32): 0, (59, 33): 0, (59, 34): 0, (59, 35): 0, (59, 36): 0, (59, 37): 0, (59, 38): 0, (59, 39): 0, (59, 40): 0, (59, 41): 0, (59, 42): 0, (60, 1): 0, (60, 2): 0, (60, 3): 0, (60, 4): 0, (60, 5): 0, (60, 6): 0, (60, 7): 0, (60, 8): 0, (60, 9): 0, (60, 10): 0, (60, 11): 0, (60, 12): 0, (60, 13): 0, (60, 14): 0, (60, 15): 0, (60, 16): 0, (60, 17): 0, (60, 18): 0, (60, 19): 0, (60, 20): 0, (60, 21): 0, (60, 22): 0, (60, 23): 0, (60, 24): 0, (60, 25): 0, (60, 26): 0, (60, 27): 0, (60, 28): 0, (60, 29): 0, (60, 30): 0, (60, 31): 0, (60, 32): 0, (60, 33): 0, (60, 34): 0, (60, 35): 0, (60, 36): 0, (60, 37): 0, (60, 38): 1, (60, 39): 1, (60, 40): 1, (60, 41): 1, (60, 42): 1, (62, 1): 0, (62, 2): 0, (62, 3): 0, (62, 4): 0, (62, 5): 0, (62, 6): 0, (62, 7): 0, (62, 8): 0, (62, 9): 0, (62, 10): 0, (62, 11): 0, (62, 12): 0, (62, 13): 0, (62, 14): 0, (62, 15): 0, (62, 16): 0, (62, 17): 0, (62, 18): 0, (62, 19): 0, (62, 20): 1, (62, 21): 1, (62, 22): 1, (62, 23): 1, (62, 24): 1, (62, 25): 1, (62, 26): 0, (62, 27): 0, (62, 28): 0, (62, 29): 0, (62, 30): 0, (62, 31): 0, (62, 32): 0, (62, 33): 0, (62, 34): 0, (62, 35): 0, (62, 36): 0, (62, 37): 0, (62, 38): 0, (62, 39): 0, (62, 40): 0, (62, 41): 0, (62, 42): 0, (63, 1): 0, (63, 2): 0, (63, 3): 0, (63, 4): 0, (63, 5): 0, (63, 6): 0, (63, 7): 0, (63, 8): 0, (63, 9): 0, (63, 10): 0, (63, 11): 0, (63, 12): 0, (63, 13): 0, (63, 14): 0, (63, 15): 0, (63, 16): 0, (63, 17): 0, (63, 18): 0, (63, 19): 0, (63, 20): 0, (63, 21): 0, (63, 22): 0, (63, 23): 0, (63, 24): 0, (63, 25): 0, (63, 26): 0, (63, 27): 0, (63, 28): 0, (63, 29): 0, (63, 30): 0, (63, 31): 0, (63, 32): 0, (63, 33): 0, (63, 34): 0, (63, 35): 0, (63, 36): 0, (63, 37): 1, (63, 38): 1, (63, 39): 1, (63, 40): 1, (63, 41): 1, (63, 42): 1, (65, 1): 0, (65, 2): 0, (65, 3): 0, (65, 4): 0, (65, 5): 0, (65, 6): 0, (65, 7): 0, (65, 8): 0, (65, 9): 0, (65, 10): 0, (65, 11): 0, (65, 12): 0, (65, 13): 0, (65, 14): 0, (65, 15): 0, (65, 16): 0, (65, 17): 0, (65, 18): 0, (65, 19): 0, (65, 20): 0, (65, 21): 0, (65, 22): 0, (65, 23): 0, (65, 24): 0, (65, 25): 0, (65, 26): 0, (65, 27): 1, (65, 28): 1, (65, 29): 1, (65, 30): 1, (65, 31): 1, (65, 32): 1, (65, 33): 0, (65, 34): 0, (65, 35): 0, (65, 36): 0, (65, 37): 0, (65, 38): 0, (65, 39): 0, (65, 40): 0, (65, 41): 0, (65, 42): 0, (66, 1): 0, (66, 2): 0, (66, 3): 0, (66, 4): 0, (66, 5): 0, (66, 6): 0, (66, 7): 0, (66, 8): 0, (66, 9): 0, (66, 10): 0, (66, 11): 0, (66, 12): 0, (66, 13): 0, (66, 14): 0, (66, 15): 0, (66, 16): 0, (66, 17): 0, (66, 18): 0, (66, 19): 0, (66, 20): 0, (66, 21): 0, (66, 22): 0, (66, 23): 0, (66, 24): 0, (66, 25): 0, (66, 26): 0, (66, 27): 0, (66, 28): 0, (66, 29): 0, (66, 30): 1, (66, 31): 1, (66, 32): 1, (66, 33): 1, (66, 34): 1, (66, 35): 0, (66, 36): 0, (66, 37): 0, (66, 38): 0, (66, 39): 0, (66, 40): 0, (66, 41): 0, (66, 42): 0, (67, 1): 0, (67, 2): 0, (67, 3): 0, (67, 4): 0, (67, 5): 0, (67, 6): 0, (67, 7): 0, (67, 8): 0, (67, 9): 0, (67, 10): 0, (67, 11): 0, (67, 12): 0, (67, 13): 0, (67, 14): 1, (67, 15): 1, (67, 16): 1, (67, 17): 1, (67, 18): 1, (67, 19): 1, (67, 20): 0, (67, 21): 0, (67, 22): 0, (67, 23): 0, (67, 24): 0, (67, 25): 0, (67, 26): 0, (67, 27): 0, (67, 28): 0, (67, 29): 0, (67, 30): 0, (67, 31): 0, (67, 32): 0, (67, 33): 0, (67, 34): 0, (67, 35): 0, (67, 36): 0, (67, 37): 0, (67, 38): 0, (67, 39): 0, (67, 40): 0, (67, 41): 0, (67, 42): 0, (70, 1): 0, (70, 2): 0, (70, 3): 0, (70, 4): 0, (70, 5): 0, (70, 6): 0, (70, 7): 0, (70, 8): 0, (70, 9): 0, (70, 10): 0, (70, 11): 0, (70, 12): 0, (70, 13): 0, (70, 14): 0, (70, 15): 0, (70, 16): 0, (70, 17): 0, (70, 18): 0, (70, 19): 0, (70, 20): 0, (70, 21): 0, (70, 22): 0, (70, 23): 0, (70, 24): 0, (70, 25): 0, (70, 26): 0, (70, 27): 0, (70, 28): 0, (70, 29): 0, (70, 30): 0, (70, 31): 0, (70, 32): 1, (70, 33): 1, (70, 34): 1, (70, 35): 1, (70, 36): 1, (70, 37): 0, (70, 38): 0, (70, 39): 0, (70, 40): 0, (70, 41): 0, (70, 42): 0, (71, 1): 0, (71, 2): 0, (71, 3): 0, (71, 4): 0, (71, 5): 0, (71, 6): 0, (71, 7): 0, (71, 8): 0, (71, 9): 0, (71, 10): 0, (71, 11): 0, (71, 12): 0, (71, 13): 0, (71, 14): 0, (71, 15): 0, (71, 16): 0, (71, 17): 0, (71, 18): 0, (71, 19): 0, (71, 20): 0, (71, 21): 0, (71, 22): 0, (71, 23): 0, (71, 24): 0, (71, 25): 0, (71, 26): 0, (71, 27): 0, (71, 28): 0, (71, 29): 0, (71, 30): 0, (71, 31): 0, (71, 32): 0, (71, 33): 1, (71, 34): 1, (71, 35): 1, (71, 36): 1, (71, 37): 1, (71, 38): 1, (71, 39): 1, (71, 40): 1, (71, 41): 0, (71, 42): 0, (73, 1): 0, (73, 2): 0, (73, 3): 0, (73, 4): 0, (73, 5): 0, (73, 6): 0, (73, 7): 0, (73, 8): 0, (73, 9): 0, (73, 10): 0, (73, 11): 0, (73, 12): 0, (73, 13): 0, (73, 14): 0, (73, 15): 0, (73, 16): 0, (73, 17): 0, (73, 18): 0, (73, 19): 0, (73, 20): 0, (73, 21): 0, (73, 22): 0, (73, 23): 0, (73, 24): 0, (73, 25): 0, (73, 26): 0, (73, 27): 0, (73, 28): 0, (73, 29): 0, (73, 30): 0, (73, 31): 1, (73, 32): 1, (73, 33): 1, (73, 34): 1, (73, 35): 1, (73, 36): 1, (73, 37): 1, (73, 38): 1, (73, 39): 1, (73, 40): 1, (73, 41): 1, (73, 42): 0, (75, 1): 0, (75, 2): 0, (75, 3): 0, (75, 4): 0, (75, 5): 0, (75, 6): 0, (75, 7): 0, (75, 8): 0, (75, 9): 0, (75, 10): 0, (75, 11): 0, (75, 12): 0, (75, 13): 0, (75, 14): 0, (75, 15): 0, (75, 16): 0, (75, 17): 0, (75, 18): 0, (75, 19): 0, (75, 20): 1, (75, 21): 1, (75, 22): 1, (75, 23): 1, (75, 24): 1, (75, 25): 1, (75, 26): 1, (75, 27): 0, (75, 28): 0, (75, 29): 0, (75, 30): 0, (75, 31): 0, (75, 32): 0, (75, 33): 0, (75, 34): 0, (75, 35): 0, (75, 36): 0, (75, 37): 0, (75, 38): 0, (75, 39): 0, (75, 40): 0, (75, 41): 0, (75, 42): 0, (77, 1): 0, (77, 2): 0, (77, 3): 0, (77, 4): 0, (77, 5): 0, (77, 6): 0, (77, 7): 0, (77, 8): 0, (77, 9): 0, (77, 10): 0, (77, 11): 0, (77, 12): 0, (77, 13): 0, (77, 14): 0, (77, 15): 0, (77, 16): 0, (77, 17): 0, (77, 18): 0, (77, 19): 0, (77, 20): 0, (77, 21): 0, (77, 22): 0, (77, 23): 0, (77, 24): 0, (77, 25): 0, (77, 26): 0, (77, 27): 0, (77, 28): 0, (77, 29): 0, (77, 30): 0, (77, 31): 0, (77, 32): 0, (77, 33): 0, (77, 34): 0, (77, 35): 0, (77, 36): 0, (77, 37): 0, (77, 38): 0, (77, 39): 0, (77, 40): 1, (77, 41): 1, (77, 42): 1, (78, 1): 0, (78, 2): 0, (78, 3): 0, (78, 4): 0, (78, 5): 0, (78, 6): 0, (78, 7): 0, (78, 8): 0, (78, 9): 0, (78, 10): 0, (78, 11): 1, (78, 12): 1, (78, 13): 1, (78, 14): 1, (78, 15): 1, (78, 16): 1, (78, 17): 1, (78, 18): 1, (78, 19): 0, (78, 20): 0, (78, 21): 0, (78, 22): 0, (78, 23): 0, (78, 24): 0, (78, 25): 0, (78, 26): 0, (78, 27): 0, (78, 28): 0, (78, 29): 0, (78, 30): 0, (78, 31): 0, (78, 32): 0, (78, 33): 0, (78, 34): 0, (78, 35): 0, (78, 36): 0, (78, 37): 0, (78, 38): 0, (78, 39): 0, (78, 40): 0, (78, 41): 0, (78, 42): 0, (79, 1): 0, (79, 2): 0, (79, 3): 0, (79, 4): 0, (79, 5): 0, (79, 6): 0, (79, 7): 0, (79, 8): 0, (79, 9): 0, (79, 10): 0, (79, 11): 0, (79, 12): 0, (79, 13): 0, (79, 14): 0, (79, 15): 0, (79, 16): 0, (79, 17): 0, (79, 18): 0, (79, 19): 0, (79, 20): 1, (79, 21): 1, (79, 22): 1, (79, 23): 1, (79, 24): 1, (79, 25): 1, (79, 26): 0, (79, 27): 0, (79, 28): 0, (79, 29): 0, (79, 30): 0, (79, 31): 0, (79, 32): 0, (79, 33): 0, (79, 34): 0, (79, 35): 0, (79, 36): 0, (79, 37): 0, (79, 38): 0, (79, 39): 0, (79, 40): 0, (79, 41): 0, (79, 42): 0, (81, 1): 0, (81, 2): 0, (81, 3): 0, (81, 4): 0, (81, 5): 0, (81, 6): 0, (81, 7): 0, (81, 8): 0, (81, 9): 0, (81, 10): 0, (81, 11): 0, (81, 12): 1, (81, 13): 1, (81, 14): 1, (81, 15): 1, (81, 16): 1, (81, 17): 1, (81, 18): 0, (81, 19): 0, (81, 20): 0, (81, 21): 0, (81, 22): 0, (81, 23): 0, (81, 24): 0, (81, 25): 0, (81, 26): 0, (81, 27): 0, (81, 28): 0, (81, 29): 0, (81, 30): 0, (81, 31): 0, (81, 32): 0, (81, 33): 0, (81, 34): 0, (81, 35): 0, (81, 36): 0, (81, 37): 0, (81, 38): 0, (81, 39): 0, (81, 40): 0, (81, 41): 0, (81, 42): 0, (82, 1): 0, (82, 2): 0, (82, 3): 0, (82, 4): 0, (82, 5): 0, (82, 6): 0, (82, 7): 0, (82, 8): 0, (82, 9): 1, (82, 10): 1, (82, 11): 1, (82, 12): 1, (82, 13): 1, (82, 14): 1, (82, 15): 1, (82, 16): 0, (82, 17): 0, (82, 18): 0, (82, 19): 0, (82, 20): 0, (82, 21): 0, (82, 22): 0, (82, 23): 0, (82, 24): 0, (82, 25): 0, (82, 26): 0, (82, 27): 0, (82, 28): 0, (82, 29): 0, (82, 30): 0, (82, 31): 0, (82, 32): 0, (82, 33): 0, (82, 34): 0, (82, 35): 0, (82, 36): 0, (82, 37): 0, (82, 38): 0, (82, 39): 0, (82, 40): 0, (82, 41): 0, (82, 42): 0}</t>
-  </si>
-  <si>
-    <t>{(2, 1): 0, (2, 2): 0, (2, 3): 0, (2, 4): 0, (2, 5): 0, (2, 6): 0, (2, 7): 0, (2, 8): 0, (2, 9): 0, (2, 10): 0, (2, 11): 0, (2, 12): 0, (2, 13): 0, (2, 14): 0, (2, 15): 0, (2, 16): 0, (2, 17): 0, (2, 18): 0, (2, 19): 0, (2, 20): 0, (2, 21): 0, (2, 22): 0, (2, 23): 0, (2, 24): 0, (2, 25): 0, (2, 26): 0, (2, 27): 0, (2, 28): 0, (2, 29): 0, (2, 30): 0, (2, 31): 0, (2, 32): 0, (2, 33): 0, (2, 34): 0, (2, 35): 0, (2, 36): 0, (2, 37): 0, (2, 38): 0, (2, 39): 0, (2, 40): 0, (2, 41): 0, (2, 42): 0, (3, 1): 0, (3, 2): 0, (3, 3): 0, (3, 4): 0, (3, 5): 0, (3, 6): 0, (3, 7): 0, (3, 8): 0, (3, 9): 0, (3, 10): 0, (3, 11): 0, (3, 12): 0, (3, 13): 0, (3, 14): 0, (3, 15): 0, (3, 16): 0, (3, 17): 0, (3, 18): 0, (3, 19): 0, (3, 20): 0, (3, 21): 0, (3, 22): 0, (3, 23): 0, (3, 24): 0, (3, 25): 0, (3, 26): 0, (3, 27): 0, (3, 28): 0, (3, 29): 0, (3, 30): 0, (3, 31): 0, (3, 32): 0, (3, 33): 0, (3, 34): 0, (3, 35): 0, (3, 36): 0, (3, 37): 0, (3, 38): 0, (3, 39): 0, (3, 40): 0, (3, 41): 0, (3, 42): 0, (4, 1): 0, (4, 2): 0, (4, 3): 0, (4, 4): 0, (4, 5): 0, (4, 6): 0, (4, 7): 0, (4, 8): 0, (4, 9): 0, (4, 10): 0, (4, 11): 0, (4, 12): 0, (4, 13): 0, (4, 14): 0, (4, 15): 0, (4, 16): 0, (4, 17): 0, (4, 18): 0, (4, 19): 0, (4, 20): 0, (4, 21): 0, (4, 22): 0, (4, 23): 0, (4, 24): 0, (4, 25): 0, (4, 26): 0, (4, 27): 0, (4, 28): 0, (4, 29): 0, (4, 30): 0, (4, 31): 0, (4, 32): 0, (4, 33): 0, (4, 34): 0, (4, 35): 0, (4, 36): 0, (4, 37): 0, (4, 38): 0, (4, 39): 0, (4, 40): 0, (4, 41): 0, (4, 42): 0, (9, 1): 0, (9, 2): 0, (9, 3): 0, (9, 4): 0, (9, 5): 0, (9, 6): 0, (9, 7): 0, (9, 8): 0, (9, 9): 0, (9, 10): 0, (9, 11): 0, (9, 12): 0, (9, 13): 0, (9, 14): 0, (9, 15): 0, (9, 16): 0, (9, 17): 0, (9, 18): 0, (9, 19): 0, (9, 20): 0, (9, 21): 0, (9, 22): 0, (9, 23): 0, (9, 24): 0, (9, 25): 0, (9, 26): 0, (9, 27): 0, (9, 28): 0, (9, 29): 0, (9, 30): 0, (9, 31): 0, (9, 32): 0, (9, 33): 0, (9, 34): 0, (9, 35): 0, (9, 36): 0, (9, 37): 0, (9, 38): 0, (9, 39): 0, (9, 40): 0, (9, 41): 0, (9, 42): 0, (15, 1): 0, (15, 2): 0, (15, 3): 0, (15, 4): 0, (15, 5): 0, (15, 6): 0, (15, 7): 0, (15, 8): 0, (15, 9): 0, (15, 10): 0, (15, 11): 0, (15, 12): 0, (15, 13): 0, (15, 14): 0, (15, 15): 0, (15, 16): 0, (15, 17): 0, (15, 18): 0, (15, 19): 0, (15, 20): 0, (15, 21): 0, (15, 22): 0, (15, 23): 0, (15, 24): 0, (15, 25): 0, (15, 26): 0, (15, 27): 0, (15, 28): 0, (15, 29): 0, (15, 30): 0, (15, 31): 0, (15, 32): 0, (15, 33): 0, (15, 34): 0, (15, 35): 0, (15, 36): 0, (15, 37): 0, (15, 38): 0, (15, 39): 0, (15, 40): 0, (15, 41): 0, (15, 42): 0, (16, 1): 0, (16, 2): 0, (16, 3): 0, (16, 4): 0, (16, 5): 0, (16, 6): 0, (16, 7): 0, (16, 8): 0, (16, 9): 0, (16, 10): 0, (16, 11): 0, (16, 12): 0, (16, 13): 0, (16, 14): 0, (16, 15): 0, (16, 16): 0, (16, 17): 0, (16, 18): 0, (16, 19): 0, (16, 20): 0, (16, 21): 0, (16, 22): 0, (16, 23): 0, (16, 24): 0, (16, 25): 0, (16, 26): 0, (16, 27): 0, (16, 28): 0, (16, 29): 0, (16, 30): 0, (16, 31): 0, (16, 32): 0, (16, 33): 0, (16, 34): 0, (16, 35): 0, (16, 36): 0, (16, 37): 0, (16, 38): 0, (16, 39): 0, (16, 40): 0, (16, 41): 0, (16, 42): 0, (20, 1): 0, (20, 2): 0, (20, 3): 0, (20, 4): 0, (20, 5): 0, (20, 6): 0, (20, 7): 0, (20, 8): 0, (20, 9): 0, (20, 10): 0, (20, 11): 0, (20, 12): 0, (20, 13): 0, (20, 14): 0, (20, 15): 0, (20, 16): 0, (20, 17): 0, (20, 18): 0, (20, 19): 0, (20, 20): 0, (20, 21): 0, (20, 22): 0, (20, 23): 0, (20, 24): 0, (20, 25): 0, (20, 26): 0, (20, 27): 0, (20, 28): 0, (20, 29): 0, (20, 30): 0, (20, 31): 0, (20, 32): 0, (20, 33): 0, (20, 34): 0, (20, 35): 0, (20, 36): 0, (20, 37): 0, (20, 38): 0, (20, 39): 0, (20, 40): 0, (20, 41): 0, (20, 42): 0, (21, 1): 0, (21, 2): 0, (21, 3): 0, (21, 4): 0, (21, 5): 0, (21, 6): 0, (21, 7): 0, (21, 8): 0, (21, 9): 0, (21, 10): 0, (21, 11): 0, (21, 12): 0, (21, 13): 0, (21, 14): 0, (21, 15): 0, (21, 16): 0, (21, 17): 0, (21, 18): 0, (21, 19): 0, (21, 20): 0, (21, 21): 0, (21, 22): 0, (21, 23): 0, (21, 24): 0, (21, 25): 0, (21, 26): 0, (21, 27): 0, (21, 28): 0, (21, 29): 0, (21, 30): 0, (21, 31): 0, (21, 32): 0, (21, 33): 0, (21, 34): 0, (21, 35): 0, (21, 36): 0, (21, 37): 0, (21, 38): 0, (21, 39): 0, (21, 40): 0, (21, 41): 0, (21, 42): 0, (22, 1): 0, (22, 2): 0, (22, 3): 0, (22, 4): 0, (22, 5): 0, (22, 6): 0, (22, 7): 0, (22, 8): 0, (22, 9): 0, (22, 10): 0, (22, 11): 0, (22, 12): 0, (22, 13): 0, (22, 14): 0, (22, 15): 0, (22, 16): 0, (22, 17): 0, (22, 18): 0, (22, 19): 0, (22, 20): 0, (22, 21): 0, (22, 22): 0, (22, 23): 0, (22, 24): 0, (22, 25): 0, (22, 26): 0, (22, 27): 0, (22, 28): 0, (22, 29): 0, (22, 30): 0, (22, 31): 0, (22, 32): 0, (22, 33): 0, (22, 34): 0, (22, 35): 0, (22, 36): 0, (22, 37): 0, (22, 38): 0, (22, 39): 0, (22, 40): 0, (22, 41): 0, (22, 42): 0, (23, 1): 0, (23, 2): 0, (23, 3): 0, (23, 4): 0, (23, 5): 0, (23, 6): 0, (23, 7): 0, (23, 8): 0, (23, 9): 0, (23, 10): 0, (23, 11): 0, (23, 12): 0, (23, 13): 0, (23, 14): 0, (23, 15): 0, (23, 16): 0, (23, 17): 0, (23, 18): 0, (23, 19): 0, (23, 20): 0, (23, 21): 0, (23, 22): 0, (23, 23): 0, (23, 24): 0, (23, 25): 0, (23, 26): 0, (23, 27): 0, (23, 28): 0, (23, 29): 0, (23, 30): 0, (23, 31): 0, (23, 32): 0, (23, 33): 0, (23, 34): 0, (23, 35): 0, (23, 36): 0, (23, 37): 0, (23, 38): 0, (23, 39): 0, (23, 40): 0, (23, 41): 0, (23, 42): 0, (24, 1): 0, (24, 2): 0, (24, 3): 0, (24, 4): 0, (24, 5): 0, (24, 6): 0, (24, 7): 0, (24, 8): 0, (24, 9): 0, (24, 10): 0, (24, 11): 0, (24, 12): 0, (24, 13): 0, (24, 14): 0, (24, 15): 0, (24, 16): 0, (24, 17): 0, (24, 18): 0, (24, 19): 0, (24, 20): 0, (24, 21): 0, (24, 22): 0, (24, 23): 0, (24, 24): 0, (24, 25): 0, (24, 26): 0, (24, 27): 0, (24, 28): 0, (24, 29): 0, (24, 30): 0, (24, 31): 0, (24, 32): 0, (24, 33): 0, (24, 34): 0, (24, 35): 0, (24, 36): 0, (24, 37): 0, (24, 38): 0, (24, 39): 0, (24, 40): 0, (24, 41): 0, (24, 42): 0, (25, 1): 0, (25, 2): 0, (25, 3): 0, (25, 4): 0, (25, 5): 0, (25, 6): 0, (25, 7): 0, (25, 8): 0, (25, 9): 0, (25, 10): 0, (25, 11): 0, (25, 12): 0, (25, 13): 0, (25, 14): 0, (25, 15): 0, (25, 16): 0, (25, 17): 0, (25, 18): 0, (25, 19): 0, (25, 20): 0, (25, 21): 0, (25, 22): 0, (25, 23): 0, (25, 24): 0, (25, 25): 0, (25, 26): 0, (25, 27): 0, (25, 28): 0, (25, 29): 0, (25, 30): 0, (25, 31): 0, (25, 32): 0, (25, 33): 0, (25, 34): 0, (25, 35): 0, (25, 36): 0, (25, 37): 0, (25, 38): 0, (25, 39): 0, (25, 40): 0, (25, 41): 0, (25, 42): 0, (26, 1): 0, (26, 2): 0, (26, 3): 0, (26, 4): 0, (26, 5): 0, (26, 6): 0, (26, 7): 0, (26, 8): 0, (26, 9): 0, (26, 10): 0, (26, 11): 0, (26, 12): 0, (26, 13): 0, (26, 14): 0, (26, 15): 0, (26, 16): 0, (26, 17): 0, (26, 18): 0, (26, 19): 0, (26, 20): 0, (26, 21): 0, (26, 22): 0, (26, 23): 0, (26, 24): 0, (26, 25): 0, (26, 26): 0, (26, 27): 0, (26, 28): 0, (26, 29): 0, (26, 30): 0, (26, 31): 0, (26, 32): 0, (26, 33): 0, (26, 34): 0, (26, 35): 0, (26, 36): 0, (26, 37): 0, (26, 38): 0, (26, 39): 0, (26, 40): 0, (26, 41): 0, (26, 42): 0, (28, 1): 0, (28, 2): 0, (28, 3): 0, (28, 4): 0, (28, 5): 0, (28, 6): 0, (28, 7): 0, (28, 8): 0, (28, 9): 0, (28, 10): 0, (28, 11): 0, (28, 12): 0, (28, 13): 0, (28, 14): 0, (28, 15): 0, (28, 16): 0, (28, 17): 0, (28, 18): 0, (28, 19): 0, (28, 20): 0, (28, 21): 0, (28, 22): 0, (28, 23): 0, (28, 24): 0, (28, 25): 0, (28, 26): 0, (28, 27): 0, (28, 28): 0, (28, 29): 0, (28, 30): 0, (28, 31): 0, (28, 32): 0, (28, 33): 0, (28, 34): 0, (28, 35): 0, (28, 36): 0, (28, 37): 0, (28, 38): 0, (28, 39): 0, (28, 40): 0, (28, 41): 0, (28, 42): 0, (30, 1): 0, (30, 2): 0, (30, 3): 0, (30, 4): 0, (30, 5): 0, (30, 6): 0, (30, 7): 0, (30, 8): 0, (30, 9): 0, (30, 10): 0, (30, 11): 0, (30, 12): 0, (30, 13): 0, (30, 14): 0, (30, 15): 0, (30, 16): 0, (30, 17): 0, (30, 18): 0, (30, 19): 0, (30, 20): 0, (30, 21): 0, (30, 22): 0, (30, 23): 0, (30, 24): 0, (30, 25): 0, (30, 26): 0, (30, 27): 0, (30, 28): 0, (30, 29): 0, (30, 30): 0, (30, 31): 0, (30, 32): 0, (30, 33): 0, (30, 34): 0, (30, 35): 0, (30, 36): 0, (30, 37): 0, (30, 38): 0, (30, 39): 0, (30, 40): 0, (30, 41): 0, (30, 42): 0, (31, 1): 0, (31, 2): 0, (31, 3): 0, (31, 4): 0, (31, 5): 0, (31, 6): 0, (31, 7): 0, (31, 8): 0, (31, 9): 0, (31, 10): 0, (31, 11): 0, (31, 12): 0, (31, 13): 0, (31, 14): 0, (31, 15): 0, (31, 16): 0, (31, 17): 0, (31, 18): 0, (31, 19): 0, (31, 20): 0, (31, 21): 0, (31, 22): 0, (31, 23): 0, (31, 24): 0, (31, 25): 0, (31, 26): 0, (31, 27): 0, (31, 28): 0, (31, 29): 0, (31, 30): 0, (31, 31): 0, (31, 32): 0, (31, 33): 0, (31, 34): 0, (31, 35): 0, (31, 36): 0, (31, 37): 0, (31, 38): 0, (31, 39): 0, (31, 40): 0, (31, 41): 0, (31, 42): 0, (36, 1): 0, (36, 2): 0, (36, 3): 0, (36, 4): 0, (36, 5): 0, (36, 6): 0, (36, 7): 0, (36, 8): 0, (36, 9): 0, (36, 10): 0, (36, 11): 0, (36, 12): 0, (36, 13): 0, (36, 14): 0, (36, 15): 0, (36, 16): 0, (36, 17): 0, (36, 18): 0, (36, 19): 0, (36, 20): 0, (36, 21): 0, (36, 22): 0, (36, 23): 0, (36, 24): 0, (36, 25): 0, (36, 26): 0, (36, 27): 0, (36, 28): 0, (36, 29): 0, (36, 30): 0, (36, 31): 0, (36, 32): 0, (36, 33): 0, (36, 34): 0, (36, 35): 0, (36, 36): 0, (36, 37): 0, (36, 38): 0, (36, 39): 0, (36, 40): 0, (36, 41): 0, (36, 42): 0, (37, 1): 0, (37, 2): 0, (37, 3): 0, (37, 4): 0, (37, 5): 0, (37, 6): 0, (37, 7): 0, (37, 8): 0, (37, 9): 0, (37, 10): 0, (37, 11): 0, (37, 12): 0, (37, 13): 0, (37, 14): 0, (37, 15): 0, (37, 16): 0, (37, 17): 0, (37, 18): 0, (37, 19): 0, (37, 20): 0, (37, 21): 0, (37, 22): 0, (37, 23): 0, (37, 24): 0, (37, 25): 0, (37, 26): 0, (37, 27): 0, (37, 28): 0, (37, 29): 0, (37, 30): 0, (37, 31): 0, (37, 32): 0, (37, 33): 0, (37, 34): 0, (37, 35): 0, (37, 36): 0, (37, 37): 0, (37, 38): 0, (37, 39): 0, (37, 40): 0, (37, 41): 0, (37, 42): 0, (38, 1): 0, (38, 2): 0, (38, 3): 0, (38, 4): 0, (38, 5): 0, (38, 6): 0, (38, 7): 0, (38, 8): 0, (38, 9): 0, (38, 10): 0, (38, 11): 0, (38, 12): 0, (38, 13): 0, (38, 14): 0, (38, 15): 0, (38, 16): 0, (38, 17): 0, (38, 18): 0, (38, 19): 0, (38, 20): 0, (38, 21): 0, (38, 22): 0, (38, 23): 0, (38, 24): 0, (38, 25): 0, (38, 26): 0, (38, 27): 0, (38, 28): 0, (38, 29): 0, (38, 30): 0, (38, 31): 0, (38, 32): 0, (38, 33): 0, (38, 34): 0, (38, 35): 0, (38, 36): 0, (38, 37): 0, (38, 38): 0, (38, 39): 0, (38, 40): 0, (38, 41): 0, (38, 42): 0, (39, 1): 0, (39, 2): 0, (39, 3): 0, (39, 4): 0, (39, 5): 0, (39, 6): 0, (39, 7): 0, (39, 8): 0, (39, 9): 0, (39, 10): 0, (39, 11): 0, (39, 12): 0, (39, 13): 0, (39, 14): 0, (39, 15): 0, (39, 16): 0, (39, 17): 0, (39, 18): 0, (39, 19): 0, (39, 20): 0, (39, 21): 0, (39, 22): 0, (39, 23): 0, (39, 24): 0, (39, 25): 0, (39, 26): 0, (39, 27): 0, (39, 28): 0, (39, 29): 0, (39, 30): 0, (39, 31): 0, (39, 32): 0, (39, 33): 0, (39, 34): 0, (39, 35): 0, (39, 36): 0, (39, 37): 0, (39, 38): 0, (39, 39): 0, (39, 40): 0, (39, 41): 0, (39, 42): 0, (40, 1): 0, (40, 2): 0, (40, 3): 0, (40, 4): 0, (40, 5): 0, (40, 6): 0, (40, 7): 0, (40, 8): 0, (40, 9): 0, (40, 10): 0, (40, 11): 0, (40, 12): 0, (40, 13): 0, (40, 14): 0, (40, 15): 0, (40, 16): 0, (40, 17): 0, (40, 18): 0, (40, 19): 0, (40, 20): 0, (40, 21): 0, (40, 22): 0, (40, 23): 0, (40, 24): 0, (40, 25): 0, (40, 26): 0, (40, 27): 0, (40, 28): 0, (40, 29): 0, (40, 30): 0, (40, 31): 0, (40, 32): 0, (40, 33): 0, (40, 34): 0, (40, 35): 0, (40, 36): 0, (40, 37): 0, (40, 38): 0, (40, 39): 0, (40, 40): 0, (40, 41): 0, (40, 42): 0, (41, 1): 0, (41, 2): 0, (41, 3): 0, (41, 4): 0, (41, 5): 0, (41, 6): 0, (41, 7): 0, (41, 8): 0, (41, 9): 0, (41, 10): 0, (41, 11): 0, (41, 12): 0, (41, 13): 0, (41, 14): 0, (41, 15): 0, (41, 16): 0, (41, 17): 0, (41, 18): 0, (41, 19): 0, (41, 20): 0, (41, 21): 0, (41, 22): 0, (41, 23): 0, (41, 24): 0, (41, 25): 0, (41, 26): 0, (41, 27): 0, (41, 28): 0, (41, 29): 0, (41, 30): 0, (41, 31): 0, (41, 32): 0, (41, 33): 0, (41, 34): 0, (41, 35): 0, (41, 36): 0, (41, 37): 0, (41, 38): 0, (41, 39): 0, (41, 40): 0, (41, 41): 0, (41, 42): 0, (43, 1): 0, (43, 2): 0, (43, 3): 0, (43, 4): 0, (43, 5): 0, (43, 6): 0, (43, 7): 0, (43, 8): 0, (43, 9): 0, (43, 10): 0, (43, 11): 0, (43, 12): 0, (43, 13): 0, (43, 14): 0, (43, 15): 0, (43, 16): 0, (43, 17): 0, (43, 18): 0, (43, 19): 0, (43, 20): 0, (43, 21): 0, (43, 22): 0, (43, 23): 0, (43, 24): 0, (43, 25): 0, (43, 26): 0, (43, 27): 0, (43, 28): 0, (43, 29): 0, (43, 30): 0, (43, 31): 0, (43, 32): 0, (43, 33): 0, (43, 34): 0, (43, 35): 0, (43, 36): 0, (43, 37): 0, (43, 38): 0, (43, 39): 0, (43, 40): 0, (43, 41): 0, (43, 42): 0, (50, 1): 0, (50, 2): 0, (50, 3): 0, (50, 4): 0, (50, 5): 0, (50, 6): 0, (50, 7): 0, (50, 8): 0, (50, 9): 0, (50, 10): 0, (50, 11): 0, (50, 12): 0, (50, 13): 0, (50, 14): 0, (50, 15): 0, (50, 16): 0, (50, 17): 0, (50, 18): 0, (50, 19): 0, (50, 20): 0, (50, 21): 0, (50, 22): 0, (50, 23): 0, (50, 24): 0, (50, 25): 0, (50, 26): 0, (50, 27): 0, (50, 28): 0, (50, 29): 0, (50, 30): 0, (50, 31): 0, (50, 32): 0, (50, 33): 0, (50, 34): 0, (50, 35): 0, (50, 36): 0, (50, 37): 0, (50, 38): 0, (50, 39): 0, (50, 40): 0, (50, 41): 0, (50, 42): 0, (59, 1): 0, (59, 2): 0, (59, 3): 0, (59, 4): 0, (59, 5): 0, (59, 6): 0, (59, 7): 0, (59, 8): 0, (59, 9): 0, (59, 10): 0, (59, 11): 0, (59, 12): 0, (59, 13): 0, (59, 14): 0, (59, 15): 0, (59, 16): 0, (59, 17): 0, (59, 18): 0, (59, 19): 0, (59, 20): 0, (59, 21): 0, (59, 22): 0, (59, 23): 0, (59, 24): 0, (59, 25): 0, (59, 26): 0, (59, 27): 0, (59, 28): 0, (59, 29): 0, (59, 30): 0, (59, 31): 0, (59, 32): 0, (59, 33): 0, (59, 34): 0, (59, 35): 0, (59, 36): 0, (59, 37): 0, (59, 38): 0, (59, 39): 0, (59, 40): 0, (59, 41): 0, (59, 42): 0, (60, 1): 0, (60, 2): 0, (60, 3): 0, (60, 4): 0, (60, 5): 0, (60, 6): 0, (60, 7): 0, (60, 8): 0, (60, 9): 0, (60, 10): 0, (60, 11): 0, (60, 12): 0, (60, 13): 0, (60, 14): 0, (60, 15): 0, (60, 16): 0, (60, 17): 0, (60, 18): 0, (60, 19): 0, (60, 20): 0, (60, 21): 0, (60, 22): 0, (60, 23): 0, (60, 24): 0, (60, 25): 0, (60, 26): 0, (60, 27): 0, (60, 28): 0, (60, 29): 0, (60, 30): 0, (60, 31): 0, (60, 32): 0, (60, 33): 0, (60, 34): 0, (60, 35): 0, (60, 36): 0, (60, 37): 0, (60, 38): 0, (60, 39): 0, (60, 40): 0, (60, 41): 0, (60, 42): 0, (62, 1): 0, (62, 2): 0, (62, 3): 0, (62, 4): 0, (62, 5): 0, (62, 6): 0, (62, 7): 0, (62, 8): 0, (62, 9): 0, (62, 10): 0, (62, 11): 0, (62, 12): 0, (62, 13): 0, (62, 14): 0, (62, 15): 0, (62, 16): 0, (62, 17): 0, (62, 18): 0, (62, 19): 0, (62, 20): 0, (62, 21): 0, (62, 22): 0, (62, 23): 0, (62, 24): 0, (62, 25): 0, (62, 26): 0, (62, 27): 0, (62, 28): 0, (62, 29): 0, (62, 30): 0, (62, 31): 0, (62, 32): 0, (62, 33): 0, (62, 34): 0, (62, 35): 0, (62, 36): 0, (62, 37): 0, (62, 38): 0, (62, 39): 0, (62, 40): 0, (62, 41): 0, (62, 42): 0, (63, 1): 0, (63, 2): 0, (63, 3): 0, (63, 4): 0, (63, 5): 0, (63, 6): 0, (63, 7): 0, (63, 8): 0, (63, 9): 0, (63, 10): 0, (63, 11): 0, (63, 12): 0, (63, 13): 0, (63, 14): 0, (63, 15): 0, (63, 16): 0, (63, 17): 0, (63, 18): 0, (63, 19): 0, (63, 20): 0, (63, 21): 0, (63, 22): 0, (63, 23): 0, (63, 24): 0, (63, 25): 0, (63, 26): 0, (63, 27): 0, (63, 28): 0, (63, 29): 0, (63, 30): 0, (63, 31): 0, (63, 32): 0, (63, 33): 0, (63, 34): 0, (63, 35): 0, (63, 36): 0, (63, 37): 0, (63, 38): 0, (63, 39): 0, (63, 40): 0, (63, 41): 0, (63, 42): 0, (65, 1): 0, (65, 2): 0, (65, 3): 0, (65, 4): 0, (65, 5): 0, (65, 6): 0, (65, 7): 0, (65, 8): 0, (65, 9): 0, (65, 10): 0, (65, 11): 0, (65, 12): 0, (65, 13): 0, (65, 14): 0, (65, 15): 0, (65, 16): 0, (65, 17): 0, (65, 18): 0, (65, 19): 0, (65, 20): 0, (65, 21): 0, (65, 22): 0, (65, 23): 0, (65, 24): 0, (65, 25): 0, (65, 26): 0, (65, 27): 0, (65, 28): 0, (65, 29): 0, (65, 30): 0, (65, 31): 0, (65, 32): 0, (65, 33): 0, (65, 34): 0, (65, 35): 0, (65, 36): 0, (65, 37): 0, (65, 38): 0, (65, 39): 0, (65, 40): 0, (65, 41): 0, (65, 42): 0, (66, 1): 0, (66, 2): 0, (66, 3): 0, (66, 4): 0, (66, 5): 0, (66, 6): 0, (66, 7): 0, (66, 8): 0, (66, 9): 0, (66, 10): 0, (66, 11): 0, (66, 12): 0, (66, 13): 0, (66, 14): 0, (66, 15): 0, (66, 16): 0, (66, 17): 0, (66, 18): 0, (66, 19): 0, (66, 20): 0, (66, 21): 0, (66, 22): 0, (66, 23): 0, (66, 24): 0, (66, 25): 0, (66, 26): 0, (66, 27): 0, (66, 28): 0, (66, 29): 0, (66, 30): 0, (66, 31): 0, (66, 32): 0, (66, 33): 0, (66, 34): 0, (66, 35): 0, (66, 36): 0, (66, 37): 0, (66, 38): 0, (66, 39): 0, (66, 40): 0, (66, 41): 0, (66, 42): 0, (67, 1): 0, (67, 2): 0, (67, 3): 0, (67, 4): 0, (67, 5): 0, (67, 6): 0, (67, 7): 0, (67, 8): 0, (67, 9): 0, (67, 10): 0, (67, 11): 0, (67, 12): 0, (67, 13): 0, (67, 14): 0, (67, 15): 0, (67, 16): 0, (67, 17): 0, (67, 18): 0, (67, 19): 0, (67, 20): 0, (67, 21): 0, (67, 22): 0, (67, 23): 0, (67, 24): 0, (67, 25): 0, (67, 26): 0, (67, 27): 0, (67, 28): 0, (67, 29): 0, (67, 30): 0, (67, 31): 0, (67, 32): 0, (67, 33): 0, (67, 34): 0, (67, 35): 0, (67, 36): 0, (67, 37): 0, (67, 38): 0, (67, 39): 0, (67, 40): 0, (67, 41): 0, (67, 42): 0, (70, 1): 0, (70, 2): 0, (70, 3): 0, (70, 4): 0, (70, 5): 0, (70, 6): 0, (70, 7): 0, (70, 8): 0, (70, 9): 0, (70, 10): 0, (70, 11): 0, (70, 12): 0, (70, 13): 0, (70, 14): 0, (70, 15): 0, (70, 16): 0, (70, 17): 0, (70, 18): 0, (70, 19): 0, (70, 20): 0, (70, 21): 0, (70, 22): 0, (70, 23): 0, (70, 24): 0, (70, 25): 0, (70, 26): 0, (70, 27): 0, (70, 28): 0, (70, 29): 0, (70, 30): 0, (70, 31): 0, (70, 32): 0, (70, 33): 0, (70, 34): 0, (70, 35): 0, (70, 36): 0, (70, 37): 0, (70, 38): 0, (70, 39): 0, (70, 40): 0, (70, 41): 0, (70, 42): 0, (71, 1): 0, (71, 2): 0, (71, 3): 0, (71, 4): 0, (71, 5): 0, (71, 6): 0, (71, 7): 0, (71, 8): 0, (71, 9): 0, (71, 10): 0, (71, 11): 0, (71, 12): 0, (71, 13): 0, (71, 14): 0, (71, 15): 0, (71, 16): 0, (71, 17): 0, (71, 18): 0, (71, 19): 0, (71, 20): 0, (71, 21): 0, (71, 22): 0, (71, 23): 0, (71, 24): 0, (71, 25): 0, (71, 26): 0, (71, 27): 0, (71, 28): 0, (71, 29): 0, (71, 30): 0, (71, 31): 0, (71, 32): 0, (71, 33): 0, (71, 34): 0, (71, 35): 0, (71, 36): 0, (71, 37): 0, (71, 38): 0, (71, 39): 0, (71, 40): 0, (71, 41): 0, (71, 42): 0, (73, 1): 0, (73, 2): 0, (73, 3): 0, (73, 4): 0, (73, 5): 0, (73, 6): 0, (73, 7): 0, (73, 8): 0, (73, 9): 0, (73, 10): 0, (73, 11): 0, (73, 12): 0, (73, 13): 0, (73, 14): 0, (73, 15): 0, (73, 16): 0, (73, 17): 0, (73, 18): 0, (73, 19): 0, (73, 20): 0, (73, 21): 0, (73, 22): 0, (73, 23): 0, (73, 24): 0, (73, 25): 0, (73, 26): 0, (73, 27): 0, (73, 28): 0, (73, 29): 0, (73, 30): 0, (73, 31): 0, (73, 32): 0, (73, 33): 0, (73, 34): 0, (73, 35): 0, (73, 36): 0, (73, 37): 0, (73, 38): 0, (73, 39): 0, (73, 40): 0, (73, 41): 0, (73, 42): 0, (75, 1): 0, (75, 2): 0, (75, 3): 0, (75, 4): 0, (75, 5): 0, (75, 6): 0, (75, 7): 0, (75, 8): 0, (75, 9): 0, (75, 10): 0, (75, 11): 0, (75, 12): 0, (75, 13): 0, (75, 14): 0, (75, 15): 0, (75, 16): 0, (75, 17): 0, (75, 18): 0, (75, 19): 0, (75, 20): 0, (75, 21): 0, (75, 22): 0, (75, 23): 0, (75, 24): 0, (75, 25): 0, (75, 26): 0, (75, 27): 0, (75, 28): 0, (75, 29): 0, (75, 30): 0, (75, 31): 0, (75, 32): 0, (75, 33): 0, (75, 34): 0, (75, 35): 0, (75, 36): 0, (75, 37): 0, (75, 38): 0, (75, 39): 0, (75, 40): 0, (75, 41): 0, (75, 42): 0, (77, 1): 0, (77, 2): 0, (77, 3): 0, (77, 4): 0, (77, 5): 0, (77, 6): 0, (77, 7): 0, (77, 8): 0, (77, 9): 0, (77, 10): 0, (77, 11): 0, (77, 12): 0, (77, 13): 0, (77, 14): 0, (77, 15): 0, (77, 16): 0, (77, 17): 0, (77, 18): 0, (77, 19): 0, (77, 20): 0, (77, 21): 0, (77, 22): 0, (77, 23): 0, (77, 24): 0, (77, 25): 0, (77, 26): 0, (77, 27): 0, (77, 28): 0, (77, 29): 0, (77, 30): 0, (77, 31): 0, (77, 32): 0, (77, 33): 0, (77, 34): 0, (77, 35): 0, (77, 36): 0, (77, 37): 0, (77, 38): 0, (77, 39): 0, (77, 40): 0, (77, 41): 0, (77, 42): 0, (78, 1): 0, (78, 2): 0, (78, 3): 0, (78, 4): 0, (78, 5): 0, (78, 6): 0, (78, 7): 0, (78, 8): 0, (78, 9): 0, (78, 10): 0, (78, 11): 0, (78, 12): 0, (78, 13): 0, (78, 14): 0, (78, 15): 0, (78, 16): 0, (78, 17): 0, (78, 18): 0, (78, 19): 0, (78, 20): 0, (78, 21): 0, (78, 22): 0, (78, 23): 0, (78, 24): 0, (78, 25): 0, (78, 26): 0, (78, 27): 0, (78, 28): 0, (78, 29): 0, (78, 30): 0, (78, 31): 0, (78, 32): 0, (78, 33): 0, (78, 34): 0, (78, 35): 0, (78, 36): 0, (78, 37): 0, (78, 38): 0, (78, 39): 0, (78, 40): 0, (78, 41): 0, (78, 42): 0, (79, 1): 0, (79, 2): 0, (79, 3): 0, (79, 4): 0, (79, 5): 0, (79, 6): 0, (79, 7): 0, (79, 8): 0, (79, 9): 0, (79, 10): 0, (79, 11): 0, (79, 12): 0, (79, 13): 0, (79, 14): 0, (79, 15): 0, (79, 16): 0, (79, 17): 0, (79, 18): 0, (79, 19): 0, (79, 20): 0, (79, 21): 0, (79, 22): 0, (79, 23): 0, (79, 24): 0, (79, 25): 0, (79, 26): 0, (79, 27): 0, (79, 28): 0, (79, 29): 0, (79, 30): 0, (79, 31): 0, (79, 32): 0, (79, 33): 0, (79, 34): 0, (79, 35): 0, (79, 36): 0, (79, 37): 0, (79, 38): 0, (79, 39): 0, (79, 40): 0, (79, 41): 0, (79, 42): 0, (81, 1): 0, (81, 2): 0, (81, 3): 0, (81, 4): 0, (81, 5): 0, (81, 6): 0, (81, 7): 0, (81, 8): 0, (81, 9): 0, (81, 10): 0, (81, 11): 0, (81, 12): 0, (81, 13): 0, (81, 14): 0, (81, 15): 0, (81, 16): 0, (81, 17): 0, (81, 18): 0, (81, 19): 0, (81, 20): 0, (81, 21): 0, (81, 22): 0, (81, 23): 0, (81, 24): 0, (81, 25): 0, (81, 26): 0, (81, 27): 0, (81, 28): 0, (81, 29): 0, (81, 30): 0, (81, 31): 0, (81, 32): 0, (81, 33): 0, (81, 34): 0, (81, 35): 0, (81, 36): 0, (81, 37): 0, (81, 38): 0, (81, 39): 0, (81, 40): 0, (81, 41): 0, (81, 42): 0, (82, 1): 0, (82, 2): 0, (82, 3): 0, (82, 4): 0, (82, 5): 0, (82, 6): 0, (82, 7): 0, (82, 8): 0, (82, 9): 0, (82, 10): 0, (82, 11): 0, (82, 12): 0, (82, 13): 0, (82, 14): 0, (82, 15): 0, (82, 16): 0, (82, 17): 0, (82, 18): 0, (82, 19): 0, (82, 20): 0, (82, 21): 0, (82, 22): 0, (82, 23): 0, (82, 24): 0, (82, 25): 0, (82, 26): 0, (82, 27): 0, (82, 28): 0, (82, 29): 0, (82, 30): 0, (82, 31): 0, (82, 32): 0, (82, 33): 0, (82, 34): 0, (82, 35): 0, (82, 36): 0, (82, 37): 0, (82, 38): 0, (82, 39): 0, (82, 40): 0, (82, 41): 0, (82, 42): 0}</t>
-  </si>
-  <si>
-    <t>{(2, 1): 0.0, (2, 2): 0.0, (2, 3): 0.0, (2, 4): 0.0, (2, 5): 0.0, (2, 6): 0.0, (2, 7): 0.0, (2, 8): 0.0, (2, 9): 0.0, (2, 10): 0.0, (2, 11): 0.0, (2, 12): 0.0, (2, 13): 0.0, (2, 14): 0.0, (2, 15): 0.0, (2, 16): 0.0, (2, 17): 0.5051001633268003, (2, 18): 0.5051001633268003, (2, 19): 0.5051001633268003, (2, 20): 0.5051001633268003, (2, 21): 0.5051001633268003, (2, 22): 0.5051001633268003, (2, 23): 0.5051001633268003, (2, 24): 0.5051001633268003, (2, 25): 0.5051001633268003, (2, 26): 0.5051001633268003, (2, 27): 0.5051001633268003, (2, 28): 0.5051001633268003, (2, 29): 0.5051001633268003, (2, 30): 0.5051001633268003, (2, 31): 0.5051001633268003, (2, 32): 0.5051001633268003, (2, 33): 0.5051001633268003, (2, 34): 0.5051001633268003, (2, 35): 0.5051001633268003, (2, 36): 0.5051001633268003, (2, 37): 0.5051001633268003, (2, 38): 0.5051001633268003, (2, 39): 0.5051001633268003, (2, 40): 0.5051001633268003, (2, 41): 0.5051001633268003, (2, 42): 0.0, (3, 1): 0.0, (3, 2): 0.0, (3, 3): 0.0, (3, 4): 0.0, (3, 5): 0.0, (3, 6): 0.0, (3, 7): 0.0, (3, 8): 0.0, (3, 9): 0.0, (3, 10): 0.0, (3, 11): 0.0, (3, 12): 0.0, (3, 13): 0.0, (3, 14): 0.0, (3, 15): 0.0, (3, 16): 0.0, (3, 17): 0.5051001633268003, (3, 18): 0.5051001633268003, (3, 19): 0.5051001633268003, (3, 20): 0.5051001633268003, (3, 21): 0.5051001633268003, (3, 22): 0.5051001633268003, (3, 23): 0.5051001633268003, (3, 24): 0.5051001633268003, (3, 25): 0.5051001633268003, (3, 26): 0.5051001633268003, (3, 27): 0.5051001633268003, (3, 28): 0.5051001633268003, (3, 29): 0.5051001633268003, (3, 30): 0.5051001633268003, (3, 31): 0.5051001633268003, (3, 32): 0.5051001633268003, (3, 33): 0.5051001633268003, (3, 34): 0.5051001633268003, (3, 35): 0.5051001633268003, (3, 36): 0.0, (3, 37): 0.0, (3, 38): 0.0, (3, 39): 0.0, (3, 40): 0.0, (3, 41): 0.0, (3, 42): 0.0, (4, 1): 0.0, (4, 2): 0.0, (4, 3): 0.0, (4, 4): 0.0, (4, 5): 0.0, (4, 6): 0.0, (4, 7): 0.0, (4, 8): 0.0, (4, 9): 0.0, (4, 10): 0.0, (4, 11): 0.0, (4, 12): 0.0, (4, 13): 0.0, (4, 14): 0.0, (4, 15): 0.0, (4, 16): 0.0, (4, 17): 0.0, (4, 18): 0.0, (4, 19): 0.0, (4, 20): 0.0, (4, 21): 0.0, (4, 22): 0.0, (4, 23): 0.0, (4, 24): 0.0, (4, 25): 0.0, (4, 26): 0.0, (4, 27): 0.0, (4, 28): 0.0, (4, 29): 0.0, (4, 30): 0.5051001633268003, (4, 31): 0.5051001633268003, (4, 32): 0.5051001633268003, (4, 33): 0.5051001633268003, (4, 34): 0.5051001633268003, (4, 35): 0.5051001633268003, (4, 36): 0.5051001633268003, (4, 37): 0.5051001633268003, (4, 38): 0.5051001633268003, (4, 39): 0.5051001633268003, (4, 40): 0.5051001633268003, (4, 41): 0.5051001633268003, (4, 42): 0.5051001633268003, (9, 1): 0.0, (9, 2): 0.0, (9, 3): 0.0, (9, 4): 0.0, (9, 5): 0.0, (9, 6): 0.0, (9, 7): 0.0, (9, 8): 0.0, (9, 9): 0.0, (9, 10): 0.0, (9, 11): 0.0, (9, 12): 0.0, (9, 13): 0.0, (9, 14): 0.0, (9, 15): 0.0, (9, 16): 0.0, (9, 17): 0.0, (9, 18): 0.0, (9, 19): 0.0, (9, 20): 0.0, (9, 21): 0.0, (9, 22): 0.5051001633268003, (9, 23): 0.5051001633268003, (9, 24): 0.5051001633268003, (9, 25): 0.5051001633268003, (9, 26): 0.5051001633268003, (9, 27): 0.5051001633268003, (9, 28): 0.5051001633268003, (9, 29): 0.5051001633268003, (9, 30): 0.5051001633268003, (9, 31): 0.5051001633268003, (9, 32): 0.5051001633268003, (9, 33): 0.5051001633268003, (9, 34): 0.5051001633268003, (9, 35): 0.5051001633268003, (9, 36): 0.5051001633268003, (9, 37): 0.5051001633268003, (9, 38): 0.5051001633268003, (9, 39): 0.0, (9, 40): 0.0, (9, 41): 0.0, (9, 42): 0.0, (15, 1): 0.0, (15, 2): 0.0, (15, 3): 0.0, (15, 4): 0.0, (15, 5): 0.0, (15, 6): 0.0, (15, 7): 0.0, (15, 8): 0.0, (15, 9): 0.0, (15, 10): 0.0, (15, 11): 0.0, (15, 12): 0.0, (15, 13): 0.0, (15, 14): 0.0, (15, 15): 0.0, (15, 16): 0.0, (15, 17): 0.0, (15, 18): 0.0, (15, 19): 0.0, (15, 20): 0.0, (15, 21): 0.0, (15, 22): 0.0, (15, 23): 0.0, (15, 24): 0.0, (15, 25): 0.0, (15, 26): 0.0, (15, 27): 0.0, (15, 28): 0.0, (15, 29): 0.0, (15, 30): 0.5051001633268003, (15, 31): 0.5051001633268003, (15, 32): 0.5051001633268003, (15, 33): 0.5051001633268003, (15, 34): 0.5051001633268003, (15, 35): 0.5051001633268003, (15, 36): 0.5051001633268003, (15, 37): 0.5051001633268003, (15, 38): 0.5051001633268003, (15, 39): 0.5051001633268003, (15, 40): 0.5051001633268003, (15, 41): 0.5051001633268003, (15, 42): 0.0, (16, 1): 0.0, (16, 2): 0.0, (16, 3): 0.0, (16, 4): 0.0, (16, 5): 0.0, (16, 6): 0.0, (16, 7): 0.0, (16, 8): 0.0, (16, 9): 0.0, (16, 10): 0.0, (16, 11): 0.5051001633268003, (16, 12): 0.5051001633268003, (16, 13): 0.5051001633268003, (16, 14): 0.5051001633268003, (16, 15): 0.5051001633268003, (16, 16): 0.5051001633268003, (16, 17): 0.5051001633268003, (16, 18): 0.5051001633268003, (16, 19): 0.5051001633268003, (16, 20): 0.0, (16, 21): 0.0, (16, 22): 0.0, (16, 23): 0.0, (16, 24): 0.0, (16, 25): 0.0, (16, 26): 0.0, (16, 27): 0.0, (16, 28): 0.0, (16, 29): 0.0, (16, 30): 0.0, (16, 31): 0.0, (16, 32): 0.0, (16, 33): 0.0, (16, 34): 0.0, (16, 35): 0.0, (16, 36): 0.0, (16, 37): 0.0, (16, 38): 0.0, (16, 39): 0.0, (16, 40): 0.0, (16, 41): 0.0, (16, 42): 0.0, (20, 1): 0.0, (20, 2): 0.0, (20, 3): 0.0, (20, 4): 0.0, (20, 5): 0.0, (20, 6): 0.0, (20, 7): 0.0, (20, 8): 0.0, (20, 9): 0.0, (20, 10): 0.0, (20, 11): 0.0, (20, 12): 0.0, (20, 13): 0.0, (20, 14): 0.0, (20, 15): 0.0, (20, 16): 0.0, (20, 17): 0.0, (20, 18): 0.0, (20, 19): 0.0, (20, 20): 0.0, (20, 21): 0.0, (20, 22): 0.0, (20, 23): 0.0, (20, 24): 0.0, (20, 25): 0.0, (20, 26): 0.0, (20, 27): 0.0, (20, 28): 0.0, (20, 29): 0.0, (20, 30): 0.0, (20, 31): 0.0, (20, 32): 0.5051001633268003, (20, 33): 0.5051001633268003, (20, 34): 0.5051001633268003, (20, 35): 0.5051001633268003, (20, 36): 0.5051001633268003, (20, 37): 0.5051001633268003, (20, 38): 0.0, (20, 39): 0.0, (20, 40): 0.0, (20, 41): 0.0, (20, 42): 0.0, (21, 1): 0.0, (21, 2): 0.0, (21, 3): 0.0, (21, 4): 0.0, (21, 5): 0.0, (21, 6): 0.0, (21, 7): 0.0, (21, 8): 0.0, (21, 9): 0.0, (21, 10): 0.0, (21, 11): 0.0, (21, 12): 0.0, (21, 13): 0.0, (21, 14): 0.0, (21, 15): 0.0, (21, 16): 0.0, (21, 17): 0.0, (21, 18): 0.0, (21, 19): 0.0, (21, 20): 0.0, (21, 21): 0.0, (21, 22): 0.0, (21, 23): 0.0, (21, 24): 0.0, (21, 25): 0.0, (21, 26): 0.0, (21, 27): 0.5051001633268003, (21, 28): 0.5051001633268003, (21, 29): 0.5051001633268003, (21, 30): 0.5051001633268003, (21, 31): 0.5051001633268003, (21, 32): 0.5051001633268003, (21, 33): 0.5051001633268003, (21, 34): 0.5051001633268003, (21, 35): 0.5051001633268003, (21, 36): 0.5051001633268003, (21, 37): 0.5051001633268003, (21, 38): 0.5051001633268003, (21, 39): 0.5051001633268003, (21, 40): 0.5051001633268003, (21, 41): 0.5051001633268003, (21, 42): 0.0, (22, 1): 0.0, (22, 2): 0.0, (22, 3): 0.0, (22, 4): 0.0, (22, 5): 0.0, (22, 6): 0.0, (22, 7): 0.0, (22, 8): 0.0, (22, 9): 0.0, (22, 10): 0.0, (22, 11): 0.0, (22, 12): 0.0, (22, 13): 0.0, (22, 14): 0.0, (22, 15): 0.0, (22, 16): 0.0, (22, 17): 0.0, (22, 18): 0.0, (22, 19): 0.0, (22, 20): 0.0, (22, 21): 0.0, (22, 22): 0.0, (22, 23): 0.0, (22, 24): 0.0, (22, 25): 0.0, (22, 26): 0.0, (22, 27): 0.5051001633268003, (22, 28): 0.5051001633268003, (22, 29): 0.5051001633268003, (22, 30): 0.5051001633268003, (22, 31): 0.5051001633268003, (22, 32): 0.5051001633268003, (22, 33): 0.5051001633268003, (22, 34): 0.5051001633268003, (22, 35): 0.5051001633268003, (22, 36): 0.5051001633268003, (22, 37): 0.5051001633268003, (22, 38): 0.5051001633268003, (22, 39): 0.5051001633268003, (22, 40): 0.0, (22, 41): 0.0, (22, 42): 0.0, (23, 1): 0.0, (23, 2): 0.0, (23, 3): 0.0, (23, 4): 0.0, (23, 5): 0.0, (23, 6): 0.0, (23, 7): 0.0, (23, 8): 0.0, (23, 9): 0.0, (23, 10): 0.0, (23, 11): 0.0, (23, 12): 0.0, (23, 13): 0.0, (23, 14): 0.0, (23, 15): 0.0, (23, 16): 0.0, (23, 17): 0.0, (23, 18): 0.0, (23, 19): 0.0, (23, 20): 0.0, (23, 21): 0.0, (23, 22): 0.0, (23, 23): 0.0, (23, 24): 0.0, (23, 25): 0.0, (23, 26): 0.0, (23, 27): 0.0, (23, 28): 0.0, (23, 29): 0.5051001633268003, (23, 30): 0.5051001633268003, (23, 31): 0.5051001633268003, (23, 32): 0.5051001633268003, (23, 33): 0.5051001633268003, (23, 34): 0.5051001633268003, (23, 35): 0.0, (23, 36): 0.0, (23, 37): 0.0, (23, 38): 0.0, (23, 39): 0.0, (23, 40): 0.0, (23, 41): 0.0, (23, 42): 0.0, (24, 1): 0.0, (24, 2): 0.0, (24, 3): 0.0, (24, 4): 0.0, (24, 5): 0.0, (24, 6): 0.0, (24, 7): 0.0, (24, 8): 0.0, (24, 9): 0.0, (24, 10): 0.0, (24, 11): 0.0, (24, 12): 0.0, (24, 13): 0.0, (24, 14): 0.0, (24, 15): 0.0, (24, 16): 0.0, (24, 17): 0.0, (24, 18): 0.0, (24, 19): 0.0, (24, 20): 0.0, (24, 21): 0.0, (24, 22): 0.5051001633268003, (24, 23): 0.5051001633268003, (24, 24): 0.5051001633268003, (24, 25): 0.5051001633268003, (24, 26): 0.5051001633268003, (24, 27): 0.5051001633268003, (24, 28): 0.5051001633268003, (24, 29): 0.5051001633268003, (24, 30): 0.0, (24, 31): 0.0, (24, 32): 0.0, (24, 33): 0.0, (24, 34): 0.0, (24, 35): 0.0, (24, 36): 0.0, (24, 37): 0.0, (24, 38): 0.0, (24, 39): 0.0, (24, 40): 0.0, (24, 41): 0.0, (24, 42): 0.0, (25, 1): 0.0, (25, 2): 0.0, (25, 3): 0.0, (25, 4): 0.0, (25, 5): 0.0, (25, 6): 0.0, (25, 7): 0.0, (25, 8): 0.0, (25, 9): 0.0, (25, 10): 0.0, (25, 11): 0.0, (25, 12): 0.0, (25, 13): 0.0, (25, 14): 0.0, (25, 15): 0.0, (25, 16): 0.0, (25, 17): 0.0, (25, 18): 0.0, (25, 19): 0.0, (25, 20): 0.0, (25, 21): 0.0, (25, 22): 0.0, (25, 23): 0.0, (25, 24): 0.0, (25, 25): 0.0, (25, 26): 0.0, (25, 27): 0.0, (25, 28): 0.0, (25, 29): 0.0, (25, 30): 0.0, (25, 31): 0.0, (25, 32): 0.0, (25, 33): 0.0, (25, 34): 0.0, (25, 35): 0.0, (25, 36): 0.0, (25, 37): 0.0, (25, 38): 0.5051001633268003, (25, 39): 0.5051001633268003, (25, 40): 0.5051001633268003, (25, 41): 0.5051001633268003, (25, 42): 0.5051001633268003, (26, 1): 0.0, (26, 2): 0.0, (26, 3): 0.0, (26, 4): 0.0, (26, 5): 0.0, (26, 6): 0.0, (26, 7): 0.0, (26, 8): 0.0, (26, 9): 0.0, (26, 10): 0.0, (26, 11): 0.0, (26, 12): 0.0, (26, 13): 0.0, (26, 14): 0.0, (26, 15): 0.0, (26, 16): 0.0, (26, 17): 0.0, (26, 18): 0.0, (26, 19): 0.0, (26, 20): 0.0, (26, 21): 0.0, (26, 22): 0.0, (26, 23): 0.0, (26, 24): 0.0, (26, 25): 0.0, (26, 26): 0.5051001633268003, (26, 27): 0.5051001633268003, (26, 28): 0.5051001633268003, (26, 29): 0.5051001633268003, (26, 30): 0.5051001633268003, (26, 31): 0.5051001633268003, (26, 32): 0.0, (26, 33): 0.0, (26, 34): 0.0, (26, 35): 0.0, (26, 36): 0.0, (26, 37): 0.0, (26, 38): 0.0, (26, 39): 0.0, (26, 40): 0.0, (26, 41): 0.0, (26, 42): 0.0, (28, 1): 0.0, (28, 2): 0.0, (28, 3): 0.0, (28, 4): 0.0, (28, 5): 0.0, (28, 6): 0.0, (28, 7): 0.0, (28, 8): 0.0, (28, 9): 0.0, (28, 10): 0.0, (28, 11): 0.0, (28, 12): 0.0, (28, 13): 0.0, (28, 14): 0.0, (28, 15): 0.0, (28, 16): 0.0, (28, 17): 0.0, (28, 18): 0.0, (28, 19): 0.0, (28, 20): 0.0, (28, 21): 0.0, (28, 22): 0.0, (28, 23): 0.0, (28, 24): 0.0, (28, 25): 0.0, (28, 26): 0.0, (28, 27): 0.0, (28, 28): 0.0, (28, 29): 0.0, (28, 30): 0.5051001633268003, (28, 31): 0.5051001633268003, (28, 32): 0.5051001633268003, (28, 33): 0.5051001633268003, (28, 34): 0.5051001633268003, (28, 35): 0.5051001633268003, (28, 36): 0.5051001633268003, (28, 37): 0.5051001633268003, (28, 38): 0.5051001633268003, (28, 39): 0.5051001633268003, (28, 40): 0.5051001633268003, (28, 41): 0.5051001633268003, (28, 42): 0.0, (30, 1): 0.0, (30, 2): 0.0, (30, 3): 0.0, (30, 4): 0.0, (30, 5): 0.0, (30, 6): 0.0, (30, 7): 0.0, (30, 8): 0.0, (30, 9): 0.0, (30, 10): 0.0, (30, 11): 0.0, (30, 12): 0.0, (30, 13): 0.0, (30, 14): 0.0, (30, 15): 0.0, (30, 16): 0.0, (30, 17): 0.0, (30, 18): 0.0, (30, 19): 0.0, (30, 20): 0.0, (30, 21): 0.0, (30, 22): 0.0, (30, 23): 0.5051001633268003, (30, 24): 0.5051001633268003, (30, 25): 0.5051001633268003, (30, 26): 0.5051001633268003, (30, 27): 0.5051001633268003, (30, 28): 0.5051001633268003, (30, 29): 0.5051001633268003, (30, 30): 0.5051001633268003, (30, 31): 0.0, (30, 32): 0.0, (30, 33): 0.0, (30, 34): 0.0, (30, 35): 0.0, (30, 36): 0.0, (30, 37): 0.0, (30, 38): 0.0, (30, 39): 0.0, (30, 40): 0.0, (30, 41): 0.0, (30, 42): 0.0, (31, 1): 0.0, (31, 2): 0.0, (31, 3): 0.0, (31, 4): 0.0, (31, 5): 0.0, (31, 6): 0.0, (31, 7): 0.0, (31, 8): 0.5051001633268003, (31, 9): 0.5051001633268003, (31, 10): 0.5051001633268003, (31, 11): 0.5051001633268003, (31, 12): 0.5051001633268003, (31, 13): 0.5051001633268003, (31, 14): 0.5051001633268003, (31, 15): 0.5051001633268003, (31, 16): 0.5051001633268003, (31, 17): 0.5051001633268003, (31, 18): 0.5051001633268003, (31, 19): 0.5051001633268003, (31, 20): 0.5051001633268003, (31, 21): 0.0, (31, 22): 0.0, (31, 23): 0.0, (31, 24): 0.0, (31, 25): 0.0, (31, 26): 0.0, (31, 27): 0.0, (31, 28): 0.0, (31, 29): 0.0, (31, 30): 0.0, (31, 31): 0.0, (31, 32): 0.0, (31, 33): 0.0, (31, 34): 0.0, (31, 35): 0.0, (31, 36): 0.0, (31, 37): 0.0, (31, 38): 0.0, (31, 39): 0.0, (31, 40): 0.0, (31, 41): 0.0, (31, 42): 0.0, (36, 1): 0.0, (36, 2): 0.0, (36, 3): 0.0, (36, 4): 0.0, (36, 5): 0.0, (36, 6): 0.0, (36, 7): 0.0, (36, 8): 0.0, (36, 9): 0.0, (36, 10): 0.0, (36, 11): 0.0, (36, 12): 0.0, (36, 13): 0.0, (36, 14): 0.0, (36, 15): 0.0, (36, 16): 0.0, (36, 17): 0.0, (36, 18): 0.0, (36, 19): 0.0, (36, 20): 0.0, (36, 21): 0.0, (36, 22): 0.0, (36, 23): 0.0, (36, 24): 0.0, (36, 25): 0.0, (36, 26): 0.0, (36, 27): 0.0, (36, 28): 0.5051001633268003, (36, 29): 0.5051001633268003, (36, 30): 0.5051001633268003, (36, 31): 0.5051001633268003, (36, 32): 0.5051001633268003, (36, 33): 0.5051001633268003, (36, 34): 0.5051001633268003, (36, 35): 0.5051001633268003, (36, 36): 0.5051001633268003, (36, 37): 0.5051001633268003, (36, 38): 0.5051001633268003, (36, 39): 0.0, (36, 40): 0.0, (36, 41): 0.0, (36, 42): 0.0, (37, 1): 0.0, (37, 2): 0.0, (37, 3): 0.0, (37, 4): 0.0, (37, 5): 0.0, (37, 6): 0.0, (37, 7): 0.0, (37, 8): 0.0, (37, 9): 0.0, (37, 10): 0.0, (37, 11): 0.0, (37, 12): 0.0, (37, 13): 0.0, (37, 14): 0.0, (37, 15): 0.0, (37, 16): 0.0, (37, 17): 0.0, (37, 18): 0.0, (37, 19): 0.0, (37, 20): 0.0, (37, 21): 0.0, (37, 22): 0.0, (37, 23): 0.0, (37, 24): 0.0, (37, 25): 0.0, (37, 26): 0.5051001633268003, (37, 27): 0.5051001633268003, (37, 28): 0.5051001633268003, (37, 29): 0.5051001633268003, (37, 30): 0.5051001633268003, (37, 31): 0.5051001633268003, (37, 32): 0.5051001633268003, (37, 33): 0.5051001633268003, (37, 34): 0.0, (37, 35): 0.0, (37, 36): 0.0, (37, 37): 0.0, (37, 38): 0.0, (37, 39): 0.0, (37, 40): 0.0, (37, 41): 0.0, (37, 42): 0.0, (38, 1): 0.0, (38, 2): 0.0, (38, 3): 0.0, (38, 4): 0.0, (38, 5): 0.0, (38, 6): 0.0, (38, 7): 0.0, (38, 8): 0.0, (38, 9): 0.0, (38, 10): 0.0, (38, 11): 0.0, (38, 12): 0.0, (38, 13): 0.0, (38, 14): 0.0, (38, 15): 0.0, (38, 16): 0.0, (38, 17): 0.0, (38, 18): 0.0, (38, 19): 0.0, (38, 20): 0.0, (38, 21): 0.0, (38, 22): 0.0, (38, 23): 0.0, (38, 24): 0.0, (38, 25): 0.0, (38, 26): 0.0, (38, 27): 0.0, (38, 28): 0.0, (38, 29): 0.0, (38, 30): 0.0, (38, 31): 0.0, (38, 32): 0.0, (38, 33): 0.0, (38, 34): 0.0, (38, 35): 0.0, (38, 36): 0.0, (38, 37): 0.0, (38, 38): 0.0, (38, 39): 0.0, (38, 40): 0.0, (38, 41): 0.5051001633268003, (38, 42): 0.5051001633268003, (39, 1): 0.0, (39, 2): 0.0, (39, 3): 0.0, (39, 4): 0.0, (39, 5): 0.0, (39, 6): 0.0, (39, 7): 0.0, (39, 8): 0.0, (39, 9): 0.0, (39, 10): 0.0, (39, 11): 0.0, (39, 12): 0.0, (39, 13): 0.0, (39, 14): 0.0, (39, 15): 0.0, (39, 16): 0.0, (39, 17): 0.0, (39, 18): 0.5051001633268003, (39, 19): 0.5051001633268003, (39, 20): 0.5051001633268003, (39, 21): 0.5051001633268003, (39, 22): 0.5051001633268003, (39, 23): 0.5051001633268003, (39, 24): 0.5051001633268003, (39, 25): 0.0, (39, 26): 0.0, (39, 27): 0.0, (39, 28): 0.0, (39, 29): 0.0, (39, 30): 0.0, (39, 31): 0.0, (39, 32): 0.0, (39, 33): 0.0, (39, 34): 0.0, (39, 35): 0.0, (39, 36): 0.0, (39, 37): 0.0, (39, 38): 0.0, (39, 39): 0.0, (39, 40): 0.0, (39, 41): 0.0, (39, 42): 0.0, (40, 1): 0.0, (40, 2): 0.0, (40, 3): 0.0, (40, 4): 0.0, (40, 5): 0.0, (40, 6): 0.0, (40, 7): 0.0, (40, 8): 0.5051001633268003, (40, 9): 0.5051001633268003, (40, 10): 0.5051001633268003, (40, 11): 0.5051001633268003, (40, 12): 0.5051001633268003, (40, 13): 0.5051001633268003, (40, 14): 0.5051001633268003, (40, 15): 0.5051001633268003, (40, 16): 0.0, (40, 17): 0.0, (40, 18): 0.0, (40, 19): 0.0, (40, 20): 0.0, (40, 21): 0.0, (40, 22): 0.0, (40, 23): 0.0, (40, 24): 0.0, (40, 25): 0.0, (40, 26): 0.0, (40, 27): 0.0, (40, 28): 0.0, (40, 29): 0.0, (40, 30): 0.0, (40, 31): 0.0, (40, 32): 0.0, (40, 33): 0.0, (40, 34): 0.0, (40, 35): 0.0, (40, 36): 0.0, (40, 37): 0.0, (40, 38): 0.0, (40, 39): 0.0, (40, 40): 0.0, (40, 41): 0.0, (40, 42): 0.0, (41, 1): 0.0, (41, 2): 0.0, (41, 3): 0.0, (41, 4): 0.0, (41, 5): 0.0, (41, 6): 0.0, (41, 7): 0.0, (41, 8): 0.0, (41, 9): 0.0, (41, 10): 0.0, (41, 11): 0.0, (41, 12): 0.0, (41, 13): 0.0, (41, 14): 0.0, (41, 15): 0.0, (41, 16): 0.0, (41, 17): 0.0, (41, 18): 0.0, (41, 19): 0.0, (41, 20): 0.0, (41, 21): 0.0, (41, 22): 0.0, (41, 23): 0.5051001633268003, (41, 24): 0.5051001633268003, (41, 25): 0.5051001633268003, (41, 26): 0.5051001633268003, (41, 27): 0.5051001633268003, (41, 28): 0.5051001633268003, (41, 29): 0.0, (41, 30): 0.0, (41, 31): 0.0, (41, 32): 0.0, (41, 33): 0.0, (41, 34): 0.0, (41, 35): 0.0, (41, 36): 0.0, (41, 37): 0.0, (41, 38): 0.0, (41, 39): 0.0, (41, 40): 0.0, (41, 41): 0.0, (41, 42): 0.0, (43, 1): 0.0, (43, 2): 0.0, (43, 3): 0.0, (43, 4): 0.0, (43, 5): 0.0, (43, 6): 0.0, (43, 7): 0.0, (43, 8): 0.0, (43, 9): 0.0, (43, 10): 0.0, (43, 11): 0.0, (43, 12): 0.0, (43, 13): 0.0, (43, 14): 0.0, (43, 15): 0.0, (43, 16): 0.0, (43, 17): 0.5051001633268003, (43, 18): 0.5051001633268003, (43, 19): 0.5051001633268003, (43, 20): 0.5051001633268003, (43, 21): 0.5051001633268003, (43, 22): 0.5051001633268003, (43, 23): 0.5051001633268003, (43, 24): 0.5051001633268003, (43, 25): 0.0, (43, 26): 0.0, (43, 27): 0.0, (43, 28): 0.0, (43, 29): 0.0, (43, 30): 0.0, (43, 31): 0.0, (43, 32): 0.0, (43, 33): 0.0, (43, 34): 0.0, (43, 35): 0.0, (43, 36): 0.0, (43, 37): 0.0, (43, 38): 0.0, (43, 39): 0.0, (43, 40): 0.0, (43, 41): 0.0, (43, 42): 0.0, (50, 1): 0.0, (50, 2): 0.0, (50, 3): 0.0, (50, 4): 0.0, (50, 5): 0.0, (50, 6): 0.0, (50, 7): 0.0, (50, 8): 0.0, (50, 9): 0.0, (50, 10): 0.0, (50, 11): 0.5051001633268003, (50, 12): 0.5051001633268003, (50, 13): 0.5051001633268003, (50, 14): 0.5051001633268003, (50, 15): 0.5051001633268003, (50, 16): 0.5051001633268003, (50, 17): 0.5051001633268003, (50, 18): 0.0, (50, 19): 0.0, (50, 20): 0.0, (50, 21): 0.0, (50, 22): 0.0, (50, 23): 0.0, (50, 24): 0.0, (50, 25): 0.0, (50, 26): 0.0, (50, 27): 0.0, (50, 28): 0.0, (50, 29): 0.0, (50, 30): 0.0, (50, 31): 0.0, (50, 32): 0.0, (50, 33): 0.0, (50, 34): 0.0, (50, 35): 0.0, (50, 36): 0.0, (50, 37): 0.0, (50, 38): 0.0, (50, 39): 0.0, (50, 40): 0.0, (50, 41): 0.0, (50, 42): 0.0, (59, 1): 0.0, (59, 2): 0.0, (59, 3): 0.0, (59, 4): 0.0, (59, 5): 0.0, (59, 6): 0.0, (59, 7): 0.0, (59, 8): 0.0, (59, 9): 0.0, (59, 10): 0.0, (59, 11): 0.0, (59, 12): 0.0, (59, 13): 0.0, (59, 14): 0.0, (59, 15): 0.5051001633268003, (59, 16): 0.5051001633268003, (59, 17): 0.5051001633268003, (59, 18): 0.5051001633268003, (59, 19): 0.5051001633268003, (59, 20): 0.5051001633268003, (59, 21): 0.5051001633268003, (59, 22): 0.5051001633268003, (59, 23): 0.5051001633268003, (59, 24): 0.0, (59, 25): 0.0, (59, 26): 0.0, (59, 27): 0.0, (59, 28): 0.0, (59, 29): 0.0, (59, 30): 0.0, (59, 31): 0.0, (59, 32): 0.0, (59, 33): 0.0, (59, 34): 0.0, (59, 35): 0.0, (59, 36): 0.0, (59, 37): 0.0, (59, 38): 0.0, (59, 39): 0.0, (59, 40): 0.0, (59, 41): 0.0, (59, 42): 0.0, (60, 1): 0.0, (60, 2): 0.0, (60, 3): 0.0, (60, 4): 0.0, (60, 5): 0.0, (60, 6): 0.0, (60, 7): 0.0, (60, 8): 0.0, (60, 9): 0.0, (60, 10): 0.0, (60, 11): 0.0, (60, 12): 0.0, (60, 13): 0.0, (60, 14): 0.0, (60, 15): 0.0, (60, 16): 0.0, (60, 17): 0.0, (60, 18): 0.0, (60, 19): 0.0, (60, 20): 0.0, (60, 21): 0.0, (60, 22): 0.0, (60, 23): 0.0, (60, 24): 0.0, (60, 25): 0.0, (60, 26): 0.0, (60, 27): 0.0, (60, 28): 0.0, (60, 29): 0.0, (60, 30): 0.0, (60, 31): 0.0, (60, 32): 0.0, (60, 33): 0.0, (60, 34): 0.0, (60, 35): 0.0, (60, 36): 0.0, (60, 37): 0.0, (60, 38): 0.5051001633268003, (60, 39): 0.5051001633268003, (60, 40): 0.5051001633268003, (60, 41): 0.5051001633268003, (60, 42): 0.5051001633268003, (62, 1): 0.0, (62, 2): 0.0, (62, 3): 0.0, (62, 4): 0.0, (62, 5): 0.0, (62, 6): 0.0, (62, 7): 0.0, (62, 8): 0.0, (62, 9): 0.0, (62, 10): 0.0, (62, 11): 0.0, (62, 12): 0.0, (62, 13): 0.0, (62, 14): 0.0, (62, 15): 0.0, (62, 16): 0.0, (62, 17): 0.0, (62, 18): 0.0, (62, 19): 0.0, (62, 20): 0.5051001633268003, (62, 21): 0.5051001633268003, (62, 22): 0.5051001633268003, (62, 23): 0.5051001633268003, (62, 24): 0.5051001633268003, (62, 25): 0.5051001633268003, (62, 26): 0.0, (62, 27): 0.0, (62, 28): 0.0, (62, 29): 0.0, (62, 30): 0.0, (62, 31): 0.0, (62, 32): 0.0, (62, 33): 0.0, (62, 34): 0.0, (62, 35): 0.0, (62, 36): 0.0, (62, 37): 0.0, (62, 38): 0.0, (62, 39): 0.0, (62, 40): 0.0, (62, 41): 0.0, (62, 42): 0.0, (63, 1): 0.0, (63, 2): 0.0, (63, 3): 0.0, (63, 4): 0.0, (63, 5): 0.0, (63, 6): 0.0, (63, 7): 0.0, (63, 8): 0.0, (63, 9): 0.0, (63, 10): 0.0, (63, 11): 0.0, (63, 12): 0.0, (63, 13): 0.0, (63, 14): 0.0, (63, 15): 0.0, (63, 16): 0.0, (63, 17): 0.0, (63, 18): 0.0, (63, 19): 0.0, (63, 20): 0.0, (63, 21): 0.0, (63, 22): 0.0, (63, 23): 0.0, (63, 24): 0.0, (63, 25): 0.0, (63, 26): 0.0, (63, 27): 0.0, (63, 28): 0.0, (63, 29): 0.0, (63, 30): 0.0, (63, 31): 0.0, (63, 32): 0.0, (63, 33): 0.0, (63, 34): 0.0, (63, 35): 0.0, (63, 36): 0.0, (63, 37): 0.5051001633268003, (63, 38): 0.5051001633268003, (63, 39): 0.5051001633268003, (63, 40): 0.5051001633268003, (63, 41): 0.5051001633268003, (63, 42): 0.5051001633268003, (65, 1): 0.0, (65, 2): 0.0, (65, 3): 0.0, (65, 4): 0.0, (65, 5): 0.0, (65, 6): 0.0, (65, 7): 0.0, (65, 8): 0.0, (65, 9): 0.0, (65, 10): 0.0, (65, 11): 0.0, (65, 12): 0.0, (65, 13): 0.0, (65, 14): 0.0, (65, 15): 0.0, (65, 16): 0.0, (65, 17): 0.0, (65, 18): 0.0, (65, 19): 0.0, (65, 20): 0.0, (65, 21): 0.0, (65, 22): 0.0, (65, 23): 0.0, (65, 24): 0.0, (65, 25): 0.0, (65, 26): 0.0, (65, 27): 0.5051001633268003, (65, 28): 0.5051001633268003, (65, 29): 0.5051001633268003, (65, 30): 0.5051001633268003, (65, 31): 0.5051001633268003, (65, 32): 0.5051001633268003, (65, 33): 0.0, (65, 34): 0.0, (65, 35): 0.0, (65, 36): 0.0, (65, 37): 0.0, (65, 38): 0.0, (65, 39): 0.0, (65, 40): 0.0, (65, 41): 0.0, (65, 42): 0.0, (66, 1): 0.0, (66, 2): 0.0, (66, 3): 0.0, (66, 4): 0.0, (66, 5): 0.0, (66, 6): 0.0, (66, 7): 0.0, (66, 8): 0.0, (66, 9): 0.0, (66, 10): 0.0, (66, 11): 0.0, (66, 12): 0.0, (66, 13): 0.0, (66, 14): 0.0, (66, 15): 0.0, (66, 16): 0.0, (66, 17): 0.0, (66, 18): 0.0, (66, 19): 0.0, (66, 20): 0.0, (66, 21): 0.0, (66, 22): 0.0, (66, 23): 0.0, (66, 24): 0.0, (66, 25): 0.0, (66, 26): 0.0, (66, 27): 0.0, (66, 28): 0.0, (66, 29): 0.0, (66, 30): 0.5051001633268003, (66, 31): 0.5051001633268003, (66, 32): 0.5051001633268003, (66, 33): 0.5051001633268003, (66, 34): 0.5051001633268003, (66, 35): 0.0, (66, 36): 0.0, (66, 37): 0.0, (66, 38): 0.0, (66, 39): 0.0, (66, 40): 0.0, (66, 41): 0.0, (66, 42): 0.0, (67, 1): 0.0, (67, 2): 0.0, (67, 3): 0.0, (67, 4): 0.0, (67, 5): 0.0, (67, 6): 0.0, (67, 7): 0.0, (67, 8): 0.0, (67, 9): 0.0, (67, 10): 0.0, (67, 11): 0.0, (67, 12): 0.0, (67, 13): 0.0, (67, 14): 0.5051001633268003, (67, 15): 0.5051001633268003, (67, 16): 0.5051001633268003, (67, 17): 0.5051001633268003, (67, 18): 0.5051001633268003, (67, 19): 0.5051001633268003, (67, 20): 0.0, (67, 21): 0.0, (67, 22): 0.0, (67, 23): 0.0, (67, 24): 0.0, (67, 25): 0.0, (67, 26): 0.0, (67, 27): 0.0, (67, 28): 0.0, (67, 29): 0.0, (67, 30): 0.0, (67, 31): 0.0, (67, 32): 0.0, (67, 33): 0.0, (67, 34): 0.0, (67, 35): 0.0, (67, 36): 0.0, (67, 37): 0.0, (67, 38): 0.0, (67, 39): 0.0, (67, 40): 0.0, (67, 41): 0.0, (67, 42): 0.0, (70, 1): 0.0, (70, 2): 0.0, (70, 3): 0.0, (70, 4): 0.0, (70, 5): 0.0, (70, 6): 0.0, (70, 7): 0.0, (70, 8): 0.0, (70, 9): 0.0, (70, 10): 0.0, (70, 11): 0.0, (70, 12): 0.0, (70, 13): 0.0, (70, 14): 0.0, (70, 15): 0.0, (70, 16): 0.0, (70, 17): 0.0, (70, 18): 0.0, (70, 19): 0.0, (70, 20): 0.0, (70, 21): 0.0, (70, 22): 0.0, (70, 23): 0.0, (70, 24): 0.0, (70, 25): 0.0, (70, 26): 0.0, (70, 27): 0.0, (70, 28): 0.0, (70, 29): 0.0, (70, 30): 0.0, (70, 31): 0.0, (70, 32): 0.5051001633268003, (70, 33): 0.5051001633268003, (70, 34): 0.5051001633268003, (70, 35): 0.5051001633268003, (70, 36): 0.5051001633268003, (70, 37): 0.0, (70, 38): 0.0, (70, 39): 0.0, (70, 40): 0.0, (70, 41): 0.0, (70, 42): 0.0, (71, 1): 0.0, (71, 2): 0.0, (71, 3): 0.0, (71, 4): 0.0, (71, 5): 0.0, (71, 6): 0.0, (71, 7): 0.0, (71, 8): 0.0, (71, 9): 0.0, (71, 10): 0.0, (71, 11): 0.0, (71, 12): 0.0, (71, 13): 0.0, (71, 14): 0.0, (71, 15): 0.0, (71, 16): 0.0, (71, 17): 0.0, (71, 18): 0.0, (71, 19): 0.0, (71, 20): 0.0, (71, 21): 0.0, (71, 22): 0.0, (71, 23): 0.0, (71, 24): 0.0, (71, 25): 0.0, (71, 26): 0.0, (71, 27): 0.0, (71, 28): 0.0, (71, 29): 0.0, (71, 30): 0.0, (71, 31): 0.0, (71, 32): 0.0, (71, 33): 0.5051001633268003, (71, 34): 0.5051001633268003, (71, 35): 0.5051001633268003, (71, 36): 0.5051001633268003, (71, 37): 0.5051001633268003, (71, 38): 0.5051001633268003, (71, 39): 0.5051001633268003, (71, 40): 0.5051001633268003, (71, 41): 0.0, (71, 42): 0.0, (73, 1): 0.0, (73, 2): 0.0, (73, 3): 0.0, (73, 4): 0.0, (73, 5): 0.0, (73, 6): 0.0, (73, 7): 0.0, (73, 8): 0.0, (73, 9): 0.0, (73, 10): 0.0, (73, 11): 0.0, (73, 12): 0.0, (73, 13): 0.0, (73, 14): 0.0, (73, 15): 0.0, (73, 16): 0.0, (73, 17): 0.0, (73, 18): 0.0, (73, 19): 0.0, (73, 20): 0.0, (73, 21): 0.0, (73, 22): 0.0, (73, 23): 0.0, (73, 24): 0.0, (73, 25): 0.0, (73, 26): 0.0, (73, 27): 0.0, (73, 28): 0.0, (73, 29): 0.0, (73, 30): 0.0, (73, 31): 0.5051001633268003, (73, 32): 0.5051001633268003, (73, 33): 0.5051001633268003, (73, 34): 0.5051001633268003, (73, 35): 0.5051001633268003, (73, 36): 0.5051001633268003, (73, 37): 0.5051001633268003, (73, 38): 0.5051001633268003, (73, 39): 0.5051001633268003, (73, 40): 0.5051001633268003, (73, 41): 0.5051001633268003, (73, 42): 0.0, (75, 1): 0.0, (75, 2): 0.0, (75, 3): 0.0, (75, 4): 0.0, (75, 5): 0.0, (75, 6): 0.0, (75, 7): 0.0, (75, 8): 0.0, (75, 9): 0.0, (75, 10): 0.0, (75, 11): 0.0, (75, 12): 0.0, (75, 13): 0.0, (75, 14): 0.0, (75, 15): 0.0, (75, 16): 0.0, (75, 17): 0.0, (75, 18): 0.0, (75, 19): 0.0, (75, 20): 0.5051001633268003, (75, 21): 0.5051001633268003, (75, 22): 0.5051001633268003, (75, 23): 0.5051001633268003, (75, 24): 0.5051001633268003, (75, 25): 0.5051001633268003, (75, 26): 0.5051001633268003, (75, 27): 0.0, (75, 28): 0.0, (75, 29): 0.0, (75, 30): 0.0, (75, 31): 0.0, (75, 32): 0.0, (75, 33): 0.0, (75, 34): 0.0, (75, 35): 0.0, (75, 36): 0.0, (75, 37): 0.0, (75, 38): 0.0, (75, 39): 0.0, (75, 40): 0.0, (75, 41): 0.0, (75, 42): 0.0, (77, 1): 0.0, (77, 2): 0.0, (77, 3): 0.0, (77, 4): 0.0, (77, 5): 0.0, (77, 6): 0.0, (77, 7): 0.0, (77, 8): 0.0, (77, 9): 0.0, (77, 10): 0.0, (77, 11): 0.0, (77, 12): 0.0, (77, 13): 0.0, (77, 14): 0.0, (77, 15): 0.0, (77, 16): 0.0, (77, 17): 0.0, (77, 18): 0.0, (77, 19): 0.0, (77, 20): 0.0, (77, 21): 0.0, (77, 22): 0.0, (77, 23): 0.0, (77, 24): 0.0, (77, 25): 0.0, (77, 26): 0.0, (77, 27): 0.0, (77, 28): 0.0, (77, 29): 0.0, (77, 30): 0.0, (77, 31): 0.0, (77, 32): 0.0, (77, 33): 0.0, (77, 34): 0.0, (77, 35): 0.0, (77, 36): 0.0, (77, 37): 0.0, (77, 38): 0.0, (77, 39): 0.0, (77, 40): 0.5051001633268003, (77, 41): 0.5051001633268003, (77, 42): 0.5051001633268003, (78, 1): 0.0, (78, 2): 0.0, (78, 3): 0.0, (78, 4): 0.0, (78, 5): 0.0, (78, 6): 0.0, (78, 7): 0.0, (78, 8): 0.0, (78, 9): 0.0, (78, 10): 0.0, (78, 11): 0.5051001633268003, (78, 12): 0.5051001633268003, (78, 13): 0.5051001633268003, (78, 14): 0.5051001633268003, (78, 15): 0.5051001633268003, (78, 16): 0.5051001633268003, (78, 17): 0.5051001633268003, (78, 18): 0.5051001633268003, (78, 19): 0.0, (78, 20): 0.0, (78, 21): 0.0, (78, 22): 0.0, (78, 23): 0.0, (78, 24): 0.0, (78, 25): 0.0, (78, 26): 0.0, (78, 27): 0.0, (78, 28): 0.0, (78, 29): 0.0, (78, 30): 0.0, (78, 31): 0.0, (78, 32): 0.0, (78, 33): 0.0, (78, 34): 0.0, (78, 35): 0.0, (78, 36): 0.0, (78, 37): 0.0, (78, 38): 0.0, (78, 39): 0.0, (78, 40): 0.0, (78, 41): 0.0, (78, 42): 0.0, (79, 1): 0.0, (79, 2): 0.0, (79, 3): 0.0, (79, 4): 0.0, (79, 5): 0.0, (79, 6): 0.0, (79, 7): 0.0, (79, 8): 0.0, (79, 9): 0.0, (79, 10): 0.0, (79, 11): 0.0, (79, 12): 0.0, (79, 13): 0.0, (79, 14): 0.0, (79, 15): 0.0, (79, 16): 0.0, (79, 17): 0.0, (79, 18): 0.0, (79, 19): 0.0, (79, 20): 0.5051001633268003, (79, 21): 0.5051001633268003, (79, 22): 0.5051001633268003, (79, 23): 0.5051001633268003, (79, 24): 0.5051001633268003, (79, 25): 0.5051001633268003, (79, 26): 0.0, (79, 27): 0.0, (79, 28): 0.0, (79, 29): 0.0, (79, 30): 0.0, (79, 31): 0.0, (79, 32): 0.0, (79, 33): 0.0, (79, 34): 0.0, (79, 35): 0.0, (79, 36): 0.0, (79, 37): 0.0, (79, 38): 0.0, (79, 39): 0.0, (79, 40): 0.0, (79, 41): 0.0, (79, 42): 0.0, (81, 1): 0.0, (81, 2): 0.0, (81, 3): 0.0, (81, 4): 0.0, (81, 5): 0.0, (81, 6): 0.0, (81, 7): 0.0, (81, 8): 0.0, (81, 9): 0.0, (81, 10): 0.0, (81, 11): 0.0, (81, 12): 0.5051001633268003, (81, 13): 0.5051001633268003, (81, 14): 0.5051001633268003, (81, 15): 0.5051001633268003, (81, 16): 0.5051001633268003, (81, 17): 0.5051001633268003, (81, 18): 0.0, (81, 19): 0.0, (81, 20): 0.0, (81, 21): 0.0, (81, 22): 0.0, (81, 23): 0.0, (81, 24): 0.0, (81, 25): 0.0, (81, 26): 0.0, (81, 27): 0.0, (81, 28): 0.0, (81, 29): 0.0, (81, 30): 0.0, (81, 31): 0.0, (81, 32): 0.0, (81, 33): 0.0, (81, 34): 0.0, (81, 35): 0.0, (81, 36): 0.0, (81, 37): 0.0, (81, 38): 0.0, (81, 39): 0.0, (81, 40): 0.0, (81, 41): 0.0, (81, 42): 0.0, (82, 1): 0.0, (82, 2): 0.0, (82, 3): 0.0, (82, 4): 0.0, (82, 5): 0.0, (82, 6): 0.0, (82, 7): 0.0, (82, 8): 0.0, (82, 9): 0.5051001633268003, (82, 10): 0.5051001633268003, (82, 11): 0.5051001633268003, (82, 12): 0.5051001633268003, (82, 13): 0.5051001633268003, (82, 14): 0.5051001633268003, (82, 15): 0.5051001633268003, (82, 16): 0.0, (82, 17): 0.0, (82, 18): 0.0, (82, 19): 0.0, (82, 20): 0.0, (82, 21): 0.0, (82, 22): 0.0, (82, 23): 0.0, (82, 24): 0.0, (82, 25): 0.0, (82, 26): 0.0, (82, 27): 0.0, (82, 28): 0.0, (82, 29): 0.0, (82, 30): 0.0, (82, 31): 0.0, (82, 32): 0.0, (82, 33): 0.0, (82, 34): 0.0, (82, 35): 0.0, (82, 36): 0.0, (82, 37): 0.0, (82, 38): 0.0, (82, 39): 0.0, (82, 40): 0.0, (82, 41): 0.0, (82, 42): 0.0}</t>
-  </si>
-  <si>
-    <t>{(2, 1): 0.0, (2, 2): 0.0, (2, 3): 0.0, (2, 4): 0.0, (2, 5): 0.0, (2, 6): 0.0, (2, 7): 0.0, (2, 8): 0.0, (2, 9): 0.0, (2, 10): 0.0, (2, 11): 0.0, (2, 12): 0.0, (2, 13): 0.0, (2, 14): 0.0, (2, 15): 0.0, (2, 16): 0.0, (2, 17): 1.0, (2, 18): 2.0, (2, 19): 3.0, (2, 20): 4.0, (2, 21): 4.0, (2, 22): 5.0, (2, 23): 6.0, (2, 24): 7.0, (2, 25): 8.0, (2, 26): 9.0, (2, 27): 10.0, (2, 28): 10.0, (2, 29): 11.0, (2, 30): 12.0, (2, 31): 13.0, (2, 32): 13.0, (2, 33): 14.0, (2, 34): 15.0, (2, 35): 15.0, (2, 36): 16.0, (2, 37): 17.0, (2, 38): 18.0, (2, 39): 18.0, (2, 40): 18.0, (2, 41): 19.0, (2, 42): 19.0, (3, 1): 0.0, (3, 2): 0.0, (3, 3): 0.0, (3, 4): 0.0, (3, 5): 0.0, (3, 6): 0.0, (3, 7): 0.0, (3, 8): 0.0, (3, 9): 0.0, (3, 10): 0.0, (3, 11): 0.0, (3, 12): 0.0, (3, 13): 0.0, (3, 14): 0.0, (3, 15): 0.0, (3, 16): 0.0, (3, 17): 1.0, (3, 18): 2.0, (3, 19): 3.0, (3, 20): 4.0, (3, 21): 5.0, (3, 22): 6.0, (3, 23): 6.0, (3, 24): 7.0, (3, 25): 8.0, (3, 26): 9.0, (3, 27): 9.0, (3, 28): 10.0, (3, 29): 10.0, (3, 30): 10.0, (3, 31): 11.0, (3, 32): 11.0, (3, 33): 12.0, (3, 34): 12.0, (3, 35): 13.0, (3, 36): 13.0, (3, 37): 13.0, (3, 38): 13.0, (3, 39): 13.0, (3, 40): 13.0, (3, 41): 13.0, (3, 42): 13.0, (4, 1): 0.0, (4, 2): 0.0, (4, 3): 0.0, (4, 4): 0.0, (4, 5): 0.0, (4, 6): 0.0, (4, 7): 0.0, (4, 8): 0.0, (4, 9): 0.0, (4, 10): 0.0, (4, 11): 0.0, (4, 12): 0.0, (4, 13): 0.0, (4, 14): 0.0, (4, 15): 0.0, (4, 16): 0.0, (4, 17): 0.0, (4, 18): 0.0, (4, 19): 0.0, (4, 20): 0.0, (4, 21): 0.0, (4, 22): 0.0, (4, 23): 0.0, (4, 24): 0.0, (4, 25): 0.0, (4, 26): 0.0, (4, 27): 0.0, (4, 28): 0.0, (4, 29): 0.0, (4, 30): 1.0, (4, 31): 2.0, (4, 32): 2.0, (4, 33): 3.0, (4, 34): 3.0, (4, 35): 3.0, (4, 36): 4.0, (4, 37): 5.0, (4, 38): 5.0, (4, 39): 5.0, (4, 40): 6.0, (4, 41): 7.0, (4, 42): 7.0, (9, 1): 0.0, (9, 2): 0.0, (9, 3): 0.0, (9, 4): 0.0, (9, 5): 0.0, (9, 6): 0.0, (9, 7): 0.0, (9, 8): 0.0, (9, 9): 0.0, (9, 10): 0.0, (9, 11): 0.0, (9, 12): 0.0, (9, 13): 0.0, (9, 14): 0.0, (9, 15): 0.0, (9, 16): 0.0, (9, 17): 0.0, (9, 18): 0.0, (9, 19): 0.0, (9, 20): 0.0, (9, 21): 0.0, (9, 22): 1.0, (9, 23): 2.0, (9, 24): 3.0, (9, 25): 4.0, (9, 26): 5.0, (9, 27): 6.0, (9, 28): 6.0, (9, 29): 7.0, (9, 30): 8.0, (9, 31): 8.0, (9, 32): 8.0, (9, 33): 9.0, (9, 34): 10.0, (9, 35): 10.0, (9, 36): 10.0, (9, 37): 10.0, (9, 38): 11.0, (9, 39): 11.0, (9, 40): 11.0, (9, 41): 11.0, (9, 42): 11.0, (15, 1): 0.0, (15, 2): 0.0, (15, 3): 0.0, (15, 4): 0.0, (15, 5): 0.0, (15, 6): 0.0, (15, 7): 0.0, (15, 8): 0.0, (15, 9): 0.0, (15, 10): 0.0, (15, 11): 0.0, (15, 12): 0.0, (15, 13): 0.0, (15, 14): 0.0, (15, 15): 0.0, (15, 16): 0.0, (15, 17): 0.0, (15, 18): 0.0, (15, 19): 0.0, (15, 20): 0.0, (15, 21): 0.0, (15, 22): 0.0, (15, 23): 0.0, (15, 24): 0.0, (15, 25): 0.0, (15, 26): 0.0, (15, 27): 0.0, (15, 28): 0.0, (15, 29): 0.0, (15, 30): 1.0, (15, 31): 2.0, (15, 32): 3.0, (15, 33): 4.0, (15, 34): 5.0, (15, 35): 6.0, (15, 36): 6.0, (15, 37): 7.0, (15, 38): 8.0, (15, 39): 9.0, (15, 40): 9.0, (15, 41): 10.0, (15, 42): 10.0, (16, 1): 0.0, (16, 2): 0.0, (16, 3): 0.0, (16, 4): 0.0, (16, 5): 0.0, (16, 6): 0.0, (16, 7): 0.0, (16, 8): 0.0, (16, 9): 0.0, (16, 10): 0.0, (16, 11): 1.0, (16, 12): 2.0, (16, 13): 3.0, (16, 14): 4.0, (16, 15): 5.0, (16, 16): 5.0, (16, 17): 6.0, (16, 18): 6.0, (16, 19): 7.0, (16, 20): 7.0, (16, 21): 7.0, (16, 22): 7.0, (16, 23): 7.0, (16, 24): 7.0, (16, 25): 7.0, (16, 26): 7.0, (16, 27): 7.0, (16, 28): 7.0, (16, 29): 7.0, (16, 30): 7.0, (16, 31): 7.0, (16, 32): 7.0, (16, 33): 7.0, (16, 34): 7.0, (16, 35): 7.0, (16, 36): 7.0, (16, 37): 7.0, (16, 38): 7.0, (16, 39): 7.0, (16, 40): 7.0, (16, 41): 7.0, (16, 42): 7.0, (20, 1): 0.0, (20, 2): 0.0, (20, 3): 0.0, (20, 4): 0.0, (20, 5): 0.0, (20, 6): 0.0, (20, 7): 0.0, (20, 8): 0.0, (20, 9): 0.0, (20, 10): 0.0, (20, 11): 0.0, (20, 12): 0.0, (20, 13): 0.0, (20, 14): 0.0, (20, 15): 0.0, (20, 16): 0.0, (20, 17): 0.0, (20, 18): 0.0, (20, 19): 0.0, (20, 20): 0.0, (20, 21): 0.0, (20, 22): 0.0, (20, 23): 0.0, (20, 24): 0.0, (20, 25): 0.0, (20, 26): 0.0, (20, 27): 0.0, (20, 28): 0.0, (20, 29): 0.0, (20, 30): 0.0, (20, 31): 0.0, (20, 32): 1.0, (20, 33): 1.0, (20, 34): 2.0, (20, 35): 2.0, (20, 36): 3.0, (20, 37): 4.0, (20, 38): 4.0, (20, 39): 4.0, (20, 40): 4.0, (20, 41): 4.0, (20, 42): 4.0, (21, 1): 0.0, (21, 2): 0.0, (21, 3): 0.0, (21, 4): 0.0, (21, 5): 0.0, (21, 6): 0.0, (21, 7): 0.0, (21, 8): 0.0, (21, 9): 0.0, (21, 10): 0.0, (21, 11): 0.0, (21, 12): 0.0, (21, 13): 0.0, (21, 14): 0.0, (21, 15): 0.0, (21, 16): 0.0, (21, 17): 0.0, (21, 18): 0.0, (21, 19): 0.0, (21, 20): 0.0, (21, 21): 0.0, (21, 22): 0.0, (21, 23): 0.0, (21, 24): 0.0, (21, 25): 0.0, (21, 26): 0.0, (21, 27): 1.0, (21, 28): 1.0, (21, 29): 2.0, (21, 30): 3.0, (21, 31): 4.0, (21, 32): 4.0, (21, 33): 5.0, (21, 34): 6.0, (21, 35): 6.0, (21, 36): 7.0, (21, 37): 8.0, (21, 38): 8.0, (21, 39): 8.0, (21, 40): 8.0, (21, 41): 9.0, (21, 42): 9.0, (22, 1): 0.0, (22, 2): 0.0, (22, 3): 0.0, (22, 4): 0.0, (22, 5): 0.0, (22, 6): 0.0, (22, 7): 0.0, (22, 8): 0.0, (22, 9): 0.0, (22, 10): 0.0, (22, 11): 0.0, (22, 12): 0.0, (22, 13): 0.0, (22, 14): 0.0, (22, 15): 0.0, (22, 16): 0.0, (22, 17): 0.0, (22, 18): 0.0, (22, 19): 0.0, (22, 20): 0.0, (22, 21): 0.0, (22, 22): 0.0, (22, 23): 0.0, (22, 24): 0.0, (22, 25): 0.0, (22, 26): 0.0, (22, 27): 1.0, (22, 28): 2.0, (22, 29): 3.0, (22, 30): 3.0, (22, 31): 4.0, (22, 32): 4.0, (22, 33): 5.0, (22, 34): 6.0, (22, 35): 7.0, (22, 36): 8.0, (22, 37): 8.0, (22, 38): 8.0, (22, 39): 9.0, (22, 40): 9.0, (22, 41): 9.0, (22, 42): 9.0, (23, 1): 0.0, (23, 2): 0.0, (23, 3): 0.0, (23, 4): 0.0, (23, 5): 0.0, (23, 6): 0.0, (23, 7): 0.0, (23, 8): 0.0, (23, 9): 0.0, (23, 10): 0.0, (23, 11): 0.0, (23, 12): 0.0, (23, 13): 0.0, (23, 14): 0.0, (23, 15): 0.0, (23, 16): 0.0, (23, 17): 0.0, (23, 18): 0.0, (23, 19): 0.0, (23, 20): 0.0, (23, 21): 0.0, (23, 22): 0.0, (23, 23): 0.0, (23, 24): 0.0, (23, 25): 0.0, (23, 26): 0.0, (23, 27): 0.0, (23, 28): 0.0, (23, 29): 1.0, (23, 30): 1.0, (23, 31): 2.0, (23, 32): 3.0, (23, 33): 3.0, (23, 34): 4.0, (23, 35): 4.0, (23, 36): 4.0, (23, 37): 4.0, (23, 38): 4.0, (23, 39): 4.0, (23, 40): 4.0, (23, 41): 4.0, (23, 42): 4.0, (24, 1): 0.0, (24, 2): 0.0, (24, 3): 0.0, (24, 4): 0.0, (24, 5): 0.0, (24, 6): 0.0, (24, 7): 0.0, (24, 8): 0.0, (24, 9): 0.0, (24, 10): 0.0, (24, 11): 0.0, (24, 12): 0.0, (24, 13): 0.0, (24, 14): 0.0, (24, 15): 0.0, (24, 16): 0.0, (24, 17): 0.0, (24, 18): 0.0, (24, 19): 0.0, (24, 20): 0.0, (24, 21): 0.0, (24, 22): 1.0, (24, 23): 2.0, (24, 24): 3.0, (24, 25): 4.0, (24, 26): 5.0, (24, 27): 5.0, (24, 28): 5.0, (24, 29): 6.0, (24, 30): 6.0, (24, 31): 6.0, (24, 32): 6.0, (24, 33): 6.0, (24, 34): 6.0, (24, 35): 6.0, (24, 36): 6.0, (24, 37): 6.0, (24, 38): 6.0, (24, 39): 6.0, (24, 40): 6.0, (24, 41): 6.0, (24, 42): 6.0, (25, 1): 0.0, (25, 2): 0.0, (25, 3): 0.0, (25, 4): 0.0, (25, 5): 0.0, (25, 6): 0.0, (25, 7): 0.0, (25, 8): 0.0, (25, 9): 0.0, (25, 10): 0.0, (25, 11): 0.0, (25, 12): 0.0, (25, 13): 0.0, (25, 14): 0.0, (25, 15): 0.0, (25, 16): 0.0, (25, 17): 0.0, (25, 18): 0.0, (25, 19): 0.0, (25, 20): 0.0, (25, 21): 0.0, (25, 22): 0.0, (25, 23): 0.0, (25, 24): 0.0, (25, 25): 0.0, (25, 26): 0.0, (25, 27): 0.0, (25, 28): 0.0, (25, 29): 0.0, (25, 30): 0.0, (25, 31): 0.0, (25, 32): 0.0, (25, 33): 0.0, (25, 34): 0.0, (25, 35): 0.0, (25, 36): 0.0, (25, 37): 0.0, (25, 38): 1.0, (25, 39): 1.0, (25, 40): 1.0, (25, 41): 1.0, (25, 42): 2.0, (26, 1): 0.0, (26, 2): 0.0, (26, 3): 0.0, (26, 4): 0.0, (26, 5): 0.0, (26, 6): 0.0, (26, 7): 0.0, (26, 8): 0.0, (26, 9): 0.0, (26, 10): 0.0, (26, 11): 0.0, (26, 12): 0.0, (26, 13): 0.0, (26, 14): 0.0, (26, 15): 0.0, (26, 16): 0.0, (26, 17): 0.0, (26, 18): 0.0, (26, 19): 0.0, (26, 20): 0.0, (26, 21): 0.0, (26, 22): 0.0, (26, 23): 0.0, (26, 24): 0.0, (26, 25): 0.0, (26, 26): 1.0, (26, 27): 2.0, (26, 28): 2.0, (26, 29): 2.0, (26, 30): 2.0, (26, 31): 3.0, (26, 32): 3.0, (26, 33): 3.0, (26, 34): 3.0, (26, 35): 3.0, (26, 36): 3.0, (26, 37): 3.0, (26, 38): 3.0, (26, 39): 3.0, (26, 40): 3.0, (26, 41): 3.0, (26, 42): 3.0, (28, 1): 0.0, (28, 2): 0.0, (28, 3): 0.0, (28, 4): 0.0, (28, 5): 0.0, (28, 6): 0.0, (28, 7): 0.0, (28, 8): 0.0, (28, 9): 0.0, (28, 10): 0.0, (28, 11): 0.0, (28, 12): 0.0, (28, 13): 0.0, (28, 14): 0.0, (28, 15): 0.0, (28, 16): 0.0, (28, 17): 0.0, (28, 18): 0.0, (28, 19): 0.0, (28, 20): 0.0, (28, 21): 0.0, (28, 22): 0.0, (28, 23): 0.0, (28, 24): 0.0, (28, 25): 0.0, (28, 26): 0.0, (28, 27): 0.0, (28, 28): 0.0, (28, 29): 0.0, (28, 30): 1.0, (28, 31): 2.0, (28, 32): 2.0, (28, 33): 3.0, (28, 34): 4.0, (28, 35): 4.0, (28, 36): 4.0, (28, 37): 5.0, (28, 38): 6.0, (28, 39): 7.0, (28, 40): 8.0, (28, 41): 9.0, (28, 42): 9.0, (30, 1): 0.0, (30, 2): 0.0, (30, 3): 0.0, (30, 4): 0.0, (30, 5): 0.0, (30, 6): 0.0, (30, 7): 0.0, (30, 8): 0.0, (30, 9): 0.0, (30, 10): 0.0, (30, 11): 0.0, (30, 12): 0.0, (30, 13): 0.0, (30, 14): 0.0, (30, 15): 0.0, (30, 16): 0.0, (30, 17): 0.0, (30, 18): 0.0, (30, 19): 0.0, (30, 20): 0.0, (30, 21): 0.0, (30, 22): 0.0, (30, 23): 1.0, (30, 24): 2.0, (30, 25): 2.0, (30, 26): 3.0, (30, 27): 4.0, (30, 28): 5.0, (30, 29): 5.0, (30, 30): 6.0, (30, 31): 6.0, (30, 32): 6.0, (30, 33): 6.0, (30, 34): 6.0, (30, 35): 6.0, (30, 36): 6.0, (30, 37): 6.0, (30, 38): 6.0, (30, 39): 6.0, (30, 40): 6.0, (30, 41): 6.0, (30, 42): 6.0, (31, 1): 0.0, (31, 2): 0.0, (31, 3): 0.0, (31, 4): 0.0, (31, 5): 0.0, (31, 6): 0.0, (31, 7): 0.0, (31, 8): 1.0, (31, 9): 2.0, (31, 10): 3.0, (31, 11): 4.0, (31, 12): 5.0, (31, 13): 6.0, (31, 14): 6.0, (31, 15): 6.0, (31, 16): 7.0, (31, 17): 8.0, (31, 18): 9.0, (31, 19): 10.0, (31, 20): 11.0, (31, 21): 11.0, (31, 22): 11.0, (31, 23): 11.0, (31, 24): 11.0, (31, 25): 11.0, (31, 26): 11.0, (31, 27): 11.0, (31, 28): 11.0, (31, 29): 11.0, (31, 30): 11.0, (31, 31): 11.0, (31, 32): 11.0, (31, 33): 11.0, (31, 34): 11.0, (31, 35): 11.0, (31, 36): 11.0, (31, 37): 11.0, (31, 38): 11.0, (31, 39): 11.0, (31, 40): 11.0, (31, 41): 11.0, (31, 42): 11.0, (36, 1): 0.0, (36, 2): 0.0, (36, 3): 0.0, (36, 4): 0.0, (36, 5): 0.0, (36, 6): 0.0, (36, 7): 0.0, (36, 8): 0.0, (36, 9): 0.0, (36, 10): 0.0, (36, 11): 0.0, (36, 12): 0.0, (36, 13): 0.0, (36, 14): 0.0, (36, 15): 0.0, (36, 16): 0.0, (36, 17): 0.0, (36, 18): 0.0, (36, 19): 0.0, (36, 20): 0.0, (36, 21): 0.0, (36, 22): 0.0, (36, 23): 0.0, (36, 24): 0.0, (36, 25): 0.0, (36, 26): 0.0, (36, 27): 0.0, (36, 28): 1.0, (36, 29): 2.0, (36, 30): 2.0, (36, 31): 3.0, (36, 32): 3.0, (36, 33): 3.0, (36, 34): 4.0, (36, 35): 5.0, (36, 36): 6.0, (36, 37): 6.0, (36, 38): 7.0, (36, 39): 7.0, (36, 40): 7.0, (36, 41): 7.0, (36, 42): 7.0, (37, 1): 0.0, (37, 2): 0.0, (37, 3): 0.0, (37, 4): 0.0, (37, 5): 0.0, (37, 6): 0.0, (37, 7): 0.0, (37, 8): 0.0, (37, 9): 0.0, (37, 10): 0.0, (37, 11): 0.0, (37, 12): 0.0, (37, 13): 0.0, (37, 14): 0.0, (37, 15): 0.0, (37, 16): 0.0, (37, 17): 0.0, (37, 18): 0.0, (37, 19): 0.0, (37, 20): 0.0, (37, 21): 0.0, (37, 22): 0.0, (37, 23): 0.0, (37, 24): 0.0, (37, 25): 0.0, (37, 26): 2.0, (37, 27): 2.0, (37, 28): 4.0, (37, 29): 5.0, (37, 30): 5.0, (37, 31): 6.0, (37, 32): 6.0, (37, 33): 8.0, (37, 34): 8.0, (37, 35): 8.0, (37, 36): 8.0, (37, 37): 8.0, (37, 38): 8.0, (37, 39): 8.0, (37, 40): 8.0, (37, 41): 8.0, (37, 42): 8.0, (38, 1): 0.0, (38, 2): 0.0, (38, 3): 0.0, (38, 4): 0.0, (38, 5): 0.0, (38, 6): 0.0, (38, 7): 0.0, (38, 8): 0.0, (38, 9): 0.0, (38, 10): 0.0, (38, 11): 0.0, (38, 12): 0.0, (38, 13): 0.0, (38, 14): 0.0, (38, 15): 0.0, (38, 16): 0.0, (38, 17): 0.0, (38, 18): 0.0, (38, 19): 0.0, (38, 20): 0.0, (38, 21): 0.0, (38, 22): 0.0, (38, 23): 0.0, (38, 24): 0.0, (38, 25): 0.0, (38, 26): 0.0, (38, 27): 0.0, (38, 28): 0.0, (38, 29): 0.0, (38, 30): 0.0, (38, 31): 0.0, (38, 32): 0.0, (38, 33): 0.0, (38, 34): 0.0, (38, 35): 0.0, (38, 36): 0.0, (38, 37): 0.0, (38, 38): 0.0, (38, 39): 0.0, (38, 40): 0.0, (38, 41): 1.0, (38, 42): 1.0, (39, 1): 0.0, (39, 2): 0.0, (39, 3): 0.0, (39, 4): 0.0, (39, 5): 0.0, (39, 6): 0.0, (39, 7): 0.0, (39, 8): 0.0, (39, 9): 0.0, (39, 10): 0.0, (39, 11): 0.0, (39, 12): 0.0, (39, 13): 0.0, (39, 14): 0.0, (39, 15): 0.0, (39, 16): 0.0, (39, 17): 0.0, (39, 18): 1.0, (39, 19): 2.0, (39, 20): 3.0, (39, 21): 3.0, (39, 22): 4.0, (39, 23): 4.0, (39, 24): 5.0, (39, 25): 5.0, (39, 26): 5.0, (39, 27): 5.0, (39, 28): 5.0, (39, 29): 5.0, (39, 30): 5.0, (39, 31): 5.0, (39, 32): 5.0, (39, 33): 5.0, (39, 34): 5.0, (39, 35): 5.0, (39, 36): 5.0, (39, 37): 5.0, (39, 38): 5.0, (39, 39): 5.0, (39, 40): 5.0, (39, 41): 5.0, (39, 42): 5.0, (40, 1): 0.0, (40, 2): 0.0, (40, 3): 0.0, (40, 4): 0.0, (40, 5): 0.0, (40, 6): 0.0, (40, 7): 0.0, (40, 8): 1.0, (40, 9): 2.0, (40, 10): 3.0, (40, 11): 4.0, (40, 12): 5.0, (40, 13): 5.0, (40, 14): 5.0, (40, 15): 6.0, (40, 16): 6.0, (40, 17): 6.0, (40, 18): 6.0, (40, 19): 6.0, (40, 20): 6.0, (40, 21): 6.0, (40, 22): 6.0, (40, 23): 6.0, (40, 24): 6.0, (40, 25): 6.0, (40, 26): 6.0, (40, 27): 6.0, (40, 28): 6.0, (40, 29): 6.0, (40, 30): 6.0, (40, 31): 6.0, (40, 32): 6.0, (40, 33): 6.0, (40, 34): 6.0, (40, 35): 6.0, (40, 36): 6.0, (40, 37): 6.0, (40, 38): 6.0, (40, 39): 6.0, (40, 40): 6.0, (40, 41): 6.0, (40, 42): 6.0, (41, 1): 0.0, (41, 2): 0.0, (41, 3): 0.0, (41, 4): 0.0, (41, 5): 0.0, (41, 6): 0.0, (41, 7): 0.0, (41, 8): 0.0, (41, 9): 0.0, (41, 10): 0.0, (41, 11): 0.0, (41, 12): 0.0, (41, 13): 0.0, (41, 14): 0.0, (41, 15): 0.0, (41, 16): 0.0, (41, 17): 0.0, (41, 18): 0.0, (41, 19): 0.0, (41, 20): 0.0, (41, 21): 0.0, (41, 22): 0.0, (41, 23): 1.0, (41, 24): 2.0, (41, 25): 3.0, (41, 26): 3.0, (41, 27): 3.0, (41, 28): 4.0, (41, 29): 4.0, (41, 30): 4.0, (41, 31): 4.0, (41, 32): 4.0, (41, 33): 4.0, (41, 34): 4.0, (41, 35): 4.0, (41, 36): 4.0, (41, 37): 4.0, (41, 38): 4.0, (41, 39): 4.0, (41, 40): 4.0, (41, 41): 4.0, (41, 42): 4.0, (43, 1): 0.0, (43, 2): 0.0, (43, 3): 0.0, (43, 4): 0.0, (43, 5): 0.0, (43, 6): 0.0, (43, 7): 0.0, (43, 8): 0.0, (43, 9): 0.0, (43, 10): 0.0, (43, 11): 0.0, (43, 12): 0.0, (43, 13): 0.0, (43, 14): 0.0, (43, 15): 0.0, (43, 16): 0.0, (43, 17): 1.0, (43, 18): 2.0, (43, 19): 2.0, (43, 20): 3.0, (43, 21): 4.0, (43, 22): 5.0, (43, 23): 5.0, (43, 24): 6.0, (43, 25): 6.0, (43, 26): 6.0, (43, 27): 6.0, (43, 28): 6.0, (43, 29): 6.0, (43, 30): 6.0, (43, 31): 6.0, (43, 32): 6.0, (43, 33): 6.0, (43, 34): 6.0, (43, 35): 6.0, (43, 36): 6.0, (43, 37): 6.0, (43, 38): 6.0, (43, 39): 6.0, (43, 40): 6.0, (43, 41): 6.0, (43, 42): 6.0, (50, 1): 0.0, (50, 2): 0.0, (50, 3): 0.0, (50, 4): 0.0, (50, 5): 0.0, (50, 6): 0.0, (50, 7): 0.0, (50, 8): 0.0, (50, 9): 0.0, (50, 10): 0.0, (50, 11): 1.0, (50, 12): 2.0, (50, 13): 2.0, (50, 14): 2.0, (50, 15): 3.0, (50, 16): 3.0, (50, 17): 4.0, (50, 18): 4.0, (50, 19): 4.0, (50, 20): 4.0, (50, 21): 4.0, (50, 22): 4.0, (50, 23): 4.0, (50, 24): 4.0, (50, 25): 4.0, (50, 26): 4.0, (50, 27): 4.0, (50, 28): 4.0, (50, 29): 4.0, (50, 30): 4.0, (50, 31): 4.0, (50, 32): 4.0, (50, 33): 4.0, (50, 34): 4.0, (50, 35): 4.0, (50, 36): 4.0, (50, 37): 4.0, (50, 38): 4.0, (50, 39): 4.0, (50, 40): 4.0, (50, 41): 4.0, (50, 42): 4.0, (59, 1): 0.0, (59, 2): 0.0, (59, 3): 0.0, (59, 4): 0.0, (59, 5): 0.0, (59, 6): 0.0, (59, 7): 0.0, (59, 8): 0.0, (59, 9): 0.0, (59, 10): 0.0, (59, 11): 0.0, (59, 12): 0.0, (59, 13): 0.0, (59, 14): 0.0, (59, 15): 1.0, (59, 16): 2.0, (59, 17): 3.0, (59, 18): 4.0, (59, 19): 5.0, (59, 20): 6.0, (59, 21): 6.0, (59, 22): 6.0, (59, 23): 7.0, (59, 24): 7.0, (59, 25): 7.0, (59, 26): 7.0, (59, 27): 7.0, (59, 28): 7.0, (59, 29): 7.0, (59, 30): 7.0, (59, 31): 7.0, (59, 32): 7.0, (59, 33): 7.0, (59, 34): 7.0, (59, 35): 7.0, (59, 36): 7.0, (59, 37): 7.0, (59, 38): 7.0, (59, 39): 7.0, (59, 40): 7.0, (59, 41): 7.0, (59, 42): 7.0, (60, 1): 0.0, (60, 2): 0.0, (60, 3): 0.0, (60, 4): 0.0, (60, 5): 0.0, (60, 6): 0.0, (60, 7): 0.0, (60, 8): 0.0, (60, 9): 0.0, (60, 10): 0.0, (60, 11): 0.0, (60, 12): 0.0, (60, 13): 0.0, (60, 14): 0.0, (60, 15): 0.0, (60, 16): 0.0, (60, 17): 0.0, (60, 18): 0.0, (60, 19): 0.0, (60, 20): 0.0, (60, 21): 0.0, (60, 22): 0.0, (60, 23): 0.0, (60, 24): 0.0, (60, 25): 0.0, (60, 26): 0.0, (60, 27): 0.0, (60, 28): 0.0, (60, 29): 0.0, (60, 30): 0.0, (60, 31): 0.0, (60, 32): 0.0, (60, 33): 0.0, (60, 34): 0.0, (60, 35): 0.0, (60, 36): 0.0, (60, 37): 0.0, (60, 38): 1.0, (60, 39): 1.0, (60, 40): 1.0, (60, 41): 1.0, (60, 42): 2.0, (62, 1): 0.0, (62, 2): 0.0, (62, 3): 0.0, (62, 4): 0.0, (62, 5): 0.0, (62, 6): 0.0, (62, 7): 0.0, (62, 8): 0.0, (62, 9): 0.0, (62, 10): 0.0, (62, 11): 0.0, (62, 12): 0.0, (62, 13): 0.0, (62, 14): 0.0, (62, 15): 0.0, (62, 16): 0.0, (62, 17): 0.0, (62, 18): 0.0, (62, 19): 0.0, (62, 20): 1.0, (62, 21): 2.0, (62, 22): 2.0, (62, 23): 3.0, (62, 24): 3.0, (62, 25): 4.0, (62, 26): 4.0, (62, 27): 4.0, (62, 28): 4.0, (62, 29): 4.0, (62, 30): 4.0, (62, 31): 4.0, (62, 32): 4.0, (62, 33): 4.0, (62, 34): 4.0, (62, 35): 4.0, (62, 36): 4.0, (62, 37): 4.0, (62, 38): 4.0, (62, 39): 4.0, (62, 40): 4.0, (62, 41): 4.0, (62, 42): 4.0, (63, 1): 0.0, (63, 2): 0.0, (63, 3): 0.0, (63, 4): 0.0, (63, 5): 0.0, (63, 6): 0.0, (63, 7): 0.0, (63, 8): 0.0, (63, 9): 0.0, (63, 10): 0.0, (63, 11): 0.0, (63, 12): 0.0, (63, 13): 0.0, (63, 14): 0.0, (63, 15): 0.0, (63, 16): 0.0, (63, 17): 0.0, (63, 18): 0.0, (63, 19): 0.0, (63, 20): 0.0, (63, 21): 0.0, (63, 22): 0.0, (63, 23): 0.0, (63, 24): 0.0, (63, 25): 0.0, (63, 26): 0.0, (63, 27): 0.0, (63, 28): 0.0, (63, 29): 0.0, (63, 30): 0.0, (63, 31): 0.0, (63, 32): 0.0, (63, 33): 0.0, (63, 34): 0.0, (63, 35): 0.0, (63, 36): 0.0, (63, 37): 1.0, (63, 38): 1.0, (63, 39): 1.0, (63, 40): 2.0, (63, 41): 3.0, (63, 42): 3.0, (65, 1): 0.0, (65, 2): 0.0, (65, 3): 0.0, (65, 4): 0.0, (65, 5): 0.0, (65, 6): 0.0, (65, 7): 0.0, (65, 8): 0.0, (65, 9): 0.0, (65, 10): 0.0, (65, 11): 0.0, (65, 12): 0.0, (65, 13): 0.0, (65, 14): 0.0, (65, 15): 0.0, (65, 16): 0.0, (65, 17): 0.0, (65, 18): 0.0, (65, 19): 0.0, (65, 20): 0.0, (65, 21): 0.0, (65, 22): 0.0, (65, 23): 0.0, (65, 24): 0.0, (65, 25): 0.0, (65, 26): 0.0, (65, 27): 1.0, (65, 28): 2.0, (65, 29): 2.0, (65, 30): 2.0, (65, 31): 2.0, (65, 32): 3.0, (65, 33): 3.0, (65, 34): 3.0, (65, 35): 3.0, (65, 36): 3.0, (65, 37): 3.0, (65, 38): 3.0, (65, 39): 3.0, (65, 40): 3.0, (65, 41): 3.0, (65, 42): 3.0, (66, 1): 0.0, (66, 2): 0.0, (66, 3): 0.0, (66, 4): 0.0, (66, 5): 0.0, (66, 6): 0.0, (66, 7): 0.0, (66, 8): 0.0, (66, 9): 0.0, (66, 10): 0.0, (66, 11): 0.0, (66, 12): 0.0, (66, 13): 0.0, (66, 14): 0.0, (66, 15): 0.0, (66, 16): 0.0, (66, 17): 0.0, (66, 18): 0.0, (66, 19): 0.0, (66, 20): 0.0, (66, 21): 0.0, (66, 22): 0.0, (66, 23): 0.0, (66, 24): 0.0, (66, 25): 0.0, (66, 26): 0.0, (66, 27): 0.0, (66, 28): 0.0, (66, 29): 0.0, (66, 30): 1.0, (66, 31): 1.0, (66, 32): 1.0, (66, 33): 1.0, (66, 34): 2.0, (66, 35): 2.0, (66, 36): 2.0, (66, 37): 2.0, (66, 38): 2.0, (66, 39): 2.0, (66, 40): 2.0, (66, 41): 2.0, (66, 42): 2.0, (67, 1): 0.0, (67, 2): 0.0, (67, 3): 0.0, (67, 4): 0.0, (67, 5): 0.0, (67, 6): 0.0, (67, 7): 0.0, (67, 8): 0.0, (67, 9): 0.0, (67, 10): 0.0, (67, 11): 0.0, (67, 12): 0.0, (67, 13): 0.0, (67, 14): 1.0, (67, 15): 1.0, (67, 16): 2.0, (67, 17): 3.0, (67, 18): 3.0, (67, 19): 4.0, (67, 20): 4.0, (67, 21): 4.0, (67, 22): 4.0, (67, 23): 4.0, (67, 24): 4.0, (67, 25): 4.0, (67, 26): 4.0, (67, 27): 4.0, (67, 28): 4.0, (67, 29): 4.0, (67, 30): 4.0, (67, 31): 4.0, (67, 32): 4.0, (67, 33): 4.0, (67, 34): 4.0, (67, 35): 4.0, (67, 36): 4.0, (67, 37): 4.0, (67, 38): 4.0, (67, 39): 4.0, (67, 40): 4.0, (67, 41): 4.0, (67, 42): 4.0, (70, 1): 0.0, (70, 2): 0.0, (70, 3): 0.0, (70, 4): 0.0, (70, 5): 0.0, (70, 6): 0.0, (70, 7): 0.0, (70, 8): 0.0, (70, 9): 0.0, (70, 10): 0.0, (70, 11): 0.0, (70, 12): 0.0, (70, 13): 0.0, (70, 14): 0.0, (70, 15): 0.0, (70, 16): 0.0, (70, 17): 0.0, (70, 18): 0.0, (70, 19): 0.0, (70, 20): 0.0, (70, 21): 0.0, (70, 22): 0.0, (70, 23): 0.0, (70, 24): 0.0, (70, 25): 0.0, (70, 26): 0.0, (70, 27): 0.0, (70, 28): 0.0, (70, 29): 0.0, (70, 30): 0.0, (70, 31): 0.0, (70, 32): 1.0, (70, 33): 1.0, (70, 34): 1.0, (70, 35): 1.0, (70, 36): 2.0, (70, 37): 2.0, (70, 38): 2.0, (70, 39): 2.0, (70, 40): 2.0, (70, 41): 2.0, (70, 42): 2.0, (71, 1): 0.0, (71, 2): 0.0, (71, 3): 0.0, (71, 4): 0.0, (71, 5): 0.0, (71, 6): 0.0, (71, 7): 0.0, (71, 8): 0.0, (71, 9): 0.0, (71, 10): 0.0, (71, 11): 0.0, (71, 12): 0.0, (71, 13): 0.0, (71, 14): 0.0, (71, 15): 0.0, (71, 16): 0.0, (71, 17): 0.0, (71, 18): 0.0, (71, 19): 0.0, (71, 20): 0.0, (71, 21): 0.0, (71, 22): 0.0, (71, 23): 0.0, (71, 24): 0.0, (71, 25): 0.0, (71, 26): 0.0, (71, 27): 0.0, (71, 28): 0.0, (71, 29): 0.0, (71, 30): 0.0, (71, 31): 0.0, (71, 32): 0.0, (71, 33): 1.0, (71, 34): 2.0, (71, 35): 3.0, (71, 36): 4.0, (71, 37): 4.0, (71, 38): 5.0, (71, 39): 5.0, (71, 40): 6.0, (71, 41): 6.0, (71, 42): 6.0, (73, 1): 0.0, (73, 2): 0.0, (73, 3): 0.0, (73, 4): 0.0, (73, 5): 0.0, (73, 6): 0.0, (73, 7): 0.0, (73, 8): 0.0, (73, 9): 0.0, (73, 10): 0.0, (73, 11): 0.0, (73, 12): 0.0, (73, 13): 0.0, (73, 14): 0.0, (73, 15): 0.0, (73, 16): 0.0, (73, 17): 0.0, (73, 18): 0.0, (73, 19): 0.0, (73, 20): 0.0, (73, 21): 0.0, (73, 22): 0.0, (73, 23): 0.0, (73, 24): 0.0, (73, 25): 0.0, (73, 26): 0.0, (73, 27): 0.0, (73, 28): 0.0, (73, 29): 0.0, (73, 30): 0.0, (73, 31): 1.0, (73, 32): 1.0, (73, 33): 2.0, (73, 34): 3.0, (73, 35): 4.0, (73, 36): 4.0, (73, 37): 5.0, (73, 38): 5.0, (73, 39): 6.0, (73, 40): 6.0, (73, 41): 7.0, (73, 42): 7.0, (75, 1): 0.0, (75, 2): 0.0, (75, 3): 0.0, (75, 4): 0.0, (75, 5): 0.0, (75, 6): 0.0, (75, 7): 0.0, (75, 8): 0.0, (75, 9): 0.0, (75, 10): 0.0, (75, 11): 0.0, (75, 12): 0.0, (75, 13): 0.0, (75, 14): 0.0, (75, 15): 0.0, (75, 16): 0.0, (75, 17): 0.0, (75, 18): 0.0, (75, 19): 0.0, (75, 20): 1.0, (75, 21): 1.0, (75, 22): 2.0, (75, 23): 2.0, (75, 24): 3.0, (75, 25): 4.0, (75, 26): 5.0, (75, 27): 5.0, (75, 28): 5.0, (75, 29): 5.0, (75, 30): 5.0, (75, 31): 5.0, (75, 32): 5.0, (75, 33): 5.0, (75, 34): 5.0, (75, 35): 5.0, (75, 36): 5.0, (75, 37): 5.0, (75, 38): 5.0, (75, 39): 5.0, (75, 40): 5.0, (75, 41): 5.0, (75, 42): 5.0, (77, 1): 0.0, (77, 2): 0.0, (77, 3): 0.0, (77, 4): 0.0, (77, 5): 0.0, (77, 6): 0.0, (77, 7): 0.0, (77, 8): 0.0, (77, 9): 0.0, (77, 10): 0.0, (77, 11): 0.0, (77, 12): 0.0, (77, 13): 0.0, (77, 14): 0.0, (77, 15): 0.0, (77, 16): 0.0, (77, 17): 0.0, (77, 18): 0.0, (77, 19): 0.0, (77, 20): 0.0, (77, 21): 0.0, (77, 22): 0.0, (77, 23): 0.0, (77, 24): 0.0, (77, 25): 0.0, (77, 26): 0.0, (77, 27): 0.0, (77, 28): 0.0, (77, 29): 0.0, (77, 30): 0.0, (77, 31): 0.0, (77, 32): 0.0, (77, 33): 0.0, (77, 34): 0.0, (77, 35): 0.0, (77, 36): 0.0, (77, 37): 0.0, (77, 38): 0.0, (77, 39): 0.0, (77, 40): 1.0, (77, 41): 1.0, (77, 42): 1.0, (78, 1): 0.0, (78, 2): 0.0, (78, 3): 0.0, (78, 4): 0.0, (78, 5): 0.0, (78, 6): 0.0, (78, 7): 0.0, (78, 8): 0.0, (78, 9): 0.0, (78, 10): 0.0, (78, 11): 1.0, (78, 12): 2.0, (78, 13): 3.0, (78, 14): 4.0, (78, 15): 5.0, (78, 16): 5.0, (78, 17): 5.0, (78, 18): 6.0, (78, 19): 6.0, (78, 20): 6.0, (78, 21): 6.0, (78, 22): 6.0, (78, 23): 6.0, (78, 24): 6.0, (78, 25): 6.0, (78, 26): 6.0, (78, 27): 6.0, (78, 28): 6.0, (78, 29): 6.0, (78, 30): 6.0, (78, 31): 6.0, (78, 32): 6.0, (78, 33): 6.0, (78, 34): 6.0, (78, 35): 6.0, (78, 36): 6.0, (78, 37): 6.0, (78, 38): 6.0, (78, 39): 6.0, (78, 40): 6.0, (78, 41): 6.0, (78, 42): 6.0, (79, 1): 0.0, (79, 2): 0.0, (79, 3): 0.0, (79, 4): 0.0, (79, 5): 0.0, (79, 6): 0.0, (79, 7): 0.0, (79, 8): 0.0, (79, 9): 0.0, (79, 10): 0.0, (79, 11): 0.0, (79, 12): 0.0, (79, 13): 0.0, (79, 14): 0.0, (79, 15): 0.0, (79, 16): 0.0, (79, 17): 0.0, (79, 18): 0.0, (79, 19): 0.0, (79, 20): 1.0, (79, 21): 2.0, (79, 22): 2.0, (79, 23): 2.0, (79, 24): 2.0, (79, 25): 3.0, (79, 26): 3.0, (79, 27): 3.0, (79, 28): 3.0, (79, 29): 3.0, (79, 30): 3.0, (79, 31): 3.0, (79, 32): 3.0, (79, 33): 3.0, (79, 34): 3.0, (79, 35): 3.0, (79, 36): 3.0, (79, 37): 3.0, (79, 38): 3.0, (79, 39): 3.0, (79, 40): 3.0, (79, 41): 3.0, (79, 42): 3.0, (81, 1): 0.0, (81, 2): 0.0, (81, 3): 0.0, (81, 4): 0.0, (81, 5): 0.0, (81, 6): 0.0, (81, 7): 0.0, (81, 8): 0.0, (81, 9): 0.0, (81, 10): 0.0, (81, 11): 0.0, (81, 12): 1.0, (81, 13): 2.0, (81, 14): 2.0, (81, 15): 2.0, (81, 16): 2.0, (81, 17): 3.0, (81, 18): 3.0, (81, 19): 3.0, (81, 20): 3.0, (81, 21): 3.0, (81, 22): 3.0, (81, 23): 3.0, (81, 24): 3.0, (81, 25): 3.0, (81, 26): 3.0, (81, 27): 3.0, (81, 28): 3.0, (81, 29): 3.0, (81, 30): 3.0, (81, 31): 3.0, (81, 32): 3.0, (81, 33): 3.0, (81, 34): 3.0, (81, 35): 3.0, (81, 36): 3.0, (81, 37): 3.0, (81, 38): 3.0, (81, 39): 3.0, (81, 40): 3.0, (81, 41): 3.0, (81, 42): 3.0, (82, 1): 0.0, (82, 2): 0.0, (82, 3): 0.0, (82, 4): 0.0, (82, 5): 0.0, (82, 6): 0.0, (82, 7): 0.0, (82, 8): 0.0, (82, 9): 1.0, (82, 10): 2.0, (82, 11): 2.0, (82, 12): 2.0, (82, 13): 3.0, (82, 14): 3.0, (82, 15): 4.0, (82, 16): 4.0, (82, 17): 4.0, (82, 18): 4.0, (82, 19): 4.0, (82, 20): 4.0, (82, 21): 4.0, (82, 22): 4.0, (82, 23): 4.0, (82, 24): 4.0, (82, 25): 4.0, (82, 26): 4.0, (82, 27): 4.0, (82, 28): 4.0, (82, 29): 4.0, (82, 30): 4.0, (82, 31): 4.0, (82, 32): 4.0, (82, 33): 4.0, (82, 34): 4.0, (82, 35): 4.0, (82, 36): 4.0, (82, 37): 4.0, (82, 38): 4.0, (82, 39): 4.0, (82, 40): 4.0, (82, 41): 4.0, (82, 42): 4.0}</t>
-  </si>
-  <si>
-    <t>{(2, 1): 0, (2, 2): 0, (2, 3): 0, (2, 4): 0, (2, 5): 0, (2, 6): 0, (2, 7): 0, (2, 8): 0, (2, 9): 0, (2, 10): 0, (2, 11): 0, (2, 12): 0, (2, 13): 0, (2, 14): 0, (2, 15): 0, (2, 16): 0, (2, 17): 0, (2, 18): 0, (2, 19): 0, (2, 20): 0, (2, 21): 0, (2, 22): 0, (2, 23): 0, (2, 24): 0, (2, 25): 0, (2, 26): 0, (2, 27): 0, (2, 28): 0, (2, 29): 0, (2, 30): 0, (2, 31): 0, (2, 32): 0, (2, 33): 0, (2, 34): 0, (2, 35): 0, (2, 36): 0, (2, 37): 0, (2, 38): 0, (2, 39): 0, (2, 40): 0, (2, 41): 1, (2, 42): 0, (3, 1): 0, (3, 2): 0, (3, 3): 0, (3, 4): 0, (3, 5): 0, (3, 6): 0, (3, 7): 0, (3, 8): 0, (3, 9): 0, (3, 10): 0, (3, 11): 0, (3, 12): 0, (3, 13): 0, (3, 14): 0, (3, 15): 0, (3, 16): 0, (3, 17): 0, (3, 18): 0, (3, 19): 0, (3, 20): 0, (3, 21): 0, (3, 22): 0, (3, 23): 0, (3, 24): 0, (3, 25): 0, (3, 26): 0, (3, 27): 0, (3, 28): 0, (3, 29): 0, (3, 30): 0, (3, 31): 0, (3, 32): 0, (3, 33): 0, (3, 34): 0, (3, 35): 1, (3, 36): 0, (3, 37): 0, (3, 38): 0, (3, 39): 0, (3, 40): 0, (3, 41): 0, (3, 42): 0, (4, 1): 0, (4, 2): 0, (4, 3): 0, (4, 4): 0, (4, 5): 0, (4, 6): 0, (4, 7): 0, (4, 8): 0, (4, 9): 0, (4, 10): 0, (4, 11): 0, (4, 12): 0, (4, 13): 0, (4, 14): 0, (4, 15): 0, (4, 16): 0, (4, 17): 0, (4, 18): 0, (4, 19): 0, (4, 20): 0, (4, 21): 0, (4, 22): 0, (4, 23): 0, (4, 24): 0, (4, 25): 0, (4, 26): 0, (4, 27): 0, (4, 28): 0, (4, 29): 0, (4, 30): 0, (4, 31): 0, (4, 32): 0, (4, 33): 0, (4, 34): 0, (4, 35): 0, (4, 36): 0, (4, 37): 0, (4, 38): 0, (4, 39): 0, (4, 40): 0, (4, 41): 0, (4, 42): 1, (9, 1): 0, (9, 2): 0, (9, 3): 0, (9, 4): 0, (9, 5): 0, (9, 6): 0, (9, 7): 0, (9, 8): 0, (9, 9): 0, (9, 10): 0, (9, 11): 0, (9, 12): 0, (9, 13): 0, (9, 14): 0, (9, 15): 0, (9, 16): 0, (9, 17): 0, (9, 18): 0, (9, 19): 0, (9, 20): 0, (9, 21): 0, (9, 22): 0, (9, 23): 0, (9, 24): 0, (9, 25): 0, (9, 26): 0, (9, 27): 0, (9, 28): 0, (9, 29): 0, (9, 30): 0, (9, 31): 0, (9, 32): 0, (9, 33): 0, (9, 34): 0, (9, 35): 0, (9, 36): 0, (9, 37): 0, (9, 38): 1, (9, 39): 0, (9, 40): 0, (9, 41): 0, (9, 42): 0, (15, 1): 0, (15, 2): 0, (15, 3): 0, (15, 4): 0, (15, 5): 0, (15, 6): 0, (15, 7): 0, (15, 8): 0, (15, 9): 0, (15, 10): 0, (15, 11): 0, (15, 12): 0, (15, 13): 0, (15, 14): 0, (15, 15): 0, (15, 16): 0, (15, 17): 0, (15, 18): 0, (15, 19): 0, (15, 20): 0, (15, 21): 0, (15, 22): 0, (15, 23): 0, (15, 24): 0, (15, 25): 0, (15, 26): 0, (15, 27): 0, (15, 28): 0, (15, 29): 0, (15, 30): 0, (15, 31): 0, (15, 32): 0, (15, 33): 0, (15, 34): 0, (15, 35): 0, (15, 36): 0, (15, 37): 0, (15, 38): 0, (15, 39): 0, (15, 40): 0, (15, 41): 1, (15, 42): 0, (16, 1): 0, (16, 2): 0, (16, 3): 0, (16, 4): 0, (16, 5): 0, (16, 6): 0, (16, 7): 0, (16, 8): 0, (16, 9): 0, (16, 10): 0, (16, 11): 0, (16, 12): 0, (16, 13): 0, (16, 14): 0, (16, 15): 0, (16, 16): 0, (16, 17): 0, (16, 18): 0, (16, 19): 1, (16, 20): 0, (16, 21): 0, (16, 22): 0, (16, 23): 0, (16, 24): 0, (16, 25): 0, (16, 26): 0, (16, 27): 0, (16, 28): 0, (16, 29): 0, (16, 30): 0, (16, 31): 0, (16, 32): 0, (16, 33): 0, (16, 34): 0, (16, 35): 0, (16, 36): 0, (16, 37): 0, (16, 38): 0, (16, 39): 0, (16, 40): 0, (16, 41): 0, (16, 42): 0, (20, 1): 0, (20, 2): 0, (20, 3): 0, (20, 4): 0, (20, 5): 0, (20, 6): 0, (20, 7): 0, (20, 8): 0, (20, 9): 0, (20, 10): 0, (20, 11): 0, (20, 12): 0, (20, 13): 0, (20, 14): 0, (20, 15): 0, (20, 16): 0, (20, 17): 0, (20, 18): 0, (20, 19): 0, (20, 20): 0, (20, 21): 0, (20, 22): 0, (20, 23): 0, (20, 24): 0, (20, 25): 0, (20, 26): 0, (20, 27): 0, (20, 28): 0, (20, 29): 0, (20, 30): 0, (20, 31): 0, (20, 32): 0, (20, 33): 0, (20, 34): 0, (20, 35): 0, (20, 36): 0, (20, 37): 1, (20, 38): 0, (20, 39): 0, (20, 40): 0, (20, 41): 0, (20, 42): 0, (21, 1): 0, (21, 2): 0, (21, 3): 0, (21, 4): 0, (21, 5): 0, (21, 6): 0, (21, 7): 0, (21, 8): 0, (21, 9): 0, (21, 10): 0, (21, 11): 0, (21, 12): 0, (21, 13): 0, (21, 14): 0, (21, 15): 0, (21, 16): 0, (21, 17): 0, (21, 18): 0, (21, 19): 0, (21, 20): 0, (21, 21): 0, (21, 22): 0, (21, 23): 0, (21, 24): 0, (21, 25): 0, (21, 26): 0, (21, 27): 0, (21, 28): 0, (21, 29): 0, (21, 30): 0, (21, 31): 0, (21, 32): 0, (21, 33): 0, (21, 34): 0, (21, 35): 0, (21, 36): 0, (21, 37): 0, (21, 38): 0, (21, 39): 0, (21, 40): 0, (21, 41): 1, (21, 42): 0, (22, 1): 0, (22, 2): 0, (22, 3): 0, (22, 4): 0, (22, 5): 0, (22, 6): 0, (22, 7): 0, (22, 8): 0, (22, 9): 0, (22, 10): 0, (22, 11): 0, (22, 12): 0, (22, 13): 0, (22, 14): 0, (22, 15): 0, (22, 16): 0, (22, 17): 0, (22, 18): 0, (22, 19): 0, (22, 20): 0, (22, 21): 0, (22, 22): 0, (22, 23): 0, (22, 24): 0, (22, 25): 0, (22, 26): 0, (22, 27): 0, (22, 28): 0, (22, 29): 0, (22, 30): 0, (22, 31): 0, (22, 32): 0, (22, 33): 0, (22, 34): 0, (22, 35): 0, (22, 36): 0, (22, 37): 0, (22, 38): 0, (22, 39): 1, (22, 40): 0, (22, 41): 0, (22, 42): 0, (23, 1): 0, (23, 2): 0, (23, 3): 0, (23, 4): 0, (23, 5): 0, (23, 6): 0, (23, 7): 0, (23, 8): 0, (23, 9): 0, (23, 10): 0, (23, 11): 0, (23, 12): 0, (23, 13): 0, (23, 14): 0, (23, 15): 0, (23, 16): 0, (23, 17): 0, (23, 18): 0, (23, 19): 0, (23, 20): 0, (23, 21): 0, (23, 22): 0, (23, 23): 0, (23, 24): 0, (23, 25): 0, (23, 26): 0, (23, 27): 0, (23, 28): 0, (23, 29): 0, (23, 30): 0, (23, 31): 0, (23, 32): 0, (23, 33): 0, (23, 34): 1, (23, 35): 0, (23, 36): 0, (23, 37): 0, (23, 38): 0, (23, 39): 0, (23, 40): 0, (23, 41): 0, (23, 42): 0, (24, 1): 0, (24, 2): 0, (24, 3): 0, (24, 4): 0, (24, 5): 0, (24, 6): 0, (24, 7): 0, (24, 8): 0, (24, 9): 0, (24, 10): 0, (24, 11): 0, (24, 12): 0, (24, 13): 0, (24, 14): 0, (24, 15): 0, (24, 16): 0, (24, 17): 0, (24, 18): 0, (24, 19): 0, (24, 20): 0, (24, 21): 0, (24, 22): 0, (24, 23): 0, (24, 24): 0, (24, 25): 0, (24, 26): 0, (24, 27): 0, (24, 28): 0, (24, 29): 1, (24, 30): 0, (24, 31): 0, (24, 32): 0, (24, 33): 0, (24, 34): 0, (24, 35): 0, (24, 36): 0, (24, 37): 0, (24, 38): 0, (24, 39): 0, (24, 40): 0, (24, 41): 0, (24, 42): 0, (25, 1): 0, (25, 2): 0, (25, 3): 0, (25, 4): 0, (25, 5): 0, (25, 6): 0, (25, 7): 0, (25, 8): 0, (25, 9): 0, (25, 10): 0, (25, 11): 0, (25, 12): 0, (25, 13): 0, (25, 14): 0, (25, 15): 0, (25, 16): 0, (25, 17): 0, (25, 18): 0, (25, 19): 0, (25, 20): 0, (25, 21): 0, (25, 22): 0, (25, 23): 0, (25, 24): 0, (25, 25): 0, (25, 26): 0, (25, 27): 0, (25, 28): 0, (25, 29): 0, (25, 30): 0, (25, 31): 0, (25, 32): 0, (25, 33): 0, (25, 34): 0, (25, 35): 0, (25, 36): 0, (25, 37): 0, (25, 38): 0, (25, 39): 0, (25, 40): 0, (25, 41): 0, (25, 42): 1, (26, 1): 0, (26, 2): 0, (26, 3): 0, (26, 4): 0, (26, 5): 0, (26, 6): 0, (26, 7): 0, (26, 8): 0, (26, 9): 0, (26, 10): 0, (26, 11): 0, (26, 12): 0, (26, 13): 0, (26, 14): 0, (26, 15): 0, (26, 16): 0, (26, 17): 0, (26, 18): 0, (26, 19): 0, (26, 20): 0, (26, 21): 0, (26, 22): 0, (26, 23): 0, (26, 24): 0, (26, 25): 0, (26, 26): 0, (26, 27): 0, (26, 28): 0, (26, 29): 0, (26, 30): 0, (26, 31): 1, (26, 32): 0, (26, 33): 0, (26, 34): 0, (26, 35): 0, (26, 36): 0, (26, 37): 0, (26, 38): 0, (26, 39): 0, (26, 40): 0, (26, 41): 0, (26, 42): 0, (28, 1): 0, (28, 2): 0, (28, 3): 0, (28, 4): 0, (28, 5): 0, (28, 6): 0, (28, 7): 0, (28, 8): 0, (28, 9): 0, (28, 10): 0, (28, 11): 0, (28, 12): 0, (28, 13): 0, (28, 14): 0, (28, 15): 0, (28, 16): 0, (28, 17): 0, (28, 18): 0, (28, 19): 0, (28, 20): 0, (28, 21): 0, (28, 22): 0, (28, 23): 0, (28, 24): 0, (28, 25): 0, (28, 26): 0, (28, 27): 0, (28, 28): 0, (28, 29): 0, (28, 30): 0, (28, 31): 0, (28, 32): 0, (28, 33): 0, (28, 34): 0, (28, 35): 0, (28, 36): 0, (28, 37): 0, (28, 38): 0, (28, 39): 0, (28, 40): 0, (28, 41): 1, (28, 42): 0, (30, 1): 0, (30, 2): 0, (30, 3): 0, (30, 4): 0, (30, 5): 0, (30, 6): 0, (30, 7): 0, (30, 8): 0, (30, 9): 0, (30, 10): 0, (30, 11): 0, (30, 12): 0, (30, 13): 0, (30, 14): 0, (30, 15): 0, (30, 16): 0, (30, 17): 0, (30, 18): 0, (30, 19): 0, (30, 20): 0, (30, 21): 0, (30, 22): 0, (30, 23): 0, (30, 24): 0, (30, 25): 0, (30, 26): 0, (30, 27): 0, (30, 28): 0, (30, 29): 0, (30, 30): 1, (30, 31): 0, (30, 32): 0, (30, 33): 0, (30, 34): 0, (30, 35): 0, (30, 36): 0, (30, 37): 0, (30, 38): 0, (30, 39): 0, (30, 40): 0, (30, 41): 0, (30, 42): 0, (31, 1): 0, (31, 2): 0, (31, 3): 0, (31, 4): 0, (31, 5): 0, (31, 6): 0, (31, 7): 0, (31, 8): 0, (31, 9): 0, (31, 10): 0, (31, 11): 0, (31, 12): 0, (31, 13): 0, (31, 14): 0, (31, 15): 0, (31, 16): 0, (31, 17): 0, (31, 18): 0, (31, 19): 0, (31, 20): 1, (31, 21): 0, (31, 22): 0, (31, 23): 0, (31, 24): 0, (31, 25): 0, (31, 26): 0, (31, 27): 0, (31, 28): 0, (31, 29): 0, (31, 30): 0, (31, 31): 0, (31, 32): 0, (31, 33): 0, (31, 34): 0, (31, 35): 0, (31, 36): 0, (31, 37): 0, (31, 38): 0, (31, 39): 0, (31, 40): 0, (31, 41): 0, (31, 42): 0, (36, 1): 0, (36, 2): 0, (36, 3): 0, (36, 4): 0, (36, 5): 0, (36, 6): 0, (36, 7): 0, (36, 8): 0, (36, 9): 0, (36, 10): 0, (36, 11): 0, (36, 12): 0, (36, 13): 0, (36, 14): 0, (36, 15): 0, (36, 16): 0, (36, 17): 0, (36, 18): 0, (36, 19): 0, (36, 20): 0, (36, 21): 0, (36, 22): 0, (36, 23): 0, (36, 24): 0, (36, 25): 0, (36, 26): 0, (36, 27): 0, (36, 28): 0, (36, 29): 0, (36, 30): 0, (36, 31): 0, (36, 32): 0, (36, 33): 0, (36, 34): 0, (36, 35): 0, (36, 36): 0, (36, 37): 0, (36, 38): 1, (36, 39): 0, (36, 40): 0, (36, 41): 0, (36, 42): 0, (37, 1): 0, (37, 2): 0, (37, 3): 0, (37, 4): 0, (37, 5): 0, (37, 6): 0, (37, 7): 0, (37, 8): 0, (37, 9): 0, (37, 10): 0, (37, 11): 0, (37, 12): 0, (37, 13): 0, (37, 14): 0, (37, 15): 0, (37, 16): 0, (37, 17): 0, (37, 18): 0, (37, 19): 0, (37, 20): 0, (37, 21): 0, (37, 22): 0, (37, 23): 0, (37, 24): 0, (37, 25): 0, (37, 26): 0, (37, 27): 0, (37, 28): 0, (37, 29): 0, (37, 30): 0, (37, 31): 0, (37, 32): 0, (37, 33): 1, (37, 34): 0, (37, 35): 0, (37, 36): 0, (37, 37): 0, (37, 38): 0, (37, 39): 0, (37, 40): 0, (37, 41): 0, (37, 42): 0, (38, 1): 0, (38, 2): 0, (38, 3): 0, (38, 4): 0, (38, 5): 0, (38, 6): 0, (38, 7): 0, (38, 8): 0, (38, 9): 0, (38, 10): 0, (38, 11): 0, (38, 12): 0, (38, 13): 0, (38, 14): 0, (38, 15): 0, (38, 16): 0, (38, 17): 0, (38, 18): 0, (38, 19): 0, (38, 20): 0, (38, 21): 0, (38, 22): 0, (38, 23): 0, (38, 24): 0, (38, 25): 0, (38, 26): 0, (38, 27): 0, (38, 28): 0, (38, 29): 0, (38, 30): 0, (38, 31): 0, (38, 32): 0, (38, 33): 0, (38, 34): 0, (38, 35): 0, (38, 36): 0, (38, 37): 0, (38, 38): 0, (38, 39): 0, (38, 40): 0, (38, 41): 0, (38, 42): 1, (39, 1): 0, (39, 2): 0, (39, 3): 0, (39, 4): 0, (39, 5): 0, (39, 6): 0, (39, 7): 0, (39, 8): 0, (39, 9): 0, (39, 10): 0, (39, 11): 0, (39, 12): 0, (39, 13): 0, (39, 14): 0, (39, 15): 0, (39, 16): 0, (39, 17): 0, (39, 18): 0, (39, 19): 0, (39, 20): 0, (39, 21): 0, (39, 22): 0, (39, 23): 0, (39, 24): 1, (39, 25): 0, (39, 26): 0, (39, 27): 0, (39, 28): 0, (39, 29): 0, (39, 30): 0, (39, 31): 0, (39, 32): 0, (39, 33): 0, (39, 34): 0, (39, 35): 0, (39, 36): 0, (39, 37): 0, (39, 38): 0, (39, 39): 0, (39, 40): 0, (39, 41): 0, (39, 42): 0, (40, 1): 0, (40, 2): 0, (40, 3): 0, (40, 4): 0, (40, 5): 0, (40, 6): 0, (40, 7): 0, (40, 8): 0, (40, 9): 0, (40, 10): 0, (40, 11): 0, (40, 12): 0, (40, 13): 0, (40, 14): 0, (40, 15): 1, (40, 16): 0, (40, 17): 0, (40, 18): 0, (40, 19): 0, (40, 20): 0, (40, 21): 0, (40, 22): 0, (40, 23): 0, (40, 24): 0, (40, 25): 0, (40, 26): 0, (40, 27): 0, (40, 28): 0, (40, 29): 0, (40, 30): 0, (40, 31): 0, (40, 32): 0, (40, 33): 0, (40, 34): 0, (40, 35): 0, (40, 36): 0, (40, 37): 0, (40, 38): 0, (40, 39): 0, (40, 40): 0, (40, 41): 0, (40, 42): 0, (41, 1): 0, (41, 2): 0, (41, 3): 0, (41, 4): 0, (41, 5): 0, (41, 6): 0, (41, 7): 0, (41, 8): 0, (41, 9): 0, (41, 10): 0, (41, 11): 0, (41, 12): 0, (41, 13): 0, (41, 14): 0, (41, 15): 0, (41, 16): 0, (41, 17): 0, (41, 18): 0, (41, 19): 0, (41, 20): 0, (41, 21): 0, (41, 22): 0, (41, 23): 0, (41, 24): 0, (41, 25): 0, (41, 26): 0, (41, 27): 0, (41, 28): 1, (41, 29): 0, (41, 30): 0, (41, 31): 0, (41, 32): 0, (41, 33): 0, (41, 34): 0, (41, 35): 0, (41, 36): 0, (41, 37): 0, (41, 38): 0, (41, 39): 0, (41, 40): 0, (41, 41): 0, (41, 42): 0, (43, 1): 0, (43, 2): 0, (43, 3): 0, (43, 4): 0, (43, 5): 0, (43, 6): 0, (43, 7): 0, (43, 8): 0, (43, 9): 0, (43, 10): 0, (43, 11): 0, (43, 12): 0, (43, 13): 0, (43, 14): 0, (43, 15): 0, (43, 16): 0, (43, 17): 0, (43, 18): 0, (43, 19): 0, (43, 20): 0, (43, 21): 0, (43, 22): 0, (43, 23): 0, (43, 24): 1, (43, 25): 0, (43, 26): 0, (43, 27): 0, (43, 28): 0, (43, 29): 0, (43, 30): 0, (43, 31): 0, (43, 32): 0, (43, 33): 0, (43, 34): 0, (43, 35): 0, (43, 36): 0, (43, 37): 0, (43, 38): 0, (43, 39): 0, (43, 40): 0, (43, 41): 0, (43, 42): 0, (50, 1): 0, (50, 2): 0, (50, 3): 0, (50, 4): 0, (50, 5): 0, (50, 6): 0, (50, 7): 0, (50, 8): 0, (50, 9): 0, (50, 10): 0, (50, 11): 0, (50, 12): 0, (50, 13): 0, (50, 14): 0, (50, 15): 0, (50, 16): 0, (50, 17): 1, (50, 18): 0, (50, 19): 0, (50, 20): 0, (50, 21): 0, (50, 22): 0, (50, 23): 0, (50, 24): 0, (50, 25): 0, (50, 26): 0, (50, 27): 0, (50, 28): 0, (50, 29): 0, (50, 30): 0, (50, 31): 0, (50, 32): 0, (50, 33): 0, (50, 34): 0, (50, 35): 0, (50, 36): 0, (50, 37): 0, (50, 38): 0, (50, 39): 0, (50, 40): 0, (50, 41): 0, (50, 42): 0, (59, 1): 0, (59, 2): 0, (59, 3): 0, (59, 4): 0, (59, 5): 0, (59, 6): 0, (59, 7): 0, (59, 8): 0, (59, 9): 0, (59, 10): 0, (59, 11): 0, (59, 12): 0, (59, 13): 0, (59, 14): 0, (59, 15): 0, (59, 16): 0, (59, 17): 0, (59, 18): 0, (59, 19): 0, (59, 20): 0, (59, 21): 0, (59, 22): 0, (59, 23): 1, (59, 24): 0, (59, 25): 0, (59, 26): 0, (59, 27): 0, (59, 28): 0, (59, 29): 0, (59, 30): 0, (59, 31): 0, (59, 32): 0, (59, 33): 0, (59, 34): 0, (59, 35): 0, (59, 36): 0, (59, 37): 0, (59, 38): 0, (59, 39): 0, (59, 40): 0, (59, 41): 0, (59, 42): 0, (60, 1): 0, (60, 2): 0, (60, 3): 0, (60, 4): 0, (60, 5): 0, (60, 6): 0, (60, 7): 0, (60, 8): 0, (60, 9): 0, (60, 10): 0, (60, 11): 0, (60, 12): 0, (60, 13): 0, (60, 14): 0, (60, 15): 0, (60, 16): 0, (60, 17): 0, (60, 18): 0, (60, 19): 0, (60, 20): 0, (60, 21): 0, (60, 22): 0, (60, 23): 0, (60, 24): 0, (60, 25): 0, (60, 26): 0, (60, 27): 0, (60, 28): 0, (60, 29): 0, (60, 30): 0, (60, 31): 0, (60, 32): 0, (60, 33): 0, (60, 34): 0, (60, 35): 0, (60, 36): 0, (60, 37): 0, (60, 38): 0, (60, 39): 0, (60, 40): 0, (60, 41): 0, (60, 42): 1, (62, 1): 0, (62, 2): 0, (62, 3): 0, (62, 4): 0, (62, 5): 0, (62, 6): 0, (62, 7): 0, (62, 8): 0, (62, 9): 0, (62, 10): 0, (62, 11): 0, (62, 12): 0, (62, 13): 0, (62, 14): 0, (62, 15): 0, (62, 16): 0, (62, 17): 0, (62, 18): 0, (62, 19): 0, (62, 20): 0, (62, 21): 0, (62, 22): 0, (62, 23): 0, (62, 24): 0, (62, 25): 1, (62, 26): 0, (62, 27): 0, (62, 28): 0, (62, 29): 0, (62, 30): 0, (62, 31): 0, (62, 32): 0, (62, 33): 0, (62, 34): 0, (62, 35): 0, (62, 36): 0, (62, 37): 0, (62, 38): 0, (62, 39): 0, (62, 40): 0, (62, 41): 0, (62, 42): 0, (63, 1): 0, (63, 2): 0, (63, 3): 0, (63, 4): 0, (63, 5): 0, (63, 6): 0, (63, 7): 0, (63, 8): 0, (63, 9): 0, (63, 10): 0, (63, 11): 0, (63, 12): 0, (63, 13): 0, (63, 14): 0, (63, 15): 0, (63, 16): 0, (63, 17): 0, (63, 18): 0, (63, 19): 0, (63, 20): 0, (63, 21): 0, (63, 22): 0, (63, 23): 0, (63, 24): 0, (63, 25): 0, (63, 26): 0, (63, 27): 0, (63, 28): 0, (63, 29): 0, (63, 30): 0, (63, 31): 0, (63, 32): 0, (63, 33): 0, (63, 34): 0, (63, 35): 0, (63, 36): 0, (63, 37): 0, (63, 38): 0, (63, 39): 0, (63, 40): 0, (63, 41): 0, (63, 42): 1, (65, 1): 0, (65, 2): 0, (65, 3): 0, (65, 4): 0, (65, 5): 0, (65, 6): 0, (65, 7): 0, (65, 8): 0, (65, 9): 0, (65, 10): 0, (65, 11): 0, (65, 12): 0, (65, 13): 0, (65, 14): 0, (65, 15): 0, (65, 16): 0, (65, 17): 0, (65, 18): 0, (65, 19): 0, (65, 20): 0, (65, 21): 0, (65, 22): 0, (65, 23): 0, (65, 24): 0, (65, 25): 0, (65, 26): 0, (65, 27): 0, (65, 28): 0, (65, 29): 0, (65, 30): 0, (65, 31): 0, (65, 32): 1, (65, 33): 0, (65, 34): 0, (65, 35): 0, (65, 36): 0, (65, 37): 0, (65, 38): 0, (65, 39): 0, (65, 40): 0, (65, 41): 0, (65, 42): 0, (66, 1): 0, (66, 2): 0, (66, 3): 0, (66, 4): 0, (66, 5): 0, (66, 6): 0, (66, 7): 0, (66, 8): 0, (66, 9): 0, (66, 10): 0, (66, 11): 0, (66, 12): 0, (66, 13): 0, (66, 14): 0, (66, 15): 0, (66, 16): 0, (66, 17): 0, (66, 18): 0, (66, 19): 0, (66, 20): 0, (66, 21): 0, (66, 22): 0, (66, 23): 0, (66, 24): 0, (66, 25): 0, (66, 26): 0, (66, 27): 0, (66, 28): 0, (66, 29): 0, (66, 30): 0, (66, 31): 0, (66, 32): 0, (66, 33): 0, (66, 34): 1, (66, 35): 0, (66, 36): 0, (66, 37): 0, (66, 38): 0, (66, 39): 0, (66, 40): 0, (66, 41): 0, (66, 42): 0, (67, 1): 0, (67, 2): 0, (67, 3): 0, (67, 4): 0, (67, 5): 0, (67, 6): 0, (67, 7): 0, (67, 8): 0, (67, 9): 0, (67, 10): 0, (67, 11): 0, (67, 12): 0, (67, 13): 0, (67, 14): 0, (67, 15): 0, (67, 16): 0, (67, 17): 0, (67, 18): 0, (67, 19): 1, (67, 20): 0, (67, 21): 0, (67, 22): 0, (67, 23): 0, (67, 24): 0, (67, 25): 0, (67, 26): 0, (67, 27): 0, (67, 28): 0, (67, 29): 0, (67, 30): 0, (67, 31): 0, (67, 32): 0, (67, 33): 0, (67, 34): 0, (67, 35): 0, (67, 36): 0, (67, 37): 0, (67, 38): 0, (67, 39): 0, (67, 40): 0, (67, 41): 0, (67, 42): 0, (70, 1): 0, (70, 2): 0, (70, 3): 0, (70, 4): 0, (70, 5): 0, (70, 6): 0, (70, 7): 0, (70, 8): 0, (70, 9): 0, (70, 10): 0, (70, 11): 0, (70, 12): 0, (70, 13): 0, (70, 14): 0, (70, 15): 0, (70, 16): 0, (70, 17): 0, (70, 18): 0, (70, 19): 0, (70, 20): 0, (70, 21): 0, (70, 22): 0, (70, 23): 0, (70, 24): 0, (70, 25): 0, (70, 26): 0, (70, 27): 0, (70, 28): 0, (70, 29): 0, (70, 30): 0, (70, 31): 0, (70, 32): 0, (70, 33): 0, (70, 34): 0, (70, 35): 0, (70, 36): 1, (70, 37): 0, (70, 38): 0, (70, 39): 0, (70, 40): 0, (70, 41): 0, (70, 42): 0, (71, 1): 0, (71, 2): 0, (71, 3): 0, (71, 4): 0, (71, 5): 0, (71, 6): 0, (71, 7): 0, (71, 8): 0, (71, 9): 0, (71, 10): 0, (71, 11): 0, (71, 12): 0, (71, 13): 0, (71, 14): 0, (71, 15): 0, (71, 16): 0, (71, 17): 0, (71, 18): 0, (71, 19): 0, (71, 20): 0, (71, 21): 0, (71, 22): 0, (71, 23): 0, (71, 24): 0, (71, 25): 0, (71, 26): 0, (71, 27): 0, (71, 28): 0, (71, 29): 0, (71, 30): 0, (71, 31): 0, (71, 32): 0, (71, 33): 0, (71, 34): 0, (71, 35): 0, (71, 36): 0, (71, 37): 0, (71, 38): 0, (71, 39): 0, (71, 40): 1, (71, 41): 0, (71, 42): 0, (73, 1): 0, (73, 2): 0, (73, 3): 0, (73, 4): 0, (73, 5): 0, (73, 6): 0, (73, 7): 0, (73, 8): 0, (73, 9): 0, (73, 10): 0, (73, 11): 0, (73, 12): 0, (73, 13): 0, (73, 14): 0, (73, 15): 0, (73, 16): 0, (73, 17): 0, (73, 18): 0, (73, 19): 0, (73, 20): 0, (73, 21): 0, (73, 22): 0, (73, 23): 0, (73, 24): 0, (73, 25): 0, (73, 26): 0, (73, 27): 0, (73, 28): 0, (73, 29): 0, (73, 30): 0, (73, 31): 0, (73, 32): 0, (73, 33): 0, (73, 34): 0, (73, 35): 0, (73, 36): 0, (73, 37): 0, (73, 38): 0, (73, 39): 0, (73, 40): 0, (73, 41): 1, (73, 42): 0, (75, 1): 0, (75, 2): 0, (75, 3): 0, (75, 4): 0, (75, 5): 0, (75, 6): 0, (75, 7): 0, (75, 8): 0, (75, 9): 0, (75, 10): 0, (75, 11): 0, (75, 12): 0, (75, 13): 0, (75, 14): 0, (75, 15): 0, (75, 16): 0, (75, 17): 0, (75, 18): 0, (75, 19): 0, (75, 20): 0, (75, 21): 0, (75, 22): 0, (75, 23): 0, (75, 24): 0, (75, 25): 0, (75, 26): 1, (75, 27): 0, (75, 28): 0, (75, 29): 0, (75, 30): 0, (75, 31): 0, (75, 32): 0, (75, 33): 0, (75, 34): 0, (75, 35): 0, (75, 36): 0, (75, 37): 0, (75, 38): 0, (75, 39): 0, (75, 40): 0, (75, 41): 0, (75, 42): 0, (77, 1): 0, (77, 2): 0, (77, 3): 0, (77, 4): 0, (77, 5): 0, (77, 6): 0, (77, 7): 0, (77, 8): 0, (77, 9): 0, (77, 10): 0, (77, 11): 0, (77, 12): 0, (77, 13): 0, (77, 14): 0, (77, 15): 0, (77, 16): 0, (77, 17): 0, (77, 18): 0, (77, 19): 0, (77, 20): 0, (77, 21): 0, (77, 22): 0, (77, 23): 0, (77, 24): 0, (77, 25): 0, (77, 26): 0, (77, 27): 0, (77, 28): 0, (77, 29): 0, (77, 30): 0, (77, 31): 0, (77, 32): 0, (77, 33): 0, (77, 34): 0, (77, 35): 0, (77, 36): 0, (77, 37): 0, (77, 38): 0, (77, 39): 0, (77, 40): 0, (77, 41): 0, (77, 42): 1, (78, 1): 0, (78, 2): 0, (78, 3): 0, (78, 4): 0, (78, 5): 0, (78, 6): 0, (78, 7): 0, (78, 8): 0, (78, 9): 0, (78, 10): 0, (78, 11): 0, (78, 12): 0, (78, 13): 0, (78, 14): 0, (78, 15): 0, (78, 16): 0, (78, 17): 0, (78, 18): 1, (78, 19): 0, (78, 20): 0, (78, 21): 0, (78, 22): 0, (78, 23): 0, (78, 24): 0, (78, 25): 0, (78, 26): 0, (78, 27): 0, (78, 28): 0, (78, 29): 0, (78, 30): 0, (78, 31): 0, (78, 32): 0, (78, 33): 0, (78, 34): 0, (78, 35): 0, (78, 36): 0, (78, 37): 0, (78, 38): 0, (78, 39): 0, (78, 40): 0, (78, 41): 0, (78, 42): 0, (79, 1): 0, (79, 2): 0, (79, 3): 0, (79, 4): 0, (79, 5): 0, (79, 6): 0, (79, 7): 0, (79, 8): 0, (79, 9): 0, (79, 10): 0, (79, 11): 0, (79, 12): 0, (79, 13): 0, (79, 14): 0, (79, 15): 0, (79, 16): 0, (79, 17): 0, (79, 18): 0, (79, 19): 0, (79, 20): 0, (79, 21): 0, (79, 22): 0, (79, 23): 0, (79, 24): 0, (79, 25): 1, (79, 26): 0, (79, 27): 0, (79, 28): 0, (79, 29): 0, (79, 30): 0, (79, 31): 0, (79, 32): 0, (79, 33): 0, (79, 34): 0, (79, 35): 0, (79, 36): 0, (79, 37): 0, (79, 38): 0, (79, 39): 0, (79, 40): 0, (79, 41): 0, (79, 42): 0, (81, 1): 0, (81, 2): 0, (81, 3): 0, (81, 4): 0, (81, 5): 0, (81, 6): 0, (81, 7): 0, (81, 8): 0, (81, 9): 0, (81, 10): 0, (81, 11): 0, (81, 12): 0, (81, 13): 0, (81, 14): 0, (81, 15): 0, (81, 16): 0, (81, 17): 1, (81, 18): 0, (81, 19): 0, (81, 20): 0, (81, 21): 0, (81, 22): 0, (81, 23): 0, (81, 24): 0, (81, 25): 0, (81, 26): 0, (81, 27): 0, (81, 28): 0, (81, 29): 0, (81, 30): 0, (81, 31): 0, (81, 32): 0, (81, 33): 0, (81, 34): 0, (81, 35): 0, (81, 36): 0, (81, 37): 0, (81, 38): 0, (81, 39): 0, (81, 40): 0, (81, 41): 0, (81, 42): 0, (82, 1): 0, (82, 2): 0, (82, 3): 0, (82, 4): 0, (82, 5): 0, (82, 6): 0, (82, 7): 0, (82, 8): 0, (82, 9): 0, (82, 10): 0, (82, 11): 0, (82, 12): 0, (82, 13): 0, (82, 14): 0, (82, 15): 1, (82, 16): 0, (82, 17): 0, (82, 18): 0, (82, 19): 0, (82, 20): 0, (82, 21): 0, (82, 22): 0, (82, 23): 0, (82, 24): 0, (82, 25): 0, (82, 26): 0, (82, 27): 0, (82, 28): 0, (82, 29): 0, (82, 30): 0, (82, 31): 0, (82, 32): 0, (82, 33): 0, (82, 34): 0, (82, 35): 0, (82, 36): 0, (82, 37): 0, (82, 38): 0, (82, 39): 0, (82, 40): 0, (82, 41): 0, (82, 42): 0}</t>
-  </si>
-  <si>
-    <t>{(2, 1): 0, (2, 2): 0, (2, 3): 0, (3, 1): 0, (3, 2): 0, (3, 3): 0, (4, 1): 0, (4, 2): 0, (4, 3): 0, (9, 1): 0, (9, 2): 0, (9, 3): 0, (15, 1): 0, (15, 2): 0, (15, 3): 0, (16, 1): 0, (16, 2): 0, (16, 3): 0, (20, 1): 0, (20, 2): 0, (20, 3): 0, (21, 1): 0, (21, 2): 0, (21, 3): 0, (22, 1): 0, (22, 2): 0, (22, 3): 0, (23, 1): 0, (23, 2): 0, (23, 3): 0, (24, 1): 0, (24, 2): 0, (24, 3): 0, (25, 1): 0, (25, 2): 0, (25, 3): 0, (26, 1): 0, (26, 2): 0, (26, 3): 0, (28, 1): 0, (28, 2): 0, (28, 3): 0, (30, 1): 0, (30, 2): 0, (30, 3): 0, (31, 1): 0, (31, 2): 0, (31, 3): 0, (36, 1): 0, (36, 2): 0, (36, 3): 0, (37, 1): 0, (37, 2): 0, (37, 3): 0, (38, 1): 0, (38, 2): 0, (38, 3): 0, (39, 1): 0, (39, 2): 0, (39, 3): 0, (40, 1): 0, (40, 2): 0, (40, 3): 0, (41, 1): 0, (41, 2): 0, (41, 3): 0, (43, 1): 0, (43, 2): 0, (43, 3): 0, (50, 1): 0, (50, 2): 0, (50, 3): 0, (59, 1): 0, (59, 2): 0, (59, 3): 0, (60, 1): 0, (60, 2): 0, (60, 3): 0, (62, 1): 0, (62, 2): 0, (62, 3): 0, (63, 1): 0, (63, 2): 0, (63, 3): 0, (65, 1): 0, (65, 2): 0, (65, 3): 0, (66, 1): 0, (66, 2): 0, (66, 3): 0, (67, 1): 0, (67, 2): 0, (67, 3): 0, (70, 1): 0, (70, 2): 0, (70, 3): 0, (71, 1): 0, (71, 2): 0, (71, 3): 0, (73, 1): 0, (73, 2): 0, (73, 3): 0, (75, 1): 0, (75, 2): 0, (75, 3): 0, (77, 1): 0, (77, 2): 0, (77, 3): 0, (78, 1): 0, (78, 2): 0, (78, 3): 0, (79, 1): 0, (79, 2): 0, (79, 3): 0, (81, 1): 0, (81, 2): 0, (81, 3): 0, (82, 1): 0, (82, 2): 0, (82, 3): 0}</t>
+    <t>{8: 10, 9: 6, 10: 12, 11: 6, 21: 8, 23: 10, 24: 10, 31: 2, 33: 4, 45: 6, 50: 7, 53: 7, 54: 6, 55: 4, 56: 9, 58: 11, 61: 9, 62: 8, 64: 6, 66: 8, 69: 6, 71: 9, 76: 5, 77: 9, 78: 5, 80: 5, 81: 7, 83: 8, 85: 11, 90: 5, 91: 6, 93: 9, 103: 6, 105: 5, 114: 8, 119: 9, 126: 6, 127: 9, 128: 6, 3: 15, 4: 14, 12: 11, 29: 13, 132: 13}</t>
+  </si>
+  <si>
+    <t>{(1, 1): 0, (1, 2): 0, (1, 3): 0, (1, 4): 0, (1, 5): 0, (1, 6): 0, (1, 7): 0, (1, 8): 0, (1, 9): 0, (1, 10): 0, (1, 11): 0, (1, 12): 0, (1, 13): 0, (1, 14): 0, (1, 15): 0, (1, 16): 1, (1, 17): 1, (1, 18): 1, (1, 19): 1, (1, 20): 1, (1, 21): 1, (1, 22): 1, (1, 23): 1, (1, 24): 1, (1, 25): 1, (1, 26): 1, (1, 27): 1, (1, 28): 0, (1, 29): 0, (1, 30): 0, (1, 31): 0, (1, 32): 0, (1, 33): 0, (1, 34): 0, (1, 35): 0, (1, 36): 0, (1, 37): 0, (1, 38): 0, (1, 39): 0, (1, 40): 0, (1, 41): 0, (1, 42): 0, (1, 43): 0, (1, 44): 0, (1, 45): 0, (1, 46): 0, (1, 47): 0, (1, 48): 0, (1, 49): 0, (1, 50): 0, (1, 51): 0, (1, 52): 0, (1, 53): 0, (1, 54): 0, (1, 55): 0, (1, 56): 0, (1, 57): 0, (1, 58): 0, (1, 59): 0, (1, 60): 0, (1, 61): 0, (1, 62): 0, (1, 63): 0, (1, 64): 0, (1, 65): 0, (1, 66): 0, (1, 67): 0, (1, 68): 0, (1, 69): 0, (2, 1): 0, (2, 2): 0, (2, 3): 0, (2, 4): 0, (2, 5): 0, (2, 6): 0, (2, 7): 0, (2, 8): 0, (2, 9): 0, (2, 10): 0, (2, 11): 0, (2, 12): 0, (2, 13): 0, (2, 14): 0, (2, 15): 1, (2, 16): 1, (2, 17): 1, (2, 18): 1, (2, 19): 1, (2, 20): 1, (2, 21): 1, (2, 22): 1, (2, 23): 1, (2, 24): 1, (2, 25): 1, (2, 26): 1, (2, 27): 1, (2, 28): 1, (2, 29): 1, (2, 30): 1, (2, 31): 0, (2, 32): 0, (2, 33): 0, (2, 34): 0, (2, 35): 0, (2, 36): 0, (2, 37): 0, (2, 38): 0, (2, 39): 0, (2, 40): 0, (2, 41): 0, (2, 42): 0, (2, 43): 0, (2, 44): 0, (2, 45): 0, (2, 46): 0, (2, 47): 0, (2, 48): 0, (2, 49): 0, (2, 50): 0, (2, 51): 0, (2, 52): 0, (2, 53): 0, (2, 54): 0, (2, 55): 0, (2, 56): 0, (2, 57): 0, (2, 58): 0, (2, 59): 0, (2, 60): 0, (2, 61): 0, (2, 62): 0, (2, 63): 0, (2, 64): 0, (2, 65): 0, (2, 66): 0, (2, 67): 0, (2, 68): 0, (2, 69): 0, (6, 1): 0, (6, 2): 0, (6, 3): 0, (6, 4): 0, (6, 5): 0, (6, 6): 0, (6, 7): 0, (6, 8): 0, (6, 9): 0, (6, 10): 0, (6, 11): 0, (6, 12): 0, (6, 13): 0, (6, 14): 0, (6, 15): 0, (6, 16): 0, (6, 17): 0, (6, 18): 0, (6, 19): 0, (6, 20): 0, (6, 21): 0, (6, 22): 1, (6, 23): 1, (6, 24): 1, (6, 25): 1, (6, 26): 1, (6, 27): 1, (6, 28): 1, (6, 29): 1, (6, 30): 1, (6, 31): 1, (6, 32): 1, (6, 33): 1, (6, 34): 1, (6, 35): 1, (6, 36): 1, (6, 37): 1, (6, 38): 1, (6, 39): 1, (6, 40): 1, (6, 41): 1, (6, 42): 1, (6, 43): 1, (6, 44): 1, (6, 45): 1, (6, 46): 1, (6, 47): 1, (6, 48): 0, (6, 49): 0, (6, 50): 0, (6, 51): 0, (6, 52): 0, (6, 53): 0, (6, 54): 0, (6, 55): 0, (6, 56): 0, (6, 57): 0, (6, 58): 0, (6, 59): 0, (6, 60): 0, (6, 61): 0, (6, 62): 0, (6, 63): 0, (6, 64): 0, (6, 65): 0, (6, 66): 0, (6, 67): 0, (6, 68): 0, (6, 69): 0, (7, 1): 0, (7, 2): 0, (7, 3): 0, (7, 4): 0, (7, 5): 0, (7, 6): 0, (7, 7): 0, (7, 8): 0, (7, 9): 0, (7, 10): 0, (7, 11): 0, (7, 12): 0, (7, 13): 0, (7, 14): 0, (7, 15): 0, (7, 16): 0, (7, 17): 0, (7, 18): 0, (7, 19): 0, (7, 20): 0, (7, 21): 0, (7, 22): 0, (7, 23): 0, (7, 24): 0, (7, 25): 0, (7, 26): 0, (7, 27): 0, (7, 28): 0, (7, 29): 0, (7, 30): 1, (7, 31): 1, (7, 32): 1, (7, 33): 1, (7, 34): 1, (7, 35): 1, (7, 36): 1, (7, 37): 1, (7, 38): 1, (7, 39): 1, (7, 40): 1, (7, 41): 1, (7, 42): 1, (7, 43): 1, (7, 44): 1, (7, 45): 1, (7, 46): 1, (7, 47): 1, (7, 48): 0, (7, 49): 0, (7, 50): 0, (7, 51): 0, (7, 52): 0, (7, 53): 0, (7, 54): 0, (7, 55): 0, (7, 56): 0, (7, 57): 0, (7, 58): 0, (7, 59): 0, (7, 60): 0, (7, 61): 0, (7, 62): 0, (7, 63): 0, (7, 64): 0, (7, 65): 0, (7, 66): 0, (7, 67): 0, (7, 68): 0, (7, 69): 0, (16, 1): 0, (16, 2): 0, (16, 3): 0, (16, 4): 0, (16, 5): 0, (16, 6): 0, (16, 7): 0, (16, 8): 0, (16, 9): 0, (16, 10): 0, (16, 11): 0, (16, 12): 0, (16, 13): 0, (16, 14): 0, (16, 15): 0, (16, 16): 0, (16, 17): 1, (16, 18): 1, (16, 19): 1, (16, 20): 0, (16, 21): 0, (16, 22): 0, (16, 23): 0, (16, 24): 0, (16, 25): 0, (16, 26): 0, (16, 27): 0, (16, 28): 0, (16, 29): 0, (16, 30): 0, (16, 31): 0, (16, 32): 0, (16, 33): 0, (16, 34): 0, (16, 35): 0, (16, 36): 0, (16, 37): 0, (16, 38): 0, (16, 39): 0, (16, 40): 0, (16, 41): 0, (16, 42): 0, (16, 43): 0, (16, 44): 0, (16, 45): 0, (16, 46): 0, (16, 47): 0, (16, 48): 0, (16, 49): 0, (16, 50): 0, (16, 51): 0, (16, 52): 0, (16, 53): 0, (16, 54): 0, (16, 55): 0, (16, 56): 0, (16, 57): 0, (16, 58): 0, (16, 59): 0, (16, 60): 0, (16, 61): 0, (16, 62): 0, (16, 63): 0, (16, 64): 0, (16, 65): 0, (16, 66): 0, (16, 67): 0, (16, 68): 0, (16, 69): 0, (26, 1): 0, (26, 2): 0, (26, 3): 0, (26, 4): 0, (26, 5): 0, (26, 6): 0, (26, 7): 0, (26, 8): 0, (26, 9): 0, (26, 10): 0, (26, 11): 0, (26, 12): 0, (26, 13): 0, (26, 14): 0, (26, 15): 0, (26, 16): 0, (26, 17): 0, (26, 18): 0, (26, 19): 0, (26, 20): 0, (26, 21): 0, (26, 22): 0, (26, 23): 0, (26, 24): 0, (26, 25): 1, (26, 26): 1, (26, 27): 1, (26, 28): 1, (26, 29): 1, (26, 30): 1, (26, 31): 1, (26, 32): 1, (26, 33): 1, (26, 34): 1, (26, 35): 1, (26, 36): 1, (26, 37): 1, (26, 38): 1, (26, 39): 0, (26, 40): 0, (26, 41): 0, (26, 42): 0, (26, 43): 0, (26, 44): 0, (26, 45): 0, (26, 46): 0, (26, 47): 0, (26, 48): 0, (26, 49): 0, (26, 50): 0, (26, 51): 0, (26, 52): 0, (26, 53): 0, (26, 54): 0, (26, 55): 0, (26, 56): 0, (26, 57): 0, (26, 58): 0, (26, 59): 0, (26, 60): 0, (26, 61): 0, (26, 62): 0, (26, 63): 0, (26, 64): 0, (26, 65): 0, (26, 66): 0, (26, 67): 0, (26, 68): 0, (26, 69): 0, (35, 1): 0, (35, 2): 0, (35, 3): 0, (35, 4): 0, (35, 5): 0, (35, 6): 1, (35, 7): 1, (35, 8): 1, (35, 9): 1, (35, 10): 1, (35, 11): 1, (35, 12): 1, (35, 13): 1, (35, 14): 1, (35, 15): 1, (35, 16): 0, (35, 17): 0, (35, 18): 0, (35, 19): 0, (35, 20): 0, (35, 21): 0, (35, 22): 0, (35, 23): 0, (35, 24): 0, (35, 25): 0, (35, 26): 0, (35, 27): 0, (35, 28): 0, (35, 29): 0, (35, 30): 0, (35, 31): 0, (35, 32): 0, (35, 33): 0, (35, 34): 0, (35, 35): 0, (35, 36): 0, (35, 37): 0, (35, 38): 0, (35, 39): 0, (35, 40): 0, (35, 41): 0, (35, 42): 0, (35, 43): 0, (35, 44): 0, (35, 45): 0, (35, 46): 0, (35, 47): 0, (35, 48): 0, (35, 49): 0, (35, 50): 0, (35, 51): 0, (35, 52): 0, (35, 53): 0, (35, 54): 0, (35, 55): 0, (35, 56): 0, (35, 57): 0, (35, 58): 0, (35, 59): 0, (35, 60): 0, (35, 61): 0, (35, 62): 0, (35, 63): 0, (35, 64): 0, (35, 65): 0, (35, 66): 0, (35, 67): 0, (35, 68): 0, (35, 69): 0, (38, 1): 0, (38, 2): 0, (38, 3): 0, (38, 4): 0, (38, 5): 1, (38, 6): 1, (38, 7): 1, (38, 8): 1, (38, 9): 1, (38, 10): 1, (38, 11): 1, (38, 12): 0, (38, 13): 0, (38, 14): 0, (38, 15): 0, (38, 16): 0, (38, 17): 0, (38, 18): 0, (38, 19): 0, (38, 20): 0, (38, 21): 0, (38, 22): 0, (38, 23): 0, (38, 24): 0, (38, 25): 0, (38, 26): 0, (38, 27): 0, (38, 28): 0, (38, 29): 0, (38, 30): 0, (38, 31): 0, (38, 32): 0, (38, 33): 0, (38, 34): 0, (38, 35): 0, (38, 36): 0, (38, 37): 0, (38, 38): 0, (38, 39): 0, (38, 40): 0, (38, 41): 0, (38, 42): 0, (38, 43): 0, (38, 44): 0, (38, 45): 0, (38, 46): 0, (38, 47): 0, (38, 48): 0, (38, 49): 0, (38, 50): 0, (38, 51): 0, (38, 52): 0, (38, 53): 0, (38, 54): 0, (38, 55): 0, (38, 56): 0, (38, 57): 0, (38, 58): 0, (38, 59): 0, (38, 60): 0, (38, 61): 0, (38, 62): 0, (38, 63): 0, (38, 64): 0, (38, 65): 0, (38, 66): 0, (38, 67): 0, (38, 68): 0, (38, 69): 0, (39, 1): 0, (39, 2): 0, (39, 3): 0, (39, 4): 0, (39, 5): 0, (39, 6): 0, (39, 7): 0, (39, 8): 0, (39, 9): 0, (39, 10): 0, (39, 11): 0, (39, 12): 0, (39, 13): 0, (39, 14): 1, (39, 15): 1, (39, 16): 1, (39, 17): 1, (39, 18): 1, (39, 19): 1, (39, 20): 1, (39, 21): 1, (39, 22): 1, (39, 23): 0, (39, 24): 0, (39, 25): 0, (39, 26): 0, (39, 27): 0, (39, 28): 0, (39, 29): 0, (39, 30): 0, (39, 31): 0, (39, 32): 0, (39, 33): 0, (39, 34): 0, (39, 35): 0, (39, 36): 0, (39, 37): 0, (39, 38): 0, (39, 39): 0, (39, 40): 0, (39, 41): 0, (39, 42): 0, (39, 43): 0, (39, 44): 0, (39, 45): 0, (39, 46): 0, (39, 47): 0, (39, 48): 0, (39, 49): 0, (39, 50): 0, (39, 51): 0, (39, 52): 0, (39, 53): 0, (39, 54): 0, (39, 55): 0, (39, 56): 0, (39, 57): 0, (39, 58): 0, (39, 59): 0, (39, 60): 0, (39, 61): 0, (39, 62): 0, (39, 63): 0, (39, 64): 0, (39, 65): 0, (39, 66): 0, (39, 67): 0, (39, 68): 0, (39, 69): 0, (41, 1): 0, (41, 2): 0, (41, 3): 0, (41, 4): 0, (41, 5): 0, (41, 6): 0, (41, 7): 0, (41, 8): 0, (41, 9): 0, (41, 10): 0, (41, 11): 0, (41, 12): 0, (41, 13): 0, (41, 14): 0, (41, 15): 0, (41, 16): 0, (41, 17): 0, (41, 18): 0, (41, 19): 0, (41, 20): 0, (41, 21): 0, (41, 22): 0, (41, 23): 0, (41, 24): 0, (41, 25): 0, (41, 26): 0, (41, 27): 0, (41, 28): 1, (41, 29): 1, (41, 30): 1, (41, 31): 1, (41, 32): 1, (41, 33): 1, (41, 34): 1, (41, 35): 1, (41, 36): 1, (41, 37): 0, (41, 38): 0, (41, 39): 0, (41, 40): 0, (41, 41): 0, (41, 42): 0, (41, 43): 0, (41, 44): 0, (41, 45): 0, (41, 46): 0, (41, 47): 0, (41, 48): 0, (41, 49): 0, (41, 50): 0, (41, 51): 0, (41, 52): 0, (41, 53): 0, (41, 54): 0, (41, 55): 0, (41, 56): 0, (41, 57): 0, (41, 58): 0, (41, 59): 0, (41, 60): 0, (41, 61): 0, (41, 62): 0, (41, 63): 0, (41, 64): 0, (41, 65): 0, (41, 66): 0, (41, 67): 0, (41, 68): 0, (41, 69): 0, (42, 1): 0, (42, 2): 0, (42, 3): 0, (42, 4): 0, (42, 5): 0, (42, 6): 0, (42, 7): 0, (42, 8): 0, (42, 9): 0, (42, 10): 0, (42, 11): 0, (42, 12): 0, (42, 13): 0, (42, 14): 0, (42, 15): 0, (42, 16): 0, (42, 17): 0, (42, 18): 0, (42, 19): 0, (42, 20): 0, (42, 21): 0, (42, 22): 1, (42, 23): 1, (42, 24): 1, (42, 25): 1, (42, 26): 1, (42, 27): 1, (42, 28): 1, (42, 29): 1, (42, 30): 1, (42, 31): 0, (42, 32): 0, (42, 33): 0, (42, 34): 0, (42, 35): 0, (42, 36): 0, (42, 37): 0, (42, 38): 0, (42, 39): 0, (42, 40): 0, (42, 41): 0, (42, 42): 0, (42, 43): 0, (42, 44): 0, (42, 45): 0, (42, 46): 0, (42, 47): 0, (42, 48): 0, (42, 49): 0, (42, 50): 0, (42, 51): 0, (42, 52): 0, (42, 53): 0, (42, 54): 0, (42, 55): 0, (42, 56): 0, (42, 57): 0, (42, 58): 0, (42, 59): 0, (42, 60): 0, (42, 61): 0, (42, 62): 0, (42, 63): 0, (42, 64): 0, (42, 65): 0, (42, 66): 0, (42, 67): 0, (42, 68): 0, (42, 69): 0, (43, 1): 0, (43, 2): 0, (43, 3): 0, (43, 4): 0, (43, 5): 0, (43, 6): 0, (43, 7): 0, (43, 8): 0, (43, 9): 0, (43, 10): 0, (43, 11): 0, (43, 12): 0, (43, 13): 0, (43, 14): 0, (43, 15): 0, (43, 16): 0, (43, 17): 0, (43, 18): 0, (43, 19): 0, (43, 20): 0, (43, 21): 0, (43, 22): 1, (43, 23): 1, (43, 24): 1, (43, 25): 1, (43, 26): 1, (43, 27): 0, (43, 28): 0, (43, 29): 0, (43, 30): 0, (43, 31): 0, (43, 32): 0, (43, 33): 0, (43, 34): 0, (43, 35): 0, (43, 36): 0, (43, 37): 0, (43, 38): 0, (43, 39): 0, (43, 40): 0, (43, 41): 0, (43, 42): 0, (43, 43): 0, (43, 44): 0, (43, 45): 0, (43, 46): 0, (43, 47): 0, (43, 48): 0, (43, 49): 0, (43, 50): 0, (43, 51): 0, (43, 52): 0, (43, 53): 0, (43, 54): 0, (43, 55): 0, (43, 56): 0, (43, 57): 0, (43, 58): 0, (43, 59): 0, (43, 60): 0, (43, 61): 0, (43, 62): 0, (43, 63): 0, (43, 64): 0, (43, 65): 0, (43, 66): 0, (43, 67): 0, (43, 68): 0, (43, 69): 0, (46, 1): 0, (46, 2): 0, (46, 3): 0, (46, 4): 0, (46, 5): 1, (46, 6): 1, (46, 7): 1, (46, 8): 1, (46, 9): 1, (46, 10): 1, (46, 11): 1, (46, 12): 1, (46, 13): 1, (46, 14): 1, (46, 15): 1, (46, 16): 0, (46, 17): 0, (46, 18): 0, (46, 19): 0, (46, 20): 0, (46, 21): 0, (46, 22): 0, (46, 23): 0, (46, 24): 0, (46, 25): 0, (46, 26): 0, (46, 27): 0, (46, 28): 0, (46, 29): 0, (46, 30): 0, (46, 31): 0, (46, 32): 0, (46, 33): 0, (46, 34): 0, (46, 35): 0, (46, 36): 0, (46, 37): 0, (46, 38): 0, (46, 39): 0, (46, 40): 0, (46, 41): 0, (46, 42): 0, (46, 43): 0, (46, 44): 0, (46, 45): 0, (46, 46): 0, (46, 47): 0, (46, 48): 0, (46, 49): 0, (46, 50): 0, (46, 51): 0, (46, 52): 0, (46, 53): 0, (46, 54): 0, (46, 55): 0, (46, 56): 0, (46, 57): 0, (46, 58): 0, (46, 59): 0, (46, 60): 0, (46, 61): 0, (46, 62): 0, (46, 63): 0, (46, 64): 0, (46, 65): 0, (46, 66): 0, (46, 67): 0, (46, 68): 0, (46, 69): 0, (48, 1): 0, (48, 2): 0, (48, 3): 0, (48, 4): 0, (48, 5): 0, (48, 6): 0, (48, 7): 0, (48, 8): 0, (48, 9): 0, (48, 10): 0, (48, 11): 0, (48, 12): 0, (48, 13): 0, (48, 14): 0, (48, 15): 0, (48, 16): 0, (48, 17): 0, (48, 18): 0, (48, 19): 0, (48, 20): 0, (48, 21): 0, (48, 22): 0, (48, 23): 0, (48, 24): 0, (48, 25): 0, (48, 26): 1, (48, 27): 1, (48, 28): 1, (48, 29): 1, (48, 30): 0, (48, 31): 0, (48, 32): 0, (48, 33): 0, (48, 34): 0, (48, 35): 0, (48, 36): 0, (48, 37): 0, (48, 38): 0, (48, 39): 0, (48, 40): 0, (48, 41): 0, (48, 42): 0, (48, 43): 0, (48, 44): 0, (48, 45): 0, (48, 46): 0, (48, 47): 0, (48, 48): 0, (48, 49): 0, (48, 50): 0, (48, 51): 0, (48, 52): 0, (48, 53): 0, (48, 54): 0, (48, 55): 0, (48, 56): 0, (48, 57): 0, (48, 58): 0, (48, 59): 0, (48, 60): 0, (48, 61): 0, (48, 62): 0, (48, 63): 0, (48, 64): 0, (48, 65): 0, (48, 66): 0, (48, 67): 0, (48, 68): 0, (48, 69): 0, (49, 1): 0, (49, 2): 0, (49, 3): 0, (49, 4): 0, (49, 5): 0, (49, 6): 0, (49, 7): 0, (49, 8): 0, (49, 9): 1, (49, 10): 1, (49, 11): 1, (49, 12): 1, (49, 13): 1, (49, 14): 1, (49, 15): 1, (49, 16): 1, (49, 17): 1, (49, 18): 0, (49, 19): 0, (49, 20): 0, (49, 21): 0, (49, 22): 0, (49, 23): 0, (49, 24): 0, (49, 25): 0, (49, 26): 0, (49, 27): 0, (49, 28): 0, (49, 29): 0, (49, 30): 0, (49, 31): 0, (49, 32): 0, (49, 33): 0, (49, 34): 0, (49, 35): 0, (49, 36): 0, (49, 37): 0, (49, 38): 0, (49, 39): 0, (49, 40): 0, (49, 41): 0, (49, 42): 0, (49, 43): 0, (49, 44): 0, (49, 45): 0, (49, 46): 0, (49, 47): 0, (49, 48): 0, (49, 49): 0, (49, 50): 0, (49, 51): 0, (49, 52): 0, (49, 53): 0, (49, 54): 0, (49, 55): 0, (49, 56): 0, (49, 57): 0, (49, 58): 0, (49, 59): 0, (49, 60): 0, (49, 61): 0, (49, 62): 0, (49, 63): 0, (49, 64): 0, (49, 65): 0, (49, 66): 0, (49, 67): 0, (49, 68): 0, (49, 69): 0, (51, 1): 0, (51, 2): 0, (51, 3): 0, (51, 4): 0, (51, 5): 0, (51, 6): 0, (51, 7): 0, (51, 8): 0, (51, 9): 0, (51, 10): 0, (51, 11): 0, (51, 12): 0, (51, 13): 1, (51, 14): 1, (51, 15): 1, (51, 16): 1, (51, 17): 1, (51, 18): 1, (51, 19): 1, (51, 20): 1, (51, 21): 0, (51, 22): 0, (51, 23): 0, (51, 24): 0, (51, 25): 0, (51, 26): 0, (51, 27): 0, (51, 28): 0, (51, 29): 0, (51, 30): 0, (51, 31): 0, (51, 32): 0, (51, 33): 0, (51, 34): 0, (51, 35): 0, (51, 36): 0, (51, 37): 0, (51, 38): 0, (51, 39): 0, (51, 40): 0, (51, 41): 0, (51, 42): 0, (51, 43): 0, (51, 44): 0, (51, 45): 0, (51, 46): 0, (51, 47): 0, (51, 48): 0, (51, 49): 0, (51, 50): 0, (51, 51): 0, (51, 52): 0, (51, 53): 0, (51, 54): 0, (51, 55): 0, (51, 56): 0, (51, 57): 0, (51, 58): 0, (51, 59): 0, (51, 60): 0, (51, 61): 0, (51, 62): 0, (51, 63): 0, (51, 64): 0, (51, 65): 0, (51, 66): 0, (51, 67): 0, (51, 68): 0, (51, 69): 0, (52, 1): 0, (52, 2): 0, (52, 3): 1, (52, 4): 1, (52, 5): 1, (52, 6): 1, (52, 7): 1, (52, 8): 1, (52, 9): 1, (52, 10): 1, (52, 11): 1, (52, 12): 1, (52, 13): 0, (52, 14): 0, (52, 15): 0, (52, 16): 0, (52, 17): 0, (52, 18): 0, (52, 19): 0, (52, 20): 0, (52, 21): 0, (52, 22): 0, (52, 23): 0, (52, 24): 0, (52, 25): 0, (52, 26): 0, (52, 27): 0, (52, 28): 0, (52, 29): 0, (52, 30): 0, (52, 31): 0, (52, 32): 0, (52, 33): 0, (52, 34): 0, (52, 35): 0, (52, 36): 0, (52, 37): 0, (52, 38): 0, (52, 39): 0, (52, 40): 0, (52, 41): 0, (52, 42): 0, (52, 43): 0, (52, 44): 0, (52, 45): 0, (52, 46): 0, (52, 47): 0, (52, 48): 0, (52, 49): 0, (52, 50): 0, (52, 51): 0, (52, 52): 0, (52, 53): 0, (52, 54): 0, (52, 55): 0, (52, 56): 0, (52, 57): 0, (52, 58): 0, (52, 59): 0, (52, 60): 0, (52, 61): 0, (52, 62): 0, (52, 63): 0, (52, 64): 0, (52, 65): 0, (52, 66): 0, (52, 67): 0, (52, 68): 0, (52, 69): 0, (57, 1): 0, (57, 2): 0, (57, 3): 0, (57, 4): 0, (57, 5): 0, (57, 6): 0, (57, 7): 0, (57, 8): 0, (57, 9): 0, (57, 10): 0, (57, 11): 0, (57, 12): 0, (57, 13): 0, (57, 14): 0, (57, 15): 0, (57, 16): 0, (57, 17): 0, (57, 18): 0, (57, 19): 0, (57, 20): 0, (57, 21): 0, (57, 22): 0, (57, 23): 0, (57, 24): 1, (57, 25): 1, (57, 26): 1, (57, 27): 1, (57, 28): 1, (57, 29): 1, (57, 30): 1, (57, 31): 1, (57, 32): 1, (57, 33): 1, (57, 34): 1, (57, 35): 0, (57, 36): 0, (57, 37): 0, (57, 38): 0, (57, 39): 0, (57, 40): 0, (57, 41): 0, (57, 42): 0, (57, 43): 0, (57, 44): 0, (57, 45): 0, (57, 46): 0, (57, 47): 0, (57, 48): 0, (57, 49): 0, (57, 50): 0, (57, 51): 0, (57, 52): 0, (57, 53): 0, (57, 54): 0, (57, 55): 0, (57, 56): 0, (57, 57): 0, (57, 58): 0, (57, 59): 0, (57, 60): 0, (57, 61): 0, (57, 62): 0, (57, 63): 0, (57, 64): 0, (57, 65): 0, (57, 66): 0, (57, 67): 0, (57, 68): 0, (57, 69): 0, (70, 1): 0, (70, 2): 0, (70, 3): 0, (70, 4): 0, (70, 5): 0, (70, 6): 0, (70, 7): 0, (70, 8): 0, (70, 9): 0, (70, 10): 0, (70, 11): 0, (70, 12): 0, (70, 13): 0, (70, 14): 0, (70, 15): 0, (70, 16): 0, (70, 17): 1, (70, 18): 1, (70, 19): 1, (70, 20): 1, (70, 21): 1, (70, 22): 1, (70, 23): 1, (70, 24): 1, (70, 25): 1, (70, 26): 1, (70, 27): 0, (70, 28): 0, (70, 29): 0, (70, 30): 0, (70, 31): 0, (70, 32): 0, (70, 33): 0, (70, 34): 0, (70, 35): 0, (70, 36): 0, (70, 37): 0, (70, 38): 0, (70, 39): 0, (70, 40): 0, (70, 41): 0, (70, 42): 0, (70, 43): 0, (70, 44): 0, (70, 45): 0, (70, 46): 0, (70, 47): 0, (70, 48): 0, (70, 49): 0, (70, 50): 0, (70, 51): 0, (70, 52): 0, (70, 53): 0, (70, 54): 0, (70, 55): 0, (70, 56): 0, (70, 57): 0, (70, 58): 0, (70, 59): 0, (70, 60): 0, (70, 61): 0, (70, 62): 0, (70, 63): 0, (70, 64): 0, (70, 65): 0, (70, 66): 0, (70, 67): 0, (70, 68): 0, (70, 69): 0, (73, 1): 0, (73, 2): 0, (73, 3): 0, (73, 4): 0, (73, 5): 0, (73, 6): 0, (73, 7): 0, (73, 8): 0, (73, 9): 0, (73, 10): 0, (73, 11): 0, (73, 12): 0, (73, 13): 0, (73, 14): 0, (73, 15): 0, (73, 16): 0, (73, 17): 0, (73, 18): 0, (73, 19): 0, (73, 20): 0, (73, 21): 0, (73, 22): 0, (73, 23): 0, (73, 24): 0, (73, 25): 0, (73, 26): 0, (73, 27): 0, (73, 28): 0, (73, 29): 0, (73, 30): 0, (73, 31): 0, (73, 32): 1, (73, 33): 1, (73, 34): 1, (73, 35): 1, (73, 36): 0, (73, 37): 0, (73, 38): 0, (73, 39): 0, (73, 40): 0, (73, 41): 0, (73, 42): 0, (73, 43): 0, (73, 44): 0, (73, 45): 0, (73, 46): 0, (73, 47): 0, (73, 48): 0, (73, 49): 0, (73, 50): 0, (73, 51): 0, (73, 52): 0, (73, 53): 0, (73, 54): 0, (73, 55): 0, (73, 56): 0, (73, 57): 0, (73, 58): 0, (73, 59): 0, (73, 60): 0, (73, 61): 0, (73, 62): 0, (73, 63): 0, (73, 64): 0, (73, 65): 0, (73, 66): 0, (73, 67): 0, (73, 68): 0, (73, 69): 0, (75, 1): 0, (75, 2): 0, (75, 3): 0, (75, 4): 0, (75, 5): 0, (75, 6): 0, (75, 7): 0, (75, 8): 1, (75, 9): 1, (75, 10): 1, (75, 11): 1, (75, 12): 1, (75, 13): 1, (75, 14): 1, (75, 15): 1, (75, 16): 0, (75, 17): 0, (75, 18): 0, (75, 19): 0, (75, 20): 0, (75, 21): 0, (75, 22): 0, (75, 23): 0, (75, 24): 0, (75, 25): 0, (75, 26): 0, (75, 27): 0, (75, 28): 0, (75, 29): 0, (75, 30): 0, (75, 31): 0, (75, 32): 0, (75, 33): 0, (75, 34): 0, (75, 35): 0, (75, 36): 0, (75, 37): 0, (75, 38): 0, (75, 39): 0, (75, 40): 0, (75, 41): 0, (75, 42): 0, (75, 43): 0, (75, 44): 0, (75, 45): 0, (75, 46): 0, (75, 47): 0, (75, 48): 0, (75, 49): 0, (75, 50): 0, (75, 51): 0, (75, 52): 0, (75, 53): 0, (75, 54): 0, (75, 55): 0, (75, 56): 0, (75, 57): 0, (75, 58): 0, (75, 59): 0, (75, 60): 0, (75, 61): 0, (75, 62): 0, (75, 63): 0, (75, 64): 0, (75, 65): 0, (75, 66): 0, (75, 67): 0, (75, 68): 0, (75, 69): 0, (82, 1): 0, (82, 2): 0, (82, 3): 0, (82, 4): 0, (82, 5): 0, (82, 6): 0, (82, 7): 0, (82, 8): 0, (82, 9): 0, (82, 10): 0, (82, 11): 0, (82, 12): 0, (82, 13): 0, (82, 14): 0, (82, 15): 0, (82, 16): 0, (82, 17): 0, (82, 18): 0, (82, 19): 0, (82, 20): 0, (82, 21): 0, (82, 22): 0, (82, 23): 0, (82, 24): 1, (82, 25): 1, (82, 26): 1, (82, 27): 1, (82, 28): 1, (82, 29): 1, (82, 30): 1, (82, 31): 1, (82, 32): 1, (82, 33): 1, (82, 34): 0, (82, 35): 0, (82, 36): 0, (82, 37): 0, (82, 38): 0, (82, 39): 0, (82, 40): 0, (82, 41): 0, (82, 42): 0, (82, 43): 0, (82, 44): 0, (82, 45): 0, (82, 46): 0, (82, 47): 0, (82, 48): 0, (82, 49): 0, (82, 50): 0, (82, 51): 0, (82, 52): 0, (82, 53): 0, (82, 54): 0, (82, 55): 0, (82, 56): 0, (82, 57): 0, (82, 58): 0, (82, 59): 0, (82, 60): 0, (82, 61): 0, (82, 62): 0, (82, 63): 0, (82, 64): 0, (82, 65): 0, (82, 66): 0, (82, 67): 0, (82, 68): 0, (82, 69): 0, (84, 1): 0, (84, 2): 0, (84, 3): 0, (84, 4): 0, (84, 5): 0, (84, 6): 0, (84, 7): 0, (84, 8): 0, (84, 9): 0, (84, 10): 0, (84, 11): 0, (84, 12): 0, (84, 13): 0, (84, 14): 0, (84, 15): 0, (84, 16): 0, (84, 17): 0, (84, 18): 0, (84, 19): 1, (84, 20): 1, (84, 21): 1, (84, 22): 1, (84, 23): 1, (84, 24): 1, (84, 25): 1, (84, 26): 0, (84, 27): 0, (84, 28): 0, (84, 29): 0, (84, 30): 0, (84, 31): 0, (84, 32): 0, (84, 33): 0, (84, 34): 0, (84, 35): 0, (84, 36): 0, (84, 37): 0, (84, 38): 0, (84, 39): 0, (84, 40): 0, (84, 41): 0, (84, 42): 0, (84, 43): 0, (84, 44): 0, (84, 45): 0, (84, 46): 0, (84, 47): 0, (84, 48): 0, (84, 49): 0, (84, 50): 0, (84, 51): 0, (84, 52): 0, (84, 53): 0, (84, 54): 0, (84, 55): 0, (84, 56): 0, (84, 57): 0, (84, 58): 0, (84, 59): 0, (84, 60): 0, (84, 61): 0, (84, 62): 0, (84, 63): 0, (84, 64): 0, (84, 65): 0, (84, 66): 0, (84, 67): 0, (84, 68): 0, (84, 69): 0, (86, 1): 0, (86, 2): 0, (86, 3): 0, (86, 4): 0, (86, 5): 0, (86, 6): 0, (86, 7): 1, (86, 8): 1, (86, 9): 1, (86, 10): 1, (86, 11): 1, (86, 12): 1, (86, 13): 0, (86, 14): 0, (86, 15): 0, (86, 16): 0, (86, 17): 0, (86, 18): 0, (86, 19): 0, (86, 20): 0, (86, 21): 0, (86, 22): 0, (86, 23): 0, (86, 24): 0, (86, 25): 0, (86, 26): 0, (86, 27): 0, (86, 28): 0, (86, 29): 0, (86, 30): 0, (86, 31): 0, (86, 32): 0, (86, 33): 0, (86, 34): 0, (86, 35): 0, (86, 36): 0, (86, 37): 0, (86, 38): 0, (86, 39): 0, (86, 40): 0, (86, 41): 0, (86, 42): 0, (86, 43): 0, (86, 44): 0, (86, 45): 0, (86, 46): 0, (86, 47): 0, (86, 48): 0, (86, 49): 0, (86, 50): 0, (86, 51): 0, (86, 52): 0, (86, 53): 0, (86, 54): 0, (86, 55): 0, (86, 56): 0, (86, 57): 0, (86, 58): 0, (86, 59): 0, (86, 60): 0, (86, 61): 0, (86, 62): 0, (86, 63): 0, (86, 64): 0, (86, 65): 0, (86, 66): 0, (86, 67): 0, (86, 68): 0, (86, 69): 0, (87, 1): 0, (87, 2): 0, (87, 3): 0, (87, 4): 0, (87, 5): 0, (87, 6): 0, (87, 7): 0, (87, 8): 0, (87, 9): 0, (87, 10): 0, (87, 11): 0, (87, 12): 0, (87, 13): 0, (87, 14): 0, (87, 15): 0, (87, 16): 0, (87, 17): 0, (87, 18): 0, (87, 19): 0, (87, 20): 0, (87, 21): 0, (87, 22): 0, (87, 23): 0, (87, 24): 0, (87, 25): 1, (87, 26): 1, (87, 27): 1, (87, 28): 1, (87, 29): 0, (87, 30): 0, (87, 31): 0, (87, 32): 0, (87, 33): 0, (87, 34): 0, (87, 35): 0, (87, 36): 0, (87, 37): 0, (87, 38): 0, (87, 39): 0, (87, 40): 0, (87, 41): 0, (87, 42): 0, (87, 43): 0, (87, 44): 0, (87, 45): 0, (87, 46): 0, (87, 47): 0, (87, 48): 0, (87, 49): 0, (87, 50): 0, (87, 51): 0, (87, 52): 0, (87, 53): 0, (87, 54): 0, (87, 55): 0, (87, 56): 0, (87, 57): 0, (87, 58): 0, (87, 59): 0, (87, 60): 0, (87, 61): 0, (87, 62): 0, (87, 63): 0, (87, 64): 0, (87, 65): 0, (87, 66): 0, (87, 67): 0, (87, 68): 0, (87, 69): 0, (89, 1): 0, (89, 2): 0, (89, 3): 0, (89, 4): 0, (89, 5): 0, (89, 6): 0, (89, 7): 0, (89, 8): 0, (89, 9): 0, (89, 10): 0, (89, 11): 0, (89, 12): 0, (89, 13): 0, (89, 14): 0, (89, 15): 0, (89, 16): 0, (89, 17): 0, (89, 18): 0, (89, 19): 0, (89, 20): 0, (89, 21): 1, (89, 22): 1, (89, 23): 1, (89, 24): 1, (89, 25): 1, (89, 26): 1, (89, 27): 0, (89, 28): 0, (89, 29): 0, (89, 30): 0, (89, 31): 0, (89, 32): 0, (89, 33): 0, (89, 34): 0, (89, 35): 0, (89, 36): 0, (89, 37): 0, (89, 38): 0, (89, 39): 0, (89, 40): 0, (89, 41): 0, (89, 42): 0, (89, 43): 0, (89, 44): 0, (89, 45): 0, (89, 46): 0, (89, 47): 0, (89, 48): 0, (89, 49): 0, (89, 50): 0, (89, 51): 0, (89, 52): 0, (89, 53): 0, (89, 54): 0, (89, 55): 0, (89, 56): 0, (89, 57): 0, (89, 58): 0, (89, 59): 0, (89, 60): 0, (89, 61): 0, (89, 62): 0, (89, 63): 0, (89, 64): 0, (89, 65): 0, (89, 66): 0, (89, 67): 0, (89, 68): 0, (89, 69): 0, (92, 1): 0, (92, 2): 0, (92, 3): 0, (92, 4): 0, (92, 5): 0, (92, 6): 0, (92, 7): 0, (92, 8): 0, (92, 9): 0, (92, 10): 0, (92, 11): 0, (92, 12): 0, (92, 13): 0, (92, 14): 0, (92, 15): 0, (92, 16): 0, (92, 17): 0, (92, 18): 0, (92, 19): 0, (92, 20): 0, (92, 21): 0, (92, 22): 0, (92, 23): 0, (92, 24): 0, (92, 25): 0, (92, 26): 0, (92, 27): 0, (92, 28): 0, (92, 29): 0, (92, 30): 0, (92, 31): 0, (92, 32): 1, (92, 33): 1, (92, 34): 1, (92, 35): 1, (92, 36): 1, (92, 37): 0, (92, 38): 0, (92, 39): 0, (92, 40): 0, (92, 41): 0, (92, 42): 0, (92, 43): 0, (92, 44): 0, (92, 45): 0, (92, 46): 0, (92, 47): 0, (92, 48): 0, (92, 49): 0, (92, 50): 0, (92, 51): 0, (92, 52): 0, (92, 53): 0, (92, 54): 0, (92, 55): 0, (92, 56): 0, (92, 57): 0, (92, 58): 0, (92, 59): 0, (92, 60): 0, (92, 61): 0, (92, 62): 0, (92, 63): 0, (92, 64): 0, (92, 65): 0, (92, 66): 0, (92, 67): 0, (92, 68): 0, (92, 69): 0, (96, 1): 0, (96, 2): 0, (96, 3): 0, (96, 4): 0, (96, 5): 0, (96, 6): 0, (96, 7): 0, (96, 8): 0, (96, 9): 0, (96, 10): 0, (96, 11): 0, (96, 12): 0, (96, 13): 0, (96, 14): 0, (96, 15): 0, (96, 16): 0, (96, 17): 0, (96, 18): 0, (96, 19): 0, (96, 20): 0, (96, 21): 0, (96, 22): 0, (96, 23): 0, (96, 24): 1, (96, 25): 1, (96, 26): 1, (96, 27): 0, (96, 28): 0, (96, 29): 0, (96, 30): 0, (96, 31): 0, (96, 32): 0, (96, 33): 0, (96, 34): 0, (96, 35): 0, (96, 36): 0, (96, 37): 0, (96, 38): 0, (96, 39): 0, (96, 40): 0, (96, 41): 0, (96, 42): 0, (96, 43): 0, (96, 44): 0, (96, 45): 0, (96, 46): 0, (96, 47): 0, (96, 48): 0, (96, 49): 0, (96, 50): 0, (96, 51): 0, (96, 52): 0, (96, 53): 0, (96, 54): 0, (96, 55): 0, (96, 56): 0, (96, 57): 0, (96, 58): 0, (96, 59): 0, (96, 60): 0, (96, 61): 0, (96, 62): 0, (96, 63): 0, (96, 64): 0, (96, 65): 0, (96, 66): 0, (96, 67): 0, (96, 68): 0, (96, 69): 0, (98, 1): 1, (98, 2): 1, (98, 3): 1, (98, 4): 1, (98, 5): 1, (98, 6): 1, (98, 7): 0, (98, 8): 0, (98, 9): 0, (98, 10): 0, (98, 11): 0, (98, 12): 0, (98, 13): 0, (98, 14): 0, (98, 15): 0, (98, 16): 0, (98, 17): 0, (98, 18): 0, (98, 19): 0, (98, 20): 0, (98, 21): 0, (98, 22): 0, (98, 23): 0, (98, 24): 0, (98, 25): 0, (98, 26): 0, (98, 27): 0, (98, 28): 0, (98, 29): 0, (98, 30): 0, (98, 31): 0, (98, 32): 0, (98, 33): 0, (98, 34): 0, (98, 35): 0, (98, 36): 0, (98, 37): 0, (98, 38): 0, (98, 39): 0, (98, 40): 0, (98, 41): 0, (98, 42): 0, (98, 43): 0, (98, 44): 0, (98, 45): 0, (98, 46): 0, (98, 47): 0, (98, 48): 0, (98, 49): 0, (98, 50): 0, (98, 51): 0, (98, 52): 0, (98, 53): 0, (98, 54): 0, (98, 55): 0, (98, 56): 0, (98, 57): 0, (98, 58): 0, (98, 59): 0, (98, 60): 0, (98, 61): 0, (98, 62): 0, (98, 63): 0, (98, 64): 0, (98, 65): 0, (98, 66): 0, (98, 67): 0, (98, 68): 0, (98, 69): 0, (100, 1): 0, (100, 2): 0, (100, 3): 0, (100, 4): 0, (100, 5): 0, (100, 6): 0, (100, 7): 0, (100, 8): 0, (100, 9): 0, (100, 10): 0, (100, 11): 0, (100, 12): 0, (100, 13): 0, (100, 14): 0, (100, 15): 0, (100, 16): 0, (100, 17): 0, (100, 18): 0, (100, 19): 0, (100, 20): 0, (100, 21): 0, (100, 22): 0, (100, 23): 0, (100, 24): 0, (100, 25): 0, (100, 26): 0, (100, 27): 0, (100, 28): 0, (100, 29): 1, (100, 30): 1, (100, 31): 0, (100, 32): 0, (100, 33): 0, (100, 34): 0, (100, 35): 0, (100, 36): 0, (100, 37): 0, (100, 38): 0, (100, 39): 0, (100, 40): 0, (100, 41): 0, (100, 42): 0, (100, 43): 0, (100, 44): 0, (100, 45): 0, (100, 46): 0, (100, 47): 0, (100, 48): 0, (100, 49): 0, (100, 50): 0, (100, 51): 0, (100, 52): 0, (100, 53): 0, (100, 54): 0, (100, 55): 0, (100, 56): 0, (100, 57): 0, (100, 58): 0, (100, 59): 0, (100, 60): 0, (100, 61): 0, (100, 62): 0, (100, 63): 0, (100, 64): 0, (100, 65): 0, (100, 66): 0, (100, 67): 0, (100, 68): 0, (100, 69): 0, (107, 1): 0, (107, 2): 0, (107, 3): 0, (107, 4): 0, (107, 5): 0, (107, 6): 0, (107, 7): 0, (107, 8): 0, (107, 9): 0, (107, 10): 0, (107, 11): 0, (107, 12): 0, (107, 13): 0, (107, 14): 0, (107, 15): 0, (107, 16): 0, (107, 17): 0, (107, 18): 0, (107, 19): 0, (107, 20): 0, (107, 21): 0, (107, 22): 0, (107, 23): 0, (107, 24): 0, (107, 25): 0, (107, 26): 0, (107, 27): 0, (107, 28): 0, (107, 29): 0, (107, 30): 0, (107, 31): 1, (107, 32): 1, (107, 33): 0, (107, 34): 0, (107, 35): 0, (107, 36): 0, (107, 37): 0, (107, 38): 0, (107, 39): 0, (107, 40): 0, (107, 41): 0, (107, 42): 0, (107, 43): 0, (107, 44): 0, (107, 45): 0, (107, 46): 0, (107, 47): 0, (107, 48): 0, (107, 49): 0, (107, 50): 0, (107, 51): 0, (107, 52): 0, (107, 53): 0, (107, 54): 0, (107, 55): 0, (107, 56): 0, (107, 57): 0, (107, 58): 0, (107, 59): 0, (107, 60): 0, (107, 61): 0, (107, 62): 0, (107, 63): 0, (107, 64): 0, (107, 65): 0, (107, 66): 0, (107, 67): 0, (107, 68): 0, (107, 69): 0, (108, 1): 1, (108, 2): 1, (108, 3): 1, (108, 4): 1, (108, 5): 1, (108, 6): 1, (108, 7): 1, (108, 8): 1, (108, 9): 1, (108, 10): 1, (108, 11): 1, (108, 12): 0, (108, 13): 0, (108, 14): 0, (108, 15): 0, (108, 16): 0, (108, 17): 0, (108, 18): 0, (108, 19): 0, (108, 20): 0, (108, 21): 0, (108, 22): 0, (108, 23): 0, (108, 24): 0, (108, 25): 0, (108, 26): 0, (108, 27): 0, (108, 28): 0, (108, 29): 0, (108, 30): 0, (108, 31): 0, (108, 32): 0, (108, 33): 0, (108, 34): 0, (108, 35): 0, (108, 36): 0, (108, 37): 0, (108, 38): 0, (108, 39): 0, (108, 40): 0, (108, 41): 0, (108, 42): 0, (108, 43): 0, (108, 44): 0, (108, 45): 0, (108, 46): 0, (108, 47): 0, (108, 48): 0, (108, 49): 0, (108, 50): 0, (108, 51): 0, (108, 52): 0, (108, 53): 0, (108, 54): 0, (108, 55): 0, (108, 56): 0, (108, 57): 0, (108, 58): 0, (108, 59): 0, (108, 60): 0, (108, 61): 0, (108, 62): 0, (108, 63): 0, (108, 64): 0, (108, 65): 0, (108, 66): 0, (108, 67): 0, (108, 68): 0, (108, 69): 0, (109, 1): 0, (109, 2): 0, (109, 3): 0, (109, 4): 0, (109, 5): 0, (109, 6): 0, (109, 7): 0, (109, 8): 0, (109, 9): 0, (109, 10): 0, (109, 11): 0, (109, 12): 0, (109, 13): 0, (109, 14): 0, (109, 15): 0, (109, 16): 0, (109, 17): 0, (109, 18): 0, (109, 19): 0, (109, 20): 0, (109, 21): 0, (109, 22): 0, (109, 23): 0, (109, 24): 0, (109, 25): 1, (109, 26): 1, (109, 27): 1, (109, 28): 1, (109, 29): 1, (109, 30): 0, (109, 31): 0, (109, 32): 0, (109, 33): 0, (109, 34): 0, (109, 35): 0, (109, 36): 0, (109, 37): 0, (109, 38): 0, (109, 39): 0, (109, 40): 0, (109, 41): 0, (109, 42): 0, (109, 43): 0, (109, 44): 0, (109, 45): 0, (109, 46): 0, (109, 47): 0, (109, 48): 0, (109, 49): 0, (109, 50): 0, (109, 51): 0, (109, 52): 0, (109, 53): 0, (109, 54): 0, (109, 55): 0, (109, 56): 0, (109, 57): 0, (109, 58): 0, (109, 59): 0, (109, 60): 0, (109, 61): 0, (109, 62): 0, (109, 63): 0, (109, 64): 0, (109, 65): 0, (109, 66): 0, (109, 67): 0, (109, 68): 0, (109, 69): 0, (110, 1): 0, (110, 2): 0, (110, 3): 0, (110, 4): 0, (110, 5): 0, (110, 6): 0, (110, 7): 0, (110, 8): 0, (110, 9): 0, (110, 10): 0, (110, 11): 0, (110, 12): 0, (110, 13): 0, (110, 14): 0, (110, 15): 0, (110, 16): 0, (110, 17): 0, (110, 18): 0, (110, 19): 0, (110, 20): 0, (110, 21): 0, (110, 22): 0, (110, 23): 0, (110, 24): 0, (110, 25): 1, (110, 26): 1, (110, 27): 1, (110, 28): 1, (110, 29): 1, (110, 30): 1, (110, 31): 1, (110, 32): 1, (110, 33): 1, (110, 34): 0, (110, 35): 0, (110, 36): 0, (110, 37): 0, (110, 38): 0, (110, 39): 0, (110, 40): 0, (110, 41): 0, (110, 42): 0, (110, 43): 0, (110, 44): 0, (110, 45): 0, (110, 46): 0, (110, 47): 0, (110, 48): 0, (110, 49): 0, (110, 50): 0, (110, 51): 0, (110, 52): 0, (110, 53): 0, (110, 54): 0, (110, 55): 0, (110, 56): 0, (110, 57): 0, (110, 58): 0, (110, 59): 0, (110, 60): 0, (110, 61): 0, (110, 62): 0, (110, 63): 0, (110, 64): 0, (110, 65): 0, (110, 66): 0, (110, 67): 0, (110, 68): 0, (110, 69): 0, (112, 1): 0, (112, 2): 0, (112, 3): 0, (112, 4): 0, (112, 5): 0, (112, 6): 0, (112, 7): 0, (112, 8): 0, (112, 9): 0, (112, 10): 0, (112, 11): 0, (112, 12): 0, (112, 13): 0, (112, 14): 1, (112, 15): 1, (112, 16): 1, (112, 17): 1, (112, 18): 1, (112, 19): 1, (112, 20): 0, (112, 21): 0, (112, 22): 0, (112, 23): 0, (112, 24): 0, (112, 25): 0, (112, 26): 0, (112, 27): 0, (112, 28): 0, (112, 29): 0, (112, 30): 0, (112, 31): 0, (112, 32): 0, (112, 33): 0, (112, 34): 0, (112, 35): 0, (112, 36): 0, (112, 37): 0, (112, 38): 0, (112, 39): 0, (112, 40): 0, (112, 41): 0, (112, 42): 0, (112, 43): 0, (112, 44): 0, (112, 45): 0, (112, 46): 0, (112, 47): 0, (112, 48): 0, (112, 49): 0, (112, 50): 0, (112, 51): 0, (112, 52): 0, (112, 53): 0, (112, 54): 0, (112, 55): 0, (112, 56): 0, (112, 57): 0, (112, 58): 0, (112, 59): 0, (112, 60): 0, (112, 61): 0, (112, 62): 0, (112, 63): 0, (112, 64): 0, (112, 65): 0, (112, 66): 0, (112, 67): 0, (112, 68): 0, (112, 69): 0, (117, 1): 0, (117, 2): 0, (117, 3): 0, (117, 4): 0, (117, 5): 0, (117, 6): 0, (117, 7): 0, (117, 8): 0, (117, 9): 0, (117, 10): 0, (117, 11): 0, (117, 12): 0, (117, 13): 0, (117, 14): 0, (117, 15): 0, (117, 16): 0, (117, 17): 0, (117, 18): 0, (117, 19): 0, (117, 20): 0, (117, 21): 0, (117, 22): 0, (117, 23): 0, (117, 24): 0, (117, 25): 0, (117, 26): 1, (117, 27): 1, (117, 28): 1, (117, 29): 1, (117, 30): 1, (117, 31): 1, (117, 32): 1, (117, 33): 1, (117, 34): 0, (117, 35): 0, (117, 36): 0, (117, 37): 0, (117, 38): 0, (117, 39): 0, (117, 40): 0, (117, 41): 0, (117, 42): 0, (117, 43): 0, (117, 44): 0, (117, 45): 0, (117, 46): 0, (117, 47): 0, (117, 48): 0, (117, 49): 0, (117, 50): 0, (117, 51): 0, (117, 52): 0, (117, 53): 0, (117, 54): 0, (117, 55): 0, (117, 56): 0, (117, 57): 0, (117, 58): 0, (117, 59): 0, (117, 60): 0, (117, 61): 0, (117, 62): 0, (117, 63): 0, (117, 64): 0, (117, 65): 0, (117, 66): 0, (117, 67): 0, (117, 68): 0, (117, 69): 0, (120, 1): 0, (120, 2): 0, (120, 3): 0, (120, 4): 0, (120, 5): 0, (120, 6): 0, (120, 7): 0, (120, 8): 0, (120, 9): 0, (120, 10): 0, (120, 11): 0, (120, 12): 0, (120, 13): 0, (120, 14): 0, (120, 15): 0, (120, 16): 0, (120, 17): 1, (120, 18): 1, (120, 19): 1, (120, 20): 1, (120, 21): 1, (120, 22): 0, (120, 23): 0, (120, 24): 0, (120, 25): 0, (120, 26): 0, (120, 27): 0, (120, 28): 0, (120, 29): 0, (120, 30): 0, (120, 31): 0, (120, 32): 0, (120, 33): 0, (120, 34): 0, (120, 35): 0, (120, 36): 0, (120, 37): 0, (120, 38): 0, (120, 39): 0, (120, 40): 0, (120, 41): 0, (120, 42): 0, (120, 43): 0</t>
+  </si>
+  <si>
+    <t>{(1, 1): 0, (1, 2): 0, (1, 3): 0, (1, 4): 0, (1, 5): 0, (1, 6): 0, (1, 7): 0, (1, 8): 0, (1, 9): 0, (1, 10): 0, (1, 11): 0, (1, 12): 0, (1, 13): 0, (1, 14): 0, (1, 15): 0, (1, 16): 0, (1, 17): 0, (1, 18): 0, (1, 19): 0, (1, 20): 0, (1, 21): 0, (1, 22): 0, (1, 23): 0, (1, 24): 0, (1, 25): 0, (1, 26): 0, (1, 27): 0, (1, 28): 0, (1, 29): 0, (1, 30): 0, (1, 31): 0, (1, 32): 0, (1, 33): 0, (1, 34): 0, (1, 35): 0, (1, 36): 0, (1, 37): 0, (1, 38): 0, (1, 39): 0, (1, 40): 0, (1, 41): 0, (1, 42): 0, (1, 43): 0, (1, 44): 0, (1, 45): 0, (1, 46): 0, (1, 47): 0, (1, 48): 0, (1, 49): 0, (1, 50): 0, (1, 51): 0, (1, 52): 0, (1, 53): 0, (1, 54): 0, (1, 55): 0, (1, 56): 0, (1, 57): 0, (1, 58): 0, (1, 59): 0, (1, 60): 0, (1, 61): 0, (1, 62): 0, (1, 63): 0, (1, 64): 0, (1, 65): 0, (1, 66): 0, (1, 67): 0, (1, 68): 0, (1, 69): 0, (2, 1): 0, (2, 2): 0, (2, 3): 0, (2, 4): 0, (2, 5): 0, (2, 6): 0, (2, 7): 0, (2, 8): 0, (2, 9): 0, (2, 10): 0, (2, 11): 0, (2, 12): 0, (2, 13): 0, (2, 14): 0, (2, 15): 0, (2, 16): 0, (2, 17): 0, (2, 18): 0, (2, 19): 0, (2, 20): 0, (2, 21): 0, (2, 22): 0, (2, 23): 0, (2, 24): 0, (2, 25): 0, (2, 26): 0, (2, 27): 0, (2, 28): 0, (2, 29): 0, (2, 30): 0, (2, 31): 0, (2, 32): 0, (2, 33): 0, (2, 34): 0, (2, 35): 0, (2, 36): 0, (2, 37): 0, (2, 38): 0, (2, 39): 0, (2, 40): 0, (2, 41): 0, (2, 42): 0, (2, 43): 0, (2, 44): 0, (2, 45): 0, (2, 46): 0, (2, 47): 0, (2, 48): 0, (2, 49): 0, (2, 50): 0, (2, 51): 0, (2, 52): 0, (2, 53): 0, (2, 54): 0, (2, 55): 0, (2, 56): 0, (2, 57): 0, (2, 58): 0, (2, 59): 0, (2, 60): 0, (2, 61): 0, (2, 62): 0, (2, 63): 0, (2, 64): 0, (2, 65): 0, (2, 66): 0, (2, 67): 0, (2, 68): 0, (2, 69): 0, (6, 1): 0, (6, 2): 0, (6, 3): 0, (6, 4): 0, (6, 5): 0, (6, 6): 0, (6, 7): 0, (6, 8): 0, (6, 9): 0, (6, 10): 0, (6, 11): 0, (6, 12): 0, (6, 13): 0, (6, 14): 0, (6, 15): 0, (6, 16): 0, (6, 17): 0, (6, 18): 0, (6, 19): 0, (6, 20): 0, (6, 21): 0, (6, 22): 0, (6, 23): 0, (6, 24): 0, (6, 25): 0, (6, 26): 0, (6, 27): 0, (6, 28): 0, (6, 29): 0, (6, 30): 0, (6, 31): 0, (6, 32): 0, (6, 33): 0, (6, 34): 0, (6, 35): 0, (6, 36): 0, (6, 37): 0, (6, 38): 0, (6, 39): 0, (6, 40): 0, (6, 41): 0, (6, 42): 0, (6, 43): 0, (6, 44): 0, (6, 45): 0, (6, 46): 0, (6, 47): 0, (6, 48): 0, (6, 49): 0, (6, 50): 0, (6, 51): 0, (6, 52): 0, (6, 53): 0, (6, 54): 0, (6, 55): 0, (6, 56): 0, (6, 57): 0, (6, 58): 0, (6, 59): 0, (6, 60): 0, (6, 61): 0, (6, 62): 0, (6, 63): 0, (6, 64): 0, (6, 65): 0, (6, 66): 0, (6, 67): 0, (6, 68): 0, (6, 69): 0, (7, 1): 0, (7, 2): 0, (7, 3): 0, (7, 4): 0, (7, 5): 0, (7, 6): 0, (7, 7): 0, (7, 8): 0, (7, 9): 0, (7, 10): 0, (7, 11): 0, (7, 12): 0, (7, 13): 0, (7, 14): 0, (7, 15): 0, (7, 16): 0, (7, 17): 0, (7, 18): 0, (7, 19): 0, (7, 20): 0, (7, 21): 0, (7, 22): 0, (7, 23): 0, (7, 24): 0, (7, 25): 0, (7, 26): 0, (7, 27): 0, (7, 28): 0, (7, 29): 0, (7, 30): 0, (7, 31): 0, (7, 32): 0, (7, 33): 0, (7, 34): 0, (7, 35): 0, (7, 36): 0, (7, 37): 0, (7, 38): 0, (7, 39): 0, (7, 40): 0, (7, 41): 0, (7, 42): 0, (7, 43): 0, (7, 44): 0, (7, 45): 0, (7, 46): 0, (7, 47): 0, (7, 48): 0, (7, 49): 0, (7, 50): 0, (7, 51): 0, (7, 52): 0, (7, 53): 0, (7, 54): 0, (7, 55): 0, (7, 56): 0, (7, 57): 0, (7, 58): 0, (7, 59): 0, (7, 60): 0, (7, 61): 0, (7, 62): 0, (7, 63): 0, (7, 64): 0, (7, 65): 0, (7, 66): 0, (7, 67): 0, (7, 68): 0, (7, 69): 0, (16, 1): 0, (16, 2): 0, (16, 3): 0, (16, 4): 0, (16, 5): 0, (16, 6): 0, (16, 7): 0, (16, 8): 0, (16, 9): 0, (16, 10): 0, (16, 11): 0, (16, 12): 0, (16, 13): 0, (16, 14): 0, (16, 15): 0, (16, 16): 0, (16, 17): 0, (16, 18): 0, (16, 19): 0, (16, 20): 0, (16, 21): 0, (16, 22): 0, (16, 23): 0, (16, 24): 0, (16, 25): 0, (16, 26): 0, (16, 27): 0, (16, 28): 0, (16, 29): 0, (16, 30): 0, (16, 31): 0, (16, 32): 0, (16, 33): 0, (16, 34): 0, (16, 35): 0, (16, 36): 0, (16, 37): 0, (16, 38): 0, (16, 39): 0, (16, 40): 0, (16, 41): 0, (16, 42): 0, (16, 43): 0, (16, 44): 0, (16, 45): 0, (16, 46): 0, (16, 47): 0, (16, 48): 0, (16, 49): 0, (16, 50): 0, (16, 51): 0, (16, 52): 0, (16, 53): 0, (16, 54): 0, (16, 55): 0, (16, 56): 0, (16, 57): 0, (16, 58): 0, (16, 59): 0, (16, 60): 0, (16, 61): 0, (16, 62): 0, (16, 63): 0, (16, 64): 0, (16, 65): 0, (16, 66): 0, (16, 67): 0, (16, 68): 0, (16, 69): 0, (26, 1): 0, (26, 2): 0, (26, 3): 0, (26, 4): 0, (26, 5): 0, (26, 6): 0, (26, 7): 0, (26, 8): 0, (26, 9): 0, (26, 10): 0, (26, 11): 0, (26, 12): 0, (26, 13): 0, (26, 14): 0, (26, 15): 0, (26, 16): 0, (26, 17): 0, (26, 18): 0, (26, 19): 0, (26, 20): 0, (26, 21): 0, (26, 22): 0, (26, 23): 0, (26, 24): 0, (26, 25): 0, (26, 26): 0, (26, 27): 0, (26, 28): 0, (26, 29): 0, (26, 30): 0, (26, 31): 0, (26, 32): 0, (26, 33): 0, (26, 34): 0, (26, 35): 0, (26, 36): 0, (26, 37): 0, (26, 38): 0, (26, 39): 0, (26, 40): 0, (26, 41): 0, (26, 42): 0, (26, 43): 0, (26, 44): 0, (26, 45): 0, (26, 46): 0, (26, 47): 0, (26, 48): 0, (26, 49): 0, (26, 50): 0, (26, 51): 0, (26, 52): 0, (26, 53): 0, (26, 54): 0, (26, 55): 0, (26, 56): 0, (26, 57): 0, (26, 58): 0, (26, 59): 0, (26, 60): 0, (26, 61): 0, (26, 62): 0, (26, 63): 0, (26, 64): 0, (26, 65): 0, (26, 66): 0, (26, 67): 0, (26, 68): 0, (26, 69): 0, (35, 1): 0, (35, 2): 0, (35, 3): 0, (35, 4): 0, (35, 5): 0, (35, 6): 0, (35, 7): 0, (35, 8): 0, (35, 9): 0, (35, 10): 0, (35, 11): 0, (35, 12): 0, (35, 13): 0, (35, 14): 0, (35, 15): 0, (35, 16): 0, (35, 17): 0, (35, 18): 0, (35, 19): 0, (35, 20): 0, (35, 21): 0, (35, 22): 0, (35, 23): 0, (35, 24): 0, (35, 25): 0, (35, 26): 0, (35, 27): 0, (35, 28): 0, (35, 29): 0, (35, 30): 0, (35, 31): 0, (35, 32): 0, (35, 33): 0, (35, 34): 0, (35, 35): 0, (35, 36): 0, (35, 37): 0, (35, 38): 0, (35, 39): 0, (35, 40): 0, (35, 41): 0, (35, 42): 0, (35, 43): 0, (35, 44): 0, (35, 45): 0, (35, 46): 0, (35, 47): 0, (35, 48): 0, (35, 49): 0, (35, 50): 0, (35, 51): 0, (35, 52): 0, (35, 53): 0, (35, 54): 0, (35, 55): 0, (35, 56): 0, (35, 57): 0, (35, 58): 0, (35, 59): 0, (35, 60): 0, (35, 61): 0, (35, 62): 0, (35, 63): 0, (35, 64): 0, (35, 65): 0, (35, 66): 0, (35, 67): 0, (35, 68): 0, (35, 69): 0, (38, 1): 0, (38, 2): 0, (38, 3): 0, (38, 4): 0, (38, 5): 0, (38, 6): 0, (38, 7): 0, (38, 8): 0, (38, 9): 0, (38, 10): 0, (38, 11): 0, (38, 12): 0, (38, 13): 0, (38, 14): 0, (38, 15): 0, (38, 16): 0, (38, 17): 0, (38, 18): 0, (38, 19): 0, (38, 20): 0, (38, 21): 0, (38, 22): 0, (38, 23): 0, (38, 24): 0, (38, 25): 0, (38, 26): 0, (38, 27): 0, (38, 28): 0, (38, 29): 0, (38, 30): 0, (38, 31): 0, (38, 32): 0, (38, 33): 0, (38, 34): 0, (38, 35): 0, (38, 36): 0, (38, 37): 0, (38, 38): 0, (38, 39): 0, (38, 40): 0, (38, 41): 0, (38, 42): 0, (38, 43): 0, (38, 44): 0, (38, 45): 0, (38, 46): 0, (38, 47): 0, (38, 48): 0, (38, 49): 0, (38, 50): 0, (38, 51): 0, (38, 52): 0, (38, 53): 0, (38, 54): 0, (38, 55): 0, (38, 56): 0, (38, 57): 0, (38, 58): 0, (38, 59): 0, (38, 60): 0, (38, 61): 0, (38, 62): 0, (38, 63): 0, (38, 64): 0, (38, 65): 0, (38, 66): 0, (38, 67): 0, (38, 68): 0, (38, 69): 0, (39, 1): 0, (39, 2): 0, (39, 3): 0, (39, 4): 0, (39, 5): 0, (39, 6): 0, (39, 7): 0, (39, 8): 0, (39, 9): 0, (39, 10): 0, (39, 11): 0, (39, 12): 0, (39, 13): 0, (39, 14): 0, (39, 15): 0, (39, 16): 0, (39, 17): 0, (39, 18): 0, (39, 19): 0, (39, 20): 0, (39, 21): 0, (39, 22): 0, (39, 23): 0, (39, 24): 0, (39, 25): 0, (39, 26): 0, (39, 27): 0, (39, 28): 0, (39, 29): 0, (39, 30): 0, (39, 31): 0, (39, 32): 0, (39, 33): 0, (39, 34): 0, (39, 35): 0, (39, 36): 0, (39, 37): 0, (39, 38): 0, (39, 39): 0, (39, 40): 0, (39, 41): 0, (39, 42): 0, (39, 43): 0, (39, 44): 0, (39, 45): 0, (39, 46): 0, (39, 47): 0, (39, 48): 0, (39, 49): 0, (39, 50): 0, (39, 51): 0, (39, 52): 0, (39, 53): 0, (39, 54): 0, (39, 55): 0, (39, 56): 0, (39, 57): 0, (39, 58): 0, (39, 59): 0, (39, 60): 0, (39, 61): 0, (39, 62): 0, (39, 63): 0, (39, 64): 0, (39, 65): 0, (39, 66): 0, (39, 67): 0, (39, 68): 0, (39, 69): 0, (41, 1): 0, (41, 2): 0, (41, 3): 0, (41, 4): 0, (41, 5): 0, (41, 6): 0, (41, 7): 0, (41, 8): 0, (41, 9): 0, (41, 10): 0, (41, 11): 0, (41, 12): 0, (41, 13): 0, (41, 14): 0, (41, 15): 0, (41, 16): 0, (41, 17): 0, (41, 18): 0, (41, 19): 0, (41, 20): 0, (41, 21): 0, (41, 22): 0, (41, 23): 0, (41, 24): 0, (41, 25): 0, (41, 26): 0, (41, 27): 0, (41, 28): 0, (41, 29): 0, (41, 30): 0, (41, 31): 0, (41, 32): 0, (41, 33): 0, (41, 34): 0, (41, 35): 0, (41, 36): 0, (41, 37): 0, (41, 38): 0, (41, 39): 0, (41, 40): 0, (41, 41): 0, (41, 42): 0, (41, 43): 0, (41, 44): 0, (41, 45): 0, (41, 46): 0, (41, 47): 0, (41, 48): 0, (41, 49): 0, (41, 50): 0, (41, 51): 0, (41, 52): 0, (41, 53): 0, (41, 54): 0, (41, 55): 0, (41, 56): 0, (41, 57): 0, (41, 58): 0, (41, 59): 0, (41, 60): 0, (41, 61): 0, (41, 62): 0, (41, 63): 0, (41, 64): 0, (41, 65): 0, (41, 66): 0, (41, 67): 0, (41, 68): 0, (41, 69): 0, (42, 1): 0, (42, 2): 0, (42, 3): 0, (42, 4): 0, (42, 5): 0, (42, 6): 0, (42, 7): 0, (42, 8): 0, (42, 9): 0, (42, 10): 0, (42, 11): 0, (42, 12): 0, (42, 13): 0, (42, 14): 0, (42, 15): 0, (42, 16): 0, (42, 17): 0, (42, 18): 0, (42, 19): 0, (42, 20): 0, (42, 21): 0, (42, 22): 0, (42, 23): 0, (42, 24): 0, (42, 25): 0, (42, 26): 0, (42, 27): 0, (42, 28): 0, (42, 29): 0, (42, 30): 0, (42, 31): 0, (42, 32): 0, (42, 33): 0, (42, 34): 0, (42, 35): 0, (42, 36): 0, (42, 37): 0, (42, 38): 0, (42, 39): 0, (42, 40): 0, (42, 41): 0, (42, 42): 0, (42, 43): 0, (42, 44): 0, (42, 45): 0, (42, 46): 0, (42, 47): 0, (42, 48): 0, (42, 49): 0, (42, 50): 0, (42, 51): 0, (42, 52): 0, (42, 53): 0, (42, 54): 0, (42, 55): 0, (42, 56): 0, (42, 57): 0, (42, 58): 0, (42, 59): 0, (42, 60): 0, (42, 61): 0, (42, 62): 0, (42, 63): 0, (42, 64): 0, (42, 65): 0, (42, 66): 0, (42, 67): 0, (42, 68): 0, (42, 69): 0, (43, 1): 0, (43, 2): 0, (43, 3): 0, (43, 4): 0, (43, 5): 0, (43, 6): 0, (43, 7): 0, (43, 8): 0, (43, 9): 0, (43, 10): 0, (43, 11): 0, (43, 12): 0, (43, 13): 0, (43, 14): 0, (43, 15): 0, (43, 16): 0, (43, 17): 0, (43, 18): 0, (43, 19): 0, (43, 20): 0, (43, 21): 0, (43, 22): 0, (43, 23): 0, (43, 24): 0, (43, 25): 0, (43, 26): 0, (43, 27): 0, (43, 28): 0, (43, 29): 0, (43, 30): 0, (43, 31): 0, (43, 32): 0, (43, 33): 0, (43, 34): 0, (43, 35): 0, (43, 36): 0, (43, 37): 0, (43, 38): 0, (43, 39): 0, (43, 40): 0, (43, 41): 0, (43, 42): 0, (43, 43): 0, (43, 44): 0, (43, 45): 0, (43, 46): 0, (43, 47): 0, (43, 48): 0, (43, 49): 0, (43, 50): 0, (43, 51): 0, (43, 52): 0, (43, 53): 0, (43, 54): 0, (43, 55): 0, (43, 56): 0, (43, 57): 0, (43, 58): 0, (43, 59): 0, (43, 60): 0, (43, 61): 0, (43, 62): 0, (43, 63): 0, (43, 64): 0, (43, 65): 0, (43, 66): 0, (43, 67): 0, (43, 68): 0, (43, 69): 0, (46, 1): 0, (46, 2): 0, (46, 3): 0, (46, 4): 0, (46, 5): 0, (46, 6): 0, (46, 7): 0, (46, 8): 0, (46, 9): 0, (46, 10): 0, (46, 11): 0, (46, 12): 0, (46, 13): 0, (46, 14): 0, (46, 15): 0, (46, 16): 0, (46, 17): 0, (46, 18): 0, (46, 19): 0, (46, 20): 0, (46, 21): 0, (46, 22): 0, (46, 23): 0, (46, 24): 0, (46, 25): 0, (46, 26): 0, (46, 27): 0, (46, 28): 0, (46, 29): 0, (46, 30): 0, (46, 31): 0, (46, 32): 0, (46, 33): 0, (46, 34): 0, (46, 35): 0, (46, 36): 0, (46, 37): 0, (46, 38): 0, (46, 39): 0, (46, 40): 0, (46, 41): 0, (46, 42): 0, (46, 43): 0, (46, 44): 0, (46, 45): 0, (46, 46): 0, (46, 47): 0, (46, 48): 0, (46, 49): 0, (46, 50): 0, (46, 51): 0, (46, 52): 0, (46, 53): 0, (46, 54): 0, (46, 55): 0, (46, 56): 0, (46, 57): 0, (46, 58): 0, (46, 59): 0, (46, 60): 0, (46, 61): 0, (46, 62): 0, (46, 63): 0, (46, 64): 0, (46, 65): 0, (46, 66): 0, (46, 67): 0, (46, 68): 0, (46, 69): 0, (48, 1): 0, (48, 2): 0, (48, 3): 0, (48, 4): 0, (48, 5): 0, (48, 6): 0, (48, 7): 0, (48, 8): 0, (48, 9): 0, (48, 10): 0, (48, 11): 0, (48, 12): 0, (48, 13): 0, (48, 14): 0, (48, 15): 0, (48, 16): 0, (48, 17): 0, (48, 18): 0, (48, 19): 0, (48, 20): 0, (48, 21): 0, (48, 22): 0, (48, 23): 0, (48, 24): 0, (48, 25): 0, (48, 26): 0, (48, 27): 0, (48, 28): 0, (48, 29): 0, (48, 30): 0, (48, 31): 0, (48, 32): 0, (48, 33): 0, (48, 34): 0, (48, 35): 0, (48, 36): 0, (48, 37): 0, (48, 38): 0, (48, 39): 0, (48, 40): 0, (48, 41): 0, (48, 42): 0, (48, 43): 0, (48, 44): 0, (48, 45): 0, (48, 46): 0, (48, 47): 0, (48, 48): 0, (48, 49): 0, (48, 50): 0, (48, 51): 0, (48, 52): 0, (48, 53): 0, (48, 54): 0, (48, 55): 0, (48, 56): 0, (48, 57): 0, (48, 58): 0, (48, 59): 0, (48, 60): 0, (48, 61): 0, (48, 62): 0, (48, 63): 0, (48, 64): 0, (48, 65): 0, (48, 66): 0, (48, 67): 0, (48, 68): 0, (48, 69): 0, (49, 1): 0, (49, 2): 0, (49, 3): 0, (49, 4): 0, (49, 5): 0, (49, 6): 0, (49, 7): 0, (49, 8): 0, (49, 9): 0, (49, 10): 0, (49, 11): 0, (49, 12): 0, (49, 13): 0, (49, 14): 1, (49, 15): 1, (49, 16): 1, (49, 17): 1, (49, 18): 1, (49, 19): 1, (49, 20): 1, (49, 21): 1, (49, 22): 1, (49, 23): 1, (49, 24): 1, (49, 25): 1, (49, 26): 1, (49, 27): 1, (49, 28): 1, (49, 29): 1, (49, 30): 1, (49, 31): 1, (49, 32): 1, (49, 33): 1, (49, 34): 1, (49, 35): 1, (49, 36): 1, (49, 37): 1, (49, 38): 1, (49, 39): 1, (49, 40): 1, (49, 41): 1, (49, 42): 1, (49, 43): 1, (49, 44): 1, (49, 45): 1, (49, 46): 1, (49, 47): 1, (49, 48): 1, (49, 49): 1, (49, 50): 1, (49, 51): 1, (49, 52): 1, (49, 53): 1, (49, 54): 1, (49, 55): 1, (49, 56): 1, (49, 57): 1, (49, 58): 1, (49, 59): 1, (49, 60): 1, (49, 61): 1, (49, 62): 1, (49, 63): 1, (49, 64): 1, (49, 65): 1, (49, 66): 1, (49, 67): 1, (49, 68): 1, (49, 69): 1, (51, 1): 0, (51, 2): 0, (51, 3): 0, (51, 4): 0, (51, 5): 0, (51, 6): 0, (51, 7): 0, (51, 8): 0, (51, 9): 0, (51, 10): 0, (51, 11): 0, (51, 12): 0, (51, 13): 0, (51, 14): 0, (51, 15): 0, (51, 16): 0, (51, 17): 1, (51, 18): 1, (51, 19): 1, (51, 20): 1, (51, 21): 1, (51, 22): 1, (51, 23): 1, (51, 24): 1, (51, 25): 1, (51, 26): 1, (51, 27): 1, (51, 28): 1, (51, 29): 1, (51, 30): 1, (51, 31): 1, (51, 32): 1, (51, 33): 1, (51, 34): 1, (51, 35): 1, (51, 36): 1, (51, 37): 1, (51, 38): 1, (51, 39): 1, (51, 40): 1, (51, 41): 1, (51, 42): 1, (51, 43): 1, (51, 44): 1, (51, 45): 1, (51, 46): 1, (51, 47): 1, (51, 48): 1, (51, 49): 1, (51, 50): 1, (51, 51): 1, (51, 52): 1, (51, 53): 1, (51, 54): 1, (51, 55): 1, (51, 56): 1, (51, 57): 1, (51, 58): 1, (51, 59): 1, (51, 60): 1, (51, 61): 1, (51, 62): 1, (51, 63): 1, (51, 64): 1, (51, 65): 1, (51, 66): 1, (51, 67): 1, (51, 68): 1, (51, 69): 1, (52, 1): 0, (52, 2): 0, (52, 3): 0, (52, 4): 0, (52, 5): 0, (52, 6): 0, (52, 7): 0, (52, 8): 0, (52, 9): 0, (52, 10): 0, (52, 11): 0, (52, 12): 0, (52, 13): 0, (52, 14): 0, (52, 15): 0, (52, 16): 0, (52, 17): 0, (52, 18): 0, (52, 19): 0, (52, 20): 0, (52, 21): 0, (52, 22): 0, (52, 23): 0, (52, 24): 0, (52, 25): 0, (52, 26): 0, (52, 27): 0, (52, 28): 0, (52, 29): 0, (52, 30): 0, (52, 31): 0, (52, 32): 0, (52, 33): 0, (52, 34): 0, (52, 35): 0, (52, 36): 0, (52, 37): 0, (52, 38): 0, (52, 39): 0, (52, 40): 0, (52, 41): 0, (52, 42): 0, (52, 43): 0, (52, 44): 0, (52, 45): 0, (52, 46): 0, (52, 47): 0, (52, 48): 0, (52, 49): 0, (52, 50): 0, (52, 51): 0, (52, 52): 0, (52, 53): 0, (52, 54): 0, (52, 55): 0, (52, 56): 0, (52, 57): 0, (52, 58): 0, (52, 59): 0, (52, 60): 0, (52, 61): 0, (52, 62): 0, (52, 63): 0, (52, 64): 0, (52, 65): 0, (52, 66): 0, (52, 67): 0, (52, 68): 0, (52, 69): 0, (57, 1): 0, (57, 2): 0, (57, 3): 0, (57, 4): 0, (57, 5): 0, (57, 6): 0, (57, 7): 0, (57, 8): 0, (57, 9): 0, (57, 10): 0, (57, 11): 0, (57, 12): 0, (57, 13): 0, (57, 14): 0, (57, 15): 0, (57, 16): 0, (57, 17): 0, (57, 18): 0, (57, 19): 0, (57, 20): 0, (57, 21): 0, (57, 22): 0, (57, 23): 0, (57, 24): 0, (57, 25): 0, (57, 26): 0, (57, 27): 0, (57, 28): 0, (57, 29): 0, (57, 30): 0, (57, 31): 0, (57, 32): 0, (57, 33): 0, (57, 34): 0, (57, 35): 0, (57, 36): 0, (57, 37): 0, (57, 38): 0, (57, 39): 0, (57, 40): 0, (57, 41): 0, (57, 42): 0, (57, 43): 0, (57, 44): 0, (57, 45): 0, (57, 46): 0, (57, 47): 0, (57, 48): 0, (57, 49): 0, (57, 50): 0, (57, 51): 0, (57, 52): 0, (57, 53): 0, (57, 54): 0, (57, 55): 0, (57, 56): 0, (57, 57): 0, (57, 58): 0, (57, 59): 0, (57, 60): 0, (57, 61): 0, (57, 62): 0, (57, 63): 0, (57, 64): 0, (57, 65): 0, (57, 66): 0, (57, 67): 0, (57, 68): 0, (57, 69): 0, (70, 1): 0, (70, 2): 0, (70, 3): 0, (70, 4): 0, (70, 5): 0, (70, 6): 0, (70, 7): 0, (70, 8): 0, (70, 9): 0, (70, 10): 0, (70, 11): 0, (70, 12): 0, (70, 13): 0, (70, 14): 0, (70, 15): 0, (70, 16): 0, (70, 17): 0, (70, 18): 0, (70, 19): 0, (70, 20): 0, (70, 21): 0, (70, 22): 0, (70, 23): 0, (70, 24): 0, (70, 25): 0, (70, 26): 0, (70, 27): 0, (70, 28): 0, (70, 29): 0, (70, 30): 0, (70, 31): 0, (70, 32): 0, (70, 33): 0, (70, 34): 0, (70, 35): 0, (70, 36): 0, (70, 37): 0, (70, 38): 0, (70, 39): 0, (70, 40): 0, (70, 41): 0, (70, 42): 0, (70, 43): 0, (70, 44): 0, (70, 45): 0, (70, 46): 0, (70, 47): 0, (70, 48): 0, (70, 49): 0, (70, 50): 0, (70, 51): 0, (70, 52): 0, (70, 53): 0, (70, 54): 0, (70, 55): 0, (70, 56): 0, (70, 57): 0, (70, 58): 0, (70, 59): 0, (70, 60): 0, (70, 61): 0, (70, 62): 0, (70, 63): 0, (70, 64): 0, (70, 65): 0, (70, 66): 0, (70, 67): 0, (70, 68): 0, (70, 69): 0, (73, 1): 0, (73, 2): 0, (73, 3): 0, (73, 4): 0, (73, 5): 0, (73, 6): 0, (73, 7): 0, (73, 8): 0, (73, 9): 0, (73, 10): 0, (73, 11): 0, (73, 12): 0, (73, 13): 0, (73, 14): 0, (73, 15): 0, (73, 16): 0, (73, 17): 0, (73, 18): 0, (73, 19): 0, (73, 20): 0, (73, 21): 0, (73, 22): 0, (73, 23): 0, (73, 24): 0, (73, 25): 0, (73, 26): 0, (73, 27): 0, (73, 28): 0, (73, 29): 0, (73, 30): 0, (73, 31): 0, (73, 32): 0, (73, 33): 0, (73, 34): 0, (73, 35): 0, (73, 36): 0, (73, 37): 0, (73, 38): 0, (73, 39): 0, (73, 40): 0, (73, 41): 0, (73, 42): 0, (73, 43): 0, (73, 44): 0, (73, 45): 0, (73, 46): 0, (73, 47): 0, (73, 48): 0, (73, 49): 0, (73, 50): 0, (73, 51): 0, (73, 52): 0, (73, 53): 0, (73, 54): 0, (73, 55): 0, (73, 56): 0, (73, 57): 0, (73, 58): 0, (73, 59): 0, (73, 60): 0, (73, 61): 0, (73, 62): 0, (73, 63): 0, (73, 64): 0, (73, 65): 0, (73, 66): 0, (73, 67): 0, (73, 68): 0, (73, 69): 0, (75, 1): 0, (75, 2): 0, (75, 3): 0, (75, 4): 0, (75, 5): 0, (75, 6): 0, (75, 7): 0, (75, 8): 0, (75, 9): 0, (75, 10): 0, (75, 11): 0, (75, 12): 0, (75, 13): 0, (75, 14): 1, (75, 15): 1, (75, 16): 1, (75, 17): 1, (75, 18): 1, (75, 19): 1, (75, 20): 1, (75, 21): 1, (75, 22): 1, (75, 23): 1, (75, 24): 1, (75, 25): 1, (75, 26): 1, (75, 27): 1, (75, 28): 1, (75, 29): 1, (75, 30): 1, (75, 31): 1, (75, 32): 1, (75, 33): 1, (75, 34): 1, (75, 35): 1, (75, 36): 1, (75, 37): 1, (75, 38): 1, (75, 39): 1, (75, 40): 1, (75, 41): 1, (75, 42): 1, (75, 43): 1, (75, 44): 1, (75, 45): 1, (75, 46): 1, (75, 47): 1, (75, 48): 1, (75, 49): 1, (75, 50): 1, (75, 51): 1, (75, 52): 1, (75, 53): 1, (75, 54): 1, (75, 55): 1, (75, 56): 1, (75, 57): 1, (75, 58): 1, (75, 59): 1, (75, 60): 1, (75, 61): 1, (75, 62): 1, (75, 63): 1, (75, 64): 1, (75, 65): 1, (75, 66): 1, (75, 67): 1, (75, 68): 1, (75, 69): 1, (82, 1): 0, (82, 2): 0, (82, 3): 0, (82, 4): 0, (82, 5): 0, (82, 6): 0, (82, 7): 0, (82, 8): 0, (82, 9): 0, (82, 10): 0, (82, 11): 0, (82, 12): 0, (82, 13): 0, (82, 14): 0, (82, 15): 0, (82, 16): 0, (82, 17): 0, (82, 18): 0, (82, 19): 0, (82, 20): 0, (82, 21): 0, (82, 22): 0, (82, 23): 0, (82, 24): 0, (82, 25): 0, (82, 26): 0, (82, 27): 0, (82, 28): 0, (82, 29): 0, (82, 30): 0, (82, 31): 0, (82, 32): 0, (82, 33): 0, (82, 34): 0, (82, 35): 0, (82, 36): 0, (82, 37): 0, (82, 38): 0, (82, 39): 0, (82, 40): 0, (82, 41): 0, (82, 42): 0, (82, 43): 0, (82, 44): 0, (82, 45): 0, (82, 46): 0, (82, 47): 0, (82, 48): 0, (82, 49): 0, (82, 50): 0, (82, 51): 0, (82, 52): 0, (82, 53): 0, (82, 54): 0, (82, 55): 0, (82, 56): 0, (82, 57): 0, (82, 58): 0, (82, 59): 0, (82, 60): 0, (82, 61): 0, (82, 62): 0, (82, 63): 0, (82, 64): 0, (82, 65): 0, (82, 66): 0, (82, 67): 0, (82, 68): 0, (82, 69): 0, (84, 1): 0, (84, 2): 0, (84, 3): 0, (84, 4): 0, (84, 5): 0, (84, 6): 0, (84, 7): 0, (84, 8): 0, (84, 9): 0, (84, 10): 0, (84, 11): 0, (84, 12): 0, (84, 13): 0, (84, 14): 0, (84, 15): 0, (84, 16): 0, (84, 17): 0, (84, 18): 0, (84, 19): 0, (84, 20): 0, (84, 21): 0, (84, 22): 0, (84, 23): 0, (84, 24): 0, (84, 25): 0, (84, 26): 0, (84, 27): 0, (84, 28): 0, (84, 29): 0, (84, 30): 0, (84, 31): 0, (84, 32): 0, (84, 33): 0, (84, 34): 0, (84, 35): 0, (84, 36): 0, (84, 37): 0, (84, 38): 0, (84, 39): 0, (84, 40): 0, (84, 41): 0, (84, 42): 0, (84, 43): 0, (84, 44): 0, (84, 45): 0, (84, 46): 0, (84, 47): 0, (84, 48): 0, (84, 49): 0, (84, 50): 0, (84, 51): 0, (84, 52): 0, (84, 53): 0, (84, 54): 0, (84, 55): 0, (84, 56): 0, (84, 57): 0, (84, 58): 0, (84, 59): 0, (84, 60): 0, (84, 61): 0, (84, 62): 0, (84, 63): 0, (84, 64): 0, (84, 65): 0, (84, 66): 0, (84, 67): 0, (84, 68): 0, (84, 69): 0, (86, 1): 0, (86, 2): 0, (86, 3): 0, (86, 4): 0, (86, 5): 0, (86, 6): 0, (86, 7): 0, (86, 8): 0, (86, 9): 0, (86, 10): 1, (86, 11): 1, (86, 12): 1, (86, 13): 1, (86, 14): 1, (86, 15): 1, (86, 16): 1, (86, 17): 1, (86, 18): 1, (86, 19): 1, (86, 20): 1, (86, 21): 1, (86, 22): 1, (86, 23): 1, (86, 24): 1, (86, 25): 1, (86, 26): 1, (86, 27): 1, (86, 28): 1, (86, 29): 1, (86, 30): 1, (86, 31): 1, (86, 32): 1, (86, 33): 1, (86, 34): 1, (86, 35): 1, (86, 36): 1, (86, 37): 1, (86, 38): 1, (86, 39): 1, (86, 40): 1, (86, 41): 1, (86, 42): 1, (86, 43): 1, (86, 44): 1, (86, 45): 1, (86, 46): 1, (86, 47): 1, (86, 48): 1, (86, 49): 1, (86, 50): 1, (86, 51): 1, (86, 52): 1, (86, 53): 1, (86, 54): 1, (86, 55): 1, (86, 56): 1, (86, 57): 1, (86, 58): 1, (86, 59): 1, (86, 60): 1, (86, 61): 1, (86, 62): 1, (86, 63): 1, (86, 64): 1, (86, 65): 1, (86, 66): 1, (86, 67): 1, (86, 68): 1, (86, 69): 1, (87, 1): 0, (87, 2): 0, (87, 3): 0, (87, 4): 0, (87, 5): 0, (87, 6): 0, (87, 7): 0, (87, 8): 0, (87, 9): 0, (87, 10): 0, (87, 11): 0, (87, 12): 0, (87, 13): 0, (87, 14): 0, (87, 15): 0, (87, 16): 0, (87, 17): 0, (87, 18): 0, (87, 19): 0, (87, 20): 0, (87, 21): 0, (87, 22): 0, (87, 23): 0, (87, 24): 0, (87, 25): 0, (87, 26): 0, (87, 27): 0, (87, 28): 0, (87, 29): 0, (87, 30): 0, (87, 31): 0, (87, 32): 0, (87, 33): 0, (87, 34): 0, (87, 35): 0, (87, 36): 0, (87, 37): 0, (87, 38): 0, (87, 39): 0, (87, 40): 0, (87, 41): 0, (87, 42): 0, (87, 43): 0, (87, 44): 0, (87, 45): 0, (87, 46): 0, (87, 47): 0, (87, 48): 0, (87, 49): 0, (87, 50): 0, (87, 51): 0, (87, 52): 0, (87, 53): 0, (87, 54): 0, (87, 55): 0, (87, 56): 0, (87, 57): 0, (87, 58): 0, (87, 59): 0, (87, 60): 0, (87, 61): 0, (87, 62): 0, (87, 63): 0, (87, 64): 0, (87, 65): 0, (87, 66): 0, (87, 67): 0, (87, 68): 0, (87, 69): 0, (89, 1): 0, (89, 2): 0, (89, 3): 0, (89, 4): 0, (89, 5): 0, (89, 6): 0, (89, 7): 0, (89, 8): 0, (89, 9): 0, (89, 10): 0, (89, 11): 0, (89, 12): 0, (89, 13): 0, (89, 14): 0, (89, 15): 0, (89, 16): 0, (89, 17): 0, (89, 18): 0, (89, 19): 0, (89, 20): 0, (89, 21): 0, (89, 22): 0, (89, 23): 0, (89, 24): 0, (89, 25): 0, (89, 26): 0, (89, 27): 0, (89, 28): 0, (89, 29): 0, (89, 30): 0, (89, 31): 0, (89, 32): 0, (89, 33): 0, (89, 34): 0, (89, 35): 0, (89, 36): 0, (89, 37): 0, (89, 38): 0, (89, 39): 0, (89, 40): 0, (89, 41): 0, (89, 42): 0, (89, 43): 0, (89, 44): 0, (89, 45): 0, (89, 46): 0, (89, 47): 0, (89, 48): 0, (89, 49): 0, (89, 50): 0, (89, 51): 0, (89, 52): 0, (89, 53): 0, (89, 54): 0, (89, 55): 0, (89, 56): 0, (89, 57): 0, (89, 58): 0, (89, 59): 0, (89, 60): 0, (89, 61): 0, (89, 62): 0, (89, 63): 0, (89, 64): 0, (89, 65): 0, (89, 66): 0, (89, 67): 0, (89, 68): 0, (89, 69): 0, (92, 1): 0, (92, 2): 0, (92, 3): 0, (92, 4): 0, (92, 5): 0, (92, 6): 0, (92, 7): 0, (92, 8): 0, (92, 9): 0, (92, 10): 0, (92, 11): 0, (92, 12): 0, (92, 13): 0, (92, 14): 0, (92, 15): 0, (92, 16): 0, (92, 17): 0, (92, 18): 0, (92, 19): 0, (92, 20): 0, (92, 21): 0, (92, 22): 0, (92, 23): 0, (92, 24): 0, (92, 25): 0, (92, 26): 0, (92, 27): 0, (92, 28): 0, (92, 29): 0, (92, 30): 0, (92, 31): 0, (92, 32): 0, (92, 33): 0, (92, 34): 0, (92, 35): 0, (92, 36): 0, (92, 37): 0, (92, 38): 0, (92, 39): 0, (92, 40): 0, (92, 41): 0, (92, 42): 0, (92, 43): 0, (92, 44): 0, (92, 45): 0, (92, 46): 0, (92, 47): 0, (92, 48): 0, (92, 49): 0, (92, 50): 0, (92, 51): 0, (92, 52): 0, (92, 53): 0, (92, 54): 0, (92, 55): 0, (92, 56): 0, (92, 57): 0, (92, 58): 0, (92, 59): 0, (92, 60): 0, (92, 61): 0, (92, 62): 0, (92, 63): 0, (92, 64): 0, (92, 65): 0, (92, 66): 0, (92, 67): 0, (92, 68): 0, (92, 69): 0, (96, 1): 0, (96, 2): 0, (96, 3): 0, (96, 4): 0, (96, 5): 0, (96, 6): 0, (96, 7): 0, (96, 8): 0, (96, 9): 0, (96, 10): 0, (96, 11): 0, (96, 12): 0, (96, 13): 0, (96, 14): 0, (96, 15): 0, (96, 16): 0, (96, 17): 0, (96, 18): 0, (96, 19): 0, (96, 20): 0, (96, 21): 0, (96, 22): 0, (96, 23): 0, (96, 24): 0, (96, 25): 0, (96, 26): 0, (96, 27): 0, (96, 28): 0, (96, 29): 0, (96, 30): 0, (96, 31): 0, (96, 32): 0, (96, 33): 0, (96, 34): 0, (96, 35): 0, (96, 36): 0, (96, 37): 0, (96, 38): 0, (96, 39): 0, (96, 40): 0, (96, 41): 0, (96, 42): 0, (96, 43): 0, (96, 44): 0, (96, 45): 0, (96, 46): 0, (96, 47): 0, (96, 48): 0, (96, 49): 0, (96, 50): 0, (96, 51): 0, (96, 52): 0, (96, 53): 0, (96, 54): 0, (96, 55): 0, (96, 56): 0, (96, 57): 0, (96, 58): 0, (96, 59): 0, (96, 60): 0, (96, 61): 0, (96, 62): 0, (96, 63): 0, (96, 64): 0, (96, 65): 0, (96, 66): 0, (96, 67): 0, (96, 68): 0, (96, 69): 0, (98, 1): 0, (98, 2): 0, (98, 3): 0, (98, 4): 0, (98, 5): 0, (98, 6): 0, (98, 7): 0, (98, 8): 0, (98, 9): 0, (98, 10): 0, (98, 11): 0, (98, 12): 0, (98, 13): 0, (98, 14): 0, (98, 15): 0, (98, 16): 0, (98, 17): 0, (98, 18): 0, (98, 19): 0, (98, 20): 0, (98, 21): 0, (98, 22): 0, (98, 23): 0, (98, 24): 0, (98, 25): 0, (98, 26): 0, (98, 27): 0, (98, 28): 0, (98, 29): 0, (98, 30): 0, (98, 31): 0, (98, 32): 0, (98, 33): 0, (98, 34): 0, (98, 35): 0, (98, 36): 0, (98, 37): 0, (98, 38): 0, (98, 39): 0, (98, 40): 0, (98, 41): 0, (98, 42): 0, (98, 43): 0, (98, 44): 0, (98, 45): 0, (98, 46): 0, (98, 47): 0, (98, 48): 0, (98, 49): 0, (98, 50): 0, (98, 51): 0, (98, 52): 0, (98, 53): 0, (98, 54): 0, (98, 55): 0, (98, 56): 0, (98, 57): 0, (98, 58): 0, (98, 59): 0, (98, 60): 0, (98, 61): 0, (98, 62): 0, (98, 63): 0, (98, 64): 0, (98, 65): 0, (98, 66): 0, (98, 67): 0, (98, 68): 0, (98, 69): 0, (100, 1): 0, (100, 2): 0, (100, 3): 0, (100, 4): 0, (100, 5): 0, (100, 6): 0, (100, 7): 0, (100, 8): 0, (100, 9): 0, (100, 10): 0, (100, 11): 0, (100, 12): 0, (100, 13): 0, (100, 14): 0, (100, 15): 0, (100, 16): 0, (100, 17): 0, (100, 18): 0, (100, 19): 0, (100, 20): 0, (100, 21): 0, (100, 22): 0, (100, 23): 0, (100, 24): 0, (100, 25): 0, (100, 26): 0, (100, 27): 0, (100, 28): 0, (100, 29): 0, (100, 30): 0, (100, 31): 0, (100, 32): 0, (100, 33): 0, (100, 34): 0, (100, 35): 0, (100, 36): 0, (100, 37): 0, (100, 38): 0, (100, 39): 0, (100, 40): 0, (100, 41): 0, (100, 42): 0, (100, 43): 0, (100, 44): 0, (100, 45): 0, (100, 46): 0, (100, 47): 0, (100, 48): 0, (100, 49): 0, (100, 50): 0, (100, 51): 0, (100, 52): 0, (100, 53): 0, (100, 54): 0, (100, 55): 0, (100, 56): 0, (100, 57): 0, (100, 58): 0, (100, 59): 0, (100, 60): 0, (100, 61): 0, (100, 62): 0, (100, 63): 0, (100, 64): 0, (100, 65): 0, (100, 66): 0, (100, 67): 0, (100, 68): 0, (100, 69): 0, (107, 1): 0, (107, 2): 0, (107, 3): 0, (107, 4): 0, (107, 5): 0, (107, 6): 0, (107, 7): 0, (107, 8): 0, (107, 9): 0, (107, 10): 0, (107, 11): 0, (107, 12): 0, (107, 13): 0, (107, 14): 0, (107, 15): 0, (107, 16): 0, (107, 17): 0, (107, 18): 0, (107, 19): 0, (107, 20): 0, (107, 21): 0, (107, 22): 0, (107, 23): 0, (107, 24): 0, (107, 25): 0, (107, 26): 0, (107, 27): 0, (107, 28): 0, (107, 29): 0, (107, 30): 0, (107, 31): 0, (107, 32): 0, (107, 33): 0, (107, 34): 0, (107, 35): 0, (107, 36): 0, (107, 37): 0, (107, 38): 0, (107, 39): 0, (107, 40): 0, (107, 41): 0, (107, 42): 0, (107, 43): 0, (107, 44): 0, (107, 45): 0, (107, 46): 0, (107, 47): 0, (107, 48): 0, (107, 49): 0, (107, 50): 0, (107, 51): 0, (107, 52): 0, (107, 53): 0, (107, 54): 0, (107, 55): 0, (107, 56): 0, (107, 57): 0, (107, 58): 0, (107, 59): 0, (107, 60): 0, (107, 61): 0, (107, 62): 0, (107, 63): 0, (107, 64): 0, (107, 65): 0, (107, 66): 0, (107, 67): 0, (107, 68): 0, (107, 69): 0, (108, 1): 0, (108, 2): 0, (108, 3): 0, (108, 4): 0, (108, 5): 0, (108, 6): 0, (108, 7): 0, (108, 8): 0, (108, 9): 0, (108, 10): 0, (108, 11): 0, (108, 12): 0, (108, 13): 0, (108, 14): 0, (108, 15): 0, (108, 16): 0, (108, 17): 0, (108, 18): 0, (108, 19): 0, (108, 20): 0, (108, 21): 0, (108, 22): 0, (108, 23): 0, (108, 24): 0, (108, 25): 0, (108, 26): 0, (108, 27): 0, (108, 28): 0, (108, 29): 0, (108, 30): 0, (108, 31): 0, (108, 32): 0, (108, 33): 0, (108, 34): 0, (108, 35): 0, (108, 36): 0, (108, 37): 0, (108, 38): 0, (108, 39): 0, (108, 40): 0, (108, 41): 0, (108, 42): 0, (108, 43): 0, (108, 44): 0, (108, 45): 0, (108, 46): 0, (108, 47): 0, (108, 48): 0, (108, 49): 0, (108, 50): 0, (108, 51): 0, (108, 52): 0, (108, 53): 0, (108, 54): 0, (108, 55): 0, (108, 56): 0, (108, 57): 0, (108, 58): 0, (108, 59): 0, (108, 60): 0, (108, 61): 0, (108, 62): 0, (108, 63): 0, (108, 64): 0, (108, 65): 0, (108, 66): 0, (108, 67): 0, (108, 68): 0, (108, 69): 0, (109, 1): 0, (109, 2): 0, (109, 3): 0, (109, 4): 0, (109, 5): 0, (109, 6): 0, (109, 7): 0, (109, 8): 0, (109, 9): 0, (109, 10): 0, (109, 11): 0, (109, 12): 0, (109, 13): 0, (109, 14): 0, (109, 15): 0, (109, 16): 0, (109, 17): 0, (109, 18): 0, (109, 19): 0, (109, 20): 0, (109, 21): 0, (109, 22): 0, (109, 23): 0, (109, 24): 0, (109, 25): 0, (109, 26): 0, (109, 27): 0, (109, 28): 0, (109, 29): 0, (109, 30): 0, (109, 31): 0, (109, 32): 0, (109, 33): 0, (109, 34): 0, (109, 35): 0, (109, 36): 0, (109, 37): 0, (109, 38): 0, (109, 39): 0, (109, 40): 0, (109, 41): 0, (109, 42): 0, (109, 43): 0, (109, 44): 0, (109, 45): 0, (109, 46): 0, (109, 47): 0, (109, 48): 0, (109, 49): 0, (109, 50): 0, (109, 51): 0, (109, 52): 0, (109, 53): 0, (109, 54): 0, (109, 55): 0, (109, 56): 0, (109, 57): 0, (109, 58): 0, (109, 59): 0, (109, 60): 0, (109, 61): 0, (109, 62): 0, (109, 63): 0, (109, 64): 0, (109, 65): 0, (109, 66): 0, (109, 67): 0, (109, 68): 0, (109, 69): 0, (110, 1): 0, (110, 2): 0, (110, 3): 0, (110, 4): 0, (110, 5): 0, (110, 6): 0, (110, 7): 0, (110, 8): 0, (110, 9): 0, (110, 10): 0, (110, 11): 0, (110, 12): 0, (110, 13): 0, (110, 14): 0, (110, 15): 0, (110, 16): 0, (110, 17): 0, (110, 18): 0, (110, 19): 0, (110, 20): 0, (110, 21): 0, (110, 22): 0, (110, 23): 0, (110, 24): 0, (110, 25): 0, (110, 26): 0, (110, 27): 0, (110, 28): 0, (110, 29): 0, (110, 30): 0, (110, 31): 0, (110, 32): 0, (110, 33): 0, (110, 34): 0, (110, 35): 0, (110, 36): 0, (110, 37): 0, (110, 38): 0, (110, 39): 0, (110, 40): 0, (110, 41): 0, (110, 42): 0, (110, 43): 0, (110, 44): 0, (110, 45): 0, (110, 46): 0, (110, 47): 0, (110, 48): 0, (110, 49): 0, (110, 50): 0, (110, 51): 0, (110, 52): 0, (110, 53): 0, (110, 54): 0, (110, 55): 0, (110, 56): 0, (110, 57): 0, (110, 58): 0, (110, 59): 0, (110, 60): 0, (110, 61): 0, (110, 62): 0, (110, 63): 0, (110, 64): 0, (110, 65): 0, (110, 66): 0, (110, 67): 0, (110, 68): 0, (110, 69): 0, (112, 1): 0, (112, 2): 0, (112, 3): 0, (112, 4): 0, (112, 5): 0, (112, 6): 0, (112, 7): 0, (112, 8): 0, (112, 9): 0, (112, 10): 0, (112, 11): 0, (112, 12): 0, (112, 13): 0, (112, 14): 0, (112, 15): 0, (112, 16): 0, (112, 17): 0, (112, 18): 0, (112, 19): 0, (112, 20): 0, (112, 21): 0, (112, 22): 0, (112, 23): 0, (112, 24): 0, (112, 25): 0, (112, 26): 0, (112, 27): 0, (112, 28): 0, (112, 29): 0, (112, 30): 0, (112, 31): 0, (112, 32): 0, (112, 33): 0, (112, 34): 0, (112, 35): 0, (112, 36): 0, (112, 37): 0, (112, 38): 0, (112, 39): 0, (112, 40): 0, (112, 41): 0, (112, 42): 0, (112, 43): 0, (112, 44): 0, (112, 45): 0, (112, 46): 0, (112, 47): 0, (112, 48): 0, (112, 49): 0, (112, 50): 0, (112, 51): 0, (112, 52): 0, (112, 53): 0, (112, 54): 0, (112, 55): 0, (112, 56): 0, (112, 57): 0, (112, 58): 0, (112, 59): 0, (112, 60): 0, (112, 61): 0, (112, 62): 0, (112, 63): 0, (112, 64): 0, (112, 65): 0, (112, 66): 0, (112, 67): 0, (112, 68): 0, (112, 69): 0, (117, 1): 0, (117, 2): 0, (117, 3): 0, (117, 4): 0, (117, 5): 0, (117, 6): 0, (117, 7): 0, (117, 8): 0, (117, 9): 0, (117, 10): 0, (117, 11): 0, (117, 12): 0, (117, 13): 0, (117, 14): 0, (117, 15): 0, (117, 16): 0, (117, 17): 0, (117, 18): 0, (117, 19): 0, (117, 20): 0, (117, 21): 0, (117, 22): 0, (117, 23): 0, (117, 24): 0, (117, 25): 0, (117, 26): 0, (117, 27): 0, (117, 28): 0, (117, 29): 0, (117, 30): 0, (117, 31): 0, (117, 32): 0, (117, 33): 0, (117, 34): 0, (117, 35): 0, (117, 36): 0, (117, 37): 0, (117, 38): 0, (117, 39): 0, (117, 40): 0, (117, 41): 0, (117, 42): 0, (117, 43): 0, (117, 44): 0, (117, 45): 0, (117, 46): 0, (117, 47): 0, (117, 48): 0, (117, 49): 0, (117, 50): 0, (117, 51): 0, (117, 52): 0, (117, 53): 0, (117, 54): 0, (117, 55): 0, (117, 56): 0, (117, 57): 0, (117, 58): 0, (117, 59): 0, (117, 60): 0, (117, 61): 0, (117, 62): 0, (117, 63): 0, (117, 64): 0, (117, 65): 0, (117, 66): 0, (117, 67): 0, (117, 68): 0, (117, 69): 0, (120, 1): 0, (120, 2): 0, (120, 3): 0, (120, 4): 0, (120, 5): 0, (120, 6): 0, (120, 7): 0, (120, 8): 0, (120, 9): 0, (120, 10): 0, (120, 11): 0, (120, 12): 0, (120, 13): 0, (120, 14): 0, (120, 15): 0, (120, 16): 0, (120, 17): 0, (120, 18): 0, (120, 19): 0, (120, 20): 0, (120, 21): 0, (120, 22): 0, (120, 23): 0, (120, 24): 0, (120, 25): 0, (120, 26): 0, (120, 27): 0, (120, 28): 0, (120, 29): 0, (120, 30): 0, (120, 31): 0, (120, 32): 0, (120, 33): 0, (120, 34): 0, (120, 35): 0, (120, 36): 0, (120, 37): 0, (120, 38): 0, (120, 39): 0, (120, 40): 0, (120, 41): 0, (120, 42): 0, (120, 43): 0</t>
+  </si>
+  <si>
+    <t>{(1, 1): 0.0, (1, 2): 0.0, (1, 3): 0.0, (1, 4): 0.0, (1, 5): 0.0, (1, 6): 0.0, (1, 7): 0.0, (1, 8): 0.0, (1, 9): 0.0, (1, 10): 0.0, (1, 11): 0.0, (1, 12): 0.0, (1, 13): 0.0, (1, 14): 0.0, (1, 15): 0.0, (1, 16): 0.5051001633268003, (1, 17): 0.5051001633268003, (1, 18): 0.5051001633268003, (1, 19): 0.5051001633268003, (1, 20): 0.5051001633268003, (1, 21): 0.5051001633268003, (1, 22): 0.5051001633268003, (1, 23): 0.5051001633268003, (1, 24): 0.5051001633268003, (1, 25): 0.5051001633268003, (1, 26): 0.5051001633268003, (1, 27): 0.5051001633268003, (1, 28): 0.0, (1, 29): 0.0, (1, 30): 0.0, (1, 31): 0.0, (1, 32): 0.0, (1, 33): 0.0, (1, 34): 0.0, (1, 35): 0.0, (1, 36): 0.0, (1, 37): 0.0, (1, 38): 0.0, (1, 39): 0.0, (1, 40): 0.0, (1, 41): 0.0, (1, 42): 0.0, (1, 43): 0.0, (1, 44): 0.0, (1, 45): 0.0, (1, 46): 0.0, (1, 47): 0.0, (1, 48): 0.0, (1, 49): 0.0, (1, 50): 0.0, (1, 51): 0.0, (1, 52): 0.0, (1, 53): 0.0, (1, 54): 0.0, (1, 55): 0.0, (1, 56): 0.0, (1, 57): 0.0, (1, 58): 0.0, (1, 59): 0.0, (1, 60): 0.0, (1, 61): 0.0, (1, 62): 0.0, (1, 63): 0.0, (1, 64): 0.0, (1, 65): 0.0, (1, 66): 0.0, (1, 67): 0.0, (1, 68): 0.0, (1, 69): 0.0, (2, 1): 0.0, (2, 2): 0.0, (2, 3): 0.0, (2, 4): 0.0, (2, 5): 0.0, (2, 6): 0.0, (2, 7): 0.0, (2, 8): 0.0, (2, 9): 0.0, (2, 10): 0.0, (2, 11): 0.0, (2, 12): 0.0, (2, 13): 0.0, (2, 14): 0.0, (2, 15): 0.5051001633268003, (2, 16): 0.5051001633268003, (2, 17): 0.5051001633268003, (2, 18): 0.5051001633268003, (2, 19): 0.5051001633268003, (2, 20): 0.5051001633268003, (2, 21): 0.5051001633268003, (2, 22): 0.5051001633268003, (2, 23): 0.5051001633268003, (2, 24): 0.5051001633268003, (2, 25): 0.5051001633268003, (2, 26): 0.5051001633268003, (2, 27): 0.5051001633268003, (2, 28): 0.5051001633268003, (2, 29): 0.5051001633268003, (2, 30): 0.5051001633268003, (2, 31): 0.0, (2, 32): 0.0, (2, 33): 0.0, (2, 34): 0.0, (2, 35): 0.0, (2, 36): 0.0, (2, 37): 0.0, (2, 38): 0.0, (2, 39): 0.0, (2, 40): 0.0, (2, 41): 0.0, (2, 42): 0.0, (2, 43): 0.0, (2, 44): 0.0, (2, 45): 0.0, (2, 46): 0.0, (2, 47): 0.0, (2, 48): 0.0, (2, 49): 0.0, (2, 50): 0.0, (2, 51): 0.0, (2, 52): 0.0, (2, 53): 0.0, (2, 54): 0.0, (2, 55): 0.0, (2, 56): 0.0, (2, 57): 0.0, (2, 58): 0.0, (2, 59): 0.0, (2, 60): 0.0, (2, 61): 0.0, (2, 62): 0.0, (2, 63): 0.0, (2, 64): 0.0, (2, 65): 0.0, (2, 66): 0.0, (2, 67): 0.0, (2, 68): 0.0, (2, 69): 0.0, (6, 1): 0.0, (6, 2): 0.0, (6, 3): 0.0, (6, 4): 0.0, (6, 5): 0.0, (6, 6): 0.0, (6, 7): 0.0, (6, 8): 0.0, (6, 9): 0.0, (6, 10): 0.0, (6, 11): 0.0, (6, 12): 0.0, (6, 13): 0.0, (6, 14): 0.0, (6, 15): 0.0, (6, 16): 0.0, (6, 17): 0.0, (6, 18): 0.0, (6, 19): 0.0, (6, 20): 0.0, (6, 21): 0.0, (6, 22): 0.5051001633268003, (6, 23): 0.5051001633268003, (6, 24): 0.5051001633268003, (6, 25): 0.5051001633268003, (6, 26): 0.5051001633268003, (6, 27): 0.5051001633268003, (6, 28): 0.5051001633268003, (6, 29): 0.5051001633268003, (6, 30): 0.5051001633268003, (6, 31): 0.5051001633268003, (6, 32): 0.5051001633268003, (6, 33): 0.5051001633268003, (6, 34): 0.5051001633268003, (6, 35): 0.5051001633268003, (6, 36): 0.5051001633268003, (6, 37): 0.5051001633268003, (6, 38): 0.5051001633268003, (6, 39): 0.5051001633268003, (6, 40): 0.5051001633268003, (6, 41): 0.5051001633268003, (6, 42): 0.5051001633268003, (6, 43): 0.5051001633268003, (6, 44): 0.5051001633268003, (6, 45): 0.5051001633268003, (6, 46): 0.5051001633268003, (6, 47): 0.5051001633268003, (6, 48): 0.0, (6, 49): 0.0, (6, 50): 0.0, (6, 51): 0.0, (6, 52): 0.0, (6, 53): 0.0, (6, 54): 0.0, (6, 55): 0.0, (6, 56): 0.0, (6, 57): 0.0, (6, 58): 0.0, (6, 59): 0.0, (6, 60): 0.0, (6, 61): 0.0, (6, 62): 0.0, (6, 63): 0.0, (6, 64): 0.0, (6, 65): 0.0, (6, 66): 0.0, (6, 67): 0.0, (6, 68): 0.0, (6, 69): 0.0, (7, 1): 0.0, (7, 2): 0.0, (7, 3): 0.0, (7, 4): 0.0, (7, 5): 0.0, (7, 6): 0.0, (7, 7): 0.0, (7, 8): 0.0, (7, 9): 0.0, (7, 10): 0.0, (7, 11): 0.0, (7, 12): 0.0, (7, 13): 0.0, (7, 14): 0.0, (7, 15): 0.0, (7, 16): 0.0, (7, 17): 0.0, (7, 18): 0.0, (7, 19): 0.0, (7, 20): 0.0, (7, 21): 0.0, (7, 22): 0.0, (7, 23): 0.0, (7, 24): 0.0, (7, 25): 0.0, (7, 26): 0.0, (7, 27): 0.0, (7, 28): 0.0, (7, 29): 0.0, (7, 30): 0.5051001633268003, (7, 31): 0.5051001633268003, (7, 32): 0.5051001633268003, (7, 33): 0.5051001633268003, (7, 34): 0.5051001633268003, (7, 35): 0.5051001633268003, (7, 36): 0.5051001633268003, (7, 37): 0.5051001633268003, (7, 38): 0.5051001633268003, (7, 39): 0.5051001633268003, (7, 40): 0.5051001633268003, (7, 41): 0.5051001633268003, (7, 42): 0.5051001633268003, (7, 43): 0.5051001633268003, (7, 44): 0.5051001633268003, (7, 45): 0.5051001633268003, (7, 46): 0.5051001633268003, (7, 47): 0.5051001633268003, (7, 48): 0.0, (7, 49): 0.0, (7, 50): 0.0, (7, 51): 0.0, (7, 52): 0.0, (7, 53): 0.0, (7, 54): 0.0, (7, 55): 0.0, (7, 56): 0.0, (7, 57): 0.0, (7, 58): 0.0, (7, 59): 0.0, (7, 60): 0.0, (7, 61): 0.0, (7, 62): 0.0, (7, 63): 0.0, (7, 64): 0.0, (7, 65): 0.0, (7, 66): 0.0, (7, 67): 0.0, (7, 68): 0.0, (7, 69): 0.0, (16, 1): 0.0, (16, 2): 0.0, (16, 3): 0.0, (16, 4): 0.0, (16, 5): 0.0, (16, 6): 0.0, (16, 7): 0.0, (16, 8): 0.0, (16, 9): 0.0, (16, 10): 0.0, (16, 11): 0.0, (16, 12): 0.0, (16, 13): 0.0, (16, 14): 0.0, (16, 15): 0.0, (16, 16): 0.0, (16, 17): 0.5051001633268003, (16, 18): 0.5051001633268003, (16, 19): 0.5051001633268003, (16, 20): 0.0, (16, 21): 0.0, (16, 22): 0.0, (16, 23): 0.0, (16, 24): 0.0, (16, 25): 0.0, (16, 26): 0.0, (16, 27): 0.0, (16, 28): 0.0, (16, 29): 0.0, (16, 30): 0.0, (16, 31): 0.0, (16, 32): 0.0, (16, 33): 0.0, (16, 34): 0.0, (16, 35): 0.0, (16, 36): 0.0, (16, 37): 0.0, (16, 38): 0.0, (16, 39): 0.0, (16, 40): 0.0, (16, 41): 0.0, (16, 42): 0.0, (16, 43): 0.0, (16, 44): 0.0, (16, 45): 0.0, (16, 46): 0.0, (16, 47): 0.0, (16, 48): 0.0, (16, 49): 0.0, (16, 50): 0.0, (16, 51): 0.0, (16, 52): 0.0, (16, 53): 0.0, (16, 54): 0.0, (16, 55): 0.0, (16, 56): 0.0, (16, 57): 0.0, (16, 58): 0.0, (16, 59): 0.0, (16, 60): 0.0, (16, 61): 0.0, (16, 62): 0.0, (16, 63): 0.0, (16, 64): 0.0, (16, 65): 0.0, (16, 66): 0.0, (16, 67): 0.0, (16, 68): 0.0, (16, 69): 0.0, (26, 1): 0.0, (26, 2): 0.0, (26, 3): 0.0, (26, 4): 0.0, (26, 5): 0.0, (26, 6): 0.0, (26, 7): 0.0, (26, 8): 0.0, (26, 9): 0.0, (26, 10): 0.0, (26, 11): 0.0, (26, 12): 0.0, (26, 13): 0.0, (26, 14): 0.0, (26, 15): 0.0, (26, 16): 0.0, (26, 17): 0.0, (26, 18): 0.0, (26, 19): 0.0, (26, 20): 0.0, (26, 21): 0.0, (26, 22): 0.0, (26, 23): 0.0, (26, 24): 0.0, (26, 25): 0.5051001633268003, (26, 26): 0.5051001633268003, (26, 27): 0.5051001633268003, (26, 28): 0.5051001633268003, (26, 29): 0.5051001633268003, (26, 30): 0.5051001633268003, (26, 31): 0.5051001633268003, (26, 32): 0.5051001633268003, (26, 33): 0.5051001633268003, (26, 34): 0.5051001633268003, (26, 35): 0.5051001633268003, (26, 36): 0.5051001633268003, (26, 37): 0.5051001633268003, (26, 38): 0.5051001633268003, (26, 39): 0.0, (26, 40): 0.0, (26, 41): 0.0, (26, 42): 0.0, (26, 43): 0.0, (26, 44): 0.0, (26, 45): 0.0, (26, 46): 0.0, (26, 47): 0.0, (26, 48): 0.0, (26, 49): 0.0, (26, 50): 0.0, (26, 51): 0.0, (26, 52): 0.0, (26, 53): 0.0, (26, 54): 0.0, (26, 55): 0.0, (26, 56): 0.0, (26, 57): 0.0, (26, 58): 0.0, (26, 59): 0.0, (26, 60): 0.0, (26, 61): 0.0, (26, 62): 0.0, (26, 63): 0.0, (26, 64): 0.0, (26, 65): 0.0, (26, 66): 0.0, (26, 67): 0.0, (26, 68): 0.0, (26, 69): 0.0, (35, 1): 0.0, (35, 2): 0.0, (35, 3): 0.0, (35, 4): 0.0, (35, 5): 0.0, (35, 6): 0.5051001633268003, (35, 7): 0.5051001633268003, (35, 8): 0.5051001633268003, (35, 9): 0.5051001633268003, (35, 10): 0.5051001633268003, (35, 11): 0.5051001633268003, (35, 12): 0.5051001633268003, (35, 13): 0.5051001633268003, (35, 14): 0.5051001633268003, (35, 15): 0.5051001633268003, (35, 16): 0.0, (35, 17): 0.0, (35, 18): 0.0, (35, 19): 0.0, (35, 20): 0.0, (35, 21): 0.0, (35, 22): 0.0, (35, 23): 0.0, (35, 24): 0.0, (35, 25): 0.0, (35, 26): 0.0, (35, 27): 0.0, (35, 28): 0.0, (35, 29): 0.0, (35, 30): 0.0, (35, 31): 0.0, (35, 32): 0.0, (35, 33): 0.0, (35, 34): 0.0, (35, 35): 0.0, (35, 36): 0.0, (35, 37): 0.0, (35, 38): 0.0, (35, 39): 0.0, (35, 40): 0.0, (35, 41): 0.0, (35, 42): 0.0, (35, 43): 0.0, (35, 44): 0.0, (35, 45): 0.0, (35, 46): 0.0, (35, 47): 0.0, (35, 48): 0.0, (35, 49): 0.0, (35, 50): 0.0, (35, 51): 0.0, (35, 52): 0.0, (35, 53): 0.0, (35, 54): 0.0, (35, 55): 0.0, (35, 56): 0.0, (35, 57): 0.0, (35, 58): 0.0, (35, 59): 0.0, (35, 60): 0.0, (35, 61): 0.0, (35, 62): 0.0, (35, 63): 0.0, (35, 64): 0.0, (35, 65): 0.0, (35, 66): 0.0, (35, 67): 0.0, (35, 68): 0.0, (35, 69): 0.0, (38, 1): 0.0, (38, 2): 0.0, (38, 3): 0.0, (38, 4): 0.0, (38, 5): 0.5051001633268003, (38, 6): 0.5051001633268003, (38, 7): 0.5051001633268003, (38, 8): 0.5051001633268003, (38, 9): 0.5051001633268003, (38, 10): 0.5051001633268003, (38, 11): 0.5051001633268003, (38, 12): 0.0, (38, 13): 0.0, (38, 14): 0.0, (38, 15): 0.0, (38, 16): 0.0, (38, 17): 0.0, (38, 18): 0.0, (38, 19): 0.0, (38, 20): 0.0, (38, 21): 0.0, (38, 22): 0.0, (38, 23): 0.0, (38, 24): 0.0, (38, 25): 0.0, (38, 26): 0.0, (38, 27): 0.0, (38, 28): 0.0, (38, 29): 0.0, (38, 30): 0.0, (38, 31): 0.0, (38, 32): 0.0, (38, 33): 0.0, (38, 34): 0.0, (38, 35): 0.0, (38, 36): 0.0, (38, 37): 0.0, (38, 38): 0.0, (38, 39): 0.0, (38, 40): 0.0, (38, 41): 0.0, (38, 42): 0.0, (38, 43): 0.0, (38, 44): 0.0, (38, 45): 0.0, (38, 46): 0.0, (38, 47): 0.0, (38, 48): 0.0, (38, 49): 0.0, (38, 50): 0.0, (38, 51): 0.0, (38, 52): 0.0, (38, 53): 0.0, (38, 54): 0.0, (38, 55): 0.0, (38, 56): 0.0, (38, 57): 0.0, (38, 58): 0.0, (38, 59): 0.0, (38, 60): 0.0, (38, 61): 0.0, (38, 62): 0.0, (38, 63): 0.0, (38, 64): 0.0, (38, 65): 0.0, (38, 66): 0.0, (38, 67): 0.0, (38, 68): 0.0, (38, 69): 0.0, (39, 1): 0.0, (39, 2): 0.0, (39, 3): 0.0, (39, 4): 0.0, (39, 5): 0.0, (39, 6): 0.0, (39, 7): 0.0, (39, 8): 0.0, (39, 9): 0.0, (39, 10): 0.0, (39, 11): 0.0, (39, 12): 0.0, (39, 13): 0.0, (39, 14): 0.5051001633268003, (39, 15): 0.5051001633268003, (39, 16): 0.5051001633268003, (39, 17): 0.5051001633268003, (39, 18): 0.5051001633268003, (39, 19): 0.5051001633268003, (39, 20): 0.5051001633268003, (39, 21): 0.5051001633268003, (39, 22): 0.5051001633268003, (39, 23): 0.0, (39, 24): 0.0, (39, 25): 0.0, (39, 26): 0.0, (39, 27): 0.0, (39, 28): 0.0, (39, 29): 0.0, (39, 30): 0.0, (39, 31): 0.0, (39, 32): 0.0, (39, 33): 0.0, (39, 34): 0.0, (39, 35): 0.0, (39, 36): 0.0, (39, 37): 0.0, (39, 38): 0.0, (39, 39): 0.0, (39, 40): 0.0, (39, 41): 0.0, (39, 42): 0.0, (39, 43): 0.0, (39, 44): 0.0, (39, 45): 0.0, (39, 46): 0.0, (39, 47): 0.0, (39, 48): 0.0, (39, 49): 0.0, (39, 50): 0.0, (39, 51): 0.0, (39, 52): 0.0, (39, 53): 0.0, (39, 54): 0.0, (39, 55): 0.0, (39, 56): 0.0, (39, 57): 0.0, (39, 58): 0.0, (39, 59): 0.0, (39, 60): 0.0, (39, 61): 0.0, (39, 62): 0.0, (39, 63): 0.0, (39, 64): 0.0, (39, 65): 0.0, (39, 66): 0.0, (39, 67): 0.0, (39, 68): 0.0, (39, 69): 0.0, (41, 1): 0.0, (41, 2): 0.0, (41, 3): 0.0, (41, 4): 0.0, (41, 5): 0.0, (41, 6): 0.0, (41, 7): 0.0, (41, 8): 0.0, (41, 9): 0.0, (41, 10): 0.0, (41, 11): 0.0, (41, 12): 0.0, (41, 13): 0.0, (41, 14): 0.0, (41, 15): 0.0, (41, 16): 0.0, (41, 17): 0.0, (41, 18): 0.0, (41, 19): 0.0, (41, 20): 0.0, (41, 21): 0.0, (41, 22): 0.0, (41, 23): 0.0, (41, 24): 0.0, (41, 25): 0.0, (41, 26): 0.0, (41, 27): 0.0, (41, 28): 0.5051001633268003, (41, 29): 0.5051001633268003, (41, 30): 0.5051001633268003, (41, 31): 0.5051001633268003, (41, 32): 0.5051001633268003, (41, 33): 0.5051001633268003, (41, 34): 0.5051001633268003, (41, 35): 0.5051001633268003, (41, 36): 0.5051001633268003, (41, 37): 0.0, (41, 38): 0.0, (41, 39): 0.0, (41, 40): 0.0, (41, 41): 0.0, (41, 42): 0.0, (41, 43): 0.0, (41, 44): 0.0, (41, 45): 0.0, (41, 46): 0.0, (41, 47): 0.0, (41, 48): 0.0, (41, 49): 0.0, (41, 50): 0.0, (41, 51): 0.0, (41, 52): 0.0, (41, 53): 0.0, (41, 54): 0.0, (41, 55): 0.0, (41, 56): 0.0, (41, 57): 0.0, (41, 58): 0.0, (41, 59): 0.0, (41, 60): 0.0, (41, 61): 0.0, (41, 62): 0.0, (41, 63): 0.0, (41, 64): 0.0, (41, 65): 0.0, (41, 66): 0.0, (41, 67): 0.0, (41, 68): 0.0, (41, 69): 0.0, (42, 1): 0.0, (42, 2): 0.0, (42, 3): 0.0, (42, 4): 0.0, (42, 5): 0.0, (42, 6): 0.0, (42, 7): 0.0, (42, 8): 0.0, (42, 9): 0.0, (42, 10): 0.0, (42, 11): 0.0, (42, 12): 0.0, (42, 13): 0.0, (42, 14): 0.0, (42, 15): 0.0, (42, 16): 0.0, (42, 17): 0.0, (42, 18): 0.0, (42, 19): 0.0, (42, 20): 0.0, (42, 21): 0.0, (42, 22): 0.5051001633268003, (42, 23): 0.5051001633268003, (42, 24): 0.5051001633268003, (42, 25): 0.5051001633268003, (42, 26): 0.5051001633268003, (42, 27): 0.5051001633268003, (42, 28): 0.5051001633268003, (42, 29): 0.5051001633268003, (42, 30): 0.5051001633268003, (42, 31): 0.0, (42, 32): 0.0, (42, 33): 0.0, (42, 34): 0.0, (42, 35): 0.0, (42, 36): 0.0, (42, 37): 0.0, (42, 38): 0.0, (42, 39): 0.0, (42, 40): 0.0, (42, 41): 0.0, (42, 42): 0.0, (42, 43): 0.0, (42, 44): 0.0, (42, 45): 0.0, (42, 46): 0.0, (42, 47): 0.0, (42, 48): 0.0, (42, 49): 0.0, (42, 50): 0.0, (42, 51): 0.0, (42, 52): 0.0, (42, 53): 0.0, (42, 54): 0.0, (42, 55): 0.0, (42, 56): 0.0, (42, 57): 0.0, (42, 58): 0.0, (42, 59): 0.0, (42, 60): 0.0, (42, 61): 0.0, (42, 62): 0.0, (42, 63): 0.0, (42, 64): 0.0, (42, 65): 0.0, (42, 66): 0.0, (42, 67): 0.0, (42, 68): 0.0, (42, 69): 0.0, (43, 1): 0.0, (43, 2): 0.0, (43, 3): 0.0, (43, 4): 0.0, (43, 5): 0.0, (43, 6): 0.0, (43, 7): 0.0, (43, 8): 0.0, (43, 9): 0.0, (43, 10): 0.0, (43, 11): 0.0, (43, 12): 0.0, (43, 13): 0.0, (43, 14): 0.0, (43, 15): 0.0, (43, 16): 0.0, (43, 17): 0.0, (43, 18): 0.0, (43, 19): 0.0, (43, 20): 0.0, (43, 21): 0.0, (43, 22): 0.5051001633268003, (43, 23): 0.5051001633268003, (43, 24): 0.5051001633268003, (43, 25): 0.5051001633268003, (43, 26): 0.5051001633268003, (43, 27): 0.0, (43, 28): 0.0, (43, 29): 0.0, (43, 30): 0.0, (43, 31): 0.0, (43, 32): 0.0, (43, 33): 0.0, (43, 34): 0.0, (43, 35): 0.0, (43, 36): 0.0, (43, 37): 0.0, (43, 38): 0.0, (43, 39): 0.0, (43, 40): 0.0, (43, 41): 0.0, (43, 42): 0.0, (43, 43): 0.0, (43, 44): 0.0, (43, 45): 0.0, (43, 46): 0.0, (43, 47): 0.0, (43, 48): 0.0, (43, 49): 0.0, (43, 50): 0.0, (43, 51): 0.0, (43, 52): 0.0, (43, 53): 0.0, (43, 54): 0.0, (43, 55): 0.0, (43, 56): 0.0, (43, 57): 0.0, (43, 58): 0.0, (43, 59): 0.0, (43, 60): 0.0, (43, 61): 0.0, (43, 62): 0.0, (43, 63): 0.0, (43, 64): 0.0, (43, 65): 0.0, (43, 66): 0.0, (43, 67): 0.0, (43, 68): 0.0, (43, 69): 0.0, (46, 1): 0.0, (46, 2): 0.0, (46, 3): 0.0, (46, 4): 0.0, (46, 5): 0.5051001633268003, (46, 6): 0.5051001633268003, (46, 7): 0.5051001633268003, (46, 8): 0.5051001633268003, (46, 9): 0.5051001633268003, (46, 10): 0.5051001633268003, (46, 11): 0.5051001633268003, (46, 12): 0.5051001633268003, (46, 13): 0.5051001633268003, (46, 14): 0.5051001633268003, (46, 15): 0.5051001633268003, (46, 16): 0.0, (46, 17): 0.0, (46, 18): 0.0, (46, 19): 0.0, (46, 20): 0.0, (46, 21): 0.0, (46, 22): 0.0, (46, 23): 0.0, (46, 24): 0.0, (46, 25): 0.0, (46, 26): 0.0, (46, 27): 0.0, (46, 28): 0.0, (46, 29): 0.0, (46, 30): 0.0, (46, 31): 0.0, (46, 32): 0.0, (46, 33): 0.0, (46, 34): 0.0, (46, 35): 0.0, (46, 36): 0.0, (46, 37): 0.0, (46, 38): 0.0, (46, 39): 0.0, (46, 40): 0.0, (46, 41): 0.0, (46, 42): 0.0, (46, 43): 0.0, (46, 44): 0.0, (46, 45): 0.0, (46, 46): 0.0, (46, 47): 0.0, (46, 48): 0.0, (46, 49): 0.0, (46, 50): 0.0, (46, 51): 0.0, (46, 52): 0.0, (46, 53): 0.0, (46, 54): 0.0, (46, 55): 0.0, (46, 56): 0.0, (46, 57): 0.0, (46, 58): 0.0, (46, 59): 0.0, (46, 60): 0.0, (46, 61): 0.0, (46, 62): 0.0, (46, 63): 0.0, (46, 64): 0.0, (46, 65): 0.0, (46, 66): 0.0, (46, 67): 0.0, (46, 68): 0.0, (46, 69): 0.0, (48, 1): 0.0, (48, 2): 0.0, (48, 3): 0.0, (48, 4): 0.0, (48, 5): 0.0, (48, 6): 0.0, (48, 7): 0.0, (48, 8): 0.0, (48, 9): 0.0, (48, 10): 0.0, (48, 11): 0.0, (48, 12): 0.0, (48, 13): 0.0, (48, 14): 0.0, (48, 15): 0.0, (48, 16): 0.0, (48, 17): 0.0, (48, 18): 0.0, (48, 19): 0.0, (48, 20): 0.0, (48, 21): 0.0, (48, 22): 0.0, (48, 23): 0.0, (48, 24): 0.0, (48, 25): 0.0, (48, 26): 0.5051001633268003, (48, 27): 0.5051001633268003, (48, 28): 0.5051001633268003, (48, 29): 0.5051001633268003, (48, 30): 0.0, (48, 31): 0.0, (48, 32): 0.0, (48, 33): 0.0, (48, 34): 0.0, (48, 35): 0.0, (48, 36): 0.0, (48, 37): 0.0, (48, 38): 0.0, (48, 39): 0.0, (48, 40): 0.0, (48, 41): 0.0, (48, 42): 0.0, (48, 43): 0.0, (48, 44): 0.0, (48, 45): 0.0, (48, 46): 0.0, (48, 47): 0.0, (48, 48): 0.0, (48, 49): 0.0, (48, 50): 0.0, (48, 51): 0.0, (48, 52): 0.0, (48, 53): 0.0, (48, 54): 0.0, (48, 55): 0.0, (48, 56): 0.0, (48, 57): 0.0, (48, 58): 0.0, (48, 59): 0.0, (48, 60): 0.0, (48, 61): 0.0, (48, 62): 0.0, (48, 63): 0.0, (48, 64): 0.0, (48, 65): 0.0, (48, 66): 0.0, (48, 67): 0.0, (48, 68): 0.0, (48, 69): 0.0, (49, 1): 0.0, (49, 2): 0.0, (49, 3): 0.0, (49, 4): 0.0, (49, 5): 0.0, (49, 6): 0.0, (49, 7): 0.0, (49, 8): 0.0, (49, 9): 0.5051001633268003, (49, 10): 0.5051001633268003, (49, 11): 0.5051001633268003, (49, 12): 0.5051001633268003, (49, 13): 0.5051001633268003, (49, 14): 0.5075500204164625, (49, 15): 0.5075500204164625, (49, 16): 0.5075500204164625, (49, 17): 0.5075500204164625, (49, 18): 0.0, (49, 19): 0.0, (49, 20): 0.0, (49, 21): 0.0, (49, 22): 0.0, (49, 23): 0.0, (49, 24): 0.0, (49, 25): 0.0, (49, 26): 0.0, (49, 27): 0.0, (49, 28): 0.0, (49, 29): 0.0, (49, 30): 0.0, (49, 31): 0.0, (49, 32): 0.0, (49, 33): 0.0, (49, 34): 0.0, (49, 35): 0.0, (49, 36): 0.0, (49, 37): 0.0, (49, 38): 0.0, (49, 39): 0.0, (49, 40): 0.0, (49, 41): 0.0, (49, 42): 0.0, (49, 43): 0.0, (49, 44): 0.0, (49, 45): 0.0, (49, 46): 0.0, (49, 47): 0.0, (49, 48): 0.0, (49, 49): 0.0, (49, 50): 0.0, (49, 51): 0.0, (49, 52): 0.0, (49, 53): 0.0, (49, 54): 0.0, (49, 55): 0.0, (49, 56): 0.0, (49, 57): 0.0, (49, 58): 0.0, (49, 59): 0.0, (49, 60): 0.0, (49, 61): 0.0, (49, 62): 0.0, (49, 63): 0.0, (49, 64): 0.0, (49, 65): 0.0, (49, 66): 0.0, (49, 67): 0.0, (49, 68): 0.0, (49, 69): 0.0, (51, 1): 0.0, (51, 2): 0.0, (51, 3): 0.0, (51, 4): 0.0, (51, 5): 0.0, (51, 6): 0.0, (51, 7): 0.0, (51, 8): 0.0, (51, 9): 0.0, (51, 10): 0.0, (51, 11): 0.0, (51, 12): 0.0, (51, 13): 0.5051001633268003, (51, 14): 0.5051001633268003, (51, 15): 0.5051001633268003, (51, 16): 0.5051001633268003, (51, 17): 0.5075500204164625, (51, 18): 0.5075500204164625, (51, 19): 0.5075500204164625, (51, 20): 0.5075500204164625, (51, 21): 0.0, (51, 22): 0.0, (51, 23): 0.0, (51, 24): 0.0, (51, 25): 0.0, (51, 26): 0.0, (51, 27): 0.0, (51, 28): 0.0, (51, 29): 0.0, (51, 30): 0.0, (51, 31): 0.0, (51, 32): 0.0, (51, 33): 0.0, (51, 34): 0.0, (51, 35): 0.0, (51, 36): 0.0, (51, 37): 0.0, (51, 38): 0.0, (51, 39): 0.0, (51, 40): 0.0, (51, 41): 0.0, (51, 42): 0.0, (51, 43): 0.0, (51, 44): 0.0, (51, 45): 0.0, (51, 46): 0.0, (51, 47): 0.0, (51, 48): 0.0, (51, 49): 0.0, (51, 50): 0.0, (51, 51): 0.0, (51, 52): 0.0, (51, 53): 0.0, (51, 54): 0.0, (51, 55): 0.0, (51, 56): 0.0, (51, 57): 0.0, (51, 58): 0.0, (51, 59): 0.0, (51, 60): 0.0, (51, 61): 0.0, (51, 62): 0.0, (51, 63): 0.0, (51, 64): 0.0, (51, 65): 0.0, (51, 66): 0.0, (51, 67): 0.0, (51, 68): 0.0, (51, 69): 0.0, (52, 1): 0.0, (52, 2): 0.0, (52, 3): 0.5051001633268003, (52, 4): 0.5051001633268003, (52, 5): 0.5051001633268003, (52, 6): 0.5051001633268003, (52, 7): 0.5051001633268003, (52, 8): 0.5051001633268003, (52, 9): 0.5051001633268003, (52, 10): 0.5051001633268003, (52, 11): 0.5051001633268003, (52, 12): 0.5051001633268003, (52, 13): 0.0, (52, 14): 0.0, (52, 15): 0.0, (52, 16): 0.0, (52, 17): 0.0, (52, 18): 0.0, (52, 19): 0.0, (52, 20): 0.0, (52, 21): 0.0, (52, 22): 0.0, (52, 23): 0.0, (52, 24): 0.0, (52, 25): 0.0, (52, 26): 0.0, (52, 27): 0.0, (52, 28): 0.0, (52, 29): 0.0, (52, 30): 0.0, (52, 31): 0.0, (52, 32): 0.0, (52, 33): 0.0, (52, 34): 0.0, (52, 35): 0.0, (52, 36): 0.0, (52, 37): 0.0, (52, 38): 0.0, (52, 39): 0.0, (52, 40): 0.0, (52, 41): 0.0, (52, 42): 0.0, (52, 43): 0.0, (52, 44): 0.0, (52, 45): 0.0, (52, 46): 0.0, (52, 47): 0.0, (52, 48): 0.0, (52, 49): 0.0, (52, 50): 0.0, (52, 51): 0.0, (52, 52): 0.0, (52, 53): 0.0, (52, 54): 0.0, (52, 55): 0.0, (52, 56): 0.0, (52, 57): 0.0, (52, 58): 0.0, (52, 59): 0.0, (52, 60): 0.0, (52, 61): 0.0, (52, 62): 0.0, (52, 63): 0.0, (52, 64): 0.0, (52, 65): 0.0, (52, 66): 0.0, (52, 67): 0.0, (52, 68): 0.0, (52, 69): 0.0, (57, 1): 0.0, (57, 2): 0.0, (57, 3): 0.0, (57, 4): 0.0, (57, 5): 0.0, (57, 6): 0.0, (57, 7): 0.0, (57, 8): 0.0, (57, 9): 0.0, (57, 10): 0.0, (57, 11): 0.0, (57, 12): 0.0, (57, 13): 0.0, (57, 14): 0.0, (57, 15): 0.0, (57, 16): 0.0, (57, 17): 0.0, (57, 18): 0.0, (57, 19): 0.0, (57, 20): 0.0, (57, 21): 0.0, (57, 22): 0.0, (57, 23): 0.0, (57, 24): 0.5051001633268003, (57, 25): 0.5051001633268003, (57, 26): 0.5051001633268003, (57, 27): 0.5051001633268003, (57, 28): 0.5051001633268003, (57, 29): 0.5051001633268003, (57, 30): 0.5051001633268003, (57, 31): 0.5051001633268003, (57, 32): 0.5051001633268003, (57, 33): 0.5051001633268003, (57, 34): 0.5051001633268003, (57, 35): 0.0, (57, 36): 0.0, (57, 37): 0.0, (57, 38): 0.0, (57, 39): 0.0, (57, 40): 0.0, (57, 41): 0.0, (57, 42): 0.0, (57, 43): 0.0, (57, 44): 0.0, (57, 45): 0.0, (57, 46): 0.0, (57, 47): 0.0, (57, 48): 0.0, (57, 49): 0.0, (57, 50): 0.0, (57, 51): 0.0, (57, 52): 0.0, (57, 53): 0.0, (57, 54): 0.0, (57, 55): 0.0, (57, 56): 0.0, (57, 57): 0.0, (57, 58): 0.0, (57, 59): 0.0, (57, 60): 0.0, (57, 61): 0.0, (57, 62): 0.0, (57, 63): 0.0, (57, 64): 0.0, (57, 65): 0.0, (57, 66): 0.0, (57, 67): 0.0, (57, 68): 0.0, (57, 69): 0.0, (70, 1): 0.0, (70, 2): 0.0, (70, 3): 0.0, (70, 4): 0.0, (70, 5): 0.0, (70, 6): 0.0, (70, 7): 0.0, (70, 8): 0.0, (70, 9): 0.0, (70, 10): 0.0, (70, 11): 0.0, (70, 12): 0.0, (70, 13): 0.0, (70, 14): 0.0, (70, 15): 0.0, (70, 16): 0.0, (70, 17): 0.5051001633268003, (70, 18): 0.5051001633268003, (70, 19): 0.5051001633268003, (70, 20): 0.5051001633268003, (70, 21): 0.5051001633268003, (70, 22): 0.5051001633268003, (70, 23): 0.5051001633268003, (70, 24): 0.5051001633268003, (70, 25): 0.5051001633268003, (70, 26): 0.5051001633268003, (70, 27): 0.0, (70, 28): 0.0, (70, 29): 0.0, (70, 30): 0.0, (70, 31): 0.0, (70, 32): 0.0, (70, 33): 0.0, (70, 34): 0.0, (70, 35): 0.0, (70, 36): 0.0, (70, 37): 0.0, (70, 38): 0.0, (70, 39): 0.0, (70, 40): 0.0, (70, 41): 0.0, (70, 42): 0.0, (70, 43): 0.0, (70, 44): 0.0, (70, 45): 0.0, (70, 46): 0.0, (70, 47): 0.0, (70, 48): 0.0, (70, 49): 0.0, (70, 50): 0.0, (70, 51): 0.0, (70, 52): 0.0, (70, 53): 0.0, (70, 54): 0.0, (70, 55): 0.0, (70, 56): 0.0, (70, 57): 0.0, (70, 58): 0.0, (70, 59): 0.0, (70, 60): 0.0, (70, 61): 0.0, (70, 62): 0.0, (70, 63): 0.0, (70, 64): 0.0, (70, 65): 0.0, (70, 66): 0.0, (70, 67): 0.0, (70, 68): 0.0, (70, 69): 0.0, (73, 1): 0.0, (73, 2): 0.0, (73, 3): 0.0, (73, 4): 0.0, (73, 5): 0.0, (73, 6): 0.0, (73, 7): 0.0, (73, 8): 0.0, (73, 9): 0.0, (73, 10): 0.0, (73, 11): 0.0, (73, 12): 0.0, (73, 13): 0.0, (73, 14): 0.0, (73, 15): 0.0, (73, 16): 0.0, (73, 17): 0.0, (73, 18): 0.0, (73, 19): 0.0, (73, 20): 0.0, (73, 21): 0.0, (73, 22): 0.0, (73, 23): 0.0, (73, 24): 0.0, (73, 25): 0.0, (73, 26): 0.0, (73, 27): 0.0, (73, 28): 0.0, (73, 29): 0.0, (73, 30): 0.0, (73, 31): 0.0, (73, 32): 0.5051001633268003, (73, 33): 0.5051001633268003, (73, 34): 0.5051001633268003, (73, 35): 0.5051001633268003, (73, 36): 0.0, (73, 37): 0.0, (73, 38): 0.0, (73, 39): 0.0, (73, 40): 0.0, (73, 41): 0.0, (73, 42): 0.0, (73, 43): 0.0, (73, 44): 0.0, (73, 45): 0.0, (73, 46): 0.0, (73, 47): 0.0, (73, 48): 0.0, (73, 49): 0.0, (73, 50): 0.0, (73, 51): 0.0, (73, 52): 0.0, (73, 53): 0.0, (73, 54): 0.0, (73, 55): 0.0, (73, 56): 0.0, (73, 57): 0.0, (73, 58): 0.0, (73, 59): 0.0, (73, 60): 0.0, (73, 61): 0.0, (73, 62): 0.0, (73, 63): 0.0, (73, 64): 0.0, (73, 65): 0.0, (73, 66): 0.0, (73, 67): 0.0, (73, 68): 0.0, (73, 69): 0.0, (75, 1): 0.0, (75, 2): 0.0, (75, 3): 0.0, (75, 4): 0.0, (75, 5): 0.0, (75, 6): 0.0, (75, 7): 0.0, (75, 8): 0.5051001633268003, (75, 9): 0.5051001633268003, (75, 10): 0.5051001633268003, (75, 11): 0.5051001633268003, (75, 12): 0.5051001633268003, (75, 13): 0.5051001633268003, (75, 14): 0.5075500204164625, (75, 15): 0.5075500204164625, (75, 16): 0.0, (75, 17): 0.0, (75, 18): 0.0, (75, 19): 0.0, (75, 20): 0.0, (75, 21): 0.0, (75, 22): 0.0, (75, 23): 0.0, (75, 24): 0.0, (75, 25): 0.0, (75, 26): 0.0, (75, 27): 0.0, (75, 28): 0.0, (75, 29): 0.0, (75, 30): 0.0, (75, 31): 0.0, (75, 32): 0.0, (75, 33): 0.0, (75, 34): 0.0, (75, 35): 0.0, (75, 36): 0.0, (75, 37): 0.0, (75, 38): 0.0, (75, 39): 0.0, (75, 40): 0.0, (75, 41): 0.0, (75, 42): 0.0, (75, 43): 0.0, (75, 44): 0.0, (75, 45): 0.0, (75, 46): 0.0, (75, 47): 0.0, (75, 48): 0.0, (75, 49): 0.0, (75, 50): 0.0, (75, 51): 0.0, (75, 52): 0.0, (75, 53): 0.0, (75, 54): 0.0, (75, 55): 0.0, (75, 56): 0.0, (75, 57): 0.0, (75, 58): 0.0, (75, 59): 0.0, (75, 60): 0.0, (75, 61): 0.0, (75, 62): 0.0, (75, 63): 0.0, (75, 64): 0.0, (75, 65): 0.0, (75, 66): 0.0, (75, 67): 0.0, (75, 68): 0.0, (75, 69): 0.0, (82, 1): 0.0, (82, 2): 0.0, (82, 3): 0.0, (82, 4): 0.0, (82, 5): 0.0, (82, 6): 0.0, (82, 7): 0.0, (82, 8): 0.0, (82, 9): 0.0, (82, 10): 0.0, (82, 11): 0.0, (82, 12): 0.0, (82, 13): 0.0, (82, 14): 0.0, (82, 15): 0.0, (82, 16): 0.0, (82, 17): 0.0, (82, 18): 0.0, (82, 19): 0.0, (82, 20): 0.0, (82, 21): 0.0, (82, 22): 0.0, (82, 23): 0.0, (82, 24): 0.5051001633268003, (82, 25): 0.5051001633268003, (82, 26): 0.5051001633268003, (82, 27): 0.5051001633268003, (82, 28): 0.5051001633268003, (82, 29): 0.5051001633268003, (82, 30): 0.5051001633268003, (82, 31): 0.5051001633268003, (82, 32): 0.5051001633268003, (82, 33): 0.5051001633268003, (82, 34): 0.0, (82, 35): 0.0, (82, 36): 0.0, (82, 37): 0.0, (82, 38): 0.0, (82, 39): 0.0, (82, 40): 0.0, (82, 41): 0.0, (82, 42): 0.0, (82, 43): 0.0, (82, 44): 0.0, (82, 45): 0.0, (82, 46): 0.0, (82, 47): 0.0, (82, 48): 0.0, (82, 49): 0.0, (82, 50): 0.0, (82, 51): 0.0, (82, 52): 0.0, (82, 53): 0.0, (82, 54): 0.0, (82, 55): 0.0, (82, 56): 0.0, (82, 57): 0.0, (82, 58): 0.0, (82, 59): 0.0, (82, 60): 0.0, (82, 61): 0.0, (82, 62): 0.0, (82, 63): 0.0, (82, 64): 0.0, (82, 65): 0.0, (82, 66): 0.0, (82, 67): 0.0, (82, 68): 0.0, (82, 69): 0.0, (84, 1): 0.0, (84, 2): 0.0, (84, 3): 0.0, (84, 4): 0.0, (84, 5): 0.0, (84, 6): 0.0, (84, 7): 0.0, (84, 8): 0.0, (84, 9): 0.0, (84, 10): 0.0, (84, 11): 0.0, (84, 12): 0.0, (84, 13): 0.0, (84, 14): 0.0, (84, 15): 0.0, (84, 16): 0.0, (84, 17): 0.0, (84, 18): 0.0, (84, 19): 0.5051001633268003, (84, 20): 0.5051001633268003, (84, 21): 0.5051001633268003, (84, 22): 0.5051001633268003, (84, 23): 0.5051001633268003, (84, 24): 0.5051001633268003, (84, 25): 0.5051001633268003, (84, 26): 0.0, (84, 27): 0.0, (84, 28): 0.0, (84, 29): 0.0, (84, 30): 0.0, (84, 31): 0.0, (84, 32): 0.0, (84, 33): 0.0, (84, 34): 0.0, (84, 35): 0.0, (84, 36): 0.0, (84, 37): 0.0, (84, 38): 0.0, (84, 39): 0.0, (84, 40): 0.0, (84, 41): 0.0, (84, 42): 0.0, (84, 43): 0.0, (84, 44): 0.0, (84, 45): 0.0, (84, 46): 0.0, (84, 47): 0.0, (84, 48): 0.0, (84, 49): 0.0, (84, 50): 0.0, (84, 51): 0.0, (84, 52): 0.0, (84, 53): 0.0, (84, 54): 0.0, (84, 55): 0.0, (84, 56): 0.0, (84, 57): 0.0, (84, 58): 0.0, (84, 59): 0.0, (84, 60): 0.0, (84, 61): 0.0, (84, 62): 0.0, (84, 63): 0.0, (84, 64): 0.0, (84, 65): 0.0, (84, 66): 0.0, (84, 67): 0.0, (84, 68): 0.0, (84, 69): 0.0, (86, 1): 0.0, (86, 2): 0.0, (86, 3): 0.0, (86, 4): 0.0, (86, 5): 0.0, (86, 6): 0.0, (86, 7): 0.5051001633268003, (86, 8): 0.5051001633268003, (86, 9): 0.5051001633268003, (86, 10): 0.5075500204164625, (86, 11): 0.5075500204164625, (86, 12): 0.5075500204164625, (86, 13): 0.0, (86, 14): 0.0, (86, 15): 0.0, (86, 16): 0.0, (86, 17): 0.0, (86, 18): 0.0, (86, 19): 0.0, (86, 20): 0.0, (86, 21): 0.0, (86, 22): 0.0, (86, 23): 0.0, (86, 24): 0.0, (86, 25): 0.0, (86, 26): 0.0, (86, 27): 0.0, (86, 28): 0.0, (86, 29): 0.0, (86, 30): 0.0, (86, 31): 0.0, (86, 32): 0.0, (86, 33): 0.0, (86, 34): 0.0, (86, 35): 0.0, (86, 36): 0.0, (86, 37): 0.0, (86, 38): 0.0, (86, 39): 0.0, (86, 40): 0.0, (86, 41): 0.0, (86, 42): 0.0, (86, 43): 0.0, (86, 44): 0.0, (86, 45): 0.0, (86, 46): 0.0, (86, 47): 0.0, (86, 48): 0.0, (86, 49): 0.0, (86, 50): 0.0, (86, 51): 0.0, (86, 52): 0.0, (86, 53): 0.0, (86, 54): 0.0, (86, 55): 0.0, (86, 56): 0.0, (86, 57): 0.0, (86, 58): 0.0, (86, 59): 0.0, (86, 60): 0.0, (86, 61): 0.0, (86, 62): 0.0, (86, 63): 0.0, (86, 64): 0.0, (86, 65): 0.0, (86, 66): 0.0, (86, 67): 0.0, (86, 68): 0.0, (86, 69): 0.0, (87, 1): 0.0, (87, 2): 0.0, (87, 3): 0.0, (87, 4): 0.0, (87, 5): 0.0, (87, 6): 0.0, (87, 7): 0.0, (87, 8): 0.0, (87, 9): 0.0, (87, 10): 0.0, (87, 11): 0.0, (87, 12): 0.0, (87, 13): 0.0, (87, 14): 0.0, (87, 15): 0.0, (87, 16): 0.0, (87, 17): 0.0, (87, 18): 0.0, (87, 19): 0.0, (87, 20): 0.0, (87, 21): 0.0, (87, 22): 0.0, (87, 23): 0.0, (87, 24): 0.0, (87, 25): 0.5051001633268003, (87, 26): 0.5051001633268003, (87, 27): 0.5051001633268003, (87, 28): 0.5051001633268003, (87, 29): 0.0, (87, 30): 0.0, (87, 31): 0.0, (87, 32): 0.0, (87, 33): 0.0, (87, 34): 0.0, (87, 35): 0.0, (87, 36): 0.0, (87, 37): 0.0, (87, 38): 0.0, (87, 39): 0.0, (87, 40): 0.0, (87, 41): 0.0, (87, 42): 0.0, (87, 43): 0.0, (87, 44): 0.0, (87, 45): 0.0, (87, 46): 0.0, (87, 47): 0.0, (87, 48): 0.0, (87, 49): 0.0, (87, 50): 0.0, (87, 51): 0.0, (87, 52): 0.0, (87, 53): 0.0, (87, 54): 0.0, (87, 55): 0.0, (87, 56): 0.0, (87, 57): 0.0, (87, 58): 0.0, (87, 59): 0.0, (87, 60): 0.0, (87, 61): 0.0, (87, 62): 0.0, (87, 63): 0.0, (87, 64): 0.0, (87, 65): 0.0, (87, 66): 0.0, (87, 67): 0.0, (87, 68): 0.0, (87, 69): 0.0, (89, 1): 0.0, (89, 2): 0.0, (89, 3): 0.0, (89, 4): 0.0, (89, 5): 0.0, (89, 6): 0.0, (89, 7): 0.0, (89, 8): 0.0, (89, 9): 0.0, (89, 10): 0.0, (89, 11): 0.0, (89, 12): 0.0, (89, 13): 0.0, (89, 14): 0.0, (89, 15): 0.0, (89, 16): 0.0, (89, 17): 0.0, (89, 18): 0.0, (89, 19): 0.0, (89, 20): 0.0, (89, 21): 0.5051001633268003, (89, 22): 0.5051001633268003, (89, 23): 0.5051001633268003, (89, 24): 0.5051001633268003, (89, 25): 0.5051001633268003, (89, 26): 0.5051001633268003, (89, 27): 0.0, (89, 28): 0.0, (89, 29): 0.0, (89, 30): 0.0, (89, 31): 0.0, (89, 32): 0.0, (89, 33): 0.0, (89, 34): 0.0, (89, 35): 0.0, (89, 36): 0.0, (89, 37): 0.0, (89, 38): 0.0, (89, 39): 0.0, (89, 40): 0.0, (89, 41): 0.0, (89, 42): 0.0, (89, 43): 0.0, (89, 44): 0.0, (89, 45): 0.0, (89, 46): 0.0, (89, 47): 0.0, (89, 48): 0.0, (89, 49): 0.0, (89, 50): 0.0, (89, 51): 0.0, (89, 52): 0.0, (89, 53): 0.0, (89, 54): 0.0, (89, 55): 0.0, (89, 56): 0.0, (89, 57): 0.0, (89, 58): 0.0, (89, 59): 0.0, (89, 60): 0.0, (89, 61): 0.0, (89, 62): 0.0, (89, 63): 0.0, (89, 64): 0.0, (89, 65): 0.0, (89, 66): 0.0, (89, 67): 0.0, (89, 68): 0.0, (89, 69): 0.0, (92, 1): 0.0, (92, 2): 0.0, (92, 3): 0.0, (92, 4): 0.0, (92, 5): 0.0, (92, 6): 0.0, (92, 7): 0.0, (92, 8): 0.0, (92, 9): 0.0, (92, 10): 0.0, (92, 11): 0.0, (92, 12): 0.0, (92, 13): 0.0, (92, 14): 0.0, (92, 15): 0.0, (92, 16): 0.0, (92, 17): 0.0, (92, 18): 0.0, (92, 19): 0.0, (92, 20): 0.0, (92, 21): 0.0, (92, 22): 0.0, (92, 23): 0.0, (92, 24): 0.0, (92, 25): 0.0, (92, 26): 0.0, (92, 27): 0.0, (92, 28): 0.0, (92, 29): 0.0, (92, 30): 0.0, (92, 31): 0.0, (92, 32): 0.5051001633268003, (92, 33): 0.5051001633268003, (92, 34): 0.5051001633268003, (92, 35): 0.5051001633268003, (92, 36): 0.5051001633268003, (92, 37): 0.0, (92, 38): 0.0, (92, 39): 0.0, (92, 40): 0.0, (92, 41): 0.0, (92, 42): 0.0, (92, 43): 0.0, (92, 44): 0.0, (92, 45): 0.0, (92, 46): 0.0, (92, 47): 0.0, (92, 48): 0.0, (92, 49): 0.0, (92, 50): 0.0, (92, 51): 0.0, (92, 52): 0.0, (92, 53): 0.0, (92, 54): 0.0, (92, 55): 0.0, (92, 56): 0.0, (92, 57): 0.0, (92, 58): 0.0, (92, 59): 0.0, (92, 60): 0.0, (92, 61): 0.0, (92, 62): 0.0, (92, 63): 0.0, (92, 64): 0.0, (92, 65): 0.0, (92, 66): 0.0, (92, 67): 0.0, (92, 68): 0.0, (92, 69): 0.0, (96, 1): 0.0, (96, 2): 0.0, (96, 3): 0.0, (96, 4): 0.0, (96, 5): 0.0, (96, 6): 0.0, (96, 7): 0.0, (96, 8): 0.0, (96, 9): 0.0, (96, 10): 0.0, (96, 11): 0.0, (96, 12): 0.0, (96, 13): 0.0, (96, 14): 0.0, (96, 15): 0.0, (96, 16): 0.0, (96, 17): 0.0, (96, 18): 0.0, (96, 19): 0.0, (96, 20): 0.0, (96, 21): 0.0, (96, 22): 0.0, (96, 23): 0.0, (96, 24): 0.5051001633268003, (96, 25): 0.5051001633268003, (96, 26): 0.5051001633268003, (96, 27): 0.0, (96, 28): 0.0, (96, 29): 0.0, (96, 30): 0.0, (96, 31): 0.0, (96, 32): 0.0, (96, 33): 0.0, (96, 34): 0.0, (96, 35): 0.0, (96, 36): 0.0, (96, 37): 0.0, (96, 38): 0.0, (96, 39): 0.0, (96, 40): 0.0, (96, 41): 0.0, (96, 42): 0.0, (96, 43): 0.0, (96, 44): 0.0, (96, 45): 0.0, (96, 46): 0.0, (96, 47): 0.0, (96, 48): 0.0, (96, 49): 0.0, (96, 50): 0.0, (96, 51): 0.0, (96, 52): 0.0, (96, 53): 0.0, (96, 54): 0.0, (96, 55): 0.0, (96, 56): 0.0, (96, 57): 0.0, (96, 58): 0.0, (96, 59): 0.0, (96, 60): 0.0, (96, 61): 0.0, (96, 62): 0.0, (96, 63): 0.0, (96, 64): 0.0, (96, 65): 0.0, (96, 66): 0.0, (96, 67): 0.0, (96, 68): 0.0, (96, 69): 0.0, (98, 1): 0.5051001633268003, (98, 2): 0.5051001633268003, (98, 3): 0.5051001633268003, (98, 4): 0.5051001633268003, (98, 5): 0.5051001633268003, (98, 6): 0.5051001633268003, (98, 7): 0.0, (98, 8): 0.0, (98, 9): 0.0, (98, 10): 0.0, (98, 11): 0.0, (98, 12): 0.0, (98, 13): 0.0, (98, 14): 0.0, (98, 15): 0.0, (98, 16): 0.0, (98, 17): 0.0, (98, 18): 0.0, (98, 19): 0.0, (98, 20): 0.0, (98, 21): 0.0, (98, 22): 0.0, (98, 23): 0.0, (98, 24): 0.0, (98, 25): 0.0, (98, 26): 0.0, (98, 27): 0.0, (98, 28): 0.0, (98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{(1, 1): 0.0, (1, 2): 0.0, (1, 3): 0.0, (1, 4): 0.0, (1, 5): 0.0, (1, 6): 0.0, (1, 7): 0.0, (1, 8): 0.0, (1, 9): 0.0, (1, 10): 0.0, (1, 11): 0.0, (1, 12): 0.0, (1, 13): 0.0, (1, 14): 0.0, (1, 15): 0.0, (1, 16): 2.0, (1, 17): 4.0, (1, 18): 6.0, (1, 19): 8.0, (1, 20): 10.0, (1, 21): 11.0, (1, 22): 12.0, (1, 23): 14.0, (1, 24): 15.0, (1, 25): 16.0, (1, 26): 18.0, (1, 27): 20.0, (1, 28): 20.0, (1, 29): 20.0, (1, 30): 20.0, (1, 31): 20.0, (1, 32): 20.0, (1, 33): 20.0, (1, 34): 20.0, (1, 35): 20.0, (1, 36): 20.0, (1, 37): 20.0, (1, 38): 20.0, (1, 39): 20.0, (1, 40): 20.0, (1, 41): 20.0, (1, 42): 20.0, (1, 43): 20.0, (1, 44): 20.0, (1, 45): 20.0, (1, 46): 20.0, (1, 47): 20.0, (1, 48): 20.0, (1, 49): 20.0, (1, 50): 20.0, (1, 51): 20.0, (1, 52): 20.0, (1, 53): 20.0, (1, 54): 20.0, (1, 55): 20.0, (1, 56): 20.0, (1, 57): 20.0, (1, 58): 20.0, (1, 59): 20.0, (1, 60): 20.0, (1, 61): 20.0, (1, 62): 20.0, (1, 63): 20.0, (1, 64): 20.0, (1, 65): 20.0, (1, 66): 20.0, (1, 67): 20.0, (1, 68): 20.0, (1, 69): 20.0, (2, 1): 0.0, (2, 2): 0.0, (2, 3): 0.0, (2, 4): 0.0, (2, 5): 0.0, (2, 6): 0.0, (2, 7): 0.0, (2, 8): 0.0, (2, 9): 0.0, (2, 10): 0.0, (2, 11): 0.0, (2, 12): 0.0, (2, 13): 0.0, (2, 14): 0.0, (2, 15): 1.0, (2, 16): 2.0, (2, 17): 2.0, (2, 18): 3.0, (2, 19): 4.0, (2, 20): 5.0, (2, 21): 6.0, (2, 22): 7.0, (2, 23): 8.0, (2, 24): 8.0, (2, 25): 9.0, (2, 26): 10.0, (2, 27): 11.0, (2, 28): 12.0, (2, 29): 13.0, (2, 30): 14.0, (2, 31): 14.0, (2, 32): 14.0, (2, 33): 14.0, (2, 34): 14.0, (2, 35): 14.0, (2, 36): 14.0, (2, 37): 14.0, (2, 38): 14.0, (2, 39): 14.0, (2, 40): 14.0, (2, 41): 14.0, (2, 42): 14.0, (2, 43): 14.0, (2, 44): 14.0, (2, 45): 14.0, (2, 46): 14.0, (2, 47): 14.0, (2, 48): 14.0, (2, 49): 14.0, (2, 50): 14.0, (2, 51): 14.0, (2, 52): 14.0, (2, 53): 14.0, (2, 54): 14.0, (2, 55): 14.0, (2, 56): 14.0, (2, 57): 14.0, (2, 58): 14.0, (2, 59): 14.0, (2, 60): 14.0, (2, 61): 14.0, (2, 62): 14.0, (2, 63): 14.0, (2, 64): 14.0, (2, 65): 14.0, (2, 66): 14.0, (2, 67): 14.0, (2, 68): 14.0, (2, 69): 14.0, (6, 1): 0.0, (6, 2): 0.0, (6, 3): 0.0, (6, 4): 0.0, (6, 5): 0.0, (6, 6): 0.0, (6, 7): 0.0, (6, 8): 0.0, (6, 9): 0.0, (6, 10): 0.0, (6, 11): 0.0, (6, 12): 0.0, (6, 13): 0.0, (6, 14): 0.0, (6, 15): 0.0, (6, 16): 0.0, (6, 17): 0.0, (6, 18): 0.0, (6, 19): 0.0, (6, 20): 0.0, (6, 21): 0.0, (6, 22): 1.0, (6, 23): 2.0, (6, 24): 3.0, (6, 25): 4.0, (6, 26): 5.0, (6, 27): 6.0, (6, 28): 6.0, (6, 29): 7.0, (6, 30): 8.0, (6, 31): 9.0, (6, 32): 10.0, (6, 33): 11.0, (6, 34): 12.0, (6, 35): 12.0, (6, 36): 13.0, (6, 37): 14.0, (6, 38): 15.0, (6, 39): 16.0, (6, 40): 17.0, (6, 41): 18.0, (6, 42): 18.0, (6, 43): 19.0, (6, 44): 20.0, (6, 45): 21.0, (6, 46): 21.0, (6, 47): 22.0, (6, 48): 22.0, (6, 49): 22.0, (6, 50): 22.0, (6, 51): 22.0, (6, 52): 22.0, (6, 53): 22.0, (6, 54): 22.0, (6, 55): 22.0, (6, 56): 22.0, (6, 57): 22.0, (6, 58): 22.0, (6, 59): 22.0, (6, 60): 22.0, (6, 61): 22.0, (6, 62): 22.0, (6, 63): 22.0, (6, 64): 22.0, (6, 65): 22.0, (6, 66): 22.0, (6, 67): 22.0, (6, 68): 22.0, (6, 69): 22.0, (7, 1): 0.0, (7, 2): 0.0, (7, 3): 0.0, (7, 4): 0.0, (7, 5): 0.0, (7, 6): 0.0, (7, 7): 0.0, (7, 8): 0.0, (7, 9): 0.0, (7, 10): 0.0, (7, 11): 0.0, (7, 12): 0.0, (7, 13): 0.0, (7, 14): 0.0, (7, 15): 0.0, (7, 16): 0.0, (7, 17): 0.0, (7, 18): 0.0, (7, 19): 0.0, (7, 20): 0.0, (7, 21): 0.0, (7, 22): 0.0, (7, 23): 0.0, (7, 24): 0.0, (7, 25): 0.0, (7, 26): 0.0, (7, 27): 0.0, (7, 28): 0.0, (7, 29): 0.0, (7, 30): 1.0, (7, 31): 2.0, (7, 32): 3.0, (7, 33): 4.0, (7, 34): 5.0, (7, 35): 5.0, (7, 36): 6.0, (7, 37): 7.0, (7, 38): 8.0, (7, 39): 9.0, (7, 40): 10.0, (7, 41): 11.0, (7, 42): 11.0, (7, 43): 12.0, (7, 44): 13.0, (7, 45): 14.0, (7, 46): 15.0, (7, 47): 16.0, (7, 48): 16.0, (7, 49): 16.0, (7, 50): 16.0, (7, 51): 16.0, (7, 52): 16.0, (7, 53): 16.0, (7, 54): 16.0, (7, 55): 16.0, (7, 56): 16.0, (7, 57): 16.0, (7, 58): 16.0, (7, 59): 16.0, (7, 60): 16.0, (7, 61): 16.0, (7, 62): 16.0, (7, 63): 16.0, (7, 64): 16.0, (7, 65): 16.0, (7, 66): 16.0, (7, 67): 16.0, (7, 68): 16.0, (7, 69): 16.0, (16, 1): 0.0, (16, 2): 0.0, (16, 3): 0.0, (16, 4): 0.0, (16, 5): 0.0, (16, 6): 0.0, (16, 7): 0.0, (16, 8): 0.0, (16, 9): 0.0, (16, 10): 0.0, (16, 11): 0.0, (16, 12): 0.0, (16, 13): 0.0, (16, 14): 0.0, (16, 15): 0.0, (16, 16): 0.0, (16, 17): 1.0, (16, 18): 2.0, (16, 19): 3.0, (16, 20): 3.0, (16, 21): 3.0, (16, 22): 3.0, (16, 23): 3.0, (16, 24): 3.0, (16, 25): 3.0, (16, 26): 3.0, (16, 27): 3.0, (16, 28): 3.0, (16, 29): 3.0, (16, 30): 3.0, (16, 31): 3.0, (16, 32): 3.0, (16, 33): 3.0, (16, 34): 3.0, (16, 35): 3.0, (16, 36): 3.0, (16, 37): 3.0, (16, 38): 3.0, (16, 39): 3.0, (16, 40): 3.0, (16, 41): 3.0, (16, 42): 3.0, (16, 43): 3.0, (16, 44): 3.0, (16, 45): 3.0, (16, 46): 3.0, (16, 47): 3.0, (16, 48): 3.0, (16, 49): 3.0, (16, 50): 3.0, (16, 51): 3.0, (16, 52): 3.0, (16, 53): 3.0, (16, 54): 3.0, (16, 55): 3.0, (16, 56): 3.0, (16, 57): 3.0, (16, 58): 3.0, (16, 59): 3.0, (16, 60): 3.0, (16, 61): 3.0, (16, 62): 3.0, (16, 63): 3.0, (16, 64): 3.0, (16, 65): 3.0, (16, 66): 3.0, (16, 67): 3.0, (16, 68): 3.0, (16, 69): 3.0, (26, 1): 0.0, (26, 2): 0.0, (26, 3): 0.0, (26, 4): 0.0, (26, 5): 0.0, (26, 6): 0.0, (26, 7): 0.0, (26, 8): 0.0, (26, 9): 0.0, (26, 10): 0.0, (26, 11): 0.0, (26, 12): 0.0, (26, 13): 0.0, (26, 14): 0.0, (26, 15): 0.0, (26, 16): 0.0, (26, 17): 0.0, (26, 18): 0.0, (26, 19): 0.0, (26, 20): 0.0, (26, 21): 0.0, (26, 22): 0.0, (26, 23): 0.0, (26, 24): 0.0, (26, 25): 1.0, (26, 26): 2.0, (26, 27): 3.0, (26, 28): 4.0, (26, 29): 4.0, (26, 30): 5.0, (26, 31): 6.0, (26, 32): 7.0, (26, 33): 8.0, (26, 34): 9.0, (26, 35): 10.0, (26, 36): 10.0, (26, 37): 11.0, (26, 38): 12.0, (26, 39): 12.0, (26, 40): 12.0, (26, 41): 12.0, (26, 42): 12.0, (26, 43): 12.0, (26, 44): 12.0, (26, 45): 12.0, (26, 46): 12.0, (26, 47): 12.0, (26, 48): 12.0, (26, 49): 12.0, (26, 50): 12.0, (26, 51): 12.0, (26, 52): 12.0, (26, 53): 12.0, (26, 54): 12.0, (26, 55): 12.0, (26, 56): 12.0, (26, 57): 12.0, (26, 58): 12.0, (26, 59): 12.0, (26, 60): 12.0, (26, 61): 12.0, (26, 62): 12.0, (26, 63): 12.0, (26, 64): 12.0, (26, 65): 12.0, (26, 66): 12.0, (26, 67): 12.0, (26, 68): 12.0, (26, 69): 12.0, (35, 1): 0.0, (35, 2): 0.0, (35, 3): 0.0, (35, 4): 0.0, (35, 5): 0.0, (35, 6): 2.0, (35, 7): 3.0, (35, 8): 5.0, (35, 9): 6.0, (35, 10): 8.0, (35, 11): 10.0, (35, 12): 12.0, (35, 13): 14.0, (35, 14): 15.0, (35, 15): 17.0, (35, 16): 17.0, (35, 17): 17.0, (35, 18): 17.0, (35, 19): 17.0, (35, 20): 17.0, (35, 21): 17.0, (35, 22): 17.0, (35, 23): 17.0, (35, 24): 17.0, (35, 25): 17.0, (35, 26): 17.0, (35, 27): 17.0, (35, 28): 17.0, (35, 29): 17.0, (35, 30): 17.0, (35, 31): 17.0, (35, 32): 17.0, (35, 33): 17.0, (35, 34): 17.0, (35, 35): 17.0, (35, 36): 17.0, (35, 37): 17.0, (35, 38): 17.0, (35, 39): 17.0, (35, 40): 17.0, (35, 41): 17.0, (35, 42): 17.0, (35, 43): 17.0, (35, 44): 17.0, (35, 45): 17.0, (35, 46): 17.0, (35, 47): 17.0, (35, 48): 17.0, (35, 49): 17.0, (35, 50): 17.0, (35, 51): 17.0, (35, 52): 17.0, (35, 53): 17.0, (35, 54): 17.0, (35, 55): 17.0, (35, 56): 17.0, (35, 57): 17.0, (35, 58): 17.0, (35, 59): 17.0, (35, 60): 17.0, (35, 61): 17.0, (35, 62): 17.0, (35, 63): 17.0, (35, 64): 17.0, (35, 65): 17.0, (35, 66): 17.0, (35, 67): 17.0, (35, 68): 17.0, (35, 69): 17.0, (38, 1): 0.0, (38, 2): 0.0, (38, 3): 0.0, (38, 4): 0.0, (38, 5): 1.0, (38, 6): 2.0, (38, 7): 3.0, (38, 8): 3.0, (38, 9): 4.0, (38, 10): 4.0, (38, 11): 5.0, (38, 12): 5.0, (38, 13): 5.0, (38, 14): 5.0, (38, 15): 5.0, (38, 16): 5.0, (38, 17): 5.0, (38, 18): 5.0, (38, 19): 5.0, (38, 20): 5.0, (38, 21): 5.0, (38, 22): 5.0, (38, 23): 5.0, (38, 24): 5.0, (38, 25): 5.0, (38, 26): 5.0, (38, 27): 5.0, (38, 28): 5.0, (38, 29): 5.0, (38, 30): 5.0, (38, 31): 5.0, (38, 32): 5.0, (38, 33): 5.0, (38, 34): 5.0, (38, 35): 5.0, (38, 36): 5.0, (38, 37): 5.0, (38, 38): 5.0, (38, 39): 5.0, (38, 40): 5.0, (38, 41): 5.0, (38, 42): 5.0, (38, 43): 5.0, (38, 44): 5.0, (38, 45): 5.0, (38, 46): 5.0, (38, 47): 5.0, (38, 48): 5.0, (38, 49): 5.0, (38, 50): 5.0, (38, 51): 5.0, (38, 52): 5.0, (38, 53): 5.0, (38, 54): 5.0, (38, 55): 5.0, (38, 56): 5.0, (38, 57): 5.0, (38, 58): 5.0, (38, 59): 5.0, (38, 60): 5.0, (38, 61): 5.0, (38, 62): 5.0, (38, 63): 5.0, (38, 64): 5.0, (38, 65): 5.0, (38, 66): 5.0, (38, 67): 5.0, (38, 68): 5.0, (38, 69): 5.0, (39, 1): 0.0, (39, 2): 0.0, (39, 3): 0.0, (39, 4): 0.0, (39, 5): 0.0, (39, 6): 0.0, (39, 7): 0.0, (39, 8): 0.0, (39, 9): 0.0, (39, 10): 0.0, (39, 11): 0.0, (39, 12): 0.0, (39, 13): 0.0, (39, 14): 1.0, (39, 15): 2.0, (39, 16): 2.0, (39, 17): 3.0, (39, 18): 4.0, (39, 19): 4.0, (39, 20): 5.0, (39, 21): 6.0, (39, 22): 7.0, (39, 23): 7.0, (39, 24): 7.0, (39, 25): 7.0, (39, 26): 7.0, (39, 27): 7.0, (39, 28): 7.0, (39, 29): 7.0, (39, 30): 7.0, (39, 31): 7.0, (39, 32): 7.0, (39, 33): 7.0, (39, 34): 7.0, (39, 35): 7.0, (39, 36): 7.0, (39, 37): 7.0, (39, 38): 7.0, (39, 39): 7.0, (39, 40): 7.0, (39, 41): 7.0, (39, 42): 7.0, (39, 43): 7.0, (39, 44): 7.0, (39, 45): 7.0, (39, 46): 7.0, (39, 47): 7.0, (39, 48): 7.0, (39, 49): 7.0, (39, 50): 7.0, (39, 51): 7.0, (39, 52): 7.0, (39, 53): 7.0, (39, 54): 7.0, (39, 55): 7.0, (39, 56): 7.0, (39, 57): 7.0, (39, 58): 7.0, (39, 59): 7.0, (39, 60): 7.0, (39, 61): 7.0, (39, 62): 7.0, (39, 63): 7.0, (39, 64): 7.0, (39, 65): 7.0, (39, 66): 7.0, (39, 67): 7.0, (39, 68): 7.0, (39, 69): 7.0, (41, 1): 0.0, (41, 2): 0.0, (41, 3): 0.0, (41, 4): 0.0, (41, 5): 0.0, (41, 6): 0.0, (41, 7): 0.0, (41, 8): 0.0, (41, 9): 0.0, (41, 10): 0.0, (41, 11): 0.0, (41, 12): 0.0, (41, 13): 0.0, (41, 14): 0.0, (41, 15): 0.0, (41, 16): 0.0, (41, 17): 0.0, (41, 18): 0.0, (41, 19): 0.0, (41, 20): 0.0, (41, 21): 0.0, (41, 22): 0.0, (41, 23): 0.0, (41, 24): 0.0, (41, 25): 0.0, (41, 26): 0.0, (41, 27): 0.0, (41, 28): 1.0, (41, 29): 2.0, (41, 30): 2.0, (41, 31): 3.0, (41, 32): 4.0, (41, 33): 5.0, (41, 34): 6.0, (41, 35): 6.0, (41, 36): 7.0, (41, 37): 7.0, (41, 38): 7.0, (41, 39): 7.0, (41, 40): 7.0, (41, 41): 7.0, (41, 42): 7.0, (41, 43): 7.0, (41, 44): 7.0, (41, 45): 7.0, (41, 46): 7.0, (41, 47): 7.0, (41, 48): 7.0, (41, 49): 7.0, (41, 50): 7.0, (41, 51): 7.0, (41, 52): 7.0, (41, 53): 7.0, (41, 54): 7.0, (41, 55): 7.0, (41, 56): 7.0, (41, 57): 7.0, (41, 58): 7.0, (41, 59): 7.0, (41, 60): 7.0, (41, 61): 7.0, (41, 62): 7.0, (41, 63): 7.0, (41, 64): 7.0, (41, 65): 7.0, (41, 66): 7.0, (41, 67): 7.0, (41, 68): 7.0, (41, 69): 7.0, (42, 1): 0.0, (42, 2): 0.0, (42, 3): 0.0, (42, 4): 0.0, (42, 5): 0.0, (42, 6): 0.0, (42, 7): 0.0, (42, 8): 0.0, (42, 9): 0.0, (42, 10): 0.0, (42, 11): 0.0, (42, 12): 0.0, (42, 13): 0.0, (42, 14): 0.0, (42, 15): 0.0, (42, 16): 0.0, (42, 17): 0.0, (42, 18): 0.0, (42, 19): 0.0, (42, 20): 0.0, (42, 21): 0.0, (42, 22): 1.0, (42, 23): 2.0, (42, 24): 2.0, (42, 25): 3.0, (42, 26): 4.0, (42, 27): 4.0, (42, 28): 5.0, (42, 29): 6.0, (42, 30): 7.0, (42, 31): 7.0, (42, 32): 7.0, (42, 33): 7.0, (42, 34): 7.0, (42, 35): 7.0, (42, 36): 7.0, (42, 37): 7.0, (42, 38): 7.0, (42, 39): 7.0, (42, 40): 7.0, (42, 41): 7.0, (42, 42): 7.0, (42, 43): 7.0, (42, 44): 7.0, (42, 45): 7.0, (42, 46): 7.0, (42, 47): 7.0, (42, 48): 7.0, (42, 49): 7.0, (42, 50): 7.0, (42, 51): 7.0, (42, 52): 7.0, (42, 53): 7.0, (42, 54): 7.0, (42, 55): 7.0, (42, 56): 7.0, (42, 57): 7.0, (42, 58): 7.0, (42, 59): 7.0, (42, 60): 7.0, (42, 61): 7.0, (42, 62): 7.0, (42, 63): 7.0, (42, 64): 7.0, (42, 65): 7.0, (42, 66): 7.0, (42, 67): 7.0, (42, 68): 7.0, (42, 69): 7.0, (43, 1): 0.0, (43, 2): 0.0, (43, 3): 0.0, (43, 4): 0.0, (43, 5): 0.0, (43, 6): 0.0, (43, 7): 0.0, (43, 8): 0.0, (43, 9): 0.0, (43, 10): 0.0, (43, 11): 0.0, (43, 12): 0.0, (43, 13): 0.0, (43, 14): 0.0, (43, 15): 0.0, (43, 16): 0.0, (43, 17): 0.0, (43, 18): 0.0, (43, 19): 0.0, (43, 20): 0.0, (43, 21): 0.0, (43, 22): 1.0, (43, 23): 2.0, (43, 24): 3.0, (43, 25): 4.0, (43, 26): 5.0, (43, 27): 5.0, (43, 28): 5.0, (43, 29): 5.0, (43, 30): 5.0, (43, 31): 5.0, (43, 32): 5.0, (43, 33): 5.0, (43, 34): 5.0, (43, 35): 5.0, (43, 36): 5.0, (43, 37): 5.0, (43, 38): 5.0, (43, 39): 5.0, (43, 40): 5.0, (43, 41): 5.0, (43, 42): 5.0, (43, 43): 5.0, (43, 44): 5.0, (43, 45): 5.0, (43, 46): 5.0, (43, 47): 5.0, (43, 48): 5.0, (43, 49): 5.0, (43, 50): 5.0, (43, 51): 5.0, (43, 52): 5.0, (43, 53): 5.0, (43, 54): 5.0, (43, 55): 5.0, (43, 56): 5.0, (43, 57): 5.0, (43, 58): 5.0, (43, 59): 5.0, (43, 60): 5.0, (43, 61): 5.0, (43, 62): 5.0, (43, 63): 5.0, (43, 64): 5.0, (43, 65): 5.0, (43, 66): 5.0, (43, 67): 5.0, (43, 68): 5.0, (43, 69): 5.0, (46, 1): 0.0, (46, 2): 0.0, (46, 3): 0.0, (46, 4): 0.0, (46, 5): 1.0, (46, 6): 2.0, (46, 7): 3.0, (46, 8): 4.0, (46, 9): 4.0, (46, 10): 4.0, (46, 11): 5.0, (46, 12): 6.0, (46, 13): 7.0, (46, 14): 8.0, (46, 15): 9.0, (46, 16): 9.0, (46, 17): 9.0, (46, 18): 9.0, (46, 19): 9.0, (46, 20): 9.0, (46, 21): 9.0, (46, 22): 9.0, (46, 23): 9.0, (46, 24): 9.0, (46, 25): 9.0, (46, 26): 9.0, (46, 27): 9.0, (46, 28): 9.0, (46, 29): 9.0, (46, 30): 9.0, (46, 31): 9.0, (46, 32): 9.0, (46, 33): 9.0, (46, 34): 9.0, (46, 35): 9.0, (46, 36): 9.0, (46, 37): 9.0, (46, 38): 9.0, (46, 39): 9.0, (46, 40): 9.0, (46, 41): 9.0, (46, 42): 9.0, (46, 43): 9.0, (46, 44): 9.0, (46, 45): 9.0, (46, 46): 9.0, (46, 47): 9.0, (46, 48): 9.0, (46, 49): 9.0, (46, 50): 9.0, (46, 51): 9.0, (46, 52): 9.0, (46, 53): 9.0, (46, 54): 9.0, (46, 55): 9.0, (46, 56): 9.0, (46, 57): 9.0, (46, 58): 9.0, (46, 59): 9.0, (46, 60): 9.0, (46, 61): 9.0, (46, 62): 9.0, (46, 63): 9.0, (46, 64): 9.0, (46, 65): 9.0, (46, 66): 9.0, (46, 67): 9.0, (46, 68): 9.0, (46, 69): 9.0, (48, 1): 0.0, (48, 2): 0.0, (48, 3): 0.0, (48, 4): 0.0, (48, 5): 0.0, (48, 6): 0.0, (48, 7): 0.0, (48, 8): 0.0, (48, 9): 0.0, (48, 10): 0.0, (48, 11): 0.0, (48, 12): 0.0, (48, 13): 0.0, (48, 14): 0.0, (48, 15): 0.0, (48, 16): 0.0, (48, 17): 0.0, (48, 18): 0.0, (48, 19): 0.0, (48, 20): 0.0, (48, 21): 0.0, (48, 22): 0.0, (48, 23): 0.0, (48, 24): 0.0, (48, 25): 0.0, (48, 26): 1.0, (48, 27): 2.0, (48, 28): 3.0, (48, 29): 4.0, (48, 30): 4.0, (48, 31): 4.0, (48, 32): 4.0, (48, 33): 4.0, (48, 34): 4.0, (48, 35): 4.0, (48, 36): 4.0, (48, 37): 4.0, (48, 38): 4.0, (48, 39): 4.0, (48, 40): 4.0, (48, 41): 4.0, (48, 42): 4.0, (48, 43): 4.0, (48, 44): 4.0, (48, 45): 4.0, (48, 46): 4.0, (48, 47): 4.0, (48, 48): 4.0, (48, 49): 4.0, (48, 50): 4.0, (48, 51): 4.0, (48, 52): 4.0, (48, 53): 4.0, (48, 54): 4.0, (48, 55): 4.0, (48, 56): 4.0, (48, 57): 4.0, (48, 58): 4.0, (48, 59): 4.0, (48, 60): 4.0, (48, 61): 4.0, (48, 62): 4.0, (48, 63): 4.0, (48, 64): 4.0, (48, 65): 4.0, (48, 66): 4.0, (48, 67): 4.0, (48, 68): 4.0, (48, 69): 4.0, (49, 1): 0.0, (49, 2): 0.0, (49, 3): 0.0, (49, 4): 0.0, (49, 5): 0.0, (49, 6): 0.0, (49, 7): 0.0, (49, 8): 0.0, (49, 9): 1.0, (49, 10): 2.0, (49, 11): 3.0, (49, 12): 4.0, (49, 13): 5.0, (49, 14): 5.5075500204164625, (49, 15): 6.5075500204164625, (49, 16): 7.5075500204164625, (49, 17): 8.507550020416463, (49, 18): 8.507550020416463, (49, 19): 8.507550020416463, (49, 20): 8.507550020416463, (49, 21): 8.507550020416463, (49, 22): 8.507550020416463, (49, 23): 8.507550020416463, (49, 24): 8.507550020416463, (49, 25): 8.507550020416463, (49, 26): 8.507550020416463, (49, 27): 8.507550020416463, (49, 28): 8.507550020416463, (49, 29): 8.507550020416463, (49, 30): 8.507550020416463, (49, 31): 8.507550020416463, (49, 32): 8.507550020416463, (49, 33): 8.507550020416463, (49, 34): 8.507550020416463, (49, 35): 8.507550020416463, (49, 36): 8.507550020416463, (49, 37): 8.507550020416463, (49, 38): 8.507550020416463, (49, 39): 8.507550020416463, (49, 40): 8.507550020416463, (49, 41): 8.507550020416463, (49, 42): 8.507550020416463, (49, 43): 8.507550020416463, (49, 44): 8.507550020416463, (49, 45): 8.507550020416463, (49, 46): 8.507550020416463, (49, 47): 8.507550020416463, (49, 48): 8.507550020416463, (49, 49): 8.507550020416463, (49, 50): 8.507550020416463, (49, 51): 8.507550020416463, (49, 52): 8.507550020416463, (49, 53): 8.507550020416463, (49, 54): 8.507550020416463, (49, 55): 8.507550020416463, (49, 56): 8.507550020416463, (49, 57): 8.507550020416463, (49, 58): 8.507550020416463, (49, 59): 8.507550020416463, (49, 60): 8.507550020416463, (49, 61): 8.507550020416463, (49, 62): 8.507550020416463, (49, 63): 8.507550020416463, (49, 64): 8.507550020416463, (49, 65): 8.507550020416463, (49, 66): 8.507550020416463, (49, 67): 8.507550020416463, (49, 68): 8.507550020416463, (49, 69): 8.507550020416463, (51, 1): 0.0, (51, 2): 0.0, (51, 3): 0.0, (51, 4): 0.0, (51, 5): 0.0, (51, 6): 0.0, (51, 7): 0.0, (51, 8): 0.0, (51, 9): 0.0, (51, 10): 0.0, (51, 11): 0.0, (51, 12): 0.0, (51, 13): 1.0, (51, 14): 2.0, (51, 15): 3.0, (51, 16): 4.0, (51, 17): 4.5075500204164625, (51, 18): 5.5075500204164625, (51, 19): 6.5075500204164625, (51, 20): 7.5075500204164625, (51, 21): 7.5075500204164625, (51, 22): 7.5075500204164625, (51, 23): 7.5075500204164625, (51, 24): 7.5075500204164625, (51, 25): 7.5075500204164625, (51, 26): 7.5075500204164625, (51, 27): 7.5075500204164625, (51, 28): 7.5075500204164625, (51, 29): 7.5075500204164625, (51, 30): 7.5075500204164625, (51, 31): 7.5075500204164625, (51, 32): 7.5075500204164625, (51, 33): 7.5075500204164625, (51, 34): 7.5075500204164625, (51, 35): 7.5075500204164625, (51, 36): 7.5075500204164625, (51, 37): 7.5075500204164625, (51, 38): 7.5075500204164625, (51, 39): 7.5075500204164625, (51, 40): 7.5075500204164625, (51, 41): 7.5075500204164625, (51, 42): 7.5075500204164625, (51, 43): 7.5075500204164625, (51, 44): 7.5075500204164625, (51, 45): 7.5075500204164625, (51, 46): 7.5075500204164625, (51, 47): 7.5075500204164625, (51, 48): 7.5075500204164625, (51, 49): 7.5075500204164625, (51, 50): 7.5075500204164625, (51, 51): 7.5075500204164625, (51, 52): 7.5075500204164625, (51, 53): 7.5075500204164625, (51, 54): 7.5075500204164625, (51, 55): 7.5075500204164625, (51, 56): 7.5075500204164625, (51, 57): 7.5075500204164625, (51, 58): 7.5075500204164625, (51, 59): 7.5075500204164625, (51, 60): 7.5075500204164625, (51, 61): 7.5075500204164625, (51, 62): 7.5075500204164625, (51, 63): 7.5075500204164625, (51, 64): 7.5075500204164625, (51, 65): 7.5075500204164625, (51, 66): 7.5075500204164625, (51, 67): 7.5075500204164625, (51, 68): 7.5075500204164625, (51, 69): 7.5075500204164625, (52, 1): 0.0, (52, 2): 0.0, (52, 3): 1.0, (52, 4): 2.0, (52, 5): 3.0, (52, 6): 4.0, (52, 7): 5.0, (52, 8): 5.0, (52, 9): 5.0, (52, 10): 6.0, (52, 11): 7.0, (52, 12): 8.0, (52, 13): 8.0, (52, 14): 8.0, (52, 15): 8.0, (52, 16): 8.0, (52, 17): 8.0, (52, 18): 8.0, (52, 19): 8.0, (52, 20): 8.0, (52, 21): 8.0, (52, 22): 8.0, (52, 23): 8.0, (52, 24): 8.0, (52, 25): 8.0, (52, 26): 8.0, (52, 27): 8.0, (52, 28): 8.0, (52, 29): 8.0, (52, 30): 8.0, (52, 31): 8.0, (52, 32): 8.0, (52, 33): 8.0, (52, 34): 8.0, (52, 35): 8.0, (52, 36): 8.0, (52, 37): 8.0, (52, 38): 8.0, (52, 39): 8.0, (52, 40): 8.0, (52, 41): 8.0, (52, 42): 8.0, (52, 43): 8.0, (52, 44): 8.0, (52, 45): 8.0, (52, 46): 8.0, (52, 47): 8.0, (52, 48): 8.0, (52, 49): 8.0, (52, 50): 8.0, (52, 51): 8.0, (52, 52): 8.0, (52, 53): 8.0, (52, 54): 8.0, (52, 55): 8.0, (52, 56): 8.0, (52, 57): 8.0, (52, 58): 8.0, (52, 59): 8.0, (52, 60): 8.0, (52, 61): 8.0, (52, 62): 8.0, (52, 63): 8.0, (52, 64): 8.0, (52, 65): 8.0, (52, 66): 8.0, (52, 67): 8.0, (52, 68): 8.0, (52, 69): 8.0, (57, 1): 0.0, (57, 2): 0.0, (57, 3): 0.0, (57, 4): 0.0, (57, 5): 0.0, (57, 6): 0.0, (57, 7): 0.0, (57, 8): 0.0, (57, 9): 0.0, (57, 10): 0.0, (57, 11): 0.0, (57, 12): 0.0, (57, 13): 0.0, (57, 14): 0.0, (57, 15): 0.0, (57, 16): 0.0, (57, 17): 0.0, (57, 18): 0.0, (57, 19): 0.0, (57, 20): 0.0, (57, 21): 0.0, (57, 22): 0.0, (57, 23): 0.0, (57, 24): 1.0, (57, 25): 2.0, (57, 26): 2.0, (57, 27): 3.0, (57, 28): 4.0, (57, 29): 5.0, (57, 30): 5.0, (57, 31): 6.0, (57, 32): 7.0, (57, 33): 8.0, (57, 34): 9.0, (57, 35): 9.0, (57, 36): 9.0, (57, 37): 9.0, (57, 38): 9.0, (57, 39): 9.0, (57, 40): 9.0, (57, 41): 9.0, (57, 42): 9.0, (57, 43): 9.0, (57, 44): 9.0, (57, 45): 9.0, (57, 46): 9.0, (57, 47): 9.0, (57, 48): 9.0, (57, 49): 9.0, (57, 50): 9.0, (57, 51): 9.0, (57, 52): 9.0, (57, 53): 9.0, (57, 54): 9.0, (57, 55): 9.0, (57, 56): 9.0, (57, 57): 9.0, (57, 58): 9.0, (57, 59): 9.0, (57, 60): 9.0, (57, 61): 9.0, (57, 62): 9.0, (57, 63): 9.0, (57, 64): 9.0, (57, 65): 9.0, (57, 66): 9.0, (57, 67): 9.0, (57, 68): 9.0, (57, 69): 9.0, (70, 1): 0.0, (70, 2): 0.0, (70, 3): 0.0, (70, 4): 0.0, (70, 5): 0.0, (70, 6): 0.0, (70, 7): 0.0, (70, 8): 0.0, (70, 9): 0.0, (70, 10): 0.0, (70, 11): 0.0, (70, 12): 0.0, (70, 13): 0.0, (70, 14): 0.0, (70, 15): 0.0, (70, 16): 0.0, (70, 17): 1.0, (70, 18): 2.0, (70, 19): 3.0, (70, 20): 4.0, (70, 21): 5.0, (70, 22): 6.0, (70, 23): 6.0, (70, 24): 7.0, (70, 25): 7.0, (70, 26): 8.0, (70, 27): 8.0, (70, 28): 8.0, (70, 29): 8.0, (70, 30): 8.0, (70, 31): 8.0, (70, 32): 8.0, (70, 33): 8.0, (70, 34): 8.0, (70, 35): 8.0, (70, 36): 8.0, (70, 37): 8.0, (70, 38): 8.0, (70, 39): 8.0, (70, 40): 8.0, (70, 41): 8.0, (70, 42): 8.0, (70, 43): 8.0, (70, 44): 8.0, (70, 45): 8.0, (70, 46): 8.0, (70, 47): 8.0, (70, 48): 8.0, (70, 49): 8.0, (70, 50): 8.0, (70, 51): 8.0, (70, 52): 8.0, (70, 53): 8.0, (70, 54): 8.0, (70, 55): 8.0, (70, 56): 8.0, (70, 57): 8.0, (70, 58): 8.0, (70, 59): 8.0, (70, 60): 8.0, (70, 61): 8.0, (70, 62): 8.0, (70, 63): 8.0, (70, 64): 8.0, (70, 65): 8.0, (70, 66): 8.0, (70, 67): 8.0, (70, 68): 8.0, (70, 69): 8.0, (73, 1): 0.0, (73, 2): 0.0, (73, 3): 0.0, (73, 4): 0.0, (73, 5): 0.0, (73, 6): 0.0, (73, 7): 0.0, (73, 8): 0.0, (73, 9): 0.0, (73, 10): 0.0, (73, 11): 0.0, (73, 12): 0.0, (73, 13): 0.0, (73, 14): 0.0, (73, 15): 0.0, (73, 16): 0.0, (73, 17): 0.0, (73, 18): 0.0, (73, 19): 0.0, (73, 20): 0.0, (73, 21): 0.0, (73, 22): 0.0, (73, 23): 0.0, (73, 24): 0.0, (73, 25): 0.0, (73, 26): 0.0, (73, 27): 0.0, (73, 28): 0.0, (73, 29): 0.0, (73, 30): 0.0, (73, 31): 0.0, (73, 32): 1.0, (73, 33): 2.0, (73, 34): 3.0, (73, 35): 4.0, (73, 36): 4.0, (73, 37): 4.0, (73, 38): 4.0, (73, 39): 4.0, (73, 40): 4.0, (73, 41): 4.0, (73, 42): 4.0, (73, 43): 4.0, (73, 44): 4.0, (73, 45): 4.0, (73, 46): 4.0, (73, 47): 4.0, (73, 48): 4.0, (73, 49): 4.0, (73, 50): 4.0, (73, 51): 4.0, (73, 52): 4.0, (73, 53): 4.0, (73, 54): 4.0, (73, 55): 4.0, (73, 56): 4.0, (73, 57): 4.0, (73, 58): 4.0, (73, 59): 4.0, (73, 60): 4.0, (73, 61): 4.0, (73, 62): 4.0, (73, 63): 4.0, (73, 64): 4.0, (73, 65): 4.0, (73, 66): 4.0, (73, 67): 4.0, (73, 68): 4.0, (73, 69): 4.0, (75, 1): 0.0, (75, 2): 0.0, (75, 3): 0.0, (75, 4): 0.0, (75, 5): 0.0, (75, 6): 0.0, (75, 7): 0.0, (75, 8): 1.0, (75, 9): 2.0, (75, 10): 3.0, (75, 11): 4.0, (75, 12): 5.0, (75, 13): 6.0, (75, 14): 6.5075500204164625, (75, 15): 7.5075500204164625, (75, 16): 7.5075500204164625, (75, 17): 7.5075500204164625, (75, 18): 7.5075500204164625, (75, 19): 7.5075500204164625, (75, 20): 7.5075500204164625, (75, 21): 7.5075500204164625, (75, 22): 7.5075500204164625, (75, 23): 7.5075500204164625, (75, 24): 7.5075500204164625, (75, 25): 7.5075500204164625, (75, 26): 7.5075500204164625, (75, 27): 7.5075500204164625, (75, 28): 7.5075500204164625, (75, 29): 7.5075500204164625, (75, 30): 7.5075500204164625, (75, 31): 7.5075500204164625, (75, 32): 7.5075500204164625, (75, 33): 7.5075500204164625, (75, 34): 7.5075500204164625, (75, 35): 7.5075500204164625, (75, 36): 7.5075500204164625, (75, 37): 7.5075500204164625, (75, 38): 7.5075500204164625, (75, 39): 7.5075500204164625, (75, 40): 7.5075500204164625, (75, 41): 7.5075500204164625, (75, 42): 7.5075500204164625, (75, 43): 7.5075500204164625, (75, 44): 7.5075500204164625, (75, 45): 7.5075500204164625, (75, 46): 7.5075500204164625, (75, 47): 7.5075500204164625, (75, 48): 7.5075500204164625, (75, 49): 7.5075500204164625, (75, 50): 7.5075500204164625, (75, 51): 7.5075500204164625, (75, 52): 7.5075500204164625, (75, 53): 7.5075500204164625, (75, 54): 7.5075500204164625, (75, 55): 7.5075500204164625, (75, 56): 7.5075500204164625, (75, 57): 7.5075500204164625, (75, 58): 7.5075500204164625, (75, 59): 7.5075500204164625, (75, 60): 7.5075500204164625, (75, 61): 7.5075500204164625, (75, 62): 7.5075500204164625, (75, 63): 7.5075500204164625, (75, 64): 7.5075500204164625, (75, 65): 7.5075500204164625, (75, 66): 7.5075500204164625, (75, 67): 7.5075500204164625, (75, 68): 7.5075500204164625, (75, 69): 7.5075500204164625, (82, 1): 0.0, (82, 2): 0.0, (82, 3): 0.0, (82, 4): 0.0, (82, 5): 0.0, (82, 6): 0.0, (82, 7): 0.0, (82, 8): 0.0, (82, 9): 0.0, (82, 10): 0.0, (82, 11): 0.0, (82, 12): 0.0, (82, 13): 0.0, (82, 14): 0.0, (82, 15): 0.0, (82, 16): 0.0, (82, 17): 0.0, (82, 18): 0.0, (82, 19): 0.0, (82, 20): 0.0, (82, 21): 0.0, (82, 22): 0.0, (82, 23): 0.0, (82, 24): 2.0, (82, 25): 3.0, (82, 26): 4.0, (82, 27): 6.0, (82, 28): 7.0, (82, 29): 8.0, (82, 30): 10.0, (82, 31): 12.0, (82, 32): 14.0, (82, 33): 16.0, (82, 34): 16.0, (82, 35): 16.0, (82, 36): 16.0, (82, 37): 16.0, (82, 38): 16.0, (82, 39): 16.0, (82, 40): 16.0, (82, 41): 16.0, (82, 42): 16.0, (82, 43): 16.0, (82, 44): 16.0, (82, 45): 16.0, (82, 46): 16.0, (82, 47): 16.0, (82, 48): 16.0, (82, 49): 16.0, (82, 50): 16.0, (82, 51): 16.0, (82, 52): 16.0, (82, 53): 16.0, (82, 54): 16.0, (82, 55): 16.0, (82, 56): 16.0, (82, 57): 16.0, (82, 58): 16.0, (82, 59): 16.0, (82, 60): 16.0, (82, 61): 16.0, (82, 62): 16.0, (82, 63): 16.0, (82, 64): 16.0, (82, 65): 16.0, (82, 66): 16.0, (82, 67): 16.0, (82, 68): 16.0, (82, 69): 16.0, (84, 1): 0.0, (84, 2): 0.0, (84, 3): 0.0, (84, 4): 0.0, (84, 5): 0.0, (84, 6): 0.0, (84, 7): 0.0, (84, 8): 0.0, (84, 9): 0.0, (84, 10): 0.0, (84, 11): 0.0, (84, 12): 0.0, (84, 13): 0.0, (84, 14): 0.0, (84, 15): 0.0, (84, 16): 0.0, (84, 17): 0.0, (84, 18): 0.0, (84, 19): 2.0, (84, 20): 4.0, (84, 21): 5.0, (84, 22): 7.0, (84, 23): 8.0, (84, 24): 8.0, (84, 25): 10.0, (84, 26): 10.0, (84, 27): 10.0, (84, 28): 10.0, (84, 29): 10.0, (84, 30): 10.0, (84, 31): 10.0, (84, 32): 10.0, (84, 33): 10.0, (84, 34): 10.0, (84, 35): 10.0, (84, 36): 10.0, (84, 37): 10.0, (84, 38): 10.0, (84, 39): 10.0, (84, 40): 10.0, (84, 41): 10.0, (84, 42): 10.0, (84, 43): 10.0, (84, 44): 10.0, (84, 45): 10.0, (84, 46): 10.0, (84, 47): 10.0, (84, 48): 10.0, (84, 49): 10.0, (84, 50): 10.0, (84, 51): 10.0, (84, 52): 10.0, (84, 53): 10.0, (84, 54): 10.0, (84, 55): 10.0, (84, 56): 10.0, (84, 57): 10.0, (84, 58): 10.0, (84, 59): 10.0, (84, 60): 10.0, (84, 61): 10.0, (84, 62): 10.0, (84, 63): 10.0, (84, 64): 10.0, (84, 65): 10.0, (84, 66): 10.0, (84, 67): 10.0, (84, 68): 10.0, (84, 69): 10.0, (86, 1): 0.0, (86, 2): 0.0, (86, 3): 0.0, (86, 4): 0.0, (86, 5): 0.0, (86, 6): 0.0, (86, 7): 1.0, (86, 8): 2.0, (86, 9): 3.0, (86, 10): 3.5075500204164625, (86, 11): 4.5075500204164625, (86, 12): 5.5075500204164625, (86, 13): 5.5075500204164625, (86, 14): 5.5075500204164625, (86, 15): 5.5075500204164625, (86, 16): 5.5075500204164625, (86, 17): 5.5075500204164625, (86, 18): 5.5075500204164625, (86, 19): 5.5075500204164625, (86, 20): 5.5075500204164625, (86, 21): 5.5075500204164625, (86, 22): 5.5075500204164625, (86, 23): 5.5075500204164625, (86, 24): 5.5075500204164625, (86, 25): 5.5075500204164625, (86, 26): 5.5075500204164625, (86, 27): 5.5075500204164625, (86, 28): 5.5075500204164625, (86, 29): 5.5075500204164625, (86, 30): 5.5075500204164625, (86, 31): 5.5075500204164625, (86, 32): 5.5075500204164625, (86, 33): 5.5075500204164625, (86, 34): 5.5075500204164625, (86, 35): 5.5075500204164625, (86, 36): 5.5075500204164625, (86, 37): 5.5075500204164625, (86, 38): 5.5075500204164625, (86, 39): 5.5075500204164625, (86, 40): 5.5075500204164625, (86, 41): 5.5075500204164625, (86, 42): 5.5075500204164625, (86, 43): 5.5075500204164625, (86, 44): 5.5075500204164625, (86, 45): 5.5075500204164625, (86, 46): 5.5075500204164625, (86, 47): 5.5075500204164625, (86, 48): 5.5075500204164625, (86, 49): 5.5075500204164625, (86, 50): 5.5075500204164625, (86, 51): 5.5075500204164625, (86, 52): 5.5075500204164625, (86, 53): 5.5075500204164625, (86, 54): 5.5075500204164625, (86, 55): 5.5075500204164625, (86, 56): 5.5075500204164625, (86, 57): 5.5075500204164625, (86, 58): 5.5075500204164625, (86, 59): 5.5075500204164625, (86, 60): 5.5075500204164625, (86, 61): 5.5075500204164625, (86, 62): 5.5075500204164625, (86, 63): 5.5075500204164625, (86, 64): 5.5075500204164625, (86, 65): 5.5075500204164625, (86, 66): 5.5075500204164625, (86, 67): 5.5075500204164625, (86, 68): 5.5075500204164625, (86, 69): 5.5075500204164625, (87, 1): 0.0, (87, 2): 0.0, (87, 3): 0.0, (87, 4): 0.0, (87, 5): 0.0, (87, 6): 0.0, (87, 7): 0.0, (87, 8): 0.0, (87, 9): 0.0, (87, 10): 0.0, (87, 11): 0.0, (87, 12): 0.0, (87, 13): 0.0, (87, 14): 0.0, (87, 15): 0.0, (87, 16): 0.0, (87, 17): 0.0, (87, 18): 0.0, (87, 19): 0.0, (87, 20): 0.0, (87, 21): 0.0, (87, 22): 0.0, (87, 23): 0.0, (87, 24): 0.0, (87, 25): 1.0, (87, 26): 2.0, (87, 27): 3.0, (87, 28): 4.0, (87, 29): 4.0, (87, 30): 4.0, (87, 31): 4.0, (87, 32): 4.0, (87, 33): 4.0, (87, 34): 4.0, (87, 35): 4.0, (87, 36): 4.0, (87, 37): 4.0, (87, 38): 4.0, (87, 39): 4.0, (87, 40): 4.0, (87, 41): 4.0, (87, 42): 4.0, (87, 43): 4.0, (87, 44): 4.0, (87, 45): 4.0, (87, 46): 4.0, (87, 47): 4.0, (87, 48): 4.0, (87, 49): 4.0, (87, 50): 4.0, (87, 51): 4.0, (87, 52): 4.0, (87, 53): 4.0, (87, 54): 4.0, (87, 55): 4.0, (87, 56): 4.0, (87, 57): 4.0, (87, 58): 4.0, (87, 59): 4.0, (87, 60): 4.0, (87, 61): 4.0, (87, 62): 4.0, (87, 63): 4.0, (87, 64): 4.0, (87, 65): 4.0, (87, 66): 4.0, (87, 67): 4.0, (87, 68): 4.0, (87, 69): 4.0, (89, 1): 0.0, (89, 2): 0.0, (89, 3): 0.0, (89, 4): 0.0, (89, 5): 0.0, (89, 6): 0.0, (89, 7): 0.0, (89, 8): 0.0, (89, 9): 0.0, (89, 10): 0.0, (89, 11): 0.0, (89, 12): 0.0, (89, 13): 0.0, (89, 14): 0.0, (89, 15): 0.0, (89, 16): 0.0, (89, 17): 0.0, (89, 18): 0.0, (89, 19): 0.0, (89, 20): 0.0, (89, 21): 1.0, (89, 22): 2.0, (89, 23): 2.0, (89, 24): 3.0, (89, 25): 3.0, (89, 26): 4.0, (89, 27): 4.0, (89, 28): 4.0, (89, 29): 4.0, (89, 30): 4.0, (89, 31): 4.0, (89, 32): 4.0, (89, 33): 4.0, (89, 34): 4.0, (89, 35): 4.0, (89, 36): 4.0, (89, 37): 4.0, (89, 38): 4.0, (89, 39): 4.0, (89, 40): 4.0, (89, 41): 4.0, (89, 42): 4.0, (89, 43): 4.0, (89, 44): 4.0, (89, 45): 4.0, (89, 46): 4.0, (89, 47): 4.0, (89, 48): 4.0, (89, 49): 4.0, (89, 50): 4.0, (89, 51): 4.0, (89, 52): 4.0, (89, 53): 4.0, (89, 54): 4.0, (89, 55): 4.0, (89, 56): 4.0, (89, 57): 4.0, (89, 58): 4.0, (89, 59): 4.0, (89, 60): 4.0, (89, 61): 4.0, (89, 62): 4.0, (89, 63): 4.0, (89, 64): 4.0, (89, 65): 4.0, (89, 66): 4.0, (89, 67): 4.0, (89, 68): 4.0, (89, 69): 4.0, (92, 1): 0.0, (92, 2): 0.0, (92, 3): 0.0, (92, 4): 0.0, (92, 5): 0.0, (92, 6): 0.0, (92, 7): 0.0, (92, 8): 0.0, (92, 9): 0.0, (92, 10): 0.0, (92, 11): 0.0, (92, 12): 0.0, (92, 13): 0.0, (92, 14): 0.0, (92, 15): 0.0, (92, 16): 0.0, (92, 17): 0.0, (92, 18): 0.0, (92, 19): 0.0, (92, 20): 0.0, (92, 21): 0.0, (92, 22): 0.0, (92, 23): 0.0, (92, 24): 0.0, (92, 25): 0.0, (92, 26): 0.0, (92, 27): 0.0, (92, 28): 0.0, (92, 29): 0.0, (92, 30): 0.0, (92, 31): 0.0, (92, 32): 1.0, (92, 33): 2.0, (92, 34): 3.0, (92, 35): 4.0, (92, 36): 5.0, (92, 37): 5.0, (92, 38): 5.0, (92, 39): 5.0, (92, 40): 5.0, (92, 41): 5.0, (92, 42): 5.0, (92, 43): 5.0, (92, 44): 5.0, (92, 45): 5.0, (92, 46): 5.0, (92, 47): 5.0, (92, 48): 5.0, (92, 49): 5.0, (92, 50): 5.0, (92, 51): 5.0, (92, 52): 5.0, (92, 53): 5.0, (92, 54): 5.0, (92, 55): 5.0, (92, 56): 5.0, (92, 57): 5.0, (92, 58): 5.0, (92, 59): 5.0, (92, 60): 5.0, (92, 61): 5.0, (92, 62): 5.0, (92, 63): 5.0, (92, 64): 5.0, (92, 65): 5.0, (92, 66): 5.0, (92, 67): 5.0, (92, 68): 5.0, (92, 69): 5.0, (96, 1): 0.0, (96, 2): 0.0, (96, 3): 0.0, (96, 4): 0.0, (96, 5): 0.0, (96, 6): 0.0, (96, 7): 0.0, (96, 8): 0.0, (96, 9): 0.0, (96, 10): 0.0, (96, 11): 0.0, (96, 12): 0.0, (96, 13): 0.0, (96, 14): 0.0, (96, 15): 0.0, (96, 16): 0.0, (96, 17): 0.0, (96, 18): 0.0, (96, 19): 0.0, (96, 20): 0.0, (96, 21): 0.0, (96, 22): 0.0, (96, 23): 0.0, (96, 24): 1.0, (96, 25): 2.0, (96, 26): 3.0, (96, 27): 3.0, (96, 28): 3.0, (96, 29): 3.0, (96, 30): 3.0, (96, 31): 3.0, (96, 32): 3.0, (96, 33): 3.0, (96, 34): 3.0, (96, 35): 3.0, (96, 36): 3.0, (96, 37): 3.0, (96, 38): 3.0, (96, 39): 3.0, (96, 40): 3.0, (96, 41): 3.0, (96, 42): 3.0, (96, 43): 3.0, (96, 44): 3.0, (96, 45): 3.0, (96, 46): 3.0, (96, 47): 3.0, (96, 48): 3.0, (96, 49): 3.0, (96, 50): 3.0, (96, 51): 3.0, (96, 52): 3.0, (96, 53): 3.0, (96, 54): 3.0, (96, 55): 3.0, (96, 56): 3.0, (96, 57): 3.0, (96, 58): 3.0, (96, 59): 3.0, (96, 60): 3.0, (96, 61): 3.0, (96, 62): 3.0, (96, 63): 3.0, (96, 64): 3.0, (96, 65): 3.0, (96, 66): 3.0, (96, 67): 3.0, (96, 68): 3.0, (96, 69): 3.0, (98, 1): 1.0, (98, 2): 2.0, (98, 3): 3.0, (98, 4): 4.0, (98, 5): 5.0, (98, 6): 6.0, (98, 7): 6.0, (98, 8): 6.0, (98, 9): 6.0, (98, 10): 6.0, (98, 11): 6.0, (98, 12): 6.0, (98, 13): 6.0, (98, 14): 6.0, (98, 15): 6.0, (98, 16): 6.0, (98, 17): 6.0, (98, 18): 6.0, (98, 19): 6.0, (98, 20): 6.0, (98, 21): 6.0, (98, 22): 6.0, (98, 23): 6.0, (98, 24): 6.0, (98, 25): 6.0, (98, 26): 6.0, (98, 27): 6.0, (98, 28): 6.0, (98, 29): 6.0, (98, 30): 6.0, (98, 31): 6.0, (98, 32): 6.0, (98, 33): 6.0, (98, 34): 6.0, (98, 35): 6.0, (98, 36): 6.0, (98, 37): 6.0, (98, 38): 6.0, (98, 39): 6.0, (98, 40): 6.0, (98, 41): 6.0, (98, 42): 6.0, (98, 43): 6.0, (98, 44): 6.0, </t>
+  </si>
+  <si>
+    <t>{(1, 1): 0, (1, 2): 0, (1, 3): 0, (1, 4): 0, (1, 5): 0, (1, 6): 0, (1, 7): 0, (1, 8): 0, (1, 9): 0, (1, 10): 0, (1, 11): 0, (1, 12): 0, (1, 13): 0, (1, 14): 0, (1, 15): 0, (1, 16): 0, (1, 17): 0, (1, 18): 0, (1, 19): 0, (1, 20): 0, (1, 21): 0, (1, 22): 0, (1, 23): 0, (1, 24): 0, (1, 25): 0, (1, 26): 0, (1, 27): 1, (1, 28): 0, (1, 29): 0, (1, 30): 0, (1, 31): 0, (1, 32): 0, (1, 33): 0, (1, 34): 0, (1, 35): 0, (1, 36): 0, (1, 37): 0, (1, 38): 0, (1, 39): 0, (1, 40): 0, (1, 41): 0, (1, 42): 0, (1, 43): 0, (1, 44): 0, (1, 45): 0, (1, 46): 0, (1, 47): 0, (1, 48): 0, (1, 49): 0, (1, 50): 0, (1, 51): 0, (1, 52): 0, (1, 53): 0, (1, 54): 0, (1, 55): 0, (1, 56): 0, (1, 57): 0, (1, 58): 0, (1, 59): 0, (1, 60): 0, (1, 61): 0, (1, 62): 0, (1, 63): 0, (1, 64): 0, (1, 65): 0, (1, 66): 0, (1, 67): 0, (1, 68): 0, (1, 69): 0, (2, 1): 0, (2, 2): 0, (2, 3): 0, (2, 4): 0, (2, 5): 0, (2, 6): 0, (2, 7): 0, (2, 8): 0, (2, 9): 0, (2, 10): 0, (2, 11): 0, (2, 12): 0, (2, 13): 0, (2, 14): 0, (2, 15): 0, (2, 16): 0, (2, 17): 0, (2, 18): 0, (2, 19): 0, (2, 20): 0, (2, 21): 0, (2, 22): 0, (2, 23): 0, (2, 24): 0, (2, 25): 0, (2, 26): 0, (2, 27): 0, (2, 28): 0, (2, 29): 0, (2, 30): 1, (2, 31): 0, (2, 32): 0, (2, 33): 0, (2, 34): 0, (2, 35): 0, (2, 36): 0, (2, 37): 0, (2, 38): 0, (2, 39): 0, (2, 40): 0, (2, 41): 0, (2, 42): 0, (2, 43): 0, (2, 44): 0, (2, 45): 0, (2, 46): 0, (2, 47): 0, (2, 48): 0, (2, 49): 0, (2, 50): 0, (2, 51): 0, (2, 52): 0, (2, 53): 0, (2, 54): 0, (2, 55): 0, (2, 56): 0, (2, 57): 0, (2, 58): 0, (2, 59): 0, (2, 60): 0, (2, 61): 0, (2, 62): 0, (2, 63): 0, (2, 64): 0, (2, 65): 0, (2, 66): 0, (2, 67): 0, (2, 68): 0, (2, 69): 0, (6, 1): 0, (6, 2): 0, (6, 3): 0, (6, 4): 0, (6, 5): 0, (6, 6): 0, (6, 7): 0, (6, 8): 0, (6, 9): 0, (6, 10): 0, (6, 11): 0, (6, 12): 0, (6, 13): 0, (6, 14): 0, (6, 15): 0, (6, 16): 0, (6, 17): 0, (6, 18): 0, (6, 19): 0, (6, 20): 0, (6, 21): 0, (6, 22): 0, (6, 23): 0, (6, 24): 0, (6, 25): 0, (6, 26): 0, (6, 27): 0, (6, 28): 0, (6, 29): 0, (6, 30): 0, (6, 31): 0, (6, 32): 0, (6, 33): 0, (6, 34): 0, (6, 35): 0, (6, 36): 0, (6, 37): 0, (6, 38): 0, (6, 39): 0, (6, 40): 0, (6, 41): 0, (6, 42): 0, (6, 43): 0, (6, 44): 0, (6, 45): 0, (6, 46): 0, (6, 47): 1, (6, 48): 0, (6, 49): 0, (6, 50): 0, (6, 51): 0, (6, 52): 0, (6, 53): 0, (6, 54): 0, (6, 55): 0, (6, 56): 0, (6, 57): 0, (6, 58): 0, (6, 59): 0, (6, 60): 0, (6, 61): 0, (6, 62): 0, (6, 63): 0, (6, 64): 0, (6, 65): 0, (6, 66): 0, (6, 67): 0, (6, 68): 0, (6, 69): 0, (7, 1): 0, (7, 2): 0, (7, 3): 0, (7, 4): 0, (7, 5): 0, (7, 6): 0, (7, 7): 0, (7, 8): 0, (7, 9): 0, (7, 10): 0, (7, 11): 0, (7, 12): 0, (7, 13): 0, (7, 14): 0, (7, 15): 0, (7, 16): 0, (7, 17): 0, (7, 18): 0, (7, 19): 0, (7, 20): 0, (7, 21): 0, (7, 22): 0, (7, 23): 0, (7, 24): 0, (7, 25): 0, (7, 26): 0, (7, 27): 0, (7, 28): 0, (7, 29): 0, (7, 30): 0, (7, 31): 0, (7, 32): 0, (7, 33): 0, (7, 34): 0, (7, 35): 0, (7, 36): 0, (7, 37): 0, (7, 38): 0, (7, 39): 0, (7, 40): 0, (7, 41): 0, (7, 42): 0, (7, 43): 0, (7, 44): 0, (7, 45): 0, (7, 46): 0, (7, 47): 1, (7, 48): 0, (7, 49): 0, (7, 50): 0, (7, 51): 0, (7, 52): 0, (7, 53): 0, (7, 54): 0, (7, 55): 0, (7, 56): 0, (7, 57): 0, (7, 58): 0, (7, 59): 0, (7, 60): 0, (7, 61): 0, (7, 62): 0, (7, 63): 0, (7, 64): 0, (7, 65): 0, (7, 66): 0, (7, 67): 0, (7, 68): 0, (7, 69): 0, (16, 1): 0, (16, 2): 0, (16, 3): 0, (16, 4): 0, (16, 5): 0, (16, 6): 0, (16, 7): 0, (16, 8): 0, (16, 9): 0, (16, 10): 0, (16, 11): 0, (16, 12): 0, (16, 13): 0, (16, 14): 0, (16, 15): 0, (16, 16): 0, (16, 17): 0, (16, 18): 0, (16, 19): 1, (16, 20): 0, (16, 21): 0, (16, 22): 0, (16, 23): 0, (16, 24): 0, (16, 25): 0, (16, 26): 0, (16, 27): 0, (16, 28): 0, (16, 29): 0, (16, 30): 0, (16, 31): 0, (16, 32): 0, (16, 33): 0, (16, 34): 0, (16, 35): 0, (16, 36): 0, (16, 37): 0, (16, 38): 0, (16, 39): 0, (16, 40): 0, (16, 41): 0, (16, 42): 0, (16, 43): 0, (16, 44): 0, (16, 45): 0, (16, 46): 0, (16, 47): 0, (16, 48): 0, (16, 49): 0, (16, 50): 0, (16, 51): 0, (16, 52): 0, (16, 53): 0, (16, 54): 0, (16, 55): 0, (16, 56): 0, (16, 57): 0, (16, 58): 0, (16, 59): 0, (16, 60): 0, (16, 61): 0, (16, 62): 0, (16, 63): 0, (16, 64): 0, (16, 65): 0, (16, 66): 0, (16, 67): 0, (16, 68): 0, (16, 69): 0, (26, 1): 0, (26, 2): 0, (26, 3): 0, (26, 4): 0, (26, 5): 0, (26, 6): 0, (26, 7): 0, (26, 8): 0, (26, 9): 0, (26, 10): 0, (26, 11): 0, (26, 12): 0, (26, 13): 0, (26, 14): 0, (26, 15): 0, (26, 16): 0, (26, 17): 0, (26, 18): 0, (26, 19): 0, (26, 20): 0, (26, 21): 0, (26, 22): 0, (26, 23): 0, (26, 24): 0, (26, 25): 0, (26, 26): 0, (26, 27): 0, (26, 28): 0, (26, 29): 0, (26, 30): 0, (26, 31): 0, (26, 32): 0, (26, 33): 0, (26, 34): 0, (26, 35): 0, (26, 36): 0, (26, 37): 0, (26, 38): 1, (26, 39): 0, (26, 40): 0, (26, 41): 0, (26, 42): 0, (26, 43): 0, (26, 44): 0, (26, 45): 0, (26, 46): 0, (26, 47): 0, (26, 48): 0, (26, 49): 0, (26, 50): 0, (26, 51): 0, (26, 52): 0, (26, 53): 0, (26, 54): 0, (26, 55): 0, (26, 56): 0, (26, 57): 0, (26, 58): 0, (26, 59): 0, (26, 60): 0, (26, 61): 0, (26, 62): 0, (26, 63): 0, (26, 64): 0, (26, 65): 0, (26, 66): 0, (26, 67): 0, (26, 68): 0, (26, 69): 0, (35, 1): 0, (35, 2): 0, (35, 3): 0, (35, 4): 0, (35, 5): 0, (35, 6): 0, (35, 7): 0, (35, 8): 0, (35, 9): 0, (35, 10): 0, (35, 11): 0, (35, 12): 0, (35, 13): 0, (35, 14): 0, (35, 15): 1, (35, 16): 0, (35, 17): 0, (35, 18): 0, (35, 19): 0, (35, 20): 0, (35, 21): 0, (35, 22): 0, (35, 23): 0, (35, 24): 0, (35, 25): 0, (35, 26): 0, (35, 27): 0, (35, 28): 0, (35, 29): 0, (35, 30): 0, (35, 31): 0, (35, 32): 0, (35, 33): 0, (35, 34): 0, (35, 35): 0, (35, 36): 0, (35, 37): 0, (35, 38): 0, (35, 39): 0, (35, 40): 0, (35, 41): 0, (35, 42): 0, (35, 43): 0, (35, 44): 0, (35, 45): 0, (35, 46): 0, (35, 47): 0, (35, 48): 0, (35, 49): 0, (35, 50): 0, (35, 51): 0, (35, 52): 0, (35, 53): 0, (35, 54): 0, (35, 55): 0, (35, 56): 0, (35, 57): 0, (35, 58): 0, (35, 59): 0, (35, 60): 0, (35, 61): 0, (35, 62): 0, (35, 63): 0, (35, 64): 0, (35, 65): 0, (35, 66): 0, (35, 67): 0, (35, 68): 0, (35, 69): 0, (38, 1): 0, (38, 2): 0, (38, 3): 0, (38, 4): 0, (38, 5): 0, (38, 6): 0, (38, 7): 0, (38, 8): 0, (38, 9): 0, (38, 10): 0, (38, 11): 1, (38, 12): 0, (38, 13): 0, (38, 14): 0, (38, 15): 0, (38, 16): 0, (38, 17): 0, (38, 18): 0, (38, 19): 0, (38, 20): 0, (38, 21): 0, (38, 22): 0, (38, 23): 0, (38, 24): 0, (38, 25): 0, (38, 26): 0, (38, 27): 0, (38, 28): 0, (38, 29): 0, (38, 30): 0, (38, 31): 0, (38, 32): 0, (38, 33): 0, (38, 34): 0, (38, 35): 0, (38, 36): 0, (38, 37): 0, (38, 38): 0, (38, 39): 0, (38, 40): 0, (38, 41): 0, (38, 42): 0, (38, 43): 0, (38, 44): 0, (38, 45): 0, (38, 46): 0, (38, 47): 0, (38, 48): 0, (38, 49): 0, (38, 50): 0, (38, 51): 0, (38, 52): 0, (38, 53): 0, (38, 54): 0, (38, 55): 0, (38, 56): 0, (38, 57): 0, (38, 58): 0, (38, 59): 0, (38, 60): 0, (38, 61): 0, (38, 62): 0, (38, 63): 0, (38, 64): 0, (38, 65): 0, (38, 66): 0, (38, 67): 0, (38, 68): 0, (38, 69): 0, (39, 1): 0, (39, 2): 0, (39, 3): 0, (39, 4): 0, (39, 5): 0, (39, 6): 0, (39, 7): 0, (39, 8): 0, (39, 9): 0, (39, 10): 0, (39, 11): 0, (39, 12): 0, (39, 13): 0, (39, 14): 0, (39, 15): 0, (39, 16): 0, (39, 17): 0, (39, 18): 0, (39, 19): 0, (39, 20): 0, (39, 21): 0, (39, 22): 1, (39, 23): 0, (39, 24): 0, (39, 25): 0, (39, 26): 0, (39, 27): 0, (39, 28): 0, (39, 29): 0, (39, 30): 0, (39, 31): 0, (39, 32): 0, (39, 33): 0, (39, 34): 0, (39, 35): 0, (39, 36): 0, (39, 37): 0, (39, 38): 0, (39, 39): 0, (39, 40): 0, (39, 41): 0, (39, 42): 0, (39, 43): 0, (39, 44): 0, (39, 45): 0, (39, 46): 0, (39, 47): 0, (39, 48): 0, (39, 49): 0, (39, 50): 0, (39, 51): 0, (39, 52): 0, (39, 53): 0, (39, 54): 0, (39, 55): 0, (39, 56): 0, (39, 57): 0, (39, 58): 0, (39, 59): 0, (39, 60): 0, (39, 61): 0, (39, 62): 0, (39, 63): 0, (39, 64): 0, (39, 65): 0, (39, 66): 0, (39, 67): 0, (39, 68): 0, (39, 69): 0, (41, 1): 0, (41, 2): 0, (41, 3): 0, (41, 4): 0, (41, 5): 0, (41, 6): 0, (41, 7): 0, (41, 8): 0, (41, 9): 0, (41, 10): 0, (41, 11): 0, (41, 12): 0, (41, 13): 0, (41, 14): 0, (41, 15): 0, (41, 16): 0, (41, 17): 0, (41, 18): 0, (41, 19): 0, (41, 20): 0, (41, 21): 0, (41, 22): 0, (41, 23): 0, (41, 24): 0, (41, 25): 0, (41, 26): 0, (41, 27): 0, (41, 28): 0, (41, 29): 0, (41, 30): 0, (41, 31): 0, (41, 32): 0, (41, 33): 0, (41, 34): 0, (41, 35): 0, (41, 36): 1, (41, 37): 0, (41, 38): 0, (41, 39): 0, (41, 40): 0, (41, 41): 0, (41, 42): 0, (41, 43): 0, (41, 44): 0, (41, 45): 0, (41, 46): 0, (41, 47): 0, (41, 48): 0, (41, 49): 0, (41, 50): 0, (41, 51): 0, (41, 52): 0, (41, 53): 0, (41, 54): 0, (41, 55): 0, (41, 56): 0, (41, 57): 0, (41, 58): 0, (41, 59): 0, (41, 60): 0, (41, 61): 0, (41, 62): 0, (41, 63): 0, (41, 64): 0, (41, 65): 0, (41, 66): 0, (41, 67): 0, (41, 68): 0, (41, 69): 0, (42, 1): 0, (42, 2): 0, (42, 3): 0, (42, 4): 0, (42, 5): 0, (42, 6): 0, (42, 7): 0, (42, 8): 0, (42, 9): 0, (42, 10): 0, (42, 11): 0, (42, 12): 0, (42, 13): 0, (42, 14): 0, (42, 15): 0, (42, 16): 0, (42, 17): 0, (42, 18): 0, (42, 19): 0, (42, 20): 0, (42, 21): 0, (42, 22): 0, (42, 23): 0, (42, 24): 0, (42, 25): 0, (42, 26): 0, (42, 27): 0, (42, 28): 0, (42, 29): 0, (42, 30): 1, (42, 31): 0, (42, 32): 0, (42, 33): 0, (42, 34): 0, (42, 35): 0, (42, 36): 0, (42, 37): 0, (42, 38): 0, (42, 39): 0, (42, 40): 0, (42, 41): 0, (42, 42): 0, (42, 43): 0, (42, 44): 0, (42, 45): 0, (42, 46): 0, (42, 47): 0, (42, 48): 0, (42, 49): 0, (42, 50): 0, (42, 51): 0, (42, 52): 0, (42, 53): 0, (42, 54): 0, (42, 55): 0, (42, 56): 0, (42, 57): 0, (42, 58): 0, (42, 59): 0, (42, 60): 0, (42, 61): 0, (42, 62): 0, (42, 63): 0, (42, 64): 0, (42, 65): 0, (42, 66): 0, (42, 67): 0, (42, 68): 0, (42, 69): 0, (43, 1): 0, (43, 2): 0, (43, 3): 0, (43, 4): 0, (43, 5): 0, (43, 6): 0, (43, 7): 0, (43, 8): 0, (43, 9): 0, (43, 10): 0, (43, 11): 0, (43, 12): 0, (43, 13): 0, (43, 14): 0, (43, 15): 0, (43, 16): 0, (43, 17): 0, (43, 18): 0, (43, 19): 0, (43, 20): 0, (43, 21): 0, (43, 22): 0, (43, 23): 0, (43, 24): 0, (43, 25): 0, (43, 26): 1, (43, 27): 0, (43, 28): 0, (43, 29): 0, (43, 30): 0, (43, 31): 0, (43, 32): 0, (43, 33): 0, (43, 34): 0, (43, 35): 0, (43, 36): 0, (43, 37): 0, (43, 38): 0, (43, 39): 0, (43, 40): 0, (43, 41): 0, (43, 42): 0, (43, 43): 0, (43, 44): 0, (43, 45): 0, (43, 46): 0, (43, 47): 0, (43, 48): 0, (43, 49): 0, (43, 50): 0, (43, 51): 0, (43, 52): 0, (43, 53): 0, (43, 54): 0, (43, 55): 0, (43, 56): 0, (43, 57): 0, (43, 58): 0, (43, 59): 0, (43, 60): 0, (43, 61): 0, (43, 62): 0, (43, 63): 0, (43, 64): 0, (43, 65): 0, (43, 66): 0, (43, 67): 0, (43, 68): 0, (43, 69): 0, (46, 1): 0, (46, 2): 0, (46, 3): 0, (46, 4): 0, (46, 5): 0, (46, 6): 0, (46, 7): 0, (46, 8): 0, (46, 9): 0, (46, 10): 0, (46, 11): 0, (46, 12): 0, (46, 13): 0, (46, 14): 0, (46, 15): 1, (46, 16): 0, (46, 17): 0, (46, 18): 0, (46, 19): 0, (46, 20): 0, (46, 21): 0, (46, 22): 0, (46, 23): 0, (46, 24): 0, (46, 25): 0, (46, 26): 0, (46, 27): 0, (46, 28): 0, (46, 29): 0, (46, 30): 0, (46, 31): 0, (46, 32): 0, (46, 33): 0, (46, 34): 0, (46, 35): 0, (46, 36): 0, (46, 37): 0, (46, 38): 0, (46, 39): 0, (46, 40): 0, (46, 41): 0, (46, 42): 0, (46, 43): 0, (46, 44): 0, (46, 45): 0, (46, 46): 0, (46, 47): 0, (46, 48): 0, (46, 49): 0, (46, 50): 0, (46, 51): 0, (46, 52): 0, (46, 53): 0, (46, 54): 0, (46, 55): 0, (46, 56): 0, (46, 57): 0, (46, 58): 0, (46, 59): 0, (46, 60): 0, (46, 61): 0, (46, 62): 0, (46, 63): 0, (46, 64): 0, (46, 65): 0, (46, 66): 0, (46, 67): 0, (46, 68): 0, (46, 69): 0, (48, 1): 0, (48, 2): 0, (48, 3): 0, (48, 4): 0, (48, 5): 0, (48, 6): 0, (48, 7): 0, (48, 8): 0, (48, 9): 0, (48, 10): 0, (48, 11): 0, (48, 12): 0, (48, 13): 0, (48, 14): 0, (48, 15): 0, (48, 16): 0, (48, 17): 0, (48, 18): 0, (48, 19): 0, (48, 20): 0, (48, 21): 0, (48, 22): 0, (48, 23): 0, (48, 24): 0, (48, 25): 0, (48, 26): 0, (48, 27): 0, (48, 28): 0, (48, 29): 1, (48, 30): 0, (48, 31): 0, (48, 32): 0, (48, 33): 0, (48, 34): 0, (48, 35): 0, (48, 36): 0, (48, 37): 0, (48, 38): 0, (48, 39): 0, (48, 40): 0, (48, 41): 0, (48, 42): 0, (48, 43): 0, (48, 44): 0, (48, 45): 0, (48, 46): 0, (48, 47): 0, (48, 48): 0, (48, 49): 0, (48, 50): 0, (48, 51): 0, (48, 52): 0, (48, 53): 0, (48, 54): 0, (48, 55): 0, (48, 56): 0, (48, 57): 0, (48, 58): 0, (48, 59): 0, (48, 60): 0, (48, 61): 0, (48, 62): 0, (48, 63): 0, (48, 64): 0, (48, 65): 0, (48, 66): 0, (48, 67): 0, (48, 68): 0, (48, 69): 0, (49, 1): 0, (49, 2): 0, (49, 3): 0, (49, 4): 0, (49, 5): 0, (49, 6): 0, (49, 7): 0, (49, 8): 0, (49, 9): 0, (49, 10): 0, (49, 11): 0, (49, 12): 0, (49, 13): 0, (49, 14): 0, (49, 15): 0, (49, 16): 0, (49, 17): 1, (49, 18): 0, (49, 19): 0, (49, 20): 0, (49, 21): 0, (49, 22): 0, (49, 23): 0, (49, 24): 0, (49, 25): 0, (49, 26): 0, (49, 27): 0, (49, 28): 0, (49, 29): 0, (49, 30): 0, (49, 31): 0, (49, 32): 0, (49, 33): 0, (49, 34): 0, (49, 35): 0, (49, 36): 0, (49, 37): 0, (49, 38): 0, (49, 39): 0, (49, 40): 0, (49, 41): 0, (49, 42): 0, (49, 43): 0, (49, 44): 0, (49, 45): 0, (49, 46): 0, (49, 47): 0, (49, 48): 0, (49, 49): 0, (49, 50): 0, (49, 51): 0, (49, 52): 0, (49, 53): 0, (49, 54): 0, (49, 55): 0, (49, 56): 0, (49, 57): 0, (49, 58): 0, (49, 59): 0, (49, 60): 0, (49, 61): 0, (49, 62): 0, (49, 63): 0, (49, 64): 0, (49, 65): 0, (49, 66): 0, (49, 67): 0, (49, 68): 0, (49, 69): 0, (51, 1): 0, (51, 2): 0, (51, 3): 0, (51, 4): 0, (51, 5): 0, (51, 6): 0, (51, 7): 0, (51, 8): 0, (51, 9): 0, (51, 10): 0, (51, 11): 0, (51, 12): 0, (51, 13): 0, (51, 14): 0, (51, 15): 0, (51, 16): 0, (51, 17): 0, (51, 18): 0, (51, 19): 0, (51, 20): 1, (51, 21): 0, (51, 22): 0, (51, 23): 0, (51, 24): 0, (51, 25): 0, (51, 26): 0, (51, 27): 0, (51, 28): 0, (51, 29): 0, (51, 30): 0, (51, 31): 0, (51, 32): 0, (51, 33): 0, (51, 34): 0, (51, 35): 0, (51, 36): 0, (51, 37): 0, (51, 38): 0, (51, 39): 0, (51, 40): 0, (51, 41): 0, (51, 42): 0, (51, 43): 0, (51, 44): 0, (51, 45): 0, (51, 46): 0, (51, 47): 0, (51, 48): 0, (51, 49): 0, (51, 50): 0, (51, 51): 0, (51, 52): 0, (51, 53): 0, (51, 54): 0, (51, 55): 0, (51, 56): 0, (51, 57): 0, (51, 58): 0, (51, 59): 0, (51, 60): 0, (51, 61): 0, (51, 62): 0, (51, 63): 0, (51, 64): 0, (51, 65): 0, (51, 66): 0, (51, 67): 0, (51, 68): 0, (51, 69): 0, (52, 1): 0, (52, 2): 0, (52, 3): 0, (52, 4): 0, (52, 5): 0, (52, 6): 0, (52, 7): 0, (52, 8): 0, (52, 9): 0, (52, 10): 0, (52, 11): 0, (52, 12): 1, (52, 13): 0, (52, 14): 0, (52, 15): 0, (52, 16): 0, (52, 17): 0, (52, 18): 0, (52, 19): 0, (52, 20): 0, (52, 21): 0, (52, 22): 0, (52, 23): 0, (52, 24): 0, (52, 25): 0, (52, 26): 0, (52, 27): 0, (52, 28): 0, (52, 29): 0, (52, 30): 0, (52, 31): 0, (52, 32): 0, (52, 33): 0, (52, 34): 0, (52, 35): 0, (52, 36): 0, (52, 37): 0, (52, 38): 0, (52, 39): 0, (52, 40): 0, (52, 41): 0, (52, 42): 0, (52, 43): 0, (52, 44): 0, (52, 45): 0, (52, 46): 0, (52, 47): 0, (52, 48): 0, (52, 49): 0, (52, 50): 0, (52, 51): 0, (52, 52): 0, (52, 53): 0, (52, 54): 0, (52, 55): 0, (52, 56): 0, (52, 57): 0, (52, 58): 0, (52, 59): 0, (52, 60): 0, (52, 61): 0, (52, 62): 0, (52, 63): 0, (52, 64): 0, (52, 65): 0, (52, 66): 0, (52, 67): 0, (52, 68): 0, (52, 69): 0, (57, 1): 0, (57, 2): 0, (57, 3): 0, (57, 4): 0, (57, 5): 0, (57, 6): 0, (57, 7): 0, (57, 8): 0, (57, 9): 0, (57, 10): 0, (57, 11): 0, (57, 12): 0, (57, 13): 0, (57, 14): 0, (57, 15): 0, (57, 16): 0, (57, 17): 0, (57, 18): 0, (57, 19): 0, (57, 20): 0, (57, 21): 0, (57, 22): 0, (57, 23): 0, (57, 24): 0, (57, 25): 0, (57, 26): 0, (57, 27): 0, (57, 28): 0, (57, 29): 0, (57, 30): 0, (57, 31): 0, (57, 32): 0, (57, 33): 0, (57, 34): 1, (57, 35): 0, (57, 36): 0, (57, 37): 0, (57, 38): 0, (57, 39): 0, (57, 40): 0, (57, 41): 0, (57, 42): 0, (57, 43): 0, (57, 44): 0, (57, 45): 0, (57, 46): 0, (57, 47): 0, (57, 48): 0, (57, 49): 0, (57, 50): 0, (57, 51): 0, (57, 52): 0, (57, 53): 0, (57, 54): 0, (57, 55): 0, (57, 56): 0, (57, 57): 0, (57, 58): 0, (57, 59): 0, (57, 60): 0, (57, 61): 0, (57, 62): 0, (57, 63): 0, (57, 64): 0, (57, 65): 0, (57, 66): 0, (57, 67): 0, (57, 68): 0, (57, 69): 0, (70, 1): 0, (70, 2): 0, (70, 3): 0, (70, 4): 0, (70, 5): 0, (70, 6): 0, (70, 7): 0, (70, 8): 0, (70, 9): 0, (70, 10): 0, (70, 11): 0, (70, 12): 0, (70, 13): 0, (70, 14): 0, (70, 15): 0, (70, 16): 0, (70, 17): 0, (70, 18): 0, (70, 19): 0, (70, 20): 0, (70, 21): 0, (70, 22): 0, (70, 23): 0, (70, 24): 0, (70, 25): 0, (70, 26): 1, (70, 27): 0, (70, 28): 0, (70, 29): 0, (70, 30): 0, (70, 31): 0, (70, 32): 0, (70, 33): 0, (70, 34): 0, (70, 35): 0, (70, 36): 0, (70, 37): 0, (70, 38): 0, (70, 39): 0, (70, 40): 0, (70, 41): 0, (70, 42): 0, (70, 43): 0, (70, 44): 0, (70, 45): 0, (70, 46): 0, (70, 47): 0, (70, 48): 0, (70, 49): 0, (70, 50): 0, (70, 51): 0, (70, 52): 0, (70, 53): 0, (70, 54): 0, (70, 55): 0, (70, 56): 0, (70, 57): 0, (70, 58): 0, (70, 59): 0, (70, 60): 0, (70, 61): 0, (70, 62): 0, (70, 63): 0, (70, 64): 0, (70, 65): 0, (70, 66): 0, (70, 67): 0, (70, 68): 0, (70, 69): 0, (73, 1): 0, (73, 2): 0, (73, 3): 0, (73, 4): 0, (73, 5): 0, (73, 6): 0, (73, 7): 0, (73, 8): 0, (73, 9): 0, (73, 10): 0, (73, 11): 0, (73, 12): 0, (73, 13): 0, (73, 14): 0, (73, 15): 0, (73, 16): 0, (73, 17): 0, (73, 18): 0, (73, 19): 0, (73, 20): 0, (73, 21): 0, (73, 22): 0, (73, 23): 0, (73, 24): 0, (73, 25): 0, (73, 26): 0, (73, 27): 0, (73, 28): 0, (73, 29): 0, (73, 30): 0, (73, 31): 0, (73, 32): 0, (73, 33): 0, (73, 34): 0, (73, 35): 1, (73, 36): 0, (73, 37): 0, (73, 38): 0, (73, 39): 0, (73, 40): 0, (73, 41): 0, (73, 42): 0, (73, 43): 0, (73, 44): 0, (73, 45): 0, (73, 46): 0, (73, 47): 0, (73, 48): 0, (73, 49): 0, (73, 50): 0, (73, 51): 0, (73, 52): 0, (73, 53): 0, (73, 54): 0, (73, 55): 0, (73, 56): 0, (73, 57): 0, (73, 58): 0, (73, 59): 0, (73, 60): 0, (73, 61): 0, (73, 62): 0, (73, 63): 0, (73, 64): 0, (73, 65): 0, (73, 66): 0, (73, 67): 0, (73, 68): 0, (73, 69): 0, (75, 1): 0, (75, 2): 0, (75, 3): 0, (75, 4): 0, (75, 5): 0, (75, 6): 0, (75, 7): 0, (75, 8): 0, (75, 9): 0, (75, 10): 0, (75, 11): 0, (75, 12): 0, (75, 13): 0, (75, 14): 0, (75, 15): 1, (75, 16): 0, (75, 17): 0, (75, 18): 0, (75, 19): 0, (75, 20): 0, (75, 21): 0, (75, 22): 0, (75, 23): 0, (75, 24): 0, (75, 25): 0, (75, 26): 0, (75, 27): 0, (75, 28): 0, (75, 29): 0, (75, 30): 0, (75, 31): 0, (75, 32): 0, (75, 33): 0, (75, 34): 0, (75, 35): 0, (75, 36): 0, (75, 37): 0, (75, 38): 0, (75, 39): 0, (75, 40): 0, (75, 41): 0, (75, 42): 0, (75, 43): 0, (75, 44): 0, (75, 45): 0, (75, 46): 0, (75, 47): 0, (75, 48): 0, (75, 49): 0, (75, 50): 0, (75, 51): 0, (75, 52): 0, (75, 53): 0, (75, 54): 0, (75, 55): 0, (75, 56): 0, (75, 57): 0, (75, 58): 0, (75, 59): 0, (75, 60): 0, (75, 61): 0, (75, 62): 0, (75, 63): 0, (75, 64): 0, (75, 65): 0, (75, 66): 0, (75, 67): 0, (75, 68): 0, (75, 69): 0, (82, 1): 0, (82, 2): 0, (82, 3): 0, (82, 4): 0, (82, 5): 0, (82, 6): 0, (82, 7): 0, (82, 8): 0, (82, 9): 0, (82, 10): 0, (82, 11): 0, (82, 12): 0, (82, 13): 0, (82, 14): 0, (82, 15): 0, (82, 16): 0, (82, 17): 0, (82, 18): 0, (82, 19): 0, (82, 20): 0, (82, 21): 0, (82, 22): 0, (82, 23): 0, (82, 24): 0, (82, 25): 0, (82, 26): 0, (82, 27): 0, (82, 28): 0, (82, 29): 0, (82, 30): 0, (82, 31): 0, (82, 32): 0, (82, 33): 1, (82, 34): 0, (82, 35): 0, (82, 36): 0, (82, 37): 0, (82, 38): 0, (82, 39): 0, (82, 40): 0, (82, 41): 0, (82, 42): 0, (82, 43): 0, (82, 44): 0, (82, 45): 0, (82, 46): 0, (82, 47): 0, (82, 48): 0, (82, 49): 0, (82, 50): 0, (82, 51): 0, (82, 52): 0, (82, 53): 0, (82, 54): 0, (82, 55): 0, (82, 56): 0, (82, 57): 0, (82, 58): 0, (82, 59): 0, (82, 60): 0, (82, 61): 0, (82, 62): 0, (82, 63): 0, (82, 64): 0, (82, 65): 0, (82, 66): 0, (82, 67): 0, (82, 68): 0, (82, 69): 0, (84, 1): 0, (84, 2): 0, (84, 3): 0, (84, 4): 0, (84, 5): 0, (84, 6): 0, (84, 7): 0, (84, 8): 0, (84, 9): 0, (84, 10): 0, (84, 11): 0, (84, 12): 0, (84, 13): 0, (84, 14): 0, (84, 15): 0, (84, 16): 0, (84, 17): 0, (84, 18): 0, (84, 19): 0, (84, 20): 0, (84, 21): 0, (84, 22): 0, (84, 23): 0, (84, 24): 0, (84, 25): 1, (84, 26): 0, (84, 27): 0, (84, 28): 0, (84, 29): 0, (84, 30): 0, (84, 31): 0, (84, 32): 0, (84, 33): 0, (84, 34): 0, (84, 35): 0, (84, 36): 0, (84, 37): 0, (84, 38): 0, (84, 39): 0, (84, 40): 0, (84, 41): 0, (84, 42): 0, (84, 43): 0, (84, 44): 0, (84, 45): 0, (84, 46): 0, (84, 47): 0, (84, 48): 0, (84, 49): 0, (84, 50): 0, (84, 51): 0, (84, 52): 0, (84, 53): 0, (84, 54): 0, (84, 55): 0, (84, 56): 0, (84, 57): 0, (84, 58): 0, (84, 59): 0, (84, 60): 0, (84, 61): 0, (84, 62): 0, (84, 63): 0, (84, 64): 0, (84, 65): 0, (84, 66): 0, (84, 67): 0, (84, 68): 0, (84, 69): 0, (86, 1): 0, (86, 2): 0, (86, 3): 0, (86, 4): 0, (86, 5): 0, (86, 6): 0, (86, 7): 0, (86, 8): 0, (86, 9): 0, (86, 10): 0, (86, 11): 0, (86, 12): 1, (86, 13): 0, (86, 14): 0, (86, 15): 0, (86, 16): 0, (86, 17): 0, (86, 18): 0, (86, 19): 0, (86, 20): 0, (86, 21): 0, (86, 22): 0, (86, 23): 0, (86, 24): 0, (86, 25): 0, (86, 26): 0, (86, 27): 0, (86, 28): 0, (86, 29): 0, (86, 30): 0, (86, 31): 0, (86, 32): 0, (86, 33): 0, (86, 34): 0, (86, 35): 0, (86, 36): 0, (86, 37): 0, (86, 38): 0, (86, 39): 0, (86, 40): 0, (86, 41): 0, (86, 42): 0, (86, 43): 0, (86, 44): 0, (86, 45): 0, (86, 46): 0, (86, 47): 0, (86, 48): 0, (86, 49): 0, (86, 50): 0, (86, 51): 0, (86, 52): 0, (86, 53): 0, (86, 54): 0, (86, 55): 0, (86, 56): 0, (86, 57): 0, (86, 58): 0, (86, 59): 0, (86, 60): 0, (86, 61): 0, (86, 62): 0, (86, 63): 0, (86, 64): 0, (86, 65): 0, (86, 66): 0, (86, 67): 0, (86, 68): 0, (86, 69): 0, (87, 1): 0, (87, 2): 0, (87, 3): 0, (87, 4): 0, (87, 5): 0, (87, 6): 0, (87, 7): 0, (87, 8): 0, (87, 9): 0, (87, 10): 0, (87, 11): 0, (87, 12): 0, (87, 13): 0, (87, 14): 0, (87, 15): 0, (87, 16): 0, (87, 17): 0, (87, 18): 0, (87, 19): 0, (87, 20): 0, (87, 21): 0, (87, 22): 0, (87, 23): 0, (87, 24): 0, (87, 25): 0, (87, 26): 0, (87, 27): 0, (87, 28): 1, (87, 29): 0, (87, 30): 0, (87, 31): 0, (87, 32): 0, (87, 33): 0, (87, 34): 0, (87, 35): 0, (87, 36): 0, (87, 37): 0, (87, 38): 0, (87, 39): 0, (87, 40): 0, (87, 41): 0, (87, 42): 0, (87, 43): 0, (87, 44): 0, (87, 45): 0, (87, 46): 0, (87, 47): 0, (87, 48): 0, (87, 49): 0, (87, 50): 0, (87, 51): 0, (87, 52): 0, (87, 53): 0, (87, 54): 0, (87, 55): 0, (87, 56): 0, (87, 57): 0, (87, 58): 0, (87, 59): 0, (87, 60): 0, (87, 61): 0, (87, 62): 0, (87, 63): 0, (87, 64): 0, (87, 65): 0, (87, 66): 0, (87, 67): 0, (87, 68): 0, (87, 69): 0, (89, 1): 0, (89, 2): 0, (89, 3): 0, (89, 4): 0, (89, 5): 0, (89, 6): 0, (89, 7): 0, (89, 8): 0, (89, 9): 0, (89, 10): 0, (89, 11): 0, (89, 12): 0, (89, 13): 0, (89, 14): 0, (89, 15): 0, (89, 16): 0, (89, 17): 0, (89, 18): 0, (89, 19): 0, (89, 20): 0, (89, 21): 0, (89, 22): 0, (89, 23): 0, (89, 24): 0, (89, 25): 0, (89, 26): 1, (89, 27): 0, (89, 28): 0, (89, 29): 0, (89, 30): 0, (89, 31): 0, (89, 32): 0, (89, 33): 0, (89, 34): 0, (89, 35): 0, (89, 36): 0, (89, 37): 0, (89, 38): 0, (89, 39): 0, (89, 40): 0, (89, 41): 0, (89, 42): 0, (89, 43): 0, (89, 44): 0, (89, 45): 0, (89, 46): 0, (89, 47): 0, (89, 48): 0, (89, 49): 0, (89, 50): 0, (89, 51): 0, (89, 52): 0, (89, 53): 0, (89, 54): 0, (89, 55): 0, (89, 56): 0, (89, 57): 0, (89, 58): 0, (89, 59): 0, (89, 60): 0, (89, 61): 0, (89, 62): 0, (89, 63): 0, (89, 64): 0, (89, 65): 0, (89, 66): 0, (89, 67): 0, (89, 68): 0, (89, 69): 0, (92, 1): 0, (92, 2): 0, (92, 3): 0, (92, 4): 0, (92, 5): 0, (92, 6): 0, (92, 7): 0, (92, 8): 0, (92, 9): 0, (92, 10): 0, (92, 11): 0, (92, 12): 0, (92, 13): 0, (92, 14): 0, (92, 15): 0, (92, 16): 0, (92, 17): 0, (92, 18): 0, (92, 19): 0, (92, 20): 0, (92, 21): 0, (92, 22): 0, (92, 23): 0, (92, 24): 0, (92, 25): 0, (92, 26): 0, (92, 27): 0, (92, 28): 0, (92, 29): 0, (92, 30): 0, (92, 31): 0, (92, 32): 0, (92, 33): 0, (92, 34): 0, (92, 35): 0, (92, 36): 1, (92, 37): 0, (92, 38): 0, (92, 39): 0, (92, 40): 0, (92, 41): 0, (92, 42): 0, (92, 43): 0, (92, 44): 0, (92, 45): 0, (92, 46): 0, (92, 47): 0, (92, 48): 0, (92, 49): 0, (92, 50): 0, (92, 51): 0, (92, 52): 0, (92, 53): 0, (92, 54): 0, (92, 55): 0, (92, 56): 0, (92, 57): 0, (92, 58): 0, (92, 59): 0, (92, 60): 0, (92, 61): 0, (92, 62): 0, (92, 63): 0, (92, 64): 0, (92, 65): 0, (92, 66): 0, (92, 67): 0, (92, 68): 0, (92, 69): 0, (96, 1): 0, (96, 2): 0, (96, 3): 0, (96, 4): 0, (96, 5): 0, (96, 6): 0, (96, 7): 0, (96, 8): 0, (96, 9): 0, (96, 10): 0, (96, 11): 0, (96, 12): 0, (96, 13): 0, (96, 14): 0, (96, 15): 0, (96, 16): 0, (96, 17): 0, (96, 18): 0, (96, 19): 0, (96, 20): 0, (96, 21): 0, (96, 22): 0, (96, 23): 0, (96, 24): 0, (96, 25): 0, (96, 26): 1, (96, 27): 0, (96, 28): 0, (96, 29): 0, (96, 30): 0, (96, 31): 0, (96, 32): 0, (96, 33): 0, (96, 34): 0, (96, 35): 0, (96, 36): 0, (96, 37): 0, (96, 38): 0, (96, 39): 0, (96, 40): 0, (96, 41): 0, (96, 42): 0, (96, 43): 0, (96, 44): 0, (96, 45): 0, (96, 46): 0, (96, 47): 0, (96, 48): 0, (96, 49): 0, (96, 50): 0, (96, 51): 0, (96, 52): 0, (96, 53): 0, (96, 54): 0, (96, 55): 0, (96, 56): 0, (96, 57): 0, (96, 58): 0, (96, 59): 0, (96, 60): 0, (96, 61): 0, (96, 62): 0, (96, 63): 0, (96, 64): 0, (96, 65): 0, (96, 66): 0, (96, 67): 0, (96, 68): 0, (96, 69): 0, (98, 1): 0, (98, 2): 0, (98, 3): 0, (98, 4): 0, (98, 5): 0, (98, 6): 1, (98, 7): 0, (98, 8): 0, (98, 9): 0, (98, 10): 0, (98, 11): 0, (98, 12): 0, (98, 13): 0, (98, 14): 0, (98, 15): 0, (98, 16): 0, (98, 17): 0, (98, 18): 0, (98, 19): 0, (98, 20): 0, (98, 21): 0, (98, 22): 0, (98, 23): 0, (98, 24): 0, (98, 25): 0, (98, 26): 0, (98, 27): 0, (98, 28): 0, (98, 29): 0, (98, 30): 0, (98, 31): 0, (98, 32): 0, (98, 33): 0, (98, 34): 0, (98, 35): 0, (98, 36): 0, (98, 37): 0, (98, 38): 0, (98, 39): 0, (98, 40): 0, (98, 41): 0, (98, 42): 0, (98, 43): 0, (98, 44): 0, (98, 45): 0, (98, 46): 0, (98, 47): 0, (98, 48): 0, (98, 49): 0, (98, 50): 0, (98, 51): 0, (98, 52): 0, (98, 53): 0, (98, 54): 0, (98, 55): 0, (98, 56): 0, (98, 57): 0, (98, 58): 0, (98, 59): 0, (98, 60): 0, (98, 61): 0, (98, 62): 0, (98, 63): 0, (98, 64): 0, (98, 65): 0, (98, 66): 0, (98, 67): 0, (98, 68): 0, (98, 69): 0, (100, 1): 0, (100, 2): 0, (100, 3): 0, (100, 4): 0, (100, 5): 0, (100, 6): 0, (100, 7): 0, (100, 8): 0, (100, 9): 0, (100, 10): 0, (100, 11): 0, (100, 12): 0, (100, 13): 0, (100, 14): 0, (100, 15): 0, (100, 16): 0, (100, 17): 0, (100, 18): 0, (100, 19): 0, (100, 20): 0, (100, 21): 0, (100, 22): 0, (100, 23): 0, (100, 24): 0, (100, 25): 0, (100, 26): 0, (100, 27): 0, (100, 28): 0, (100, 29): 0, (100, 30): 1, (100, 31): 0, (100, 32): 0, (100, 33): 0, (100, 34): 0, (100, 35): 0, (100, 36): 0, (100, 37): 0, (100, 38): 0, (100, 39): 0, (100, 40): 0, (100, 41): 0, (100, 42): 0, (100, 43): 0, (100, 44): 0, (100, 45): 0, (100, 46): 0, (100, 47): 0, (100, 48): 0, (100, 49): 0, (100, 50): 0, (100, 51): 0, (100, 52): 0, (100, 53): 0, (100, 54): 0, (100, 55): 0, (100, 56): 0, (100, 57): 0, (100, 58): 0, (100, 59): 0, (100, 60): 0, (100, 61): 0, (100, 62): 0, (100, 63): 0, (100, 64): 0, (100, 65): 0, (100, 66): 0, (100, 67): 0, (100, 68): 0, (100, 69): 0, (107, 1): 0, (107, 2): 0, (107, 3): 0, (107, 4): 0, (107, 5): 0, (107, 6): 0, (107, 7): 0, (107, 8): 0, (107, 9): 0, (107, 10): 0, (107, 11): 0, (107, 12): 0, (107, 13): 0, (107, 14): 0, (107, 15): 0, (107, 16): 0, (107, 17): 0, (107, 18): 0, (107, 19): 0, (107, 20): 0, (107, 21): 0, (107, 22): 0, (107, 23): 0, (107, 24): 0, (107, 25): 0, (107, 26): 0, (107, 27): 0, (107, 28): 0, (107, 29): 0, (107, 30): 0, (107, 31): 0, (107, 32): 1, (107, 33): 0, (107, 34): 0, (107, 35): 0, (107, 36): 0, (107, 37): 0, (107, 38): 0, (107, 39): 0, (107, 40): 0, (107, 41): 0, (107, 42): 0, (107, 43): 0, (107, 44): 0, (107, 45): 0, (107, 46): 0, (107, 47): 0, (107, 48): 0, (107, 49): 0, (107, 50): 0, (107, 51): 0, (107, 52): 0, (107, 53): 0, (107, 54): 0, (107, 55): 0, (107, 56): 0, (107, 57): 0, (107, 58): 0, (107, 59): 0, (107, 60): 0, (107, 61): 0, (107, 62): 0, (107, 63): 0, (107, 64): 0, (107, 65): 0, (107, 66): 0, (107, 67): 0, (107, 68): 0, (107, 69): 0, (108, 1): 0, (108, 2): 0, (108, 3): 0, (108, 4): 0, (108, 5): 0, (108, 6): 0, (108, 7): 0, (108, 8): 0, (108, 9): 0, (108, 10): 0, (108, 11): 1, (108, 12): 0, (108, 13): 0, (108, 14): 0, (108, 15): 0, (108, 16): 0, (108, 17): 0, (108, 18): 0, (108, 19): 0, (108, 20): 0, (108, 21): 0, (108, 22): 0, (108, 23): 0, (108, 24): 0, (108, 25): 0, (108, 26): 0, (108, 27): 0, (108, 28): 0, (108, 29): 0, (108, 30): 0, (108, 31): 0, (108, 32): 0, (108, 33): 0, (108, 34): 0, (108, 35): 0, (108, 36): 0, (108, 37): 0, (108, 38): 0, (108, 39): 0, (108, 40): 0, (108, 41): 0, (108, 42): 0, (108, 43): 0, (108, 44): 0, (108, 45): 0, (108, 46): 0, (108, 47): 0, (108, 48): 0, (108, 49): 0, (108, 50): 0, (108, 51): 0, (108, 52): 0, (108, 53): 0, (108, 54): 0, (108, 55): 0, (108, 56): 0, (108, 57): 0, (108, 58): 0, (108, 59): 0, (108, 60): 0, (108, 61): 0, (108, 62): 0, (108, 63): 0, (108, 64): 0, (108, 65): 0, (108, 66): 0, (108, 67): 0, (108, 68): 0, (108, 69): 0, (109, 1): 0, (109, 2): 0, (109, 3): 0, (109, 4): 0, (109, 5): 0, (109, 6): 0, (109, 7): 0, (109, 8): 0, (109, 9): 0, (109, 10): 0, (109, 11): 0, (109, 12): 0, (109, 13): 0, (109, 14): 0, (109, 15): 0, (109, 16): 0, (109, 17): 0, (109, 18): 0, (109, 19): 0, (109, 20): 0, (109, 21): 0, (109, 22): 0, (109, 23): 0, (109, 24): 0, (109, 25): 0, (109, 26): 0, (109, 27): 0, (109, 28): 0, (109, 29): 1, (109, 30): 0, (109, 31): 0, (109, 32): 0, (109, 33): 0, (109, 34): 0, (109, 35): 0, (109, 36): 0, (109, 37): 0, (109, 38): 0, (109, 39): 0, (109, 40): 0, (109, 41): 0, (109, 42): 0, (109, 43): 0, (109, 44): 0, (109, 45): 0, (109, 46): 0, (109, 47): 0, (109, 48): 0, (109, 49): 0, (109, 50): 0, (109, 51): 0, (109, 52): 0, (109, 53): 0, (109, 54): 0, (109, 55): 0, (109, 56): 0, (109, 57): 0, (109, 58): 0, (109, 59): 0, (109, 60): 0, (109, 61): 0, (109, 62): 0, (109, 63): 0, (109, 64): 0, (109, 65): 0, (109, 66): 0, (109, 67): 0, (109, 68): 0, (109, 69): 0, (110, 1): 0, (110, 2): 0, (110, 3): 0, (110, 4): 0, (110, 5): 0, (110, 6): 0, (110, 7): 0, (110, 8): 0, (110, 9): 0, (110, 10): 0, (110, 11): 0, (110, 12): 0, (110, 13): 0, (110, 14): 0, (110, 15): 0, (110, 16): 0, (110, 17): 0, (110, 18): 0, (110, 19): 0, (110, 20): 0, (110, 21): 0, (110, 22): 0, (110, 23): 0, (110, 24): 0, (110, 25): 0, (110, 26): 0, (110, 27): 0, (110, 28): 0, (110, 29): 0, (110, 30): 0, (110, 31): 0, (110, 32): 0, (110, 33): 1, (110, 34): 0, (110, 35): 0, (110, 36): 0, (110, 37): 0, (110, 38): 0, (110, 39): 0, (110, 40): 0, (110, 41): 0, (110, 42): 0, (110, 43): 0, (110, 44): 0, (110, 45): 0, (110, 46): 0, (110, 47): 0, (110, 48): 0, (110, 49): 0, (110, 50): 0, (110, 51): 0, (110, 52): 0, (110, 53): 0, (110, 54): 0, (110, 55): 0, (110, 56): 0, (110, 57): 0, (110, 58): 0, (110, 59): 0, (110, 60): 0, (110, 61): 0, (110, 62): 0, (110, 63): 0, (110, 64): 0, (110, 65): 0, (110, 66): 0, (110, 67): 0, (110, 68): 0, (110, 69): 0, (112, 1): 0, (112, 2): 0, (112, 3): 0, (112, 4): 0, (112, 5): 0, (112, 6): 0, (112, 7): 0, (112, 8): 0, (112, 9): 0, (112, 10): 0, (112, 11): 0, (112, 12): 0, (112, 13): 0, (112, 14): 0, (112, 15): 0, (112, 16): 0, (112, 17): 0, (112, 18): 0, (112, 19): 1, (112, 20): 0, (112, 21): 0, (112, 22): 0, (112, 23): 0, (112, 24): 0, (112, 25): 0, (112, 26): 0, (112, 27): 0, (112, 28): 0, (112, 29): 0, (112, 30): 0, (112, 31): 0, (112, 32): 0, (112, 33): 0, (112, 34): 0, (112, 35): 0, (112, 36): 0, (112, 37): 0, (112, 38): 0, (112, 39): 0, (112, 40): 0, (112, 41): 0, (112, 42): 0, (112, 43): 0, (112, 44): 0, (112, 45): 0, (112, 46): 0, (112, 47): 0, (112, 48): 0, (112, 49): 0, (112, 50): 0, (112, 51): 0, (112, 52): 0, (112, 53): 0, (112, 54): 0, (112, 55): 0, (112, 56): 0, (112, 57): 0, (112, 58): 0, (112, 59): 0, (112, 60): 0, (112, 61): 0, (112, 62): 0, (112, 63): 0, (112, 64): 0, (112, 65): 0, (112, 66): 0, (112, 67): 0, (112, 68): 0, (112, 69): 0, (117, 1): 0, (117, 2): 0, (117, 3): 0, (117, 4): 0, (117, 5): 0, (117, 6): 0, (117, 7): 0, (117, 8): 0, (117, 9): 0, (117, 10): 0, (117, 11): 0, (117, 12): 0, (117, 13): 0, (117, 14): 0, (117, 15): 0, (117, 16): 0, (117, 17): 0, (117, 18): 0, (117, 19): 0, (117, 20): 0, (117, 21): 0, (117, 22): 0, (117, 23): 0, (117, 24): 0, (117, 25): 0, (117, 26): 0, (117, 27): 0, (117, 28): 0, (117, 29): 0, (117, 30): 0, (117, 31): 0, (117, 32): 0, (117, 33): 1, (117, 34): 0, (117, 35): 0, (117, 36): 0, (117, 37): 0, (117, 38): 0, (117, 39): 0, (117, 40): 0, (117, 41): 0, (117, 42): 0, (117, 43): 0, (117, 44): 0, (117, 45): 0, (117, 46): 0, (117, 47): 0, (117, 48): 0, (117, 49): 0, (117, 50): 0, (117, 51): 0, (117, 52): 0, (117, 53): 0, (117, 54): 0, (117, 55): 0, (117, 56): 0, (117, 57): 0, (117, 58): 0, (117, 59): 0, (117, 60): 0, (117, 61): 0, (117, 62): 0, (117, 63): 0, (117, 64): 0, (117, 65): 0, (117, 66): 0, (117, 67): 0, (117, 68): 0, (117, 69): 0, (120, 1): 0, (120, 2): 0, (120, 3): 0, (120, 4): 0, (120, 5): 0, (120, 6): 0, (120, 7): 0, (120, 8): 0, (120, 9): 0, (120, 10): 0, (120, 11): 0, (120, 12): 0, (120, 13): 0, (120, 14): 0, (120, 15): 0, (120, 16): 0, (120, 17): 0, (120, 18): 0, (120, 19): 0, (120, 20): 0, (120, 21): 1, (120, 22): 0, (120, 23): 0, (120, 24): 0, (120, 25): 0, (120, 26): 0, (120, 27): 0, (120, 28): 0, (120, 29): 0, (120, 30): 0, (120, 31): 0, (120, 32): 0, (120, 33): 0, (120, 34): 0, (120, 35): 0, (120, 36): 0, (120, 37): 0, (120, 38): 0, (120, 39): 0, (120, 40): 0, (120, 41): 0, (120, 42): 0, (120, 43): 0</t>
+  </si>
+  <si>
+    <t>{(1, 1): 0, (1, 2): 0, (1, 3): 0, (1, 4): 0, (2, 1): 0, (2, 2): 0, (2, 3): 0, (2, 4): 0, (6, 1): 0, (6, 2): 0, (6, 3): 0, (6, 4): 0, (7, 1): 0, (7, 2): 0, (7, 3): 0, (7, 4): 0, (16, 1): 0, (16, 2): 0, (16, 3): 0, (16, 4): 0, (26, 1): 0, (26, 2): 0, (26, 3): 0, (26, 4): 0, (35, 1): 0, (35, 2): 0, (35, 3): 0, (35, 4): 0, (38, 1): 0, (38, 2): 0, (38, 3): 0, (38, 4): 0, (39, 1): 0, (39, 2): 0, (39, 3): 0, (39, 4): 0, (41, 1): 0, (41, 2): 0, (41, 3): 0, (41, 4): 0, (42, 1): 0, (42, 2): 0, (42, 3): 0, (42, 4): 0, (43, 1): 1, (43, 2): 0, (43, 3): 0, (43, 4): 0, (46, 1): 0, (46, 2): 0, (46, 3): 0, (46, 4): 0, (48, 1): 0, (48, 2): 0, (48, 3): 1, (48, 4): 0, (49, 1): 1, (49, 2): 0, (49, 3): 0, (49, 4): 0, (51, 1): 0, (51, 2): 0, (51, 3): 0, (51, 4): 1, (52, 1): 0, (52, 2): 0, (52, 3): 0, (52, 4): 0, (57, 1): 0, (57, 2): 0, (57, 3): 0, (57, 4): 0, (70, 1): 0, (70, 2): 0, (70, 3): 0, (70, 4): 0, (73, 1): 0, (73, 2): 0, (73, 3): 0, (73, 4): 0, (75, 1): 1, (75, 2): 0, (75, 3): 0, (75, 4): 0, (82, 1): 0, (82, 2): 0, (82, 3): 0, (82, 4): 0, (84, 1): 0, (84, 2): 0, (84, 3): 0, (84, 4): 0, (86, 1): 0, (86, 2): 0, (86, 3): 0, (86, 4): 1, (87, 1): 0, (87, 2): 0, (87, 3): 0, (87, 4): 0, (89, 1): 0, (89, 2): 0, (89, 3): 0, (89, 4): 0, (92, 1): 0, (92, 2): 0, (92, 3): 0, (92, 4): 0, (96, 1): 0, (96, 2): 0, (96, 3): 1, (96, 4): 0, (98, 1): 1, (98, 2): 0, (98, 3): 0, (98, 4): 0, (100, 1): 1, (100, 2): 0, (100, 3): 0, (100, 4): 0, (107, 1): 1, (107, 2): 0, (107, 3): 0, (107, 4): 0, (108, 1): 0, (108, 2): 0, (108, 3): 0, (108, 4): 0, (109, 1): 0, (109, 2): 0, (109, 3): 0, (109, 4): 0, (110, 1): 0, (110, 2): 0, (110, 3): 0, (110, 4): 0, (112, 1): 0, (112, 2): 0, (112, 3): 0, (112, 4): 0, (117, 1): 0, (117, 2): 0, (117, 3): 0, (117, 4): 0, (120, 1): 0, (120, 2): 0, (120, 3): 0, (120, 4): 0, (121, 1): 0, (121, 2): 0, (121, 3): 0, (121, 4): 0, (123, 1): 1, (123, 2): 0, (123, 3): 0, (123, 4): 0, (125, 1): 0, (125, 2): 0, (125, 3): 0, (125, 4): 0, (131, 1): 0, (131, 2): 0, (131, 3): 0, (131, 4): 0, (133, 1): 0, (133, 2): 0, (133, 3): 0, (133, 4): 0, (134, 1): 1, (134, 2): 0, (134, 3): 0, (134, 4): 0, (135, 1): 0, (135, 2): 0, (135, 3): 0, (135, 4): 0}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{(3, 1): 0, (3, 2): 0, (3, 3): 0, (3, 4): 0, (3, 5): 0, (3, 6): 0, (3, 7): 0, (3, 8): 0, (3, 9): 0, (3, 10): 0, (3, 11): 0, (3, 12): 0, (3, 13): 0, (3, 14): 0, (3, 15): 0, (3, 16): 0, (3, 17): 0, (3, 18): 0, (3, 19): 0, (3, 20): 0, (3, 21): 0, (3, 22): 0, (3, 23): 0, (3, 24): 0, (3, 25): 0, (3, 26): 0, (3, 27): 0, (3, 28): 0, (3, 29): 0, (3, 30): 0, (3, 31): 0, (3, 32): 0, (3, 33): 0, (3, 34): 0, (3, 35): 0, (3, 36): 0, (3, 37): 0, (3, 38): 0, (3, 39): 0, (3, 40): 0, (3, 41): 0, (3, 42): 0, (3, 43): 0, (3, 44): 0, (3, 45): 1, (3, 46): 1, (3, 47): 1, (3, 48): 1, (3, 49): 1, (3, 50): 1, (3, 51): 1, (3, 52): 1, (3, 53): 1, (3, 54): 1, (3, 55): 1, (3, 56): 1, (3, 57): 1, (3, 58): 1, (3, 59): 1, (3, 60): 0, (3, 61): 0, (3, 62): 0, (3, 63): 0, (3, 64): 0, (3, 65): 0, (3, 66): 0, (3, 67): 0, (3, 68): 0, (3, 69): 0, (4, 1): 0, (4, 2): 0, (4, 3): 0, (4, 4): 0, (4, 5): 0, (4, 6): 0, (4, 7): 0, (4, 8): 0, (4, 9): 0, (4, 10): 0, (4, 11): 0, (4, 12): 0, (4, 13): 0, (4, 14): 0, (4, 15): 0, (4, 16): 0, (4, 17): 0, (4, 18): 0, (4, 19): 0, (4, 20): 0, (4, 21): 0, (4, 22): 0, (4, 23): 0, (4, 24): 0, (4, 25): 0, (4, 26): 0, (4, 27): 0, (4, 28): 0, (4, 29): 0, (4, 30): 0, (4, 31): 0, (4, 32): 0, (4, 33): 0, (4, 34): 0, (4, 35): 0, (4, 36): 0, (4, 37): 0, (4, 38): 0, (4, 39): 0, (4, 40): 0, (4, 41): 0, (4, 42): 0, (4, 43): 0, (4, 44): 0, (4, 45): 0, (4, 46): 0, (4, 47): 0, (4, 48): 0, (4, 49): 0, (4, 50): 1, (4, 51): 1, (4, 52): 1, (4, 53): 1, (4, 54): 1, (4, 55): 1, (4, 56): 1, (4, 57): 1, (4, 58): 1, (4, 59): 1, (4, 60): 1, (4, 61): 1, (4, 62): 1, (4, 63): 1, (4, 64): 0, (4, 65): 0, (4, 66): 0, (4, 67): 0, (4, 68): 0, (4, 69): 0, (8, 1): 0, (8, 2): 0, (8, 3): 0, (8, 4): 0, (8, 5): 0, (8, 6): 0, (8, 7): 0, (8, 8): 0, (8, 9): 0, (8, 10): 0, (8, 11): 0, (8, 12): 0, (8, 13): 0, (8, 14): 0, (8, 15): 0, (8, 16): 0, (8, 17): 0, (8, 18): 0, (8, 19): 0, (8, 20): 0, (8, 21): 0, (8, 22): 0, (8, 23): 0, (8, 24): 0, (8, 25): 0, (8, 26): 0, (8, 27): 0, (8, 28): 0, (8, 29): 0, (8, 30): 0, (8, 31): 0, (8, 32): 0, (8, 33): 0, (8, 34): 0, (8, 35): 0, (8, 36): 0, (8, 37): 0, (8, 38): 0, (8, 39): 1, (8, 40): 1, (8, 41): 1, (8, 42): 1, (8, 43): 1, (8, 44): 1, (8, 45): 1, (8, 46): 1, (8, 47): 1, (8, 48): 1, (8, 49): 0, (8, 50): 0, (8, 51): 0, (8, 52): 0, (8, 53): 0, (8, 54): 0, (8, 55): 0, (8, 56): 0, (8, 57): 0, (8, 58): 0, (8, 59): 0, (8, 60): 0, (8, 61): 0, (8, 62): 0, (8, 63): 0, (8, 64): 0, (8, 65): 0, (8, 66): 0, (8, 67): 0, (8, 68): 0, (8, 69): 0, (9, 1): 0, (9, 2): 0, (9, 3): 0, (9, 4): 0, (9, 5): 0, (9, 6): 0, (9, 7): 0, (9, 8): 0, (9, 9): 0, (9, 10): 0, (9, 11): 0, (9, 12): 0, (9, 13): 0, (9, 14): 0, (9, 15): 0, (9, 16): 0, (9, 17): 0, (9, 18): 0, (9, 19): 0, (9, 20): 0, (9, 21): 0, (9, 22): 0, (9, 23): 0, (9, 24): 0, (9, 25): 0, (9, 26): 0, (9, 27): 0, (9, 28): 0, (9, 29): 0, (9, 30): 0, (9, 31): 0, (9, 32): 0, (9, 33): 0, (9, 34): 0, (9, 35): 0, (9, 36): 0, (9, 37): 0, (9, 38): 0, (9, 39): 0, (9, 40): 0, (9, 41): 0, (9, 42): 0, (9, 43): 0, (9, 44): 0, (9, 45): 0, (9, 46): 0, (9, 47): 0, (9, 48): 0, (9, 49): 0, (9, 50): 0, (9, 51): 0, (9, 52): 0, (9, 53): 0, (9, 54): 0, (9, 55): 0, (9, 56): 0, (9, 57): 0, (9, 58): 0, (9, 59): 0, (9, 60): 0, (9, 61): 0, (9, 62): 0, (9, 63): 0, (9, 64): 1, (9, 65): 1, (9, 66): 1, (9, 67): 1, (9, 68): 1, (9, 69): 1, (10, 1): 0, (10, 2): 0, (10, 3): 0, (10, 4): 0, (10, 5): 0, (10, 6): 0, (10, 7): 0, (10, 8): 0, (10, 9): 0, (10, 10): 0, (10, 11): 0, (10, 12): 0, (10, 13): 0, (10, 14): 0, (10, 15): 0, (10, 16): 0, (10, 17): 0, (10, 18): 0, (10, 19): 0, (10, 20): 0, (10, 21): 0, (10, 22): 0, (10, 23): 0, (10, 24): 0, (10, 25): 0, (10, 26): 0, (10, 27): 0, (10, 28): 0, (10, 29): 0, (10, 30): 0, (10, 31): 0, (10, 32): 0, (10, 33): 0, (10, 34): 0, (10, 35): 0, (10, 36): 0, (10, 37): 0, (10, 38): 0, (10, 39): 0, (10, 40): 0, (10, 41): 0, (10, 42): 0, (10, 43): 1, (10, 44): 1, (10, 45): 1, (10, 46): 1, (10, 47): 1, (10, 48): 1, (10, 49): 1, (10, 50): 1, (10, 51): 1, (10, 52): 1, (10, 53): 1, (10, 54): 1, (10, 55): 0, (10, 56): 0, (10, 57): 0, (10, 58): 0, (10, 59): 0, (10, 60): 0, (10, 61): 0, (10, 62): 0, (10, 63): 0, (10, 64): 0, (10, 65): 0, (10, 66): 0, (10, 67): 0, (10, 68): 0, (10, 69): 0, (11, 1): 0, (11, 2): 0, (11, 3): 0, (11, 4): 0, (11, 5): 0, (11, 6): 0, (11, 7): 0, (11, 8): 0, (11, 9): 0, (11, 10): 0, (11, 11): 0, (11, 12): 0, (11, 13): 0, (11, 14): 0, (11, 15): 0, (11, 16): 0, (11, 17): 0, (11, 18): 0, (11, 19): 0, (11, 20): 0, (11, 21): 0, (11, 22): 0, (11, 23): 0, (11, 24): 0, (11, 25): 0, (11, 26): 0, (11, 27): 0, (11, 28): 0, (11, 29): 0, (11, 30): 0, (11, 31): 0, (11, 32): 0, (11, 33): 0, (11, 34): 0, (11, 35): 0, (11, 36): 0, (11, 37): 0, (11, 38): 0, (11, 39): 0, (11, 40): 0, (11, 41): 0, (11, 42): 0, (11, 43): 0, (11, 44): 0, (11, 45): 0, (11, 46): 0, (11, 47): 0, (11, 48): 0, (11, 49): 0, (11, 50): 0, (11, 51): 0, (11, 52): 0, (11, 53): 0, (11, 54): 0, (11, 55): 0, (11, 56): 0, (11, 57): 1, (11, 58): 1, (11, 59): 1, (11, 60): 1, (11, 61): 1, (11, 62): 1, (11, 63): 0, (11, 64): 0, (11, 65): 0, (11, 66): 0, (11, 67): 0, (11, 68): 0, (11, 69): 0, (12, 1): 0, (12, 2): 0, (12, 3): 0, (12, 4): 0, (12, 5): 0, (12, 6): 0, (12, 7): 0, (12, 8): 0, (12, 9): 0, (12, 10): 0, (12, 11): 0, (12, 12): 0, (12, 13): 0, (12, 14): 0, (12, 15): 0, (12, 16): 0, (12, 17): 0, (12, 18): 0, (12, 19): 0, (12, 20): 0, (12, 21): 0, (12, 22): 0, (12, 23): 0, (12, 24): 0, (12, 25): 0, (12, 26): 0, (12, 27): 0, (12, 28): 0, (12, 29): 0, (12, 30): 0, (12, 31): 0, (12, 32): 0, (12, 33): 0, (12, 34): 1, (12, 35): 1, (12, 36): 1, (12, 37): 1, (12, 38): 1, (12, 39): 1, (12, 40): 1, (12, 41): 1, (12, 42): 1, (12, 43): 1, (12, 44): 1, (12, 45): 0, (12, 46): 0, (12, 47): 0, (12, 48): 0, (12, 49): 0, (12, 50): 0, (12, 51): 0, (12, 52): 0, (12, 53): 0, (12, 54): 0, (12, 55): 0, (12, 56): 0, (12, 57): 0, (12, 58): 0, (12, 59): 0, (12, 60): 0, (12, 61): 0, (12, 62): 0, (12, 63): 0, (12, 64): 0, (12, 65): 0, (12, 66): 0, (12, 67): 0, (12, 68): 0, (12, 69): 0, (21, 1): 0, (21, 2): 0, (21, 3): 0, (21, 4): 0, (21, 5): 0, (21, 6): 0, (21, 7): 0, (21, 8): 0, (21, 9): 0, (21, 10): 0, (21, 11): 0, (21, 12): 0, (21, 13): 0, (21, 14): 0, (21, 15): 0, (21, 16): 0, (21, 17): 0, (21, 18): 0, (21, 19): 0, (21, 20): 0, (21, 21): 0, (21, 22): 0, (21, 23): 0, (21, 24): 0, (21, 25): 0, (21, 26): 0, (21, 27): 0, (21, 28): 0, (21, 29): 0, (21, 30): 0, (21, 31): 0, (21, 32): 0, (21, 33): 0, (21, 34): 0, (21, 35): 0, (21, 36): 0, (21, 37): 0, (21, 38): 0, (21, 39): 0, (21, 40): 0, (21, 41): 0, (21, 42): 0, (21, 43): 0, (21, 44): 0, (21, 45): 1, (21, 46): 1, (21, 47): 1, (21, 48): 1, (21, 49): 1, (21, 50): 1, (21, 51): 1, (21, 52): 1, (21, 53): 0, (21, 54): 0, (21, 55): 0, (21, 56): 0, (21, 57): 0, (21, 58): 0, (21, 59): 0, (21, 60): 0, (21, 61): 0, (21, 62): 0, (21, 63): 0, (21, 64): 0, (21, 65): 0, (21, 66): 0, (21, 67): 0, (21, 68): 0, (21, 69): 0, (23, 1): 0, (23, 2): 0, (23, 3): 0, (23, 4): 0, (23, 5): 0, (23, 6): 0, (23, 7): 0, (23, 8): 0, (23, 9): 0, (23, 10): 0, (23, 11): 0, (23, 12): 0, (23, 13): 0, (23, 14): 0, (23, 15): 0, (23, 16): 0, (23, 17): 0, (23, 18): 0, (23, 19): 0, (23, 20): 0, (23, 21): 0, (23, 22): 0, (23, 23): 0, (23, 24): 0, (23, 25): 0, (23, 26): 0, (23, 27): 0, (23, 28): 0, (23, 29): 0, (23, 30): 0, (23, 31): 0, (23, 32): 0, (23, 33): 1, (23, 34): 1, (23, 35): 1, (23, 36): 1, (23, 37): 1, (23, 38): 1, (23, 39): 1, (23, 40): 1, (23, 41): 1, (23, 42): 1, (23, 43): 0, (23, 44): 0, (23, 45): 0, (23, 46): 0, (23, 47): 0, (23, 48): 0, (23, 49): 0, (23, 50): 0, (23, 51): 0, (23, 52): 0, (23, 53): 0, (23, 54): 0, (23, 55): 0, (23, 56): 0, (23, 57): 0, (23, 58): 0, (23, 59): 0, (23, 60): 0, (23, 61): 0, (23, 62): 0, (23, 63): 0, (23, 64): 0, (23, 65): 0, (23, 66): 0, (23, 67): 0, (23, 68): 0, (23, 69): 0, (24, 1): 0, (24, 2): 0, (24, 3): 0, (24, 4): 0, (24, 5): 0, (24, 6): 0, (24, 7): 0, (24, 8): 0, (24, 9): 0, (24, 10): 0, (24, 11): 0, (24, 12): 0, (24, 13): 0, (24, 14): 0, (24, 15): 0, (24, 16): 0, (24, 17): 0, (24, 18): 0, (24, 19): 0, (24, 20): 0, (24, 21): 0, (24, 22): 0, (24, 23): 0, (24, 24): 0, (24, 25): 0, (24, 26): 0, (24, 27): 0, (24, 28): 0, (24, 29): 0, (24, 30): 0, (24, 31): 0, (24, 32): 0, (24, 33): 0, (24, 34): 0, (24, 35): 0, (24, 36): 0, (24, 37): 0, (24, 38): 0, (24, 39): 0, (24, 40): 0, (24, 41): 0, (24, 42): 0, (24, 43): 0, (24, 44): 0, (24, 45): 0, (24, 46): 0, (24, 47): 0, (24, 48): 0, (24, 49): 0, (24, 50): 0, (24, 51): 0, (24, 52): 0, (24, 53): 0, (24, 54): 0, (24, 55): 0, (24, 56): 0, (24, 57): 0, (24, 58): 0, (24, 59): 1, (24, 60): 1, (24, 61): 1, (24, 62): 1, (24, 63): 1, (24, 64): 1, (24, 65): 1, (24, 66): 1, (24, 67): 1, (24, 68): 1, (24, 69): 0, (29, 1): 0, (29, 2): 0, (29, 3): 0, (29, 4): 0, (29, 5): 0, (29, 6): 0, (29, 7): 0, (29, 8): 0, (29, 9): 0, (29, 10): 0, (29, 11): 0, (29, 12): 0, (29, 13): 0, (29, 14): 0, (29, 15): 0, (29, 16): 0, (29, 17): 0, (29, 18): 0, (29, 19): 0, (29, 20): 0, (29, 21): 0, (29, 22): 0, (29, 23): 0, (29, 24): 0, (29, 25): 0, (29, 26): 0, (29, 27): 0, (29, 28): 0, (29, 29): 0, (29, 30): 0, (29, 31): 0, (29, 32): 0, (29, 33): 0, (29, 34): 0, (29, 35): 0, (29, 36): 0, (29, 37): 0, (29, 38): 1, (29, 39): 1, (29, 40): 1, (29, 41): 1, (29, 42): 1, (29, 43): 1, (29, 44): 1, (29, 45): 1, (29, 46): 1, (29, 47): 1, (29, 48): 1, (29, 49): 1, (29, 50): 1, (29, 51): 0, (29, 52): 0, (29, 53): 0, (29, 54): 0, (29, 55): 0, (29, 56): 0, (29, 57): 0, (29, 58): 0, (29, 59): 0, (29, 60): 0, (29, 61): 0, (29, 62): 0, (29, 63): 0, (29, 64): 0, (29, 65): 0, (29, 66): 0, (29, 67): 0, (29, 68): 0, (29, 69): 0, (31, 1): 0, (31, 2): 0, (31, 3): 0, (31, 4): 0, (31, 5): 0, (31, 6): 0, (31, 7): 0, (31, 8): 0, (31, 9): 0, (31, 10): 0, (31, 11): 0, (31, 12): 0, (31, 13): 0, (31, 14): 0, (31, 15): 0, (31, 16): 0, (31, 17): 0, (31, 18): 0, (31, 19): 0, (31, 20): 0, (31, 21): 0, (31, 22): 0, (31, 23): 0, (31, 24): 0, (31, 25): 0, (31, 26): 0, (31, 27): 0, (31, 28): 0, (31, 29): 0, (31, 30): 0, (31, 31): 0, (31, 32): 0, (31, 33): 0, (31, 34): 0, (31, 35): 0, (31, 36): 0, (31, 37): 0, (31, 38): 0, (31, 39): 0, (31, 40): 0, (31, 41): 0, (31, 42): 0, (31, 43): 0, (31, 44): 0, (31, 45): 0, (31, 46): 0, (31, 47): 0, (31, 48): 0, (31, 49): 0, (31, 50): 0, (31, 51): 0, (31, 52): 0, (31, 53): 0, (31, 54): 0, (31, 55): 0, (31, 56): 0, (31, 57): 0, (31, 58): 0, (31, 59): 0, (31, 60): 0, (31, 61): 0, (31, 62): 0, (31, 63): 0, (31, 64): 0, (31, 65): 0, (31, 66): 0, (31, 67): 0, (31, 68): 1, (31, 69): 1, (33, 1): 0, (33, 2): 0, (33, 3): 0, (33, 4): 0, (33, 5): 0, (33, 6): 0, (33, 7): 0, (33, 8): 0, (33, 9): 0, (33, 10): 0, (33, 11): 0, (33, 12): 0, (33, 13): 0, (33, 14): 0, (33, 15): 0, (33, 16): 0, (33, 17): 0, (33, 18): 0, (33, 19): 0, (33, 20): 0, (33, 21): 0, (33, 22): 0, (33, 23): 0, (33, 24): 0, (33, 25): 0, (33, 26): 0, (33, 27): 0, (33, 28): 0, (33, 29): 0, (33, 30): 0, (33, 31): 0, (33, 32): 0, (33, 33): 0, (33, 34): 0, (33, 35): 0, (33, 36): 0, (33, 37): 0, (33, 38): 0, (33, 39): 0, (33, 40): 0, (33, 41): 0, (33, 42): 0, (33, 43): 0, (33, 44): 0, (33, 45): 0, (33, 46): 0, (33, 47): 0, (33, 48): 0, (33, 49): 0, (33, 50): 0, (33, 51): 0, (33, 52): 0, (33, 53): 0, (33, 54): 0, (33, 55): 0, (33, 56): 0, (33, 57): 0, (33, 58): 0, (33, 59): 0, (33, 60): 0, (33, 61): 0, (33, 62): 0, (33, 63): 0, (33, 64): 0, (33, 65): 0, (33, 66): 1, (33, 67): 1, (33, 68): 1, (33, 69): 1, (45, 1): 0, (45, 2): 0, (45, 3): 0, (45, 4): 0, (45, 5): 0, (45, 6): 0, (45, 7): 0, (45, 8): 0, (45, 9): 0, (45, 10): 0, (45, 11): 0, (45, 12): 0, (45, 13): 0, (45, 14): 0, (45, 15): 0, (45, 16): 0, (45, 17): 0, (45, 18): 0, (45, 19): 0, (45, 20): 0, (45, 21): 0, (45, 22): 0, (45, 23): 0, (45, 24): 0, (45, 25): 0, (45, 26): 0, (45, 27): 0, (45, 28): 0, (45, 29): 0, (45, 30): 0, (45, 31): 0, (45, 32): 0, (45, 33): 0, (45, 34): 0, (45, 35): 0, (45, 36): 0, (45, 37): 0, (45, 38): 0, (45, 39): 0, (45, 40): 0, (45, 41): 0, (45, 42): 0, (45, 43): 0, (45, 44): 0, (45, 45): 0, (45, 46): 0, (45, 47): 0, (45, 48): 0, (45, 49): 0, (45, 50): 0, (45, 51): 0, (45, 52): 0, (45, 53): 0, (45, 54): 0, (45, 55): 0, (45, 56): 0, (45, 57): 0, (45, 58): 0, (45, 59): 0, (45, 60): 1, (45, 61): 1, (45, 62): 1, (45, 63): 1, (45, 64): 1, (45, 65): 1, (45, 66): 0, (45, 67): 0, (45, 68): 0, (45, 69): 0, (50, 1): 0, (50, 2): 0, (50, 3): 0, (50, 4): 0, (50, 5): 0, (50, 6): 0, (50, 7): 0, (50, 8): 0, (50, 9): 0, (50, 10): 0, (50, 11): 0, (50, 12): 0, (50, 13): 0, (50, 14): 0, (50, 15): 0, (50, 16): 0, (50, 17): 0, (50, 18): 0, (50, 19): 0, (50, 20): 0, (50, 21): 0, (50, 22): 0, (50, 23): 0, (50, 24): 0, (50, 25): 0, (50, 26): 0, (50, 27): 0, (50, 28): 0, (50, 29): 0, (50, 30): 0, (50, 31): 0, (50, 32): 0, (50, 33): 0, (50, 34): 0, (50, 35): 0, (50, 36): 0, (50, 37): 0, (50, 38): 0, (50, 39): 0, (50, 40): 0, (50, 41): 0, (50, 42): 0, (50, 43): 0, (50, 44): 0, (50, 45): 0, (50, 46): 0, (50, 47): 0, (50, 48): 0, (50, 49): 0, (50, 50): 0, (50, 51): 0, (50, 52): 0, (50, 53): 0, (50, 54): 0, (50, 55): 0, (50, 56): 0, (50, 57): 0, (50, 58): 0, (50, 59): 0, (50, 60): 0, (50, 61): 1, (50, 62): 1, (50, 63): 1, (50, 64): 1, (50, 65): 1, (50, 66): 1, (50, 67): 1, (50, 68): 0, (50, 69): 0, (53, 1): 0, (53, 2): 0, (53, 3): 0, (53, 4): 0, (53, 5): 0, (53, 6): 0, (53, 7): 0, (53, 8): 0, (53, 9): 0, (53, 10): 0, (53, 11): 0, (53, 12): 0, (53, 13): 0, (53, 14): 0, (53, 15): 0, (53, 16): 0, (53, 17): 0, (53, 18): 0, (53, 19): 0, (53, 20): 0, (53, 21): 0, (53, 22): 0, (53, 23): 0, (53, 24): 0, (53, 25): 0, (53, 26): 0, (53, 27): 0, (53, 28): 0, (53, 29): 0, (53, 30): 0, (53, 31): 0, (53, 32): 0, (53, 33): 0, (53, 34): 0, (53, 35): 0, (53, 36): 0, (53, 37): 0, (53, 38): 0, (53, 39): 0, (53, 40): 0, (53, 41): 0, (53, 42): 0, (53, 43): 0, (53, 44): 0, (53, 45): 0, (53, 46): 0, (53, 47): 0, (53, 48): 0, (53, 49): 0, (53, 50): 0, (53, 51): 0, (53, 52): 1, (53, 53): 1, (53, 54): 1, (53, 55): 1, (53, 56): 1, (53, 57): 1, (53, 58): 1, (53, 59): 0, (53, 60): 0, (53, 61): 0, (53, 62): 0, (53, 63): 0, (53, 64): 0, (53, 65): 0, (53, 66): 0, (53, 67): 0, (53, 68): 0, (53, 69): 0, (54, 1): 0, (54, 2): 0, (54, 3): 0, (54, 4): 0, (54, 5): 0, (54, 6): 0, (54, 7): 0, (54, 8): 0, (54, 9): 0, (54, 10): 0, (54, 11): 0, (54, 12): 0, (54, 13): 0, (54, 14): 0, (54, 15): 0, (54, 16): 0, (54, 17): 0, (54, 18): 0, (54, 19): 0, (54, 20): 0, (54, 21): 0, (54, 22): 0, (54, 23): 0, (54, 24): 0, (54, 25): 0, (54, 26): 0, (54, 27): 0, (54, 28): 0, (54, 29): 0, (54, 30): 0, (54, 31): 0, (54, 32): 0, (54, 33): 0, (54, 34): 0, (54, 35): 0, (54, 36): 0, (54, 37): 0, (54, 38): 0, (54, 39): 0, (54, 40): 0, (54, 41): 0, (54, 42): 0, (54, 43): 0, (54, 44): 0, (54, 45): 0, (54, 46): 0, (54, 47): 0, (54, 48): 0, (54, 49): 0, (54, 50): 1, (54, 51): 1, (54, 52): 1, (54, 53): 1, (54, 54): 1, (54, 55): 1, (54, 56): 0, (54, 57): 0, (54, 58): 0, (54, 59): 0, (54, 60): 0, (54, 61): 0, (54, 62): 0, (54, 63): 0, (54, 64): 0, (54, 65): 0, (54, 66): 0, (54, 67): 0, (54, 68): 0, (54, 69): 0, (55, 1): 0, (55, 2): 0, (55, 3): 0, (55, 4): 0, (55, 5): 0, (55, 6): 0, (55, 7): 0, (55, 8): 0, (55, 9): 0, (55, 10): 0, (55, 11): 0, (55, 12): 0, (55, 13): 0, (55, 14): 0, (55, 15): 0, (55, 16): 0, (55, 17): 0, (55, 18): 0, (55, 19): 0, (55, 20): 0, (55, 21): 0, (55, 22): 0, (55, 23): 0, (55, 24): 0, (55, 25): 0, (55, 26): 0, (55, 27): 0, (55, 28): 0, (55, 29): 0, (55, 30): 0, (55, 31): 0, (55, 32): 0, (55, 33): 0, (55, 34): 0, (55, 35): 0, (55, 36): 0, (55, 37): 0, (55, 38): 0, (55, 39): 0, (55, 40): 0, (55, 41): 0, (55, 42): 0, (55, 43): 0, (55, 44): 0, (55, 45): 0, (55, 46): 0, (55, 47): 0, (55, 48): 0, (55, 49): 0, (55, 50): 0, (55, 51): 0, (55, 52): 0, (55, 53): 0, (55, 54): 0, (55, 55): 0, (55, 56): 0, (55, 57): 0, (55, 58): 0, (55, 59): 0, (55, 60): 0, (55, 61): 0, (55, 62): 0, (55, 63): 0, (55, 64): 0, (55, 65): 0, (55, 66): 1, (55, 67): 1, (55, 68): 1, (55, 69): 1, (56, 1): 0, (56, 2): 0, (56, 3): 0, (56, 4): 0, (56, 5): 0, (56, 6): 0, (56, 7): 0, (56, 8): 0, (56, 9): 0, (56, 10): 0, (56, 11): 0, (56, 12): 0, (56, 13): 0, (56, 14): 0, (56, 15): 0, (56, 16): 0, (56, 17): 0, (56, 18): 0, (56, 19): 0, (56, 20): 0, (56, 21): 0, (56, 22): 0, (56, 23): 0, (56, 24): 0, (56, 25): 0, (56, 26): 0, (56, 27): 0, (56, 28): 0, (56, 29): 0, (56, 30): 0, (56, 31): 0, (56, 32): 0, (56, 33): 0, (56, 34): 0, (56, 35): 0, (56, 36): 0, (56, 37): 0, (56, 38): 0, (56, 39): 0, (56, 40): 0, (56, 41): 0, (56, 42): 0, (56, 43): 0, (56, 44): 0, (56, 45): 0, (56, 46): 0, (56, 47): 0, (56, 48): 0, (56, 49): 0, (56, 50): 0, (56, 51): 0, (56, 52): 0, (56, 53): 0, (56, 54): 1, (56, 55): 1, (56, 56): 1, (56, 57): 1, (56, 58): 1, (56, 59): 1, (56, 60): 1, (56, 61): 1, (56, 62): 1, (56, 63): 0, (56, 64): 0, (56, 65): 0, (56, 66): 0, (56, 67): 0, (56, 68): 0, (56, 69): 0, (58, 1): 0, (58, 2): 0, (58, 3): 0, (58, 4): 0, (58, 5): 0, (58, 6): 0, (58, 7): 0, (58, 8): 0, (58, 9): 0, (58, 10): 0, (58, 11): 0, (58, 12): 0, (58, 13): 0, (58, 14): 0, (58, 15): 0, (58, 16): 0, (58, 17): 0, (58, 18): 0, (58, 19): 0, (58, 20): 0, (58, 21): 0, (58, 22): 0, (58, 23): 0, (58, 24): 0, (58, 25): 0, (58, 26): 0, (58, 27): 0, (58, 28): 0, (58, 29): 0, (58, 30): 0, (58, 31): 0, (58, 32): 0, (58, 33): 0, (58, 34): 0, (58, 35): 0, (58, 36): 0, (58, 37): 0, (58, 38): 0, (58, 39): 0, (58, 40): 0, (58, 41): 0, (58, 42): 0, (58, 43): 0, (58, 44): 0, (58, 45): 0, (58, 46): 0, (58, 47): 0, (58, 48): 0, (58, 49): 0, (58, 50): 0, (58, 51): 0, (58, 52): 1, (58, 53): 1, (58, 54): 1, (58, 55): 1, (58, 56): 1, (58, 57): 1, (58, 58): 1, (58, 59): 1, (58, 60): 1, (58, 61): 1, (58, 62): 1, (58, 63): 0, (58, 64): 0, (58, 65): 0, (58, 66): 0, (58, 67): 0, (58, 68): 0, (58, 69): 0, (61, 1): 0, (61, 2): 0, (61, 3): 0, (61, 4): 0, (61, 5): 0, (61, 6): 0, (61, 7): 0, (61, 8): 0, (61, 9): 0, (61, 10): 0, (61, 11): 0, (61, 12): 0, (61, 13): 0, (61, 14): 0, (61, 15): 0, (61, 16): 0, (61, 17): 0, (61, 18): 0, (61, 19): 0, (61, 20): 0, (61, 21): 0, (61, 22): 0, (61, 23): 0, (61, 24): 0, (61, 25): 0, (61, 26): 0, (61, 27): 0, (61, 28): 0, (61, 29): 0, (61, 30): 0, (61, 31): 0, (61, 32): 0, (61, 33): 0, (61, 34): 1, (61, 35): 1, (61, 36): 1, (61, 37): 1, (61, 38): 1, (61, 39): 1, (61, 40): 1, (61, 41): 1, (61, 42): 1, (61, 43): 0, (61, 44): 0, (61, 45): 0, (61, 46): 0, (61, 47): 0, (61, 48): 0, (61, 49): 0, (61, 50): 0, (61, 51): 0, (61, 52): 0, (61, 53): 0, (61, 54): 0, (61, 55): 0, (61, 56): 0, (61, 57): 0, (61, 58): 0, (61, 59): 0, (61, 60): 0, (61, 61): 0, (61, 62): 0, (61, 63): 0, (61, 64): 0, (61, 65): 0, (61, 66): 0, (61, 67): 0, (61, 68): 0, (61, 69): 0, (62, 1): 0, (62, 2): 0, (62, 3): 0, (62, 4): 0, (62, 5): 0, (62, 6): 0, (62, 7): 0, (62, 8): 0, (62, 9): 0, (62, 10): 0, (62, 11): 0, (62, 12): 0, (62, 13): 0, (62, 14): 0, (62, 15): 0, (62, 16): 0, (62, 17): 0, (62, 18): 0, (62, 19): 0, (62, 20): 0, (62, 21): 0, (62, 22): 0, (62, 23): 0, (62, 24): 0, (62, 25): 0, (62, 26): 0, (62, 27): 0, (62, 28): 0, (62, 29): 0, (62, 30): 0, (62, 31): 0, (62, 32): 0, (62, 33): 0, (62, 34): 0, (62, 35): 0, (62, 36): 0, (62, 37): 0, (62, 38): 0, (62, 39): 0, (62, 40): 0, (62, 41): 0, (62, 42): 0, (62, 43): 0, (62, 44): 0, (62, 45): 0, (62, 46): 0, (62, 47): 1, (62, 48): 1, (62, 49): 1, (62, 50): 1, (62, 51): 1, (62, 52): 1, (62, 53): 1, (62, 54): 1, (62, 55): 0, (62, 56): 0, (62, 57): 0, (62, 58): 0, (62, 59): 0, (62, 60): 0, (62, 61): 0, (62, 62): 0, (62, 63): 0, (62, 64): 0, (62, 65): 0, (62, 66): 0, (62, 67): 0, (62, 68): 0, (62, 69): 0, (64, 1): 0, (64, 2): 0, (64, 3): 0, (64, 4): 0, (64, 5): 0, (64, 6): 0, (64, 7): 0, (64, 8): 0, (64, 9): 0, (64, 10): 0, (64, 11): 0, (64, 12): 0, (64, 13): 0, (64, 14): 0, (64, 15): 0, (64, 16): 0, (64, 17): 0, (64, 18): 0, (64, 19): 0, (64, 20): 0, (64, 21): 0, (64, 22): 0, (64, 23): 0, (64, 24): 0, (64, 25): 0, (64, 26): 0, (64, 27): 0, (64, 28): 0, (64, 29): 0, (64, 30): 0, (64, 31): 0, (64, 32): 0, (64, 33): 0, (64, 34): 0, (64, 35): 0, (64, 36): 0, (64, 37): 0, (64, 38): 0, (64, 39): 0, (64, 40): 0, (64, 41): 0, (64, 42): 0, (64, 43): 0, (64, 44): 1, (64, 45): 1, (64, 46): 1, (64, 47): 1, (64, 48): 1, (64, 49): 1, (64, 50): 0, (64, 51): 0, (64, 52): 0, (64, 53): 0, (64, 54): 0, (64, 55): 0, (64, 56): 0, (64, 57): 0, (64, 58): 0, (64, 59): 0, (64, 60): 0, (64, 61): 0, (64, 62): 0, (64, 63): 0, (64, 64): 0, (64, 65): 0, (64, 66): 0, (64, 67): 0, (64, 68): 0, (64, 69): 0, (66, 1): 0, (66, 2): 0, (66, 3): 0, (66, 4): 0, (66, 5): 0, (66, 6): 0, (66, 7): 0, (66, 8): 0, (66, 9): 0, (66, 10): 0, (66, 11): 0, (66, 12): 0, (66, 13): 0, (66, 14): 0, (66, 15): 0, (66, 16): 0, (66, 17): 0, (66, 18): 0, (66, 19): 0, (66, 20): 0, (66, 21): 0, (66, 22): 0, (66, 23): 0, (66, 24): 0, (66, 25): 0, (66, 26): 0, (66, 27): 0, (66, 28): 0, (66, 29): 0, (66, 30): 0, (66, 31): 0, (66, 32): 0, (66, 33): 0, (66, 34): 0, (66, 35): 0, (66, 36): 0, (66, 37): 0, (66, 38): 0, (66, 39): 0, (66, 40): 0, (66, 41): 0, (66, 42): 0, (66, 43): 0, (66, 44): 0, (66, 45): 0, (66, 46): 0, (66, 47): 0, (66, 48): 0, (66, 49): 0, (66, 50): 0, (66, 51): 0, (66, 52): 0, (66, 53): 1, (66, 54): 1, (66, 55): 1, (66, 56): 1, (66, 57): 1, (66, 58): 1, (66, 59): 1, (66, 60): 1, (66, 61): 0, (66, 62): 0, (66, 63): 0, (66, 64): 0, (66, 65): 0, (66, 66): 0, (66, 67): 0, (66, 68): 0, (66, 69): 0, (69, 1): 0, (69, 2): 0, (69, 3): 0, (69, 4): 0, (69, 5): 0, (69, 6): 0, (69, 7): 0, (69, 8): 0, (69, 9): 0, (69, 10): 0, (69, 11): 0, (69, 12): 0, (69, 13): 0, (69, 14): 0, (69, 15): 0, (69, 16): 0, (69, 17): 0, (69, 18): 0, (69, 19): 0, (69, 20): 0, (69, 21): 0, (69, 22): 0, (69, 23): 0, (69, 24): 0, (69, 25): 0, (69, 26): 0, (69, 27): 0, (69, 28): 0, (69, 29): 0, (69, 30): 0, (69, 31): 0, (69, 32): 0, (69, 33): 0, (69, 34): 0, (69, 35): 0, (69, 36): 0, (69, 37): 0, (69, 38): 0, (69, 39): 0, (69, 40): 0, (69, 41): 0, (69, 42): 0, (69, 43): 0, (69, 44): 0, (69, 45): 0, (69, 46): 1, (69, 47): 1, (69, 48): 1, (69, 49): 1, (69, 50): 1, (69, 51): 1, (69, 52): 0, (69, 53): 0, (69, 54): 0, (69, 55): 0, (69, 56): 0, (69, 57): 0, (69, 58): 0, (69, 59): 0, (69, 60): 0, (69, 61): 0, (69, 62): 0, (69, 63): 0, (69, 64): 0, (69, 65): 0, (69, 66): 0, (69, 67): 0, (69, 68): 0, (69, 69): 0, (71, 1): 0, (71, 2): 0, (71, 3): 0, (71, 4): 0, (71, 5): 0, (71, 6): 0, (71, 7): 0, (71, 8): 0, (71, 9): 0, (71, 10): 0, (71, 11): 0, (71, 12): 0, (71, 13): 0, (71, 14): 0, (71, 15): 0, (71, 16): 0, (71, 17): 0, (71, 18): 0, (71, 19): 0, (71, 20): 0, (71, 21): 0, (71, 22): 0, (71, 23): 0, (71, 24): 0, (71, 25): 0, (71, 26): 0, (71, 27): 0, (71, 28): 0, (71, 29): 0, (71, 30): 0, (71, 31): 0, (71, 32): 0, (71, 33): 0, (71, 34): 0, (71, 35): 0, (71, 36): 0, (71, 37): 0, (71, 38): 0, (71, 39): 0, (71, 40): 0, (71, 41): 0, (71, 42): 0, (71, 43): 0, (71, 44): 0, (71, 45): 0, (71, 46): 0, (71, 47): 0, (71, 48): 0, (71, 49): 0, (71, 50): 0, (71, 51): 1, (71, 52): 1, (71, 53): 1, (71, 54): 1, (71, 55): 1, (71, 56): 1, (71, 57): 1, (71, 58): 1, (71, 59): 1, (71, 60): 0, (71, 61): 0, (71, 62): 0, (71, 63): 0, (71, 64): 0, (71, 65): 0, (71, 66): 0, (71, 67): 0, (71, 68): 0, (71, 69): 0, (76, 1): 0, (76, 2): 0, (76, 3): 0, (76, 4): 0, (76, 5): 0, (76, 6): 0, (76, 7): 0, (76, 8): 0, (76, 9): 0, (76, 10): 0, (76, 11): 0, (76, 12): 0, (76, 13): 0, (76, 14): 0, (76, 15): 0, (76, 16): 0, (76, 17): 0, (76, 18): 0, (76, 19): 0, (76, 20): 0, (76, 21): 0, (76, 22): 0, (76, 23): 0, (76, 24): 0, (76, 25): 0, (76, 26): 0, (76, 27): 0, (76, 28): 0, (76, 29): 0, (76, 30): 0, (76, 31): 0, (76, 32): 0, (76, 33): 0, (76, 34): 0, (76, 35): 0, (76, 36): 0, (76, 37): 0, (76, 38): 0, (76, 39): 0, (76, 40): 0, (76, 41): 0, (76, 42): 0, (76, 43): 0, (76, 44): 0, (76, 45): 0, (76, 46): 0, (76, 47): 0, (76, 48): 0, (76, 49): 0, (76, 50): 0, (76, 51): 0, (76, 52): 0, (76, 53): 0, (76, 54): 0, (76, 55): 0, (76, 56): 1, (76, 57): 1, (76, 58): 1, (76, 59): 1, (76, 60): 1, (76, 61): 0, (76, 62): 0, (76, 63): 0, (76, 64): 0, (76, 65): 0, (76, 66): 0, (76, 67): 0, (76, 68): 0, (76, 69): 0, (77, 1): 0, (77, 2): 0, (77, 3): 0, (77, 4): 0, (77, 5): 0, (77, 6): 0, (77, 7): 0, (77, 8): 0, (77, 9): 0, (77, 10): 0, (77, 11): 0, (77, 12): 0, (77, 13): 0, (77, 14): 0, (77, 15): 0, (77, 16): 0, (77, 17): 0, (77, 18): 0, (77, 19): 0, (77, 20): 0, (77, 21): 0, (77, 22): 0, (77, 23): 0, (77, 24): 0, (77, 25): 0, (77, 26): 0, (77, 27): 0, (77, 28): 0, (77, 29): 0, (77, 30): 0, (77, 31): 0, (77, 32): 0, (77, 33): 0, (77, 34): 0, (77, 35): 0, (77, 36): 1, (77, 37): 1, (77, 38): 1, (77, 39): 1, (77, 40): 1, (77, 41): 1, (77, 42): 1, (77, 43): 1, (77, 44): 1, (77, 45): 0, (77, 46): 0, (77, 47): 0, (77, 48): 0, (77, 49): 0, (77, 50): 0, (77, 51): 0, (77, 52): 0, (77, 53): 0, (77, 54): 0, (77, 55): 0, (77, 56): 0, (77, 57): 0, (77, 58): 0, (77, 59): 0, (77, 60): 0, (77, 61): 0, (77, 62): 0, (77, 63): 0, (77, 64): 0, (77, 65): 0, (77, 66): 0, (77, 67): 0, (77, 68): 0, (77, 69): 0, (78, 1): 0, (78, 2): 0, (78, 3): 0, (78, 4): 0, (78, 5): 0, (78, 6): 0, (78, 7): 0, (78, 8): 0, (78, 9): 0, (78, 10): 0, (78, 11): 0, (78, 12): 0, (78, 13): 0, (78, 14): 0, (78, 15): 0, (78, 16): 0, (78, 17): 0, (78, 18): 0, (78, 19): 0, (78, 20): 0, (78, 21): 0, (78, 22): 0, (78, 23): 0, (78, 24): 0, (78, 25): 0, (78, 26): 0, (78, 27): 0, (78, 28): 0, (78, 29): 0, (78, 30): 0, (78, 31): 0, (78, 32): 0, (78, 33): 0, (78, 34): 0, (78, 35): 0, (78, 36): 0, (78, 37): 0, (78, 38): 0, (78, 39): 1, (78, 40): 1, (78, 41): 1, (78, 42): 1, (78, 43): 1, (78, 44): 0, (78, 45): 0, (78, 46): 0, (78, 47): 0, (78, 48): 0, (78, 49): 0, (78, 50): 0, (78, 51): 0, (78, 52): 0, (78, 53): 0, (78, 54): 0, (78, 55): 0, (78, 56): 0, (78, 57): 0, (78, 58): 0, (78, 59): 0, (78, 60): 0, (78, 61): 0, (78, 62): 0, (78, 63): 0, (78, 64): 0, (78, 65): 0, (78, 66): 0, (78, 67): 0, (78, 68): 0, (78, 69): 0, (80, 1): 0, (80, 2): 0, (80, 3): 0, (80, 4): 0, (80, 5): 0, (80, 6): 0, (80, 7): 0, (80, 8): 0, (80, 9): 0, (80, 10): 0, (80, 11): 0, (80, 12): 0, (80, 13): 0, (80, 14): 0, (80, 15): 0, (80, 16): 0, (80, 17): 0, (80, 18): 0, (80, 19): 0, (80, 20): 0, (80, 21): 0, (80, 22): 0, (80, 23): 0, (80, 24): 0, (80, 25): 0, (80, 26): 0, (80, 27): 0, (80, 28): 0, (80, 29): 0, (80, 30): 0, (80, 31): 0, (80, 32): 0, (80, 33): 0, (80, 34): 0, (80, 35): 0, (80, 36): 0, (80, 37): 0, (80, 38): 0, (80, 39): 0, (80, 40): 0, (80, 41): 0, (80, 42): 0, (80, 43): 0, (80, 44): 0, (80, 45): 0, (80, 46): 0, (80, 47): 0, (80, 48): 0, (80, 49): 0, (80, 50): 0, (80, 51): 0, (80, 52): 0, (80, 53): 0, (80, 54): 0, (80, 55): 0, (80, 56): 0, (80, 57): 0, (80, 58): 0, (80, 59): 0, (80, 60): 0, (80, 61): 0, (80, 62): 0, (80, 63): 1, (80, 64): 1, (80, 65): 1, (80, 66): 1, (80, 67): 1, (80, 68): 0, (80, 69): 0, (81, 1): 0, (81, 2): 0, (81, 3): 0, (81, 4): 0, (81, 5): 0, (81, 6): 0, (81, 7): 0, (81, 8): 0, (81, 9): 0, (81, 10): 0, (81, 11): 0, (81, 12): 0, (81, 13): 0, (81, 14): 0, (81, 15): 0, (81, 16): 0, (81, 17): 0, (81, 18): 0, (81, 19): 0, (81, 20): 0, (81, 21): 0, (81, 22): 0, (81, 23): 0, (81, 24): 0, (81, 25): 0, (81, 26): 0, (81, 27): 0, (81, 28): 0, (81, 29): 0, (81, 30): 0, (81, 31): 0, (81, 32): 0, (81, 33): 0, (81, 34): 0, (81, 35): 0, (81, 36): 0, (81, 37): 0, (81, 38): 0, (81, 39): 0, (81, 40): 0, (81, 41): 0, (81, 42): 0, (81, 43): 0, (81, 44): 0, (81, 45): 0, (81, 46): 0, (81, 47): 0, (81, 48): 0, (81, 49): 0, (81, 50): 0, (81, 51): 0, (81, 52): 0, (81, 53): 0, (81, 54): 0, (81, 55): 0, (81, 56): 0, (81, 57): 0, (81, 58): 0, (81, 59): 1, (81, 60): 1, (81, 61): 1, (81, 62): 1, (81, 63): 1, (81, 64): 1, (81, 65): 1, (81, 66): 0, (81, 67): 0, (81, 68): 0, (81, 69): 0, (83, 1): 0, (83, 2): 0, (83, 3): 0, (83, 4): 0, (83, 5): 0, (83, 6): 0, (83, 7): 0, (83, 8): 0, (83, 9): 0, (83, 10): 0, (83, 11): 0, (83, 12): 0, (83, 13): 0, (83, 14): 0, (83, 15): 0, (83, 16): 0, (83, 17): 0, (83, 18): 0, (83, 19): 0, (83, 20): 0, (83, 21): 0, (83, 22): 0, (83, 23): 0, (83, 24): 0, (83, 25): 0, (83, 26): 0, (83, 27): 0, (83, 28): 0, (83, 29): 0, (83, 30): 0, (83, 31): 0, (83, 32): 0, (83, 33): 0, (83, 34): 0, (83, 35): 0, (83, 36): 0, (83, 37): 0, (83, 38): 0, (83, 39): 0, (83, 40): 0, (83, 41): 0, (83, 42): 0, (83, 43): 0, (83, 44): 0, (83, 45): 0, (83, 46): 0, (83, 47): 0, (83, 48): 0, (83, 49): 0, (83, 50): 1, (83, 51): 1, (83, 52): 1, (83, 53): 1, (83, 54): 1, (83, 55): 1, (83, 56): 1, (83, 57): 1, (83, 58): 0, (83, 59): 0, (83, 60): 0, (83, 61): 0, (83, 62): 0, (83, 63): 0, (83, 64): 0, (83, 65): 0, (83, 66): 0, (83, 67): 0, (83, 68): 0, (83, 69): 0, (85, 1): 0, (85, 2): 0, (85, 3): 0, (85, 4): 0, (85, 5): 0, (85, 6): 0, (85, 7): 0, (85, 8): 0, (85, 9): 0, (85, 10): 0, (85, 11): 0, (85, 12): 0, (85, 13): 0, (85, 14): 0, (85, 15): 0, (85, 16): 0, (85, 17): 0, (85, 18): 0, (85, 19): 0, (85, 20): 0, (85, 21): 0, (85, 22): 0, (85, 23): 0, (85, 24): 0, (85, 25): 0, (85, 26): 0, (85, 27): 0, (85, 28): 0, (85, 29): 0, (85, 30): 0, (85, 31): 0, (85, 32): 0, (85, 33): 0, (85, 34): 0, (85, 35): 0, (85, 36): 0, (85, 37): 0, (85, 38): 0, (85, 39): 0, (85, 40): 0, (85, 41): 0, (85, 42): 0, (85, 43): 0, (85, 44): 0, (85, 45): 0, (85, 46): 0, (85, 47): 0, (85, 48): 0, (85, 49): 0, (85, 50): 0, (85, 51): 1, (85, 52): 1, (85, 53): 1, (85, 54): 1, (85, 55): 1, (85, 56): 1, (85, 57): 1, (85, 58): 1, (85, 59): 1, (85, 60): 1, (85, 61): 1, (85, 62): 0, (85, 63): 0, (85, 64): 0, (85, 65): 0, (85, 66): 0, (85, 67): 0, (85, 68): 0, (85, 69): 0, (90, 1): 0, (90, 2): 0, (90, 3): 0, (90, 4): 0, (90, 5): 0, (90, 6): 0, (90, 7): 0, (90, 8): 0, (90, 9): 0, (90, 10): 0, (90, 11): 0, (90, 12): 0, (90, 13): 0, (90, 14): 0, (90, 15): 0, (90, 16): 0, (90, 17): 0, (90, 18): 0, (90, 19): 0, (90, 20): 0, (90, 21): 0, (90, 22): 0, (90, 23): 0, (90, 24): 0, (90, 25): 0, (90, 26): 0, (90, 27): 0, (90, 28): 0, (90, 29): 0, (90, 30): 0, (90, 31): 0, (90, 32): 0, (90, 33): 0, (90, 34): 0, (90, 35): 0, (90, 36): 0, (90, 37): 0, (90, 38): 0, (90, 39): 0, (90, 40): 0, (90, 41): 0, (90, 42): 0, (90, 43): 0, (90, 44): 0, (90, 45): 0, (90, 46): 0, (90, 47): 0, (90, 48): 0, (90, 49): 0, (90, 50): 0, (90, 51): 0, (90, 52): 0, (90, 53): 0, (90, 54): 0, (90, 55): 0, (90, 56): 0, (90, 57): 0, (90, 58): 0, (90, 59): 0, (90, 60): 0, (90, 61): 0, (90, 62): 0, (90, 63): 0, (90, 64): 0, (90, 65): 1, (90, 66): 1, (90, 67): 1, (90, 68): 1, (90, 69): 1, (91, 1): 0, (91, 2): 0, (91, 3): 0, (91, 4): 0, (91, 5): 0, (91, 6): 0, (91, 7): 0, (91, 8): 0, (91, 9): 0, (91, 10): 0, (91, 11): 0, (91, 12): 0, (91, 13): 0, (91, 14): 0, (91, 15): 0, (91, 16): 0, (91, 17): 0, (91, 18): 0, (91, 19): 0, (91, 20): 0, (91, 21): 0, (91, 22): 0, (91, 23): 0, (91, 24): 0, (91, 25): 0, (91, 26): 0, (91, 27): 0, (91, 28): 0, (91, 29): 0, (91, 30): 0, (91, 31): 0, (91, 32): 0, (91, 33): 0, (91, 34): 0, (91, 35): 0, (91, 36): 0, (91, 37): 0, (91, 38): 0, (91, 39): 0, (91, 40): 0, (91, 41): 0, (91, 42): 0, (91, 43): 0, (91, 44): 0, (91, 45): 0, (91, 46): 0, (91, 47): 0, (91, 48): 0, (91, 49): 0, (91, 50): 0, (91, 51): 0, (91, 52): 0, (91, 53): 0, (91, 54): 0, (91, 55): 0, (91, 56): 0, (91, 57): 0, (91, 58): 1, (91, 59): 1, (91, 60): 1, (91, 61): 1, (91, 62): 1, (91, 63): 1, (91, 64): 0, (91, 65): 0, (91, 66): 0, (91, 67): 0, (91, 68): 0, (91, 69): 0, (93, 1): 0, (93, 2): 0, (93, 3): 0, (93, 4): 0, (93, 5): 0, (93, 6): 0, (93, 7): 0, (93, 8): 0, (93, 9): 0, (93, 10): 0, (93, 11): 0, (93, 12): 0, (93, 13): 0, (93, 14): 0, (93, 15): 0, (93, 16): 0, (93, 17): 0, (93, 18): 0, (93, 19): 0, (93, 20): 0, (93, 21): 0, (93, 22): 0, (93, 23): 0, (93, 24): 0, (93, 25): 0, (93, 26): 0, (93, 27): 0, (93, 28): 0, (93, 29): 0, (93, 30): 0, (93, 31): 0, (93, 32): 0, (93, 33): 0, (93, 34): 0, (93, 35): 0, (93, 36): 0, (93, 37): 0, (93, 38): 1, (93, 39): 1, (93, 40): 1, (93, 41): 1, (93, 42): 1, (93, 43): 1, (93, 44): 1, (93, 45): 1, (93, 46): 1, (93, 47): 0, (93, 48): 0, (93, 49): 0, (93, 50): 0, (93, 51): 0, (93, 52): 0, (93, 53): 0, (93, 54): 0, (93, 55): 0, (93, 56): 0, (93, 57): 0, (93, 58): 0, (93, 59): 0, (93, 60): 0, (93, 61): 0, (93, 62): 0, (93, 63): 0, (93, 64): 0, (93, 65): 0, (93, 66): 0, (93, 67): 0, (93, 68): 0, (93, 69): 0, (103, 1): 0, (103, 2): 0, (103, 3): 0, (103, 4): 0, (103, 5): 0, (103, 6): 0, (103, 7): 0, (103, 8): 0, (103, 9): 0, (103, 10): 0, (103, 11): 0, (103, 12): 0, (103, 13): 0, (103, 14): 0, (103, 15): 0, (103, 16): 0, (103, 17): 0, (103, 18): 0, (103, 19): 0, (103, 20): 0, (103, 21): 0, (103, 22): 0, (103, 23): 0, (103, 24): 0, (103, 25): 0, (103, 26): 0, (103, 27): 0, (103, 28): 0, (103, 29): 0, (103, 30): 0, (103, 31): 0, (103, 32): 0, (103, 33): 0, (103, 34): 0, (103, 35): 0, (103, 36): 0, (103, 37): 0, (103, 38): 0, (103, 39): 0, (103, 40): 0, (103, 41): 0, (103, 42): 0, (103, 43): 0, (103, 44): 0, (103, 45): 0, (103, 46): 0, (103, 47): 0, (103, 48): 0, (103, 49): 0, (103, 50): 0, (103, 51): 0, (103, 52): 0, (103, 53): 0, (103, 54): 0, (103, 55): 0, (103, 56): 0, (103, 57): 1, (103, 58): 1, (103, 59): 1, (103, 60): 1, (103, 61): 1, (103, 62): 1, (103, 63): 0, (103, 64): 0, (103, 65): 0, (103, 66): 0, (103, 67): 0, (103, 68): 0, (103, 69): 0, (105, 1): 0, (105, 2): 0, (105, 3): 0, (105, 4): 0, (105, 5): 0, (105, 6): 0, (105, 7): 0, (105, 8): 0, (105, 9): 0, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">{(3, 1): 0, (3, 2): 0, (3, 3): 0, (3, 4): 0, (3, 5): 0, (3, 6): 0, (3, 7): 0, (3, 8): 0, (3, 9): 0, (3, 10): 0, (3, 11): 0, (3, 12): 0, (3, 13): 0, (3, 14): 0, (3, 15): 0, (3, 16): 0, (3, 17): 0, (3, 18): 0, (3, 19): 0, (3, 20): 0, (3, 21): 0, (3, 22): 0, (3, 23): 0, (3, 24): 0, (3, 25): 0, (3, 26): 0, (3, 27): 0, (3, 28): 0, (3, 29): 0, (3, 30): 0, (3, 31): 0, (3, 32): 0, (3, 33): 0, (3, 34): 0, (3, 35): 0, (3, 36): 0, (3, 37): 0, (3, 38): 0, (3, 39): 0, (3, 40): 0, (3, 41): 0, (3, 42): 0, (3, 43): 0, (3, 44): 0, (3, 45): 0, (3, 46): 0, (3, 47): 0, (3, 48): 0, (3, 49): 0, (3, 50): 0, (3, 51): 0, (3, 52): 0, (3, 53): 0, (3, 54): 0, (3, 55): 0, (3, 56): 0, (3, 57): 0, (3, 58): 0, (3, 59): 0, (3, 60): 0, (3, 61): 0, (3, 62): 0, (3, 63): 0, (3, 64): 0, (3, 65): 0, (3, 66): 0, (3, 67): 0, (3, 68): 0, (3, 69): 0, (4, 1): 0, (4, 2): 0, (4, 3): 0, (4, 4): 0, (4, 5): 0, (4, 6): 0, (4, 7): 0, (4, 8): 0, (4, 9): 0, (4, 10): 0, (4, 11): 0, (4, 12): 0, (4, 13): 0, (4, 14): 0, (4, 15): 0, (4, 16): 0, (4, 17): 0, (4, 18): 0, (4, 19): 0, (4, 20): 0, (4, 21): 0, (4, 22): 0, (4, 23): 0, (4, 24): 0, (4, 25): 0, (4, 26): 0, (4, 27): 0, (4, 28): 0, (4, 29): 0, (4, 30): 0, (4, 31): 0, (4, 32): 0, (4, 33): 0, (4, 34): 0, (4, 35): 0, (4, 36): 0, (4, 37): 0, (4, 38): 0, (4, 39): 0, (4, 40): 0, (4, 41): 0, (4, 42): 0, (4, 43): 0, (4, 44): 0, (4, 45): 0, (4, 46): 0, (4, 47): 0, (4, 48): 0, (4, 49): 0, (4, 50): 0, (4, 51): 0, (4, 52): 0, (4, 53): 0, (4, 54): 0, (4, 55): 0, (4, 56): 0, (4, 57): 0, (4, 58): 0, (4, 59): 0, (4, 60): 0, (4, 61): 0, (4, 62): 0, (4, 63): 0, (4, 64): 0, (4, 65): 0, (4, 66): 0, (4, 67): 0, (4, 68): 0, (4, 69): 0, (8, 1): 0, (8, 2): 0, (8, 3): 0, (8, 4): 0, (8, 5): 0, (8, 6): 0, (8, 7): 0, (8, 8): 0, (8, 9): 0, (8, 10): 0, (8, 11): 0, (8, 12): 0, (8, 13): 0, (8, 14): 0, (8, 15): 0, (8, 16): 0, (8, 17): 0, (8, 18): 0, (8, 19): 0, (8, 20): 0, (8, 21): 0, (8, 22): 0, (8, 23): 0, (8, 24): 0, (8, 25): 0, (8, 26): 0, (8, 27): 0, (8, 28): 0, (8, 29): 0, (8, 30): 0, (8, 31): 0, (8, 32): 0, (8, 33): 0, (8, 34): 0, (8, 35): 0, (8, 36): 0, (8, 37): 0, (8, 38): 0, (8, 39): 0, (8, 40): 0, (8, 41): 0, (8, 42): 0, (8, 43): 0, (8, 44): 0, (8, 45): 0, (8, 46): 0, (8, 47): 0, (8, 48): 0, (8, 49): 0, (8, 50): 0, (8, 51): 0, (8, 52): 0, (8, 53): 0, (8, 54): 0, (8, 55): 0, (8, 56): 0, (8, 57): 0, (8, 58): 0, (8, 59): 0, (8, 60): 0, (8, 61): 0, (8, 62): 0, (8, 63): 0, (8, 64): 0, (8, 65): 0, (8, 66): 0, (8, 67): 0, (8, 68): 0, (8, 69): 0, (9, 1): 0, (9, 2): 0, (9, 3): 0, (9, 4): 0, (9, 5): 0, (9, 6): 0, (9, 7): 0, (9, 8): 0, (9, 9): 0, (9, 10): 0, (9, 11): 0, (9, 12): 0, (9, 13): 0, (9, 14): 0, (9, 15): 0, (9, 16): 0, (9, 17): 0, (9, 18): 0, (9, 19): 0, (9, 20): 0, (9, 21): 0, (9, 22): 0, (9, 23): 0, (9, 24): 0, (9, 25): 0, (9, 26): 0, (9, 27): 0, (9, 28): 0, (9, 29): 0, (9, 30): 0, (9, 31): 0, (9, 32): 0, (9, 33): 0, (9, 34): 0, (9, 35): 0, (9, 36): 0, (9, 37): 0, (9, 38): 0, (9, 39): 0, (9, 40): 0, (9, 41): 0, (9, 42): 0, (9, 43): 0, (9, 44): 0, (9, 45): 0, (9, 46): 0, (9, 47): 0, (9, 48): 0, (9, 49): 0, (9, 50): 0, (9, 51): 0, (9, 52): 0, (9, 53): 0, (9, 54): 0, (9, 55): 0, (9, 56): 0, (9, 57): 0, (9, 58): 0, (9, 59): 0, (9, 60): 0, (9, 61): 0, (9, 62): 0, (9, 63): 0, (9, 64): 0, (9, 65): 0, (9, 66): 0, (9, 67): 0, (9, 68): 0, (9, 69): 0, (10, 1): 0, (10, 2): 0, (10, 3): 0, (10, 4): 0, (10, 5): 0, (10, 6): 0, (10, 7): 0, (10, 8): 0, (10, 9): 0, (10, 10): 0, (10, 11): 0, (10, 12): 0, (10, 13): 0, (10, 14): 0, (10, 15): 0, (10, 16): 0, (10, 17): 0, (10, 18): 0, (10, 19): 0, (10, 20): 0, (10, 21): 0, (10, 22): 0, (10, 23): 0, (10, 24): 0, (10, 25): 0, (10, 26): 0, (10, 27): 0, (10, 28): 0, (10, 29): 0, (10, 30): 0, (10, 31): 0, (10, 32): 0, (10, 33): 0, (10, 34): 0, (10, 35): 0, (10, 36): 0, (10, 37): 0, (10, 38): 0, (10, 39): 0, (10, 40): 0, (10, 41): 0, (10, 42): 0, (10, 43): 0, (10, 44): 0, (10, 45): 0, (10, 46): 0, (10, 47): 0, (10, 48): 0, (10, 49): 0, (10, 50): 0, (10, 51): 0, (10, 52): 0, (10, 53): 0, (10, 54): 0, (10, 55): 0, (10, 56): 0, (10, 57): 0, (10, 58): 0, (10, 59): 0, (10, 60): 0, (10, 61): 0, (10, 62): 0, (10, 63): 0, (10, 64): 0, (10, 65): 0, (10, 66): 0, (10, 67): 0, (10, 68): 0, (10, 69): 0, (11, 1): 0, (11, 2): 0, (11, 3): 0, (11, 4): 0, (11, 5): 0, (11, 6): 0, (11, 7): 0, (11, 8): 0, (11, 9): 0, (11, 10): 0, (11, 11): 0, (11, 12): 0, (11, 13): 0, (11, 14): 0, (11, 15): 0, (11, 16): 0, (11, 17): 0, (11, 18): 0, (11, 19): 0, (11, 20): 0, (11, 21): 0, (11, 22): 0, (11, 23): 0, (11, 24): 0, (11, 25): 0, (11, 26): 0, (11, 27): 0, (11, 28): 0, (11, 29): 0, (11, 30): 0, (11, 31): 0, (11, 32): 0, (11, 33): 0, (11, 34): 0, (11, 35): 0, (11, 36): 0, (11, 37): 0, (11, 38): 0, (11, 39): 0, (11, 40): 0, (11, 41): 0, (11, 42): 0, (11, 43): 0, (11, 44): 0, (11, 45): 0, (11, 46): 0, (11, 47): 0, (11, 48): 0, (11, 49): 0, (11, 50): 0, (11, 51): 0, (11, 52): 0, (11, 53): 0, (11, 54): 0, (11, 55): 0, (11, 56): 0, (11, 57): 0, (11, 58): 0, (11, 59): 0, (11, 60): 0, (11, 61): 0, (11, 62): 0, (11, 63): 0, (11, 64): 0, (11, 65): 0, (11, 66): 0, (11, 67): 0, (11, 68): 0, (11, 69): 0, (12, 1): 0, (12, 2): 0, (12, 3): 0, (12, 4): 0, (12, 5): 0, (12, 6): 0, (12, 7): 0, (12, 8): 0, (12, 9): 0, (12, 10): 0, (12, 11): 0, (12, 12): 0, (12, 13): 0, (12, 14): 0, (12, 15): 0, (12, 16): 0, (12, 17): 0, (12, 18): 0, (12, 19): 0, (12, 20): 0, (12, 21): 0, (12, 22): 0, (12, 23): 0, (12, 24): 0, (12, 25): 0, (12, 26): 0, (12, 27): 0, (12, 28): 0, (12, 29): 0, (12, 30): 0, (12, 31): 0, (12, 32): 0, (12, 33): 0, (12, 34): 0, (12, 35): 0, (12, 36): 0, (12, 37): 0, (12, 38): 0, (12, 39): 0, (12, 40): 0, (12, 41): 0, (12, 42): 0, (12, 43): 0, (12, 44): 0, (12, 45): 0, (12, 46): 0, (12, 47): 0, (12, 48): 0, (12, 49): 0, (12, 50): 0, (12, 51): 0, (12, 52): 0, (12, 53): 0, (12, 54): 0, (12, 55): 0, (12, 56): 0, (12, 57): 0, (12, 58): 0, (12, 59): 0, (12, 60): 0, (12, 61): 0, (12, 62): 0, (12, 63): 0, (12, 64): 0, (12, 65): 0, (12, 66): 0, (12, 67): 0, (12, 68): 0, (12, 69): 0, (21, 1): 0, (21, 2): 0, (21, 3): 0, (21, 4): 0, (21, 5): 0, (21, 6): 0, (21, 7): 0, (21, 8): 0, (21, 9): 0, (21, 10): 0, (21, 11): 0, (21, 12): 0, (21, 13): 0, (21, 14): 0, (21, 15): 0, (21, 16): 0, (21, 17): 0, (21, 18): 0, (21, 19): 0, (21, 20): 0, (21, 21): 0, (21, 22): 0, (21, 23): 0, (21, 24): 0, (21, 25): 0, (21, 26): 0, (21, 27): 0, (21, 28): 0, (21, 29): 0, (21, 30): 0, (21, 31): 0, (21, 32): 0, (21, 33): 0, (21, 34): 0, (21, 35): 0, (21, 36): 0, (21, 37): 0, (21, 38): 0, (21, 39): 0, (21, 40): 0, (21, 41): 0, (21, 42): 0, (21, 43): 0, (21, 44): 0, (21, 45): 0, (21, 46): 0, (21, 47): 0, (21, 48): 0, (21, 49): 0, (21, 50): 0, (21, 51): 0, (21, 52): 0, (21, 53): 0, (21, 54): 0, (21, 55): 0, (21, 56): 0, (21, 57): 0, (21, 58): 0, (21, 59): 0, (21, 60): 0, (21, 61): 0, (21, 62): 0, (21, 63): 0, (21, 64): 0, (21, 65): 0, (21, 66): 0, (21, 67): 0, (21, 68): 0, (21, 69): 0, (23, 1): 0, (23, 2): 0, (23, 3): 0, (23, 4): 0, (23, 5): 0, (23, 6): 0, (23, 7): 0, (23, 8): 0, (23, 9): 0, (23, 10): 0, (23, 11): 0, (23, 12): 0, (23, 13): 0, (23, 14): 0, (23, 15): 0, (23, 16): 0, (23, 17): 0, (23, 18): 0, (23, 19): 0, (23, 20): 0, (23, 21): 0, (23, 22): 0, (23, 23): 0, (23, 24): 0, (23, 25): 0, (23, 26): 0, (23, 27): 0, (23, 28): 0, (23, 29): 0, (23, 30): 0, (23, 31): 0, (23, 32): 0, (23, 33): 0, (23, 34): 0, (23, 35): 0, (23, 36): 0, (23, 37): 0, (23, 38): 0, (23, 39): 0, (23, 40): 0, (23, 41): 0, (23, 42): 0, (23, 43): 0, (23, 44): 0, (23, 45): 0, (23, 46): 0, (23, 47): 0, (23, 48): 0, (23, 49): 0, (23, 50): 0, (23, 51): 0, (23, 52): 0, (23, 53): 0, (23, 54): 0, (23, 55): 0, (23, 56): 0, (23, 57): 0, (23, 58): 0, (23, 59): 0, (23, 60): 0, (23, 61): 0, (23, 62): 0, (23, 63): 0, (23, 64): 0, (23, 65): 0, (23, 66): 0, (23, 67): 0, (23, 68): 0, (23, 69): 0, (24, 1): 0, (24, 2): 0, (24, 3): 0, (24, 4): 0, (24, 5): 0, (24, 6): 0, (24, 7): 0, (24, 8): 0, (24, 9): 0, (24, 10): 0, (24, 11): 0, (24, 12): 0, (24, 13): 0, (24, 14): 0, (24, 15): 0, (24, 16): 0, (24, 17): 0, (24, 18): 0, (24, 19): 0, (24, 20): 0, (24, 21): 0, (24, 22): 0, (24, 23): 0, (24, 24): 0, (24, 25): 0, (24, 26): 0, (24, 27): 0, (24, 28): 0, (24, 29): 0, (24, 30): 0, (24, 31): 0, (24, 32): 0, (24, 33): 0, (24, 34): 0, (24, 35): 0, (24, 36): 0, (24, 37): 0, (24, 38): 0, (24, 39): 0, (24, 40): 0, (24, 41): 0, (24, 42): 0, (24, 43): 0, (24, 44): 0, (24, 45): 0, (24, 46): 0, (24, 47): 0, (24, 48): 0, (24, 49): 0, (24, 50): 0, (24, 51): 0, (24, 52): 0, (24, 53): 0, (24, 54): 0, (24, 55): 0, (24, 56): 0, (24, 57): 0, (24, 58): 0, (24, 59): 0, (24, 60): 0, (24, 61): 0, (24, 62): 0, (24, 63): 0, (24, 64): 0, (24, 65): 0, (24, 66): 0, (24, 67): 0, (24, 68): 0, (24, 69): 0, (29, 1): 0, (29, 2): 0, (29, 3): 0, (29, 4): 0, (29, 5): 0, (29, 6): 0, (29, 7): 0, (29, 8): 0, (29, 9): 0, (29, 10): 0, (29, 11): 0, (29, 12): 0, (29, 13): 0, (29, 14): 0, (29, 15): 0, (29, 16): 0, (29, 17): 0, (29, 18): 0, (29, 19): 0, (29, 20): 0, (29, 21): 0, (29, 22): 0, (29, 23): 0, (29, 24): 0, (29, 25): 0, (29, 26): 0, (29, 27): 0, (29, 28): 0, (29, 29): 0, (29, 30): 0, (29, 31): 0, (29, 32): 0, (29, 33): 0, (29, 34): 0, (29, 35): 0, (29, 36): 0, (29, 37): 0, (29, 38): 0, (29, 39): 0, (29, 40): 0, (29, 41): 0, (29, 42): 0, (29, 43): 0, (29, 44): 0, (29, 45): 0, (29, 46): 0, (29, 47): 0, (29, 48): 0, (29, 49): 0, (29, 50): 0, (29, 51): 0, (29, 52): 0, (29, 53): 0, (29, 54): 0, (29, 55): 0, (29, 56): 0, (29, 57): 0, (29, 58): 0, (29, 59): 0, (29, 60): 0, (29, 61): 0, (29, 62): 0, (29, 63): 0, (29, 64): 0, (29, 65): 0, (29, 66): 0, (29, 67): 0, (29, 68): 0, (29, 69): 0, (31, 1): 0, (31, 2): 0, (31, 3): 0, (31, 4): 0, (31, 5): 0, (31, 6): 0, (31, 7): 0, (31, 8): 0, (31, 9): 0, (31, 10): 0, (31, 11): 0, (31, 12): 0, (31, 13): 0, (31, 14): 0, (31, 15): 0, (31, 16): 0, (31, 17): 0, (31, 18): 0, (31, 19): 0, (31, 20): 0, (31, 21): 0, (31, 22): 0, (31, 23): 0, (31, 24): 0, (31, 25): 0, (31, 26): 0, (31, 27): 0, (31, 28): 0, (31, 29): 0, (31, 30): 0, (31, 31): 0, (31, 32): 0, (31, 33): 0, (31, 34): 0, (31, 35): 0, (31, 36): 0, (31, 37): 0, (31, 38): 0, (31, 39): 0, (31, 40): 0, (31, 41): 0, (31, 42): 0, (31, 43): 0, (31, 44): 0, (31, 45): 0, (31, 46): 0, (31, 47): 0, (31, 48): 0, (31, 49): 0, (31, 50): 0, (31, 51): 0, (31, 52): 0, (31, 53): 0, (31, 54): 0, (31, 55): 0, (31, 56): 0, (31, 57): 0, (31, 58): 0, (31, 59): 0, (31, 60): 0, (31, 61): 0, (31, 62): 0, (31, 63): 0, (31, 64): 0, (31, 65): 0, (31, 66): 0, (31, 67): 0, (31, 68): 0, (31, 69): 0, (33, 1): 0, (33, 2): 0, (33, 3): 0, (33, 4): 0, (33, 5): 0, (33, 6): 0, (33, 7): 0, (33, 8): 0, (33, 9): 0, (33, 10): 0, (33, 11): 0, (33, 12): 0, (33, 13): 0, (33, 14): 0, (33, 15): 0, (33, 16): 0, (33, 17): 0, (33, 18): 0, (33, 19): 0, (33, 20): 0, (33, 21): 0, (33, 22): 0, (33, 23): 0, (33, 24): 0, (33, 25): 0, (33, 26): 0, (33, 27): 0, (33, 28): 0, (33, 29): 0, (33, 30): 0, (33, 31): 0, (33, 32): 0, (33, 33): 0, (33, 34): 0, (33, 35): 0, (33, 36): 0, (33, 37): 0, (33, 38): 0, (33, 39): 0, (33, 40): 0, (33, 41): 0, (33, 42): 0, (33, 43): 0, (33, 44): 0, (33, 45): 0, (33, 46): 0, (33, 47): 0, (33, 48): 0, (33, 49): 0, (33, 50): 0, (33, 51): 0, (33, 52): 0, (33, 53): 0, (33, 54): 0, (33, 55): 0, (33, 56): 0, (33, 57): 0, (33, 58): 0, (33, 59): 0, (33, 60): 0, (33, 61): 0, (33, 62): 0, (33, 63): 0, (33, 64): 0, (33, 65): 0, (33, 66): 0, (33, 67): 0, (33, 68): 0, (33, 69): 0, (45, 1): 0, (45, 2): 0, (45, 3): 0, (45, 4): 0, (45, 5): 0, (45, 6): 0, (45, 7): 0, (45, 8): 0, (45, 9): 0, (45, 10): 0, (45, 11): 0, (45, 12): 0, (45, 13): 0, (45, 14): 0, (45, 15): 0, (45, 16): 0, (45, 17): 0, (45, 18): 0, (45, 19): 0, (45, 20): 0, (45, 21): 0, (45, 22): 0, (45, 23): 0, (45, 24): 0, (45, 25): 0, (45, 26): 0, (45, 27): 0, (45, 28): 0, (45, 29): 0, (45, 30): 0, (45, 31): 0, (45, 32): 0, (45, 33): 0, (45, 34): 0, (45, 35): 0, (45, 36): 0, (45, 37): 0, (45, 38): 0, (45, 39): 0, (45, 40): 0, (45, 41): 0, (45, 42): 0, (45, 43): 0, (45, 44): 0, (45, 45): 0, (45, 46): 0, (45, 47): 0, (45, 48): 0, (45, 49): 0, (45, 50): 0, (45, 51): 0, (45, 52): 0, (45, 53): 0, (45, 54): 0, (45, 55): 0, (45, 56): 0, (45, 57): 0, (45, 58): 0, (45, 59): 0, (45, 60): 0, (45, 61): 0, (45, 62): 0, (45, 63): 0, (45, 64): 0, (45, 65): 0, (45, 66): 0, (45, 67): 0, (45, 68): 0, (45, 69): 0, (50, 1): 0, (50, 2): 0, (50, 3): 0, (50, 4): 0, (50, 5): 0, (50, 6): 0, (50, 7): 0, (50, 8): 0, (50, 9): 0, (50, 10): 0, (50, 11): 0, (50, 12): 0, (50, 13): 0, (50, 14): 0, (50, 15): 0, (50, 16): 0, (50, 17): 0, (50, 18): 0, (50, 19): 0, (50, 20): 0, (50, 21): 0, (50, 22): 0, (50, 23): 0, (50, 24): 0, (50, 25): 0, (50, 26): 0, (50, 27): 0, (50, 28): 0, (50, 29): 0, (50, 30): 0, (50, 31): 0, (50, 32): 0, (50, 33): 0, (50, 34): 0, (50, 35): 0, (50, 36): 0, (50, 37): 0, (50, 38): 0, (50, 39): 0, (50, 40): 0, (50, 41): 0, (50, 42): 0, (50, 43): 0, (50, 44): 0, (50, 45): 0, (50, 46): 0, (50, 47): 0, (50, 48): 0, (50, 49): 0, (50, 50): 0, (50, 51): 0, (50, 52): 0, (50, 53): 0, (50, 54): 0, (50, 55): 0, (50, 56): 0, (50, 57): 0, (50, 58): 0, (50, 59): 0, (50, 60): 0, (50, 61): 0, (50, 62): 0, (50, 63): 0, (50, 64): 0, (50, 65): 0, (50, 66): 0, (50, 67): 0, (50, 68): 0, (50, 69): 0, (53, 1): 0, (53, 2): 0, (53, 3): 0, (53, 4): 0, (53, 5): 0, (53, 6): 0, (53, 7): 0, (53, 8): 0, (53, 9): 0, (53, 10): 0, (53, 11): 0, (53, 12): 0, (53, 13): 0, (53, 14): 0, (53, 15): 0, (53, 16): 0, (53, 17): 0, (53, 18): 0, (53, 19): 0, (53, 20): 0, (53, 21): 0, (53, 22): 0, (53, 23): 0, (53, 24): 0, (53, 25): 0, (53, 26): 0, (53, 27): 0, (53, 28): 0, (53, 29): 0, (53, 30): 0, (53, 31): 0, (53, 32): 0, (53, 33): 0, (53, 34): 0, (53, 35): 0, (53, 36): 0, (53, 37): 0, (53, 38): 0, (53, 39): 0, (53, 40): 0, (53, 41): 0, (53, 42): 0, (53, 43): 0, (53, 44): 0, (53, 45): 0, (53, 46): 0, (53, 47): 0, (53, 48): 0, (53, 49): 0, (53, 50): 0, (53, 51): 0, (53, 52): 0, (53, 53): 0, (53, 54): 0, (53, 55): 0, (53, 56): 0, (53, 57): 0, (53, 58): 0, (53, 59): 0, (53, 60): 0, (53, 61): 0, (53, 62): 0, (53, 63): 0, (53, 64): 0, (53, 65): 0, (53, 66): 0, (53, 67): 0, (53, 68): 0, (53, 69): 0, (54, 1): 0, (54, 2): 0, (54, 3): 0, (54, 4): 0, (54, 5): 0, (54, 6): 0, (54, 7): 0, (54, 8): 0, (54, 9): 0, (54, 10): 0, (54, 11): 0, (54, 12): 0, (54, 13): 0, (54, 14): 0, (54, 15): 0, (54, 16): 0, (54, 17): 0, (54, 18): 0, (54, 19): 0, (54, 20): 0, (54, 21): 0, (54, 22): 0, (54, 23): 0, (54, 24): 0, (54, 25): 0, (54, 26): 0, (54, 27): 0, (54, 28): 0, (54, 29): 0, (54, 30): 0, (54, 31): 0, (54, 32): 0, (54, 33): 0, (54, 34): 0, (54, 35): 0, (54, 36): 0, (54, 37): 0, (54, 38): 0, (54, 39): 0, (54, 40): 0, (54, 41): 0, (54, 42): 0, (54, 43): 0, (54, 44): 0, (54, 45): 0, (54, 46): 0, (54, 47): 0, (54, 48): 0, (54, 49): 0, (54, 50): 0, (54, 51): 0, (54, 52): 0, (54, 53): 0, (54, 54): 0, (54, 55): 0, (54, 56): 0, (54, 57): 0, (54, 58): 0, (54, 59): 0, (54, 60): 0, (54, 61): 0, (54, 62): 0, (54, 63): 0, (54, 64): 0, (54, 65): 0, (54, 66): 0, (54, 67): 0, (54, 68): 0, (54, 69): 0, (55, 1): 0, (55, 2): 0, (55, 3): 0, (55, 4): 0, (55, 5): 0, (55, 6): 0, (55, 7): 0, (55, 8): 0, (55, 9): 0, (55, 10): 0, (55, 11): 0, (55, 12): 0, (55, 13): 0, (55, 14): 0, (55, 15): 0, (55, 16): 0, (55, 17): 0, (55, 18): 0, (55, 19): 0, (55, 20): 0, (55, 21): 0, (55, 22): 0, (55, 23): 0, (55, 24): 0, (55, 25): 0, (55, 26): 0, (55, 27): 0, (55, 28): 0, (55, 29): 0, (55, 30): 0, (55, 31): 0, (55, 32): 0, (55, 33): 0, (55, 34): 0, (55, 35): 0, (55, 36): 0, (55, 37): 0, (55, 38): 0, (55, 39): 0, (55, 40): 0, (55, 41): 0, (55, 42): 0, (55, 43): 0, (55, 44): 0, (55, 45): 0, (55, 46): 0, (55, 47): 0, (55, 48): 0, (55, 49): 0, (55, 50): 0, (55, 51): 0, (55, 52): 0, (55, 53): 0, (55, 54): 0, (55, 55): 0, (55, 56): 0, (55, 57): 0, (55, 58): 0, (55, 59): 0, (55, 60): 0, (55, 61): 0, (55, 62): 0, (55, 63): 0, (55, 64): 0, (55, 65): 0, (55, 66): 0, (55, 67): 0, (55, 68): 0, (55, 69): 0, (56, 1): 0, (56, 2): 0, (56, 3): 0, (56, 4): 0, (56, 5): 0, (56, 6): 0, (56, 7): 0, (56, 8): 0, (56, 9): 0, (56, 10): 0, (56, 11): 0, (56, 12): 0, (56, 13): 0, (56, 14): 0, (56, 15): 0, (56, 16): 0, (56, 17): 0, (56, 18): 0, (56, 19): 0, (56, 20): 0, (56, 21): 0, (56, 22): 0, (56, 23): 0, (56, 24): 0, (56, 25): 0, (56, 26): 0, (56, 27): 0, (56, 28): 0, (56, 29): 0, (56, 30): 0, (56, 31): 0, (56, 32): 0, (56, 33): 0, (56, 34): 0, (56, 35): 0, (56, 36): 0, (56, 37): 0, (56, 38): 0, (56, 39): 0, (56, 40): 0, (56, 41): 0, (56, 42): 0, (56, 43): 0, (56, 44): 0, (56, 45): 0, (56, 46): 0, (56, 47): 0, (56, 48): 0, (56, 49): 0, (56, 50): 0, (56, 51): 0, (56, 52): 0, (56, 53): 0, (56, 54): 0, (56, 55): 0, (56, 56): 0, (56, 57): 0, (56, 58): 0, (56, 59): 0, (56, 60): 0, (56, 61): 0, (56, 62): 0, (56, 63): 0, (56, 64): 0, (56, 65): 0, (56, 66): 0, (56, 67): 0, (56, 68): 0, (56, 69): 0, (58, 1): 0, (58, 2): 0, (58, 3): 0, (58, 4): 0, (58, 5): 0, (58, 6): 0, (58, 7): 0, (58, 8): 0, (58, 9): 0, (58, 10): 0, (58, 11): 0, (58, 12): 0, (58, 13): 0, (58, 14): 0, (58, 15): 0, (58, 16): 0, (58, 17): 0, (58, 18): 0, (58, 19): 0, (58, 20): 0, (58, 21): 0, (58, 22): 0, (58, 23): 0, (58, 24): 0, (58, 25): 0, (58, 26): 0, (58, 27): 0, (58, 28): 0, (58, 29): 0, (58, 30): 0, (58, 31): 0, (58, 32): 0, (58, 33): 0, (58, 34): 0, (58, 35): 0, (58, 36): 0, (58, 37): 0, (58, 38): 0, (58, 39): 0, (58, 40): 0, (58, 41): 0, (58, 42): 0, (58, 43): 0, (58, 44): 0, (58, 45): 0, (58, 46): 0, (58, 47): 0, (58, 48): 0, (58, 49): 0, (58, 50): 0, (58, 51): 0, (58, 52): 0, (58, 53): 0, (58, 54): 0, (58, 55): 0, (58, 56): 0, (58, 57): 0, (58, 58): 0, (58, 59): 0, (58, 60): 0, (58, 61): 0, (58, 62): 0, (58, 63): 0, (58, 64): 0, (58, 65): 0, (58, 66): 0, (58, 67): 0, (58, 68): 0, (58, 69): 0, (61, 1): 0, (61, 2): 0, (61, 3): 0, (61, 4): 0, (61, 5): 0, (61, 6): 0, (61, 7): 0, (61, 8): 0, (61, 9): 0, (61, 10): 0, (61, 11): 0, (61, 12): 0, (61, 13): 0, (61, 14): 0, (61, 15): 0, (61, 16): 0, (61, 17): 0, (61, 18): 0, (61, 19): 0, (61, 20): 0, (61, 21): 0, (61, 22): 0, (61, 23): 0, (61, 24): 0, (61, 25): 0, (61, 26): 0, (61, 27): 0, (61, 28): 0, (61, 29): 0, (61, 30): 0, (61, 31): 0, (61, 32): 0, (61, 33): 0, (61, 34): 0, (61, 35): 0, (61, 36): 0, (61, 37): 0, (61, 38): 0, (61, 39): 0, (61, 40): 0, (61, 41): 0, (61, 42): 0, (61, 43): 0, (61, 44): 0, (61, 45): 0, (61, 46): 0, (61, 47): 0, (61, 48): 0, (61, 49): 0, (61, 50): 0, (61, 51): 0, (61, 52): 0, (61, 53): 0, (61, 54): 0, (61, 55): 0, (61, 56): 0, (61, 57): 0, (61, 58): 0, (61, 59): 0, (61, 60): 0, (61, 61): 0, (61, 62): 0, (61, 63): 0, (61, 64): 0, (61, 65): 0, (61, 66): 0, (61, 67): 0, (61, 68): 0, (61, 69): 0, (62, 1): 0, (62, 2): 0, (62, 3): 0, (62, 4): 0, (62, 5): 0, (62, 6): 0, (62, 7): 0, (62, 8): 0, (62, 9): 0, (62, 10): 0, (62, 11): 0, (62, 12): 0, (62, 13): 0, (62, 14): 0, (62, 15): 0, (62, 16): 0, (62, 17): 0, (62, 18): 0, (62, 19): 0, (62, 20): 0, (62, 21): 0, (62, 22): 0, (62, 23): 0, (62, 24): 0, (62, 25): 0, (62, 26): 0, (62, 27): 0, (62, 28): 0, (62, 29): 0, (62, 30): 0, (62, 31): 0, (62, 32): 0, (62, 33): 0, (62, 34): 0, (62, 35): 0, (62, 36): 0, (62, 37): 0, (62, 38): 0, (62, 39): 0, (62, 40): 0, (62, 41): 0, (62, 42): 0, (62, 43): 0, (62, 44): 0, (62, 45): 0, (62, 46): 0, (62, 47): 0, (62, 48): 0, (62, 49): 0, (62, 50): 0, (62, 51): 0, (62, 52): 0, (62, 53): 0, (62, 54): 0, (62, 55): 0, (62, 56): 0, (62, 57): 0, (62, 58): 0, (62, 59): 0, (62, 60): 0, (62, 61): 0, (62, 62): 0, (62, 63): 0, (62, 64): 0, (62, 65): 0, (62, 66): 0, (62, 67): 0, (62, 68): 0, (62, 69): 0, (64, 1): 0, (64, 2): 0, (64, 3): 0, (64, 4): 0, (64, 5): 0, (64, 6): 0, (64, 7): 0, (64, 8): 0, (64, 9): 0, (64, 10): 0, (64, 11): 0, (64, 12): 0, (64, 13): 0, (64, 14): 0, (64, 15): 0, (64, 16): 0, (64, 17): 0, (64, 18): 0, (64, 19): 0, (64, 20): 0, (64, 21): 0, (64, 22): 0, (64, 23): 0, (64, 24): 0, (64, 25): 0, (64, 26): 0, (64, 27): 0, (64, 28): 0, (64, 29): 0, (64, 30): 0, (64, 31): 0, (64, 32): 0, (64, 33): 0, (64, 34): 0, (64, 35): 0, (64, 36): 0, (64, 37): 0, (64, 38): 0, (64, 39): 0, (64, 40): 0, (64, 41): 0, (64, 42): 0, (64, 43): 0, (64, 44): 0, (64, 45): 0, (64, 46): 0, (64, 47): 0, (64, 48): 0, (64, 49): 0, (64, 50): 0, (64, 51): 0, (64, 52): 0, (64, 53): 0, (64, 54): 0, (64, 55): 0, (64, 56): 0, (64, 57): 0, (64, 58): 0, (64, 59): 0, (64, 60): 0, (64, 61): 0, (64, 62): 0, (64, 63): 0, (64, 64): 0, (64, 65): 0, (64, 66): 0, (64, 67): 0, (64, 68): 0, (64, 69): 0, (66, 1): 0, (66, 2): 0, (66, 3): 0, (66, 4): 0, (66, 5): 0, (66, 6): 0, (66, 7): 0, (66, 8): 0, (66, 9): 0, (66, 10): 0, (66, 11): 0, (66, 12): 0, (66, 13): 0, (66, 14): 0, (66, 15): 0, (66, 16): 0, (66, 17): 0, (66, 18): 0, (66, 19): 0, (66, 20): 0, (66, 21): 0, (66, 22): 0, (66, 23): 0, (66, 24): 0, (66, 25): 0, (66, 26): 0, (66, 27): 0, (66, 28): 0, (66, 29): 0, (66, 30): 0, (66, 31): 0, (66, 32): 0, (66, 33): 0, (66, 34): 0, (66, 35): 0, (66, 36): 0, (66, 37): 0, (66, 38): 0, (66, 39): 0, (66, 40): 0, (66, 41): 0, (66, 42): 0, (66, 43): 0, (66, 44): 0, (66, 45): 0, (66, 46): 0, (66, 47): 0, (66, 48): 0, (66, 49): 0, (66, 50): 0, (66, 51): 0, (66, 52): 0, (66, 53): 0, (66, 54): 0, (66, 55): 0, (66, 56): 0, (66, 57): 0, (66, 58): 0, (66, 59): 0, (66, 60): 0, (66, 61): 0, (66, 62): 0, (66, 63): 0, (66, 64): 0, (66, 65): 0, (66, 66): 0, (66, 67): 0, (66, 68): 0, (66, 69): 0, (69, 1): 0, (69, 2): 0, (69, 3): 0, (69, 4): 0, (69, 5): 0, (69, 6): 0, (69, 7): 0, (69, 8): 0, (69, 9): 0, (69, 10): 0, (69, 11): 0, (69, 12): 0, (69, 13): 0, (69, 14): 0, (69, 15): 0, (69, 16): 0, (69, 17): 0, (69, 18): 0, (69, 19): 0, (69, 20): 0, (69, 21): 0, (69, 22): 0, (69, 23): 0, (69, 24): 0, (69, 25): 0, (69, 26): 0, (69, 27): 0, (69, 28): 0, (69, 29): 0, (69, 30): 0, (69, 31): 0, (69, 32): 0, (69, 33): 0, (69, 34): 0, (69, 35): 0, (69, 36): 0, (69, 37): 0, (69, 38): 0, (69, 39): 0, (69, 40): 0, (69, 41): 0, (69, 42): 0, (69, 43): 0, (69, 44): 0, (69, 45): 0, (69, 46): 0, (69, 47): 0, (69, 48): 0, (69, 49): 0, (69, 50): 0, (69, 51): 0, (69, 52): 0, (69, 53): 0, (69, 54): 0, (69, 55): 0, (69, 56): 0, (69, 57): 0, (69, 58): 0, (69, 59): 0, (69, 60): 0, (69, 61): 0, (69, 62): 0, (69, 63): 0, (69, 64): 0, (69, 65): 0, (69, 66): 0, (69, 67): 0, (69, 68): 0, (69, 69): 0, (71, 1): 0, (71, 2): 0, (71, 3): 0, (71, 4): 0, (71, 5): 0, (71, 6): 0, (71, 7): 0, (71, 8): 0, (71, 9): 0, (71, 10): 0, (71, 11): 0, (71, 12): 0, (71, 13): 0, (71, 14): 0, (71, 15): 0, (71, 16): 0, (71, 17): 0, (71, 18): 0, (71, 19): 0, (71, 20): 0, (71, 21): 0, (71, 22): 0, (71, 23): 0, (71, 24): 0, (71, 25): 0, (71, 26): 0, (71, 27): 0, (71, 28): 0, (71, 29): 0, (71, 30): 0, (71, 31): 0, (71, 32): 0, (71, 33): 0, (71, 34): 0, (71, 35): 0, (71, 36): 0, (71, 37): 0, (71, 38): 0, (71, 39): 0, (71, 40): 0, (71, 41): 0, (71, 42): 0, (71, 43): 0, (71, 44): 0, (71, 45): 0, (71, 46): 0, (71, 47): 0, (71, 48): 0, (71, 49): 0, (71, 50): 0, (71, 51): 0, (71, 52): 0, (71, 53): 0, (71, 54): 0, (71, 55): 0, (71, 56): 0, (71, 57): 0, (71, 58): 0, (71, 59): 0, (71, 60): 0, (71, 61): 0, (71, 62): 0, (71, 63): 0, (71, 64): 0, (71, 65): 0, (71, 66): 0, (71, 67): 0, (71, 68): 0, (71, 69): 0, (76, 1): 0, (76, 2): 0, (76, 3): 0, (76, 4): 0, (76, 5): 0, (76, 6): 0, (76, 7): 0, (76, 8): 0, (76, 9): 0, (76, 10): 0, (76, 11): 0, (76, 12): 0, (76, 13): 0, (76, 14): 0, (76, 15): 0, (76, 16): 0, (76, 17): 0, (76, 18): 0, (76, 19): 0, (76, 20): 0, (76, 21): 0, (76, 22): 0, (76, 23): 0, (76, 24): 0, (76, 25): 0, (76, 26): 0, (76, 27): 0, (76, 28): 0, (76, 29): 0, (76, 30): 0, (76, 31): 0, (76, 32): 0, (76, 33): 0, (76, 34): 0, (76, 35): 0, (76, 36): 0, (76, 37): 0, (76, 38): 0, (76, 39): 0, (76, 40): 0, (76, 41): 0, (76, 42): 0, (76, 43): 0, (76, 44): 0, (76, 45): 0, (76, 46): 0, (76, 47): 0, (76, 48): 0, (76, 49): 0, (76, 50): 0, (76, 51): 0, (76, 52): 0, (76, 53): 0, (76, 54): 0, (76, 55): 0, (76, 56): 0, (76, 57): 0, (76, 58): 0, (76, 59): 0, (76, 60): 0, (76, 61): 0, (76, 62): 0, (76, 63): 0, (76, 64): 0, (76, 65): 0, (76, 66): 0, (76, 67): 0, (76, 68): 0, (76, 69): 0, (77, 1): 0, (77, 2): 0, (77, 3): 0, (77, 4): 0, (77, 5): 0, (77, 6): 0, (77, 7): 0, (77, 8): 0, (77, 9): 0, (77, 10): 0, (77, 11): 0, (77, 12): 0, (77, 13): 0, (77, 14): 0, (77, 15): 0, (77, 16): 0, (77, 17): 0, (77, 18): 0, (77, 19): 0, (77, 20): 0, (77, 21): 0, (77, 22): 0, (77, 23): 0, (77, 24): 0, (77, 25): 0, (77, 26): 0, (77, 27): 0, (77, 28): 0, (77, 29): 0, (77, 30): 0, (77, 31): 0, (77, 32): 0, (77, 33): 0, (77, 34): 0, (77, 35): 0, (77, 36): 0, (77, 37): 0, (77, 38): 0, (77, 39): 0, (77, 40): 0, (77, 41): 0, (77, 42): 0, (77, 43): 0, (77, 44): 0, (77, 45): 0, (77, 46): 0, (77, 47): 0, (77, 48): 0, (77, 49): 0, (77, 50): 0, (77, 51): 0, (77, 52): 0, (77, 53): 0, (77, 54): 0, (77, 55): 0, (77, 56): 0, (77, 57): 0, (77, 58): 0, (77, 59): 0, (77, 60): 0, (77, 61): 0, (77, 62): 0, (77, 63): 0, (77, 64): 0, (77, 65): 0, (77, 66): 0, (77, 67): 0, (77, 68): 0, (77, 69): 0, (78, 1): 0, (78, 2): 0, (78, 3): 0, (78, 4): 0, (78, 5): 0, (78, 6): 0, (78, 7): 0, (78, 8): 0, (78, 9): 0, (78, 10): 0, (78, 11): 0, (78, 12): 0, (78, 13): 0, (78, 14): 0, (78, 15): 0, (78, 16): 0, (78, 17): 0, (78, 18): 0, (78, 19): 0, (78, 20): 0, (78, 21): 0, (78, 22): 0, (78, 23): 0, (78, 24): 0, (78, 25): 0, (78, 26): 0, (78, 27): 0, (78, 28): 0, (78, 29): 0, (78, 30): 0, (78, 31): 0, (78, 32): 0, (78, 33): 0, (78, 34): 0, (78, 35): 0, (78, 36): 0, (78, 37): 0, (78, 38): 0, (78, 39): 0, (78, 40): 0, (78, 41): 0, (78, 42): 0, (78, 43): 0, (78, 44): 0, (78, 45): 0, (78, 46): 0, (78, 47): 0, (78, 48): 0, (78, 49): 0, (78, 50): 0, (78, 51): 0, (78, 52): 0, (78, 53): 0, (78, 54): 0, (78, 55): 0, (78, 56): 0, (78, 57): 0, (78, 58): 0, (78, 59): 0, (78, 60): 0, (78, 61): 0, (78, 62): 0, (78, 63): 0, (78, 64): 0, (78, 65): 0, (78, 66): 0, (78, 67): 0, (78, 68): 0, (78, 69): 0, (80, 1): 0, (80, 2): 0, (80, 3): 0, (80, 4): 0, (80, 5): 0, (80, 6): 0, (80, 7): 0, (80, 8): 0, (80, 9): 0, (80, 10): 0, (80, 11): 0, (80, 12): 0, (80, 13): 0, (80, 14): 0, (80, 15): 0, (80, 16): 0, (80, 17): 0, (80, 18): 0, (80, 19): 0, (80, 20): 0, (80, 21): 0, (80, 22): 0, (80, 23): 0, (80, 24): 0, (80, 25): 0, (80, 26): 0, (80, 27): 0, (80, 28): 0, (80, 29): 0, (80, 30): 0, (80, 31): 0, (80, 32): 0, (80, 33): 0, (80, 34): 0, (80, 35): 0, (80, 36): 0, (80, 37): 0, (80, 38): 0, (80, 39): 0, (80, 40): 0, (80, 41): 0, (80, 42): 0, (80, 43): 0, (80, 44): 0, (80, 45): 0, (80, 46): 0, (80, 47): 0, (80, 48): 0, (80, 49): 0, (80, 50): 0, (80, 51): 0, (80, 52): 0, (80, 53): 0, (80, 54): 0, (80, 55): 0, (80, 56): 0, (80, 57): 0, (80, 58): 0, (80, 59): 0, (80, 60): 0, (80, 61): 0, (80, 62): 0, (80, 63): 0, (80, 64): 0, (80, 65): 0, (80, 66): 0, (80, 67): 0, (80, 68): 0, (80, 69): 0, (81, 1): 0, (81, 2): 0, (81, 3): 0, (81, 4): 0, (81, 5): 0, (81, 6): 0, (81, 7): 0, (81, 8): 0, (81, 9): 0, (81, 10): 0, (81, 11): 0, (81, 12): 0, (81, 13): 0, (81, 14): 0, (81, 15): 0, (81, 16): 0, (81, 17): 0, (81, 18): 0, (81, 19): 0, (81, 20): 0, (81, 21): 0, (81, 22): 0, (81, 23): 0, (81, 24): 0, (81, 25): 0, (81, 26): 0, (81, 27): 0, (81, 28): 0, (81, 29): 0, (81, 30): 0, (81, 31): 0, (81, 32): 0, (81, 33): 0, (81, 34): 0, (81, 35): 0, (81, 36): 0, (81, 37): 0, (81, 38): 0, (81, 39): 0, (81, 40): 0, (81, 41): 0, (81, 42): 0, (81, 43): 0, (81, 44): 0, (81, 45): 0, (81, 46): 0, (81, 47): 0, (81, 48): 0, (81, 49): 0, (81, 50): 0, (81, 51): 0, (81, 52): 0, (81, 53): 0, (81, 54): 0, (81, 55): 0, (81, 56): 0, (81, 57): 0, (81, 58): 0, (81, 59): 0, (81, 60): 0, (81, 61): 0, (81, 62): 0, (81, 63): 0, (81, 64): 0, (81, 65): 0, (81, 66): 0, (81, 67): 0, (81, 68): 0, (81, 69): 0, (83, 1): 0, (83, 2): 0, (83, 3): 0, (83, 4): 0, (83, 5): 0, (83, 6): 0, (83, 7): 0, (83, 8): 0, (83, 9): 0, (83, 10): 0, (83, 11): 0, (83, 12): 0, (83, 13): 0, (83, 14): 0, (83, 15): 0, (83, 16): 0, (83, 17): 0, (83, 18): 0, (83, 19): 0, (83, 20): 0, (83, 21): 0, (83, 22): 0, (83, 23): 0, (83, 24): 0, (83, 25): 0, (83, 26): 0, (83, 27): 0, (83, 28): 0, (83, 29): 0, (83, 30): 0, (83, 31): 0, (83, 32): 0, (83, 33): 0, (83, 34): 0, (83, 35): 0, (83, 36): 0, (83, 37): 0, (83, 38): 0, (83, 39): 0, (83, 40): 0, (83, 41): 0, (83, 42): 0, (83, 43): 0, (83, 44): 0, (83, 45): 0, (83, 46): 0, (83, 47): 0, (83, 48): 0, (83, 49): 0, (83, 50): 0, (83, 51): 0, (83, 52): 0, (83, 53): 0, (83, 54): 0, (83, 55): 0, (83, 56): 0, (83, 57): 0, (83, 58): 0, (83, 59): 0, (83, 60): 0, (83, 61): 0, (83, 62): 0, (83, 63): 0, (83, 64): 0, (83, 65): 0, (83, 66): 0, (83, 67): 0, (83, 68): 0, (83, 69): 0, (85, 1): 0, (85, 2): 0, (85, 3): 0, (85, 4): 0, (85, 5): 0, (85, 6): 0, (85, 7): 0, (85, 8): 0, (85, 9): 0, (85, 10): 0, (85, 11): 0, (85, 12): 0, (85, 13): 0, (85, 14): 0, (85, 15): 0, (85, 16): 0, (85, 17): 0, (85, 18): 0, (85, 19): 0, (85, 20): 0, (85, 21): 0, (85, 22): 0, (85, 23): 0, (85, 24): 0, (85, 25): 0, (85, 26): 0, (85, 27): 0, (85, 28): 0, (85, 29): 0, (85, 30): 0, (85, 31): 0, (85, 32): 0, (85, 33): 0, (85, 34): 0, (85, 35): 0, (85, 36): 0, (85, 37): 0, (85, 38): 0, (85, 39): 0, (85, 40): 0, (85, 41): 0, (85, 42): 0, (85, 43): 0, (85, 44): 0, (85, 45): 0, (85, 46): 0, (85, 47): 0, (85, 48): 0, (85, 49): 0, (85, 50): 0, (85, 51): 0, (85, 52): 0, (85, 53): 0, (85, 54): 0, (85, 55): 0, (85, 56): 0, (85, 57): 0, (85, 58): 0, (85, 59): 0, (85, 60): 0, (85, 61): 0, (85, 62): 0, (85, 63): 0, (85, 64): 0, (85, 65): 0, (85, 66): 0, (85, 67): 0, (85, 68): 0, (85, 69): 0, (90, 1): 0, (90, 2): 0, (90, 3): 0, (90, 4): 0, (90, 5): 0, (90, 6): 0, (90, 7): 0, (90, 8): 0, (90, 9): 0, (90, 10): 0, (90, 11): 0, (90, 12): 0, (90, 13): 0, (90, 14): 0, (90, 15): 0, (90, 16): 0, (90, 17): 0, (90, 18): 0, (90, 19): 0, (90, 20): 0, (90, 21): 0, (90, 22): 0, (90, 23): 0, (90, 24): 0, (90, 25): 0, (90, 26): 0, (90, 27): 0, (90, 28): 0, (90, 29): 0, (90, 30): 0, (90, 31): 0, (90, 32): 0, (90, 33): 0, (90, 34): 0, (90, 35): 0, (90, 36): 0, (90, 37): 0, (90, 38): 0, (90, 39): 0, (90, 40): 0, (90, 41): 0, (90, 42): 0, (90, 43): 0, (90, 44): 0, (90, 45): 0, (90, 46): 0, (90, 47): 0, (90, 48): 0, (90, 49): 0, (90, 50): 0, (90, 51): 0, (90, 52): 0, (90, 53): 0, (90, 54): 0, (90, 55): 0, (90, 56): 0, (90, 57): 0, (90, 58): 0, (90, 59): 0, (90, 60): 0, (90, 61): 0, (90, 62): 0, (90, 63): 0, (90, 64): 0, (90, 65): 0, (90, 66): 0, (90, 67): 0, (90, 68): 0, (90, 69): 0, (91, 1): 0, (91, 2): 0, (91, 3): 0, (91, 4): 0, (91, 5): 0, (91, 6): 0, (91, 7): 0, (91, 8): 0, (91, 9): 0, (91, 10): 0, (91, 11): 0, (91, 12): 0, (91, 13): 0, (91, 14): 0, (91, 15): 0, (91, 16): 0, (91, 17): 0, (91, 18): 0, (91, 19): 0, (91, 20): 0, (91, 21): 0, (91, 22): 0, (91, 23): 0, (91, 24): 0, (91, 25): 0, (91, 26): 0, (91, 27): 0, (91, 28): 0, (91, 29): 0, (91, 30): 0, (91, 31): 0, (91, 32): 0, (91, 33): 0, (91, 34): 0, (91, 35): 0, (91, 36): 0, (91, 37): 0, (91, 38): 0, (91, 39): 0, (91, 40): 0, (91, 41): 0, (91, 42): 0, (91, 43): 0, (91, 44): 0, (91, 45): 0, (91, 46): 0, (91, 47): 0, (91, 48): 0, (91, 49): 0, (91, 50): 0, (91, 51): 0, (91, 52): 0, (91, 53): 0, (91, 54): 0, (91, 55): 0, (91, 56): 0, (91, 57): 0, (91, 58): 0, (91, 59): 0, (91, 60): 0, (91, 61): 0, (91, 62): 0, (91, 63): 0, (91, 64): 0, (91, 65): 0, (91, 66): 0, (91, 67): 0, (91, 68): 0, (91, 69): 0, (93, 1): 0, (93, 2): 0, (93, 3): 0, (93, 4): 0, (93, 5): 0, (93, 6): 0, (93, 7): 0, (93, 8): 0, (93, 9): 0, (93, 10): 0, (93, 11): 0, (93, 12): 0, (93, 13): 0, (93, 14): 0, (93, 15): 0, (93, 16): 0, (93, 17): 0, (93, 18): 0, (93, 19): 0, (93, 20): 0, (93, 21): 0, (93, 22): 0, (93, 23): 0, (93, 24): 0, (93, 25): 0, (93, 26): 0, (93, 27): 0, (93, 28): 0, (93, 29): 0, (93, 30): 0, (93, 31): 0, (93, 32): 0, (93, 33): 0, (93, 34): 0, (93, 35): 0, (93, 36): 0, (93, 37): 0, (93, 38): 0, (93, 39): 0, (93, 40): 0, (93, 41): 0, (93, 42): 0, (93, 43): 0, (93, 44): 0, (93, 45): 0, (93, 46): 0, (93, 47): 0, (93, 48): 0, (93, 49): 0, (93, 50): 0, (93, 51): 0, (93, 52): 0, (93, 53): 0, (93, 54): 0, (93, 55): 0, (93, 56): 0, (93, 57): 0, (93, 58): 0, (93, 59): 0, (93, 60): 0, (93, 61): 0, (93, 62): 0, (93, 63): 0, (93, 64): 0, (93, 65): 0, (93, 66): 0, (93, 67): 0, (93, 68): 0, (93, 69): 0, (103, 1): 0, (103, 2): 0, (103, 3): 0, (103, 4): 0, (103, 5): 0, (103, 6): 0, (103, 7): 0, (103, 8): 0, (103, 9): 0, (103, 10): 0, (103, 11): 0, (103, 12): 0, (103, 13): 0, (103, 14): 0, (103, 15): 0, (103, 16): 0, (103, 17): 0, (103, 18): 0, (103, 19): 0, (103, 20): 0, (103, 21): 0, (103, 22): 0, (103, 23): 0, (103, 24): 0, (103, 25): 0, (103, 26): 0, (103, 27): 0, (103, 28): 0, (103, 29): 0, (103, 30): 0, (103, 31): 0, (103, 32): 0, (103, 33): 0, (103, 34): 0, (103, 35): 0, (103, 36): 0, (103, 37): 0, (103, 38): 0, (103, 39): 0, (103, 40): 0, (103, 41): 0, (103, 42): 0, (103, 43): 0, (103, 44): 0, (103, 45): 0, (103, 46): 0, (103, 47): 0, (103, 48): 0, (103, 49): 0, (103, 50): 0, (103, 51): 0, (103, 52): 0, (103, 53): 0, (103, 54): 0, (103, 55): 0, (103, 56): 0, (103, 57): 0, (103, 58): 0, (103, 59): 0, (103, 60): 0, (103, 61): 0, (103, 62): 0, (103, 63): 0, (103, 64): 0, (103, 65): 0, (103, 66): 0, (103, 67): 0, (103, 68): 0, (103, 69): 0, (105, 1): 0, (105, 2): 0, (105, 3): 0, (105, 4): 0, (105, 5): 0, (105, 6): 0, (105, 7): 0, (105, 8): 0, (105, 9): 0, </t>
+  </si>
+  <si>
+    <t>{(3, 1): 0.0, (3, 2): 0.0, (3, 3): 0.0, (3, 4): 0.0, (3, 5): 0.0, (3, 6): 0.0, (3, 7): 0.0, (3, 8): 0.0, (3, 9): 0.0, (3, 10): 0.0, (3, 11): 0.0, (3, 12): 0.0, (3, 13): 0.0, (3, 14): 0.0, (3, 15): 0.0, (3, 16): 0.0, (3, 17): 0.0, (3, 18): 0.0, (3, 19): 0.0, (3, 20): 0.0, (3, 21): 0.0, (3, 22): 0.0, (3, 23): 0.0, (3, 24): 0.0, (3, 25): 0.0, (3, 26): 0.0, (3, 27): 0.0, (3, 28): 0.0, (3, 29): 0.0, (3, 30): 0.0, (3, 31): 0.0, (3, 32): 0.0, (3, 33): 0.0, (3, 34): 0.0, (3, 35): 0.0, (3, 36): 0.0, (3, 37): 0.0, (3, 38): 0.0, (3, 39): 0.0, (3, 40): 0.0, (3, 41): 0.0, (3, 42): 0.0, (3, 43): 0.0, (3, 44): 0.0, (3, 45): 0.5051001633268003, (3, 46): 0.5051001633268003, (3, 47): 0.5051001633268003, (3, 48): 0.5051001633268003, (3, 49): 0.5051001633268003, (3, 50): 0.5051001633268003, (3, 51): 0.5051001633268003, (3, 52): 0.5051001633268003, (3, 53): 0.5051001633268003, (3, 54): 0.5051001633268003, (3, 55): 0.5051001633268003, (3, 56): 0.5051001633268003, (3, 57): 0.5051001633268003, (3, 58): 0.5051001633268003, (3, 59): 0.5051001633268003, (3, 60): 0.0, (3, 61): 0.0, (3, 62): 0.0, (3, 63): 0.0, (3, 64): 0.0, (3, 65): 0.0, (3, 66): 0.0, (3, 67): 0.0, (3, 68): 0.0, (3, 69): 0.0, (4, 1): 0.0, (4, 2): 0.0, (4, 3): 0.0, (4, 4): 0.0, (4, 5): 0.0, (4, 6): 0.0, (4, 7): 0.0, (4, 8): 0.0, (4, 9): 0.0, (4, 10): 0.0, (4, 11): 0.0, (4, 12): 0.0, (4, 13): 0.0, (4, 14): 0.0, (4, 15): 0.0, (4, 16): 0.0, (4, 17): 0.0, (4, 18): 0.0, (4, 19): 0.0, (4, 20): 0.0, (4, 21): 0.0, (4, 22): 0.0, (4, 23): 0.0, (4, 24): 0.0, (4, 25): 0.0, (4, 26): 0.0, (4, 27): 0.0, (4, 28): 0.0, (4, 29): 0.0, (4, 30): 0.0, (4, 31): 0.0, (4, 32): 0.0, (4, 33): 0.0, (4, 34): 0.0, (4, 35): 0.0, (4, 36): 0.0, (4, 37): 0.0, (4, 38): 0.0, (4, 39): 0.0, (4, 40): 0.0, (4, 41): 0.0, (4, 42): 0.0, (4, 43): 0.0, (4, 44): 0.0, (4, 45): 0.0, (4, 46): 0.0, (4, 47): 0.0, (4, 48): 0.0, (4, 49): 0.0, (4, 50): 0.5051001633268003, (4, 51): 0.5051001633268003, (4, 52): 0.5051001633268003, (4, 53): 0.5051001633268003, (4, 54): 0.5051001633268003, (4, 55): 0.5051001633268003, (4, 56): 0.5051001633268003, (4, 57): 0.5051001633268003, (4, 58): 0.5051001633268003, (4, 59): 0.5051001633268003, (4, 60): 0.5051001633268003, (4, 61): 0.5051001633268003, (4, 62): 0.5051001633268003, (4, 63): 0.5051001633268003, (4, 64): 0.0, (4, 65): 0.0, (4, 66): 0.0, (4, 67): 0.0, (4, 68): 0.0, (4, 69): 0.0, (8, 1): 0.0, (8, 2): 0.0, (8, 3): 0.0, (8, 4): 0.0, (8, 5): 0.0, (8, 6): 0.0, (8, 7): 0.0, (8, 8): 0.0, (8, 9): 0.0, (8, 10): 0.0, (8, 11): 0.0, (8, 12): 0.0, (8, 13): 0.0, (8, 14): 0.0, (8, 15): 0.0, (8, 16): 0.0, (8, 17): 0.0, (8, 18): 0.0, (8, 19): 0.0, (8, 20): 0.0, (8, 21): 0.0, (8, 22): 0.0, (8, 23): 0.0, (8, 24): 0.0, (8, 25): 0.0, (8, 26): 0.0, (8, 27): 0.0, (8, 28): 0.0, (8, 29): 0.0, (8, 30): 0.0, (8, 31): 0.0, (8, 32): 0.0, (8, 33): 0.0, (8, 34): 0.0, (8, 35): 0.0, (8, 36): 0.0, (8, 37): 0.0, (8, 38): 0.0, (8, 39): 0.5051001633268003, (8, 40): 0.5051001633268003, (8, 41): 0.5051001633268003, (8, 42): 0.5051001633268003, (8, 43): 0.5051001633268003, (8, 44): 0.5051001633268003, (8, 45): 0.5051001633268003, (8, 46): 0.5051001633268003, (8, 47): 0.5051001633268003, (8, 48): 0.5051001633268003, (8, 49): 0.0, (8, 50): 0.0, (8, 51): 0.0, (8, 52): 0.0, (8, 53): 0.0, (8, 54): 0.0, (8, 55): 0.0, (8, 56): 0.0, (8, 57): 0.0, (8, 58): 0.0, (8, 59): 0.0, (8, 60): 0.0, (8, 61): 0.0, (8, 62): 0.0, (8, 63): 0.0, (8, 64): 0.0, (8, 65): 0.0, (8, 66): 0.0, (8, 67): 0.0, (8, 68): 0.0, (8, 69): 0.0, (9, 1): 0.0, (9, 2): 0.0, (9, 3): 0.0, (9, 4): 0.0, (9, 5): 0.0, (9, 6): 0.0, (9, 7): 0.0, (9, 8): 0.0, (9, 9): 0.0, (9, 10): 0.0, (9, 11): 0.0, (9, 12): 0.0, (9, 13): 0.0, (9, 14): 0.0, (9, 15): 0.0, (9, 16): 0.0, (9, 17): 0.0, (9, 18): 0.0, (9, 19): 0.0, (9, 20): 0.0, (9, 21): 0.0, (9, 22): 0.0, (9, 23): 0.0, (9, 24): 0.0, (9, 25): 0.0, (9, 26): 0.0, (9, 27): 0.0, (9, 28): 0.0, (9, 29): 0.0, (9, 30): 0.0, (9, 31): 0.0, (9, 32): 0.0, (9, 33): 0.0, (9, 34): 0.0, (9, 35): 0.0, (9, 36): 0.0, (9, 37): 0.0, (9, 38): 0.0, (9, 39): 0.0, (9, 40): 0.0, (9, 41): 0.0, (9, 42): 0.0, (9, 43): 0.0, (9, 44): 0.0, (9, 45): 0.0, (9, 46): 0.0, (9, 47): 0.0, (9, 48): 0.0, (9, 49): 0.0, (9, 50): 0.0, (9, 51): 0.0, (9, 52): 0.0, (9, 53): 0.0, (9, 54): 0.0, (9, 55): 0.0, (9, 56): 0.0, (9, 57): 0.0, (9, 58): 0.0, (9, 59): 0.0, (9, 60): 0.0, (9, 61): 0.0, (9, 62): 0.0, (9, 63): 0.0, (9, 64): 0.5051001633268003, (9, 65): 0.5051001633268003, (9, 66): 0.5051001633268003, (9, 67): 0.5051001633268003, (9, 68): 0.5051001633268003, (9, 69): 0.5051001633268003, (10, 1): 0.0, (10, 2): 0.0, (10, 3): 0.0, (10, 4): 0.0, (10, 5): 0.0, (10, 6): 0.0, (10, 7): 0.0, (10, 8): 0.0, (10, 9): 0.0, (10, 10): 0.0, (10, 11): 0.0, (10, 12): 0.0, (10, 13): 0.0, (10, 14): 0.0, (10, 15): 0.0, (10, 16): 0.0, (10, 17): 0.0, (10, 18): 0.0, (10, 19): 0.0, (10, 20): 0.0, (10, 21): 0.0, (10, 22): 0.0, (10, 23): 0.0, (10, 24): 0.0, (10, 25): 0.0, (10, 26): 0.0, (10, 27): 0.0, (10, 28): 0.0, (10, 29): 0.0, (10, 30): 0.0, (10, 31): 0.0, (10, 32): 0.0, (10, 33): 0.0, (10, 34): 0.0, (10, 35): 0.0, (10, 36): 0.0, (10, 37): 0.0, (10, 38): 0.0, (10, 39): 0.0, (10, 40): 0.0, (10, 41): 0.0, (10, 42): 0.0, (10, 43): 0.5051001633268003, (10, 44): 0.5051001633268003, (10, 45): 0.5051001633268003, (10, 46): 0.5051001633268003, (10, 47): 0.5051001633268003, (10, 48): 0.5051001633268003, (10, 49): 0.5051001633268003, (10, 50): 0.5051001633268003, (10, 51): 0.5051001633268003, (10, 52): 0.5051001633268003, (10, 53): 0.5051001633268003, (10, 54): 0.5051001633268003, (10, 55): 0.0, (10, 56): 0.0, (10, 57): 0.0, (10, 58): 0.0, (10, 59): 0.0, (10, 60): 0.0, (10, 61): 0.0, (10, 62): 0.0, (10, 63): 0.0, (10, 64): 0.0, (10, 65): 0.0, (10, 66): 0.0, (10, 67): 0.0, (10, 68): 0.0, (10, 69): 0.0, (11, 1): 0.0, (11, 2): 0.0, (11, 3): 0.0, (11, 4): 0.0, (11, 5): 0.0, (11, 6): 0.0, (11, 7): 0.0, (11, 8): 0.0, (11, 9): 0.0, (11, 10): 0.0, (11, 11): 0.0, (11, 12): 0.0, (11, 13): 0.0, (11, 14): 0.0, (11, 15): 0.0, (11, 16): 0.0, (11, 17): 0.0, (11, 18): 0.0, (11, 19): 0.0, (11, 20): 0.0, (11, 21): 0.0, (11, 22): 0.0, (11, 23): 0.0, (11, 24): 0.0, (11, 25): 0.0, (11, 26): 0.0, (11, 27): 0.0, (11, 28): 0.0, (11, 29): 0.0, (11, 30): 0.0, (11, 31): 0.0, (11, 32): 0.0, (11, 33): 0.0, (11, 34): 0.0, (11, 35): 0.0, (11, 36): 0.0, (11, 37): 0.0, (11, 38): 0.0, (11, 39): 0.0, (11, 40): 0.0, (11, 41): 0.0, (11, 42): 0.0, (11, 43): 0.0, (11, 44): 0.0, (11, 45): 0.0, (11, 46): 0.0, (11, 47): 0.0, (11, 48): 0.0, (11, 49): 0.0, (11, 50): 0.0, (11, 51): 0.0, (11, 52): 0.0, (11, 53): 0.0, (11, 54): 0.0, (11, 55): 0.0, (11, 56): 0.0, (11, 57): 0.5051001633268003, (11, 58): 0.5051001633268003, (11, 59): 0.5051001633268003, (11, 60): 0.5051001633268003, (11, 61): 0.5051001633268003, (11, 62): 0.5051001633268003, (11, 63): 0.0, (11, 64): 0.0, (11, 65): 0.0, (11, 66): 0.0, (11, 67): 0.0, (11, 68): 0.0, (11, 69): 0.0, (12, 1): 0.0, (12, 2): 0.0, (12, 3): 0.0, (12, 4): 0.0, (12, 5): 0.0, (12, 6): 0.0, (12, 7): 0.0, (12, 8): 0.0, (12, 9): 0.0, (12, 10): 0.0, (12, 11): 0.0, (12, 12): 0.0, (12, 13): 0.0, (12, 14): 0.0, (12, 15): 0.0, (12, 16): 0.0, (12, 17): 0.0, (12, 18): 0.0, (12, 19): 0.0, (12, 20): 0.0, (12, 21): 0.0, (12, 22): 0.0, (12, 23): 0.0, (12, 24): 0.0, (12, 25): 0.0, (12, 26): 0.0, (12, 27): 0.0, (12, 28): 0.0, (12, 29): 0.0, (12, 30): 0.0, (12, 31): 0.0, (12, 32): 0.0, (12, 33): 0.0, (12, 34): 0.5051001633268003, (12, 35): 0.5051001633268003, (12, 36): 0.5051001633268003, (12, 37): 0.5051001633268003, (12, 38): 0.5051001633268003, (12, 39): 0.5051001633268003, (12, 40): 0.5051001633268003, (12, 41): 0.5051001633268003, (12, 42): 0.5051001633268003, (12, 43): 0.5051001633268003, (12, 44): 0.5051001633268003, (12, 45): 0.0, (12, 46): 0.0, (12, 47): 0.0, (12, 48): 0.0, (12, 49): 0.0, (12, 50): 0.0, (12, 51): 0.0, (12, 52): 0.0, (12, 53): 0.0, (12, 54): 0.0, (12, 55): 0.0, (12, 56): 0.0, (12, 57): 0.0, (12, 58): 0.0, (12, 59): 0.0, (12, 60): 0.0, (12, 61): 0.0, (12, 62): 0.0, (12, 63): 0.0, (12, 64): 0.0, (12, 65): 0.0, (12, 66): 0.0, (12, 67): 0.0, (12, 68): 0.0, (12, 69): 0.0, (21, 1): 0.0, (21, 2): 0.0, (21, 3): 0.0, (21, 4): 0.0, (21, 5): 0.0, (21, 6): 0.0, (21, 7): 0.0, (21, 8): 0.0, (21, 9): 0.0, (21, 10): 0.0, (21, 11): 0.0, (21, 12): 0.0, (21, 13): 0.0, (21, 14): 0.0, (21, 15): 0.0, (21, 16): 0.0, (21, 17): 0.0, (21, 18): 0.0, (21, 19): 0.0, (21, 20): 0.0, (21, 21): 0.0, (21, 22): 0.0, (21, 23): 0.0, (21, 24): 0.0, (21, 25): 0.0, (21, 26): 0.0, (21, 27): 0.0, (21, 28): 0.0, (21, 29): 0.0, (21, 30): 0.0, (21, 31): 0.0, (21, 32): 0.0, (21, 33): 0.0, (21, 34): 0.0, (21, 35): 0.0, (21, 36): 0.0, (21, 37): 0.0, (21, 38): 0.0, (21, 39): 0.0, (21, 40): 0.0, (21, 41): 0.0, (21, 42): 0.0, (21, 43): 0.0, (21, 44): 0.0, (21, 45): 0.5051001633268003, (21, 46): 0.5051001633268003, (21, 47): 0.5051001633268003, (21, 48): 0.5051001633268003, (21, 49): 0.5051001633268003, (21, 50): 0.5051001633268003, (21, 51): 0.5051001633268003, (21, 52): 0.5051001633268003, (21, 53): 0.0, (21, 54): 0.0, (21, 55): 0.0, (21, 56): 0.0, (21, 57): 0.0, (21, 58): 0.0, (21, 59): 0.0, (21, 60): 0.0, (21, 61): 0.0, (21, 62): 0.0, (21, 63): 0.0, (21, 64): 0.0, (21, 65): 0.0, (21, 66): 0.0, (21, 67): 0.0, (21, 68): 0.0, (21, 69): 0.0, (23, 1): 0.0, (23, 2): 0.0, (23, 3): 0.0, (23, 4): 0.0, (23, 5): 0.0, (23, 6): 0.0, (23, 7): 0.0, (23, 8): 0.0, (23, 9): 0.0, (23, 10): 0.0, (23, 11): 0.0, (23, 12): 0.0, (23, 13): 0.0, (23, 14): 0.0, (23, 15): 0.0, (23, 16): 0.0, (23, 17): 0.0, (23, 18): 0.0, (23, 19): 0.0, (23, 20): 0.0, (23, 21): 0.0, (23, 22): 0.0, (23, 23): 0.0, (23, 24): 0.0, (23, 25): 0.0, (23, 26): 0.0, (23, 27): 0.0, (23, 28): 0.0, (23, 29): 0.0, (23, 30): 0.0, (23, 31): 0.0, (23, 32): 0.0, (23, 33): 0.5051001633268003, (23, 34): 0.5051001633268003, (23, 35): 0.5051001633268003, (23, 36): 0.5051001633268003, (23, 37): 0.5051001633268003, (23, 38): 0.5051001633268003, (23, 39): 0.5051001633268003, (23, 40): 0.5051001633268003, (23, 41): 0.5051001633268003, (23, 42): 0.5051001633268003, (23, 43): 0.0, (23, 44): 0.0, (23, 45): 0.0, (23, 46): 0.0, (23, 47): 0.0, (23, 48): 0.0, (23, 49): 0.0, (23, 50): 0.0, (23, 51): 0.0, (23, 52): 0.0, (23, 53): 0.0, (23, 54): 0.0, (23, 55): 0.0, (23, 56): 0.0, (23, 57): 0.0, (23, 58): 0.0, (23, 59): 0.0, (23, 60): 0.0, (23, 61): 0.0, (23, 62): 0.0, (23, 63): 0.0, (23, 64): 0.0, (23, 65): 0.0, (23, 66): 0.0, (23, 67): 0.0, (23, 68): 0.0, (23, 69): 0.0, (24, 1): 0.0, (24, 2): 0.0, (24, 3): 0.0, (24, 4): 0.0, (24, 5): 0.0, (24, 6): 0.0, (24, 7): 0.0, (24, 8): 0.0, (24, 9): 0.0, (24, 10): 0.0, (24, 11): 0.0, (24, 12): 0.0, (24, 13): 0.0, (24, 14): 0.0, (24, 15): 0.0, (24, 16): 0.0, (24, 17): 0.0, (24, 18): 0.0, (24, 19): 0.0, (24, 20): 0.0, (24, 21): 0.0, (24, 22): 0.0, (24, 23): 0.0, (24, 24): 0.0, (24, 25): 0.0, (24, 26): 0.0, (24, 27): 0.0, (24, 28): 0.0, (24, 29): 0.0, (24, 30): 0.0, (24, 31): 0.0, (24, 32): 0.0, (24, 33): 0.0, (24, 34): 0.0, (24, 35): 0.0, (24, 36): 0.0, (24, 37): 0.0, (24, 38): 0.0, (24, 39): 0.0, (24, 40): 0.0, (24, 41): 0.0, (24, 42): 0.0, (24, 43): 0.0, (24, 44): 0.0, (24, 45): 0.0, (24, 46): 0.0, (24, 47): 0.0, (24, 48): 0.0, (24, 49): 0.0, (24, 50): 0.0, (24, 51): 0.0, (24, 52): 0.0, (24, 53): 0.0, (24, 54): 0.0, (24, 55): 0.0, (24, 56): 0.0, (24, 57): 0.0, (24, 58): 0.0, (24, 59): 0.5051001633268003, (24, 60): 0.5051001633268003, (24, 61): 0.5051001633268003, (24, 62): 0.5051001633268003, (24, 63): 0.5051001633268003, (24, 64): 0.5051001633268003, (24, 65): 0.5051001633268003, (24, 66): 0.5051001633268003, (24, 67): 0.5051001633268003, (24, 68): 0.5051001633268003, (24, 69): 0.0, (29, 1): 0.0, (29, 2): 0.0, (29, 3): 0.0, (29, 4): 0.0, (29, 5): 0.0, (29, 6): 0.0, (29, 7): 0.0, (29, 8): 0.0, (29, 9): 0.0, (29, 10): 0.0, (29, 11): 0.0, (29, 12): 0.0, (29, 13): 0.0, (29, 14): 0.0, (29, 15): 0.0, (29, 16): 0.0, (29, 17): 0.0, (29, 18): 0.0, (29, 19): 0.0, (29, 20): 0.0, (29, 21): 0.0, (29, 22): 0.0, (29, 23): 0.0, (29, 24): 0.0, (29, 25): 0.0, (29, 26): 0.0, (29, 27): 0.0, (29, 28): 0.0, (29, 29): 0.0, (29, 30): 0.0, (29, 31): 0.0, (29, 32): 0.0, (29, 33): 0.0, (29, 34): 0.0, (29, 35): 0.0, (29, 36): 0.0, (29, 37): 0.0, (29, 38): 0.5051001633268003, (29, 39): 0.5051001633268003, (29, 40): 0.5051001633268003, (29, 41): 0.5051001633268003, (29, 42): 0.5051001633268003, (29, 43): 0.5051001633268003, (29, 44): 0.5051001633268003, (29, 45): 0.5051001633268003, (29, 46): 0.5051001633268003, (29, 47): 0.5051001633268003, (29, 48): 0.5051001633268003, (29, 49): 0.5051001633268003, (29, 50): 0.5051001633268003, (29, 51): 0.0, (29, 52): 0.0, (29, 53): 0.0, (29, 54): 0.0, (29, 55): 0.0, (29, 56): 0.0, (29, 57): 0.0, (29, 58): 0.0, (29, 59): 0.0, (29, 60): 0.0, (29, 61): 0.0, (29, 62): 0.0, (29, 63): 0.0, (29, 64): 0.0, (29, 65): 0.0, (29, 66): 0.0, (29, 67): 0.0, (29, 68): 0.0, (29, 69): 0.0, (31, 1): 0.0, (31, 2): 0.0, (31, 3): 0.0, (31, 4): 0.0, (31, 5): 0.0, (31, 6): 0.0, (31, 7): 0.0, (31, 8): 0.0, (31, 9): 0.0, (31, 10): 0.0, (31, 11): 0.0, (31, 12): 0.0, (31, 13): 0.0, (31, 14): 0.0, (31, 15): 0.0, (31, 16): 0.0, (31, 17): 0.0, (31, 18): 0.0, (31, 19): 0.0, (31, 20): 0.0, (31, 21): 0.0, (31, 22): 0.0, (31, 23): 0.0, (31, 24): 0.0, (31, 25): 0.0, (31, 26): 0.0, (31, 27): 0.0, (31, 28): 0.0, (31, 29): 0.0, (31, 30): 0.0, (31, 31): 0.0, (31, 32): 0.0, (31, 33): 0.0, (31, 34): 0.0, (31, 35): 0.0, (31, 36): 0.0, (31, 37): 0.0, (31, 38): 0.0, (31, 39): 0.0, (31, 40): 0.0, (31, 41): 0.0, (31, 42): 0.0, (31, 43): 0.0, (31, 44): 0.0, (31, 45): 0.0, (31, 46): 0.0, (31, 47): 0.0, (31, 48): 0.0, (31, 49): 0.0, (31, 50): 0.0, (31, 51): 0.0, (31, 52): 0.0, (31, 53): 0.0, (31, 54): 0.0, (31, 55): 0.0, (31, 56): 0.0, (31, 57): 0.0, (31, 58): 0.0, (31, 59): 0.0, (31, 60): 0.0, (31, 61): 0.0, (31, 62): 0.0, (31, 63): 0.0, (31, 64): 0.0, (31, 65): 0.0, (31, 66): 0.0, (31, 67): 0.0, (31, 68): 0.5051001633268003, (31, 69): 0.5051001633268003, (33, 1): 0.0, (33, 2): 0.0, (33, 3): 0.0, (33, 4): 0.0, (33, 5): 0.0, (33, 6): 0.0, (33, 7): 0.0, (33, 8): 0.0, (33, 9): 0.0, (33, 10): 0.0, (33, 11): 0.0, (33, 12): 0.0, (33, 13): 0.0, (33, 14): 0.0, (33, 15): 0.0, (33, 16): 0.0, (33, 17): 0.0, (33, 18): 0.0, (33, 19): 0.0, (33, 20): 0.0, (33, 21): 0.0, (33, 22): 0.0, (33, 23): 0.0, (33, 24): 0.0, (33, 25): 0.0, (33, 26): 0.0, (33, 27): 0.0, (33, 28): 0.0, (33, 29): 0.0, (33, 30): 0.0, (33, 31): 0.0, (33, 32): 0.0, (33, 33): 0.0, (33, 34): 0.0, (33, 35): 0.0, (33, 36): 0.0, (33, 37): 0.0, (33, 38): 0.0, (33, 39): 0.0, (33, 40): 0.0, (33, 41): 0.0, (33, 42): 0.0, (33, 43): 0.0, (33, 44): 0.0, (33, 45): 0.0, (33, 46): 0.0, (33, 47): 0.0, (33, 48): 0.0, (33, 49): 0.0, (33, 50): 0.0, (33, 51): 0.0, (33, 52): 0.0, (33, 53): 0.0, (33, 54): 0.0, (33, 55): 0.0, (33, 56): 0.0, (33, 57): 0.0, (33, 58): 0.0, (33, 59): 0.0, (33, 60): 0.0, (33, 61): 0.0, (33, 62): 0.0, (33, 63): 0.0, (33, 64): 0.0, (33, 65): 0.0, (33, 66): 0.5051001633268003, (33, 67): 0.5051001633268003, (33, 68): 0.5051001633268003, (33, 69): 0.5051001633268003, (45, 1): 0.0, (45, 2): 0.0, (45, 3): 0.0, (45, 4): 0.0, (45, 5): 0.0, (45, 6): 0.0, (45, 7): 0.0, (45, 8): 0.0, (45, 9): 0.0, (45, 10): 0.0, (45, 11): 0.0, (45, 12): 0.0, (45, 13): 0.0, (45, 14): 0.0, (45, 15): 0.0, (45, 16): 0.0, (45, 17): 0.0, (45, 18): 0.0, (45, 19): 0.0, (45, 20): 0.0, (45, 21): 0.0, (45, 22): 0.0, (45, 23): 0.0, (45, 24): 0.0, (45, 25): 0.0, (45, 26): 0.0, (45, 27): 0.0, (45, 28): 0.0, (45, 29): 0.0, (45, 30): 0.0, (45, 31): 0.0, (45, 32): 0.0, (45, 33): 0.0, (45, 34): 0.0, (45, 35): 0.0, (45, 36): 0.0, (45, 37): 0.0, (45, 38): 0.0, (45, 39): 0.0, (45, 40): 0.0, (45, 41): 0.0, (45, 42): 0.0, (45, 43): 0.0, (45, 44): 0.0, (45, 45): 0.0, (45, 46): 0.0, (45, 47): 0.0, (45, 48): 0.0, (45, 49): 0.0, (45, 50): 0.0, (45, 51): 0.0, (45, 52): 0.0, (45, 53): 0.0, (45, 54): 0.0, (45, 55): 0.0, (45, 56): 0.0, (45, 57): 0.0, (45, 58): 0.0, (45, 59): 0.0, (45, 60): 0.5051001633268003, (45, 61): 0.5051001633268003, (45, 62): 0.5051001633268003, (45, 63): 0.5051001633268003, (45, 64): 0.5051001633268003, (45, 65): 0.5051001633268003, (45, 66): 0.0, (45, 67): 0.0, (45, 68): 0.0, (45, 69): 0.0, (50, 1): 0.0, (50, 2): 0.0, (50, 3): 0.0, (50, 4): 0.0, (50, 5): 0.0, (50, 6): 0.0, (50, 7): 0.0, (50, 8): 0.0, (50, 9): 0.0, (50, 10): 0.0, (50, 11): 0.0, (50, 12): 0.0, (50, 13): 0.0, (50, 14): 0.0, (50, 15): 0.0, (50, 16): 0.0, (50, 17): 0.0, (50, 18): 0.0, (50, 19): 0.0, (50, 20): 0.0, (50, 21): 0.0, (50, 22): 0.0, (50, 23): 0.0, (50, 24): 0.0, (50, 25): 0.0, (50, 26): 0.0, (50, 27): 0.0, (50, 28): 0.0, (50, 29): 0.0, (50, 30): 0.0, (50, 31): 0.0, (50, 32): 0.0, (50, 33): 0.0, (50, 34): 0.0, (50, 35): 0.0, (50, 36): 0.0, (50, 37): 0.0, (50, 38): 0.0, (50, 39): 0.0, (50, 40): 0.0, (50, 41): 0.0, (50, 42): 0.0, (50, 43): 0.0, (50, 44): 0.0, (50, 45): 0.0, (50, 46): 0.0, (50, 47): 0.0, (50, 48): 0.0, (50, 49): 0.0, (50, 50): 0.0, (50, 51): 0.0, (50, 52): 0.0, (50, 53): 0.0, (50, 54): 0.0, (50, 55): 0.0, (50, 56): 0.0, (50, 57): 0.0, (50, 58): 0.0, (50, 59): 0.0, (50, 60): 0.0, (50, 61): 0.5051001633268003, (50, 62): 0.5051001633268003, (50, 63): 0.5051001633268003, (50, 64): 0.5051001633268003, (50, 65): 0.5051001633268003, (50, 66): 0.5051001633268003, (50, 67): 0.5051001633268003, (50, 68): 0.0, (50, 69): 0.0, (53, 1): 0.0, (53, 2): 0.0, (53, 3): 0.0, (53, 4): 0.0, (53, 5): 0.0, (53, 6): 0.0, (53, 7): 0.0, (53, 8): 0.0, (53, 9): 0.0, (53, 10): 0.0, (53, 11): 0.0, (53, 12): 0.0, (53, 13): 0.0, (53, 14): 0.0, (53, 15): 0.0, (53, 16): 0.0, (53, 17): 0.0, (53, 18): 0.0, (53, 19): 0.0, (53, 20): 0.0, (53, 21): 0.0, (53, 22): 0.0, (53, 23): 0.0, (53, 24): 0.0, (53, 25): 0.0, (53, 26): 0.0, (53, 27): 0.0, (53, 28): 0.0, (53, 29): 0.0, (53, 30): 0.0, (53, 31): 0.0, (53, 32): 0.0, (53, 33): 0.0, (53, 34): 0.0, (53, 35): 0.0, (53, 36): 0.0, (53, 37): 0.0, (53, 38): 0.0, (53, 39): 0.0, (53, 40): 0.0, (53, 41): 0.0, (53, 42): 0.0, (53, 43): 0.0, (53, 44): 0.0, (53, 45): 0.0, (53, 46): 0.0, (53, 47): 0.0, (53, 48): 0.0, (53, 49): 0.0, (53, 50): 0.0, (53, 51): 0.0, (53, 52): 0.5051001633268003, (53, 53): 0.5051001633268003, (53, 54): 0.5051001633268003, (53, 55): 0.5051001633268003, (53, 56): 0.5051001633268003, (53, 57): 0.5051001633268003, (53, 58): 0.5051001633268003, (53, 59): 0.0, (53, 60): 0.0, (53, 61): 0.0, (53, 62): 0.0, (53, 63): 0.0, (53, 64): 0.0, (53, 65): 0.0, (53, 66): 0.0, (53, 67): 0.0, (53, 68): 0.0, (53, 69): 0.0, (54, 1): 0.0, (54, 2): 0.0, (54, 3): 0.0, (54, 4): 0.0, (54, 5): 0.0, (54, 6): 0.0, (54, 7): 0.0, (54, 8): 0.0, (54, 9): 0.0, (54, 10): 0.0, (54, 11): 0.0, (54, 12): 0.0, (54, 13): 0.0, (54, 14): 0.0, (54, 15): 0.0, (54, 16): 0.0, (54, 17): 0.0, (54, 18): 0.0, (54, 19): 0.0, (54, 20): 0.0, (54, 21): 0.0, (54, 22): 0.0, (54, 23): 0.0, (54, 24): 0.0, (54, 25): 0.0, (54, 26): 0.0, (54, 27): 0.0, (54, 28): 0.0, (54, 29): 0.0, (54, 30): 0.0, (54, 31): 0.0, (54, 32): 0.0, (54, 33): 0.0, (54, 34): 0.0, (54, 35): 0.0, (54, 36): 0.0, (54, 37): 0.0, (54, 38): 0.0, (54, 39): 0.0, (54, 40): 0.0, (54, 41): 0.0, (54, 42): 0.0, (54, 43): 0.0, (54, 44): 0.0, (54, 45): 0.0, (54, 46): 0.0, (54, 47): 0.0, (54, 48): 0.0, (54, 49): 0.0, (54, 50): 0.5051001633268003, (54, 51): 0.5051001633268003, (54, 52): 0.5051001633268003, (54, 53): 0.5051001633268003, (54, 54): 0.5051001633268003, (54, 55): 0.5051001633268003, (54, 56): 0.0, (54, 57): 0.0, (54, 58): 0.0, (54, 59): 0.0, (54, 60): 0.0, (54, 61): 0.0, (54, 62): 0.0, (54, 63): 0.0, (54, 64): 0.0, (54, 65): 0.0, (54, 66): 0.0, (54, 67): 0.0, (54, 68): 0.0, (54, 69): 0.0, (55, 1): 0.0, (55, 2): 0.0, (55, 3): 0.0, (55, 4): 0.0, (55, 5): 0.0, (55, 6): 0.0, (55, 7): 0.0, (55, 8): 0.0, (55, 9): 0.0, (55, 10): 0.0, (55, 11): 0.0, (55, 12): 0.0, (55, 13): 0.0, (55, 14): 0.0, (55, 15): 0.0, (55, 16): 0.0, (55, 17): 0.0, (55, 18): 0.0, (55, 19): 0.0, (55, 20): 0.0, (55, 21): 0.0, (55, 22): 0.0, (55, 23): 0.0, (55, 24): 0.0, (55, 25): 0.0, (55, 26): 0.0, (55, 27): 0.0, (55, 28): 0.0, (55, 29): 0.0, (55, 30): 0.0, (55, 31): 0.0, (55, 32): 0.0, (55, 33): 0.0, (55, 34): 0.0, (55, 35): 0.0, (55, 36): 0.0, (55, 37): 0.0, (55, 38): 0.0, (55, 39): 0.0, (55, 40): 0.0, (55, 41): 0.0, (55, 42): 0.0, (55, 43): 0.0, (55, 44): 0.0, (55, 45): 0.0, (55, 46): 0.0, (55, 47): 0.0, (55, 48): 0.0, (55, 49): 0.0, (55, 50): 0.0, (55, 51): 0.0, (55, 52): 0.0, (55, 53): 0.0, (55, 54): 0.0, (55, 55): 0.0, (55, 56): 0.0, (55, 57): 0.0, (55, 58): 0.0, (55, 59): 0.0, (55, 60): 0.0, (55, 61): 0.0, (55, 62): 0.0, (55, 63): 0.0, (55, 64): 0.0, (55, 65): 0.0, (55, 66): 0.5051001633268003, (55, 67): 0.5051001633268003, (55, 68): 0.5051001633268003, (55, 69): 0.5051001633268003, (56, 1): 0.0, (56, 2): 0.0, (56, 3): 0.0, (56, 4): 0.0, (56, 5): 0.0, (56, 6): 0.0, (56, 7): 0.0, (56, 8): 0.0, (56, 9): 0.0, (56, 10): 0.0, (56, 11): 0.0, (56, 12): 0.0, (56, 13): 0.0, (56, 14): 0.0, (56, 15): 0.0, (56, 16): 0.0, (56, 17): 0.0, (56, 18): 0.0, (56, 19): 0.0, (56, 20): 0.0, (56, 21): 0.0, (56, 22): 0.0, (56, 23): 0.0, (56, 24): 0.0, (56, 25): 0.0, (56, 26): 0.0, (56, 27): 0.0, (56, 28): 0.0, (56, 29): 0.0, (56, 30): 0.0, (56, 31): 0.0, (56, 32): 0.0, (56, 33): 0.0, (56, 34): 0.0, (56, 35): 0.0, (56, 36): 0.0, (56, 37): 0.0, (56, 38): 0.0, (56, 39): 0.0, (56, 40): 0.0, (56, 41): 0.0, (56, 42): 0.0, (56, 43): 0.0, (56, 44): 0.0, (56, 45): 0.0, (56, 46): 0.0, (56, 47): 0.0, (56, 48): 0.0, (56, 49): 0.0, (56, 50): 0.0, (56, 51): 0.0, (56, 52): 0.0, (56, 53): 0.0, (56, 54): 0.5051001633268003, (56, 55): 0.5051001633268003, (56, 56): 0.5051001633268003, (56, 57): 0.5051001633268003, (56, 58): 0.5051001633268003, (56, 59): 0.5051001633268003, (56, 60): 0.5051001633268003, (56, 61): 0.5051001633268003, (56, 62): 0.5051001633268003, (56, 63): 0.0, (56, 64): 0.0, (56, 65): 0.0, (56, 66): 0.0, (56, 67): 0.0, (56, 68): 0.0, (56, 69): 0.0, (58, 1): 0.0, (58, 2): 0.0, (58, 3): 0.0, (58, 4): 0.0, (58, 5): 0.0, (58, 6): 0.0, (58, 7): 0.0, (58, 8): 0.0, (58, 9): 0.0, (58, 10): 0.0, (58, 11): 0.0, (58, 12): 0.0, (58, 13): 0.0, (58, 14): 0.0, (58, 15): 0.0, (58, 16): 0.0, (58, 17): 0.0, (58, 18): 0.0, (58, 19): 0.0, (58, 20): 0.0, (58, 21): 0.0, (58, 22): 0.0, (58, 23): 0.0, (58, 24): 0.0, (58, 25): 0.0, (58, 26): 0.0, (58, 27): 0.0, (58, 28): 0.0, (58, 29): 0.0, (58, 30): 0.0, (58, 31): 0.0, (58, 32): 0.0, (58, 33): 0.0, (58, 34): 0.0, (58, 35): 0.0, (58, 36): 0.0, (58, 37): 0.0, (58, 38): 0.0, (58, 39): 0.0, (58, 40): 0.0, (58, 41): 0.0, (58, 42): 0.0, (58, 43): 0.0, (58, 44): 0.0, (58, 45): 0.0, (58, 46): 0.0, (58, 47): 0.0, (58, 48): 0.0, (58, 49): 0.0, (58, 50): 0.0, (58, 51): 0.0, (58, 52): 0.5051001633268003, (58, 53): 0.5051001633268003, (58, 54): 0.5051001633268003, (58, 55): 0.5051001633268003, (58, 56): 0.5051001633268003, (58, 57): 0.5051001633268003, (58, 58): 0.5051001633268003, (58, 59): 0.5051001633268003, (58, 60): 0.5051001633268003, (58, 61): 0.5051001633268003, (58, 62): 0.5051001633268003, (58, 63): 0.0, (58, 64): 0.0, (58, 65): 0.0, (58, 66): 0.0, (58, 67): 0.0, (58, 68): 0.0, (58, 69): 0.0, (61, 1): 0.0, (61, 2): 0.0, (61, 3): 0.0, (61, 4): 0.0, (61, 5): 0.0, (61, 6): 0.0, (61, 7): 0.0, (61, 8): 0.0, (61, 9): 0.0, (61, 10): 0.0, (61, 11): 0.0, (61, 12): 0.0, (61, 13): 0.0, (61, 14): 0.0, (61, 15): 0.0, (61, 16): 0.0, (61, 17): 0.0, (61, 18): 0.0, (61, 19): 0.0, (61, 20): 0.0, (61, 21): 0.0, (61, 22): 0.0, (61, 23): 0.0, (61, 24): 0.0, (61, 25): 0.0, (61, 26): 0.0, (61, 27): 0.0, (61, 28): 0.0, (61, 29): 0.0, (61, 30): 0.0, (61, 31): 0.0, (61, 32): 0.0, (61, 33): 0.0, (61, 34): 0.5051001633268003, (61, 35): 0.5051001633268003, (61, 36): 0.5051001633268003, (61, 37): 0.5051001633268003, (61, 38): 0.5051001633268003, (61, 39): 0.5051001633268003, (61, 40): 0.5051001633268003, (61, 41): 0.5051001633268003, (61, 42): 0.5051001633268003, (61, 43): 0.0, (61, 44): 0.0, (61, 45): 0.0, (61, 46): 0.0, (61, 47): 0.0, (61, 48): 0.0, (61, 49): 0.0, (61, 50): 0.0, (61, 51): 0.0, (61, 52): 0.0, (61, 53): 0.0, (61, 54): 0.0, (61, 55): 0.0, (61, 56): 0.0, (61, 57): 0.0, (61, 58): 0.0, (61, 59): 0.0, (61, 60): 0.0, (61, 61): 0.0, (61, 62): 0.0, (61, 63): 0.0, (61, 64): 0.0, (61, 65): 0.0, (61, 66): 0.0, (61, 67): 0.0, (61, 68): 0.0, (61, 69): 0.0, (62, 1): 0.0, (62, 2): 0.0, (62, 3): 0.0, (62, 4): 0.0, (62, 5): 0.0, (62, 6): 0.0, (62, 7): 0.0, (62, 8): 0.0, (62, 9): 0.0, (62, 10): 0.0, (62, 11): 0.0, (62, 12): 0.0, (62, 13): 0.0, (62, 14): 0.0, (62, 15): 0.0, (62, 16): 0.0, (62, 17): 0.0, (62, 18): 0.0, (62, 19): 0.0, (62, 20): 0.0, (62, 21): 0.0, (62, 22): 0.0, (62, 23): 0.0, (62, 24): 0.0, (62, 25): 0.0, (62, 26): 0.0, (62, 27): 0.0, (62, 28): 0.0, (62, 29): 0.0, (62, 30): 0.0, (62, 31): 0.0, (62, 32): 0.0, (62, 33): 0.0, (62, 34): 0.0, (62, 35): 0.0, (62, 36): 0.0, (62, 37): 0.0, (62, 38): 0.0, (62, 39): 0.0, (62, 40): 0.0, (62, 41): 0.0, (62, 42): 0.0, (62, 43): 0.0, (62, 44): 0.0, (62, 45): 0.0, (62, 46): 0.0, (62, 47): 0.5051001633268003, (62, 48): 0.5051001633268003, (62, 49): 0.5051001633268003, (62, 50): 0.5051001633268003, (62, 51): 0.5051001633268003, (62, 52): 0.5051001633268003, (62, 53): 0.5051001633268003, (62, 54): 0.5051001633268003, (62, 55): 0.0, (62, 56): 0.0, (62, 57): 0.0, (62, 58): 0.0, (62, 59): 0.0, (62, 60): 0.0, (62, 61): 0.0, (62, 62): 0.0, (62, 63): 0.0, (62, 64): 0.0, (62, 65): 0.0, (62, 66): 0.0, (62, 67): 0.0, (62, 68): 0.0, (62, 69): 0.0, (64, 1): 0.0, (64, 2): 0.0, (64, 3): 0.0, (64, 4): 0.0, (64, 5): 0.0, (64, 6): 0.0, (64, 7): 0.0, (64, 8): 0.0, (64, 9): 0.0, (64, 10): 0.0, (64, 11): 0.0, (64, 12): 0.0, (64, 13): 0.0, (64, 14): 0.0, (64, 15): 0.0, (64, 16): 0.0, (64, 17): 0.0, (64, 18): 0.0, (64, 19): 0.0, (64, 20): 0.0, (64, 21): 0.0, (64, 22): 0.0, (64, 23): 0.0, (64, 24): 0.0, (64, 25): 0.0, (64, 26): 0.0, (64, 27): 0.0, (64, 28): 0.0, (64, 29): 0.0, (64, 30): 0.0, (64, 31): 0.0, (64, 32): 0.0, (64, 33): 0.0, (64, 34): 0.0, (64, 35): 0.0, (64, 36): 0.0, (64, 37): 0.0, (64, 38): 0.0, (64, 39): 0.0, (64, 40): 0.0, (64, 41): 0.0, (64, 42): 0.0, (64, 43): 0.0, (64, 44): 0.5051001633268003, (64, 45): 0.5051001633268003, (64, 46): 0.5051001633268003, (64, 47): 0.5051001633268003, (64, 48): 0.5051001633268003, (64, 49): 0.5051001633268003, (64, 50): 0.0, (64, 51): 0.0, (64, 52): 0.0, (64, 53): 0.0, (64, 54): 0.0, (64, 55): 0.0, (64, 56): 0.0, (64, 57): 0.0, (64, 58): 0.0, (64, 59): 0.0, (64, 60): 0.0, (64, 61): 0.0, (64, 62): 0.0, (64, 63): 0.0, (64, 64): 0.0, (64, 65): 0.0, (64, 66): 0.0, (64, 67): 0.0, (64, 68): 0.0, (64, 69): 0.0, (66, 1): 0.0, (66, 2): 0.0, (66, 3): 0.0, (66, 4): 0.0, (66, 5): 0.0, (66, 6): 0.0, (66, 7): 0.0, (66, 8): 0.0, (66, 9): 0.0, (66, 10): 0.0, (66, 11): 0.0, (66, 12): 0.0, (66, 13): 0.0, (66, 14): 0.0, (66, 15): 0.0, (66, 16): 0.0, (66, 17): 0.0, (66, 18): 0.0, (66, 19): 0.0, (66, 20): 0.0, (66, 21): 0.0, (66, 22): 0.0, (66, 23): 0.0, (66, 24): 0.0, (66, 25): 0.0, (66, 26): 0.0, (66, 27): 0.0, (66, 28): 0.0, (66, 29): 0.0, (66, 30): 0.0, (66, 31): 0.0, (66, 32): 0.0, (66, 33): 0.0, (66, 34): 0.0, (66, 35): 0.0, (66, 36): 0.0, (66, 37): 0.0, (66, 38): 0.0, (66, 39): 0.0, (66, 40): 0.0, (66, 41): 0.0, (66, 42): 0.0, (66, 43): 0.0, (66, 44): 0.0, (66, 45): 0.0, (66, 46): 0.0, (66, 47): 0.0, (66, 48): 0.0, (66, 49): 0.0, (66, 50): 0.0, (66, 51): 0.0, (66, 52): 0.0, (66, 53): 0.5051001633268003, (66, 54): 0.5051001633268003, (66, 55): 0.5051001633268003, (66, 56): 0.5051001633268003, (66, 57): 0.5051001633268003, (66, 58): 0.5051001633268003, (66, 59): 0.5051001633268003, (66, 60): 0.5051001633268003, (66, 61): 0.0, (66, 62): 0.0, (66, 63): 0.0, (66, 64): 0.0, (66, 65): 0.0, (66, 66): 0.0, (66, 67): 0.0, (66, 68): 0.0, (66, 69): 0.0, (69, 1): 0.0, (69, 2): 0.0, (69, 3): 0.0, (69, 4): 0.0, (69, 5): 0.0, (69, 6): 0.0, (69, 7): 0.0, (69, 8): 0.0, (69, 9): 0.0, (69, 10): 0.0, (69, 11): 0.0, (69, 12): 0.0, (69, 13): 0.0, (69, 14): 0.0, (69, 15): 0.0, (69, 16): 0.0, (69, 17): 0.0, (69, 18): 0.0, (69, 19): 0.0, (69, 20): 0.0, (69, 21): 0.0, (69, 22): 0.0, (69, 23): 0.0, (69, 24): 0.0, (69, 25): 0.0, (69, 26): 0.0, (69, 27): 0.0, (69, 28): 0.0, (69, 29): 0.0, (69, 30): 0.0, (69, 31): 0.0, (69, 32): 0.0, (69, 33): 0.0, (69, 34): 0.0, (69, 35): 0.0, (69, 36): 0.0, (69, 37): 0.0, (69, 38): 0.0, (69, 39): 0.0, (69, 40): 0.0, (69, 41): 0.0, (69, 42): 0.0, (69, 43): 0.0, (69, 44): 0.0, (69, 45): 0.0, (69, 46): 0.5051001633268003, (69, 47): 0.5051001633268003, (69, 48): 0.5051001633268003, (69, 49): 0.5051001633268003, (69, 50): 0.5051001633268003, (69, 51): 0.5051001633268003, (69, 52): 0.0, (69, 53): 0.0, (69, 54): 0.0, (69, 55): 0.0, (69, 56): 0.0, (69, 57): 0.0, (69, 58): 0.0, (69, 59): 0.0, (69, 60): 0.0, (69, 61): 0.0, (69, 62): 0.0, (69, 63): 0.0, (69, 64): 0.0, (69, 65): 0.0, (69, 66): 0.0, (69, 67): 0.0, (69, 68): 0.0, (69, 69): 0.0, (71, 1): 0.0, (71, 2): 0.0, (71, 3): 0.0, (71, 4): 0.0, (71, 5): 0.0, (71, 6): 0.0, (71, 7): 0.0, (71, 8): 0.0, (71, 9): 0.0, (71, 10): 0.0, (71, 11): 0.0, (71, 12): 0.0, (71, 13): 0.0, (71, 14): 0.0, (71, 15): 0.0, (71, 16): 0.0, (71, 17): 0.0, (71, 18): 0.0, (71, 19): 0.0, (71, 20): 0.0, (71, 21): 0.0, (71, 22): 0.0, (71, 23): 0.0, (71, 24): 0.0, (71, 25): 0.0, (71, 26): 0.0, (71, 27): 0.0, (71, 28): 0.0, (71, 29): 0.0, (71, 30): 0.0, (71, 31): 0.0, (71, 32): 0.0, (71, 33): 0.0, (71, 34): 0.0, (71, 35): 0.0, (71, 36): 0.0, (71, 37): 0.0, (71, 38): 0.0, (71, 39): 0.0, (71, 40): 0.0, (71, 41): 0.0, (71, 42): 0.0, (71, 43): 0.0, (71, 44): 0.0, (71, 45): 0.0, (71, 46): 0.0, (71, 47): 0.0, (71, 48): 0.0, (71, 49): 0.0, (71, 50): 0.0, (71, 51): 0.5051001633268003, (71, 52): 0.5051001633268003, (71, 53): 0.5051001633268003, (71, 54): 0.5051001633268003, (71, 55): 0.5051001633268003, (71, 56): 0.5051001633268003, (71, 57): 0.5051001633268003, (71, 58): 0.5051001633268003, (71, 59): 0.5051001633268003, (71, 60): 0.0, (71, 61): 0.0, (71, 62): 0.0, (71, 63): 0.0, (71, 64): 0.0, (71, 65): 0.0, (71, 66): 0.0, (71, 67): 0.0, (71, 68): 0.0, (71, 69): 0.0, (76, 1): 0.0, (76, 2): 0.0, (76, 3): 0.0, (76, 4): 0.0, (76, 5): 0.0, (76, 6): 0.0, (76, 7): 0.0, (76, 8): 0.0, (76, 9): 0.0, (76, 10): 0.0, (76, 11): 0.0, (76, 12): 0.0, (76, 13): 0.0, (76, 14): 0.0, (76, 15): 0.0, (76, 16): 0.0, (76, 17): 0.0, (76, 18): 0.0, (76, 19): 0.0, (76, 20): 0.0, (76, 21): 0.0, (76, 22): 0.0, (76, 23): 0.0, (76, 24): 0.0, (76, 25): 0.0, (76, 26): 0.0, (76, 27): 0.0, (76, 28): 0.0, (76, 29): 0.0, (76, 30): 0.0, (76, 31): 0.0, (76, 32): 0.0, (76, 33): 0.0, (76, 34): 0.0, (76, 35): 0.0, (76, 36): 0.0, (76, 37): 0.0, (76, 38): 0.0, (76, 39): 0.0, (76, 40): 0.0, (76, 41): 0.0, (76, 42): 0.0, (76, 43): 0.0, (76, 44): 0.0, (76, 45): 0.0, (76, 46): 0.0, (76, 47): 0.0, (76, 48): 0.0, (76, 49): 0.0, (76, 50): 0.0, (76, 51): 0.0, (76, 52): 0.0, (76, 53): 0.0, (76, 54): 0.0, (76, 55): 0.0, (76, 56): 0.5051001633268003, (76, 57): 0.5051001633268003, (76, 58): 0.5051001633268003, (76, 59): 0.5051001633268003, (76, 60): 0.5051001633268003, (76, 61): 0.0, (76, 62): 0.0, (76, 63): 0.0, (76, 64): 0.0, (76, 65): 0.0, (76, 66): 0.0, (76, 67): 0.0, (76, 68): 0.0, (76, 69): 0.0, (77, 1): 0.0, (77, 2): 0.0, (77, 3): 0.0, (77, 4): 0.0, (77, 5): 0.0, (77, 6): 0.0, (77, 7): 0.0, (77, 8): 0.0, (77, 9): 0.0, (77, 10): 0.0, (77, 11): 0.0, (77, 12): 0.0, (77, 13): 0.0, (77, 14): 0.0, (77, 15): 0.0, (77, 16): 0.0, (77, 17): 0.0, (77, 18): 0.0, (77, 19): 0.0, (77, 20): 0.0, (77, 21): 0.0, (77, 22): 0.0, (77, 23): 0.0, (77, 24): 0.0, (77, 25): 0.0, (77, 26): 0.0, (77, 27): 0.0, (77, 28): 0.0, (77, 29): 0.0, (77, 30): 0.0, (77, 31): 0.0, (77, 32): 0.0, (77, 33): 0.0, (77, 34): 0.0, (77, 35): 0.0, (77, 36): 0.5051001633268003, (77, 37): 0.5051001633268003, (77, 38): 0.5051001633268003, (77, 39): 0.5051001633268003, (77, 40): 0.5051001633268003, (77, 41): 0.5051001633268003, (77, 42): 0.5051001633268003, (77, 43): 0.5051001633268003, (77, 44): 0.5051001633268003, (77, 45): 0.0, (77, 46): 0.0, (77, 47): 0.0, (77, 48): 0.0, (77, 49): 0.0, (77, 50): 0.0, (77, 51): 0.0, (77, 52): 0.0, (77, 53): 0.0, (77, 54): 0.0, (77, 55): 0.0, (77, 56): 0.0, (77, 57): 0.0, (77, 58): 0.0, (77, 59): 0.0, (77, 60): 0.0, (77, 61): 0.0, (77, 62): 0.0, (77, 63): 0.0, (77, 64): 0.0, (77, 65): 0.0, (77, 66): 0.0, (77, 67): 0.0, (77, 68): 0.0, (77, 69): 0.0, (78, 1): 0.0, (78, 2): 0.0, (78, 3): 0.0, (78, 4): 0.0, (78, 5): 0.0, (78, 6): 0.0, (78, 7): 0.0, (78, 8): 0.0, (78, 9): 0.0, (78, 10): 0.0, (78, 11): 0.0, (78, 12): 0.0, (78, 13): 0.0, (78, 14): 0.0, (78, 15): 0.0, (78, 16): 0.0, (78, 17): 0.0, (78, 18): 0.0, (78, 19): 0.0, (78, 20): 0.0, (78, 21): 0.0, (78, 22): 0.0, (78, 23): 0.0, (78, 24): 0.0, (78, 25): 0.0, (78, 26): 0.0, (78, 27): 0.0, (78, 28): 0.0, (78, 29): 0.0, (78, 30): 0.0, (78, 31): 0.0, (78, 32): 0.0, (78, 33): 0.0, (78, 34): 0.0, (78, 35): 0.0, (78, 36): 0.0, (78, 37): 0.0, (78, 38): 0.0, (78, 39): 0.5051001633268003, (78, 40): 0.5051001633268003, (78, 41): 0.5051001633268003, (78, 42): 0.5051001633268003, (78, 43): 0.5051001633268003, (78, 44): 0.0, (78, 45): 0.0, (78, 46): 0.0, (78, 47): 0.0, (78, 48): 0.0, (78, 49): 0.0, (78, 50): 0.0, (78, 51): 0.0, (78, 52): 0.0, (78</t>
+  </si>
+  <si>
+    <t>{(3, 1): 0.0, (3, 2): 0.0, (3, 3): 0.0, (3, 4): 0.0, (3, 5): 0.0, (3, 6): 0.0, (3, 7): 0.0, (3, 8): 0.0, (3, 9): 0.0, (3, 10): 0.0, (3, 11): 0.0, (3, 12): 0.0, (3, 13): 0.0, (3, 14): 0.0, (3, 15): 0.0, (3, 16): 0.0, (3, 17): 0.0, (3, 18): 0.0, (3, 19): 0.0, (3, 20): 0.0, (3, 21): 0.0, (3, 22): 0.0, (3, 23): 0.0, (3, 24): 0.0, (3, 25): 0.0, (3, 26): 0.0, (3, 27): 0.0, (3, 28): 0.0, (3, 29): 0.0, (3, 30): 0.0, (3, 31): 0.0, (3, 32): 0.0, (3, 33): 0.0, (3, 34): 0.0, (3, 35): 0.0, (3, 36): 0.0, (3, 37): 0.0, (3, 38): 0.0, (3, 39): 0.0, (3, 40): 0.0, (3, 41): 0.0, (3, 42): 0.0, (3, 43): 0.0, (3, 44): 0.0, (3, 45): 1.0, (3, 46): 2.0, (3, 47): 3.0, (3, 48): 4.0, (3, 49): 5.0, (3, 50): 6.0, (3, 51): 6.0, (3, 52): 7.0, (3, 53): 8.0, (3, 54): 9.0, (3, 55): 10.0, (3, 56): 11.0, (3, 57): 12.0, (3, 58): 12.0, (3, 59): 13.0, (3, 60): 13.0, (3, 61): 13.0, (3, 62): 13.0, (3, 63): 13.0, (3, 64): 13.0, (3, 65): 13.0, (3, 66): 13.0, (3, 67): 13.0, (3, 68): 13.0, (3, 69): 13.0, (4, 1): 0.0, (4, 2): 0.0, (4, 3): 0.0, (4, 4): 0.0, (4, 5): 0.0, (4, 6): 0.0, (4, 7): 0.0, (4, 8): 0.0, (4, 9): 0.0, (4, 10): 0.0, (4, 11): 0.0, (4, 12): 0.0, (4, 13): 0.0, (4, 14): 0.0, (4, 15): 0.0, (4, 16): 0.0, (4, 17): 0.0, (4, 18): 0.0, (4, 19): 0.0, (4, 20): 0.0, (4, 21): 0.0, (4, 22): 0.0, (4, 23): 0.0, (4, 24): 0.0, (4, 25): 0.0, (4, 26): 0.0, (4, 27): 0.0, (4, 28): 0.0, (4, 29): 0.0, (4, 30): 0.0, (4, 31): 0.0, (4, 32): 0.0, (4, 33): 0.0, (4, 34): 0.0, (4, 35): 0.0, (4, 36): 0.0, (4, 37): 0.0, (4, 38): 0.0, (4, 39): 0.0, (4, 40): 0.0, (4, 41): 0.0, (4, 42): 0.0, (4, 43): 0.0, (4, 44): 0.0, (4, 45): 0.0, (4, 46): 0.0, (4, 47): 0.0, (4, 48): 0.0, (4, 49): 0.0, (4, 50): 1.0, (4, 51): 1.0, (4, 52): 2.0, (4, 53): 3.0, (4, 54): 4.0, (4, 55): 5.0, (4, 56): 6.0, (4, 57): 7.0, (4, 58): 7.0, (4, 59): 8.0, (4, 60): 9.0, (4, 61): 10.0, (4, 62): 11.0, (4, 63): 12.0, (4, 64): 12.0, (4, 65): 12.0, (4, 66): 12.0, (4, 67): 12.0, (4, 68): 12.0, (4, 69): 12.0, (8, 1): 0.0, (8, 2): 0.0, (8, 3): 0.0, (8, 4): 0.0, (8, 5): 0.0, (8, 6): 0.0, (8, 7): 0.0, (8, 8): 0.0, (8, 9): 0.0, (8, 10): 0.0, (8, 11): 0.0, (8, 12): 0.0, (8, 13): 0.0, (8, 14): 0.0, (8, 15): 0.0, (8, 16): 0.0, (8, 17): 0.0, (8, 18): 0.0, (8, 19): 0.0, (8, 20): 0.0, (8, 21): 0.0, (8, 22): 0.0, (8, 23): 0.0, (8, 24): 0.0, (8, 25): 0.0, (8, 26): 0.0, (8, 27): 0.0, (8, 28): 0.0, (8, 29): 0.0, (8, 30): 0.0, (8, 31): 0.0, (8, 32): 0.0, (8, 33): 0.0, (8, 34): 0.0, (8, 35): 0.0, (8, 36): 0.0, (8, 37): 0.0, (8, 38): 0.0, (8, 39): 1.0, (8, 40): 2.0, (8, 41): 3.0, (8, 42): 4.0, (8, 43): 5.0, (8, 44): 5.0, (8, 45): 5.0, (8, 46): 6.0, (8, 47): 7.0, (8, 48): 8.0, (8, 49): 8.0, (8, 50): 8.0, (8, 51): 8.0, (8, 52): 8.0, (8, 53): 8.0, (8, 54): 8.0, (8, 55): 8.0, (8, 56): 8.0, (8, 57): 8.0, (8, 58): 8.0, (8, 59): 8.0, (8, 60): 8.0, (8, 61): 8.0, (8, 62): 8.0, (8, 63): 8.0, (8, 64): 8.0, (8, 65): 8.0, (8, 66): 8.0, (8, 67): 8.0, (8, 68): 8.0, (8, 69): 8.0, (9, 1): 0.0, (9, 2): 0.0, (9, 3): 0.0, (9, 4): 0.0, (9, 5): 0.0, (9, 6): 0.0, (9, 7): 0.0, (9, 8): 0.0, (9, 9): 0.0, (9, 10): 0.0, (9, 11): 0.0, (9, 12): 0.0, (9, 13): 0.0, (9, 14): 0.0, (9, 15): 0.0, (9, 16): 0.0, (9, 17): 0.0, (9, 18): 0.0, (9, 19): 0.0, (9, 20): 0.0, (9, 21): 0.0, (9, 22): 0.0, (9, 23): 0.0, (9, 24): 0.0, (9, 25): 0.0, (9, 26): 0.0, (9, 27): 0.0, (9, 28): 0.0, (9, 29): 0.0, (9, 30): 0.0, (9, 31): 0.0, (9, 32): 0.0, (9, 33): 0.0, (9, 34): 0.0, (9, 35): 0.0, (9, 36): 0.0, (9, 37): 0.0, (9, 38): 0.0, (9, 39): 0.0, (9, 40): 0.0, (9, 41): 0.0, (9, 42): 0.0, (9, 43): 0.0, (9, 44): 0.0, (9, 45): 0.0, (9, 46): 0.0, (9, 47): 0.0, (9, 48): 0.0, (9, 49): 0.0, (9, 50): 0.0, (9, 51): 0.0, (9, 52): 0.0, (9, 53): 0.0, (9, 54): 0.0, (9, 55): 0.0, (9, 56): 0.0, (9, 57): 0.0, (9, 58): 0.0, (9, 59): 0.0, (9, 60): 0.0, (9, 61): 0.0, (9, 62): 0.0, (9, 63): 0.0, (9, 64): 1.0, (9, 65): 1.0, (9, 66): 1.0, (9, 67): 1.0, (9, 68): 2.0, (9, 69): 3.0, (10, 1): 0.0, (10, 2): 0.0, (10, 3): 0.0, (10, 4): 0.0, (10, 5): 0.0, (10, 6): 0.0, (10, 7): 0.0, (10, 8): 0.0, (10, 9): 0.0, (10, 10): 0.0, (10, 11): 0.0, (10, 12): 0.0, (10, 13): 0.0, (10, 14): 0.0, (10, 15): 0.0, (10, 16): 0.0, (10, 17): 0.0, (10, 18): 0.0, (10, 19): 0.0, (10, 20): 0.0, (10, 21): 0.0, (10, 22): 0.0, (10, 23): 0.0, (10, 24): 0.0, (10, 25): 0.0, (10, 26): 0.0, (10, 27): 0.0, (10, 28): 0.0, (10, 29): 0.0, (10, 30): 0.0, (10, 31): 0.0, (10, 32): 0.0, (10, 33): 0.0, (10, 34): 0.0, (10, 35): 0.0, (10, 36): 0.0, (10, 37): 0.0, (10, 38): 0.0, (10, 39): 0.0, (10, 40): 0.0, (10, 41): 0.0, (10, 42): 0.0, (10, 43): 1.0, (10, 44): 2.0, (10, 45): 3.0, (10, 46): 4.0, (10, 47): 5.0, (10, 48): 6.0, (10, 49): 6.0, (10, 50): 7.0, (10, 51): 8.0, (10, 52): 9.0, (10, 53): 9.0, (10, 54): 10.0, (10, 55): 10.0, (10, 56): 10.0, (10, 57): 10.0, (10, 58): 10.0, (10, 59): 10.0, (10, 60): 10.0, (10, 61): 10.0, (10, 62): 10.0, (10, 63): 10.0, (10, 64): 10.0, (10, 65): 10.0, (10, 66): 10.0, (10, 67): 10.0, (10, 68): 10.0, (10, 69): 10.0, (11, 1): 0.0, (11, 2): 0.0, (11, 3): 0.0, (11, 4): 0.0, (11, 5): 0.0, (11, 6): 0.0, (11, 7): 0.0, (11, 8): 0.0, (11, 9): 0.0, (11, 10): 0.0, (11, 11): 0.0, (11, 12): 0.0, (11, 13): 0.0, (11, 14): 0.0, (11, 15): 0.0, (11, 16): 0.0, (11, 17): 0.0, (11, 18): 0.0, (11, 19): 0.0, (11, 20): 0.0, (11, 21): 0.0, (11, 22): 0.0, (11, 23): 0.0, (11, 24): 0.0, (11, 25): 0.0, (11, 26): 0.0, (11, 27): 0.0, (11, 28): 0.0, (11, 29): 0.0, (11, 30): 0.0, (11, 31): 0.0, (11, 32): 0.0, (11, 33): 0.0, (11, 34): 0.0, (11, 35): 0.0, (11, 36): 0.0, (11, 37): 0.0, (11, 38): 0.0, (11, 39): 0.0, (11, 40): 0.0, (11, 41): 0.0, (11, 42): 0.0, (11, 43): 0.0, (11, 44): 0.0, (11, 45): 0.0, (11, 46): 0.0, (11, 47): 0.0, (11, 48): 0.0, (11, 49): 0.0, (11, 50): 0.0, (11, 51): 0.0, (11, 52): 0.0, (11, 53): 0.0, (11, 54): 0.0, (11, 55): 0.0, (11, 56): 0.0, (11, 57): 1.0, (11, 58): 1.0, (11, 59): 1.0, (11, 60): 2.0, (11, 61): 3.0, (11, 62): 4.0, (11, 63): 4.0, (11, 64): 4.0, (11, 65): 4.0, (11, 66): 4.0, (11, 67): 4.0, (11, 68): 4.0, (11, 69): 4.0, (12, 1): 0.0, (12, 2): 0.0, (12, 3): 0.0, (12, 4): 0.0, (12, 5): 0.0, (12, 6): 0.0, (12, 7): 0.0, (12, 8): 0.0, (12, 9): 0.0, (12, 10): 0.0, (12, 11): 0.0, (12, 12): 0.0, (12, 13): 0.0, (12, 14): 0.0, (12, 15): 0.0, (12, 16): 0.0, (12, 17): 0.0, (12, 18): 0.0, (12, 19): 0.0, (12, 20): 0.0, (12, 21): 0.0, (12, 22): 0.0, (12, 23): 0.0, (12, 24): 0.0, (12, 25): 0.0, (12, 26): 0.0, (12, 27): 0.0, (12, 28): 0.0, (12, 29): 0.0, (12, 30): 0.0, (12, 31): 0.0, (12, 32): 0.0, (12, 33): 0.0, (12, 34): 1.0, (12, 35): 2.0, (12, 36): 3.0, (12, 37): 4.0, (12, 38): 4.0, (12, 39): 5.0, (12, 40): 5.0, (12, 41): 6.0, (12, 42): 6.0, (12, 43): 6.0, (12, 44): 7.0, (12, 45): 7.0, (12, 46): 7.0, (12, 47): 7.0, (12, 48): 7.0, (12, 49): 7.0, (12, 50): 7.0, (12, 51): 7.0, (12, 52): 7.0, (12, 53): 7.0, (12, 54): 7.0, (12, 55): 7.0, (12, 56): 7.0, (12, 57): 7.0, (12, 58): 7.0, (12, 59): 7.0, (12, 60): 7.0, (12, 61): 7.0, (12, 62): 7.0, (12, 63): 7.0, (12, 64): 7.0, (12, 65): 7.0, (12, 66): 7.0, (12, 67): 7.0, (12, 68): 7.0, (12, 69): 7.0, (21, 1): 0.0, (21, 2): 0.0, (21, 3): 0.0, (21, 4): 0.0, (21, 5): 0.0, (21, 6): 0.0, (21, 7): 0.0, (21, 8): 0.0, (21, 9): 0.0, (21, 10): 0.0, (21, 11): 0.0, (21, 12): 0.0, (21, 13): 0.0, (21, 14): 0.0, (21, 15): 0.0, (21, 16): 0.0, (21, 17): 0.0, (21, 18): 0.0, (21, 19): 0.0, (21, 20): 0.0, (21, 21): 0.0, (21, 22): 0.0, (21, 23): 0.0, (21, 24): 0.0, (21, 25): 0.0, (21, 26): 0.0, (21, 27): 0.0, (21, 28): 0.0, (21, 29): 0.0, (21, 30): 0.0, (21, 31): 0.0, (21, 32): 0.0, (21, 33): 0.0, (21, 34): 0.0, (21, 35): 0.0, (21, 36): 0.0, (21, 37): 0.0, (21, 38): 0.0, (21, 39): 0.0, (21, 40): 0.0, (21, 41): 0.0, (21, 42): 0.0, (21, 43): 0.0, (21, 44): 0.0, (21, 45): 1.0, (21, 46): 2.0, (21, 47): 3.0, (21, 48): 4.0, (21, 49): 5.0, (21, 50): 5.0, (21, 51): 5.0, (21, 52): 6.0, (21, 53): 6.0, (21, 54): 6.0, (21, 55): 6.0, (21, 56): 6.0, (21, 57): 6.0, (21, 58): 6.0, (21, 59): 6.0, (21, 60): 6.0, (21, 61): 6.0, (21, 62): 6.0, (21, 63): 6.0, (21, 64): 6.0, (21, 65): 6.0, (21, 66): 6.0, (21, 67): 6.0, (21, 68): 6.0, (21, 69): 6.0, (23, 1): 0.0, (23, 2): 0.0, (23, 3): 0.0, (23, 4): 0.0, (23, 5): 0.0, (23, 6): 0.0, (23, 7): 0.0, (23, 8): 0.0, (23, 9): 0.0, (23, 10): 0.0, (23, 11): 0.0, (23, 12): 0.0, (23, 13): 0.0, (23, 14): 0.0, (23, 15): 0.0, (23, 16): 0.0, (23, 17): 0.0, (23, 18): 0.0, (23, 19): 0.0, (23, 20): 0.0, (23, 21): 0.0, (23, 22): 0.0, (23, 23): 0.0, (23, 24): 0.0, (23, 25): 0.0, (23, 26): 0.0, (23, 27): 0.0, (23, 28): 0.0, (23, 29): 0.0, (23, 30): 0.0, (23, 31): 0.0, (23, 32): 0.0, (23, 33): 1.0, (23, 34): 2.0, (23, 35): 3.0, (23, 36): 3.0, (23, 37): 3.0, (23, 38): 4.0, (23, 39): 5.0, (23, 40): 6.0, (23, 41): 7.0, (23, 42): 8.0, (23, 43): 8.0, (23, 44): 8.0, (23, 45): 8.0, (23, 46): 8.0, (23, 47): 8.0, (23, 48): 8.0, (23, 49): 8.0, (23, 50): 8.0, (23, 51): 8.0, (23, 52): 8.0, (23, 53): 8.0, (23, 54): 8.0, (23, 55): 8.0, (23, 56): 8.0, (23, 57): 8.0, (23, 58): 8.0, (23, 59): 8.0, (23, 60): 8.0, (23, 61): 8.0, (23, 62): 8.0, (23, 63): 8.0, (23, 64): 8.0, (23, 65): 8.0, (23, 66): 8.0, (23, 67): 8.0, (23, 68): 8.0, (23, 69): 8.0, (24, 1): 0.0, (24, 2): 0.0, (24, 3): 0.0, (24, 4): 0.0, (24, 5): 0.0, (24, 6): 0.0, (24, 7): 0.0, (24, 8): 0.0, (24, 9): 0.0, (24, 10): 0.0, (24, 11): 0.0, (24, 12): 0.0, (24, 13): 0.0, (24, 14): 0.0, (24, 15): 0.0, (24, 16): 0.0, (24, 17): 0.0, (24, 18): 0.0, (24, 19): 0.0, (24, 20): 0.0, (24, 21): 0.0, (24, 22): 0.0, (24, 23): 0.0, (24, 24): 0.0, (24, 25): 0.0, (24, 26): 0.0, (24, 27): 0.0, (24, 28): 0.0, (24, 29): 0.0, (24, 30): 0.0, (24, 31): 0.0, (24, 32): 0.0, (24, 33): 0.0, (24, 34): 0.0, (24, 35): 0.0, (24, 36): 0.0, (24, 37): 0.0, (24, 38): 0.0, (24, 39): 0.0, (24, 40): 0.0, (24, 41): 0.0, (24, 42): 0.0, (24, 43): 0.0, (24, 44): 0.0, (24, 45): 0.0, (24, 46): 0.0, (24, 47): 0.0, (24, 48): 0.0, (24, 49): 0.0, (24, 50): 0.0, (24, 51): 0.0, (24, 52): 0.0, (24, 53): 0.0, (24, 54): 0.0, (24, 55): 0.0, (24, 56): 0.0, (24, 57): 0.0, (24, 58): 0.0, (24, 59): 1.0, (24, 60): 2.0, (24, 61): 3.0, (24, 62): 4.0, (24, 63): 5.0, (24, 64): 5.0, (24, 65): 5.0, (24, 66): 6.0, (24, 67): 7.0, (24, 68): 8.0, (24, 69): 8.0, (29, 1): 0.0, (29, 2): 0.0, (29, 3): 0.0, (29, 4): 0.0, (29, 5): 0.0, (29, 6): 0.0, (29, 7): 0.0, (29, 8): 0.0, (29, 9): 0.0, (29, 10): 0.0, (29, 11): 0.0, (29, 12): 0.0, (29, 13): 0.0, (29, 14): 0.0, (29, 15): 0.0, (29, 16): 0.0, (29, 17): 0.0, (29, 18): 0.0, (29, 19): 0.0, (29, 20): 0.0, (29, 21): 0.0, (29, 22): 0.0, (29, 23): 0.0, (29, 24): 0.0, (29, 25): 0.0, (29, 26): 0.0, (29, 27): 0.0, (29, 28): 0.0, (29, 29): 0.0, (29, 30): 0.0, (29, 31): 0.0, (29, 32): 0.0, (29, 33): 0.0, (29, 34): 0.0, (29, 35): 0.0, (29, 36): 0.0, (29, 37): 0.0, (29, 38): 1.0, (29, 39): 2.0, (29, 40): 3.0, (29, 41): 4.0, (29, 42): 5.0, (29, 43): 6.0, (29, 44): 6.0, (29, 45): 7.0, (29, 46): 8.0, (29, 47): 9.0, (29, 48): 10.0, (29, 49): 11.0, (29, 50): 12.0, (29, 51): 12.0, (29, 52): 12.0, (29, 53): 12.0, (29, 54): 12.0, (29, 55): 12.0, (29, 56): 12.0, (29, 57): 12.0, (29, 58): 12.0, (29, 59): 12.0, (29, 60): 12.0, (29, 61): 12.0, (29, 62): 12.0, (29, 63): 12.0, (29, 64): 12.0, (29, 65): 12.0, (29, 66): 12.0, (29, 67): 12.0, (29, 68): 12.0, (29, 69): 12.0, (31, 1): 0.0, (31, 2): 0.0, (31, 3): 0.0, (31, 4): 0.0, (31, 5): 0.0, (31, 6): 0.0, (31, 7): 0.0, (31, 8): 0.0, (31, 9): 0.0, (31, 10): 0.0, (31, 11): 0.0, (31, 12): 0.0, (31, 13): 0.0, (31, 14): 0.0, (31, 15): 0.0, (31, 16): 0.0, (31, 17): 0.0, (31, 18): 0.0, (31, 19): 0.0, (31, 20): 0.0, (31, 21): 0.0, (31, 22): 0.0, (31, 23): 0.0, (31, 24): 0.0, (31, 25): 0.0, (31, 26): 0.0, (31, 27): 0.0, (31, 28): 0.0, (31, 29): 0.0, (31, 30): 0.0, (31, 31): 0.0, (31, 32): 0.0, (31, 33): 0.0, (31, 34): 0.0, (31, 35): 0.0, (31, 36): 0.0, (31, 37): 0.0, (31, 38): 0.0, (31, 39): 0.0, (31, 40): 0.0, (31, 41): 0.0, (31, 42): 0.0, (31, 43): 0.0, (31, 44): 0.0, (31, 45): 0.0, (31, 46): 0.0, (31, 47): 0.0, (31, 48): 0.0, (31, 49): 0.0, (31, 50): 0.0, (31, 51): 0.0, (31, 52): 0.0, (31, 53): 0.0, (31, 54): 0.0, (31, 55): 0.0, (31, 56): 0.0, (31, 57): 0.0, (31, 58): 0.0, (31, 59): 0.0, (31, 60): 0.0, (31, 61): 0.0, (31, 62): 0.0, (31, 63): 0.0, (31, 64): 0.0, (31, 65): 0.0, (31, 66): 0.0, (31, 67): 0.0, (31, 68): 1.0, (31, 69): 1.0, (33, 1): 0.0, (33, 2): 0.0, (33, 3): 0.0, (33, 4): 0.0, (33, 5): 0.0, (33, 6): 0.0, (33, 7): 0.0, (33, 8): 0.0, (33, 9): 0.0, (33, 10): 0.0, (33, 11): 0.0, (33, 12): 0.0, (33, 13): 0.0, (33, 14): 0.0, (33, 15): 0.0, (33, 16): 0.0, (33, 17): 0.0, (33, 18): 0.0, (33, 19): 0.0, (33, 20): 0.0, (33, 21): 0.0, (33, 22): 0.0, (33, 23): 0.0, (33, 24): 0.0, (33, 25): 0.0, (33, 26): 0.0, (33, 27): 0.0, (33, 28): 0.0, (33, 29): 0.0, (33, 30): 0.0, (33, 31): 0.0, (33, 32): 0.0, (33, 33): 0.0, (33, 34): 0.0, (33, 35): 0.0, (33, 36): 0.0, (33, 37): 0.0, (33, 38): 0.0, (33, 39): 0.0, (33, 40): 0.0, (33, 41): 0.0, (33, 42): 0.0, (33, 43): 0.0, (33, 44): 0.0, (33, 45): 0.0, (33, 46): 0.0, (33, 47): 0.0, (33, 48): 0.0, (33, 49): 0.0, (33, 50): 0.0, (33, 51): 0.0, (33, 52): 0.0, (33, 53): 0.0, (33, 54): 0.0, (33, 55): 0.0, (33, 56): 0.0, (33, 57): 0.0, (33, 58): 0.0, (33, 59): 0.0, (33, 60): 0.0, (33, 61): 0.0, (33, 62): 0.0, (33, 63): 0.0, (33, 64): 0.0, (33, 65): 0.0, (33, 66): 1.0, (33, 67): 1.0, (33, 68): 1.0, (33, 69): 1.0, (45, 1): 0.0, (45, 2): 0.0, (45, 3): 0.0, (45, 4): 0.0, (45, 5): 0.0, (45, 6): 0.0, (45, 7): 0.0, (45, 8): 0.0, (45, 9): 0.0, (45, 10): 0.0, (45, 11): 0.0, (45, 12): 0.0, (45, 13): 0.0, (45, 14): 0.0, (45, 15): 0.0, (45, 16): 0.0, (45, 17): 0.0, (45, 18): 0.0, (45, 19): 0.0, (45, 20): 0.0, (45, 21): 0.0, (45, 22): 0.0, (45, 23): 0.0, (45, 24): 0.0, (45, 25): 0.0, (45, 26): 0.0, (45, 27): 0.0, (45, 28): 0.0, (45, 29): 0.0, (45, 30): 0.0, (45, 31): 0.0, (45, 32): 0.0, (45, 33): 0.0, (45, 34): 0.0, (45, 35): 0.0, (45, 36): 0.0, (45, 37): 0.0, (45, 38): 0.0, (45, 39): 0.0, (45, 40): 0.0, (45, 41): 0.0, (45, 42): 0.0, (45, 43): 0.0, (45, 44): 0.0, (45, 45): 0.0, (45, 46): 0.0, (45, 47): 0.0, (45, 48): 0.0, (45, 49): 0.0, (45, 50): 0.0, (45, 51): 0.0, (45, 52): 0.0, (45, 53): 0.0, (45, 54): 0.0, (45, 55): 0.0, (45, 56): 0.0, (45, 57): 0.0, (45, 58): 0.0, (45, 59): 0.0, (45, 60): 1.0, (45, 61): 1.0, (45, 62): 1.0, (45, 63): 1.0, (45, 64): 2.0, (45, 65): 3.0, (45, 66): 3.0, (45, 67): 3.0, (45, 68): 3.0, (45, 69): 3.0, (50, 1): 0.0, (50, 2): 0.0, (50, 3): 0.0, (50, 4): 0.0, (50, 5): 0.0, (50, 6): 0.0, (50, 7): 0.0, (50, 8): 0.0, (50, 9): 0.0, (50, 10): 0.0, (50, 11): 0.0, (50, 12): 0.0, (50, 13): 0.0, (50, 14): 0.0, (50, 15): 0.0, (50, 16): 0.0, (50, 17): 0.0, (50, 18): 0.0, (50, 19): 0.0, (50, 20): 0.0, (50, 21): 0.0, (50, 22): 0.0, (50, 23): 0.0, (50, 24): 0.0, (50, 25): 0.0, (50, 26): 0.0, (50, 27): 0.0, (50, 28): 0.0, (50, 29): 0.0, (50, 30): 0.0, (50, 31): 0.0, (50, 32): 0.0, (50, 33): 0.0, (50, 34): 0.0, (50, 35): 0.0, (50, 36): 0.0, (50, 37): 0.0, (50, 38): 0.0, (50, 39): 0.0, (50, 40): 0.0, (50, 41): 0.0, (50, 42): 0.0, (50, 43): 0.0, (50, 44): 0.0, (50, 45): 0.0, (50, 46): 0.0, (50, 47): 0.0, (50, 48): 0.0, (50, 49): 0.0, (50, 50): 0.0, (50, 51): 0.0, (50, 52): 0.0, (50, 53): 0.0, (50, 54): 0.0, (50, 55): 0.0, (50, 56): 0.0, (50, 57): 0.0, (50, 58): 0.0, (50, 59): 0.0, (50, 60): 0.0, (50, 61): 1.0, (50, 62): 1.0, (50, 63): 2.0, (50, 64): 3.0, (50, 65): 3.0, (50, 66): 4.0, (50, 67): 5.0, (50, 68): 5.0, (50, 69): 5.0, (53, 1): 0.0, (53, 2): 0.0, (53, 3): 0.0, (53, 4): 0.0, (53, 5): 0.0, (53, 6): 0.0, (53, 7): 0.0, (53, 8): 0.0, (53, 9): 0.0, (53, 10): 0.0, (53, 11): 0.0, (53, 12): 0.0, (53, 13): 0.0, (53, 14): 0.0, (53, 15): 0.0, (53, 16): 0.0, (53, 17): 0.0, (53, 18): 0.0, (53, 19): 0.0, (53, 20): 0.0, (53, 21): 0.0, (53, 22): 0.0, (53, 23): 0.0, (53, 24): 0.0, (53, 25): 0.0, (53, 26): 0.0, (53, 27): 0.0, (53, 28): 0.0, (53, 29): 0.0, (53, 30): 0.0, (53, 31): 0.0, (53, 32): 0.0, (53, 33): 0.0, (53, 34): 0.0, (53, 35): 0.0, (53, 36): 0.0, (53, 37): 0.0, (53, 38): 0.0, (53, 39): 0.0, (53, 40): 0.0, (53, 41): 0.0, (53, 42): 0.0, (53, 43): 0.0, (53, 44): 0.0, (53, 45): 0.0, (53, 46): 0.0, (53, 47): 0.0, (53, 48): 0.0, (53, 49): 0.0, (53, 50): 0.0, (53, 51): 0.0, (53, 52): 1.0, (53, 53): 1.0, (53, 54): 2.0, (53, 55): 3.0, (53, 56): 4.0, (53, 57): 4.0, (53, 58): 5.0, (53, 59): 5.0, (53, 60): 5.0, (53, 61): 5.0, (53, 62): 5.0, (53, 63): 5.0, (53, 64): 5.0, (53, 65): 5.0, (53, 66): 5.0, (53, 67): 5.0, (53, 68): 5.0, (53, 69): 5.0, (54, 1): 0.0, (54, 2): 0.0, (54, 3): 0.0, (54, 4): 0.0, (54, 5): 0.0, (54, 6): 0.0, (54, 7): 0.0, (54, 8): 0.0, (54, 9): 0.0, (54, 10): 0.0, (54, 11): 0.0, (54, 12): 0.0, (54, 13): 0.0, (54, 14): 0.0, (54, 15): 0.0, (54, 16): 0.0, (54, 17): 0.0, (54, 18): 0.0, (54, 19): 0.0, (54, 20): 0.0, (54, 21): 0.0, (54, 22): 0.0, (54, 23): 0.0, (54, 24): 0.0, (54, 25): 0.0, (54, 26): 0.0, (54, 27): 0.0, (54, 28): 0.0, (54, 29): 0.0, (54, 30): 0.0, (54, 31): 0.0, (54, 32): 0.0, (54, 33): 0.0, (54, 34): 0.0, (54, 35): 0.0, (54, 36): 0.0, (54, 37): 0.0, (54, 38): 0.0, (54, 39): 0.0, (54, 40): 0.0, (54, 41): 0.0, (54, 42): 0.0, (54, 43): 0.0, (54, 44): 0.0, (54, 45): 0.0, (54, 46): 0.0, (54, 47): 0.0, (54, 48): 0.0, (54, 49): 0.0, (54, 50): 1.0, (54, 51): 1.0, (54, 52): 1.0, (54, 53): 2.0, (54, 54): 2.0, (54, 55): 3.0, (54, 56): 3.0, (54, 57): 3.0, (54, 58): 3.0, (54, 59): 3.0, (54, 60): 3.0, (54, 61): 3.0, (54, 62): 3.0, (54, 63): 3.0, (54, 64): 3.0, (54, 65): 3.0, (54, 66): 3.0, (54, 67): 3.0, (54, 68): 3.0, (54, 69): 3.0, (55, 1): 0.0, (55, 2): 0.0, (55, 3): 0.0, (55, 4): 0.0, (55, 5): 0.0, (55, 6): 0.0, (55, 7): 0.0, (55, 8): 0.0, (55, 9): 0.0, (55, 10): 0.0, (55, 11): 0.0, (55, 12): 0.0, (55, 13): 0.0, (55, 14): 0.0, (55, 15): 0.0, (55, 16): 0.0, (55, 17): 0.0, (55, 18): 0.0, (55, 19): 0.0, (55, 20): 0.0, (55, 21): 0.0, (55, 22): 0.0, (55, 23): 0.0, (55, 24): 0.0, (55, 25): 0.0, (55, 26): 0.0, (55, 27): 0.0, (55, 28): 0.0, (55, 29): 0.0, (55, 30): 0.0, (55, 31): 0.0, (55, 32): 0.0, (55, 33): 0.0, (55, 34): 0.0, (55, 35): 0.0, (55, 36): 0.0, (55, 37): 0.0, (55, 38): 0.0, (55, 39): 0.0, (55, 40): 0.0, (55, 41): 0.0, (55, 42): 0.0, (55, 43): 0.0, (55, 44): 0.0, (55, 45): 0.0, (55, 46): 0.0, (55, 47): 0.0, (55, 48): 0.0, (55, 49): 0.0, (55, 50): 0.0, (55, 51): 0.0, (55, 52): 0.0, (55, 53): 0.0, (55, 54): 0.0, (55, 55): 0.0, (55, 56): 0.0, (55, 57): 0.0, (55, 58): 0.0, (55, 59): 0.0, (55, 60): 0.0, (55, 61): 0.0, (55, 62): 0.0, (55, 63): 0.0, (55, 64): 0.0, (55, 65): 0.0, (55, 66): 1.0, (55, 67): 1.0, (55, 68): 1.0, (55, 69): 1.0, (56, 1): 0.0, (56, 2): 0.0, (56, 3): 0.0, (56, 4): 0.0, (56, 5): 0.0, (56, 6): 0.0, (56, 7): 0.0, (56, 8): 0.0, (56, 9): 0.0, (56, 10): 0.0, (56, 11): 0.0, (56, 12): 0.0, (56, 13): 0.0, (56, 14): 0.0, (56, 15): 0.0, (56, 16): 0.0, (56, 17): 0.0, (56, 18): 0.0, (56, 19): 0.0, (56, 20): 0.0, (56, 21): 0.0, (56, 22): 0.0, (56, 23): 0.0, (56, 24): 0.0, (56, 25): 0.0, (56, 26): 0.0, (56, 27): 0.0, (56, 28): 0.0, (56, 29): 0.0, (56, 30): 0.0, (56, 31): 0.0, (56, 32): 0.0, (56, 33): 0.0, (56, 34): 0.0, (56, 35): 0.0, (56, 36): 0.0, (56, 37): 0.0, (56, 38): 0.0, (56, 39): 0.0, (56, 40): 0.0, (56, 41): 0.0, (56, 42): 0.0, (56, 43): 0.0, (56, 44): 0.0, (56, 45): 0.0, (56, 46): 0.0, (56, 47): 0.0, (56, 48): 0.0, (56, 49): 0.0, (56, 50): 0.0, (56, 51): 0.0, (56, 52): 0.0, (56, 53): 0.0, (56, 54): 1.0, (56, 55): 2.0, (56, 56): 3.0, (56, 57): 4.0, (56, 58): 4.0, (56, 59): 4.0, (56, 60): 5.0, (56, 61): 6.0, (56, 62): 7.0, (56, 63): 7.0, (56, 64): 7.0, (56, 65): 7.0, (56, 66): 7.0, (56, 67): 7.0, (56, 68): 7.0, (56, 69): 7.0, (58, 1): 0.0, (58, 2): 0.0, (58, 3): 0.0, (58, 4): 0.0, (58, 5): 0.0, (58, 6): 0.0, (58, 7): 0.0, (58, 8): 0.0, (58, 9): 0.0, (58, 10): 0.0, (58, 11): 0.0, (58, 12): 0.0, (58, 13): 0.0, (58, 14): 0.0, (58, 15): 0.0, (58, 16): 0.0, (58, 17): 0.0, (58, 18): 0.0, (58, 19): 0.0, (58, 20): 0.0, (58, 21): 0.0, (58, 22): 0.0, (58, 23): 0.0, (58, 24): 0.0, (58, 25): 0.0, (58, 26): 0.0, (58, 27): 0.0, (58, 28): 0.0, (58, 29): 0.0, (58, 30): 0.0, (58, 31): 0.0, (58, 32): 0.0, (58, 33): 0.0, (58, 34): 0.0, (58, 35): 0.0, (58, 36): 0.0, (58, 37): 0.0, (58, 38): 0.0, (58, 39): 0.0, (58, 40): 0.0, (58, 41): 0.0, (58, 42): 0.0, (58, 43): 0.0, (58, 44): 0.0, (58, 45): 0.0, (58, 46): 0.0, (58, 47): 0.0, (58, 48): 0.0, (58, 49): 0.0, (58, 50): 0.0, (58, 51): 0.0, (58, 52): 1.0, (58, 53): 2.0, (58, 54): 3.0, (58, 55): 4.0, (58, 56): 4.0, (58, 57): 4.0, (58, 58): 5.0, (58, 59): 6.0, (58, 60): 7.0, (58, 61): 8.0, (58, 62): 9.0, (58, 63): 9.0, (58, 64): 9.0, (58, 65): 9.0, (58, 66): 9.0, (58, 67): 9.0, (58, 68): 9.0, (58, 69): 9.0, (61, 1): 0.0, (61, 2): 0.0, (61, 3): 0.0, (61, 4): 0.0, (61, 5): 0.0, (61, 6): 0.0, (61, 7): 0.0, (61, 8): 0.0, (61, 9): 0.0, (61, 10): 0.0, (61, 11): 0.0, (61, 12): 0.0, (61, 13): 0.0, (61, 14): 0.0, (61, 15): 0.0, (61, 16): 0.0, (61, 17): 0.0, (61, 18): 0.0, (61, 19): 0.0, (61, 20): 0.0, (61, 21): 0.0, (61, 22): 0.0, (61, 23): 0.0, (61, 24): 0.0, (61, 25): 0.0, (61, 26): 0.0, (61, 27): 0.0, (61, 28): 0.0, (61, 29): 0.0, (61, 30): 0.0, (61, 31): 0.0, (61, 32): 0.0, (61, 33): 0.0, (61, 34): 1.0, (61, 35): 2.0, (61, 36): 3.0, (61, 37): 3.0, (61, 38): 4.0, (61, 39): 5.0, (61, 40): 6.0, (61, 41): 7.0, (61, 42): 8.0, (61, 43): 8.0, (61, 44): 8.0, (61, 45): 8.0, (61, 46): 8.0, (61, 47): 8.0, (61, 48): 8.0, (61, 49): 8.0, (61, 50): 8.0, (61, 51): 8.0, (61, 52): 8.0, (61, 53): 8.0, (61, 54): 8.0, (61, 55): 8.0, (61, 56): 8.0, (61, 57): 8.0, (61, 58): 8.0, (61, 59): 8.0, (61, 60): 8.0, (61, 61): 8.0, (61, 62): 8.0, (61, 63): 8.0, (61, 64): 8.0, (61, 65): 8.0, (61, 66): 8.0, (61, 67): 8.0, (61, 68): 8.0, (61, 69): 8.0, (62, 1): 0.0, (62, 2): 0.0, (62, 3): 0.0, (62, 4): 0.0, (62, 5): 0.0, (62, 6): 0.0, (62, 7): 0.0, (62, 8): 0.0, (62, 9): 0.0, (62, 10): 0.0, (62, 11): 0.0, (62, 12): 0.0, (62, 13): 0.0, (62, 14): 0.0, (62, 15): 0.0, (62, 16): 0.0, (62, 17): 0.0, (62, 18): 0.0, (62, 19): 0.0, (62, 20): 0.0, (62, 21): 0.0, (62, 22): 0.0, (62, 23): 0.0, (62, 24): 0.0, (62, 25): 0.0, (62, 26): 0.0, (62, 27): 0.0, (62, 28): 0.0, (62, 29): 0.0, (62, 30): 0.0, (62, 31): 0.0, (62, 32): 0.0, (62, 33): 0.0, (62, 34): 0.0, (62, 35): 0.0, (62, 36): 0.0, (62, 37): 0.0, (62, 38): 0.0, (62, 39): 0.0, (62, 40): 0.0, (62, 41): 0.0, (62, 42): 0.0, (62, 43): 0.0, (62, 44): 0.0, (62, 45): 0.0, (62, 46): 0.0, (62, 47): 1.0, (62, 48): 2.0, (62, 49): 3.0, (62, 50): 3.0, (62, 51): 3.0, (62, 52): 4.0, (62, 53): 5.0, (62, 54): 6.0, (62, 55): 6.0, (62, 56): 6.0, (62, 57): 6.0, (62, 58): 6.0, (62, 59): 6.0, (62, 60): 6.0, (62, 61): 6.0, (62, 62): 6.0, (62, 63): 6.0, (62, 64): 6.0, (62, 65): 6.0, (62, 66): 6.0, (62, 67): 6.0, (62, 68): 6.0, (62, 69): 6.0, (64, 1): 0.0, (64, 2): 0.0, (64, 3): 0.0, (64, 4): 0.0, (64, 5): 0.0, (64, 6): 0.0, (64, 7): 0.0, (64, 8): 0.0, (64, 9): 0.0, (64, 10): 0.0, (64, 11): 0.0, (64, 12): 0.0, (64, 13): 0.0, (64, 14): 0.0, (64, 15): 0.0, (64, 16): 0.0, (64, 17): 0.0, (64, 18): 0.0, (64, 19): 0.0, (64, 20): 0.0, (64, 21): 0.0, (64, 22): 0.0, (64, 23): 0.0, (64, 24): 0.0, (64, 25): 0.0, (64, 26): 0.0, (64, 27): 0.0, (64, 28): 0.0, (64, 29): 0.0, (64, 30): 0.0, (64, 31): 0.0, (64, 32): 0.0, (64, 33): 0.0, (64, 34): 0.0, (64, 35): 0.0, (64, 36): 0.0, (64, 37): 0.0, (64, 38): 0.0, (64, 39): 0.0, (64, 40): 0.0, (64, 41): 0.0, (64, 42): 0.0, (64, 43): 0.0, (64, 44): 1.0, (64, 45): 2.0, (64, 46): 3.0, (64, 47): 4.0, (64, 48): 5.0, (64, 49): 6.0, (64, 50): 6.0, (64, 51): 6.0, (64, 52): 6.0, (64, 53): 6.0, (64, 54): 6.0, (64, 55): 6.0, (64, 56): 6.0, (64, 57): 6.0, (64, 58): 6.0, (64, 59): 6.0, (64, 60): 6.0, (64, 61): 6.0, (64, 62): 6.0, (64, 63): 6.0, (64, 64): 6.0, (64, 65): 6.0, (64, 66): 6.0, (64, 67): 6.0, (64, 68): 6.0, (64, 69): 6.0, (66, 1): 0.0, (66, 2): 0.0, (66, 3): 0.0, (66, 4): 0.0, (66, 5): 0.0, (66, 6): 0.0, (66, 7): 0.0, (66, 8): 0.0, (66, 9): 0.0, (66, 10): 0.0, (66, 11): 0.0, (66, 12): 0.0, (66, 13): 0.0, (66, 14): 0.0, (66, 15): 0.0, (66, 16): 0.0, (66, 17): 0.0, (66, 18): 0.0, (66, 19): 0.0, (66, 20): 0.0, (66, 21): 0.0, (66, 22): 0.0, (66, 23): 0.0, (66, 24): 0.0, (66, 25): 0.0, (66, 26): 0.0, (66, 27): 0.0, (66, 28): 0.0, (66, 29): 0.0, (66, 30): 0.0, (66, 31): 0.0, (66, 32): 0.0, (66, 33): 0.0, (66, 34): 0.0, (66, 35): 0.0, (66, 36): 0.0, (66, 37): 0.0, (66, 38): 0.0, (66, 39): 0.0, (66, 40): 0.0, (66, 41): 0.0, (66, 42): 0.0, (66, 43): 0.0, (66, 44): 0.0, (66, 45): 0.0, (66, 46): 0.0, (66, 47): 0.0, (66, 48): 0.0, (66, 49): 0.0, (66, 50): 0.0, (66, 51): 0.0, (66, 52): 0.0, (66, 53): 1.0, (66, 54): 2.0, (66, 55): 2.0, (66, 56): 3.0, (66, 57): 3.0, (66, 58): 4.0, (66, 59): 5.0, (66, 60): 6.0, (66, 61): 6.0, (66, 62): 6.0, (66, 63): 6.0, (66, 64): 6.0, (66, 65): 6.0, (66, 66): 6.0, (66, 67): 6.0, (66, 68): 6.0, (66, 69): 6.0, (69, 1): 0.0, (69, 2): 0.0, (69, 3): 0.0, (69, 4): 0.0, (69, 5): 0.0, (69, 6): 0.0, (69, 7): 0.0, (69, 8): 0.0, (69, 9): 0.0, (69, 10): 0.0, (69, 11): 0.0, (69, 12): 0.0, (69, 13): 0.0, (69, 14): 0.0, (69, 15): 0.0, (69, 16): 0.0, (69, 17): 0.0, (69, 18): 0.0, (69, 19): 0.0, (69, 20): 0.0, (69, 21): 0.0, (69, 22): 0.0, (69, 23): 0.0, (69, 24): 0.0, (69, 25): 0.0, (69, 26): 0.0, (69, 27): 0.0, (69, 28): 0.0, (69, 29): 0.0, (69, 30): 0.0, (69, 31): 0.0, (69, 32): 0.0, (69, 33): 0.0, (69, 34): 0.0, (69, 35): 0.0, (69, 36): 0.0, (69, 37): 0.0, (69, 38): 0.0, (69, 39): 0.0, (69, 40): 0.0, (69, 41): 0.0, (69, 42): 0.0, (69, 43): 0.0, (69, 44): 0.0, (69, 45): 0.0, (69, 46): 1.0, (69, 47): 2.0, (69, 48): 3.0, (69, 49): 4.0, (69, 50): 5.0, (69, 51): 6.0, (69, 52): 6.0, (69, 53): 6.0, (69, 54): 6.0, (69, 55): 6.0, (69, 56): 6.0, (69, 57): 6.0, (69, 58): 6.0, (69, 59): 6.0, (69, 60): 6.0, (69, 61): 6.0, (69, 62): 6.0, (69, 63): 6.0, (69, 64): 6.0, (69, 65): 6.0, (69, 66): 6.0, (69, 67): 6.0, (69, 68): 6.0, (69, 69): 6.0, (71, 1): 0.0, (71, 2): 0.0, (71, 3): 0.0, (71, 4): 0.0, (71, 5): 0.0, (71, 6): 0.0, (71, 7): 0.0, (71, 8): 0.0, (71, 9): 0.0, (71, 10): 0.0, (71, 11): 0.0, (71, 12): 0.0, (71, 13): 0.0, (71, 14): 0.0, (71, 15): 0.0, (71, 16): 0.0, (71, 17): 0.0, (71, 18): 0.0, (71, 19): 0.0, (71, 20): 0.0, (71, 21): 0.0, (71, 22): 0.0, (71, 23): 0.0, (71, 24): 0.0, (71, 25): 0.0, (71, 26): 0.0, (71, 27): 0.0, (71, 28): 0.0, (71, 29): 0.0, (71, 30): 0.0, (71, 31): 0.0, (71, 32): 0.0, (71, 33): 0.0, (71, 34): 0.0, (71, 35): 0.0, (71, 36): 0.0, (71, 37): 0.0, (71, 38): 0.0, (71, 39): 0.0, (71, 40): 0.0, (71, 41): 0.0, (71, 42): 0.0, (71, 43): 0.0, (71, 44): 0.0, (71, 45): 0.0, (71, 46): 0.0, (71, 47): 0.0, (71, 48): 0.0, (71, 49): 0.0, (71, 50): 0.0, (71, 51): 1.0, (71, 52): 2.0, (71, 53): 3.0, (71, 54): 4.0, (71, 55): 5.0, (71, 56): 6.0, (71, 57): 6.0, (71, 58): 6.0, (71, 59): 7.0, (71, 60): 7.0, (71, 61): 7.0, (71, 62): 7.0, (71, 63): 7.0, (71, 64): 7.0, (71, 65): 7.0, (71, 66): 7.0, (71, 67): 7.0, (71, 68): 7.0, (71, 69): 7.0, (76, 1): 0.0, (76, 2): 0.0, (76, 3): 0.0, (76, 4): 0.0, (76, 5): 0.0, (76, 6): 0.0, (76, 7): 0.0, (76, 8): 0.0, (76, 9): 0.0, (76, 10): 0.0, (76, 11): 0.0, (76, 12): 0.0, (76, 13): 0.0, (76, 14): 0.0, (76, 15): 0.0, (76, 16): 0.0, (76, 17): 0.0, (76, 18): 0.0, (76, 19): 0.0, (76, 20): 0.0, (76, 21): 0.0, (76, 22): 0.0, (76, 23): 0.0, (76, 24): 0.0, (76, 25): 0.0, (76, 26): 0.0, (76, 27): 0.0, (76, 28): 0.0, (76, 29): 0.0, (76, 30): 0.0, (76, 31): 0.0, (76, 32): 0.0, (76, 33): 0.0, (76, 34): 0.0, (76, 35): 0.0, (76, 36): 0.0, (76, 37): 0.0, (76, 38): 0.0, (76, 39): 0.0, (76, 40): 0.0, (76, 41): 0.0, (76, 42): 0.0, (76, 43): 0.0, (76, 44): 0.0, (76, 45): 0.0, (76, 46): 0.0, (76, 47): 0.0, (76, 48): 0.0, (76, 49): 0.0, (76, 50): 0.0, (76, 51): 0.0, (76, 52): 0.0, (76, 53): 0.0, (76, 54): 0.0, (76, 55): 0.0, (76, 56): 1.0, (76, 57): 2.0, (76, 58): 2.0, (76, 59): 2.0, (76, 60): 3.0, (76, 61): 3.0, (76, 62): 3.0, (76, 63): 3.0, (76, 64): 3.0, (76, 65): 3.0, (76, 66): 3.0, (76, 67): 3.0, (76, 68): 3.0, (76, 69): 3.0, (77, 1): 0.0, (77, 2): 0.0, (77, 3): 0.0, (77, 4): 0.0, (77, 5): 0.0, (77, 6): 0.0, (77, 7): 0.0, (77, 8): 0.0, (77, 9): 0.0, (77, 10): 0.0, (77, 11): 0.0, (77, 12): 0.0, (77, 13): 0.0, (77, 14): 0.0, (77, 15): 0.0, (77, 16): 0.0, (77, 17): 0.0, (77, 18): 0.0, (77, 19): 0.0, (77, 20): 0.0, (77, 21): 0.0, (77, 22): 0.0, (77, 23): 0.0, (77, 24): 0.0, (77, 25): 0.0, (77, 26): 0.0, (77, 27): 0.0, (77, 28): 0.0, (77, 29): 0.0, (77, 30): 0.0, (77, 31): 0.0, (77, 32): 0.0, (77, 33): 0.0, (77, 34): 0.0, (77, 35): 0.0, (77, 36): 1.0, (77, 37): 2.0, (77, 38): 3.0, (77, 39): 4.0, (77, 40): 5.0, (77, 41): 6.0, (77, 42): 6.0, (77, 43): 6.0, (77, 44): 7.0, (77, 45): 7.0, (77, 46): 7.0, (77, 47): 7.0, (77, 48): 7.0, (77, 49): 7.0, (77, 50): 7.0, (77, 51): 7.0, (77, 52): 7.0, (77, 53): 7.0, (77, 54): 7.0, (77, 55): 7.0, (77, 56): 7.0, (77, 57): 7.0, (77, 58): 7.0, (77, 59): 7.0, (77, 60): 7.0, (77, 61): 7.0, (77, 62): 7.0, (77, 63): 7.0, (77, 64): 7.0, (77, 65): 7.0, (77, 66): 7.0, (77, 67): 7.0, (77, 68): 7.0, (77, 69): 7.0, (78, 1): 0.0, (78, 2): 0.0, (78, 3): 0.0, (78, 4): 0.0, (78, 5): 0.0, (78, 6): 0.0, (78, 7): 0.0, (78, 8): 0.0, (78, 9): 0.0, (78, 10): 0.0, (78, 11): 0.0, (78, 12): 0.0, (78, 13): 0.0, (78, 14): 0.0, (78, 15): 0.0, (78, 16): 0.0, (78, 17): 0.0, (78, 18): 0.0, (78, 19): 0.0, (78, 20): 0.0, (78, 21): 0.0, (78, 22): 0.0, (78, 23): 0.0, (78, 24): 0.0, (78, 25): 0.0, (78, 26): 0.0, (78, 27): 0.0, (78, 28): 0.0, (78, 29): 0.0, (78, 30): 0.0, (78, 31): 0.0, (78, 32): 0.0, (78, 33): 0.0, (78, 34): 0.0, (78, 35): 0.0, (78, 36): 0.0, (78, 37): 0.0, (78, 38): 0.0, (78, 39): 1.0, (78, 40): 2.0, (78, 41): 2.0, (78, 42): 2.0, (78, 43): 3.0, (78, 44): 3.0, (78, 45): 3.0, (78, 46): 3.0, (78, 47): 3.0, (78, 48): 3.0, (78, 49): 3.0, (78, 50): 3.0, (78, 51): 3.0, (78, 52): 3.0, (78, 53): 3.0, (78, 54): 3.0, (78, 55): 3.0, (78, 56): 3.0, (78, 57): 3.0, (78, 58): 3.0, (78, 59): 3.0, (78, 60): 3.0, (78, 61): 3.0, (78, 62): 3.0, (78, 63): 3.0, (78, 64): 3.0, (78, 65): 3.0, (78, 66): 3.0, (78, 67): 3.0, (78, 68): 3.0, (78, 69): 3.0, (80, 1): 0.0, (80, 2): 0.0, (80, 3): 0.0, (80, 4): 0.0, (80, 5): 0.0, (80, 6): 0.0, (80, 7): 0.0, (80, 8): 0.0, (80, 9): 0.0, (80, 10): 0.0, (80, 11): 0.0, (80, 12): 0.0, (80, 13): 0.0, (80, 14): 0.0, (80, 15): 0.0, (80, 16): 0.0, (80, 17): 0.0, (80, 18): 0.0, (80, 19): 0.0, (80, 20): 0.0, (80, 21): 0.0, (80, 22): 0.0, (80, 23): 0.0, (80, 24): 0.0, (80, 25): 0.0, (80, 26): 0.0, (80, 27): 0.0, (80, 28): 0.0, (80, 29): 0.0, (80, 30): 0.0, (80, 31): 0.0, (80, 32): 0.0, (80, 33): 0.0, (80, 34): 0.0, (80, 35): 0.0, (80, 36): 0.0, (80, 37): 0.0, (80, 38): 0.0, (80, 39): 0.0, (80, 40): 0.0, (80, 41): 0.0, (80, 42): 0.0, (80, 43): 0.0, (80, 44): 0.0, (80, 45): 0.0, (80, 46): 0.0, (80, 47): 0.0, (80, 48): 0.0, (80, 49): 0.0, (80, 50): 0.0, (80, 51): 0.0, (80, 52): 0.0, (80, 53): 0.0, (80, 54): 0.0, (80, 55): 0.0, (80, 56): 0.0, (80, 57): 0.0, (80, 58): 0.0, (80, 59): 0.0, (80, 60): 0.0, (80, 61): 0.0, (80, 62): 0.0, (80, 63): 1.0, (80, 64): 1.0, (80, 65): 2.0, (80, 66): 2.0, (80, 67): 3.0, (80, 68): 3.0, (80, 69): 3.0, (81, 1): 0.0, (81, 2): 0.0, (81, 3): 0.0, (81, 4): 0.0, (81, 5): 0.0, (81, 6): 0.0, (81, 7): 0.0, (81, 8): 0.0, (81, 9): 0.0, (81, 10): 0.0, (81, 11): 0.0, (81, 12): 0.0, (81, 13): 0.0, (81, 14): 0.0, (81, 15): 0.0, (81, 16): 0.0, (81, 17): 0.0, (81, 18): 0.0, (81, 19): 0.0, (81, 20): 0.0, (81, 21): 0.0, (81, 22): 0.0, (81, 23): 0.0, (81, 24): 0.0, (81, 25): 0.0, (81, 26): 0.0, (81, 27): 0.0, (81, 28): 0.0, (81, 29): 0.0, (81, 30): 0.0, (81, 31): 0.0, (81, 32): 0.0, (81, 33): 0.0, (81, 34): 0.0, (81, 35): 0.0, (81, 36): 0.0, (81, 37): 0.0, (81, 38): 0.0, (81, 39): 0.0, (81, 40): 0.0, (81, 41): 0.0, (81, 42): 0.0, (81, 43): 0.0, (81, 44): 0.0, (81, 45): 0.0, (81, 46): 0.0, (81, 47): 0.0, (81, 48): 0.0, (81, 49): 0.0, (81, 50): 0.0, (81, 51): 0.0, (81, 52): 0.0, (81, 53): 0.0, (81, 54): 0.0, (81, 55): 0.0, (81, 56): 0.0, (81, 57): 0.0, (81, 58): 0.0, (81, 59): 1.0, (81, 60): 1.0, (81, 61): 2.0, (81, 62): 3.0, (81, 63): 4.0, (81, 64): 4.0, (81, 65): 5.0, (81, 66): 5.0, (81, 67): 5.0, (81, 68): 5.0, (81, 69): 5.0, (83, 1): 0.0, (83, 2): 0.0, (83, 3): 0.0, (83, 4): 0.0, (83, 5): 0.0, (83, 6): 0.0, (83, 7): 0.0, (83, 8): 0.0, (83, 9): 0.0, (83, 10): 0.0, (83, 11): 0.0, (83, 12): 0.0, (83, 13): 0.0, (83, 14): 0.0, (83, 15): 0.0, (83, 16): 0.0, (83, 17): 0.0, (83, 18): 0.0, (83, 19): 0.0, (83, 20): 0.0, (83, 21): 0.0, (83, 22): 0.0, (83, 23): 0.0, (83, 24): 0.0, (83, 25): 0.0, (83, 26): 0.0, (83, 27): 0.0, (83, 28): 0.0, (83, 29): 0.0, (83, 30): 0.0, (83, 31): 0.0, (83, 32): 0.0, (83, 33): 0.0, (83, 34): 0.0, (83, 35): 0.0, (83, 36): 0.0, (83, 37): 0.0, (83, 38): 0.0, (83, 39): 0.0, (83, 40): 0.0, (83, 41): 0.0, (83, 42): 0.0, (83, 43): 0.0, (83, 44): 0.0, (83, 45): 0.0, (83, 46): 0.0, (83, 47): 0.0, (83, 48): 0.0, (83, 49): 0.0, (83, 50): 1.0, (83, 51): 2.0, (83, 52): 3.0, (83, 53): 4.0, (83, 54): 5.0, (83, 55): 5.0, (83, 56): 5.0, (83, 57): 6.0, (83, 58): 6.0, (83, 59): 6.0, (83, 60): 6.0, (83, 61): 6.0, (83, 62): 6.0, (83, 63): 6.0, (83, 64): 6.0, (83, 65): 6.0, (83, 66): 6.0, (83, 67): 6.0, (83, 68): 6.0, (83, 69): 6.0, (85, 1): 0.0, (85, 2): 0.0, (85, 3): 0.0, (85, 4): 0.0, (85, 5): 0.0, (85, 6): 0.0, (85, 7): 0.0, (85, 8): 0.0, (85, 9): 0.0, (85, 10): 0.0, (85, 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{(3, 1): 0, (3, 2): 0, (3, 3): 0, (3, 4): 0, (3, 5): 0, (3, 6): 0, (3, 7): 0, (3, 8): 0, (3, 9): 0, (3, 10): 0, (3, 11): 0, (3, 12): 0, (3, 13): 0, (3, 14): 0, (3, 15): 0, (3, 16): 0, (3, 17): 0, (3, 18): 0, (3, 19): 0, (3, 20): 0, (3, 21): 0, (3, 22): 0, (3, 23): 0, (3, 24): 0, (3, 25): 0, (3, 26): 0, (3, 27): 0, (3, 28): 0, (3, 29): 0, (3, 30): 0, (3, 31): 0, (3, 32): 0, (3, 33): 0, (3, 34): 0, (3, 35): 0, (3, 36): 0, (3, 37): 0, (3, 38): 0, (3, 39): 0, (3, 40): 0, (3, 41): 0, (3, 42): 0, (3, 43): 0, (3, 44): 0, (3, 45): 0, (3, 46): 0, (3, 47): 0, (3, 48): 0, (3, 49): 0, (3, 50): 0, (3, 51): 0, (3, 52): 0, (3, 53): 0, (3, 54): 0, (3, 55): 0, (3, 56): 0, (3, 57): 0, (3, 58): 0, (3, 59): 1, (3, 60): 0, (3, 61): 0, (3, 62): 0, (3, 63): 0, (3, 64): 0, (3, 65): 0, (3, 66): 0, (3, 67): 0, (3, 68): 0, (3, 69): 0, (4, 1): 0, (4, 2): 0, (4, 3): 0, (4, 4): 0, (4, 5): 0, (4, 6): 0, (4, 7): 0, (4, 8): 0, (4, 9): 0, (4, 10): 0, (4, 11): 0, (4, 12): 0, (4, 13): 0, (4, 14): 0, (4, 15): 0, (4, 16): 0, (4, 17): 0, (4, 18): 0, (4, 19): 0, (4, 20): 0, (4, 21): 0, (4, 22): 0, (4, 23): 0, (4, 24): 0, (4, 25): 0, (4, 26): 0, (4, 27): 0, (4, 28): 0, (4, 29): 0, (4, 30): 0, (4, 31): 0, (4, 32): 0, (4, 33): 0, (4, 34): 0, (4, 35): 0, (4, 36): 0, (4, 37): 0, (4, 38): 0, (4, 39): 0, (4, 40): 0, (4, 41): 0, (4, 42): 0, (4, 43): 0, (4, 44): 0, (4, 45): 0, (4, 46): 0, (4, 47): 0, (4, 48): 0, (4, 49): 0, (4, 50): 0, (4, 51): 0, (4, 52): 0, (4, 53): 0, (4, 54): 0, (4, 55): 0, (4, 56): 0, (4, 57): 0, (4, 58): 0, (4, 59): 0, (4, 60): 0, (4, 61): 0, (4, 62): 0, (4, 63): 1, (4, 64): 0, (4, 65): 0, (4, 66): 0, (4, 67): 0, (4, 68): 0, (4, 69): 0, (8, 1): 0, (8, 2): 0, (8, 3): 0, (8, 4): 0, (8, 5): 0, (8, 6): 0, (8, 7): 0, (8, 8): 0, (8, 9): 0, (8, 10): 0, (8, 11): 0, (8, 12): 0, (8, 13): 0, (8, 14): 0, (8, 15): 0, (8, 16): 0, (8, 17): 0, (8, 18): 0, (8, 19): 0, (8, 20): 0, (8, 21): 0, (8, 22): 0, (8, 23): 0, (8, 24): 0, (8, 25): 0, (8, 26): 0, (8, 27): 0, (8, 28): 0, (8, 29): 0, (8, 30): 0, (8, 31): 0, (8, 32): 0, (8, 33): 0, (8, 34): 0, (8, 35): 0, (8, 36): 0, (8, 37): 0, (8, 38): 0, (8, 39): 0, (8, 40): 0, (8, 41): 0, (8, 42): 0, (8, 43): 0, (8, 44): 0, (8, 45): 0, (8, 46): 0, (8, 47): 0, (8, 48): 1, (8, 49): 0, (8, 50): 0, (8, 51): 0, (8, 52): 0, (8, 53): 0, (8, 54): 0, (8, 55): 0, (8, 56): 0, (8, 57): 0, (8, 58): 0, (8, 59): 0, (8, 60): 0, (8, 61): 0, (8, 62): 0, (8, 63): 0, (8, 64): 0, (8, 65): 0, (8, 66): 0, (8, 67): 0, (8, 68): 0, (8, 69): 0, (9, 1): 0, (9, 2): 0, (9, 3): 0, (9, 4): 0, (9, 5): 0, (9, 6): 0, (9, 7): 0, (9, 8): 0, (9, 9): 0, (9, 10): 0, (9, 11): 0, (9, 12): 0, (9, 13): 0, (9, 14): 0, (9, 15): 0, (9, 16): 0, (9, 17): 0, (9, 18): 0, (9, 19): 0, (9, 20): 0, (9, 21): 0, (9, 22): 0, (9, 23): 0, (9, 24): 0, (9, 25): 0, (9, 26): 0, (9, 27): 0, (9, 28): 0, (9, 29): 0, (9, 30): 0, (9, 31): 0, (9, 32): 0, (9, 33): 0, (9, 34): 0, (9, 35): 0, (9, 36): 0, (9, 37): 0, (9, 38): 0, (9, 39): 0, (9, 40): 0, (9, 41): 0, (9, 42): 0, (9, 43): 0, (9, 44): 0, (9, 45): 0, (9, 46): 0, (9, 47): 0, (9, 48): 0, (9, 49): 0, (9, 50): 0, (9, 51): 0, (9, 52): 0, (9, 53): 0, (9, 54): 0, (9, 55): 0, (9, 56): 0, (9, 57): 0, (9, 58): 0, (9, 59): 0, (9, 60): 0, (9, 61): 0, (9, 62): 0, (9, 63): 0, (9, 64): 0, (9, 65): 0, (9, 66): 0, (9, 67): 0, (9, 68): 0, (9, 69): 1, (10, 1): 0, (10, 2): 0, (10, 3): 0, (10, 4): 0, (10, 5): 0, (10, 6): 0, (10, 7): 0, (10, 8): 0, (10, 9): 0, (10, 10): 0, (10, 11): 0, (10, 12): 0, (10, 13): 0, (10, 14): 0, (10, 15): 0, (10, 16): 0, (10, 17): 0, (10, 18): 0, (10, 19): 0, (10, 20): 0, (10, 21): 0, (10, 22): 0, (10, 23): 0, (10, 24): 0, (10, 25): 0, (10, 26): 0, (10, 27): 0, (10, 28): 0, (10, 29): 0, (10, 30): 0, (10, 31): 0, (10, 32): 0, (10, 33): 0, (10, 34): 0, (10, 35): 0, (10, 36): 0, (10, 37): 0, (10, 38): 0, (10, 39): 0, (10, 40): 0, (10, 41): 0, (10, 42): 0, (10, 43): 0, (10, 44): 0, (10, 45): 0, (10, 46): 0, (10, 47): 0, (10, 48): 0, (10, 49): 0, (10, 50): 0, (10, 51): 0, (10, 52): 0, (10, 53): 0, (10, 54): 1, (10, 55): 0, (10, 56): 0, (10, 57): 0, (10, 58): 0, (10, 59): 0, (10, 60): 0, (10, 61): 0, (10, 62): 0, (10, 63): 0, (10, 64): 0, (10, 65): 0, (10, 66): 0, (10, 67): 0, (10, 68): 0, (10, 69): 0, (11, 1): 0, (11, 2): 0, (11, 3): 0, (11, 4): 0, (11, 5): 0, (11, 6): 0, (11, 7): 0, (11, 8): 0, (11, 9): 0, (11, 10): 0, (11, 11): 0, (11, 12): 0, (11, 13): 0, (11, 14): 0, (11, 15): 0, (11, 16): 0, (11, 17): 0, (11, 18): 0, (11, 19): 0, (11, 20): 0, (11, 21): 0, (11, 22): 0, (11, 23): 0, (11, 24): 0, (11, 25): 0, (11, 26): 0, (11, 27): 0, (11, 28): 0, (11, 29): 0, (11, 30): 0, (11, 31): 0, (11, 32): 0, (11, 33): 0, (11, 34): 0, (11, 35): 0, (11, 36): 0, (11, 37): 0, (11, 38): 0, (11, 39): 0, (11, 40): 0, (11, 41): 0, (11, 42): 0, (11, 43): 0, (11, 44): 0, (11, 45): 0, (11, 46): 0, (11, 47): 0, (11, 48): 0, (11, 49): 0, (11, 50): 0, (11, 51): 0, (11, 52): 0, (11, 53): 0, (11, 54): 0, (11, 55): 0, (11, 56): 0, (11, 57): 0, (11, 58): 0, (11, 59): 0, (11, 60): 0, (11, 61): 0, (11, 62): 1, (11, 63): 0, (11, 64): 0, (11, 65): 0, (11, 66): 0, (11, 67): 0, (11, 68): 0, (11, 69): 0, (12, 1): 0, (12, 2): 0, (12, 3): 0, (12, 4): 0, (12, 5): 0, (12, 6): 0, (12, 7): 0, (12, 8): 0, (12, 9): 0, (12, 10): 0, (12, 11): 0, (12, 12): 0, (12, 13): 0, (12, 14): 0, (12, 15): 0, (12, 16): 0, (12, 17): 0, (12, 18): 0, (12, 19): 0, (12, 20): 0, (12, 21): 0, (12, 22): 0, (12, 23): 0, (12, 24): 0, (12, 25): 0, (12, 26): 0, (12, 27): 0, (12, 28): 0, (12, 29): 0, (12, 30): 0, (12, 31): 0, (12, 32): 0, (12, 33): 0, (12, 34): 0, (12, 35): 0, (12, 36): 0, (12, 37): 0, (12, 38): 0, (12, 39): 0, (12, 40): 0, (12, 41): 0, (12, 42): 0, (12, 43): 0, (12, 44): 1, (12, 45): 0, (12, 46): 0, (12, 47): 0, (12, 48): 0, (12, 49): 0, (12, 50): 0, (12, 51): 0, (12, 52): 0, (12, 53): 0, (12, 54): 0, (12, 55): 0, (12, 56): 0, (12, 57): 0, (12, 58): 0, (12, 59): 0, (12, 60): 0, (12, 61): 0, (12, 62): 0, (12, 63): 0, (12, 64): 0, (12, 65): 0, (12, 66): 0, (12, 67): 0, (12, 68): 0, (12, 69): 0, (21, 1): 0, (21, 2): 0, (21, 3): 0, (21, 4): 0, (21, 5): 0, (21, 6): 0, (21, 7): 0, (21, 8): 0, (21, 9): 0, (21, 10): 0, (21, 11): 0, (21, 12): 0, (21, 13): 0, (21, 14): 0, (21, 15): 0, (21, 16): 0, (21, 17): 0, (21, 18): 0, (21, 19): 0, (21, 20): 0, (21, 21): 0, (21, 22): 0, (21, 23): 0, (21, 24): 0, (21, 25): 0, (21, 26): 0, (21, 27): 0, (21, 28): 0, (21, 29): 0, (21, 30): 0, (21, 31): 0, (21, 32): 0, (21, 33): 0, (21, 34): 0, (21, 35): 0, (21, 36): 0, (21, 37): 0, (21, 38): 0, (21, 39): 0, (21, 40): 0, (21, 41): 0, (21, 42): 0, (21, 43): 0, (21, 44): 0, (21, 45): 0, (21, 46): 0, (21, 47): 0, (21, 48): 0, (21, 49): 0, (21, 50): 0, (21, 51): 0, (21, 52): 1, (21, 53): 0, (21, 54): 0, (21, 55): 0, (21, 56): 0, (21, 57): 0, (21, 58): 0, (21, 59): 0, (21, 60): 0, (21, 61): 0, (21, 62): 0, (21, 63): 0, (21, 64): 0, (21, 65): 0, (21, 66): 0, (21, 67): 0, (21, 68): 0, (21, 69): 0, (23, 1): 0, (23, 2): 0, (23, 3): 0, (23, 4): 0, (23, 5): 0, (23, 6): 0, (23, 7): 0, (23, 8): 0, (23, 9): 0, (23, 10): 0, (23, 11): 0, (23, 12): 0, (23, 13): 0, (23, 14): 0, (23, 15): 0, (23, 16): 0, (23, 17): 0, (23, 18): 0, (23, 19): 0, (23, 20): 0, (23, 21): 0, (23, 22): 0, (23, 23): 0, (23, 24): 0, (23, 25): 0, (23, 26): 0, (23, 27): 0, (23, 28): 0, (23, 29): 0, (23, 30): 0, (23, 31): 0, (23, 32): 0, (23, 33): 0, (23, 34): 0, (23, 35): 0, (23, 36): 0, (23, 37): 0, (23, 38): 0, (23, 39): 0, (23, 40): 0, (23, 41): 0, (23, 42): 1, (23, 43): 0, (23, 44): 0, (23, 45): 0, (23, 46): 0, (23, 47): 0, (23, 48): 0, (23, 49): 0, (23, 50): 0, (23, 51): 0, (23, 52): 0, (23, 53): 0, (23, 54): 0, (23, 55): 0, (23, 56): 0, (23, 57): 0, (23, 58): 0, (23, 59): 0, (23, 60): 0, (23, 61): 0, (23, 62): 0, (23, 63): 0, (23, 64): 0, (23, 65): 0, (23, 66): 0, (23, 67): 0, (23, 68): 0, (23, 69): 0, (24, 1): 0, (24, 2): 0, (24, 3): 0, (24, 4): 0, (24, 5): 0, (24, 6): 0, (24, 7): 0, (24, 8): 0, (24, 9): 0, (24, 10): 0, (24, 11): 0, (24, 12): 0, (24, 13): 0, (24, 14): 0, (24, 15): 0, (24, 16): 0, (24, 17): 0, (24, 18): 0, (24, 19): 0, (24, 20): 0, (24, 21): 0, (24, 22): 0, (24, 23): 0, (24, 24): 0, (24, 25): 0, (24, 26): 0, (24, 27): 0, (24, 28): 0, (24, 29): 0, (24, 30): 0, (24, 31): 0, (24, 32): 0, (24, 33): 0, (24, 34): 0, (24, 35): 0, (24, 36): 0, (24, 37): 0, (24, 38): 0, (24, 39): 0, (24, 40): 0, (24, 41): 0, (24, 42): 0, (24, 43): 0, (24, 44): 0, (24, 45): 0, (24, 46): 0, (24, 47): 0, (24, 48): 0, (24, 49): 0, (24, 50): 0, (24, 51): 0, (24, 52): 0, (24, 53): 0, (24, 54): 0, (24, 55): 0, (24, 56): 0, (24, 57): 0, (24, 58): 0, (24, 59): 0, (24, 60): 0, (24, 61): 0, (24, 62): 0, (24, 63): 0, (24, 64): 0, (24, 65): 0, (24, 66): 0, (24, 67): 0, (24, 68): 1, (24, 69): 0, (29, 1): 0, (29, 2): 0, (29, 3): 0, (29, 4): 0, (29, 5): 0, (29, 6): 0, (29, 7): 0, (29, 8): 0, (29, 9): 0, (29, 10): 0, (29, 11): 0, (29, 12): 0, (29, 13): 0, (29, 14): 0, (29, 15): 0, (29, 16): 0, (29, 17): 0, (29, 18): 0, (29, 19): 0, (29, 20): 0, (29, 21): 0, (29, 22): 0, (29, 23): 0, (29, 24): 0, (29, 25): 0, (29, 26): 0, (29, 27): 0, (29, 28): 0, (29, 29): 0, (29, 30): 0, (29, 31): 0, (29, 32): 0, (29, 33): 0, (29, 34): 0, (29, 35): 0, (29, 36): 0, (29, 37): 0, (29, 38): 0, (29, 39): 0, (29, 40): 0, (29, 41): 0, (29, 42): 0, (29, 43): 0, (29, 44): 0, (29, 45): 0, (29, 46): 0, (29, 47): 0, (29, 48): 0, (29, 49): 0, (29, 50): 1, (29, 51): 0, (29, 52): 0, (29, 53): 0, (29, 54): 0, (29, 55): 0, (29, 56): 0, (29, 57): 0, (29, 58): 0, (29, 59): 0, (29, 60): 0, (29, 61): 0, (29, 62): 0, (29, 63): 0, (29, 64): 0, (29, 65): 0, (29, 66): 0, (29, 67): 0, (29, 68): 0, (29, 69): 0, (31, 1): 0, (31, 2): 0, (31, 3): 0, (31, 4): 0, (31, 5): 0, (31, 6): 0, (31, 7): 0, (31, 8): 0, (31, 9): 0, (31, 10): 0, (31, 11): 0, (31, 12): 0, (31, 13): 0, (31, 14): 0, (31, 15): 0, (31, 16): 0, (31, 17): 0, (31, 18): 0, (31, 19): 0, (31, 20): 0, (31, 21): 0, (31, 22): 0, (31, 23): 0, (31, 24): 0, (31, 25): 0, (31, 26): 0, (31, 27): 0, (31, 28): 0, (31, 29): 0, (31, 30): 0, (31, 31): 0, (31, 32): 0, (31, 33): 0, (31, 34): 0, (31, 35): 0, (31, 36): 0, (31, 37): 0, (31, 38): 0, (31, 39): 0, (31, 40): 0, (31, 41): 0, (31, 42): 0, (31, 43): 0, (31, 44): 0, (31, 45): 0, (31, 46): 0, (31, 47): 0, (31, 48): 0, (31, 49): 0, (31, 50): 0, (31, 51): 0, (31, 52): 0, (31, 53): 0, (31, 54): 0, (31, 55): 0, (31, 56): 0, (31, 57): 0, (31, 58): 0, (31, 59): 0, (31, 60): 0, (31, 61): 0, (31, 62): 0, (31, 63): 0, (31, 64): 0, (31, 65): 0, (31, 66): 0, (31, 67): 0, (31, 68): 0, (31, 69): 1, (33, 1): 0, (33, 2): 0, (33, 3): 0, (33, 4): 0, (33, 5): 0, (33, 6): 0, (33, 7): 0, (33, 8): 0, (33, 9): 0, (33, 10): 0, (33, 11): 0, (33, 12): 0, (33, 13): 0, (33, 14): 0, (33, 15): 0, (33, 16): 0, (33, 17): 0, (33, 18): 0, (33, 19): 0, (33, 20): 0, (33, 21): 0, (33, 22): 0, (33, 23): 0, (33, 24): 0, (33, 25): 0, (33, 26): 0, (33, 27): 0, (33, 28): 0, (33, 29): 0, (33, 30): 0, (33, 31): 0, (33, 32): 0, (33, 33): 0, (33, 34): 0, (33, 35): 0, (33, 36): 0, (33, 37): 0, (33, 38): 0, (33, 39): 0, (33, 40): 0, (33, 41): 0, (33, 42): 0, (33, 43): 0, (33, 44): 0, (33, 45): 0, (33, 46): 0, (33, 47): 0, (33, 48): 0, (33, 49): 0, (33, 50): 0, (33, 51): 0, (33, 52): 0, (33, 53): 0, (33, 54): 0, (33, 55): 0, (33, 56): 0, (33, 57): 0, (33, 58): 0, (33, 59): 0, (33, 60): 0, (33, 61): 0, (33, 62): 0, (33, 63): 0, (33, 64): 0, (33, 65): 0, (33, 66): 0, (33, 67): 0, (33, 68): 0, (33, 69): 1, (45, 1): 0, (45, 2): 0, (45, 3): 0, (45, 4): 0, (45, 5): 0, (45, 6): 0, (45, 7): 0, (45, 8): 0, (45, 9): 0, (45, 10): 0, (45, 11): 0, (45, 12): 0, (45, 13): 0, (45, 14): 0, (45, 15): 0, (45, 16): 0, (45, 17): 0, (45, 18): 0, (45, 19): 0, (45, 20): 0, (45, 21): 0, (45, 22): 0, (45, 23): 0, (45, 24): 0, (45, 25): 0, (45, 26): 0, (45, 27): 0, (45, 28): 0, (45, 29): 0, (45, 30): 0, (45, 31): 0, (45, 32): 0, (45, 33): 0, (45, 34): 0, (45, 35): 0, (45, 36): 0, (45, 37): 0, (45, 38): 0, (45, 39): 0, (45, 40): 0, (45, 41): 0, (45, 42): 0, (45, 43): 0, (45, 44): 0, (45, 45): 0, (45, 46): 0, (45, 47): 0, (45, 48): 0, (45, 49): 0, (45, 50): 0, (45, 51): 0, (45, 52): 0, (45, 53): 0, (45, 54): 0, (45, 55): 0, (45, 56): 0, (45, 57): 0, (45, 58): 0, (45, 59): 0, (45, 60): 0, (45, 61): 0, (45, 62): 0, (45, 63): 0, (45, 64): 0, (45, 65): 1, (45, 66): 0, (45, 67): 0, (45, 68): 0, (45, 69): 0, (50, 1): 0, (50, 2): 0, (50, 3): 0, (50, 4): 0, (50, 5): 0, (50, 6): 0, (50, 7): 0, (50, 8): 0, (50, 9): 0, (50, 10): 0, (50, 11): 0, (50, 12): 0, (50, 13): 0, (50, 14): 0, (50, 15): 0, (50, 16): 0, (50, 17): 0, (50, 18): 0, (50, 19): 0, (50, 20): 0, (50, 21): 0, (50, 22): 0, (50, 23): 0, (50, 24): 0, (50, 25): 0, (50, 26): 0, (50, 27): 0, (50, 28): 0, (50, 29): 0, (50, 30): 0, (50, 31): 0, (50, 32): 0, (50, 33): 0, (50, 34): 0, (50, 35): 0, (50, 36): 0, (50, 37): 0, (50, 38): 0, (50, 39): 0, (50, 40): 0, (50, 41): 0, (50, 42): 0, (50, 43): 0, (50, 44): 0, (50, 45): 0, (50, 46): 0, (50, 47): 0, (50, 48): 0, (50, 49): 0, (50, 50): 0, (50, 51): 0, (50, 52): 0, (50, 53): 0, (50, 54): 0, (50, 55): 0, (50, 56): 0, (50, 57): 0, (50, 58): 0, (50, 59): 0, (50, 60): 0, (50, 61): 0, (50, 62): 0, (50, 63): 0, (50, 64): 0, (50, 65): 0, (50, 66): 0, (50, 67): 1, (50, 68): 0, (50, 69): 0, (53, 1): 0, (53, 2): 0, (53, 3): 0, (53, 4): 0, (53, 5): 0, (53, 6): 0, (53, 7): 0, (53, 8): 0, (53, 9): 0, (53, 10): 0, (53, 11): 0, (53, 12): 0, (53, 13): 0, (53, 14): 0, (53, 15): 0, (53, 16): 0, (53, 17): 0, (53, 18): 0, (53, 19): 0, (53, 20): 0, (53, 21): 0, (53, 22): 0, (53, 23): 0, (53, 24): 0, (53, 25): 0, (53, 26): 0, (53, 27): 0, (53, 28): 0, (53, 29): 0, (53, 30): 0, (53, 31): 0, (53, 32): 0, (53, 33): 0, (53, 34): 0, (53, 35): 0, (53, 36): 0, (53, 37): 0, (53, 38): 0, (53, 39): 0, (53, 40): 0, (53, 41): 0, (53, 42): 0, (53, 43): 0, (53, 44): 0, (53, 45): 0, (53, 46): 0, (53, 47): 0, (53, 48): 0, (53, 49): 0, (53, 50): 0, (53, 51): 0, (53, 52): 0, (53, 53): 0, (53, 54): 0, (53, 55): 0, (53, 56): 0, (53, 57): 0, (53, 58): 1, (53, 59): 0, (53, 60): 0, (53, 61): 0, (53, 62): 0, (53, 63): 0, (53, 64): 0, (53, 65): 0, (53, 66): 0, (53, 67): 0, (53, 68): 0, (53, 69): 0, (54, 1): 0, (54, 2): 0, (54, 3): 0, (54, 4): 0, (54, 5): 0, (54, 6): 0, (54, 7): 0, (54, 8): 0, (54, 9): 0, (54, 10): 0, (54, 11): 0, (54, 12): 0, (54, 13): 0, (54, 14): 0, (54, 15): 0, (54, 16): 0, (54, 17): 0, (54, 18): 0, (54, 19): 0, (54, 20): 0, (54, 21): 0, (54, 22): 0, (54, 23): 0, (54, 24): 0, (54, 25): 0, (54, 26): 0, (54, 27): 0, (54, 28): 0, (54, 29): 0, (54, 30): 0, (54, 31): 0, (54, 32): 0, (54, 33): 0, (54, 34): 0, (54, 35): 0, (54, 36): 0, (54, 37): 0, (54, 38): 0, (54, 39): 0, (54, 40): 0, (54, 41): 0, (54, 42): 0, (54, 43): 0, (54, 44): 0, (54, 45): 0, (54, 46): 0, (54, 47): 0, (54, 48): 0, (54, 49): 0, (54, 50): 0, (54, 51): 0, (54, 52): 0, (54, 53): 0, (54, 54): 0, (54, 55): 1, (54, 56): 0, (54, 57): 0, (54, 58): 0, (54, 59): 0, (54, 60): 0, (54, 61): 0, (54, 62): 0, (54, 63): 0, (54, 64): 0, (54, 65): 0, (54, 66): 0, (54, 67): 0, (54, 68): 0, (54, 69): 0, (55, 1): 0, (55, 2): 0, (55, 3): 0, (55, 4): 0, (55, 5): 0, (55, 6): 0, (55, 7): 0, (55, 8): 0, (55, 9): 0, (55, 10): 0, (55, 11): 0, (55, 12): 0, (55, 13): 0, (55, 14): 0, (55, 15): 0, (55, 16): 0, (55, 17): 0, (55, 18): 0, (55, 19): 0, (55, 20): 0, (55, 21): 0, (55, 22): 0, (55, 23): 0, (55, 24): 0, (55, 25): 0, (55, 26): 0, (55, 27): 0, (55, 28): 0, (55, 29): 0, (55, 30): 0, (55, 31): 0, (55, 32): 0, (55, 33): 0, (55, 34): 0, (55, 35): 0, (55, 36): 0, (55, 37): 0, (55, 38): 0, (55, 39): 0, (55, 40): 0, (55, 41): 0, (55, 42): 0, (55, 43): 0, (55, 44): 0, (55, 45): 0, (55, 46): 0, (55, 47): 0, (55, 48): 0, (55, 49): 0, (55, 50): 0, (55, 51): 0, (55, 52): 0, (55, 53): 0, (55, 54): 0, (55, 55): 0, (55, 56): 0, (55, 57): 0, (55, 58): 0, (55, 59): 0, (55, 60): 0, (55, 61): 0, (55, 62): 0, (55, 63): 0, (55, 64): 0, (55, 65): 0, (55, 66): 0, (55, 67): 0, (55, 68): 0, (55, 69): 1, (56, 1): 0, (56, 2): 0, (56, 3): 0, (56, 4): 0, (56, 5): 0, (56, 6): 0, (56, 7): 0, (56, 8): 0, (56, 9): 0, (56, 10): 0, (56, 11): 0, (56, 12): 0, (56, 13): 0, (56, 14): 0, (56, 15): 0, (56, 16): 0, (56, 17): 0, (56, 18): 0, (56, 19): 0, (56, 20): 0, (56, 21): 0, (56, 22): 0, (56, 23): 0, (56, 24): 0, (56, 25): 0, (56, 26): 0, (56, 27): 0, (56, 28): 0, (56, 29): 0, (56, 30): 0, (56, 31): 0, (56, 32): 0, (56, 33): 0, (56, 34): 0, (56, 35): 0, (56, 36): 0, (56, 37): 0, (56, 38): 0, (56, 39): 0, (56, 40): 0, (56, 41): 0, (56, 42): 0, (56, 43): 0, (56, 44): 0, (56, 45): 0, (56, 46): 0, (56, 47): 0, (56, 48): 0, (56, 49): 0, (56, 50): 0, (56, 51): 0, (56, 52): 0, (56, 53): 0, (56, 54): 0, (56, 55): 0, (56, 56): 0, (56, 57): 0, (56, 58): 0, (56, 59): 0, (56, 60): 0, (56, 61): 0, (56, 62): 1, (56, 63): 0, (56, 64): 0, (56, 65): 0, (56, 66): 0, (56, 67): 0, (56, 68): 0, (56, 69): 0, (58, 1): 0, (58, 2): 0, (58, 3): 0, (58, 4): 0, (58, 5): 0, (58, 6): 0, (58, 7): 0, (58, 8): 0, (58, 9): 0, (58, 10): 0, (58, 11): 0, (58, 12): 0, (58, 13): 0, (58, 14): 0, (58, 15): 0, (58, 16): 0, (58, 17): 0, (58, 18): 0, (58, 19): 0, (58, 20): 0, (58, 21): 0, (58, 22): 0, (58, 23): 0, (58, 24): 0, (58, 25): 0, (58, 26): 0, (58, 27): 0, (58, 28): 0, (58, 29): 0, (58, 30): 0, (58, 31): 0, (58, 32): 0, (58, 33): 0, (58, 34): 0, (58, 35): 0, (58, 36): 0, (58, 37): 0, (58, 38): 0, (58, 39): 0, (58, 40): 0, (58, 41): 0, (58, 42): 0, (58, 43): 0, (58, 44): 0, (58, 45): 0, (58, 46): 0, (58, 47): 0, (58, 48): 0, (58, 49): 0, (58, 50): 0, (58, 51): 0, (58, 52): 0, (58, 53): 0, (58, 54): 0, (58, 55): 0, (58, 56): 0, (58, 57): 0, (58, 58): 0, (58, 59): 0, (58, 60): 0, (58, 61): 0, (58, 62): 1, (58, 63): 0, (58, 64): 0, (58, 65): 0, (58, 66): 0, (58, 67): 0, (58, 68): 0, (58, 69): 0, (61, 1): 0, (61, 2): 0, (61, 3): 0, (61, 4): 0, (61, 5): 0, (61, 6): 0, (61, 7): 0, (61, 8): 0, (61, 9): 0, (61, 10): 0, (61, 11): 0, (61, 12): 0, (61, 13): 0, (61, 14): 0, (61, 15): 0, (61, 16): 0, (61, 17): 0, (61, 18): 0, (61, 19): 0, (61, 20): 0, (61, 21): 0, (61, 22): 0, (61, 23): 0, (61, 24): 0, (61, 25): 0, (61, 26): 0, (61, 27): 0, (61, 28): 0, (61, 29): 0, (61, 30): 0, (61, 31): 0, (61, 32): 0, (61, 33): 0, (61, 34): 0, (61, 35): 0, (61, 36): 0, (61, 37): 0, (61, 38): 0, (61, 39): 0, (61, 40): 0, (61, 41): 0, (61, 42): 1, (61, 43): 0, (61, 44): 0, (61, 45): 0, (61, 46): 0, (61, 47): 0, (61, 48): 0, (61, 49): 0, (61, 50): 0, (61, 51): 0, (61, 52): 0, (61, 53): 0, (61, 54): 0, (61, 55): 0, (61, 56): 0, (61, 57): 0, (61, 58): 0, (61, 59): 0, (61, 60): 0, (61, 61): 0, (61, 62): 0, (61, 63): 0, (61, 64): 0, (61, 65): 0, (61, 66): 0, (61, 67): 0, (61, 68): 0, (61, 69): 0, (62, 1): 0, (62, 2): 0, (62, 3): 0, (62, 4): 0, (62, 5): 0, (62, 6): 0, (62, 7): 0, (62, 8): 0, (62, 9): 0, (62, 10): 0, (62, 11): 0, (62, 12): 0, (62, 13): 0, (62, 14): 0, (62, 15): 0, (62, 16): 0, (62, 17): 0, (62, 18): 0, (62, 19): 0, (62, 20): 0, (62, 21): 0, (62, 22): 0, (62, 23): 0, (62, 24): 0, (62, 25): 0, (62, 26): 0, (62, 27): 0, (62, 28): 0, (62, 29): 0, (62, 30): 0, (62, 31): 0, (62, 32): 0, (62, 33): 0, (62, 34): 0, (62, 35): 0, (62, 36): 0, (62, 37): 0, (62, 38): 0, (62, 39): 0, (62, 40): 0, (62, 41): 0, (62, 42): 0, (62, 43): 0, (62, 44): 0, (62, 45): 0, (62, 46): 0, (62, 47): 0, (62, 48): 0, (62, 49): 0, (62, 50): 0, (62, 51): 0, (62, 52): 0, (62, 53): 0, (62, 54): 1, (62, 55): 0, (62, 56): 0, (62, 57): 0, (62, 58): 0, (62, 59): 0, (62, 60): 0, (62, 61): 0, (62, 62): 0, (62, 63): 0, (62, 64): 0, (62, 65): 0, (62, 66): 0, (62, 67): 0, (62, 68): 0, (62, 69): 0, (64, 1): 0, (64, 2): 0, (64, 3): 0, (64, 4): 0, (64, 5): 0, (64, 6): 0, (64, 7): 0, (64, 8): 0, (64, 9): 0, (64, 10): 0, (64, 11): 0, (64, 12): 0, (64, 13): 0, (64, 14): 0, (64, 15): 0, (64, 16): 0, (64, 17): 0, (64, 18): 0, (64, 19): 0, (64, 20): 0, (64, 21): 0, (64, 22): 0, (64, 23): 0, (64, 24): 0, (64, 25): 0, (64, 26): 0, (64, 27): 0, (64, 28): 0, (64, 29): 0, (64, 30): 0, (64, 31): 0, (64, 32): 0, (64, 33): 0, (64, 34): 0, (64, 35): 0, (64, 36): 0, (64, 37): 0, (64, 38): 0, (64, 39): 0, (64, 40): 0, (64, 41): 0, (64, 42): 0, (64, 43): 0, (64, 44): 0, (64, 45): 0, (64, 46): 0, (64, 47): 0, (64, 48): 0, (64, 49): 1, (64, 50): 0, (64, 51): 0, (64, 52): 0, (64, 53): 0, (64, 54): 0, (64, 55): 0, (64, 56): 0, (64, 57): 0, (64, 58): 0, (64, 59): 0, (64, 60): 0, (64, 61): 0, (64, 62): 0, (64, 63): 0, (64, 64): 0, (64, 65): 0, (64, 66): 0, (64, 67): 0, (64, 68): 0, (64, 69): 0, (66, 1): 0, (66, 2): 0, (66, 3): 0, (66, 4): 0, (66, 5): 0, (66, 6): 0, (66, 7): 0, (66, 8): 0, (66, 9): 0, (66, 10): 0, (66, 11): 0, (66, 12): 0, (66, 13): 0, (66, 14): 0, (66, 15): 0, (66, 16): 0, (66, 17): 0, (66, 18): 0, (66, 19): 0, (66, 20): 0, (66, 21): 0, (66, 22): 0, (66, 23): 0, (66, 24): 0, (66, 25): 0, (66, 26): 0, (66, 27): 0, (66, 28): 0, (66, 29): 0, (66, 30): 0, (66, 31): 0, (66, 32): 0, (66, 33): 0, (66, 34): 0, (66, 35): 0, (66, 36): 0, (66, 37): 0, (66, 38): 0, (66, 39): 0, (66, 40): 0, (66, 41): 0, (66, 42): 0, (66, 43): 0, (66, 44): 0, (66, 45): 0, (66, 46): 0, (66, 47): 0, (66, 48): 0, (66, 49): 0, (66, 50): 0, (66, 51): 0, (66, 52): 0, (66, 53): 0, (66, 54): 0, (66, 55): 0, (66, 56): 0, (66, 57): 0, (66, 58): 0, (66, 59): 0, (66, 60): 1, (66, 61): 0, (66, 62): 0, (66, 63): 0, (66, 64): 0, (66, 65): 0, (66, 66): 0, (66, 67): 0, (66, 68): 0, (66, 69): 0, (69, 1): 0, (69, 2): 0, (69, 3): 0, (69, 4): 0, (69, 5): 0, (69, 6): 0, (69, 7): 0, (69, 8): 0, (69, 9): 0, (69, 10): 0, (69, 11): 0, (69, 12): 0, (69, 13): 0, (69, 14): 0, (69, 15): 0, (69, 16): 0, (69, 17): 0, (69, 18): 0, (69, 19): 0, (69, 20): 0, (69, 21): 0, (69, 22): 0, (69, 23): 0, (69, 24): 0, (69, 25): 0, (69, 26): 0, (69, 27): 0, (69, 28): 0, (69, 29): 0, (69, 30): 0, (69, 31): 0, (69, 32): 0, (69, 33): 0, (69, 34): 0, (69, 35): 0, (69, 36): 0, (69, 37): 0, (69, 38): 0, (69, 39): 0, (69, 40): 0, (69, 41): 0, (69, 42): 0, (69, 43): 0, (69, 44): 0, (69, 45): 0, (69, 46): 0, (69, 47): 0, (69, 48): 0, (69, 49): 0, (69, 50): 0, (69, 51): 1, (69, 52): 0, (69, 53): 0, (69, 54): 0, (69, 55): 0, (69, 56): 0, (69, 57): 0, (69, 58): 0, (69, 59): 0, (69, 60): 0, (69, 61): 0, (69, 62): 0, (69, 63): 0, (69, 64): 0, (69, 65): 0, (69, 66): 0, (69, 67): 0, (69, 68): 0, (69, 69): 0, (71, 1): 0, (71, 2): 0, (71, 3): 0, (71, 4): 0, (71, 5): 0, (71, 6): 0, (71, 7): 0, (71, 8): 0, (71, 9): 0, (71, 10): 0, (71, 11): 0, (71, 12): 0, (71, 13): 0, (71, 14): 0, (71, 15): 0, (71, 16): 0, (71, 17): 0, (71, 18): 0, (71, 19): 0, (71, 20): 0, (71, 21): 0, (71, 22): 0, (71, 23): 0, (71, 24): 0, (71, 25): 0, (71, 26): 0, (71, 27): 0, (71, 28): 0, (71, 29): 0, (71, 30): 0, (71, 31): 0, (71, 32): 0, (71, 33): 0, (71, 34): 0, (71, 35): 0, (71, 36): 0, (71, 37): 0, (71, 38): 0, (71, 39): 0, (71, 40): 0, (71, 41): 0, (71, 42): 0, (71, 43): 0, (71, 44): 0, (71, 45): 0, (71, 46): 0, (71, 47): 0, (71, 48): 0, (71, 49): 0, (71, 50): 0, (71, 51): 0, (71, 52): 0, (71, 53): 0, (71, 54): 0, (71, 55): 0, (71, 56): 0, (71, 57): 0, (71, 58): 0, (71, 59): 1, (71, 60): 0, (71, 61): 0, (71, 62): 0, (71, 63): 0, (71, 64): 0, (71, 65): 0, (71, 66): 0, (71, 67): 0, (71, 68): 0, (71, 69): 0, (76, 1): 0, (76, 2): 0, (76, 3): 0, (76, 4): 0, (76, 5): 0, (76, 6): 0, (76, 7): 0, (76, 8): 0, (76, 9): 0, (76, 10): 0, (76, 11): 0, (76, 12): 0, (76, 13): 0, (76, 14): 0, (76, 15): 0, (76, 16): 0, (76, 17): 0, (76, 18): 0, (76, 19): 0, (76, 20): 0, (76, 21): 0, (76, 22): 0, (76, 23): 0, (76, 24): 0, (76, 25): 0, (76, 26): 0, (76, 27): 0, (76, 28): 0, (76, 29): 0, (76, 30): 0, (76, 31): 0, (76, 32): 0, (76, 33): 0, (76, 34): 0, (76, 35): 0, (76, 36): 0, (76, 37): 0, (76, 38): 0, (76, 39): 0, (76, 40): 0, (76, 41): 0, (76, 42): 0, (76, 43): 0, (76, 44): 0, (76, 45): 0, (76, 46): 0, (76, 47): 0, (76, 48): 0, (76, 49): 0, (76, 50): 0, (76, 51): 0, (76, 52): 0, (76, 53): 0, (76, 54): 0, (76, 55): 0, (76, 56): 0, (76, 57): 0, (76, 58): 0, (76, 59): 0, (76, 60): 1, (76, 61): 0, (76, 62): 0, (76, 63): 0, (76, 64): 0, (76, 65): 0, (76, 66): 0, (76, 67): 0, (76, 68): 0, (76, 69): 0, (77, 1): 0, (77, 2): 0, (77, 3): 0, (77, 4): 0, (77, 5): 0, (77, 6): 0, (77, 7): 0, (77, 8): 0, (77, 9): 0, (77, 10): 0, (77, 11): 0, (77, 12): 0, (77, 13): 0, (77, 14): 0, (77, 15): 0, (77, 16): 0, (77, 17): 0, (77, 18): 0, (77, 19): 0, (77, 20): 0, (77, 21): 0, (77, 22): 0, (77, 23): 0, (77, 24): 0, (77, 25): 0, (77, 26): 0, (77, 27): 0, (77, 28): 0, (77, 29): 0, (77, 30): 0, (77, 31): 0, (77, 32): 0, (77, 33): 0, (77, 34): 0, (77, 35): 0, (77, 36): 0, (77, 37): 0, (77, 38): 0, (77, 39): 0, (77, 40): 0, (77, 41): 0, (77, 42): 0, (77, 43): 0, (77, 44): 1, (77, 45): 0, (77, 46): 0, (77, 47): 0, (77, 48): 0, (77, 49): 0, (77, 50): 0, (77, 51): 0, (77, 52): 0, (77, 53): 0, (77, 54): 0, (77, 55): 0, (77, 56): 0, (77, 57): 0, (77, 58): 0, (77, 59): 0, (77, 60): 0, (77, 61): 0, (77, 62): 0, (77, 63): 0, (77, 64): 0, (77, 65): 0, (77, 66): 0, (77, 67): 0, (77, 68): 0, (77, 69): 0, (78, 1): 0, (78, 2): 0, (78, 3): 0, (78, 4): 0, (78, 5): 0, (78, 6): 0, (78, 7): 0, (78, 8): 0, (78, 9): 0, (78, 10): 0, (78, 11): 0, (78, 12): 0, (78, 13): 0, (78, 14): 0, (78, 15): 0, (78, 16): 0, (78, 17): 0, (78, 18): 0, (78, 19): 0, (78, 20): 0, (78, 21): 0, (78, 22): 0, (78, 23): 0, (78, 24): 0, (78, 25): 0, (78, 26): 0, (78, 27): 0, (78, 28): 0, (78, 29): 0, (78, 30): 0, (78, 31): 0, (78, 32): 0, (78, 33): 0, (78, 34): 0, (78, 35): 0, (78, 36): 0, (78, 37): 0, (78, 38): 0, (78, 39): 0, (78, 40): 0, (78, 41): 0, (78, 42): 0, (78, 43): 1, (78, 44): 0, (78, 45): 0, (78, 46): 0, (78, 47): 0, (78, 48): 0, (78, 49): 0, (78, 50): 0, (78, 51): 0, (78, 52): 0, (78, 53): 0, (78, 54): 0, (78, 55): 0, (78, 56): 0, (78, 57): 0, (78, 58): 0, (78, 59): 0, (78, 60): 0, (78, 61): 0, (78, 62): 0, (78, 63): 0, (78, 64): 0, (78, 65): 0, (78, 66): 0, (78, 67): 0, (78, 68): 0, (78, 69): 0, (80, 1): 0, (80, 2): 0, (80, 3): 0, (80, 4): 0, (80, 5): 0, (80, 6): 0, (80, 7): 0, (80, 8): 0, (80, 9): 0, (80, 10): 0, (80, 11): 0, (80, 12): 0, (80, 13): 0, (80, 14): 0, (80, 15): 0, (80, 16): 0, (80, 17): 0, (80, 18): 0, (80, 19): 0, (80, 20): 0, (80, 21): 0, (80, 22): 0, (80, 23): 0, (80, 24): 0, (80, 25): 0, (80, 26): 0, (80, 27): 0, (80, 28): 0, (80, 29): 0, (80, 30): 0, (80, 31): 0, (80, 32): 0, (80, 33): 0, (80, 34): 0, (80, 35): 0, (80, 36): 0, (80, 37): 0, (80, 38): 0, (80, 39): 0, (80, 40): 0, (80, 41): 0, (80, 42): 0, (80, 43): 0, (80, 44): 0, (80, 45): 0, (80, 46): 0, (80, 47): 0, (80, 48): 0, (80, 49): 0, (80, 50): 0, (80, 51): 0, (80, 52): 0, (80, 53): 0, (80, 54): 0, (80, 55): 0, (80, 56): 0, (80, 57): 0, (80, 58): 0, (80, 59): 0, (80, 60): 0, (80, 61): 0, (80, 62): 0, (80, 63): 0, (80, 64): 0, (80, 65): 0, (80, 66): 0, (80, 67): 1, (80, 68): 0, (80, 69): 0, (81, 1): 0, (81, 2): 0, (81, 3): 0, (81, 4): 0, (81, 5): 0, (81, 6): 0, (81, 7): 0, (81, 8): 0, (81, 9): 0, (81, 10): 0, (81, 11): 0, (81, 12): 0, (81, 13): 0, (81, 14): 0, (81, 15): 0, (81, 16): 0, (81, 17): 0, (81, 18): 0, (81, 19): 0, (81, 20): 0, (81, 21): 0, (81, 22): 0, (81, 23): 0, (81, 24): 0, (81, 25): 0, (81, 26): 0, (81, 27): 0, (81, 28): 0, (81, 29): 0, (81, 30): 0, (81, 31): 0, (81, 32): 0, (81, 33): 0, (81, 34): 0, (81, 35): 0, (81, 36): 0, (81, 37): 0, (81, 38): 0, (81, 39): 0, (81, 40): 0, (81, 41): 0, (81, 42): 0, (81, 43): 0, (81, 44): 0, (81, 45): 0, (81, 46): 0, (81, 47): 0, (81, 48): 0, (81, 49): 0, (81, 50): 0, (81, 51): 0, (81, 52): 0, (81, 53): 0, (81, 54): 0, (81, 55): 0, (81, 56): 0, (81, 57): 0, (81, 58): 0, (81, 59): 0, (81, 60): 0, (81, 61): 0, (81, 62): 0, (81, 63): 0, (81, 64): 0, (81, 65): 1, (81, 66): 0, (81, 67): 0, (81, 68): 0, (81, 69): 0, (83, 1): 0, (83, 2): 0, (83, 3): 0, (83, 4): 0, (83, 5): 0, (83, 6): 0, (83, 7): 0, (83, 8): 0, (83, 9): 0, (83, 10): 0, (83, 11): 0, (83, 12): 0, (83, 13): 0, (83, 14): 0, (83, 15): 0, (83, 16): 0, (83, 17): 0, (83, 18): 0, (83, 19): 0, (83, 20): 0, (83, 21): 0, (83, 22): 0, (83, 23): 0, (83, 24): 0, (83, 25): 0, (83, 26): 0, (83, 27): 0, (83, 28): 0, (83, 29): 0, (83, 30): 0, (83, 31): 0, (83, 32): 0, (83, 33): 0, (83, 34): 0, (83, 35): 0, (83, 36): 0, (83, 37): 0, (83, 38): 0, (83, 39): 0, (83, 40): 0, (83, 41): 0, (83, 42): 0, (83, 43): 0, (83, 44): 0, (83, 45): 0, (83, 46): 0, (83, 47): 0, (83, 48): 0, (83, 49): 0, (83, 50): 0, (83, 51): 0, (83, 52): 0, (83, 53): 0, (83, 54): 0, (83, 55): 0, (83, 56): 0, (83, 57): 1, (83, 58): 0, (83, 59): 0, (83, 60): 0, (83, 61): 0, (83, 62): 0, (83, 63): 0, (83, 64): 0, (83, 65): 0, (83, 66): 0, (83, 67): 0, (83, 68): 0, (83, 69): 0, (85, 1): 0, (85, 2): 0, (85, 3): 0, (85, 4): 0, (85, 5): 0, (85, 6): 0, (85, 7): 0, (85, 8): 0, (85, 9): 0, (85, 10): 0, (85, 11): 0, (85, 12): 0, (85, 13): 0, (85, 14): 0, (85, 15): 0, (85, 16): 0, (85, 17): 0, (85, 18): 0, (85, 19): 0, (85, 20): 0, (85, 21): 0, (85, 22): 0, (85, 23): 0, (85, 24): 0, (85, 25): 0, (85, 26): 0, (85, 27): 0, (85, 28): 0, (85, 29): 0, (85, 30): 0, (85, 31): 0, (85, 32): 0, (85, 33): 0, (85, 34): 0, (85, 35): 0, (85, 36): 0, (85, 37): 0, (85, 38): 0, (85, 39): 0, (85, 40): 0, (85, 41): 0, (85, 42): 0, (85, 43): 0, (85, 44): 0, (85, 45): 0, (85, 46): 0, (85, 47): 0, (85, 48): 0, (85, 49): 0, (85, 50): 0, (85, 51): 0, (85, 52): 0, (85, 53): 0, (85, 54): 0, (85, 55): 0, (85, 56): 0, (85, 57): 0, (85, 58): 0, (85, 59): 0, (85, 60): 0, (85, 61): 1, (85, 62): 0, (85, 63): 0, (85, 64): 0, (85, 65): 0, (85, 66): 0, (85, 67): 0, (85, 68): 0, (85, 69): 0, (90, 1): 0, (90, 2): 0, (90, 3): 0, (90, 4): 0, (90, 5): 0, (90, 6): 0, (90, 7): 0, (90, 8): 0, (90, 9): 0, (90, 10): 0, (90, 11): 0, (90, 12): 0, (90, 13): 0, (90, 14): 0, (90, 15): 0, (90, 16): 0, (90, 17): 0, (90, 18): 0, (90, 19): 0, (90, 20): 0, (90, 21): 0, (90, 22): 0, (90, 23): 0, (90, 24): 0, (90, 25): 0, (90, 26): 0, (90, 27): 0, (90, 28): 0, (90, 29): 0, (90, 30): 0, (90, 31): 0, (90, 32): 0, (90, 33): 0, (90, 34): 0, (90, 35): 0, (90, 36): 0, (90, 37): 0, (90, 38): 0, (90, 39): 0, (90, 40): 0, (90, 41): 0, (90, 42): 0, (90, 43): 0, (90, 44): 0, (90, 45): 0, (90, 46): 0, (90, 47): 0, (90, 48): 0, (90, 49): 0, (90, 50): 0, (90, 51): 0, (90, 52): 0, (90, 53): 0, (90, 54): 0, (90, 55): 0, (90, 56): 0, (90, 57): 0, (90, 58): 0, (90, 59): 0, (90, 60): 0, (90, 61): 0, (90, 62): 0, (90, 63): 0, (90, 64): 0, (90, 65): 0, (90, 66): 0, (90, 67): 0, (90, 68): 0, (90, 69): 1, (91, 1): 0, (91, 2): 0, (91, 3): 0, (91, 4): 0, (91, 5): 0, (91, 6): 0, (91, 7): 0, (91, 8): 0, (91, 9): 0, (91, 10): 0, (91, 11): 0, (91, 12): 0, (91, 13): 0, (91, 14): 0, (91, 15): 0, (91, 16): 0, (91, 17): 0, (91, 18): 0, (91, 19): 0, (91, 20): 0, (91, 21): 0, (91, 22): 0, (91, 23): 0, (91, 24): 0, (91, 25): 0, (91, 26): 0, (91, 27): 0, (91, 28): 0, (91, 29): 0, (91, 30): 0, (91, 31): 0, (91, 32): 0, (91, 33): 0, (91, 34): 0, (91, 35): 0, (91, 36): 0, (91, 37): 0, (91, 38): 0, (91, 39): 0, (91, 40): 0, (91, 41): 0, (91, 42): 0, (91, 43): 0, (91, 44): 0, (91, 45): 0, (91, 46): 0, (91, 47): 0, (91, 48): 0, (91, 49): 0, (91, 50): 0, (91, 51): 0, (91, 52): 0, (91, 53): 0, (91, 54): 0, (91, 55): 0, (91, 56): 0, (91, 57): 0, (91, 58): 0, (91, 59): 0, (91, 60): 0, (91, 61): 0, (91, 62): 0, (91, 63): 1, (91, 64): 0, (91, 65): 0, (91, 66): 0, (91, 67): 0, (91, 68): 0, (91, 69): 0, (93, 1): 0, (93, 2): 0, (93, 3): 0, (93, 4): 0, (93, 5): 0, (93, 6): 0, (93, 7): 0, (93, 8): 0, (93, 9): 0, (93, 10): 0, (93, 11): 0, (93, 12): 0, (93, 13): 0, (93, 14): 0, (93, 15): 0, (93, 16): 0, (93, 17): 0, (93, 18): 0, (93, 19): 0, (93, 20): 0, (93, 21): 0, (93, 22): 0, (93, 23): 0, (93, 24): 0, (93, 25): 0, (93, 26): 0, (93, 27): 0, (93, 28): 0, (93, 29): 0, (93, 30): 0, (93, 31): 0, (93, 32): 0, (93, 33): 0, (93, 34): 0, (93, 35): 0, (93, 36): 0, (93, 37): 0, (93, 38): 0, (93, 39): 0, (93, 40): 0, (93, 41): 0, (93, 42): 0, (93, 43): 0, (93, 44): 0, (93, 45): 0, (93, 46): 1, (93, 47): 0, (93, 48): 0, (93, 49): 0, (93, 50): 0, (93, 51): 0, (93, 52): 0, (93, 53): 0, (93, 54): 0, (93, 55): 0, (93, 56): 0, (93, 57): 0, (93, 58): 0, (93, 59): 0, (93, 60): 0, (93, 61): 0, (93, 62): 0, (93, 63): 0, (93, 64): 0, (93, 65): 0, (93, 66): 0, (93, 67): 0, (93, 68): 0, (93, 69): 0, (103, 1): 0, (103, 2): 0, (103, 3): 0, (103, 4): 0, (103, 5): 0, (103, 6): 0, (103, 7): 0, (103, 8): 0, (103, 9): 0, (103, 10): 0, (103, 11): 0, (103, 12): 0, (103, 13): 0, (103, 14): 0, (103, 15): 0, (103, 16): 0, (103, 17): 0, (103, 18): 0, (103, 19): 0, (103, 20): 0, (103, 21): 0, (103, 22): 0, (103, 23): 0, (103, 24): 0, (103, 25): 0, (103, 26): 0, (103, 27): 0, (103, 28): 0, (103, 29): 0, (103, 30): 0, (103, 31): 0, (103, 32): 0, (103, 33): 0, (103, 34): 0, (103, 35): 0, (103, 36): 0, (103, 37): 0, (103, 38): 0, (103, 39): 0, (103, 40): 0, (103, 41): 0, (103, 42): 0, (103, 43): 0, (103, 44): 0, (103, 45): 0, (103, 46): 0, (103, 47): 0, (103, 48): 0, (103, 49): 0, (103, 50): 0, (103, 51): 0, (103, 52): 0, (103, 53): 0, (103, 54): 0, (103, 55): 0, (103, 56): 0, (103, 57): 0, (103, 58): 0, (103, 59): 0, (103, 60): 0, (103, 61): 0, (103, 62): 1, (103, 63): 0, (103, 64): 0, (103, 65): 0, (103, 66): 0, (103, 67): 0, (103, 68): 0, (103, 69): 0, (105, 1): 0, (105, 2): 0, (105, 3): 0, (105, 4): 0, (105, 5): 0, (105, 6): 0, (105, 7): 0, (105, 8): 0, (105, 9): 0, </t>
+  </si>
+  <si>
+    <t>{(3, 1): 0, (3, 2): 0, (3, 3): 0, (3, 4): 0, (4, 1): 0, (4, 2): 0, (4, 3): 0, (4, 4): 0, (8, 1): 0, (8, 2): 0, (8, 3): 0, (8, 4): 0, (9, 1): 0, (9, 2): 0, (9, 3): 0, (9, 4): 0, (10, 1): 0, (10, 2): 0, (10, 3): 0, (10, 4): 0, (11, 1): 0, (11, 2): 0, (11, 3): 0, (11, 4): 0, (12, 1): 0, (12, 2): 0, (12, 3): 0, (12, 4): 0, (21, 1): 0, (21, 2): 0, (21, 3): 0, (21, 4): 0, (23, 1): 0, (23, 2): 0, (23, 3): 0, (23, 4): 0, (24, 1): 0, (24, 2): 0, (24, 3): 0, (24, 4): 0, (29, 1): 0, (29, 2): 0, (29, 3): 0, (29, 4): 0, (31, 1): 0, (31, 2): 0, (31, 3): 0, (31, 4): 0, (33, 1): 0, (33, 2): 0, (33, 3): 0, (33, 4): 0, (45, 1): 0, (45, 2): 0, (45, 3): 0, (45, 4): 0, (50, 1): 0, (50, 2): 0, (50, 3): 0, (50, 4): 0, (53, 1): 0, (53, 2): 0, (53, 3): 0, (53, 4): 0, (54, 1): 0, (54, 2): 0, (54, 3): 0, (54, 4): 0, (55, 1): 0, (55, 2): 0, (55, 3): 0, (55, 4): 0, (56, 1): 0, (56, 2): 0, (56, 3): 0, (56, 4): 0, (58, 1): 0, (58, 2): 0, (58, 3): 0, (58, 4): 0, (61, 1): 0, (61, 2): 0, (61, 3): 0, (61, 4): 0, (62, 1): 0, (62, 2): 0, (62, 3): 0, (62, 4): 0, (64, 1): 0, (64, 2): 0, (64, 3): 0, (64, 4): 0, (66, 1): 0, (66, 2): 0, (66, 3): 0, (66, 4): 0, (69, 1): 0, (69, 2): 0, (69, 3): 0, (69, 4): 0, (71, 1): 0, (71, 2): 0, (71, 3): 0, (71, 4): 0, (76, 1): 0, (76, 2): 0, (76, 3): 0, (76, 4): 0, (77, 1): 0, (77, 2): 0, (77, 3): 0, (77, 4): 0, (78, 1): 0, (78, 2): 0, (78, 3): 0, (78, 4): 0, (80, 1): 0, (80, 2): 0, (80, 3): 0, (80, 4): 0, (81, 1): 0, (81, 2): 0, (81, 3): 0, (81, 4): 0, (83, 1): 0, (83, 2): 0, (83, 3): 0, (83, 4): 0, (85, 1): 0, (85, 2): 0, (85, 3): 0, (85, 4): 0, (90, 1): 0, (90, 2): 0, (90, 3): 0, (90, 4): 0, (91, 1): 0, (91, 2): 0, (91, 3): 0, (91, 4): 0, (93, 1): 0, (93, 2): 0, (93, 3): 0, (93, 4): 0, (103, 1): 0, (103, 2): 0, (103, 3): 0, (103, 4): 0, (105, 1): 0, (105, 2): 0, (105, 3): 0, (105, 4): 0, (114, 1): 0, (114, 2): 0, (114, 3): 0, (114, 4): 0, (119, 1): 0, (119, 2): 0, (119, 3): 0, (119, 4): 0, (126, 1): 0, (126, 2): 0, (126, 3): 0, (126, 4): 0, (127, 1): 0, (127, 2): 0, (127, 3): 0, (127, 4): 0, (128, 1): 0, (128, 2): 0, (128, 3): 0, (128, 4): 0, (132, 1): 0, (132, 2): 0, (132, 3): 0, (132, 4): 0}</t>
   </si>
 </sst>
 </file>
@@ -836,10 +851,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:DT2"/>
+  <dimension ref="A1:DY2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:124">
+    <row r="1" spans="1:129">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1212,369 +1227,396 @@
       <c r="DT1" s="1" t="s">
         <v>123</v>
       </c>
+      <c r="DU1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="DV1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="DW1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="DX1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="DY1" s="1" t="s">
+        <v>128</v>
+      </c>
     </row>
-    <row r="2" spans="1:124">
+    <row r="2" spans="1:129">
       <c r="A2">
-        <v>13</v>
+        <v>133</v>
       </c>
       <c r="B2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D2">
+        <v>130</v>
+      </c>
+      <c r="D2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E2">
         <v>0.02</v>
-      </c>
-      <c r="E2">
-        <v>0.01</v>
       </c>
       <c r="F2">
         <v>0.01</v>
       </c>
       <c r="G2">
+        <v>0.01</v>
+      </c>
+      <c r="H2">
         <v>2</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>5</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>2</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>6</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>1</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>4</v>
       </c>
-      <c r="M2">
-        <v>3</v>
-      </c>
       <c r="N2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O2">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="P2">
-        <v>21</v>
+        <v>403</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>403</v>
       </c>
       <c r="R2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>403</v>
       </c>
       <c r="T2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>5</v>
-      </c>
-      <c r="V2" t="s">
-        <v>126</v>
-      </c>
-      <c r="W2" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V2">
+        <v>6</v>
+      </c>
+      <c r="W2" t="s">
+        <v>132</v>
       </c>
       <c r="X2" t="b">
         <v>1</v>
       </c>
-      <c r="Y2">
+      <c r="Y2" t="b">
         <v>1</v>
       </c>
       <c r="Z2">
-        <v>3.052764177322388</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>0.04080820083618164</v>
+        <v>20.37765693664551</v>
       </c>
       <c r="AB2">
-        <v>2.771916627883911</v>
+        <v>0.105273962020874</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>19.93135619163513</v>
       </c>
       <c r="AD2">
-        <v>2.662731885910034</v>
+        <v>0</v>
       </c>
       <c r="AE2">
-        <v>0</v>
-      </c>
-      <c r="AG2">
-        <v>0.2400393486022949</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>127</v>
-      </c>
-      <c r="AI2">
-        <v>44</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>128</v>
+        <v>20.3570339679718</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0.341026782989502</v>
+      </c>
+      <c r="AJ2">
+        <v>88</v>
       </c>
       <c r="AK2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="AL2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="AM2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AN2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AO2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="AP2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="AQ2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="AR2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="AS2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AT2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AU2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="AV2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="AW2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="AX2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="AY2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="AZ2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="BA2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="BB2" t="s">
+        <v>150</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>151</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>152</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>153</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>154</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>155</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>156</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>157</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>159</v>
+      </c>
+      <c r="BL2">
+        <v>328</v>
+      </c>
+      <c r="BM2">
+        <v>4</v>
+      </c>
+      <c r="BN2">
+        <v>332</v>
+      </c>
+      <c r="BO2">
+        <v>1.204819277108434</v>
+      </c>
+      <c r="BP2">
+        <v>98.79518072289156</v>
+      </c>
+      <c r="BQ2">
+        <v>82</v>
+      </c>
+      <c r="BR2">
+        <v>114</v>
+      </c>
+      <c r="BS2">
+        <v>436</v>
+      </c>
+      <c r="BT2">
+        <v>0.03443864749955457</v>
+      </c>
+      <c r="BU2">
+        <v>0</v>
+      </c>
+      <c r="BV2">
+        <v>0.5053228776076787</v>
+      </c>
+      <c r="BX2">
+        <v>0</v>
+      </c>
+      <c r="BY2">
+        <v>0.5075500204164625</v>
+      </c>
+      <c r="BZ2">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="CA2">
+        <v>1</v>
+      </c>
+      <c r="CB2">
+        <v>41</v>
+      </c>
+      <c r="CC2">
+        <v>0.9318181818181818</v>
+      </c>
+      <c r="CD2">
+        <v>4</v>
+      </c>
+      <c r="CE2">
+        <v>18</v>
+      </c>
+      <c r="CF2">
+        <v>16.75</v>
+      </c>
+      <c r="CG2">
+        <v>0</v>
+      </c>
+      <c r="CH2">
+        <v>11</v>
+      </c>
+      <c r="CI2">
+        <v>8.181818181818182</v>
+      </c>
+      <c r="CJ2">
+        <v>7.454545454545454</v>
+      </c>
+      <c r="CK2">
+        <v>1.176470588235294</v>
+      </c>
+      <c r="CL2">
+        <v>29</v>
+      </c>
+      <c r="CM2">
+        <v>6.413793103448276</v>
+      </c>
+      <c r="CN2">
+        <v>5.896551724137931</v>
+      </c>
+      <c r="CO2">
+        <v>1.714285714285714</v>
+      </c>
+      <c r="CP2" t="s">
         <v>146</v>
       </c>
-      <c r="BC2" t="s">
-        <v>147</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>148</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>149</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>150</v>
-      </c>
-      <c r="BG2" t="s">
-        <v>151</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>152</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>153</v>
-      </c>
-      <c r="BJ2" t="s">
-        <v>154</v>
-      </c>
-      <c r="BK2">
-        <v>19</v>
-      </c>
-      <c r="BL2">
+      <c r="CQ2">
+        <v>1</v>
+      </c>
+      <c r="CR2">
+        <v>0</v>
+      </c>
+      <c r="CS2">
+        <v>254</v>
+      </c>
+      <c r="CT2">
+        <v>0</v>
+      </c>
+      <c r="CU2">
+        <v>254</v>
+      </c>
+      <c r="CV2">
+        <v>0</v>
+      </c>
+      <c r="CW2">
+        <v>100</v>
+      </c>
+      <c r="CX2">
+        <v>63.5</v>
+      </c>
+      <c r="CY2">
+        <v>87</v>
+      </c>
+      <c r="CZ2">
+        <v>512</v>
+      </c>
+      <c r="DA2">
+        <v>0</v>
+      </c>
+      <c r="DB2">
+        <v>0.06887729499910913</v>
+      </c>
+      <c r="DC2">
+        <v>0.5051001633268004</v>
+      </c>
+      <c r="DE2">
+        <v>0</v>
+      </c>
+      <c r="DF2">
+        <v>0</v>
+      </c>
+      <c r="DG2">
+        <v>0</v>
+      </c>
+      <c r="DH2">
+        <v>0</v>
+      </c>
+      <c r="DI2">
+        <v>95</v>
+      </c>
+      <c r="DJ2">
+        <v>2.159090909090909</v>
+      </c>
+      <c r="DK2">
         <v>2</v>
       </c>
-      <c r="BM2">
-        <v>21</v>
-      </c>
-      <c r="BN2">
-        <v>9.523809523809524</v>
-      </c>
-      <c r="BO2">
-        <v>90.47619047619048</v>
-      </c>
-      <c r="BP2">
-        <v>6.333333333333333</v>
-      </c>
-      <c r="BQ2">
-        <v>11</v>
-      </c>
-      <c r="BR2">
-        <v>52</v>
-      </c>
-      <c r="BS2">
-        <v>0</v>
-      </c>
-      <c r="BT2">
-        <v>0</v>
-      </c>
-      <c r="BU2">
-        <v>0.5063250918716313</v>
-      </c>
-      <c r="BW2">
-        <v>0</v>
-      </c>
-      <c r="BX2">
-        <v>0.5075500204164625</v>
-      </c>
-      <c r="BY2">
-        <v>0.5</v>
-      </c>
-      <c r="BZ2">
-        <v>1</v>
-      </c>
-      <c r="CA2">
-        <v>0</v>
-      </c>
-      <c r="CB2">
-        <v>0</v>
-      </c>
-      <c r="CC2">
-        <v>1</v>
-      </c>
-      <c r="CD2">
-        <v>6</v>
-      </c>
-      <c r="CE2">
-        <v>5</v>
-      </c>
-      <c r="CF2">
-        <v>16.66666666666666</v>
-      </c>
-      <c r="CG2">
-        <v>3</v>
-      </c>
-      <c r="CH2">
-        <v>5</v>
-      </c>
-      <c r="CI2">
-        <v>4.666666666666667</v>
-      </c>
-      <c r="CJ2">
-        <v>6.666666666666667</v>
-      </c>
-      <c r="CK2" t="s">
-        <v>141</v>
-      </c>
-      <c r="CL2">
-        <v>1</v>
-      </c>
-      <c r="CM2">
-        <v>0</v>
-      </c>
-      <c r="CN2">
-        <v>233</v>
-      </c>
-      <c r="CO2">
-        <v>0</v>
-      </c>
-      <c r="CP2">
-        <v>233</v>
-      </c>
-      <c r="CQ2">
-        <v>0</v>
-      </c>
-      <c r="CR2">
-        <v>100</v>
-      </c>
-      <c r="CS2">
-        <v>77.66666666666666</v>
-      </c>
-      <c r="CT2">
-        <v>96</v>
-      </c>
-      <c r="CU2">
-        <v>380</v>
-      </c>
-      <c r="CV2">
-        <v>0</v>
-      </c>
-      <c r="CW2">
-        <v>0.07576502449902003</v>
-      </c>
-      <c r="CX2">
-        <v>0.5051001633268003</v>
-      </c>
-      <c r="CZ2">
-        <v>0</v>
-      </c>
-      <c r="DA2">
-        <v>0</v>
-      </c>
-      <c r="DB2">
-        <v>0</v>
-      </c>
-      <c r="DC2">
-        <v>0</v>
-      </c>
-      <c r="DD2">
-        <v>118</v>
-      </c>
-      <c r="DE2">
-        <v>2.95</v>
-      </c>
-      <c r="DF2">
-        <v>3</v>
-      </c>
-      <c r="DG2">
-        <v>19</v>
-      </c>
-      <c r="DH2">
-        <v>19.33333333333333</v>
-      </c>
-      <c r="DI2">
-        <v>0</v>
-      </c>
-      <c r="DJ2">
-        <v>10</v>
-      </c>
-      <c r="DK2">
-        <v>9.699999999999999</v>
-      </c>
       <c r="DL2">
-        <v>8.5</v>
+        <v>14.5</v>
       </c>
       <c r="DM2">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="DN2">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="DO2">
-        <v>7.185185185185185</v>
+        <v>12</v>
       </c>
       <c r="DP2">
-        <v>6.407407407407407</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="DQ2">
-        <v>0</v>
-      </c>
-      <c r="DR2" t="s">
-        <v>141</v>
+        <v>7.833333333333333</v>
+      </c>
+      <c r="DR2">
+        <v>0</v>
       </c>
       <c r="DS2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="DT2">
+        <v>7.4</v>
+      </c>
+      <c r="DU2">
+        <v>6.633333333333334</v>
+      </c>
+      <c r="DV2">
+        <v>0</v>
+      </c>
+      <c r="DW2" t="s">
+        <v>146</v>
+      </c>
+      <c r="DX2">
+        <v>0</v>
+      </c>
+      <c r="DY2">
         <v>0</v>
       </c>
     </row>
